--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F252FDA1-D3E8-42C6-A48D-F44F6A354ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700039E2-141F-40C6-9362-33DADD86C1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4997" uniqueCount="1242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5082" uniqueCount="1281">
   <si>
     <t>Contact</t>
   </si>
@@ -3377,9 +3377,6 @@
     <t>XX</t>
   </si>
   <si>
-    <t>Restaurant en pied d'un batiment autonome dans une zone d'activité</t>
-  </si>
-  <si>
     <t>Date d'ajout</t>
   </si>
   <si>
@@ -3425,9 +3422,6 @@
     <t>23 Avenue des Frères Lumière</t>
   </si>
   <si>
-    <t xml:space="preserve"> Lotissement d'activité économique Castel Les Espaluns, Avenue de l'Université</t>
-  </si>
-  <si>
     <t>330 Avenue Marcou Delanglade</t>
   </si>
   <si>
@@ -3440,9 +3434,6 @@
     <t>14 Rue Serpente</t>
   </si>
   <si>
-    <t>12 Rue Serpente</t>
-  </si>
-  <si>
     <t>Herblay-sur-Seine</t>
   </si>
   <si>
@@ -3473,9 +3464,6 @@
     <t>Aulnoy-lez-Valenciennes</t>
   </si>
   <si>
-    <t>352 Route nationale, Rue des Fusillés de 1940</t>
-  </si>
-  <si>
     <t>Ennetières-en-Weppes</t>
   </si>
   <si>
@@ -3491,12 +3479,6 @@
     <t>Plan de Campagne, Chemin des Pennes CD6</t>
   </si>
   <si>
-    <t>43.439381</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.241938</t>
-  </si>
-  <si>
     <t>43.416553</t>
   </si>
   <si>
@@ -3533,9 +3515,6 @@
     <t>Avant Cap, Barnéoud, Kiabi, La Maison du Convertible, Conforama, SoCooc, …</t>
   </si>
   <si>
-    <t>Local dans l'une des principales zones commerciales de France</t>
-  </si>
-  <si>
     <t>Leclerc Drive, Noz, Monsieur Meuble, Pêche, Action, Electro Dépôt</t>
   </si>
   <si>
@@ -3566,9 +3545,6 @@
     <t xml:space="preserve"> 6.182956</t>
   </si>
   <si>
-    <t>Ancien Five Guys. Emplacement exceptionnel en angle et en cœur de ville de Nancy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mcdonald's, Buger King, Nex Yorker, Lush, restaurants, librairie, bijouterie, </t>
   </si>
   <si>
@@ -3593,9 +3569,6 @@
     <t>7.3127756</t>
   </si>
   <si>
-    <t>Orchestra, Stokomani, Animalis, Action, Jardinerie</t>
-  </si>
-  <si>
     <t>48.255557</t>
   </si>
   <si>
@@ -3605,9 +3578,6 @@
     <t>Basic Fit, Jardinerie, Netto, Carglass</t>
   </si>
   <si>
-    <t>Ancienne La Halle dans une petite zone commerciale et d'habitation</t>
-  </si>
-  <si>
     <t>43.136512</t>
   </si>
   <si>
@@ -3620,9 +3590,6 @@
     <t>Mcdonald's, Chaussea, V&amp;B, Basic Fit, Poltronesofa, Wingstop, Fiveguys</t>
   </si>
   <si>
-    <t>Ancien Casa dans une zone commerciale forte à proximité d'Avenue 83 et Toulon Grand Var</t>
-  </si>
-  <si>
     <t>43.137481</t>
   </si>
   <si>
@@ -3647,21 +3614,12 @@
     <t xml:space="preserve"> 2.531077</t>
   </si>
   <si>
-    <t>48.817952</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.532064</t>
-  </si>
-  <si>
     <t>48.817472</t>
   </si>
   <si>
     <t xml:space="preserve"> 2.531197</t>
   </si>
   <si>
-    <t>Zone commerciale à côté du Leclerc de Champigny. Proximité directe avec les habitations</t>
-  </si>
-  <si>
     <t>Lidl, patisserie, pièce automobile, maison, confodis, entreprises</t>
   </si>
   <si>
@@ -3677,67 +3635,13 @@
     <t>Leroy Merlin, Nike, Alinea, Truffaut, Décathlon, Fnac, Intersport, Action, Animalis, Cuisine</t>
   </si>
   <si>
-    <t>Local situé dans la Patte d'Oie d'Herblay</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/2.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/1.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/2.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/3.jpg</t>
-  </si>
-  <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/39%20-%20Saint-Doulchard/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/39%20-%20Saint-Doulchard/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/39%20-%20Saint-Doulchard/3.jpg</t>
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/41%20-%20Aulnoy-lez-Valenciennes/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/41%20-%20Aulnoy-lez-Valenciennes/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/41%20-%20Aulnoy-lez-Valenciennes/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/41%20-%20Aulnoy-lez-Valenciennes/4.jpg</t>
   </si>
   <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/42%20-%20Enneti%C3%A8res-en-Weppes/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/42%20-%20Enneti%C3%A8res-en-Weppes/2.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/43%20-%20Wittenheim/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/43%20-%20Wittenheim/2.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/44%20-%20Nemours/1.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/2.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.2%20-%20La%20Valette-du-Var/1.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.1%20-%20Champigny-sur-Marne/1.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/46%20-%20Avignon/1.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.2%20-%20Champigny-sur-Marne/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.2%20-%20Champigny-sur-Marne/2.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.3%20-%20Champigny-sur-Marne/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.3%20-%20Champigny-sur-Marne/2.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/2.jpg</t>
-  </si>
-  <si>
-    <t>Ancien KFC à proximité du centre Englos. Local divisible à partir de 150 m².</t>
-  </si>
-  <si>
     <t>Ancien Cuisine Plus à proximité du Carrefour Wittenheim. Local divisible à partir de 300 m².</t>
-  </si>
-  <si>
-    <t>Ancienne boulangerie dans une zone commerciale forte à proximité d'avenue 83 et Toulon Grand Var. Avec terrasse extérieur</t>
-  </si>
-  <si>
-    <t>Ancien Point B (burger) dans une zone commercial à proximité du centre Auchan Mistral 7 au sud d'Avignon. Avec mezzanine et terrasse</t>
   </si>
   <si>
     <t>En face des Machines de l'Île. A proximité du Palais de Justice, et de l'école des Beaux-Arts. Nouvelle construction dans un quartier d'habitation et de bureaux. Gaine à installer. Les charges incluent la taxe foncière</t>
@@ -3772,6 +3676,219 @@
   </si>
   <si>
     <t>MIM</t>
+  </si>
+  <si>
+    <t>10 % du montant de la cession avec un minimum de 15 000 € HT</t>
+  </si>
+  <si>
+    <t>221 €/m² = 40 000 €</t>
+  </si>
+  <si>
+    <t>Restaurant en pied d'un batiment autonome dans une zone d'activité et d'entreprises (22 000 emplois). Proximité de l'A7 et de l'aéroport de Marseille. Baill 6/9/10 ans</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L2A</t>
+  </si>
+  <si>
+    <t>43.439428</t>
+  </si>
+  <si>
+    <t>5.241793</t>
+  </si>
+  <si>
+    <t>36.1</t>
+  </si>
+  <si>
+    <t>36.2</t>
+  </si>
+  <si>
+    <t>Local d'activité/bureau en pied d'un batiment autonome dans une zone d'activité et d'entreprises (22 000 emplois). Proximité de l'A7 et de l'aéroport de Marseille. Baill 6/9/10 ans</t>
+  </si>
+  <si>
+    <t>Local d'activité/bureau en pied d'un batiment autonome dans une zone d'activité et d'entreprises (22 000 emplois). Proximité de l'A7 et de l'aéroport de Marseille. Possibilité de réunir avec le lot L1. Baill 6/9/10 ans</t>
+  </si>
+  <si>
+    <t>150 €/m² = 15 000 €</t>
+  </si>
+  <si>
+    <t>43.439776</t>
+  </si>
+  <si>
+    <t>5.241409</t>
+  </si>
+  <si>
+    <t>95 €/m² = 42 370 €</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>95 €/m² = 54 000 €</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>43.439527</t>
+  </si>
+  <si>
+    <t>5.241554</t>
+  </si>
+  <si>
+    <t>Bureaux</t>
+  </si>
+  <si>
+    <t>195 €/m² = 270 000 €</t>
+  </si>
+  <si>
+    <t>700 + 690</t>
+  </si>
+  <si>
+    <t>Local dans l'une des principales zones commerciales de France (+40M de flux annuel). Environ une cinquantaine de places de parking. Bail 6/9/10 ans. Frais de rédaction d'acte 2 000 €HT</t>
+  </si>
+  <si>
+    <t>90 €/m² = 90 000 €</t>
+  </si>
+  <si>
+    <t>535 €/m² = 240 000 €</t>
+  </si>
+  <si>
+    <t>100 (SS) + 155 + 295</t>
+  </si>
+  <si>
+    <t>Ancien Five Guys. Emplacement exceptionnel en angle et en cœur de ville de Nancy avec 70 m² de terrasse. 16M de flux annuel. Bail 6/9/10 ans</t>
+  </si>
+  <si>
+    <t>5001 Rue des Fusillés de 1940</t>
+  </si>
+  <si>
+    <t>Ancien KFC à proximité du centre Englos : 3ème Auchan de France 220 M€/an. Local divisible à partir de 150 m². Environ 50 places de parking</t>
+  </si>
+  <si>
+    <t>149 €/m² = 139 000 €</t>
+  </si>
+  <si>
+    <t>Boulanger, Cultura, Décathlon, But, Truffaut, Orchestra, Stokomani, Animalis, Action, Jardinerie</t>
+  </si>
+  <si>
+    <t>100 €/m² = 76 000</t>
+  </si>
+  <si>
+    <t>740 + 21</t>
+  </si>
+  <si>
+    <t>Ancienne La Halle dans une petite zone commerciale et d'habitation. Environ 120 places de parking. Local divisible.</t>
+  </si>
+  <si>
+    <t>209 + 67</t>
+  </si>
+  <si>
+    <t>Ancienne boulangerie dans une zone commerciale forte à proximité d'avenue 83 et Toulon Grand Var. Terrasse de 100 m². Bail 6/9/10 ans.</t>
+  </si>
+  <si>
+    <t>83 Avenue de l'Université</t>
+  </si>
+  <si>
+    <t>298 €/m² = 140 000 €</t>
+  </si>
+  <si>
+    <t>Ancien Casa dans une zone commerciale forte à proximité d'Avenue 83 et Toulon Grand Var. Frais de rédaction : 2 000 € HT. Bail 6/9/10 ans.</t>
+  </si>
+  <si>
+    <t>145 €/m² = 90 000 €</t>
+  </si>
+  <si>
+    <t>420 + 196</t>
+  </si>
+  <si>
+    <t>Ancien Point B (burger) dans une zone commercial à proximité du centre Auchan Mistral 7 au sud d'Avignon. 15M de flux annuel. Avec mezzanine et terrasse. Frais de rédaction d'acte : 2 000 € HT. Bail 6/9/10 ans.</t>
+  </si>
+  <si>
+    <t>180 €/m² = 70 000 €</t>
+  </si>
+  <si>
+    <t>48.817272</t>
+  </si>
+  <si>
+    <t>2.532284</t>
+  </si>
+  <si>
+    <t>180 €/m² = 130 000 €</t>
+  </si>
+  <si>
+    <t>375 €/m² = 150 000 €</t>
+  </si>
+  <si>
+    <t>Zone commerciale à côté du Leclerc de Champigny. Proximité directe avec les habitations. Frais de rédaction d'acte : 2 500 € HT. Bail 6/9/10 ans.</t>
+  </si>
+  <si>
+    <t>Local situé dans la Patte d'Oie d'Herblay. 60M de flux annuel. Frais de rédaction d'acte : 2 500 € HT. Bail 6/9/10 ans.</t>
+  </si>
+  <si>
+    <t>74 + 52 (mezz)</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/6.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/7.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/8%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/5%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/6%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.3%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.3%20-%20Vitrolles/2%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.4%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.4%20-%20Vitrolles/2%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/6%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/7%20Plan%20R%2B1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/37%20-%20Les%20Pennes-Mirabeau/7%20Plan%20RDC.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/6%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/38%20-%20Saint-Germain-du-Puy/7%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/6.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/7%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/8%20Plan%20R-1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/9%20Plan%20RDC.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/40%20-%20Nancy/10%20Plan%20R%2B1.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/42%20-%20Enneti%C3%A8res-en-Weppes/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/42%20-%20Enneti%C3%A8res-en-Weppes/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/42%20-%20Enneti%C3%A8res-en-Weppes/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/42%20-%20Enneti%C3%A8res-en-Weppes/4%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/42%20-%20Enneti%C3%A8res-en-Weppes/5%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/43%20-%20Wittenheim/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/43%20-%20Wittenheim/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/43%20-%20Wittenheim/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/43%20-%20Wittenheim/4%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/43%20-%20Wittenheim/5%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/44%20-%20Nemours/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/44%20-%20Nemours/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/44%20-%20Nemours/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/44%20-%20Nemours/4%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/44%20-%20Nemours/5%20Plan%20RDC.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/44%20-%20Nemours/6%20Plan%20R%2B1.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/5%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.1%20-%20La%20Valette-du-Var/6%20Plan%20RDC.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.2%20-%20La%20Valette-du-Var/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.2%20-%20La%20Valette-du-Var/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.2%20-%20La%20Valette-du-Var/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.2%20-%20La%20Valette-du-Var/4%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/45.2%20-%20La%20Valette-du-Var/5%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/46%20-%20Avignon/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/46%20-%20Avignon/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/46%20-%20Avignon/3%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/46%20-%20Avignon/4%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.1%20-%20Champigny-sur-Marne/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.1%20-%20Champigny-sur-Marne/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.1%20-%20Champigny-sur-Marne/3%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.1%20-%20Champigny-sur-Marne/4%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.2%20-%20Champigny-sur-Marne/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.2%20-%20Champigny-sur-Marne/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.2%20-%20Champigny-sur-Marne/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.1%20-%20Champigny-sur-Marne/3%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.2%20-%20Champigny-sur-Marne/5%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.3%20-%20Champigny-sur-Marne/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.3%20-%20Champigny-sur-Marne/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.3%20-%20Champigny-sur-Marne/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.3%20-%20Champigny-sur-Marne/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.1%20-%20Champigny-sur-Marne/3%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/47.3%20-%20Champigny-sur-Marne/6%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/5%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/6%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/1.JPG; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/2.JPG; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/3.JPG; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/4%20Plan%20de%20situation.png</t>
   </si>
 </sst>
 </file>
@@ -3861,7 +3978,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3877,6 +3994,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3896,7 +4019,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -4017,7 +4140,12 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -4388,8 +4516,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU169" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AU169" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU172" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AU172" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="47">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="46" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -4781,7 +4909,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BD175"/>
+  <dimension ref="A1:BD178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -4977,7 +5105,7 @@
         <v>12</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
@@ -26893,7 +27021,7 @@
         <v>1035</v>
       </c>
       <c r="AK144" s="11" t="s">
-        <v>1231</v>
+        <v>1199</v>
       </c>
       <c r="AL144" s="5" t="s">
         <v>370</v>
@@ -27045,7 +27173,7 @@
         <v>1035</v>
       </c>
       <c r="AK145" s="11" t="s">
-        <v>1232</v>
+        <v>1200</v>
       </c>
       <c r="AL145" s="5" t="s">
         <v>370</v>
@@ -27463,7 +27591,7 @@
         <v>56000</v>
       </c>
       <c r="AD148" s="12" t="str">
-        <f t="shared" ref="AD148:AD152" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AD148:AE172" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
         <v>3 mois = 10 000 €</v>
       </c>
       <c r="AE148" s="6" t="s">
@@ -28136,7 +28264,7 @@
         <v>45999</v>
       </c>
     </row>
-    <row r="153" spans="1:47" ht="25.5">
+    <row r="153" spans="1:47" ht="38.25">
       <c r="A153" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -28175,8 +28303,12 @@
       <c r="K153" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L153" s="12"/>
-      <c r="M153" s="36"/>
+      <c r="L153" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M153" s="36" t="s">
+        <v>1213</v>
+      </c>
       <c r="N153" s="34">
         <v>181</v>
       </c>
@@ -28189,26 +28321,38 @@
       <c r="Q153" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R153" s="12"/>
+      <c r="R153" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>45250</v>
+      </c>
       <c r="S153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T153" s="12"/>
+        <v>3770.8333333333335</v>
+      </c>
+      <c r="T153" s="12">
+        <v>250</v>
+      </c>
       <c r="U153" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V153" s="12"/>
+      <c r="V153" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1306.82</v>
+      </c>
       <c r="W153" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X153" s="12"/>
+        <v>108.90166666666666</v>
+      </c>
+      <c r="X153" s="12">
+        <v>7.22</v>
+      </c>
       <c r="Y153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z153" s="12"/>
+        <v>2360.2399999999998</v>
+      </c>
+      <c r="Z153" s="12">
+        <v>13.04</v>
+      </c>
       <c r="AA153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -28218,14 +28362,17 @@
       </c>
       <c r="AC153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD153" s="12"/>
+        <v>48917.06</v>
+      </c>
+      <c r="AD153" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 11 313 €</v>
+      </c>
       <c r="AE153" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF153" s="6" t="s">
-        <v>104</v>
+      <c r="AF153" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG153" s="12" t="s">
         <v>365</v>
@@ -28237,39 +28384,41 @@
         <v>372</v>
       </c>
       <c r="AJ153" s="10" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="AK153" s="11" t="s">
-        <v>1110</v>
+        <v>1212</v>
       </c>
       <c r="AL153" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="AM153" s="11" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AN153" s="11" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AO153" s="11">
-        <v>36</v>
+      <c r="AM153" s="11">
+        <v>43.4393873</v>
+      </c>
+      <c r="AN153" s="11">
+        <v>5.2419589999999996</v>
+      </c>
+      <c r="AO153" s="11" t="s">
+        <v>1217</v>
       </c>
       <c r="AP153" s="36" t="s">
-        <v>1211</v>
+        <v>1263</v>
       </c>
       <c r="AQ153" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR153" s="11"/>
+      <c r="AR153" s="11" t="s">
+        <v>1211</v>
+      </c>
       <c r="AS153" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT153" s="14"/>
       <c r="AU153" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="154" spans="1:47" ht="38.25">
+    <row r="154" spans="1:47" ht="51">
       <c r="A154" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -28283,21 +28432,21 @@
         <v>13</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>1147</v>
+        <v>1107</v>
       </c>
       <c r="E154" s="10">
-        <v>13170</v>
+        <v>13128</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>1134</v>
+        <v>1103</v>
       </c>
       <c r="G154" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>Plan de Campagne, Chemin des Pennes CD6
-13170 - Les Pennes-Mirabeau</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>1112</v>
+        <v>14 Boulevard de l'Europe
+13128 - Vitrolles</v>
+      </c>
+      <c r="H154" s="15" t="s">
+        <v>1108</v>
       </c>
       <c r="I154" s="12" t="s">
         <v>47</v>
@@ -28306,12 +28455,16 @@
         <v>48</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="L154" s="12"/>
-      <c r="M154" s="36"/>
+        <v>1232</v>
+      </c>
+      <c r="L154" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M154" s="36" t="s">
+        <v>1214</v>
+      </c>
       <c r="N154" s="34">
-        <v>1390</v>
+        <v>100</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>104</v>
@@ -28322,26 +28475,38 @@
       <c r="Q154" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R154" s="12"/>
+      <c r="R154" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>20000</v>
+      </c>
       <c r="S154" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T154" s="12"/>
+        <v>1666.6666666666667</v>
+      </c>
+      <c r="T154" s="12">
+        <v>200</v>
+      </c>
       <c r="U154" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V154" s="12"/>
+      <c r="V154" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>722</v>
+      </c>
       <c r="W154" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X154" s="12"/>
+        <v>60.166666666666664</v>
+      </c>
+      <c r="X154" s="12">
+        <v>7.22</v>
+      </c>
       <c r="Y154" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z154" s="12"/>
+        <v>1304</v>
+      </c>
+      <c r="Z154" s="12">
+        <v>13.04</v>
+      </c>
       <c r="AA154" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -28351,86 +28516,91 @@
       </c>
       <c r="AC154" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD154" s="12"/>
+        <v>22026</v>
+      </c>
+      <c r="AD154" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 5 000 €</v>
+      </c>
       <c r="AE154" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF154" s="6" t="s">
-        <v>104</v>
+      <c r="AF154" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG154" s="12" t="s">
         <v>365</v>
       </c>
       <c r="AH154" s="10" t="s">
-        <v>379</v>
+        <v>76</v>
       </c>
       <c r="AI154" s="10" t="s">
         <v>372</v>
       </c>
       <c r="AJ154" s="10" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
       <c r="AK154" s="11" t="s">
-        <v>1162</v>
+        <v>1220</v>
       </c>
       <c r="AL154" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM154" s="11" t="s">
-        <v>1150</v>
+        <v>1215</v>
       </c>
       <c r="AN154" s="11" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AO154" s="11">
-        <v>37</v>
+        <v>1216</v>
+      </c>
+      <c r="AO154" s="11" t="s">
+        <v>1218</v>
       </c>
       <c r="AP154" s="36" t="s">
-        <v>1212</v>
+        <v>1264</v>
       </c>
       <c r="AQ154" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR154" s="11"/>
+      <c r="AR154" s="11" t="s">
+        <v>1221</v>
+      </c>
       <c r="AS154" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT154" s="14"/>
       <c r="AU154" s="44">
-        <v>46003</v>
+        <v>46004</v>
       </c>
     </row>
-    <row r="155" spans="1:47" ht="25.5">
+    <row r="155" spans="1:47" ht="38.25">
       <c r="A155" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Centre-Val de Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B155" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Cher</v>
+        <v>Bouches-du-Rhône</v>
       </c>
       <c r="C155" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>1135</v>
+        <v>1107</v>
       </c>
       <c r="E155" s="10">
-        <v>18390</v>
+        <v>13129</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>1136</v>
+        <v>1103</v>
       </c>
       <c r="G155" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>8 Rue des Vignes
-18390 - Saint-Germain-du-Puy</v>
+        <v>14 Boulevard de l'Europe
+13129 - Vitrolles</v>
       </c>
       <c r="H155" s="15" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>47</v>
@@ -28439,12 +28609,16 @@
         <v>48</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="L155" s="12"/>
-      <c r="M155" s="36"/>
+        <v>1232</v>
+      </c>
+      <c r="L155" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M155" s="36" t="s">
+        <v>1225</v>
+      </c>
       <c r="N155" s="34">
-        <v>1000</v>
+        <v>446</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>104</v>
@@ -28455,26 +28629,38 @@
       <c r="Q155" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R155" s="12"/>
+      <c r="R155" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>55750</v>
+      </c>
       <c r="S155" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T155" s="12"/>
+        <v>4645.833333333333</v>
+      </c>
+      <c r="T155" s="12">
+        <v>125</v>
+      </c>
       <c r="U155" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V155" s="12"/>
+      <c r="V155" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3220.12</v>
+      </c>
       <c r="W155" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X155" s="12"/>
+        <v>268.34333333333331</v>
+      </c>
+      <c r="X155" s="12">
+        <v>7.22</v>
+      </c>
       <c r="Y155" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z155" s="12"/>
+        <v>5815.8399999999992</v>
+      </c>
+      <c r="Z155" s="12">
+        <v>13.04</v>
+      </c>
       <c r="AA155" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -28484,100 +28670,109 @@
       </c>
       <c r="AC155" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD155" s="12"/>
+        <v>64785.96</v>
+      </c>
+      <c r="AD155" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 13 938 €</v>
+      </c>
       <c r="AE155" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF155" s="6" t="s">
-        <v>104</v>
+      <c r="AF155" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG155" s="12" t="s">
         <v>365</v>
       </c>
       <c r="AH155" s="10" t="s">
-        <v>379</v>
+        <v>53</v>
       </c>
       <c r="AI155" s="10" t="s">
-        <v>372</v>
+        <v>104</v>
       </c>
       <c r="AJ155" s="10" t="s">
-        <v>1163</v>
+        <v>1154</v>
       </c>
       <c r="AK155" s="11" t="s">
-        <v>1164</v>
+        <v>1219</v>
       </c>
       <c r="AL155" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM155" s="11" t="s">
-        <v>1165</v>
+        <v>1222</v>
       </c>
       <c r="AN155" s="11" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AO155" s="11">
-        <v>38</v>
+        <v>1223</v>
+      </c>
+      <c r="AO155" s="11" t="s">
+        <v>1227</v>
       </c>
       <c r="AP155" s="36" t="s">
-        <v>1213</v>
+        <v>1265</v>
       </c>
       <c r="AQ155" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR155" s="11"/>
+      <c r="AR155" s="11" t="s">
+        <v>1224</v>
+      </c>
       <c r="AS155" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT155" s="14"/>
       <c r="AU155" s="44">
-        <v>46003</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="156" spans="1:47" ht="38.25">
       <c r="A156" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Centre-Val de Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B156" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Cher</v>
+        <v>Bouches-du-Rhône</v>
       </c>
       <c r="C156" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>1138</v>
+        <v>1107</v>
       </c>
       <c r="E156" s="10">
-        <v>18230</v>
+        <v>13130</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>1137</v>
+        <v>1103</v>
       </c>
       <c r="G156" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>Centre Commercial Géant,  548 Route d'Orléans
-18230 -  Saint-Doulchard</v>
+        <v>14 Boulevard de l'Europe
+13130 - Vitrolles</v>
       </c>
       <c r="H156" s="15" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="I156" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J156" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="L156" s="12"/>
-      <c r="M156" s="36"/>
+        <v>1232</v>
+      </c>
+      <c r="L156" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M156" s="36" t="s">
+        <v>1226</v>
+      </c>
       <c r="N156" s="34">
-        <v>5000</v>
+        <v>567</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>104</v>
@@ -28588,26 +28783,38 @@
       <c r="Q156" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R156" s="12"/>
+      <c r="R156" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>70875</v>
+      </c>
       <c r="S156" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T156" s="12"/>
+        <v>5906.25</v>
+      </c>
+      <c r="T156" s="12">
+        <v>125</v>
+      </c>
       <c r="U156" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V156" s="12"/>
+      <c r="V156" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>4093.74</v>
+      </c>
       <c r="W156" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X156" s="12"/>
+        <v>341.14499999999998</v>
+      </c>
+      <c r="X156" s="12">
+        <v>7.22</v>
+      </c>
       <c r="Y156" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z156" s="12"/>
+        <v>7393.6799999999994</v>
+      </c>
+      <c r="Z156" s="12">
+        <v>13.04</v>
+      </c>
       <c r="AA156" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -28617,14 +28824,17 @@
       </c>
       <c r="AC156" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD156" s="12"/>
+        <v>82362.42</v>
+      </c>
+      <c r="AD156" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 17 719 €</v>
+      </c>
       <c r="AE156" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF156" s="6" t="s">
-        <v>104</v>
+      <c r="AF156" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG156" s="12" t="s">
         <v>365</v>
@@ -28636,84 +28846,88 @@
         <v>104</v>
       </c>
       <c r="AJ156" s="10" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="AK156" s="11" t="s">
-        <v>1170</v>
+        <v>1219</v>
       </c>
       <c r="AL156" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM156" s="11" t="s">
-        <v>1168</v>
+        <v>1230</v>
       </c>
       <c r="AN156" s="11" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO156" s="11">
-        <v>39</v>
+        <v>1231</v>
+      </c>
+      <c r="AO156" s="11" t="s">
+        <v>1229</v>
       </c>
       <c r="AP156" s="36" t="s">
-        <v>1215</v>
+        <v>1266</v>
       </c>
       <c r="AQ156" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR156" s="11"/>
+      <c r="AR156" s="11" t="s">
+        <v>1228</v>
+      </c>
       <c r="AS156" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT156" s="14"/>
       <c r="AU156" s="44">
-        <v>46003</v>
+        <v>46006</v>
       </c>
     </row>
-    <row r="157" spans="1:47" ht="25.5">
+    <row r="157" spans="1:47" ht="38.25">
       <c r="A157" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B157" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Meurthe-et-Moselle</v>
+        <v>Bouches-du-Rhône</v>
       </c>
       <c r="C157" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="E157" s="10">
-        <v>54000</v>
+        <v>13170</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>1104</v>
+        <v>1131</v>
       </c>
       <c r="G157" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>50 Rue Saint-Dizier
-54000 - Nancy</v>
-      </c>
-      <c r="H157" s="15" t="s">
-        <v>1115</v>
+        <v>Plan de Campagne, Chemin des Pennes CD6
+13170 - Les Pennes-Mirabeau</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>1111</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J157" s="12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K157" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L157" s="12"/>
+      <c r="L157" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="M157" s="36"/>
       <c r="N157" s="34">
-        <v>449</v>
+        <v>1390</v>
       </c>
       <c r="O157" s="6" t="s">
-        <v>104</v>
+        <v>1234</v>
       </c>
       <c r="P157" s="34" t="s">
         <v>104</v>
@@ -28721,26 +28935,38 @@
       <c r="Q157" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R157" s="12"/>
+      <c r="R157" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>312750</v>
+      </c>
       <c r="S157" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T157" s="12"/>
+        <v>26062.5</v>
+      </c>
+      <c r="T157" s="12">
+        <v>225</v>
+      </c>
       <c r="U157" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V157" s="12"/>
+      <c r="V157" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>9730</v>
+      </c>
       <c r="W157" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X157" s="12"/>
+        <v>810.83333333333337</v>
+      </c>
+      <c r="X157" s="12">
+        <v>7</v>
+      </c>
       <c r="Y157" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z157" s="12"/>
+        <v>20850</v>
+      </c>
+      <c r="Z157" s="12">
+        <v>15</v>
+      </c>
       <c r="AA157" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -28750,51 +28976,57 @@
       </c>
       <c r="AC157" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD157" s="12"/>
-      <c r="AE157" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF157" s="6" t="s">
-        <v>104</v>
+        <v>343330</v>
+      </c>
+      <c r="AD157" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 78 188 €</v>
+      </c>
+      <c r="AE157" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R157,0),"### ### ##0 €")</f>
+        <v>6 mois = 156 375 €</v>
+      </c>
+      <c r="AF157" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG157" s="12" t="s">
         <v>365</v>
       </c>
       <c r="AH157" s="10" t="s">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="AI157" s="10" t="s">
         <v>372</v>
       </c>
       <c r="AJ157" s="10" t="s">
-        <v>1174</v>
+        <v>1155</v>
       </c>
       <c r="AK157" s="11" t="s">
-        <v>1173</v>
+        <v>1235</v>
       </c>
       <c r="AL157" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM157" s="11" t="s">
-        <v>1171</v>
+        <v>1144</v>
       </c>
       <c r="AN157" s="11" t="s">
-        <v>1172</v>
+        <v>1145</v>
       </c>
       <c r="AO157" s="11">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AP157" s="36" t="s">
-        <v>1214</v>
+        <v>1267</v>
       </c>
       <c r="AQ157" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR157" s="11"/>
+      <c r="AR157" s="11" t="s">
+        <v>1233</v>
+      </c>
       <c r="AS157" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT157" s="14"/>
       <c r="AU157" s="44">
@@ -28804,46 +29036,48 @@
     <row r="158" spans="1:47" ht="25.5">
       <c r="A158" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Hauts-de-France</v>
+        <v>Centre-Val de Loire</v>
       </c>
       <c r="B158" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Nord</v>
+        <v>Cher</v>
       </c>
       <c r="C158" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
       <c r="E158" s="10">
-        <v>59300</v>
+        <v>18390</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
       <c r="G158" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>ZAC D'Aulnoy
-59300 - Aulnoy-lez-Valenciennes</v>
+        <v>8 Rue des Vignes
+18390 - Saint-Germain-du-Puy</v>
       </c>
       <c r="H158" s="15" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="I158" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J158" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K158" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L158" s="12"/>
+      <c r="L158" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="M158" s="36"/>
-      <c r="N158" s="34" t="s">
-        <v>1109</v>
+      <c r="N158" s="34">
+        <v>1000</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>104</v>
@@ -28854,26 +29088,38 @@
       <c r="Q158" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R158" s="12"/>
+      <c r="R158" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>150000</v>
+      </c>
       <c r="S158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T158" s="12"/>
+        <v>12500</v>
+      </c>
+      <c r="T158" s="12">
+        <v>150</v>
+      </c>
       <c r="U158" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V158" s="12"/>
+      <c r="V158" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3500</v>
+      </c>
       <c r="W158" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X158" s="12"/>
+        <v>291.66666666666669</v>
+      </c>
+      <c r="X158" s="12">
+        <v>3.5</v>
+      </c>
       <c r="Y158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z158" s="12"/>
+        <v>12650</v>
+      </c>
+      <c r="Z158" s="12">
+        <v>12.65</v>
+      </c>
       <c r="AA158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -28883,49 +29129,56 @@
       </c>
       <c r="AC158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD158" s="12"/>
+        <v>166150</v>
+      </c>
+      <c r="AD158" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 37 500 €</v>
+      </c>
       <c r="AE158" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF158" s="6" t="s">
-        <v>104</v>
+      <c r="AF158" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG158" s="12" t="s">
         <v>365</v>
       </c>
       <c r="AH158" s="10" t="s">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="AI158" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="AJ158" s="10"/>
+      <c r="AJ158" s="10" t="s">
+        <v>1156</v>
+      </c>
       <c r="AK158" s="11" t="s">
-        <v>1177</v>
+        <v>1157</v>
       </c>
       <c r="AL158" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM158" s="11" t="s">
-        <v>1175</v>
+        <v>1158</v>
       </c>
       <c r="AN158" s="11" t="s">
-        <v>1176</v>
+        <v>1159</v>
       </c>
       <c r="AO158" s="11">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AP158" s="36" t="s">
-        <v>1216</v>
+        <v>1268</v>
       </c>
       <c r="AQ158" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR158" s="11"/>
+      <c r="AR158" s="11" t="s">
+        <v>1236</v>
+      </c>
       <c r="AS158" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT158" s="14"/>
       <c r="AU158" s="44">
@@ -28935,38 +29188,38 @@
     <row r="159" spans="1:47" ht="38.25">
       <c r="A159" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Hauts-de-France</v>
+        <v>Centre-Val de Loire</v>
       </c>
       <c r="B159" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Nord</v>
+        <v>Cher</v>
       </c>
       <c r="C159" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="E159" s="10">
-        <v>59320</v>
+        <v>18230</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>1143</v>
+        <v>1134</v>
       </c>
       <c r="G159" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>352 Route nationale, Rue des Fusillés de 1940
-59320 - Ennetières-en-Weppes</v>
+        <v>Centre Commercial Géant,  548 Route d'Orléans
+18230 -  Saint-Doulchard</v>
       </c>
       <c r="H159" s="15" t="s">
-        <v>1179</v>
+        <v>1113</v>
       </c>
       <c r="I159" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J159" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K159" s="10" t="s">
         <v>104</v>
@@ -28974,7 +29227,7 @@
       <c r="L159" s="12"/>
       <c r="M159" s="36"/>
       <c r="N159" s="34">
-        <v>750</v>
+        <v>5000</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>104</v>
@@ -28985,7 +29238,10 @@
       <c r="Q159" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R159" s="12"/>
+      <c r="R159" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="S159" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>0</v>
@@ -28994,7 +29250,10 @@
       <c r="U159" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V159" s="12"/>
+      <c r="V159" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W159" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -29016,7 +29275,10 @@
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>0</v>
       </c>
-      <c r="AD159" s="12"/>
+      <c r="AD159" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 0 €</v>
+      </c>
       <c r="AE159" s="6" t="s">
         <v>104</v>
       </c>
@@ -29027,90 +29289,92 @@
         <v>365</v>
       </c>
       <c r="AH159" s="10" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="AI159" s="10" t="s">
-        <v>372</v>
+        <v>104</v>
       </c>
       <c r="AJ159" s="10" t="s">
-        <v>1178</v>
+        <v>1160</v>
       </c>
       <c r="AK159" s="11" t="s">
-        <v>1227</v>
+        <v>1163</v>
       </c>
       <c r="AL159" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM159" s="11" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="AN159" s="11" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="AO159" s="11">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="AP159" s="36" t="s">
-        <v>1217</v>
+        <v>1196</v>
       </c>
       <c r="AQ159" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR159" s="11"/>
       <c r="AS159" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT159" s="14"/>
       <c r="AU159" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="160" spans="1:47" ht="25.5">
+    <row r="160" spans="1:47" ht="38.25">
       <c r="A160" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
       </c>
       <c r="B160" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Haut-Rhin</v>
+        <v>Meurthe-et-Moselle</v>
       </c>
       <c r="C160" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
       <c r="E160" s="10">
-        <v>68270</v>
+        <v>54000</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>1145</v>
+        <v>1104</v>
       </c>
       <c r="G160" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>11 Rue de Soultz
-68270 - Wittenheim</v>
+        <v>50 Rue Saint-Dizier
+54000 - Nancy</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K160" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L160" s="12"/>
+      <c r="L160" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="M160" s="36"/>
       <c r="N160" s="34">
-        <v>930</v>
+        <v>550</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>104</v>
+        <v>1238</v>
       </c>
       <c r="P160" s="34" t="s">
         <v>104</v>
@@ -29118,26 +29382,38 @@
       <c r="Q160" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R160" s="12"/>
+      <c r="R160" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>330000</v>
+      </c>
       <c r="S160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T160" s="12"/>
+        <v>27500</v>
+      </c>
+      <c r="T160" s="12">
+        <v>600</v>
+      </c>
       <c r="U160" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V160" s="12"/>
+      <c r="V160" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2750</v>
+      </c>
       <c r="W160" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X160" s="12"/>
+        <v>229.16666666666666</v>
+      </c>
+      <c r="X160" s="12">
+        <v>5</v>
+      </c>
       <c r="Y160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z160" s="12"/>
+        <v>8250</v>
+      </c>
+      <c r="Z160" s="12">
+        <v>15</v>
+      </c>
       <c r="AA160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -29147,51 +29423,56 @@
       </c>
       <c r="AC160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD160" s="12"/>
+        <v>341000</v>
+      </c>
+      <c r="AD160" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 82 500 €</v>
+      </c>
       <c r="AE160" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF160" s="6" t="s">
-        <v>104</v>
+      <c r="AF160" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG160" s="12" t="s">
         <v>365</v>
       </c>
       <c r="AH160" s="10" t="s">
-        <v>379</v>
+        <v>76</v>
       </c>
       <c r="AI160" s="10" t="s">
         <v>372</v>
       </c>
       <c r="AJ160" s="10" t="s">
-        <v>1182</v>
+        <v>1166</v>
       </c>
       <c r="AK160" s="11" t="s">
-        <v>1228</v>
+        <v>1239</v>
       </c>
       <c r="AL160" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM160" s="11" t="s">
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="AN160" s="11" t="s">
-        <v>1181</v>
+        <v>1165</v>
       </c>
       <c r="AO160" s="11">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AP160" s="36" t="s">
-        <v>1218</v>
+        <v>1269</v>
       </c>
       <c r="AQ160" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR160" s="11"/>
+      <c r="AR160" s="11" t="s">
+        <v>1237</v>
+      </c>
       <c r="AS160" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT160" s="14"/>
       <c r="AU160" s="44">
@@ -29201,46 +29482,46 @@
     <row r="161" spans="1:47" ht="25.5">
       <c r="A161" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
+        <v>Hauts-de-France</v>
       </c>
       <c r="B161" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Seine-et-Marne</v>
+        <v>Nord</v>
       </c>
       <c r="C161" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>1146</v>
+        <v>1137</v>
       </c>
       <c r="E161" s="10">
-        <v>77140</v>
+        <v>59300</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G161" s="39" t="str">
+        <v>1138</v>
+      </c>
+      <c r="G161" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>31 Rue de Montargis
-77140 - Nemours</v>
+        <v>ZAC D'Aulnoy
+59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H161" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="I161" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J161" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K161" s="10" t="s">
         <v>104</v>
       </c>
       <c r="L161" s="12"/>
       <c r="M161" s="36"/>
-      <c r="N161" s="34">
-        <v>760</v>
+      <c r="N161" s="34" t="s">
+        <v>1109</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>104</v>
@@ -29251,19 +29532,25 @@
       <c r="Q161" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R161" s="12"/>
-      <c r="S161" s="12">
+      <c r="R161" s="12" t="e">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S161" s="12" t="str">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T161" s="12"/>
       <c r="U161" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V161" s="12"/>
-      <c r="W161" s="12">
+      <c r="V161" s="6" t="e">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W161" s="12" t="e">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="X161" s="12"/>
       <c r="Y161" s="12">
@@ -29278,11 +29565,14 @@
       <c r="AB161" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AC161" s="12">
+      <c r="AC161" s="12" t="str">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD161" s="12"/>
+        <v/>
+      </c>
+      <c r="AD161" s="12" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="AE161" s="6" t="s">
         <v>104</v>
       </c>
@@ -29293,87 +29583,87 @@
         <v>365</v>
       </c>
       <c r="AH161" s="10" t="s">
-        <v>379</v>
+        <v>76</v>
       </c>
       <c r="AI161" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="AJ161" s="10" t="s">
-        <v>1185</v>
-      </c>
+      <c r="AJ161" s="10"/>
       <c r="AK161" s="11" t="s">
-        <v>1186</v>
+        <v>1169</v>
       </c>
       <c r="AL161" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM161" s="11" t="s">
-        <v>1183</v>
+        <v>1167</v>
       </c>
       <c r="AN161" s="11" t="s">
-        <v>1184</v>
+        <v>1168</v>
       </c>
       <c r="AO161" s="11">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AP161" s="36" t="s">
-        <v>1219</v>
+        <v>1197</v>
       </c>
       <c r="AQ161" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR161" s="11"/>
       <c r="AS161" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT161" s="14"/>
       <c r="AU161" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="162" spans="1:47" ht="25.5">
+    <row r="162" spans="1:47" ht="38.25">
       <c r="A162" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Provence-Alpes-Côte d'Azur</v>
+        <v>Hauts-de-France</v>
       </c>
       <c r="B162" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Var</v>
+        <v>Nord</v>
       </c>
       <c r="C162" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1125</v>
+        <v>1240</v>
       </c>
       <c r="E162" s="10">
-        <v>83160</v>
+        <v>59320</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>1124</v>
-      </c>
-      <c r="G162" s="39" t="str">
+        <v>1139</v>
+      </c>
+      <c r="G162" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>23 Avenue des Frères Lumière
-83160 - La Valette-du-Var</v>
+        <v>5001 Rue des Fusillés de 1940
+59320 - Ennetières-en-Weppes</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>1119</v>
+        <v>1171</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K162" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L162" s="12"/>
+      <c r="L162" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="M162" s="36"/>
       <c r="N162" s="34">
-        <v>276</v>
+        <v>750</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>104</v>
@@ -29384,7 +29674,10 @@
       <c r="Q162" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R162" s="12"/>
+      <c r="R162" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="S162" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>0</v>
@@ -29393,7 +29686,10 @@
       <c r="U162" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V162" s="12"/>
+      <c r="V162" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W162" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -29415,7 +29711,10 @@
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>0</v>
       </c>
-      <c r="AD162" s="12"/>
+      <c r="AD162" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 0 €</v>
+      </c>
       <c r="AE162" s="6" t="s">
         <v>104</v>
       </c>
@@ -29432,81 +29731,83 @@
         <v>372</v>
       </c>
       <c r="AJ162" s="10" t="s">
-        <v>1189</v>
+        <v>1170</v>
       </c>
       <c r="AK162" s="11" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="AL162" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM162" s="11" t="s">
-        <v>1187</v>
+        <v>1152</v>
       </c>
       <c r="AN162" s="11" t="s">
-        <v>1188</v>
-      </c>
-      <c r="AO162" s="11" t="s">
         <v>1153</v>
       </c>
+      <c r="AO162" s="11">
+        <v>42</v>
+      </c>
       <c r="AP162" s="36" t="s">
-        <v>1220</v>
+        <v>1270</v>
       </c>
       <c r="AQ162" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR162" s="11"/>
       <c r="AS162" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT162" s="14"/>
       <c r="AU162" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="163" spans="1:47" ht="51">
+    <row r="163" spans="1:47" ht="25.5">
       <c r="A163" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Provence-Alpes-Côte d'Azur</v>
+        <v>Grand Est</v>
       </c>
       <c r="B163" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Var</v>
+        <v>Haut-Rhin</v>
       </c>
       <c r="C163" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>1126</v>
+        <v>1140</v>
       </c>
       <c r="E163" s="10">
-        <v>83161</v>
+        <v>68270</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="G163" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v xml:space="preserve"> Lotissement d'activité économique Castel Les Espaluns, Avenue de l'Université
-83161 - La Valette-du-Var</v>
+        <v>11 Rue de Soultz
+68270 - Wittenheim</v>
       </c>
       <c r="H163" s="15" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J163" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K163" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L163" s="12"/>
+      <c r="L163" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="M163" s="36"/>
       <c r="N163" s="34">
-        <v>470</v>
+        <v>930</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>104</v>
@@ -29517,26 +29818,38 @@
       <c r="Q163" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R163" s="12"/>
+      <c r="R163" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>209250</v>
+      </c>
       <c r="S163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T163" s="12"/>
+        <v>17437.5</v>
+      </c>
+      <c r="T163" s="12">
+        <v>225</v>
+      </c>
       <c r="U163" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V163" s="12"/>
+      <c r="V163" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3069</v>
+      </c>
       <c r="W163" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X163" s="12"/>
+        <v>255.75</v>
+      </c>
+      <c r="X163" s="12">
+        <v>3.3</v>
+      </c>
       <c r="Y163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z163" s="12"/>
+        <v>12276</v>
+      </c>
+      <c r="Z163" s="12">
+        <v>13.2</v>
+      </c>
       <c r="AA163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -29546,14 +29859,17 @@
       </c>
       <c r="AC163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD163" s="12"/>
+        <v>224595</v>
+      </c>
+      <c r="AD163" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 52 313 €</v>
+      </c>
       <c r="AE163" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF163" s="6" t="s">
-        <v>104</v>
+      <c r="AF163" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG163" s="12" t="s">
         <v>365</v>
@@ -29565,32 +29881,34 @@
         <v>372</v>
       </c>
       <c r="AJ163" s="10" t="s">
-        <v>1190</v>
+        <v>1243</v>
       </c>
       <c r="AK163" s="11" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="AL163" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM163" s="11" t="s">
-        <v>1192</v>
+        <v>1172</v>
       </c>
       <c r="AN163" s="11" t="s">
-        <v>1193</v>
-      </c>
-      <c r="AO163" s="11" t="s">
-        <v>1152</v>
+        <v>1173</v>
+      </c>
+      <c r="AO163" s="11">
+        <v>43</v>
       </c>
       <c r="AP163" s="36" t="s">
-        <v>1221</v>
+        <v>1271</v>
       </c>
       <c r="AQ163" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR163" s="11"/>
+      <c r="AR163" s="11" t="s">
+        <v>1242</v>
+      </c>
       <c r="AS163" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT163" s="14"/>
       <c r="AU163" s="44">
@@ -29600,32 +29918,32 @@
     <row r="164" spans="1:47" ht="25.5">
       <c r="A164" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Provence-Alpes-Côte d'Azur</v>
+        <v>Ile-de-France</v>
       </c>
       <c r="B164" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Vaucluse</v>
+        <v>Seine-et-Marne</v>
       </c>
       <c r="C164" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1127</v>
+        <v>1142</v>
       </c>
       <c r="E164" s="10">
-        <v>84140</v>
+        <v>77140</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G164" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>330 Avenue Marcou Delanglade
-84140 - Avignon</v>
+        <v>31 Rue de Montargis
+77140 - Nemours</v>
       </c>
       <c r="H164" s="15" t="s">
-        <v>1197</v>
+        <v>1117</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>47</v>
@@ -29636,13 +29954,15 @@
       <c r="K164" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L164" s="12"/>
+      <c r="L164" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="M164" s="36"/>
       <c r="N164" s="34">
-        <v>420</v>
+        <v>760</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>104</v>
+        <v>1245</v>
       </c>
       <c r="P164" s="34" t="s">
         <v>104</v>
@@ -29650,26 +29970,38 @@
       <c r="Q164" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R164" s="12"/>
+      <c r="R164" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>95000</v>
+      </c>
       <c r="S164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T164" s="12"/>
+        <v>7916.666666666667</v>
+      </c>
+      <c r="T164" s="12">
+        <v>125</v>
+      </c>
       <c r="U164" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V164" s="12"/>
+      <c r="V164" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3800</v>
+      </c>
       <c r="W164" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X164" s="12"/>
+        <v>316.66666666666669</v>
+      </c>
+      <c r="X164" s="12">
+        <v>5</v>
+      </c>
       <c r="Y164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z164" s="12"/>
+        <v>17480</v>
+      </c>
+      <c r="Z164" s="12">
+        <v>23</v>
+      </c>
       <c r="AA164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -29679,51 +30011,56 @@
       </c>
       <c r="AC164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD164" s="12"/>
+        <v>116280</v>
+      </c>
+      <c r="AD164" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 23 750 €</v>
+      </c>
       <c r="AE164" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF164" s="6" t="s">
-        <v>104</v>
+      <c r="AF164" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG164" s="12" t="s">
         <v>365</v>
       </c>
       <c r="AH164" s="10" t="s">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="AI164" s="10" t="s">
         <v>372</v>
       </c>
       <c r="AJ164" s="10" t="s">
-        <v>1196</v>
+        <v>1176</v>
       </c>
       <c r="AK164" s="11" t="s">
-        <v>1230</v>
+        <v>1246</v>
       </c>
       <c r="AL164" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM164" s="11" t="s">
-        <v>1194</v>
+        <v>1174</v>
       </c>
       <c r="AN164" s="11" t="s">
-        <v>1195</v>
+        <v>1175</v>
       </c>
       <c r="AO164" s="11">
-        <v>46</v>
-      </c>
-      <c r="AP164" s="45" t="s">
-        <v>1223</v>
+        <v>44</v>
+      </c>
+      <c r="AP164" s="36" t="s">
+        <v>1272</v>
       </c>
       <c r="AQ164" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR164" s="11"/>
+      <c r="AR164" s="11" t="s">
+        <v>1244</v>
+      </c>
       <c r="AS164" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT164" s="14"/>
       <c r="AU164" s="44">
@@ -29733,38 +30070,38 @@
     <row r="165" spans="1:47" ht="25.5">
       <c r="A165" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B165" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Val-de-Marne</v>
+        <v>Var</v>
       </c>
       <c r="C165" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="E165" s="10">
-        <v>94500</v>
+        <v>83160</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>1129</v>
-      </c>
-      <c r="G165" s="39" t="str">
+        <v>1123</v>
+      </c>
+      <c r="G165" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>12 Rue Serpente
-94500 - Champigny-sur-Marne</v>
+        <v>23 Avenue des Frères Lumière
+83160 - La Valette-du-Var</v>
       </c>
       <c r="H165" s="15" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="I165" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J165" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K165" s="10" t="s">
         <v>104</v>
@@ -29772,10 +30109,10 @@
       <c r="L165" s="12"/>
       <c r="M165" s="36"/>
       <c r="N165" s="34">
-        <v>875</v>
+        <v>276</v>
       </c>
       <c r="O165" s="6" t="s">
-        <v>104</v>
+        <v>1247</v>
       </c>
       <c r="P165" s="34" t="s">
         <v>104</v>
@@ -29783,7 +30120,10 @@
       <c r="Q165" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R165" s="12"/>
+      <c r="R165" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="S165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>0</v>
@@ -29792,17 +30132,24 @@
       <c r="U165" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V165" s="12"/>
+      <c r="V165" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2760</v>
+      </c>
       <c r="W165" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X165" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="X165" s="12">
+        <v>10</v>
+      </c>
       <c r="Y165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z165" s="12"/>
+        <v>6348</v>
+      </c>
+      <c r="Z165" s="12">
+        <v>23</v>
+      </c>
       <c r="AA165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -29812,9 +30159,12 @@
       </c>
       <c r="AC165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD165" s="12"/>
+        <v>9108</v>
+      </c>
+      <c r="AD165" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 0 €</v>
+      </c>
       <c r="AE165" s="6" t="s">
         <v>104</v>
       </c>
@@ -29825,38 +30175,38 @@
         <v>365</v>
       </c>
       <c r="AH165" s="10" t="s">
-        <v>379</v>
+        <v>76</v>
       </c>
       <c r="AI165" s="10" t="s">
         <v>372</v>
       </c>
       <c r="AJ165" s="10" t="s">
-        <v>1205</v>
+        <v>1179</v>
       </c>
       <c r="AK165" s="11" t="s">
-        <v>1204</v>
+        <v>1248</v>
       </c>
       <c r="AL165" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM165" s="11" t="s">
-        <v>1198</v>
+        <v>1177</v>
       </c>
       <c r="AN165" s="11" t="s">
-        <v>1199</v>
+        <v>1178</v>
       </c>
       <c r="AO165" s="11" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AP165" s="45" t="s">
-        <v>1222</v>
+        <v>1147</v>
+      </c>
+      <c r="AP165" s="36" t="s">
+        <v>1273</v>
       </c>
       <c r="AQ165" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR165" s="11"/>
       <c r="AS165" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT165" s="14"/>
       <c r="AU165" s="44">
@@ -29866,46 +30216,48 @@
     <row r="166" spans="1:47" ht="25.5">
       <c r="A166" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B166" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Val-de-Marne</v>
+        <v>Var</v>
       </c>
       <c r="C166" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>1128</v>
+        <v>1249</v>
       </c>
       <c r="E166" s="10">
-        <v>94500</v>
+        <v>83161</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="G166" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>13 Rue Serpente
-94500 - Champigny-sur-Marne</v>
+        <v>83 Avenue de l'Université
+83161 - La Valette-du-Var</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="I166" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J166" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K166" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L166" s="12"/>
+      <c r="L166" s="12">
+        <v>60000</v>
+      </c>
       <c r="M166" s="36"/>
       <c r="N166" s="34">
-        <v>387</v>
+        <v>470</v>
       </c>
       <c r="O166" s="6" t="s">
         <v>104</v>
@@ -29916,26 +30268,38 @@
       <c r="Q166" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R166" s="12"/>
+      <c r="R166" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>188000</v>
+      </c>
       <c r="S166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T166" s="12"/>
-      <c r="U166" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="V166" s="12"/>
+        <v>15666.666666666666</v>
+      </c>
+      <c r="T166" s="12">
+        <v>400</v>
+      </c>
+      <c r="U166" s="46">
+        <v>0.08</v>
+      </c>
+      <c r="V166" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2350</v>
+      </c>
       <c r="W166" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X166" s="12"/>
+        <v>195.83333333333334</v>
+      </c>
+      <c r="X166" s="12">
+        <v>5</v>
+      </c>
       <c r="Y166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z166" s="12"/>
+        <v>16450</v>
+      </c>
+      <c r="Z166" s="12">
+        <v>35</v>
+      </c>
       <c r="AA166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -29945,14 +30309,18 @@
       </c>
       <c r="AC166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD166" s="12"/>
-      <c r="AE166" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF166" s="6" t="s">
-        <v>104</v>
+        <v>206800</v>
+      </c>
+      <c r="AD166" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 47 000 €</v>
+      </c>
+      <c r="AE166" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R166,0),"### ### ##0 €")</f>
+        <v>6 mois = 94 000 €</v>
+      </c>
+      <c r="AF166" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG166" s="12" t="s">
         <v>365</v>
@@ -29964,203 +30332,225 @@
         <v>372</v>
       </c>
       <c r="AJ166" s="10" t="s">
-        <v>1205</v>
+        <v>1180</v>
       </c>
       <c r="AK166" s="11" t="s">
-        <v>1204</v>
+        <v>1251</v>
       </c>
       <c r="AL166" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM166" s="11" t="s">
-        <v>1200</v>
+        <v>1181</v>
       </c>
       <c r="AN166" s="11" t="s">
-        <v>1201</v>
+        <v>1182</v>
       </c>
       <c r="AO166" s="11" t="s">
-        <v>1155</v>
+        <v>1146</v>
       </c>
       <c r="AP166" s="36" t="s">
-        <v>1224</v>
+        <v>1274</v>
       </c>
       <c r="AQ166" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR166" s="11"/>
+      <c r="AR166" s="11" t="s">
+        <v>1250</v>
+      </c>
       <c r="AS166" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT166" s="14"/>
       <c r="AU166" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="167" spans="1:47" ht="25.5">
+    <row r="167" spans="1:47" ht="51">
       <c r="A167" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B167" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Val-de-Marne</v>
+        <v>Vaucluse</v>
       </c>
       <c r="C167" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E167" s="10">
+        <v>84140</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G167" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>330 Avenue Marcou Delanglade
+84140 - Avignon</v>
+      </c>
+      <c r="H167" s="15" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J167" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K167" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L167" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M167" s="36"/>
+      <c r="N167" s="34">
+        <v>616</v>
+      </c>
+      <c r="O167" s="6" t="s">
+        <v>1253</v>
+      </c>
+      <c r="P167" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q167" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R167" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>123200</v>
+      </c>
+      <c r="S167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>10266.666666666666</v>
+      </c>
+      <c r="T167" s="12">
+        <v>200</v>
+      </c>
+      <c r="U167" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="V167" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11088</v>
+      </c>
+      <c r="W167" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>924</v>
+      </c>
+      <c r="X167" s="12">
+        <v>18</v>
+      </c>
+      <c r="Y167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>8624</v>
+      </c>
+      <c r="Z167" s="12">
+        <v>14</v>
+      </c>
+      <c r="AA167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB167" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>142912</v>
+      </c>
+      <c r="AD167" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 30 800 €</v>
+      </c>
+      <c r="AE167" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R167,0),"### ### ##0 €")</f>
+        <v>6 mois = 61 600 €</v>
+      </c>
+      <c r="AF167" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG167" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="AH167" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI167" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="AJ167" s="10" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AK167" s="11" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AL167" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="AM167" s="11" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AN167" s="11" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AO167" s="11">
+        <v>46</v>
+      </c>
+      <c r="AP167" s="45" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AQ167" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR167" s="11" t="s">
+        <v>1252</v>
+      </c>
+      <c r="AS167" s="13" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT167" s="14"/>
+      <c r="AU167" s="44">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="168" spans="1:47" ht="38.25">
+      <c r="A168" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B168" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C168" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>94</v>
       </c>
-      <c r="D167" s="10" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E167" s="10">
+      <c r="D168" s="10" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E168" s="10">
         <v>94500</v>
       </c>
-      <c r="F167" s="10" t="s">
-        <v>1129</v>
-      </c>
-      <c r="G167" s="39" t="str">
+      <c r="F168" s="10" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G168" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>14 Rue Serpente
 94500 - Champigny-sur-Marne</v>
       </c>
-      <c r="H167" s="15" t="s">
+      <c r="H168" s="15" t="s">
         <v>1122</v>
       </c>
-      <c r="I167" s="12" t="s">
+      <c r="I168" s="12" t="s">
         <v>45</v>
-      </c>
-      <c r="J167" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="K167" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="L167" s="12"/>
-      <c r="M167" s="36"/>
-      <c r="N167" s="34">
-        <v>723</v>
-      </c>
-      <c r="O167" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="P167" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q167" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="R167" s="12"/>
-      <c r="S167" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T167" s="12"/>
-      <c r="U167" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="V167" s="12"/>
-      <c r="W167" s="12">
-        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X167" s="12"/>
-      <c r="Y167" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z167" s="12"/>
-      <c r="AA167" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB167" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC167" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD167" s="12"/>
-      <c r="AE167" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF167" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG167" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="AH167" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="AI167" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="AJ167" s="10" t="s">
-        <v>1205</v>
-      </c>
-      <c r="AK167" s="11" t="s">
-        <v>1204</v>
-      </c>
-      <c r="AL167" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="AM167" s="11" t="s">
-        <v>1202</v>
-      </c>
-      <c r="AN167" s="11" t="s">
-        <v>1203</v>
-      </c>
-      <c r="AO167" s="11" t="s">
-        <v>1156</v>
-      </c>
-      <c r="AP167" s="36" t="s">
-        <v>1225</v>
-      </c>
-      <c r="AQ167" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AR167" s="11"/>
-      <c r="AS167" s="13" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AT167" s="14"/>
-      <c r="AU167" s="44">
-        <v>46003</v>
-      </c>
-    </row>
-    <row r="168" spans="1:47" ht="25.5">
-      <c r="A168" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
-      </c>
-      <c r="B168" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Val-D'Oise</v>
-      </c>
-      <c r="C168" s="38">
-        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>95</v>
-      </c>
-      <c r="D168" s="10" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E168" s="10">
-        <v>95220</v>
-      </c>
-      <c r="F168" s="10" t="s">
-        <v>1132</v>
-      </c>
-      <c r="G168" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>8 Avenue Paul Langevin
-95220 - Herblay-sur-Seine</v>
-      </c>
-      <c r="H168" s="15" t="s">
-        <v>1206</v>
-      </c>
-      <c r="I168" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="J168" s="12" t="s">
         <v>48</v>
@@ -30168,10 +30558,12 @@
       <c r="K168" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L168" s="12"/>
+      <c r="L168" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="M168" s="36"/>
       <c r="N168" s="34">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="O168" s="6" t="s">
         <v>104</v>
@@ -30182,7 +30574,10 @@
       <c r="Q168" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R168" s="12"/>
+      <c r="R168" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="S168" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>0</v>
@@ -30191,7 +30586,10 @@
       <c r="U168" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V168" s="12"/>
+      <c r="V168" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W168" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -30213,12 +30611,16 @@
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>0</v>
       </c>
-      <c r="AD168" s="12"/>
-      <c r="AE168" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF168" s="6" t="s">
-        <v>104</v>
+      <c r="AD168" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 0 €</v>
+      </c>
+      <c r="AE168" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R168,0),"### ### ##0 €")</f>
+        <v>6 mois = 0 €</v>
+      </c>
+      <c r="AF168" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG168" s="12" t="s">
         <v>365</v>
@@ -30230,32 +30632,32 @@
         <v>372</v>
       </c>
       <c r="AJ168" s="10" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="AK168" s="11" t="s">
-        <v>1210</v>
+        <v>1260</v>
       </c>
       <c r="AL168" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM168" s="11" t="s">
-        <v>1207</v>
+        <v>1187</v>
       </c>
       <c r="AN168" s="11" t="s">
-        <v>1208</v>
-      </c>
-      <c r="AO168" s="11">
-        <v>48</v>
-      </c>
-      <c r="AP168" s="36" t="s">
-        <v>1226</v>
+        <v>1188</v>
+      </c>
+      <c r="AO168" s="11" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AP168" s="45" t="s">
+        <v>1276</v>
       </c>
       <c r="AQ168" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR168" s="11"/>
       <c r="AS168" s="13" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="AT168" s="14"/>
       <c r="AU168" s="44">
@@ -30265,144 +30667,620 @@
     <row r="169" spans="1:47" ht="38.25">
       <c r="A169" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Ile-de-France</v>
       </c>
       <c r="B169" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Bas-Rhin</v>
+        <v>Val-de-Marne</v>
       </c>
       <c r="C169" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E169" s="10">
+        <v>94500</v>
+      </c>
+      <c r="F169" s="10" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G169" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>13 Rue Serpente
+94500 - Champigny-sur-Marne</v>
+      </c>
+      <c r="H169" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K169" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L169" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M169" s="36"/>
+      <c r="N169" s="34">
+        <v>387</v>
+      </c>
+      <c r="O169" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P169" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q169" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R169" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>96750</v>
+      </c>
+      <c r="S169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>8062.5</v>
+      </c>
+      <c r="T169" s="12">
+        <v>250</v>
+      </c>
+      <c r="U169" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="V169" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2322</v>
+      </c>
+      <c r="W169" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>193.5</v>
+      </c>
+      <c r="X169" s="12">
+        <v>6</v>
+      </c>
+      <c r="Y169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>5418</v>
+      </c>
+      <c r="Z169" s="12">
+        <v>14</v>
+      </c>
+      <c r="AA169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB169" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>104490</v>
+      </c>
+      <c r="AD169" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 24 188 €</v>
+      </c>
+      <c r="AE169" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R169,0),"### ### ##0 €")</f>
+        <v>6 mois = 48 375 €</v>
+      </c>
+      <c r="AF169" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG169" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="AH169" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI169" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="AJ169" s="10" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AK169" s="11" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AL169" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="AM169" s="11" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AN169" s="11" t="s">
+        <v>1257</v>
+      </c>
+      <c r="AO169" s="11" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP169" s="36" t="s">
+        <v>1277</v>
+      </c>
+      <c r="AQ169" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR169" s="11" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AS169" s="13" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT169" s="14"/>
+      <c r="AU169" s="44">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="170" spans="1:47" ht="38.25">
+      <c r="A170" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B170" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C170" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E170" s="10">
+        <v>94500</v>
+      </c>
+      <c r="F170" s="10" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G170" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>14 Rue Serpente
+94500 - Champigny-sur-Marne</v>
+      </c>
+      <c r="H170" s="15" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J170" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K170" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L170" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M170" s="36"/>
+      <c r="N170" s="34">
+        <v>723</v>
+      </c>
+      <c r="O170" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P170" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q170" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R170" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>162675</v>
+      </c>
+      <c r="S170" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>13556.25</v>
+      </c>
+      <c r="T170" s="12">
+        <v>225</v>
+      </c>
+      <c r="U170" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="V170" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>4338</v>
+      </c>
+      <c r="W170" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>361.5</v>
+      </c>
+      <c r="X170" s="12">
+        <v>6</v>
+      </c>
+      <c r="Y170" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>9399</v>
+      </c>
+      <c r="Z170" s="12">
+        <v>13</v>
+      </c>
+      <c r="AA170" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB170" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC170" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>176412</v>
+      </c>
+      <c r="AD170" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 40 669 €</v>
+      </c>
+      <c r="AE170" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R170,0),"### ### ##0 €")</f>
+        <v>6 mois = 81 338 €</v>
+      </c>
+      <c r="AF170" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG170" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="AH170" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI170" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="AJ170" s="10" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AK170" s="11" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AL170" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="AM170" s="11" t="s">
+        <v>1189</v>
+      </c>
+      <c r="AN170" s="11" t="s">
+        <v>1190</v>
+      </c>
+      <c r="AO170" s="11" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AP170" s="36" t="s">
+        <v>1278</v>
+      </c>
+      <c r="AQ170" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR170" s="11" t="s">
+        <v>1258</v>
+      </c>
+      <c r="AS170" s="13" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT170" s="14"/>
+      <c r="AU170" s="44">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="171" spans="1:47" ht="25.5">
+      <c r="A171" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B171" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-D'Oise</v>
+      </c>
+      <c r="C171" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>95</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E171" s="10">
+        <v>95220</v>
+      </c>
+      <c r="F171" s="10" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G171" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>8 Avenue Paul Langevin
+95220 - Herblay-sur-Seine</v>
+      </c>
+      <c r="H171" s="15" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J171" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K171" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L171" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M171" s="36"/>
+      <c r="N171" s="34">
+        <v>402</v>
+      </c>
+      <c r="O171" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P171" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q171" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R171" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>180900</v>
+      </c>
+      <c r="S171" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>15075</v>
+      </c>
+      <c r="T171" s="12">
+        <v>450</v>
+      </c>
+      <c r="U171" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="V171" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3618</v>
+      </c>
+      <c r="W171" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>301.5</v>
+      </c>
+      <c r="X171" s="12">
+        <v>9</v>
+      </c>
+      <c r="Y171" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>5226</v>
+      </c>
+      <c r="Z171" s="12">
+        <v>13</v>
+      </c>
+      <c r="AA171" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB171" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC171" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>189744</v>
+      </c>
+      <c r="AD171" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 45 225 €</v>
+      </c>
+      <c r="AE171" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R171,0),"### ### ##0 €")</f>
+        <v>6 mois = 90 450 €</v>
+      </c>
+      <c r="AF171" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG171" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="AH171" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI171" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="AJ171" s="10" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AK171" s="11" t="s">
+        <v>1261</v>
+      </c>
+      <c r="AL171" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="AM171" s="11" t="s">
+        <v>1193</v>
+      </c>
+      <c r="AN171" s="11" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AO171" s="11">
+        <v>48</v>
+      </c>
+      <c r="AP171" s="36" t="s">
+        <v>1279</v>
+      </c>
+      <c r="AQ171" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR171" s="11" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AS171" s="13" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT171" s="14"/>
+      <c r="AU171" s="44">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="172" spans="1:47" ht="38.25">
+      <c r="A172" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B172" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Bas-Rhin</v>
+      </c>
+      <c r="C172" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>67</v>
       </c>
-      <c r="D169" s="11" t="s">
-        <v>1234</v>
-      </c>
-      <c r="E169" s="10">
+      <c r="D172" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E172" s="10">
         <v>6700</v>
       </c>
-      <c r="F169" s="10" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G169" s="39" t="str">
+      <c r="F172" s="10" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G172" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>CAP 3000
 217 Av. Eugène Donadeï
 6700 - Saint-Laurent-du-Var</v>
       </c>
-      <c r="H169" s="46" t="s">
-        <v>1235</v>
-      </c>
-      <c r="I169" s="12" t="s">
+      <c r="H172" s="15" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I172" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J169" s="12" t="s">
+      <c r="J172" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K169" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="L169" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M169" s="36"/>
-      <c r="N169" s="34">
-        <v>80</v>
-      </c>
-      <c r="O169" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="P169" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q169" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="R169" s="12"/>
-      <c r="S169" s="12">
+      <c r="K172" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L172" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="M172" s="36"/>
+      <c r="N172" s="34">
+        <v>126</v>
+      </c>
+      <c r="O172" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="P172" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q172" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R172" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>139986</v>
+      </c>
+      <c r="S172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T169" s="12"/>
-      <c r="U169" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="V169" s="12"/>
-      <c r="W169" s="12">
+        <v>11665.5</v>
+      </c>
+      <c r="T172" s="12">
+        <v>1111</v>
+      </c>
+      <c r="U172" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="V172" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>20790</v>
+      </c>
+      <c r="W172" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X169" s="12"/>
-      <c r="Y169" s="12">
+        <v>1732.5</v>
+      </c>
+      <c r="X172" s="12">
+        <v>165</v>
+      </c>
+      <c r="Y172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z169" s="12"/>
-      <c r="AA169" s="12">
+        <v>4536</v>
+      </c>
+      <c r="Z172" s="12">
+        <v>36</v>
+      </c>
+      <c r="AA172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB169" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC169" s="12">
+      <c r="AB172" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD169" s="12"/>
-      <c r="AE169" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF169" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG169" s="12" t="s">
+        <v>165312</v>
+      </c>
+      <c r="AD172" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 34 997 €</v>
+      </c>
+      <c r="AE172" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF172" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG172" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="AH169" s="10" t="s">
+      <c r="AH172" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AI169" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="AJ169" s="10" t="s">
-        <v>1238</v>
-      </c>
-      <c r="AK169" s="11" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AL169" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="AM169" s="11" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AN169" s="11" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AO169" s="11">
+      <c r="AI172" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ172" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="AK172" s="11" t="s">
+        <v>1205</v>
+      </c>
+      <c r="AL172" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AM172" s="11" t="s">
+        <v>1207</v>
+      </c>
+      <c r="AN172" s="11" t="s">
+        <v>1208</v>
+      </c>
+      <c r="AO172" s="11">
         <v>49</v>
       </c>
-      <c r="AP169" s="36"/>
-      <c r="AQ169" s="11" t="s">
+      <c r="AP172" s="36" t="s">
+        <v>1280</v>
+      </c>
+      <c r="AQ172" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AR169" s="11"/>
-      <c r="AS169" s="13" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AT169" s="14"/>
-      <c r="AU169" s="44">
+      <c r="AR172" s="11"/>
+      <c r="AS172" s="13" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AT172" s="14"/>
+      <c r="AU172" s="44">
         <v>46010</v>
       </c>
     </row>
-    <row r="174" spans="1:47">
-      <c r="F174" s="1" t="s">
+    <row r="177" spans="6:6">
+      <c r="F177" s="1" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="175" spans="1:47">
-      <c r="F175" s="1" t="s">
+    <row r="178" spans="6:6">
+      <c r="F178" s="1" t="s">
         <v>1038</v>
       </c>
     </row>
@@ -30528,21 +31406,25 @@
     <hyperlink ref="H151" r:id="rId117" xr:uid="{6B38E304-7485-42E7-9EFC-3CDA0B79C692}"/>
     <hyperlink ref="H152" r:id="rId118" xr:uid="{9BAD643D-2774-4811-AF7F-3253EB54E8FC}"/>
     <hyperlink ref="H153" r:id="rId119" xr:uid="{8C4EE05C-7B50-4EF6-B2F7-FACAB92DA663}"/>
-    <hyperlink ref="H154" r:id="rId120" xr:uid="{0D1E98E9-4BCF-4406-AFDA-600010FB176B}"/>
-    <hyperlink ref="H155" r:id="rId121" xr:uid="{580F9DBE-E800-4F84-BEDC-E8B38FD61F7A}"/>
-    <hyperlink ref="H156" r:id="rId122" xr:uid="{372123E9-8C5B-4111-8443-C1645E86AD4D}"/>
-    <hyperlink ref="H157" r:id="rId123" xr:uid="{CC20D8BA-62C0-4205-8CD5-E236C90A7669}"/>
-    <hyperlink ref="H158" r:id="rId124" xr:uid="{C2AFB330-1F62-4366-8E85-4A36FC54F3CA}"/>
-    <hyperlink ref="H159" r:id="rId125" xr:uid="{D9CEB66C-2A2B-4C50-90E4-25DDB2866B82}"/>
-    <hyperlink ref="H160" r:id="rId126" xr:uid="{77194CDF-321B-4F1D-8892-C65AB2918B74}"/>
-    <hyperlink ref="H161" r:id="rId127" xr:uid="{A510C509-E61B-4228-AC93-D0093532C7D2}"/>
-    <hyperlink ref="H162" r:id="rId128" xr:uid="{13D66F57-470F-41F4-93A6-03D5A2A4CCDB}"/>
-    <hyperlink ref="H163" r:id="rId129" xr:uid="{5B7EA501-9646-45C8-A6A4-6075F4FADE70}"/>
-    <hyperlink ref="H164" r:id="rId130" xr:uid="{6D822EC9-F492-4D93-A1BA-8FA65E1327B7}"/>
-    <hyperlink ref="H166" r:id="rId131" xr:uid="{3C8BCE0A-AAD1-4E3F-915C-B7BFA9B07703}"/>
-    <hyperlink ref="H167" r:id="rId132" xr:uid="{EB1761D0-DA2C-4FCB-8A87-DC3BF56A199A}"/>
-    <hyperlink ref="H165" r:id="rId133" xr:uid="{AC7B9731-155A-409D-B7DE-6A2C81027D18}"/>
-    <hyperlink ref="H168" r:id="rId134" xr:uid="{ED7C6A33-7CA0-4B59-BFC3-713467DF5837}"/>
+    <hyperlink ref="H157" r:id="rId120" xr:uid="{0D1E98E9-4BCF-4406-AFDA-600010FB176B}"/>
+    <hyperlink ref="H158" r:id="rId121" xr:uid="{580F9DBE-E800-4F84-BEDC-E8B38FD61F7A}"/>
+    <hyperlink ref="H159" r:id="rId122" xr:uid="{372123E9-8C5B-4111-8443-C1645E86AD4D}"/>
+    <hyperlink ref="H160" r:id="rId123" xr:uid="{CC20D8BA-62C0-4205-8CD5-E236C90A7669}"/>
+    <hyperlink ref="H161" r:id="rId124" xr:uid="{C2AFB330-1F62-4366-8E85-4A36FC54F3CA}"/>
+    <hyperlink ref="H162" r:id="rId125" xr:uid="{D9CEB66C-2A2B-4C50-90E4-25DDB2866B82}"/>
+    <hyperlink ref="H163" r:id="rId126" xr:uid="{77194CDF-321B-4F1D-8892-C65AB2918B74}"/>
+    <hyperlink ref="H164" r:id="rId127" xr:uid="{A510C509-E61B-4228-AC93-D0093532C7D2}"/>
+    <hyperlink ref="H165" r:id="rId128" xr:uid="{13D66F57-470F-41F4-93A6-03D5A2A4CCDB}"/>
+    <hyperlink ref="H166" r:id="rId129" xr:uid="{5B7EA501-9646-45C8-A6A4-6075F4FADE70}"/>
+    <hyperlink ref="H167" r:id="rId130" xr:uid="{6D822EC9-F492-4D93-A1BA-8FA65E1327B7}"/>
+    <hyperlink ref="H169" r:id="rId131" xr:uid="{3C8BCE0A-AAD1-4E3F-915C-B7BFA9B07703}"/>
+    <hyperlink ref="H170" r:id="rId132" xr:uid="{EB1761D0-DA2C-4FCB-8A87-DC3BF56A199A}"/>
+    <hyperlink ref="H168" r:id="rId133" xr:uid="{AC7B9731-155A-409D-B7DE-6A2C81027D18}"/>
+    <hyperlink ref="H171" r:id="rId134" xr:uid="{ED7C6A33-7CA0-4B59-BFC3-713467DF5837}"/>
+    <hyperlink ref="H154" r:id="rId135" xr:uid="{84DBA056-5C11-4ECE-9D32-78D0DE5AACCA}"/>
+    <hyperlink ref="H155" r:id="rId136" xr:uid="{3F6F7192-2423-4CFD-AC54-5D69482DCDAA}"/>
+    <hyperlink ref="H156" r:id="rId137" xr:uid="{34F05E83-B67A-4D2E-97A2-715EF4DB16F0}"/>
+    <hyperlink ref="H172" r:id="rId138" xr:uid="{0DCDD234-61DD-4535-96A0-1CB0ED1C39E2}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -30551,7 +31433,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId135"/>
+    <tablePart r:id="rId139"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700039E2-141F-40C6-9362-33DADD86C1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207ACF22-7DB6-4C4A-A218-654013AA3549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -2423,9 +2423,6 @@
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/11%20-%20Paris/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/11%20-%20Paris/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/11%20-%20Paris/3%20Plan%20RDC.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/11%20-%20Paris/4%20Plan%20R%C3%A9serves%20d%C3%A9port%C3%A9es%20R%20-2.jpg</t>
   </si>
   <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/1%20Vue%20d'ensemble.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/1%20Vue%20d'ensemble.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/5%20Plan.jpg</t>
-  </si>
-  <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/14%20-%20Paris/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/14%20-%20Paris/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/14%20-%20Paris/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/14%20-%20Paris/4%20Plan%20R%20-1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/14%20-%20Paris/5%20Plan%20RDC.jpg</t>
   </si>
   <si>
@@ -3837,9 +3834,6 @@
     <t>74 + 52 (mezz)</t>
   </si>
   <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/6.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/7.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/8%20Plan.jpg</t>
-  </si>
-  <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/5%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.2%20-%20Vitrolles/6%20Plan.jpg</t>
   </si>
   <si>
@@ -3888,7 +3882,13 @@
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/5%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/48%20-%20Herblay-sur-Seine/6%20Plan.jpg</t>
   </si>
   <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/1.JPG; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/2.JPG; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/3.JPG; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/4%20Plan%20de%20situation.png</t>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/1.JPG; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/49%20-%20Saint-Laurent-du-Var/4%20Plan%20de%20situation.png</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36%20-%20Vitrolles/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/6.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/7.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/36.1%20-%20Vitrolles/8%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/1%20Vue%20d'ensemble.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/12%20-%20Paris/5%20Plan.jpg</t>
   </si>
 </sst>
 </file>
@@ -5105,7 +5105,7 @@
         <v>12</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
@@ -12623,7 +12623,7 @@
         <v>310</v>
       </c>
       <c r="AP50" s="35" t="s">
-        <v>792</v>
+        <v>1280</v>
       </c>
       <c r="AQ50" s="5" t="s">
         <v>76</v>
@@ -12929,7 +12929,7 @@
         <v>490</v>
       </c>
       <c r="AP52" s="35" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AQ52" s="5" t="s">
         <v>76</v>
@@ -13083,7 +13083,7 @@
         <v>491</v>
       </c>
       <c r="AP53" s="35" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AQ53" s="5" t="s">
         <v>76</v>
@@ -13237,7 +13237,7 @@
         <v>492</v>
       </c>
       <c r="AP54" s="35" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AQ54" s="5" t="s">
         <v>76</v>
@@ -13391,7 +13391,7 @@
         <v>493</v>
       </c>
       <c r="AP55" s="35" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AQ55" s="5" t="s">
         <v>76</v>
@@ -13545,7 +13545,7 @@
         <v>494</v>
       </c>
       <c r="AP56" s="35" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AQ56" s="5" t="s">
         <v>76</v>
@@ -13700,7 +13700,7 @@
         <v>495</v>
       </c>
       <c r="AP57" s="35" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AQ57" s="5" t="s">
         <v>76</v>
@@ -13855,7 +13855,7 @@
         <v>496</v>
       </c>
       <c r="AP58" s="35" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AQ58" s="5" t="s">
         <v>76</v>
@@ -14010,7 +14010,7 @@
         <v>497</v>
       </c>
       <c r="AP59" s="35" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AQ59" s="5" t="s">
         <v>76</v>
@@ -14165,7 +14165,7 @@
         <v>498</v>
       </c>
       <c r="AP60" s="35" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AQ60" s="5" t="s">
         <v>76</v>
@@ -14320,7 +14320,7 @@
         <v>499</v>
       </c>
       <c r="AP61" s="35" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AQ61" s="5" t="s">
         <v>76</v>
@@ -14475,7 +14475,7 @@
         <v>500</v>
       </c>
       <c r="AP62" s="35" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="AQ62" s="5" t="s">
         <v>76</v>
@@ -14630,7 +14630,7 @@
         <v>501</v>
       </c>
       <c r="AP63" s="35" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AQ63" s="5" t="s">
         <v>76</v>
@@ -14785,7 +14785,7 @@
         <v>502</v>
       </c>
       <c r="AP64" s="35" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AQ64" s="5" t="s">
         <v>76</v>
@@ -14939,7 +14939,7 @@
         <v>503</v>
       </c>
       <c r="AP65" s="35" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AQ65" s="5" t="s">
         <v>76</v>
@@ -15093,7 +15093,7 @@
         <v>504</v>
       </c>
       <c r="AP66" s="36" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AQ66" s="5" t="s">
         <v>76</v>
@@ -15138,7 +15138,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>45</v>
@@ -15153,7 +15153,7 @@
         <v>104</v>
       </c>
       <c r="M67" s="35" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N67" s="34">
         <v>321</v>
@@ -15230,7 +15230,7 @@
         <v>372</v>
       </c>
       <c r="AJ67" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK67" s="5" t="s">
         <v>358</v>
@@ -15239,16 +15239,16 @@
         <v>370</v>
       </c>
       <c r="AM67" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="AN67" s="5" t="s">
         <v>864</v>
-      </c>
-      <c r="AN67" s="5" t="s">
-        <v>865</v>
       </c>
       <c r="AO67" s="32" t="s">
         <v>505</v>
       </c>
       <c r="AP67" s="35" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AQ67" s="5" t="s">
         <v>76</v>
@@ -15293,7 +15293,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>45</v>
@@ -15308,7 +15308,7 @@
         <v>104</v>
       </c>
       <c r="M68" s="36" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N68" s="34">
         <v>159</v>
@@ -15385,7 +15385,7 @@
         <v>372</v>
       </c>
       <c r="AJ68" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK68" s="5" t="s">
         <v>358</v>
@@ -15394,16 +15394,16 @@
         <v>370</v>
       </c>
       <c r="AM68" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="AN68" s="11" t="s">
         <v>866</v>
-      </c>
-      <c r="AN68" s="11" t="s">
-        <v>867</v>
       </c>
       <c r="AO68" s="32" t="s">
         <v>506</v>
       </c>
       <c r="AP68" s="35" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AQ68" s="5" t="s">
         <v>76</v>
@@ -15448,7 +15448,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>45</v>
@@ -15463,7 +15463,7 @@
         <v>104</v>
       </c>
       <c r="M69" s="36" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="N69" s="34">
         <v>281</v>
@@ -15540,7 +15540,7 @@
         <v>372</v>
       </c>
       <c r="AJ69" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK69" s="5" t="s">
         <v>358</v>
@@ -15549,16 +15549,16 @@
         <v>370</v>
       </c>
       <c r="AM69" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="AN69" s="11" t="s">
         <v>868</v>
-      </c>
-      <c r="AN69" s="11" t="s">
-        <v>869</v>
       </c>
       <c r="AO69" s="32" t="s">
         <v>507</v>
       </c>
       <c r="AP69" s="35" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="AQ69" s="5" t="s">
         <v>76</v>
@@ -15603,7 +15603,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>45</v>
@@ -15618,7 +15618,7 @@
         <v>104</v>
       </c>
       <c r="M70" s="36" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N70" s="34">
         <v>168</v>
@@ -15695,7 +15695,7 @@
         <v>372</v>
       </c>
       <c r="AJ70" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK70" s="5" t="s">
         <v>358</v>
@@ -15704,16 +15704,16 @@
         <v>370</v>
       </c>
       <c r="AM70" s="11" t="s">
+        <v>869</v>
+      </c>
+      <c r="AN70" s="11" t="s">
         <v>870</v>
-      </c>
-      <c r="AN70" s="11" t="s">
-        <v>871</v>
       </c>
       <c r="AO70" s="32" t="s">
         <v>508</v>
       </c>
       <c r="AP70" s="35" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AQ70" s="5" t="s">
         <v>76</v>
@@ -15758,7 +15758,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>45</v>
@@ -15850,7 +15850,7 @@
         <v>372</v>
       </c>
       <c r="AJ71" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK71" s="5" t="s">
         <v>358</v>
@@ -15859,16 +15859,16 @@
         <v>370</v>
       </c>
       <c r="AM71" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="AN71" s="11" t="s">
         <v>848</v>
-      </c>
-      <c r="AN71" s="11" t="s">
-        <v>849</v>
       </c>
       <c r="AO71" s="32" t="s">
         <v>509</v>
       </c>
       <c r="AP71" s="35" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="AQ71" s="5" t="s">
         <v>76</v>
@@ -15913,7 +15913,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>45</v>
@@ -16005,7 +16005,7 @@
         <v>372</v>
       </c>
       <c r="AJ72" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK72" s="5" t="s">
         <v>358</v>
@@ -16014,16 +16014,16 @@
         <v>370</v>
       </c>
       <c r="AM72" s="11" t="s">
+        <v>849</v>
+      </c>
+      <c r="AN72" s="11" t="s">
         <v>850</v>
-      </c>
-      <c r="AN72" s="11" t="s">
-        <v>851</v>
       </c>
       <c r="AO72" s="32" t="s">
         <v>510</v>
       </c>
       <c r="AP72" s="35" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="AQ72" s="5" t="s">
         <v>76</v>
@@ -16068,7 +16068,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>45</v>
@@ -16160,7 +16160,7 @@
         <v>372</v>
       </c>
       <c r="AJ73" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK73" s="5" t="s">
         <v>358</v>
@@ -16169,16 +16169,16 @@
         <v>370</v>
       </c>
       <c r="AM73" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="AN73" s="11" t="s">
         <v>846</v>
-      </c>
-      <c r="AN73" s="11" t="s">
-        <v>847</v>
       </c>
       <c r="AO73" s="32" t="s">
         <v>511</v>
       </c>
       <c r="AP73" s="35" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="AQ73" s="5" t="s">
         <v>76</v>
@@ -16223,7 +16223,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>45</v>
@@ -16315,7 +16315,7 @@
         <v>372</v>
       </c>
       <c r="AJ74" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK74" s="5" t="s">
         <v>358</v>
@@ -16324,16 +16324,16 @@
         <v>370</v>
       </c>
       <c r="AM74" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="AN74" s="11" t="s">
         <v>852</v>
-      </c>
-      <c r="AN74" s="11" t="s">
-        <v>853</v>
       </c>
       <c r="AO74" s="32" t="s">
         <v>512</v>
       </c>
       <c r="AP74" s="35" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AQ74" s="5" t="s">
         <v>76</v>
@@ -16378,7 +16378,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>45</v>
@@ -16470,7 +16470,7 @@
         <v>372</v>
       </c>
       <c r="AJ75" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK75" s="5" t="s">
         <v>358</v>
@@ -16479,16 +16479,16 @@
         <v>370</v>
       </c>
       <c r="AM75" s="11" t="s">
+        <v>853</v>
+      </c>
+      <c r="AN75" s="11" t="s">
         <v>854</v>
-      </c>
-      <c r="AN75" s="11" t="s">
-        <v>855</v>
       </c>
       <c r="AO75" s="32" t="s">
         <v>513</v>
       </c>
       <c r="AP75" s="35" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="AQ75" s="5" t="s">
         <v>76</v>
@@ -16533,7 +16533,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>45</v>
@@ -16625,7 +16625,7 @@
         <v>372</v>
       </c>
       <c r="AJ76" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK76" s="5" t="s">
         <v>358</v>
@@ -16634,16 +16634,16 @@
         <v>370</v>
       </c>
       <c r="AM76" s="11" t="s">
+        <v>855</v>
+      </c>
+      <c r="AN76" s="11" t="s">
         <v>856</v>
-      </c>
-      <c r="AN76" s="11" t="s">
-        <v>857</v>
       </c>
       <c r="AO76" s="32" t="s">
         <v>514</v>
       </c>
       <c r="AP76" s="35" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="AQ76" s="5" t="s">
         <v>76</v>
@@ -16688,7 +16688,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H77" s="15" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>45</v>
@@ -16780,7 +16780,7 @@
         <v>372</v>
       </c>
       <c r="AJ77" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK77" s="5" t="s">
         <v>358</v>
@@ -16789,16 +16789,16 @@
         <v>370</v>
       </c>
       <c r="AM77" s="11" t="s">
+        <v>857</v>
+      </c>
+      <c r="AN77" s="11" t="s">
         <v>858</v>
-      </c>
-      <c r="AN77" s="11" t="s">
-        <v>859</v>
       </c>
       <c r="AO77" s="32" t="s">
         <v>515</v>
       </c>
       <c r="AP77" s="35" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AQ77" s="5" t="s">
         <v>76</v>
@@ -16843,7 +16843,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>45</v>
@@ -16935,7 +16935,7 @@
         <v>372</v>
       </c>
       <c r="AJ78" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK78" s="5" t="s">
         <v>358</v>
@@ -16944,16 +16944,16 @@
         <v>370</v>
       </c>
       <c r="AM78" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="AN78" s="11" t="s">
         <v>822</v>
-      </c>
-      <c r="AN78" s="11" t="s">
-        <v>823</v>
       </c>
       <c r="AO78" s="32" t="s">
         <v>516</v>
       </c>
       <c r="AP78" s="35" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="AQ78" s="5" t="s">
         <v>76</v>
@@ -16998,7 +16998,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>45</v>
@@ -17090,7 +17090,7 @@
         <v>372</v>
       </c>
       <c r="AJ79" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK79" s="5" t="s">
         <v>358</v>
@@ -17099,16 +17099,16 @@
         <v>370</v>
       </c>
       <c r="AM79" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="AN79" s="11" t="s">
         <v>824</v>
-      </c>
-      <c r="AN79" s="11" t="s">
-        <v>825</v>
       </c>
       <c r="AO79" s="32" t="s">
         <v>517</v>
       </c>
       <c r="AP79" s="35" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="AQ79" s="5" t="s">
         <v>76</v>
@@ -17153,7 +17153,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>45</v>
@@ -17245,7 +17245,7 @@
         <v>372</v>
       </c>
       <c r="AJ80" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK80" s="5" t="s">
         <v>358</v>
@@ -17254,16 +17254,16 @@
         <v>370</v>
       </c>
       <c r="AM80" s="11" t="s">
+        <v>825</v>
+      </c>
+      <c r="AN80" s="11" t="s">
         <v>826</v>
-      </c>
-      <c r="AN80" s="11" t="s">
-        <v>827</v>
       </c>
       <c r="AO80" s="32" t="s">
         <v>518</v>
       </c>
       <c r="AP80" s="35" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="AQ80" s="5" t="s">
         <v>76</v>
@@ -17308,7 +17308,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H81" s="15" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>45</v>
@@ -17400,7 +17400,7 @@
         <v>372</v>
       </c>
       <c r="AJ81" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK81" s="5" t="s">
         <v>358</v>
@@ -17409,16 +17409,16 @@
         <v>370</v>
       </c>
       <c r="AM81" s="11" t="s">
+        <v>827</v>
+      </c>
+      <c r="AN81" s="11" t="s">
         <v>828</v>
-      </c>
-      <c r="AN81" s="11" t="s">
-        <v>829</v>
       </c>
       <c r="AO81" s="32" t="s">
         <v>519</v>
       </c>
       <c r="AP81" s="35" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="AQ81" s="5" t="s">
         <v>76</v>
@@ -17463,7 +17463,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>45</v>
@@ -17555,7 +17555,7 @@
         <v>372</v>
       </c>
       <c r="AJ82" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK82" s="5" t="s">
         <v>358</v>
@@ -17564,16 +17564,16 @@
         <v>370</v>
       </c>
       <c r="AM82" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="AN82" s="11" t="s">
         <v>830</v>
-      </c>
-      <c r="AN82" s="11" t="s">
-        <v>831</v>
       </c>
       <c r="AO82" s="32" t="s">
         <v>520</v>
       </c>
       <c r="AP82" s="35" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="AQ82" s="5" t="s">
         <v>76</v>
@@ -17618,7 +17618,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>45</v>
@@ -17710,7 +17710,7 @@
         <v>372</v>
       </c>
       <c r="AJ83" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK83" s="5" t="s">
         <v>358</v>
@@ -17719,16 +17719,16 @@
         <v>370</v>
       </c>
       <c r="AM83" s="11" t="s">
+        <v>831</v>
+      </c>
+      <c r="AN83" s="11" t="s">
         <v>832</v>
-      </c>
-      <c r="AN83" s="11" t="s">
-        <v>833</v>
       </c>
       <c r="AO83" s="32" t="s">
         <v>521</v>
       </c>
       <c r="AP83" s="35" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AQ83" s="5" t="s">
         <v>76</v>
@@ -17773,7 +17773,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>45</v>
@@ -17865,7 +17865,7 @@
         <v>372</v>
       </c>
       <c r="AJ84" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK84" s="5" t="s">
         <v>358</v>
@@ -17874,16 +17874,16 @@
         <v>370</v>
       </c>
       <c r="AM84" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="AN84" s="11" t="s">
         <v>834</v>
-      </c>
-      <c r="AN84" s="11" t="s">
-        <v>835</v>
       </c>
       <c r="AO84" s="32" t="s">
         <v>522</v>
       </c>
       <c r="AP84" s="35" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="AQ84" s="5" t="s">
         <v>76</v>
@@ -17928,7 +17928,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H85" s="15" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>45</v>
@@ -18020,7 +18020,7 @@
         <v>372</v>
       </c>
       <c r="AJ85" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK85" s="5" t="s">
         <v>358</v>
@@ -18029,16 +18029,16 @@
         <v>370</v>
       </c>
       <c r="AM85" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="AN85" s="11" t="s">
         <v>836</v>
-      </c>
-      <c r="AN85" s="11" t="s">
-        <v>837</v>
       </c>
       <c r="AO85" s="32" t="s">
         <v>523</v>
       </c>
       <c r="AP85" s="35" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="AQ85" s="5" t="s">
         <v>76</v>
@@ -18083,7 +18083,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>45</v>
@@ -18175,7 +18175,7 @@
         <v>372</v>
       </c>
       <c r="AJ86" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK86" s="5" t="s">
         <v>358</v>
@@ -18184,16 +18184,16 @@
         <v>370</v>
       </c>
       <c r="AM86" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="AN86" s="11" t="s">
         <v>838</v>
-      </c>
-      <c r="AN86" s="11" t="s">
-        <v>839</v>
       </c>
       <c r="AO86" s="32" t="s">
         <v>524</v>
       </c>
       <c r="AP86" s="35" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AQ86" s="5" t="s">
         <v>76</v>
@@ -18238,7 +18238,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>45</v>
@@ -18330,7 +18330,7 @@
         <v>372</v>
       </c>
       <c r="AJ87" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK87" s="5" t="s">
         <v>358</v>
@@ -18339,16 +18339,16 @@
         <v>370</v>
       </c>
       <c r="AM87" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="AN87" s="11" t="s">
         <v>840</v>
-      </c>
-      <c r="AN87" s="11" t="s">
-        <v>841</v>
       </c>
       <c r="AO87" s="32" t="s">
         <v>525</v>
       </c>
       <c r="AP87" s="35" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AQ87" s="5" t="s">
         <v>76</v>
@@ -18393,7 +18393,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>45</v>
@@ -18485,7 +18485,7 @@
         <v>372</v>
       </c>
       <c r="AJ88" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK88" s="5" t="s">
         <v>358</v>
@@ -18494,16 +18494,16 @@
         <v>370</v>
       </c>
       <c r="AM88" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="AN88" s="11" t="s">
         <v>842</v>
-      </c>
-      <c r="AN88" s="11" t="s">
-        <v>843</v>
       </c>
       <c r="AO88" s="32" t="s">
         <v>526</v>
       </c>
       <c r="AP88" s="35" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AQ88" s="5" t="s">
         <v>76</v>
@@ -18548,7 +18548,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>45</v>
@@ -18640,7 +18640,7 @@
         <v>372</v>
       </c>
       <c r="AJ89" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AK89" s="5" t="s">
         <v>358</v>
@@ -18649,16 +18649,16 @@
         <v>370</v>
       </c>
       <c r="AM89" s="11" t="s">
+        <v>843</v>
+      </c>
+      <c r="AN89" s="11" t="s">
         <v>844</v>
-      </c>
-      <c r="AN89" s="11" t="s">
-        <v>845</v>
       </c>
       <c r="AO89" s="32" t="s">
         <v>527</v>
       </c>
       <c r="AP89" s="35" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="AQ89" s="5" t="s">
         <v>76</v>
@@ -18812,7 +18812,7 @@
         <v>528</v>
       </c>
       <c r="AP90" s="35" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AQ90" s="5" t="s">
         <v>76</v>
@@ -18966,7 +18966,7 @@
         <v>529</v>
       </c>
       <c r="AP91" s="35" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AQ91" s="5" t="s">
         <v>76</v>
@@ -19120,7 +19120,7 @@
         <v>530</v>
       </c>
       <c r="AP92" s="35" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AQ92" s="5" t="s">
         <v>76</v>
@@ -19274,7 +19274,7 @@
         <v>531</v>
       </c>
       <c r="AP93" s="36" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AQ93" s="5" t="s">
         <v>76</v>
@@ -19428,7 +19428,7 @@
         <v>532</v>
       </c>
       <c r="AP94" s="36" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AQ94" s="5" t="s">
         <v>76</v>
@@ -19582,7 +19582,7 @@
         <v>533</v>
       </c>
       <c r="AP95" s="36" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AQ95" s="5" t="s">
         <v>76</v>
@@ -19736,7 +19736,7 @@
         <v>534</v>
       </c>
       <c r="AP96" s="36" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AQ96" s="5" t="s">
         <v>76</v>
@@ -19890,7 +19890,7 @@
         <v>712</v>
       </c>
       <c r="AP97" s="36" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AQ97" s="5" t="s">
         <v>76</v>
@@ -20045,7 +20045,7 @@
         <v>535</v>
       </c>
       <c r="AP98" s="35" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AQ98" s="5" t="s">
         <v>76</v>
@@ -20200,7 +20200,7 @@
         <v>536</v>
       </c>
       <c r="AP99" s="35" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="AQ99" s="5" t="s">
         <v>76</v>
@@ -20355,7 +20355,7 @@
         <v>537</v>
       </c>
       <c r="AP100" s="35" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AQ100" s="5" t="s">
         <v>76</v>
@@ -20510,7 +20510,7 @@
         <v>538</v>
       </c>
       <c r="AP101" s="35" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AQ101" s="5" t="s">
         <v>76</v>
@@ -20665,7 +20665,7 @@
         <v>539</v>
       </c>
       <c r="AP102" s="35" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AQ102" s="5" t="s">
         <v>76</v>
@@ -20819,7 +20819,7 @@
         <v>540</v>
       </c>
       <c r="AP103" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ103" s="5" t="s">
         <v>76</v>
@@ -20973,7 +20973,7 @@
         <v>541</v>
       </c>
       <c r="AP104" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ104" s="5" t="s">
         <v>76</v>
@@ -21130,7 +21130,7 @@
         <v>542</v>
       </c>
       <c r="AP105" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ105" s="5" t="s">
         <v>76</v>
@@ -21279,7 +21279,7 @@
         <v>543</v>
       </c>
       <c r="AP106" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ106" s="5" t="s">
         <v>76</v>
@@ -21430,7 +21430,7 @@
         <v>544</v>
       </c>
       <c r="AP107" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ107" s="5" t="s">
         <v>76</v>
@@ -21581,7 +21581,7 @@
         <v>545</v>
       </c>
       <c r="AP108" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ108" s="5" t="s">
         <v>76</v>
@@ -21732,7 +21732,7 @@
         <v>546</v>
       </c>
       <c r="AP109" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ109" s="5" t="s">
         <v>76</v>
@@ -21883,7 +21883,7 @@
         <v>547</v>
       </c>
       <c r="AP110" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ110" s="5" t="s">
         <v>76</v>
@@ -22034,7 +22034,7 @@
         <v>548</v>
       </c>
       <c r="AP111" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ111" s="5" t="s">
         <v>76</v>
@@ -22185,7 +22185,7 @@
         <v>549</v>
       </c>
       <c r="AP112" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ112" s="5" t="s">
         <v>76</v>
@@ -22339,7 +22339,7 @@
         <v>550</v>
       </c>
       <c r="AP113" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ113" s="5" t="s">
         <v>76</v>
@@ -22493,7 +22493,7 @@
         <v>551</v>
       </c>
       <c r="AP114" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ114" s="5" t="s">
         <v>76</v>
@@ -22647,7 +22647,7 @@
         <v>552</v>
       </c>
       <c r="AP115" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ115" s="5" t="s">
         <v>76</v>
@@ -22801,7 +22801,7 @@
         <v>553</v>
       </c>
       <c r="AP116" s="35" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AQ116" s="5" t="s">
         <v>76</v>
@@ -22832,13 +22832,13 @@
         <v>67</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E117" s="10">
         <v>67600</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G117" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -22846,7 +22846,7 @@
 67600 - Sélestat</v>
       </c>
       <c r="H117" s="15" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>45</v>
@@ -22861,7 +22861,7 @@
         <v>7500</v>
       </c>
       <c r="M117" s="36" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N117" s="34">
         <v>98</v>
@@ -22938,25 +22938,25 @@
         <v>371</v>
       </c>
       <c r="AJ117" s="10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="AK117" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="AL117" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM117" s="11" t="s">
+        <v>897</v>
+      </c>
+      <c r="AN117" s="11" t="s">
         <v>898</v>
-      </c>
-      <c r="AN117" s="11" t="s">
-        <v>899</v>
       </c>
       <c r="AO117" s="11">
         <v>25</v>
       </c>
       <c r="AP117" s="36" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="AQ117" s="11" t="s">
         <v>76</v>
@@ -22965,7 +22965,7 @@
         <v>380</v>
       </c>
       <c r="AS117" s="13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AT117" s="14"/>
       <c r="AU117" s="44"/>
@@ -22987,13 +22987,13 @@
         <v>84</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E118" s="26">
         <v>84507</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G118" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -23001,7 +23001,7 @@
 84507 - Bollène</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I118" s="12" t="s">
         <v>47</v>
@@ -23093,34 +23093,34 @@
         <v>372</v>
       </c>
       <c r="AJ118" s="10" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK118" s="11" t="s">
         <v>909</v>
-      </c>
-      <c r="AK118" s="11" t="s">
-        <v>910</v>
       </c>
       <c r="AL118" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM118" s="11" t="s">
+        <v>910</v>
+      </c>
+      <c r="AN118" s="11" t="s">
         <v>911</v>
-      </c>
-      <c r="AN118" s="11" t="s">
-        <v>912</v>
       </c>
       <c r="AO118" s="11">
         <v>26</v>
       </c>
       <c r="AP118" s="36" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AQ118" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR118" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="AS118" s="13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AT118" s="14"/>
       <c r="AU118" s="44"/>
@@ -23142,7 +23142,7 @@
         <v>92</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E119" s="10">
         <v>92100</v>
@@ -23156,7 +23156,7 @@
 92100 - Boulogne-Billancourt</v>
       </c>
       <c r="H119" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="I119" s="12" t="s">
         <v>45</v>
@@ -23171,7 +23171,7 @@
         <v>104</v>
       </c>
       <c r="M119" s="36" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="N119" s="34">
         <v>254</v>
@@ -23248,22 +23248,22 @@
       </c>
       <c r="AJ119" s="10"/>
       <c r="AK119" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="AL119" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM119" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="AN119" s="11" t="s">
         <v>919</v>
-      </c>
-      <c r="AN119" s="11" t="s">
-        <v>920</v>
       </c>
       <c r="AO119" s="11">
         <v>27</v>
       </c>
       <c r="AP119" s="36" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AQ119" s="11" t="s">
         <v>76</v>
@@ -23294,7 +23294,7 @@
         <v>75</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E120" s="10">
         <v>75020</v>
@@ -23308,7 +23308,7 @@
 75020 - Paris</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="I120" s="12" t="s">
         <v>45</v>
@@ -23399,31 +23399,31 @@
         <v>371</v>
       </c>
       <c r="AJ120" s="10" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="AK120" s="11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AL120" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM120" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="AN120" s="11" t="s">
         <v>924</v>
-      </c>
-      <c r="AN120" s="11" t="s">
-        <v>925</v>
       </c>
       <c r="AO120" s="11">
         <v>28</v>
       </c>
       <c r="AP120" s="36" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AQ120" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR120" s="11" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="AS120" s="13" t="s">
         <v>31</v>
@@ -23448,13 +23448,13 @@
         <v>93</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E121" s="10">
         <v>93430</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G121" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -23462,7 +23462,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H121" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I121" s="12" t="s">
         <v>45</v>
@@ -23477,7 +23477,7 @@
         <v>104</v>
       </c>
       <c r="M121" s="36" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="N121" s="34">
         <v>163</v>
@@ -23554,34 +23554,34 @@
         <v>372</v>
       </c>
       <c r="AJ121" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK121" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL121" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM121" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="AN121" s="11" t="s">
         <v>958</v>
       </c>
-      <c r="AN121" s="11" t="s">
-        <v>959</v>
-      </c>
       <c r="AO121" s="11" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AP121" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ121" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR121" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS121" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS121" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT121" s="14"/>
       <c r="AU121" s="44"/>
@@ -23603,13 +23603,13 @@
         <v>93</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E122" s="10">
         <v>93430</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G122" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -23617,7 +23617,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H122" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I122" s="12" t="s">
         <v>45</v>
@@ -23709,34 +23709,34 @@
         <v>371</v>
       </c>
       <c r="AJ122" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK122" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL122" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM122" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AN122" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="AN122" s="11" t="s">
-        <v>961</v>
-      </c>
       <c r="AO122" s="11" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AP122" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ122" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR122" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS122" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS122" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT122" s="14"/>
       <c r="AU122" s="44"/>
@@ -23758,13 +23758,13 @@
         <v>93</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E123" s="10">
         <v>93430</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G123" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -23772,7 +23772,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H123" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I123" s="12" t="s">
         <v>45</v>
@@ -23864,34 +23864,34 @@
         <v>371</v>
       </c>
       <c r="AJ123" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK123" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL123" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM123" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="AN123" s="11" t="s">
         <v>962</v>
       </c>
-      <c r="AN123" s="11" t="s">
-        <v>963</v>
-      </c>
       <c r="AO123" s="11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="AP123" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ123" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR123" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS123" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS123" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT123" s="14"/>
       <c r="AU123" s="44"/>
@@ -23913,13 +23913,13 @@
         <v>93</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E124" s="10">
         <v>93430</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G124" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -23927,7 +23927,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I124" s="12" t="s">
         <v>45</v>
@@ -23942,7 +23942,7 @@
         <v>104</v>
       </c>
       <c r="M124" s="36" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="N124" s="34">
         <v>438</v>
@@ -24019,34 +24019,34 @@
         <v>372</v>
       </c>
       <c r="AJ124" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK124" s="11" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AL124" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM124" s="11" t="s">
+        <v>963</v>
+      </c>
+      <c r="AN124" s="11" t="s">
         <v>964</v>
       </c>
-      <c r="AN124" s="11" t="s">
-        <v>965</v>
-      </c>
       <c r="AO124" s="11" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AP124" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ124" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR124" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS124" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS124" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT124" s="14"/>
       <c r="AU124" s="44"/>
@@ -24068,13 +24068,13 @@
         <v>93</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E125" s="10">
         <v>93430</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G125" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24082,7 +24082,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H125" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I125" s="12" t="s">
         <v>45</v>
@@ -24097,7 +24097,7 @@
         <v>104</v>
       </c>
       <c r="M125" s="36" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="N125" s="34">
         <v>97</v>
@@ -24174,34 +24174,34 @@
         <v>371</v>
       </c>
       <c r="AJ125" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK125" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL125" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM125" s="11" t="s">
+        <v>965</v>
+      </c>
+      <c r="AN125" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="AN125" s="11" t="s">
-        <v>967</v>
-      </c>
       <c r="AO125" s="11" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AP125" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ125" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR125" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS125" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS125" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT125" s="14"/>
       <c r="AU125" s="44"/>
@@ -24223,13 +24223,13 @@
         <v>93</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E126" s="10">
         <v>93430</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G126" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24237,7 +24237,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I126" s="12" t="s">
         <v>45</v>
@@ -24329,34 +24329,34 @@
         <v>371</v>
       </c>
       <c r="AJ126" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK126" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL126" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM126" s="11" t="s">
+        <v>973</v>
+      </c>
+      <c r="AN126" s="11" t="s">
         <v>974</v>
       </c>
-      <c r="AN126" s="11" t="s">
-        <v>975</v>
-      </c>
       <c r="AO126" s="11" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AP126" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ126" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR126" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS126" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS126" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT126" s="14"/>
       <c r="AU126" s="44"/>
@@ -24375,13 +24375,13 @@
         <v>93</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E127" s="10">
         <v>93430</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G127" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24389,7 +24389,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H127" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I127" s="12" t="s">
         <v>45</v>
@@ -24404,7 +24404,7 @@
         <v>104</v>
       </c>
       <c r="M127" s="36" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="N127" s="34">
         <v>125</v>
@@ -24481,34 +24481,34 @@
         <v>371</v>
       </c>
       <c r="AJ127" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK127" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL127" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM127" s="11" t="s">
+        <v>971</v>
+      </c>
+      <c r="AN127" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="AN127" s="11" t="s">
-        <v>973</v>
-      </c>
       <c r="AO127" s="11" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="AP127" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ127" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR127" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS127" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS127" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT127" s="14"/>
       <c r="AU127" s="44"/>
@@ -24527,13 +24527,13 @@
         <v>93</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E128" s="10">
         <v>93430</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G128" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24541,7 +24541,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H128" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I128" s="12" t="s">
         <v>45</v>
@@ -24633,34 +24633,34 @@
         <v>371</v>
       </c>
       <c r="AJ128" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK128" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL128" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM128" s="11" t="s">
+        <v>969</v>
+      </c>
+      <c r="AN128" s="11" t="s">
         <v>970</v>
       </c>
-      <c r="AN128" s="11" t="s">
-        <v>971</v>
-      </c>
       <c r="AO128" s="11" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="AP128" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ128" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR128" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS128" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS128" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT128" s="14"/>
       <c r="AU128" s="44"/>
@@ -24679,13 +24679,13 @@
         <v>93</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E129" s="10">
         <v>93430</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G129" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24693,7 +24693,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H129" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I129" s="12" t="s">
         <v>45</v>
@@ -24785,34 +24785,34 @@
         <v>371</v>
       </c>
       <c r="AJ129" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK129" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL129" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM129" s="11" t="s">
+        <v>967</v>
+      </c>
+      <c r="AN129" s="11" t="s">
         <v>968</v>
       </c>
-      <c r="AN129" s="11" t="s">
-        <v>969</v>
-      </c>
       <c r="AO129" s="11" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="AP129" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ129" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR129" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS129" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS129" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT129" s="14"/>
       <c r="AU129" s="44"/>
@@ -24831,13 +24831,13 @@
         <v>93</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E130" s="10">
         <v>93430</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G130" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24845,7 +24845,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H130" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I130" s="12" t="s">
         <v>45</v>
@@ -24937,34 +24937,34 @@
         <v>371</v>
       </c>
       <c r="AJ130" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK130" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL130" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM130" s="11" t="s">
+        <v>975</v>
+      </c>
+      <c r="AN130" s="11" t="s">
         <v>976</v>
       </c>
-      <c r="AN130" s="11" t="s">
-        <v>977</v>
-      </c>
       <c r="AO130" s="11" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="AP130" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ130" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR130" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS130" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS130" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT130" s="14"/>
       <c r="AU130" s="44"/>
@@ -24983,13 +24983,13 @@
         <v>93</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E131" s="10">
         <v>93430</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G131" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24997,7 +24997,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H131" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I131" s="12" t="s">
         <v>45</v>
@@ -25089,34 +25089,34 @@
         <v>371</v>
       </c>
       <c r="AJ131" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK131" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL131" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM131" s="11" t="s">
+        <v>977</v>
+      </c>
+      <c r="AN131" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="AN131" s="11" t="s">
-        <v>979</v>
-      </c>
       <c r="AO131" s="11" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="AP131" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ131" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR131" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS131" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS131" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT131" s="14"/>
       <c r="AU131" s="44"/>
@@ -25135,13 +25135,13 @@
         <v>93</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E132" s="10">
         <v>93430</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G132" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25149,7 +25149,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H132" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I132" s="12" t="s">
         <v>45</v>
@@ -25241,34 +25241,34 @@
         <v>371</v>
       </c>
       <c r="AJ132" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK132" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL132" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM132" s="11" t="s">
+        <v>979</v>
+      </c>
+      <c r="AN132" s="11" t="s">
         <v>980</v>
       </c>
-      <c r="AN132" s="11" t="s">
-        <v>981</v>
-      </c>
       <c r="AO132" s="11" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AP132" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ132" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR132" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS132" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS132" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT132" s="14"/>
       <c r="AU132" s="44"/>
@@ -25287,13 +25287,13 @@
         <v>93</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E133" s="10">
         <v>93430</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G133" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25301,7 +25301,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H133" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I133" s="12" t="s">
         <v>45</v>
@@ -25393,34 +25393,34 @@
         <v>371</v>
       </c>
       <c r="AJ133" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK133" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL133" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM133" s="11" t="s">
+        <v>981</v>
+      </c>
+      <c r="AN133" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="AN133" s="11" t="s">
-        <v>983</v>
-      </c>
       <c r="AO133" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AP133" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ133" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR133" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS133" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS133" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT133" s="14"/>
       <c r="AU133" s="44"/>
@@ -25439,13 +25439,13 @@
         <v>93</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E134" s="10">
         <v>93430</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G134" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25453,7 +25453,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I134" s="12" t="s">
         <v>45</v>
@@ -25545,34 +25545,34 @@
         <v>371</v>
       </c>
       <c r="AJ134" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK134" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL134" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM134" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="AN134" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="AN134" s="11" t="s">
-        <v>985</v>
-      </c>
       <c r="AO134" s="11" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AP134" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ134" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR134" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS134" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS134" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT134" s="14"/>
       <c r="AU134" s="44"/>
@@ -25591,13 +25591,13 @@
         <v>93</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E135" s="10">
         <v>93430</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G135" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25605,7 +25605,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H135" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I135" s="12" t="s">
         <v>45</v>
@@ -25697,34 +25697,34 @@
         <v>371</v>
       </c>
       <c r="AJ135" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK135" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL135" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM135" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="AN135" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="AN135" s="11" t="s">
-        <v>987</v>
-      </c>
       <c r="AO135" s="11" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AP135" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ135" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR135" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS135" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS135" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT135" s="14"/>
       <c r="AU135" s="44"/>
@@ -25743,13 +25743,13 @@
         <v>93</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E136" s="10">
         <v>93430</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G136" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25757,7 +25757,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H136" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I136" s="12" t="s">
         <v>45</v>
@@ -25849,34 +25849,34 @@
         <v>371</v>
       </c>
       <c r="AJ136" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK136" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL136" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM136" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="AN136" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="AN136" s="11" t="s">
-        <v>989</v>
-      </c>
       <c r="AO136" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AP136" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ136" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR136" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS136" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS136" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT136" s="14"/>
       <c r="AU136" s="44"/>
@@ -25895,13 +25895,13 @@
         <v>93</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E137" s="10">
         <v>93430</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G137" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25909,7 +25909,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H137" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I137" s="12" t="s">
         <v>45</v>
@@ -25924,7 +25924,7 @@
         <v>104</v>
       </c>
       <c r="M137" s="36" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="N137" s="34">
         <v>62</v>
@@ -26001,34 +26001,34 @@
         <v>371</v>
       </c>
       <c r="AJ137" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AK137" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AL137" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM137" s="11" t="s">
+        <v>989</v>
+      </c>
+      <c r="AN137" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="AN137" s="11" t="s">
-        <v>991</v>
-      </c>
       <c r="AO137" s="11" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AP137" s="36" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ137" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR137" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="AS137" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="AS137" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="AT137" s="14"/>
       <c r="AU137" s="44"/>
@@ -26047,13 +26047,13 @@
         <v>95</v>
       </c>
       <c r="D138" s="42" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E138" s="10">
         <v>95290</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G138" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26061,7 +26061,7 @@
 95290 - L'Isle-Adam</v>
       </c>
       <c r="H138" s="15" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="I138" s="12" t="s">
         <v>47</v>
@@ -26076,7 +26076,7 @@
         <v>104</v>
       </c>
       <c r="M138" s="36" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="N138" s="34">
         <v>60</v>
@@ -26153,34 +26153,34 @@
         <v>371</v>
       </c>
       <c r="AJ138" s="10" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AK138" s="11" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="AL138" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM138" s="11" t="s">
+        <v>999</v>
+      </c>
+      <c r="AN138" s="11" t="s">
         <v>1000</v>
-      </c>
-      <c r="AN138" s="11" t="s">
-        <v>1001</v>
       </c>
       <c r="AO138" s="11">
         <v>30</v>
       </c>
       <c r="AP138" s="36" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="AQ138" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR138" s="11" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AS138" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AT138" s="14"/>
       <c r="AU138" s="44"/>
@@ -26199,13 +26199,13 @@
         <v>95</v>
       </c>
       <c r="D139" s="42" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E139" s="10">
         <v>95260</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G139" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26213,7 +26213,7 @@
 95260 - Mours</v>
       </c>
       <c r="H139" s="15" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I139" s="12" t="s">
         <v>47</v>
@@ -26298,32 +26298,32 @@
         <v>372</v>
       </c>
       <c r="AJ139" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="AK139" s="11" t="s">
         <v>1012</v>
-      </c>
-      <c r="AK139" s="11" t="s">
-        <v>1013</v>
       </c>
       <c r="AL139" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM139" s="11" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AN139" s="11" t="s">
         <v>1014</v>
       </c>
-      <c r="AN139" s="11" t="s">
-        <v>1015</v>
-      </c>
       <c r="AO139" s="11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AP139" s="36" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AQ139" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR139" s="11"/>
       <c r="AS139" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AT139" s="14"/>
       <c r="AU139" s="44"/>
@@ -26342,13 +26342,13 @@
         <v>95</v>
       </c>
       <c r="D140" s="42" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E140" s="10">
         <v>95260</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G140" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26356,7 +26356,7 @@
 95260 - Mours</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I140" s="12" t="s">
         <v>47</v>
@@ -26441,32 +26441,32 @@
         <v>372</v>
       </c>
       <c r="AJ140" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="AK140" s="11" t="s">
         <v>1012</v>
-      </c>
-      <c r="AK140" s="11" t="s">
-        <v>1013</v>
       </c>
       <c r="AL140" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM140" s="11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AN140" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="AN140" s="11" t="s">
-        <v>1017</v>
-      </c>
       <c r="AO140" s="11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="AP140" s="36" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AQ140" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR140" s="11"/>
       <c r="AS140" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AT140" s="14"/>
       <c r="AU140" s="44"/>
@@ -26485,13 +26485,13 @@
         <v>95</v>
       </c>
       <c r="D141" s="42" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E141" s="10">
         <v>95260</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G141" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26499,7 +26499,7 @@
 95260 - Mours</v>
       </c>
       <c r="H141" s="15" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I141" s="12" t="s">
         <v>47</v>
@@ -26584,32 +26584,32 @@
         <v>372</v>
       </c>
       <c r="AJ141" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="AK141" s="11" t="s">
         <v>1012</v>
-      </c>
-      <c r="AK141" s="11" t="s">
-        <v>1013</v>
       </c>
       <c r="AL141" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM141" s="11" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AN141" s="11" t="s">
         <v>1018</v>
       </c>
-      <c r="AN141" s="11" t="s">
-        <v>1019</v>
-      </c>
       <c r="AO141" s="11" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AP141" s="36" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AQ141" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR141" s="11"/>
       <c r="AS141" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AT141" s="14"/>
       <c r="AU141" s="44"/>
@@ -26628,13 +26628,13 @@
         <v>95</v>
       </c>
       <c r="D142" s="42" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E142" s="10">
         <v>95260</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G142" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26642,7 +26642,7 @@
 95260 - Mours</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>47</v>
@@ -26727,32 +26727,32 @@
         <v>372</v>
       </c>
       <c r="AJ142" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="AK142" s="11" t="s">
         <v>1012</v>
-      </c>
-      <c r="AK142" s="11" t="s">
-        <v>1013</v>
       </c>
       <c r="AL142" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM142" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AN142" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="AN142" s="11" t="s">
-        <v>1021</v>
-      </c>
       <c r="AO142" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AP142" s="36" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AQ142" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR142" s="11"/>
       <c r="AS142" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AT142" s="14"/>
       <c r="AU142" s="44"/>
@@ -26771,13 +26771,13 @@
         <v>95</v>
       </c>
       <c r="D143" s="42" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E143" s="10">
         <v>95260</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G143" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26785,7 +26785,7 @@
 95260 - Mours</v>
       </c>
       <c r="H143" s="15" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>47</v>
@@ -26868,32 +26868,32 @@
         <v>372</v>
       </c>
       <c r="AJ143" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="AK143" s="11" t="s">
         <v>1012</v>
-      </c>
-      <c r="AK143" s="11" t="s">
-        <v>1013</v>
       </c>
       <c r="AL143" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM143" s="11" t="s">
+        <v>1021</v>
+      </c>
+      <c r="AN143" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="AN143" s="11" t="s">
-        <v>1023</v>
-      </c>
       <c r="AO143" s="11" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AP143" s="36" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="AQ143" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR143" s="11"/>
       <c r="AS143" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AT143" s="14"/>
       <c r="AU143" s="44"/>
@@ -26912,13 +26912,13 @@
         <v>44</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E144" s="10">
         <v>44200</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G144" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26926,7 +26926,7 @@
 44200 - Nantes</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="I144" s="12" t="s">
         <v>45</v>
@@ -27018,31 +27018,31 @@
         <v>372</v>
       </c>
       <c r="AJ144" s="10" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AK144" s="11" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="AL144" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM144" s="11" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AN144" s="11" t="s">
         <v>1031</v>
       </c>
-      <c r="AN144" s="11" t="s">
-        <v>1032</v>
-      </c>
       <c r="AO144" s="11" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AP144" s="36" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AQ144" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR144" s="11" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AS144" s="13" t="s">
         <v>37</v>
@@ -27064,13 +27064,13 @@
         <v>44</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E145" s="10">
         <v>44200</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G145" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27078,7 +27078,7 @@
 44200 - Nantes</v>
       </c>
       <c r="H145" s="15" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="I145" s="12" t="s">
         <v>45</v>
@@ -27170,31 +27170,31 @@
         <v>371</v>
       </c>
       <c r="AJ145" s="10" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AK145" s="11" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="AL145" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM145" s="11" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AN145" s="11" t="s">
         <v>1033</v>
       </c>
-      <c r="AN145" s="11" t="s">
-        <v>1034</v>
-      </c>
       <c r="AO145" s="11" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="AP145" s="36" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AQ145" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR145" s="11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AS145" s="13" t="s">
         <v>37</v>
@@ -27216,13 +27216,13 @@
         <v>68</v>
       </c>
       <c r="D146" s="42" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E146" s="10">
         <v>68330</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G146" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27230,7 +27230,7 @@
 68330 - Huningue</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I146" s="12" t="s">
         <v>45</v>
@@ -27245,7 +27245,7 @@
         <v>104</v>
       </c>
       <c r="M146" s="36" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="N146" s="34">
         <v>287</v>
@@ -27310,29 +27310,29 @@
       <c r="AI146" s="10"/>
       <c r="AJ146" s="10"/>
       <c r="AK146" s="11" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AL146" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM146" s="11" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AN146" s="11" t="s">
         <v>1046</v>
-      </c>
-      <c r="AN146" s="11" t="s">
-        <v>1047</v>
       </c>
       <c r="AO146" s="11">
         <v>33</v>
       </c>
       <c r="AP146" s="36" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="AQ146" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR146" s="11"/>
       <c r="AS146" s="13" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="AT146" s="14"/>
       <c r="AU146" s="44"/>
@@ -27351,13 +27351,13 @@
         <v>37</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E147" s="10">
         <v>37600</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G147" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27365,7 +27365,7 @@
 37600 - Loches</v>
       </c>
       <c r="H147" s="15" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I147" s="12" t="s">
         <v>47</v>
@@ -27455,34 +27455,34 @@
         <v>104</v>
       </c>
       <c r="AJ147" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="AK147" s="11" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="AL147" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM147" s="11" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AN147" s="11" t="s">
         <v>1051</v>
-      </c>
-      <c r="AN147" s="11" t="s">
-        <v>1052</v>
       </c>
       <c r="AO147" s="11">
         <v>34</v>
       </c>
       <c r="AP147" s="36" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AQ147" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR147" s="43" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="AS147" s="13" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AT147" s="14"/>
       <c r="AU147" s="44">
@@ -27503,13 +27503,13 @@
         <v>37</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E148" s="10">
         <v>37600</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G148" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27517,7 +27517,7 @@
 37600 - Loches</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>47</v>
@@ -27610,34 +27610,34 @@
         <v>104</v>
       </c>
       <c r="AJ148" s="10" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AK148" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AL148" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM148" s="11" t="s">
+        <v>1068</v>
+      </c>
+      <c r="AN148" s="11" t="s">
         <v>1069</v>
       </c>
-      <c r="AN148" s="11" t="s">
-        <v>1070</v>
-      </c>
       <c r="AO148" s="11" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AP148" s="36" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AQ148" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR148" s="11" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AS148" s="13" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AT148" s="14"/>
       <c r="AU148" s="44">
@@ -27658,13 +27658,13 @@
         <v>37</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E149" s="10">
         <v>37601</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G149" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27672,7 +27672,7 @@
 37601 - Loches</v>
       </c>
       <c r="H149" s="15" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I149" s="12" t="s">
         <v>47</v>
@@ -27765,34 +27765,34 @@
         <v>104</v>
       </c>
       <c r="AJ149" s="10" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AK149" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AL149" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM149" s="11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AN149" s="11" t="s">
         <v>1071</v>
       </c>
-      <c r="AN149" s="11" t="s">
-        <v>1072</v>
-      </c>
       <c r="AO149" s="11" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AP149" s="36" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AQ149" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR149" s="11" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AS149" s="13" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AT149" s="14"/>
       <c r="AU149" s="44">
@@ -27813,13 +27813,13 @@
         <v>37</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E150" s="10">
         <v>37602</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G150" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27827,7 +27827,7 @@
 37602 - Loches</v>
       </c>
       <c r="H150" s="15" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I150" s="12" t="s">
         <v>47</v>
@@ -27920,34 +27920,34 @@
         <v>104</v>
       </c>
       <c r="AJ150" s="10" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AK150" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AL150" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM150" s="11" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AN150" s="11" t="s">
         <v>1073</v>
       </c>
-      <c r="AN150" s="11" t="s">
-        <v>1074</v>
-      </c>
       <c r="AO150" s="11" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AP150" s="36" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AQ150" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR150" s="11" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AS150" s="13" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AT150" s="14"/>
       <c r="AU150" s="44">
@@ -27968,13 +27968,13 @@
         <v>37</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E151" s="10">
         <v>37603</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G151" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27982,7 +27982,7 @@
 37603 - Loches</v>
       </c>
       <c r="H151" s="15" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I151" s="12" t="s">
         <v>47</v>
@@ -28075,34 +28075,34 @@
         <v>104</v>
       </c>
       <c r="AJ151" s="10" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AK151" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AL151" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM151" s="11" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AN151" s="11" t="s">
         <v>1075</v>
       </c>
-      <c r="AN151" s="11" t="s">
-        <v>1076</v>
-      </c>
       <c r="AO151" s="11" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AP151" s="36" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AQ151" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR151" s="11" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AS151" s="13" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AT151" s="14"/>
       <c r="AU151" s="44">
@@ -28123,13 +28123,13 @@
         <v>37</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E152" s="10">
         <v>37604</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G152" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28137,7 +28137,7 @@
 37604 - Loches</v>
       </c>
       <c r="H152" s="15" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I152" s="12" t="s">
         <v>47</v>
@@ -28230,34 +28230,34 @@
         <v>104</v>
       </c>
       <c r="AJ152" s="10" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AK152" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AL152" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM152" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AN152" s="11" t="s">
         <v>1077</v>
       </c>
-      <c r="AN152" s="11" t="s">
+      <c r="AO152" s="11" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AP152" s="36" t="s">
         <v>1078</v>
-      </c>
-      <c r="AO152" s="11" t="s">
-        <v>1068</v>
-      </c>
-      <c r="AP152" s="36" t="s">
-        <v>1079</v>
       </c>
       <c r="AQ152" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR152" s="11" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AS152" s="13" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AT152" s="14"/>
       <c r="AU152" s="44">
@@ -28278,13 +28278,13 @@
         <v>13</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E153" s="10">
         <v>13127</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G153" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28292,7 +28292,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I153" s="12" t="s">
         <v>47</v>
@@ -28307,7 +28307,7 @@
         <v>104</v>
       </c>
       <c r="M153" s="36" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="N153" s="34">
         <v>181</v>
@@ -28384,10 +28384,10 @@
         <v>372</v>
       </c>
       <c r="AJ153" s="10" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AK153" s="11" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AL153" s="5" t="s">
         <v>370</v>
@@ -28399,19 +28399,19 @@
         <v>5.2419589999999996</v>
       </c>
       <c r="AO153" s="11" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="AP153" s="36" t="s">
-        <v>1263</v>
+        <v>1279</v>
       </c>
       <c r="AQ153" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR153" s="11" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="AS153" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT153" s="14"/>
       <c r="AU153" s="44">
@@ -28432,13 +28432,13 @@
         <v>13</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E154" s="10">
         <v>13128</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G154" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28446,7 +28446,7 @@
 13128 - Vitrolles</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I154" s="12" t="s">
         <v>47</v>
@@ -28455,13 +28455,13 @@
         <v>48</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="L154" s="12" t="s">
         <v>104</v>
       </c>
       <c r="M154" s="36" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="N154" s="34">
         <v>100</v>
@@ -28538,34 +28538,34 @@
         <v>372</v>
       </c>
       <c r="AJ154" s="10" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AK154" s="11" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="AL154" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM154" s="11" t="s">
+        <v>1214</v>
+      </c>
+      <c r="AN154" s="11" t="s">
         <v>1215</v>
       </c>
-      <c r="AN154" s="11" t="s">
-        <v>1216</v>
-      </c>
       <c r="AO154" s="11" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="AP154" s="36" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="AQ154" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR154" s="11" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="AS154" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT154" s="14"/>
       <c r="AU154" s="44">
@@ -28586,13 +28586,13 @@
         <v>13</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E155" s="10">
         <v>13129</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G155" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28600,7 +28600,7 @@
 13129 - Vitrolles</v>
       </c>
       <c r="H155" s="15" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>47</v>
@@ -28609,13 +28609,13 @@
         <v>48</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="L155" s="12" t="s">
         <v>104</v>
       </c>
       <c r="M155" s="36" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="N155" s="34">
         <v>446</v>
@@ -28692,34 +28692,34 @@
         <v>104</v>
       </c>
       <c r="AJ155" s="10" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AK155" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="AL155" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM155" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AN155" s="11" t="s">
         <v>1222</v>
       </c>
-      <c r="AN155" s="11" t="s">
-        <v>1223</v>
-      </c>
       <c r="AO155" s="11" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="AP155" s="36" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="AQ155" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR155" s="11" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="AS155" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT155" s="14"/>
       <c r="AU155" s="44">
@@ -28740,13 +28740,13 @@
         <v>13</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E156" s="10">
         <v>13130</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G156" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28754,7 +28754,7 @@
 13130 - Vitrolles</v>
       </c>
       <c r="H156" s="15" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I156" s="12" t="s">
         <v>47</v>
@@ -28763,13 +28763,13 @@
         <v>48</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="L156" s="12" t="s">
         <v>104</v>
       </c>
       <c r="M156" s="36" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="N156" s="34">
         <v>567</v>
@@ -28846,34 +28846,34 @@
         <v>104</v>
       </c>
       <c r="AJ156" s="10" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AK156" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="AL156" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM156" s="11" t="s">
+        <v>1229</v>
+      </c>
+      <c r="AN156" s="11" t="s">
         <v>1230</v>
       </c>
-      <c r="AN156" s="11" t="s">
-        <v>1231</v>
-      </c>
       <c r="AO156" s="11" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="AP156" s="36" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="AQ156" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR156" s="11" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="AS156" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT156" s="14"/>
       <c r="AU156" s="44">
@@ -28894,13 +28894,13 @@
         <v>13</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E157" s="10">
         <v>13170</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G157" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28908,7 +28908,7 @@
 13170 - Les Pennes-Mirabeau</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="I157" s="12" t="s">
         <v>47</v>
@@ -28927,7 +28927,7 @@
         <v>1390</v>
       </c>
       <c r="O157" s="6" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="P157" s="34" t="s">
         <v>104</v>
@@ -28999,34 +28999,34 @@
         <v>372</v>
       </c>
       <c r="AJ157" s="10" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="AK157" s="11" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="AL157" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM157" s="11" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AN157" s="11" t="s">
         <v>1144</v>
-      </c>
-      <c r="AN157" s="11" t="s">
-        <v>1145</v>
       </c>
       <c r="AO157" s="11">
         <v>37</v>
       </c>
       <c r="AP157" s="36" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="AQ157" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR157" s="11" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="AS157" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT157" s="14"/>
       <c r="AU157" s="44">
@@ -29047,13 +29047,13 @@
         <v>18</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="E158" s="10">
         <v>18390</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G158" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29061,7 +29061,7 @@
 18390 - Saint-Germain-du-Puy</v>
       </c>
       <c r="H158" s="15" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="I158" s="12" t="s">
         <v>47</v>
@@ -29151,34 +29151,34 @@
         <v>372</v>
       </c>
       <c r="AJ158" s="10" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AK158" s="11" t="s">
         <v>1156</v>
-      </c>
-      <c r="AK158" s="11" t="s">
-        <v>1157</v>
       </c>
       <c r="AL158" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM158" s="11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AN158" s="11" t="s">
         <v>1158</v>
-      </c>
-      <c r="AN158" s="11" t="s">
-        <v>1159</v>
       </c>
       <c r="AO158" s="11">
         <v>38</v>
       </c>
       <c r="AP158" s="36" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="AQ158" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR158" s="11" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="AS158" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT158" s="14"/>
       <c r="AU158" s="44">
@@ -29199,13 +29199,13 @@
         <v>18</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E159" s="10">
         <v>18230</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G159" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29213,7 +29213,7 @@
 18230 -  Saint-Doulchard</v>
       </c>
       <c r="H159" s="15" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="I159" s="12" t="s">
         <v>47</v>
@@ -29295,32 +29295,32 @@
         <v>104</v>
       </c>
       <c r="AJ159" s="10" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AK159" s="11" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="AL159" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM159" s="11" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AN159" s="11" t="s">
         <v>1161</v>
-      </c>
-      <c r="AN159" s="11" t="s">
-        <v>1162</v>
       </c>
       <c r="AO159" s="11">
         <v>39</v>
       </c>
       <c r="AP159" s="36" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="AQ159" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR159" s="11"/>
       <c r="AS159" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT159" s="14"/>
       <c r="AU159" s="44">
@@ -29341,13 +29341,13 @@
         <v>54</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E160" s="10">
         <v>54000</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G160" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29355,7 +29355,7 @@
 54000 - Nancy</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="I160" s="12" t="s">
         <v>45</v>
@@ -29374,7 +29374,7 @@
         <v>550</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="P160" s="34" t="s">
         <v>104</v>
@@ -29445,34 +29445,34 @@
         <v>372</v>
       </c>
       <c r="AJ160" s="10" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AK160" s="11" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="AL160" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM160" s="11" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AN160" s="11" t="s">
         <v>1164</v>
-      </c>
-      <c r="AN160" s="11" t="s">
-        <v>1165</v>
       </c>
       <c r="AO160" s="11">
         <v>40</v>
       </c>
       <c r="AP160" s="36" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="AQ160" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR160" s="11" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="AS160" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT160" s="14"/>
       <c r="AU160" s="44">
@@ -29493,13 +29493,13 @@
         <v>59</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E161" s="10">
         <v>59300</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G161" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29507,7 +29507,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H161" s="15" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="I161" s="12" t="s">
         <v>47</v>
@@ -29521,7 +29521,7 @@
       <c r="L161" s="12"/>
       <c r="M161" s="36"/>
       <c r="N161" s="34" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>104</v>
@@ -29590,29 +29590,29 @@
       </c>
       <c r="AJ161" s="10"/>
       <c r="AK161" s="11" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="AL161" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM161" s="11" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AN161" s="11" t="s">
         <v>1167</v>
-      </c>
-      <c r="AN161" s="11" t="s">
-        <v>1168</v>
       </c>
       <c r="AO161" s="11">
         <v>41</v>
       </c>
       <c r="AP161" s="36" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="AQ161" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR161" s="11"/>
       <c r="AS161" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT161" s="14"/>
       <c r="AU161" s="44">
@@ -29633,13 +29633,13 @@
         <v>59</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E162" s="10">
         <v>59320</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G162" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29647,7 +29647,7 @@
 59320 - Ennetières-en-Weppes</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="I162" s="12" t="s">
         <v>47</v>
@@ -29731,32 +29731,32 @@
         <v>372</v>
       </c>
       <c r="AJ162" s="10" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="AK162" s="11" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="AL162" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM162" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AN162" s="11" t="s">
         <v>1152</v>
-      </c>
-      <c r="AN162" s="11" t="s">
-        <v>1153</v>
       </c>
       <c r="AO162" s="11">
         <v>42</v>
       </c>
       <c r="AP162" s="36" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="AQ162" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR162" s="11"/>
       <c r="AS162" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT162" s="14"/>
       <c r="AU162" s="44">
@@ -29777,13 +29777,13 @@
         <v>68</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E163" s="10">
         <v>68270</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G163" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29791,7 +29791,7 @@
 68270 - Wittenheim</v>
       </c>
       <c r="H163" s="15" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="I163" s="12" t="s">
         <v>47</v>
@@ -29881,34 +29881,34 @@
         <v>372</v>
       </c>
       <c r="AJ163" s="10" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="AK163" s="11" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="AL163" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM163" s="11" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AN163" s="11" t="s">
         <v>1172</v>
-      </c>
-      <c r="AN163" s="11" t="s">
-        <v>1173</v>
       </c>
       <c r="AO163" s="11">
         <v>43</v>
       </c>
       <c r="AP163" s="36" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="AQ163" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR163" s="11" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="AS163" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT163" s="14"/>
       <c r="AU163" s="44">
@@ -29929,13 +29929,13 @@
         <v>77</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E164" s="10">
         <v>77140</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G164" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29943,7 +29943,7 @@
 77140 - Nemours</v>
       </c>
       <c r="H164" s="15" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>47</v>
@@ -29962,7 +29962,7 @@
         <v>760</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="P164" s="34" t="s">
         <v>104</v>
@@ -30033,34 +30033,34 @@
         <v>372</v>
       </c>
       <c r="AJ164" s="10" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="AK164" s="11" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="AL164" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM164" s="11" t="s">
+        <v>1173</v>
+      </c>
+      <c r="AN164" s="11" t="s">
         <v>1174</v>
-      </c>
-      <c r="AN164" s="11" t="s">
-        <v>1175</v>
       </c>
       <c r="AO164" s="11">
         <v>44</v>
       </c>
       <c r="AP164" s="36" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="AQ164" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR164" s="11" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="AS164" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT164" s="14"/>
       <c r="AU164" s="44">
@@ -30081,13 +30081,13 @@
         <v>83</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E165" s="10">
         <v>83160</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G165" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30095,7 +30095,7 @@
 83160 - La Valette-du-Var</v>
       </c>
       <c r="H165" s="15" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="I165" s="12" t="s">
         <v>45</v>
@@ -30112,7 +30112,7 @@
         <v>276</v>
       </c>
       <c r="O165" s="6" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="P165" s="34" t="s">
         <v>104</v>
@@ -30181,32 +30181,32 @@
         <v>372</v>
       </c>
       <c r="AJ165" s="10" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AK165" s="11" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AL165" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM165" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="AN165" s="11" t="s">
         <v>1177</v>
       </c>
-      <c r="AN165" s="11" t="s">
-        <v>1178</v>
-      </c>
       <c r="AO165" s="11" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AP165" s="36" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="AQ165" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR165" s="11"/>
       <c r="AS165" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT165" s="14"/>
       <c r="AU165" s="44">
@@ -30227,13 +30227,13 @@
         <v>83</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E166" s="10">
         <v>83161</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G166" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30241,7 +30241,7 @@
 83161 - La Valette-du-Var</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I166" s="12" t="s">
         <v>45</v>
@@ -30332,34 +30332,34 @@
         <v>372</v>
       </c>
       <c r="AJ166" s="10" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AK166" s="11" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="AL166" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM166" s="11" t="s">
+        <v>1180</v>
+      </c>
+      <c r="AN166" s="11" t="s">
         <v>1181</v>
       </c>
-      <c r="AN166" s="11" t="s">
-        <v>1182</v>
-      </c>
       <c r="AO166" s="11" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="AP166" s="36" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="AQ166" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR166" s="11" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="AS166" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT166" s="14"/>
       <c r="AU166" s="44">
@@ -30380,13 +30380,13 @@
         <v>84</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E167" s="10">
         <v>84140</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G167" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30394,7 +30394,7 @@
 84140 - Avignon</v>
       </c>
       <c r="H167" s="15" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="I167" s="12" t="s">
         <v>47</v>
@@ -30413,7 +30413,7 @@
         <v>616</v>
       </c>
       <c r="O167" s="6" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="P167" s="34" t="s">
         <v>104</v>
@@ -30485,34 +30485,34 @@
         <v>372</v>
       </c>
       <c r="AJ167" s="10" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AK167" s="11" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="AL167" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM167" s="11" t="s">
+        <v>1182</v>
+      </c>
+      <c r="AN167" s="11" t="s">
         <v>1183</v>
-      </c>
-      <c r="AN167" s="11" t="s">
-        <v>1184</v>
       </c>
       <c r="AO167" s="11">
         <v>46</v>
       </c>
       <c r="AP167" s="45" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="AQ167" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR167" s="11" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="AS167" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT167" s="14"/>
       <c r="AU167" s="44">
@@ -30533,13 +30533,13 @@
         <v>94</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E168" s="10">
         <v>94500</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G168" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30547,7 +30547,7 @@
 94500 - Champigny-sur-Marne</v>
       </c>
       <c r="H168" s="15" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="I168" s="12" t="s">
         <v>45</v>
@@ -30632,32 +30632,32 @@
         <v>372</v>
       </c>
       <c r="AJ168" s="10" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AK168" s="11" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AL168" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM168" s="11" t="s">
+        <v>1186</v>
+      </c>
+      <c r="AN168" s="11" t="s">
         <v>1187</v>
       </c>
-      <c r="AN168" s="11" t="s">
-        <v>1188</v>
-      </c>
       <c r="AO168" s="11" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AP168" s="45" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="AQ168" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR168" s="11"/>
       <c r="AS168" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT168" s="14"/>
       <c r="AU168" s="44">
@@ -30678,13 +30678,13 @@
         <v>94</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E169" s="10">
         <v>94500</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G169" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30692,7 +30692,7 @@
 94500 - Champigny-sur-Marne</v>
       </c>
       <c r="H169" s="15" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I169" s="12" t="s">
         <v>45</v>
@@ -30783,34 +30783,34 @@
         <v>372</v>
       </c>
       <c r="AJ169" s="10" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AK169" s="11" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AL169" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM169" s="11" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AN169" s="11" t="s">
         <v>1256</v>
       </c>
-      <c r="AN169" s="11" t="s">
-        <v>1257</v>
-      </c>
       <c r="AO169" s="11" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="AP169" s="36" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="AQ169" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR169" s="11" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="AS169" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT169" s="14"/>
       <c r="AU169" s="44">
@@ -30831,13 +30831,13 @@
         <v>94</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E170" s="10">
         <v>94500</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G170" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30845,7 +30845,7 @@
 94500 - Champigny-sur-Marne</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I170" s="12" t="s">
         <v>45</v>
@@ -30936,34 +30936,34 @@
         <v>372</v>
       </c>
       <c r="AJ170" s="10" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AK170" s="11" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AL170" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM170" s="11" t="s">
+        <v>1188</v>
+      </c>
+      <c r="AN170" s="11" t="s">
         <v>1189</v>
       </c>
-      <c r="AN170" s="11" t="s">
-        <v>1190</v>
-      </c>
       <c r="AO170" s="11" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AP170" s="36" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="AQ170" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR170" s="11" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="AS170" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT170" s="14"/>
       <c r="AU170" s="44">
@@ -30984,13 +30984,13 @@
         <v>95</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E171" s="10">
         <v>95220</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G171" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30998,7 +30998,7 @@
 95220 - Herblay-sur-Seine</v>
       </c>
       <c r="H171" s="15" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I171" s="12" t="s">
         <v>47</v>
@@ -31089,34 +31089,34 @@
         <v>372</v>
       </c>
       <c r="AJ171" s="10" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AK171" s="11" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="AL171" s="5" t="s">
         <v>370</v>
       </c>
       <c r="AM171" s="11" t="s">
+        <v>1192</v>
+      </c>
+      <c r="AN171" s="11" t="s">
         <v>1193</v>
-      </c>
-      <c r="AN171" s="11" t="s">
-        <v>1194</v>
       </c>
       <c r="AO171" s="11">
         <v>48</v>
       </c>
       <c r="AP171" s="36" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="AQ171" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR171" s="11" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="AS171" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AT171" s="14"/>
       <c r="AU171" s="44">
@@ -31137,13 +31137,13 @@
         <v>67</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E172" s="10">
         <v>6700</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G172" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -31152,7 +31152,7 @@
 6700 - Saint-Laurent-du-Var</v>
       </c>
       <c r="H172" s="15" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="I172" s="12" t="s">
         <v>47</v>
@@ -31164,14 +31164,14 @@
         <v>104</v>
       </c>
       <c r="L172" s="12" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="M172" s="36"/>
       <c r="N172" s="34">
         <v>126</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="P172" s="34" t="s">
         <v>104</v>
@@ -31242,32 +31242,32 @@
         <v>104</v>
       </c>
       <c r="AJ172" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="AK172" s="11" t="s">
+        <v>1204</v>
+      </c>
+      <c r="AL172" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AM172" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="AK172" s="11" t="s">
-        <v>1205</v>
-      </c>
-      <c r="AL172" s="5" t="s">
-        <v>1210</v>
-      </c>
-      <c r="AM172" s="11" t="s">
+      <c r="AN172" s="11" t="s">
         <v>1207</v>
-      </c>
-      <c r="AN172" s="11" t="s">
-        <v>1208</v>
       </c>
       <c r="AO172" s="11">
         <v>49</v>
       </c>
       <c r="AP172" s="36" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="AQ172" s="11" t="s">
         <v>76</v>
       </c>
       <c r="AR172" s="11"/>
       <c r="AS172" s="13" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AT172" s="14"/>
       <c r="AU172" s="44">
@@ -31276,12 +31276,12 @@
     </row>
     <row r="177" spans="6:6">
       <c r="F177" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="178" spans="6:6">
       <c r="F178" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC938CB-5B0A-4541-A249-76AE0430FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D4AF62-A788-418D-9CD8-EEB8EB41CECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -29687,7 +29687,7 @@
         <v>377</v>
       </c>
       <c r="AI161" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ161" s="10" t="s">
         <v>1300</v>
@@ -29836,10 +29836,10 @@
         <v>363</v>
       </c>
       <c r="AH162" s="10" t="s">
-        <v>53</v>
+        <v>377</v>
       </c>
       <c r="AI162" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ162" s="10" t="s">
         <v>1300</v>
@@ -29986,10 +29986,10 @@
         <v>363</v>
       </c>
       <c r="AH163" s="10" t="s">
-        <v>53</v>
+        <v>377</v>
       </c>
       <c r="AI163" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ163" s="10" t="s">
         <v>1300</v>
@@ -30286,10 +30286,10 @@
         <v>363</v>
       </c>
       <c r="AH165" s="10" t="s">
-        <v>53</v>
+        <v>377</v>
       </c>
       <c r="AI165" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ165" s="10" t="s">
         <v>1300</v>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D4AF62-A788-418D-9CD8-EEB8EB41CECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC26A113-E0B9-4238-B851-668F77CB5A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5202" uniqueCount="1312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5449" uniqueCount="1393">
   <si>
     <t>Contact</t>
   </si>
@@ -3982,6 +3982,249 @@
   </si>
   <si>
     <t>30 (SS) + 55</t>
+  </si>
+  <si>
+    <t>23 avenue Paul Doumer</t>
+  </si>
+  <si>
+    <t>Melun</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/iuyJpb23bTGqeB1K7</t>
+  </si>
+  <si>
+    <t>300 (SS) + 230</t>
+  </si>
+  <si>
+    <t>Immeuble en cœur de ville de Melun avec possibilité d'extraction</t>
+  </si>
+  <si>
+    <t>FNAC, Prêt-à-porter, opticiens, alimentaire, services</t>
+  </si>
+  <si>
+    <t>48.539540</t>
+  </si>
+  <si>
+    <t>2.660129</t>
+  </si>
+  <si>
+    <t>188 €/m² = 100 000 €</t>
+  </si>
+  <si>
+    <t>F&amp;A AM</t>
+  </si>
+  <si>
+    <t>1 boulevard Exelmans</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RvTG1EctYY1Bm17a8</t>
+  </si>
+  <si>
+    <t>37 (SS) + 150</t>
+  </si>
+  <si>
+    <t>481 €/m² = 90 000 €</t>
+  </si>
+  <si>
+    <t>48.839598</t>
+  </si>
+  <si>
+    <t>2.266925</t>
+  </si>
+  <si>
+    <t>Restaurant, crèches, services, bureaux</t>
+  </si>
+  <si>
+    <t>90 rue d'Alésia</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1jMgZMcv7EFgTvAK7</t>
+  </si>
+  <si>
+    <t>15 (SS) + 44</t>
+  </si>
+  <si>
+    <t>711 €/m² = 42 000 €</t>
+  </si>
+  <si>
+    <t>48.829019</t>
+  </si>
+  <si>
+    <t>2.323831</t>
+  </si>
+  <si>
+    <t>Monoprix, Normal, Gifi, prêt-à-porter, services, alimentaire</t>
+  </si>
+  <si>
+    <t>356 rue des Pyrénées</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5tYy72axTe6ybMqH8</t>
+  </si>
+  <si>
+    <t>897 €/m² = 35 000 €</t>
+  </si>
+  <si>
+    <t>2.386496</t>
+  </si>
+  <si>
+    <t>48.873986</t>
+  </si>
+  <si>
+    <t>McDonald's, carrefour, tabac, banque, alimentaire, services</t>
+  </si>
+  <si>
+    <t>103 rue Legendre</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tjMaHorSgGr3n8rT8</t>
+  </si>
+  <si>
+    <t>645 €/m² = 60 000 €</t>
+  </si>
+  <si>
+    <t>Axe commerçant majeur du 17èm. Local disponible en juin 2026</t>
+  </si>
+  <si>
+    <t>Prêt-à-porter, décoration, restaurants, services, banques, crèche</t>
+  </si>
+  <si>
+    <t>86 avenue Edouard Vaillant</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FVhfY8aR3d29ecvj8</t>
+  </si>
+  <si>
+    <t>709 €/m² = 100 000 €</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jbz4ipieRFJ7Dw9XA</t>
+  </si>
+  <si>
+    <t>73 bis rue Saint-Jean</t>
+  </si>
+  <si>
+    <t>Le Touquet-Paris-Plage</t>
+  </si>
+  <si>
+    <t>44 + 42</t>
+  </si>
+  <si>
+    <t>46 (SS) + 95</t>
+  </si>
+  <si>
+    <t>581 €/m² = 50 000 €</t>
+  </si>
+  <si>
+    <t>50.523456</t>
+  </si>
+  <si>
+    <t>1.586291</t>
+  </si>
+  <si>
+    <t>65 rue du Bourg</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/diStniyzoSdM1MyY9</t>
+  </si>
+  <si>
+    <t>90 (SS) + 245</t>
+  </si>
+  <si>
+    <t>298 €/m² = 100 000 €</t>
+  </si>
+  <si>
+    <t>5.039061</t>
+  </si>
+  <si>
+    <t>47.320272</t>
+  </si>
+  <si>
+    <t>2.245769</t>
+  </si>
+  <si>
+    <t>48.834521</t>
+  </si>
+  <si>
+    <t>48.888632</t>
+  </si>
+  <si>
+    <t>2.321784</t>
+  </si>
+  <si>
+    <t>97 rue Emile Zola</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/MfExA2kLYmXWnAtz5</t>
+  </si>
+  <si>
+    <t>188 + 190</t>
+  </si>
+  <si>
+    <t>190 €/m² = 72 000 €</t>
+  </si>
+  <si>
+    <t>48.295789</t>
+  </si>
+  <si>
+    <t>4.073447</t>
+  </si>
+  <si>
+    <t>9 Rue du Marché Saint-Honoré</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/UERKrpwZMN1CAx7L9</t>
+  </si>
+  <si>
+    <t>48 + cave</t>
+  </si>
+  <si>
+    <t>2500 €/m² = 120 000 €</t>
+  </si>
+  <si>
+    <t>48.866245</t>
+  </si>
+  <si>
+    <t>2.331224</t>
+  </si>
+  <si>
+    <t>Local en angle avec vue sur la Seine. Historiquement un restaurant. Local disponible en juillet 2026</t>
+  </si>
+  <si>
+    <t>Axe commerçant majeur du 14èm. Local disponible en juillet 2026</t>
+  </si>
+  <si>
+    <t>Extraction possible (monopropriété). Local disponible en juillet 2026.</t>
+  </si>
+  <si>
+    <t>Division et extraction possible</t>
+  </si>
+  <si>
+    <t>Emplacement en angle sur l'un des axes majeurs de Boulogne, à 35 m de la place Marcel Sembat. Restauration froide acceptée</t>
+  </si>
+  <si>
+    <t>Restaurants, décoration, automobile, services, banques</t>
+  </si>
+  <si>
+    <t>Saint-James, Kujten, Des Petits Hauts, Yves Rocher, Mango, Promod</t>
+  </si>
+  <si>
+    <t>Des Petits Hauts, Franprix, Caroll, Comptoir des Cotonniers, American Vintage</t>
+  </si>
+  <si>
+    <t>Sephora, Yves Rocher, Promod, Caroll, Kiko, Courir, Calzedonia, Undiz</t>
+  </si>
+  <si>
+    <t>Pain de sucre, Essentiel, Heschung, Oh my Cream !, restaurants</t>
+  </si>
+  <si>
+    <t>Rue commercante reliant la rue St-Honoré à la place du marché, en plein cœur de Paris</t>
   </si>
 </sst>
 </file>
@@ -4609,8 +4852,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU177" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AU177" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU187" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AU187" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="47">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="46" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -5002,7 +5245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BD183"/>
+  <dimension ref="A1:BD204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -27684,7 +27927,7 @@
         <v>56000</v>
       </c>
       <c r="AD148" s="12" t="str">
-        <f t="shared" ref="AD148:AD177" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AD148:AD187" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
         <v>3 mois = 10 000 €</v>
       </c>
       <c r="AE148" s="6" t="s">
@@ -29594,7 +29837,7 @@
       <c r="F161" s="10" t="s">
         <v>1133</v>
       </c>
-      <c r="G161" s="47" t="str">
+      <c r="G161" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>ZAC D'Aulnoy
 59300 - Aulnoy-lez-Valenciennes</v>
@@ -29661,14 +29904,14 @@
       </c>
       <c r="AA161" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>12000</v>
-      </c>
-      <c r="AB161" s="6">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="AB161" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="AC161" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>205680</v>
+        <v>193680</v>
       </c>
       <c r="AD161" s="12" t="str">
         <f t="shared" si="6"/>
@@ -29746,7 +29989,7 @@
       <c r="F162" s="10" t="s">
         <v>1133</v>
       </c>
-      <c r="G162" s="47" t="str">
+      <c r="G162" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>ZAC D'Aulnoy
 59300 - Aulnoy-lez-Valenciennes</v>
@@ -29896,7 +30139,7 @@
       <c r="F163" s="10" t="s">
         <v>1133</v>
       </c>
-      <c r="G163" s="47" t="str">
+      <c r="G163" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>ZAC D'Aulnoy
 59300 - Aulnoy-lez-Valenciennes</v>
@@ -30046,7 +30289,7 @@
       <c r="F164" s="10" t="s">
         <v>1133</v>
       </c>
-      <c r="G164" s="47" t="str">
+      <c r="G164" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>ZAC D'Aulnoy
 59300 - Aulnoy-lez-Valenciennes</v>
@@ -30196,7 +30439,7 @@
       <c r="F165" s="10" t="s">
         <v>1133</v>
       </c>
-      <c r="G165" s="47" t="str">
+      <c r="G165" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>ZAC D'Aulnoy
 59300 - Aulnoy-lez-Valenciennes</v>
@@ -30346,7 +30589,7 @@
       <c r="F166" s="10" t="s">
         <v>1133</v>
       </c>
-      <c r="G166" s="47" t="str">
+      <c r="G166" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>ZAC D'Aulnoy
 59300 - Aulnoy-lez-Valenciennes</v>
@@ -32150,13 +32393,1417 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="182" spans="1:47">
-      <c r="F182" s="1" t="s">
+    <row r="178" spans="1:47" ht="25.5">
+      <c r="A178" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B178" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Seine-et-Marne</v>
+      </c>
+      <c r="C178" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>77</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E178" s="10">
+        <v>77000</v>
+      </c>
+      <c r="F178" s="10" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G178" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>23 avenue Paul Doumer
+77000 - Melun</v>
+      </c>
+      <c r="H178" s="15" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J178" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K178" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L178" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M178" s="36"/>
+      <c r="N178" s="34">
+        <v>530</v>
+      </c>
+      <c r="O178" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="P178" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q178" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R178" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>132500</v>
+      </c>
+      <c r="S178" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>11041.666666666666</v>
+      </c>
+      <c r="T178" s="12">
+        <v>250</v>
+      </c>
+      <c r="U178" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V178" s="12"/>
+      <c r="W178" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X178" s="12"/>
+      <c r="Y178" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z178" s="12"/>
+      <c r="AA178" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB178" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC178" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>132500</v>
+      </c>
+      <c r="AD178" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 33 125 €</v>
+      </c>
+      <c r="AE178" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF178" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG178" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH178" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI178" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ178" s="10" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AK178" s="11" t="s">
+        <v>1316</v>
+      </c>
+      <c r="AL178" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM178" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="AN178" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="AO178" s="11">
+        <v>50</v>
+      </c>
+      <c r="AP178" s="36"/>
+      <c r="AQ178" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR178" s="11" t="s">
+        <v>1320</v>
+      </c>
+      <c r="AS178" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT178" s="14"/>
+      <c r="AU178" s="44">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="179" spans="1:47" ht="25.5">
+      <c r="A179" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B179" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Paris</v>
+      </c>
+      <c r="C179" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>75</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E179" s="10">
+        <v>75016</v>
+      </c>
+      <c r="F179" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G179" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>1 boulevard Exelmans
+75016 - Paris</v>
+      </c>
+      <c r="H179" s="15" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I179" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J179" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K179" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L179" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M179" s="36"/>
+      <c r="N179" s="34">
+        <v>187</v>
+      </c>
+      <c r="O179" s="12" t="s">
+        <v>1324</v>
+      </c>
+      <c r="P179" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q179" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R179" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>112200</v>
+      </c>
+      <c r="S179" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>9350</v>
+      </c>
+      <c r="T179" s="12">
+        <v>600</v>
+      </c>
+      <c r="U179" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V179" s="12"/>
+      <c r="W179" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X179" s="12"/>
+      <c r="Y179" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z179" s="12"/>
+      <c r="AA179" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB179" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC179" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>112200</v>
+      </c>
+      <c r="AD179" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 28 050 €</v>
+      </c>
+      <c r="AE179" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF179" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG179" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH179" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI179" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ179" s="10" t="s">
+        <v>1328</v>
+      </c>
+      <c r="AK179" s="11" t="s">
+        <v>1382</v>
+      </c>
+      <c r="AL179" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM179" s="11" t="s">
+        <v>1326</v>
+      </c>
+      <c r="AN179" s="11" t="s">
+        <v>1327</v>
+      </c>
+      <c r="AO179" s="11">
+        <v>51</v>
+      </c>
+      <c r="AP179" s="36"/>
+      <c r="AQ179" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR179" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="AS179" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT179" s="14"/>
+      <c r="AU179" s="44"/>
+    </row>
+    <row r="180" spans="1:47" ht="25.5">
+      <c r="A180" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B180" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Paris</v>
+      </c>
+      <c r="C180" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>75</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E180" s="10">
+        <v>75014</v>
+      </c>
+      <c r="F180" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G180" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>90 rue d'Alésia
+75014 - Paris</v>
+      </c>
+      <c r="H180" s="15" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I180" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J180" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K180" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L180" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M180" s="36"/>
+      <c r="N180" s="34">
+        <v>59</v>
+      </c>
+      <c r="O180" s="12" t="s">
+        <v>1331</v>
+      </c>
+      <c r="P180" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q180" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R180" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>53100</v>
+      </c>
+      <c r="S180" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4425</v>
+      </c>
+      <c r="T180" s="12">
+        <v>900</v>
+      </c>
+      <c r="U180" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V180" s="12"/>
+      <c r="W180" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X180" s="12"/>
+      <c r="Y180" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z180" s="12"/>
+      <c r="AA180" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB180" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC180" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>53100</v>
+      </c>
+      <c r="AD180" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 13 275 €</v>
+      </c>
+      <c r="AE180" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF180" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG180" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH180" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI180" s="10"/>
+      <c r="AJ180" s="10" t="s">
+        <v>1335</v>
+      </c>
+      <c r="AK180" s="11" t="s">
+        <v>1383</v>
+      </c>
+      <c r="AL180" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM180" s="11" t="s">
+        <v>1333</v>
+      </c>
+      <c r="AN180" s="11" t="s">
+        <v>1334</v>
+      </c>
+      <c r="AO180" s="11">
+        <v>52</v>
+      </c>
+      <c r="AP180" s="36"/>
+      <c r="AQ180" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR180" s="11" t="s">
+        <v>1332</v>
+      </c>
+      <c r="AS180" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT180" s="14"/>
+      <c r="AU180" s="44"/>
+    </row>
+    <row r="181" spans="1:47" ht="25.5">
+      <c r="A181" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B181" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Paris</v>
+      </c>
+      <c r="C181" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>75</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E181" s="10">
+        <v>75020</v>
+      </c>
+      <c r="F181" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G181" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>356 rue des Pyrénées
+75020 - Paris</v>
+      </c>
+      <c r="H181" s="15" t="s">
+        <v>1337</v>
+      </c>
+      <c r="I181" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J181" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K181" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L181" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M181" s="36"/>
+      <c r="N181" s="34">
+        <v>39</v>
+      </c>
+      <c r="O181" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="P181" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q181" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R181" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>42900</v>
+      </c>
+      <c r="S181" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3575</v>
+      </c>
+      <c r="T181" s="12">
+        <v>1100</v>
+      </c>
+      <c r="U181" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V181" s="12"/>
+      <c r="W181" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X181" s="12"/>
+      <c r="Y181" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z181" s="12"/>
+      <c r="AA181" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB181" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC181" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>42900</v>
+      </c>
+      <c r="AD181" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 10 725 €</v>
+      </c>
+      <c r="AE181" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF181" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG181" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH181" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI181" s="10"/>
+      <c r="AJ181" s="10" t="s">
+        <v>1341</v>
+      </c>
+      <c r="AK181" s="11"/>
+      <c r="AL181" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM181" s="11" t="s">
+        <v>1340</v>
+      </c>
+      <c r="AN181" s="11" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AO181" s="11">
+        <v>53</v>
+      </c>
+      <c r="AP181" s="36"/>
+      <c r="AQ181" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR181" s="11" t="s">
+        <v>1338</v>
+      </c>
+      <c r="AS181" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT181" s="14"/>
+      <c r="AU181" s="44"/>
+    </row>
+    <row r="182" spans="1:47" ht="25.5">
+      <c r="A182" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B182" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Paris</v>
+      </c>
+      <c r="C182" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>75</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E182" s="26">
+        <v>75017</v>
+      </c>
+      <c r="F182" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G182" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>103 rue Legendre
+75017 - Paris</v>
+      </c>
+      <c r="H182" s="15" t="s">
+        <v>1343</v>
+      </c>
+      <c r="I182" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J182" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K182" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L182" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M182" s="36"/>
+      <c r="N182" s="34">
+        <v>93</v>
+      </c>
+      <c r="O182" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="P182" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q182" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R182" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>74400</v>
+      </c>
+      <c r="S182" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>6200</v>
+      </c>
+      <c r="T182" s="12">
+        <v>800</v>
+      </c>
+      <c r="U182" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V182" s="12"/>
+      <c r="W182" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X182" s="12"/>
+      <c r="Y182" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z182" s="12"/>
+      <c r="AA182" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB182" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC182" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>74400</v>
+      </c>
+      <c r="AD182" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 18 600 €</v>
+      </c>
+      <c r="AE182" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF182" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG182" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH182" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI182" s="10"/>
+      <c r="AJ182" s="10" t="s">
+        <v>1346</v>
+      </c>
+      <c r="AK182" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="AL182" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM182" s="11" t="s">
+        <v>1367</v>
+      </c>
+      <c r="AN182" s="11" t="s">
+        <v>1368</v>
+      </c>
+      <c r="AO182" s="11">
+        <v>54</v>
+      </c>
+      <c r="AP182" s="36"/>
+      <c r="AQ182" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR182" s="11" t="s">
+        <v>1344</v>
+      </c>
+      <c r="AS182" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT182" s="14"/>
+      <c r="AU182" s="44"/>
+    </row>
+    <row r="183" spans="1:47" ht="25.5">
+      <c r="A183" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B183" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Hauts-de-Seine</v>
+      </c>
+      <c r="C183" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>92</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E183" s="10">
+        <v>92100</v>
+      </c>
+      <c r="F183" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G183" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>86 avenue Edouard Vaillant
+92100 - Boulogne-Billancourt</v>
+      </c>
+      <c r="H183" s="15" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I183" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J183" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K183" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L183" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M183" s="36"/>
+      <c r="N183" s="34">
+        <v>141</v>
+      </c>
+      <c r="O183" s="12" t="s">
+        <v>1354</v>
+      </c>
+      <c r="P183" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q183" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R183" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>112800</v>
+      </c>
+      <c r="S183" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>9400</v>
+      </c>
+      <c r="T183" s="12">
+        <v>800</v>
+      </c>
+      <c r="U183" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V183" s="12"/>
+      <c r="W183" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X183" s="12"/>
+      <c r="Y183" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z183" s="12"/>
+      <c r="AA183" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB183" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC183" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>112800</v>
+      </c>
+      <c r="AD183" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 28 200 €</v>
+      </c>
+      <c r="AE183" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF183" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG183" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH183" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI183" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AJ183" s="10" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AK183" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AL183" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM183" s="11" t="s">
+        <v>1366</v>
+      </c>
+      <c r="AN183" s="11" t="s">
+        <v>1365</v>
+      </c>
+      <c r="AO183" s="11">
+        <v>55</v>
+      </c>
+      <c r="AP183" s="36"/>
+      <c r="AQ183" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR183" s="11" t="s">
+        <v>1349</v>
+      </c>
+      <c r="AS183" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT183" s="14"/>
+      <c r="AU183" s="44"/>
+    </row>
+    <row r="184" spans="1:47" ht="25.5">
+      <c r="A184" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B184" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Pas-de-Calais</v>
+      </c>
+      <c r="C184" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>62</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E184" s="10">
+        <v>62520</v>
+      </c>
+      <c r="F184" s="10" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G184" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>73 bis rue Saint-Jean
+62520 - Le Touquet-Paris-Plage</v>
+      </c>
+      <c r="H184" s="15" t="s">
+        <v>1350</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K184" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L184" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M184" s="36"/>
+      <c r="N184" s="34">
+        <v>86</v>
+      </c>
+      <c r="O184" s="12" t="s">
+        <v>1353</v>
+      </c>
+      <c r="P184" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q184" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R184" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>60200</v>
+      </c>
+      <c r="S184" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5016.666666666667</v>
+      </c>
+      <c r="T184" s="12">
+        <v>700</v>
+      </c>
+      <c r="U184" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V184" s="12"/>
+      <c r="W184" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X184" s="12"/>
+      <c r="Y184" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z184" s="12"/>
+      <c r="AA184" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB184" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC184" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>60200</v>
+      </c>
+      <c r="AD184" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 15 050 €</v>
+      </c>
+      <c r="AE184" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF184" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG184" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH184" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI184" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ184" s="10" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AK184" s="11" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AL184" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM184" s="11" t="s">
+        <v>1356</v>
+      </c>
+      <c r="AN184" s="11" t="s">
+        <v>1357</v>
+      </c>
+      <c r="AO184" s="11">
+        <v>56</v>
+      </c>
+      <c r="AP184" s="36"/>
+      <c r="AQ184" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR184" s="11" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AS184" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT184" s="14"/>
+      <c r="AU184" s="44"/>
+    </row>
+    <row r="185" spans="1:47" ht="25.5">
+      <c r="A185" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Bourgogne-Franche-Comté</v>
+      </c>
+      <c r="B185" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Côte-d'Or</v>
+      </c>
+      <c r="C185" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>21</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E185" s="10">
+        <v>21000</v>
+      </c>
+      <c r="F185" s="10" t="s">
+        <v>1359</v>
+      </c>
+      <c r="G185" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>65 rue du Bourg
+21000 - Dijon</v>
+      </c>
+      <c r="H185" s="15" t="s">
+        <v>1360</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J185" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K185" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L185" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M185" s="36"/>
+      <c r="N185" s="34">
+        <v>335</v>
+      </c>
+      <c r="O185" s="12" t="s">
+        <v>1361</v>
+      </c>
+      <c r="P185" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q185" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R185" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>134000</v>
+      </c>
+      <c r="S185" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>11166.666666666666</v>
+      </c>
+      <c r="T185" s="12">
+        <v>400</v>
+      </c>
+      <c r="U185" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V185" s="12"/>
+      <c r="W185" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X185" s="12"/>
+      <c r="Y185" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z185" s="12"/>
+      <c r="AA185" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB185" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC185" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>134000</v>
+      </c>
+      <c r="AD185" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 33 500 €</v>
+      </c>
+      <c r="AE185" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF185" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG185" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH185" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI185" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ185" s="10" t="s">
+        <v>1389</v>
+      </c>
+      <c r="AK185" s="11" t="s">
+        <v>1385</v>
+      </c>
+      <c r="AL185" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM185" s="11" t="s">
+        <v>1364</v>
+      </c>
+      <c r="AN185" s="11" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AO185" s="11">
+        <v>57</v>
+      </c>
+      <c r="AP185" s="36"/>
+      <c r="AQ185" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR185" s="11" t="s">
+        <v>1362</v>
+      </c>
+      <c r="AS185" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT185" s="14"/>
+      <c r="AU185" s="44"/>
+    </row>
+    <row r="186" spans="1:47" ht="25.5">
+      <c r="A186" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B186" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Aube</v>
+      </c>
+      <c r="C186" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>10</v>
+      </c>
+      <c r="D186" s="10" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E186" s="10">
+        <v>10000</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G186" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>97 rue Emile Zola
+10000 - Troyes</v>
+      </c>
+      <c r="H186" s="15" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I186" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K186" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L186" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M186" s="36"/>
+      <c r="N186" s="34">
+        <v>378</v>
+      </c>
+      <c r="O186" s="12" t="s">
+        <v>1372</v>
+      </c>
+      <c r="P186" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q186" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R186" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>113400</v>
+      </c>
+      <c r="S186" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>9450</v>
+      </c>
+      <c r="T186" s="12">
+        <v>300</v>
+      </c>
+      <c r="U186" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V186" s="12"/>
+      <c r="W186" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X186" s="12"/>
+      <c r="Y186" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z186" s="12"/>
+      <c r="AA186" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB186" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC186" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>113400</v>
+      </c>
+      <c r="AD186" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 28 350 €</v>
+      </c>
+      <c r="AE186" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF186" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG186" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH186" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI186" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ186" s="10" t="s">
+        <v>1390</v>
+      </c>
+      <c r="AK186" s="11" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AL186" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM186" s="11" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AN186" s="11" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AO186" s="11">
+        <v>58</v>
+      </c>
+      <c r="AP186" s="36"/>
+      <c r="AQ186" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR186" s="11" t="s">
+        <v>1373</v>
+      </c>
+      <c r="AS186" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT186" s="14"/>
+      <c r="AU186" s="44"/>
+    </row>
+    <row r="187" spans="1:47" ht="25.5">
+      <c r="A187" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B187" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Paris</v>
+      </c>
+      <c r="C187" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>75</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E187" s="10">
+        <v>75001</v>
+      </c>
+      <c r="F187" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G187" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>9 Rue du Marché Saint-Honoré
+75001 - Paris</v>
+      </c>
+      <c r="H187" s="15" t="s">
+        <v>1377</v>
+      </c>
+      <c r="I187" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J187" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K187" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L187" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M187" s="36"/>
+      <c r="N187" s="34">
+        <v>48</v>
+      </c>
+      <c r="O187" s="12" t="s">
+        <v>1378</v>
+      </c>
+      <c r="P187" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q187" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R187" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>134400</v>
+      </c>
+      <c r="S187" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>11200</v>
+      </c>
+      <c r="T187" s="12">
+        <v>2800</v>
+      </c>
+      <c r="U187" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V187" s="12"/>
+      <c r="W187" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X187" s="12"/>
+      <c r="Y187" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z187" s="12"/>
+      <c r="AA187" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB187" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC187" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>134400</v>
+      </c>
+      <c r="AD187" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 33 600 €</v>
+      </c>
+      <c r="AE187" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF187" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG187" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH187" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI187" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AJ187" s="10" t="s">
+        <v>1391</v>
+      </c>
+      <c r="AK187" s="11" t="s">
+        <v>1392</v>
+      </c>
+      <c r="AL187" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM187" s="11" t="s">
+        <v>1380</v>
+      </c>
+      <c r="AN187" s="11" t="s">
+        <v>1381</v>
+      </c>
+      <c r="AO187" s="11">
+        <v>59</v>
+      </c>
+      <c r="AP187" s="36"/>
+      <c r="AQ187" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR187" s="11" t="s">
+        <v>1379</v>
+      </c>
+      <c r="AS187" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="AT187" s="14"/>
+      <c r="AU187" s="44"/>
+    </row>
+    <row r="203" spans="6:6">
+      <c r="F203" s="1" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="183" spans="1:47">
-      <c r="F183" s="1" t="s">
+    <row r="204" spans="6:6">
+      <c r="F204" s="1" t="s">
         <v>1035</v>
       </c>
     </row>
@@ -32302,6 +33949,15 @@
     <hyperlink ref="H177" r:id="rId137" xr:uid="{0DCDD234-61DD-4535-96A0-1CB0ED1C39E2}"/>
     <hyperlink ref="H161" r:id="rId138" xr:uid="{69AC0ECC-2E2A-4A8B-BC81-EF4428A37640}"/>
     <hyperlink ref="H162:H166" r:id="rId139" display="https://maps.app.goo.gl/jjHUN2H4tKUGyBEQ7" xr:uid="{2DDA41A9-46D6-46F1-BFA4-95D30FE59882}"/>
+    <hyperlink ref="H178" r:id="rId140" xr:uid="{F6366A42-B67C-40CD-AFBC-6C8424BEB013}"/>
+    <hyperlink ref="H180" r:id="rId141" xr:uid="{AC4BD242-08DC-4A93-AF73-32CF15E14420}"/>
+    <hyperlink ref="H181" r:id="rId142" xr:uid="{3FEF2131-529B-4B74-9649-3B4B1CFC2613}"/>
+    <hyperlink ref="H182" r:id="rId143" xr:uid="{3F02EB48-A165-461F-8BAF-AC050FE23690}"/>
+    <hyperlink ref="H183" r:id="rId144" xr:uid="{145A22A7-33A1-43C0-A440-9E0FD9BB1AD1}"/>
+    <hyperlink ref="H184" r:id="rId145" xr:uid="{A5000FCA-4DF3-47B7-97D9-DAAC213C360B}"/>
+    <hyperlink ref="H185" r:id="rId146" xr:uid="{9FF463BE-AA91-4BC5-AE7D-4936D1C6D265}"/>
+    <hyperlink ref="H186" r:id="rId147" xr:uid="{EED7450E-F5F5-483A-B269-54C932486E0F}"/>
+    <hyperlink ref="H187" r:id="rId148" xr:uid="{B52E97C0-A3E5-471B-BD01-7BEB96586BB6}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -32310,7 +33966,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId140"/>
+    <tablePart r:id="rId149"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC26A113-E0B9-4238-B851-668F77CB5A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130416FF-20CB-4DA6-8053-837E8702F0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5449" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5474" uniqueCount="1404">
   <si>
     <t>Contact</t>
   </si>
@@ -4225,6 +4225,40 @@
   </si>
   <si>
     <t>Rue commercante reliant la rue St-Honoré à la place du marché, en plein cœur de Paris</t>
+  </si>
+  <si>
+    <t>06 700</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/e1ddei1i8yHZXuQi8</t>
+  </si>
+  <si>
+    <t>01 000</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Cap Émeraude
+Avenue du Capitaine Dhonne</t>
+  </si>
+  <si>
+    <t>46.221075</t>
+  </si>
+  <si>
+    <t>5.241758</t>
+  </si>
+  <si>
+    <t>1er centre commercial de l'Ain. 1,3 M de Tickets hyper/an. 50 magasins</t>
+  </si>
+  <si>
+    <t>H&amp;M, Intersport, Mango, Kingjouet, Gemo, Promod, Eram, Graind e Malice, Armand Thierry, restaurants</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/5%20Plan%20de%20situation.jpg</t>
+  </si>
+  <si>
+    <t>Leclerc Bourg-en-Bresse</t>
   </si>
 </sst>
 </file>
@@ -4355,7 +4389,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -4481,6 +4515,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4852,8 +4892,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU187" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AU187" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU188" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AU188" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="47">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="46" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -21188,7 +21228,7 @@
       <c r="D104" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E104" s="10">
+      <c r="E104" s="26">
         <v>34470</v>
       </c>
       <c r="F104" s="10" t="s">
@@ -21345,7 +21385,7 @@
       <c r="D105" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E105" s="10">
+      <c r="E105" s="25">
         <v>34470</v>
       </c>
       <c r="F105" s="10" t="s">
@@ -21496,7 +21536,7 @@
       <c r="D106" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E106" s="10">
+      <c r="E106" s="26">
         <v>34470</v>
       </c>
       <c r="F106" s="10" t="s">
@@ -21645,7 +21685,7 @@
       <c r="D107" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E107" s="10">
+      <c r="E107" s="25">
         <v>34470</v>
       </c>
       <c r="F107" s="10" t="s">
@@ -21796,7 +21836,7 @@
       <c r="D108" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E108" s="10">
+      <c r="E108" s="26">
         <v>34470</v>
       </c>
       <c r="F108" s="10" t="s">
@@ -21947,7 +21987,7 @@
       <c r="D109" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E109" s="10">
+      <c r="E109" s="25">
         <v>34470</v>
       </c>
       <c r="F109" s="10" t="s">
@@ -22098,7 +22138,7 @@
       <c r="D110" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E110" s="10">
+      <c r="E110" s="26">
         <v>34470</v>
       </c>
       <c r="F110" s="10" t="s">
@@ -22249,7 +22289,7 @@
       <c r="D111" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E111" s="10">
+      <c r="E111" s="25">
         <v>34470</v>
       </c>
       <c r="F111" s="10" t="s">
@@ -22400,7 +22440,7 @@
       <c r="D112" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E112" s="10">
+      <c r="E112" s="26">
         <v>34470</v>
       </c>
       <c r="F112" s="10" t="s">
@@ -22554,7 +22594,7 @@
       <c r="D113" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E113" s="10">
+      <c r="E113" s="25">
         <v>34470</v>
       </c>
       <c r="F113" s="10" t="s">
@@ -22708,7 +22748,7 @@
       <c r="D114" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E114" s="10">
+      <c r="E114" s="26">
         <v>34470</v>
       </c>
       <c r="F114" s="10" t="s">
@@ -22862,7 +22902,7 @@
       <c r="D115" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E115" s="10">
+      <c r="E115" s="25">
         <v>34470</v>
       </c>
       <c r="F115" s="10" t="s">
@@ -23016,7 +23056,7 @@
       <c r="D116" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E116" s="10">
+      <c r="E116" s="26">
         <v>34470</v>
       </c>
       <c r="F116" s="10" t="s">
@@ -23170,7 +23210,7 @@
       <c r="D117" s="10" t="s">
         <v>904</v>
       </c>
-      <c r="E117" s="10">
+      <c r="E117" s="26">
         <v>67600</v>
       </c>
       <c r="F117" s="10" t="s">
@@ -23480,7 +23520,7 @@
       <c r="D119" s="10" t="s">
         <v>915</v>
       </c>
-      <c r="E119" s="10">
+      <c r="E119" s="26">
         <v>92100</v>
       </c>
       <c r="F119" s="10" t="s">
@@ -23632,7 +23672,7 @@
       <c r="D120" s="10" t="s">
         <v>918</v>
       </c>
-      <c r="E120" s="10">
+      <c r="E120" s="26">
         <v>75020</v>
       </c>
       <c r="F120" s="10" t="s">
@@ -23786,7 +23826,7 @@
       <c r="D121" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E121" s="10">
+      <c r="E121" s="26">
         <v>93430</v>
       </c>
       <c r="F121" s="10" t="s">
@@ -23941,7 +23981,7 @@
       <c r="D122" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E122" s="10">
+      <c r="E122" s="26">
         <v>93430</v>
       </c>
       <c r="F122" s="10" t="s">
@@ -24096,7 +24136,7 @@
       <c r="D123" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E123" s="10">
+      <c r="E123" s="26">
         <v>93430</v>
       </c>
       <c r="F123" s="10" t="s">
@@ -24251,7 +24291,7 @@
       <c r="D124" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E124" s="10">
+      <c r="E124" s="26">
         <v>93430</v>
       </c>
       <c r="F124" s="10" t="s">
@@ -24406,7 +24446,7 @@
       <c r="D125" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E125" s="10">
+      <c r="E125" s="26">
         <v>93430</v>
       </c>
       <c r="F125" s="10" t="s">
@@ -24561,7 +24601,7 @@
       <c r="D126" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E126" s="10">
+      <c r="E126" s="26">
         <v>93430</v>
       </c>
       <c r="F126" s="10" t="s">
@@ -24713,7 +24753,7 @@
       <c r="D127" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E127" s="10">
+      <c r="E127" s="26">
         <v>93430</v>
       </c>
       <c r="F127" s="10" t="s">
@@ -24865,7 +24905,7 @@
       <c r="D128" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E128" s="10">
+      <c r="E128" s="26">
         <v>93430</v>
       </c>
       <c r="F128" s="10" t="s">
@@ -25017,7 +25057,7 @@
       <c r="D129" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E129" s="10">
+      <c r="E129" s="26">
         <v>93430</v>
       </c>
       <c r="F129" s="10" t="s">
@@ -25169,7 +25209,7 @@
       <c r="D130" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E130" s="10">
+      <c r="E130" s="26">
         <v>93430</v>
       </c>
       <c r="F130" s="10" t="s">
@@ -25321,7 +25361,7 @@
       <c r="D131" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E131" s="10">
+      <c r="E131" s="26">
         <v>93430</v>
       </c>
       <c r="F131" s="10" t="s">
@@ -25473,7 +25513,7 @@
       <c r="D132" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E132" s="10">
+      <c r="E132" s="26">
         <v>93430</v>
       </c>
       <c r="F132" s="10" t="s">
@@ -25625,7 +25665,7 @@
       <c r="D133" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E133" s="10">
+      <c r="E133" s="26">
         <v>93430</v>
       </c>
       <c r="F133" s="10" t="s">
@@ -25777,7 +25817,7 @@
       <c r="D134" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E134" s="10">
+      <c r="E134" s="26">
         <v>93430</v>
       </c>
       <c r="F134" s="10" t="s">
@@ -25929,7 +25969,7 @@
       <c r="D135" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E135" s="10">
+      <c r="E135" s="26">
         <v>93430</v>
       </c>
       <c r="F135" s="10" t="s">
@@ -26081,7 +26121,7 @@
       <c r="D136" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E136" s="10">
+      <c r="E136" s="26">
         <v>93430</v>
       </c>
       <c r="F136" s="10" t="s">
@@ -26233,7 +26273,7 @@
       <c r="D137" s="10" t="s">
         <v>928</v>
       </c>
-      <c r="E137" s="10">
+      <c r="E137" s="26">
         <v>93430</v>
       </c>
       <c r="F137" s="10" t="s">
@@ -26385,7 +26425,7 @@
       <c r="D138" s="42" t="s">
         <v>992</v>
       </c>
-      <c r="E138" s="10">
+      <c r="E138" s="26">
         <v>95290</v>
       </c>
       <c r="F138" s="10" t="s">
@@ -26537,7 +26577,7 @@
       <c r="D139" s="42" t="s">
         <v>1002</v>
       </c>
-      <c r="E139" s="10">
+      <c r="E139" s="26">
         <v>95260</v>
       </c>
       <c r="F139" s="10" t="s">
@@ -26680,7 +26720,7 @@
       <c r="D140" s="42" t="s">
         <v>1002</v>
       </c>
-      <c r="E140" s="10">
+      <c r="E140" s="26">
         <v>95260</v>
       </c>
       <c r="F140" s="10" t="s">
@@ -26823,7 +26863,7 @@
       <c r="D141" s="42" t="s">
         <v>1002</v>
       </c>
-      <c r="E141" s="10">
+      <c r="E141" s="26">
         <v>95260</v>
       </c>
       <c r="F141" s="10" t="s">
@@ -26966,7 +27006,7 @@
       <c r="D142" s="42" t="s">
         <v>1002</v>
       </c>
-      <c r="E142" s="10">
+      <c r="E142" s="26">
         <v>95260</v>
       </c>
       <c r="F142" s="10" t="s">
@@ -27109,7 +27149,7 @@
       <c r="D143" s="42" t="s">
         <v>1002</v>
       </c>
-      <c r="E143" s="10">
+      <c r="E143" s="26">
         <v>95260</v>
       </c>
       <c r="F143" s="10" t="s">
@@ -27250,7 +27290,7 @@
       <c r="D144" s="10" t="s">
         <v>1024</v>
       </c>
-      <c r="E144" s="10">
+      <c r="E144" s="26">
         <v>44200</v>
       </c>
       <c r="F144" s="10" t="s">
@@ -27402,7 +27442,7 @@
       <c r="D145" s="10" t="s">
         <v>1024</v>
       </c>
-      <c r="E145" s="10">
+      <c r="E145" s="26">
         <v>44200</v>
       </c>
       <c r="F145" s="10" t="s">
@@ -27554,7 +27594,7 @@
       <c r="D146" s="42" t="s">
         <v>1040</v>
       </c>
-      <c r="E146" s="10">
+      <c r="E146" s="26">
         <v>68330</v>
       </c>
       <c r="F146" s="10" t="s">
@@ -27689,7 +27729,7 @@
       <c r="D147" s="10" t="s">
         <v>1046</v>
       </c>
-      <c r="E147" s="10">
+      <c r="E147" s="26">
         <v>37600</v>
       </c>
       <c r="F147" s="10" t="s">
@@ -27841,7 +27881,7 @@
       <c r="D148" s="10" t="s">
         <v>1046</v>
       </c>
-      <c r="E148" s="10">
+      <c r="E148" s="26">
         <v>37600</v>
       </c>
       <c r="F148" s="10" t="s">
@@ -27927,7 +27967,7 @@
         <v>56000</v>
       </c>
       <c r="AD148" s="12" t="str">
-        <f t="shared" ref="AD148:AD187" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AD148:AD188" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
         <v>3 mois = 10 000 €</v>
       </c>
       <c r="AE148" s="6" t="s">
@@ -27996,8 +28036,8 @@
       <c r="D149" s="10" t="s">
         <v>1046</v>
       </c>
-      <c r="E149" s="10">
-        <v>37601</v>
+      <c r="E149" s="26">
+        <v>37600</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>901</v>
@@ -28005,7 +28045,7 @@
       <c r="G149" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Super U 38 Route de Vauzelles, Rue du Bon Raisin
-37601 - Loches</v>
+37600 - Loches</v>
       </c>
       <c r="H149" s="15" t="s">
         <v>1057</v>
@@ -28151,8 +28191,8 @@
       <c r="D150" s="10" t="s">
         <v>1046</v>
       </c>
-      <c r="E150" s="10">
-        <v>37602</v>
+      <c r="E150" s="26">
+        <v>37600</v>
       </c>
       <c r="F150" s="10" t="s">
         <v>901</v>
@@ -28160,7 +28200,7 @@
       <c r="G150" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Super U 38 Route de Vauzelles, Rue du Bon Raisin
-37602 - Loches</v>
+37600 - Loches</v>
       </c>
       <c r="H150" s="15" t="s">
         <v>1057</v>
@@ -28306,8 +28346,8 @@
       <c r="D151" s="10" t="s">
         <v>1046</v>
       </c>
-      <c r="E151" s="10">
-        <v>37603</v>
+      <c r="E151" s="26">
+        <v>37600</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>901</v>
@@ -28315,7 +28355,7 @@
       <c r="G151" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Super U 38 Route de Vauzelles, Rue du Bon Raisin
-37603 - Loches</v>
+37600 - Loches</v>
       </c>
       <c r="H151" s="15" t="s">
         <v>1057</v>
@@ -28461,8 +28501,8 @@
       <c r="D152" s="10" t="s">
         <v>1046</v>
       </c>
-      <c r="E152" s="10">
-        <v>37604</v>
+      <c r="E152" s="26">
+        <v>37600</v>
       </c>
       <c r="F152" s="10" t="s">
         <v>901</v>
@@ -28470,7 +28510,7 @@
       <c r="G152" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Super U 38 Route de Vauzelles, Rue du Bon Raisin
-37604 - Loches</v>
+37600 - Loches</v>
       </c>
       <c r="H152" s="15" t="s">
         <v>1057</v>
@@ -28616,7 +28656,7 @@
       <c r="D153" s="10" t="s">
         <v>1104</v>
       </c>
-      <c r="E153" s="10">
+      <c r="E153" s="26">
         <v>13127</v>
       </c>
       <c r="F153" s="10" t="s">
@@ -28770,8 +28810,8 @@
       <c r="D154" s="10" t="s">
         <v>1104</v>
       </c>
-      <c r="E154" s="10">
-        <v>13128</v>
+      <c r="E154" s="26">
+        <v>13127</v>
       </c>
       <c r="F154" s="10" t="s">
         <v>1100</v>
@@ -28779,7 +28819,7 @@
       <c r="G154" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>14 Boulevard de l'Europe
-13128 - Vitrolles</v>
+13127 - Vitrolles</v>
       </c>
       <c r="H154" s="15" t="s">
         <v>1105</v>
@@ -28924,8 +28964,8 @@
       <c r="D155" s="10" t="s">
         <v>1104</v>
       </c>
-      <c r="E155" s="10">
-        <v>13129</v>
+      <c r="E155" s="26">
+        <v>13127</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>1100</v>
@@ -28933,7 +28973,7 @@
       <c r="G155" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>14 Boulevard de l'Europe
-13129 - Vitrolles</v>
+13127 - Vitrolles</v>
       </c>
       <c r="H155" s="15" t="s">
         <v>1105</v>
@@ -29078,8 +29118,8 @@
       <c r="D156" s="10" t="s">
         <v>1104</v>
       </c>
-      <c r="E156" s="10">
-        <v>13130</v>
+      <c r="E156" s="26">
+        <v>13127</v>
       </c>
       <c r="F156" s="10" t="s">
         <v>1100</v>
@@ -29087,7 +29127,7 @@
       <c r="G156" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>14 Boulevard de l'Europe
-13130 - Vitrolles</v>
+13127 - Vitrolles</v>
       </c>
       <c r="H156" s="15" t="s">
         <v>1105</v>
@@ -29232,7 +29272,7 @@
       <c r="D157" s="10" t="s">
         <v>1138</v>
       </c>
-      <c r="E157" s="10">
+      <c r="E157" s="26">
         <v>13170</v>
       </c>
       <c r="F157" s="10" t="s">
@@ -29385,7 +29425,7 @@
       <c r="D158" s="10" t="s">
         <v>1127</v>
       </c>
-      <c r="E158" s="10">
+      <c r="E158" s="26">
         <v>18390</v>
       </c>
       <c r="F158" s="10" t="s">
@@ -29537,7 +29577,7 @@
       <c r="D159" s="10" t="s">
         <v>1130</v>
       </c>
-      <c r="E159" s="10">
+      <c r="E159" s="26">
         <v>18230</v>
       </c>
       <c r="F159" s="10" t="s">
@@ -29679,7 +29719,7 @@
       <c r="D160" s="10" t="s">
         <v>1131</v>
       </c>
-      <c r="E160" s="10">
+      <c r="E160" s="26">
         <v>54000</v>
       </c>
       <c r="F160" s="10" t="s">
@@ -29831,7 +29871,7 @@
       <c r="D161" s="10" t="s">
         <v>1132</v>
       </c>
-      <c r="E161" s="10">
+      <c r="E161" s="26">
         <v>59300</v>
       </c>
       <c r="F161" s="10" t="s">
@@ -29983,7 +30023,7 @@
       <c r="D162" s="10" t="s">
         <v>1132</v>
       </c>
-      <c r="E162" s="10">
+      <c r="E162" s="26">
         <v>59300</v>
       </c>
       <c r="F162" s="10" t="s">
@@ -30133,7 +30173,7 @@
       <c r="D163" s="10" t="s">
         <v>1132</v>
       </c>
-      <c r="E163" s="10">
+      <c r="E163" s="26">
         <v>59300</v>
       </c>
       <c r="F163" s="10" t="s">
@@ -30283,7 +30323,7 @@
       <c r="D164" s="10" t="s">
         <v>1132</v>
       </c>
-      <c r="E164" s="10">
+      <c r="E164" s="26">
         <v>59300</v>
       </c>
       <c r="F164" s="10" t="s">
@@ -30433,7 +30473,7 @@
       <c r="D165" s="10" t="s">
         <v>1132</v>
       </c>
-      <c r="E165" s="10">
+      <c r="E165" s="26">
         <v>59300</v>
       </c>
       <c r="F165" s="10" t="s">
@@ -30583,7 +30623,7 @@
       <c r="D166" s="10" t="s">
         <v>1132</v>
       </c>
-      <c r="E166" s="10">
+      <c r="E166" s="26">
         <v>59300</v>
       </c>
       <c r="F166" s="10" t="s">
@@ -30733,7 +30773,7 @@
       <c r="D167" s="10" t="s">
         <v>1231</v>
       </c>
-      <c r="E167" s="10">
+      <c r="E167" s="26">
         <v>59320</v>
       </c>
       <c r="F167" s="10" t="s">
@@ -30885,7 +30925,7 @@
       <c r="D168" s="10" t="s">
         <v>1135</v>
       </c>
-      <c r="E168" s="10">
+      <c r="E168" s="26">
         <v>68270</v>
       </c>
       <c r="F168" s="10" t="s">
@@ -31037,7 +31077,7 @@
       <c r="D169" s="10" t="s">
         <v>1137</v>
       </c>
-      <c r="E169" s="10">
+      <c r="E169" s="26">
         <v>77140</v>
       </c>
       <c r="F169" s="10" t="s">
@@ -31189,7 +31229,7 @@
       <c r="D170" s="10" t="s">
         <v>1119</v>
       </c>
-      <c r="E170" s="10">
+      <c r="E170" s="26">
         <v>83160</v>
       </c>
       <c r="F170" s="10" t="s">
@@ -31340,8 +31380,8 @@
       <c r="D171" s="10" t="s">
         <v>1239</v>
       </c>
-      <c r="E171" s="10">
-        <v>83161</v>
+      <c r="E171" s="26">
+        <v>83160</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>1118</v>
@@ -31349,7 +31389,7 @@
       <c r="G171" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>83 Avenue de l'Université
-83161 - La Valette-du-Var</v>
+83160 - La Valette-du-Var</v>
       </c>
       <c r="H171" s="15" t="s">
         <v>1114</v>
@@ -31493,7 +31533,7 @@
       <c r="D172" s="10" t="s">
         <v>1120</v>
       </c>
-      <c r="E172" s="10">
+      <c r="E172" s="26">
         <v>84140</v>
       </c>
       <c r="F172" s="10" t="s">
@@ -31646,7 +31686,7 @@
       <c r="D173" s="10" t="s">
         <v>1123</v>
       </c>
-      <c r="E173" s="10">
+      <c r="E173" s="26">
         <v>94500</v>
       </c>
       <c r="F173" s="10" t="s">
@@ -31799,7 +31839,7 @@
       <c r="D174" s="10" t="s">
         <v>1121</v>
       </c>
-      <c r="E174" s="10">
+      <c r="E174" s="26">
         <v>94500</v>
       </c>
       <c r="F174" s="10" t="s">
@@ -31952,7 +31992,7 @@
       <c r="D175" s="10" t="s">
         <v>1123</v>
       </c>
-      <c r="E175" s="10">
+      <c r="E175" s="26">
         <v>94500</v>
       </c>
       <c r="F175" s="10" t="s">
@@ -32105,7 +32145,7 @@
       <c r="D176" s="10" t="s">
         <v>1125</v>
       </c>
-      <c r="E176" s="10">
+      <c r="E176" s="26">
         <v>95220</v>
       </c>
       <c r="F176" s="10" t="s">
@@ -32245,21 +32285,21 @@
     <row r="177" spans="1:47" ht="38.25">
       <c r="A177" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B177" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Bas-Rhin</v>
+        <v>Alpes-Maritimes</v>
       </c>
       <c r="C177" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D177" s="11" t="s">
         <v>1193</v>
       </c>
-      <c r="E177" s="10">
-        <v>6700</v>
+      <c r="E177" s="48" t="s">
+        <v>1393</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>1192</v>
@@ -32268,7 +32308,7 @@
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>CAP 3000
 217 Av. Eugène Donadeï
-6700 - Saint-Laurent-du-Var</v>
+06 700 - Saint-Laurent-du-Var</v>
       </c>
       <c r="H177" s="15" t="s">
         <v>1194</v>
@@ -32409,7 +32449,7 @@
       <c r="D178" s="10" t="s">
         <v>1312</v>
       </c>
-      <c r="E178" s="10">
+      <c r="E178" s="26">
         <v>77000</v>
       </c>
       <c r="F178" s="10" t="s">
@@ -32462,7 +32502,10 @@
       <c r="U178" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="V178" s="12"/>
+      <c r="V178" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W178" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -32552,7 +32595,7 @@
       <c r="D179" s="10" t="s">
         <v>1322</v>
       </c>
-      <c r="E179" s="10">
+      <c r="E179" s="26">
         <v>75016</v>
       </c>
       <c r="F179" s="10" t="s">
@@ -32605,7 +32648,10 @@
       <c r="U179" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="V179" s="12"/>
+      <c r="V179" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W179" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -32693,7 +32739,7 @@
       <c r="D180" s="10" t="s">
         <v>1329</v>
       </c>
-      <c r="E180" s="10">
+      <c r="E180" s="26">
         <v>75014</v>
       </c>
       <c r="F180" s="10" t="s">
@@ -32746,7 +32792,10 @@
       <c r="U180" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="V180" s="12"/>
+      <c r="V180" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W180" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -32832,7 +32881,7 @@
       <c r="D181" s="10" t="s">
         <v>1336</v>
       </c>
-      <c r="E181" s="10">
+      <c r="E181" s="26">
         <v>75020</v>
       </c>
       <c r="F181" s="10" t="s">
@@ -32885,7 +32934,10 @@
       <c r="U181" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="V181" s="12"/>
+      <c r="V181" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W181" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -33022,7 +33074,10 @@
       <c r="U182" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="V182" s="12"/>
+      <c r="V182" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W182" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -33108,7 +33163,7 @@
       <c r="D183" s="10" t="s">
         <v>1347</v>
       </c>
-      <c r="E183" s="10">
+      <c r="E183" s="26">
         <v>92100</v>
       </c>
       <c r="F183" s="10" t="s">
@@ -33161,7 +33216,10 @@
       <c r="U183" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="V183" s="12"/>
+      <c r="V183" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W183" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -33249,7 +33307,7 @@
       <c r="D184" s="10" t="s">
         <v>1351</v>
       </c>
-      <c r="E184" s="10">
+      <c r="E184" s="26">
         <v>62520</v>
       </c>
       <c r="F184" s="10" t="s">
@@ -33302,7 +33360,10 @@
       <c r="U184" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="V184" s="12"/>
+      <c r="V184" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W184" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -33390,7 +33451,7 @@
       <c r="D185" s="10" t="s">
         <v>1358</v>
       </c>
-      <c r="E185" s="10">
+      <c r="E185" s="26">
         <v>21000</v>
       </c>
       <c r="F185" s="10" t="s">
@@ -33443,7 +33504,10 @@
       <c r="U185" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="V185" s="12"/>
+      <c r="V185" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W185" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -33531,7 +33595,7 @@
       <c r="D186" s="10" t="s">
         <v>1369</v>
       </c>
-      <c r="E186" s="10">
+      <c r="E186" s="26">
         <v>10000</v>
       </c>
       <c r="F186" s="10" t="s">
@@ -33584,7 +33648,10 @@
       <c r="U186" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="V186" s="12"/>
+      <c r="V186" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W186" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -33672,7 +33739,7 @@
       <c r="D187" s="10" t="s">
         <v>1376</v>
       </c>
-      <c r="E187" s="10">
+      <c r="E187" s="26">
         <v>75001</v>
       </c>
       <c r="F187" s="10" t="s">
@@ -33725,7 +33792,10 @@
       <c r="U187" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="V187" s="12"/>
+      <c r="V187" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="W187" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -33796,6 +33866,152 @@
       </c>
       <c r="AT187" s="14"/>
       <c r="AU187" s="44"/>
+    </row>
+    <row r="188" spans="1:47" ht="38.25">
+      <c r="A188" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B188" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Ain</v>
+      </c>
+      <c r="C188" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>1</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E188" s="49" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G188" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;Tableau1[[#This Row],[Code Postal]]&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Cap Émeraude
+Avenue du Capitaine Dhonne01 000Bourg-en-Bresse</v>
+      </c>
+      <c r="H188" s="15" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I188" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J188" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K188" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L188" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M188" s="36"/>
+      <c r="N188" s="34">
+        <v>196</v>
+      </c>
+      <c r="O188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="P188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R188" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>113680</v>
+      </c>
+      <c r="S188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>9473.3333333333339</v>
+      </c>
+      <c r="T188" s="12">
+        <v>580</v>
+      </c>
+      <c r="U188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V188" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11172</v>
+      </c>
+      <c r="W188" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>931</v>
+      </c>
+      <c r="X188" s="12">
+        <v>57</v>
+      </c>
+      <c r="Y188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>6468</v>
+      </c>
+      <c r="Z188" s="12">
+        <v>33</v>
+      </c>
+      <c r="AA188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3920</v>
+      </c>
+      <c r="AB188" s="12">
+        <v>20</v>
+      </c>
+      <c r="AC188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>135240</v>
+      </c>
+      <c r="AD188" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 28 420 €</v>
+      </c>
+      <c r="AE188" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF188" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG188" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH188" s="10"/>
+      <c r="AI188" s="10"/>
+      <c r="AJ188" s="10" t="s">
+        <v>1401</v>
+      </c>
+      <c r="AK188" s="11" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AL188" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM188" s="11" t="s">
+        <v>1398</v>
+      </c>
+      <c r="AN188" s="11" t="s">
+        <v>1399</v>
+      </c>
+      <c r="AO188" s="11">
+        <v>60</v>
+      </c>
+      <c r="AP188" s="36" t="s">
+        <v>1402</v>
+      </c>
+      <c r="AQ188" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR188" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="AS188" s="13" t="s">
+        <v>1403</v>
+      </c>
+      <c r="AT188" s="14"/>
+      <c r="AU188" s="44"/>
     </row>
     <row r="203" spans="6:6">
       <c r="F203" s="1" t="s">
@@ -33958,6 +34174,7 @@
     <hyperlink ref="H185" r:id="rId146" xr:uid="{9FF463BE-AA91-4BC5-AE7D-4936D1C6D265}"/>
     <hyperlink ref="H186" r:id="rId147" xr:uid="{EED7450E-F5F5-483A-B269-54C932486E0F}"/>
     <hyperlink ref="H187" r:id="rId148" xr:uid="{B52E97C0-A3E5-471B-BD01-7BEB96586BB6}"/>
+    <hyperlink ref="H188" r:id="rId149" xr:uid="{6D139DEB-1BCB-45F1-9FA5-40A114985687}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -33966,7 +34183,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId149"/>
+    <tablePart r:id="rId150"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130416FF-20CB-4DA6-8053-837E8702F0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1CA2A9-8711-4DB2-830F-1B1728B2872E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5474" uniqueCount="1404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5509" uniqueCount="1414">
   <si>
     <t>Contact</t>
   </si>
@@ -3029,27 +3029,15 @@
     <t>https://maps.app.goo.gl/brvAXB8JH7CUWKEZ8</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>Hyper Carrefour, Sephora, Nocibé, Chevignon, Histoire d'Or, Yves Rocher, Armand Thierry, Micromania</t>
   </si>
   <si>
     <t>Entre 350 et 600 €/m²</t>
   </si>
   <si>
-    <t>49.125388</t>
-  </si>
-  <si>
-    <t>2.245052</t>
-  </si>
-  <si>
     <t>Charges taxes comprises. Zone commercial en périphérie d'une très belle zone du Vexin avec Décathlon, La Grande Récré, Kiabi, Naturalia, Mc Donald's.</t>
   </si>
   <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30%20-%20L'Isle-Adam/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30%20-%20L'Isle-Adam/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30%20-%20L'Isle-Adam/3.jpg</t>
-  </si>
-  <si>
     <t>Mours</t>
   </si>
   <si>
@@ -3156,9 +3144,6 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/32.1%20-%20Nantes/1%20Vue%20d'ensemble.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/32.1%20-%20Nantes/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/32.1%20-%20Nantes/3.jpg</t>
-  </si>
-  <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/29.1%20-%20Villetaneuse/1%20Vue%20d'ensemble.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/29.1%20-%20Villetaneuse/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/29.1%20-%20Villetaneuse/3.jpg</t>
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/31.1%20-%20Mours/1%20Vue%20d'ensemble.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/31.1%20-%20Mours/2%20Plan%20de%20masse.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/31.1%20-%20Mours/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/31.1%20-%20Mours/4.jpg</t>
@@ -4255,10 +4240,55 @@
     <t>H&amp;M, Intersport, Mango, Kingjouet, Gemo, Promod, Eram, Graind e Malice, Armand Thierry, restaurants</t>
   </si>
   <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/5%20Plan%20de%20situation.jpg</t>
-  </si>
-  <si>
     <t>Leclerc Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/5%20Plan%20de%20situation.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/60%20-%20Bourg-en-Bresse/6%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/29.1%20-%20Villetaneuse/1%20Vue%20d'ensemble.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/29.1%20-%20Villetaneuse/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/29.1%20-%20Villetaneuse/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/29.1%20-%20Villetaneuse/4%20Plan%20du%20centre.jpg</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>129 + 38</t>
+  </si>
+  <si>
+    <t>66 + 58</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/4%20Plan%20du%20centre.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/5%20Plan%20RDC.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/6%20Plan%20R%2B1.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.1%20-%20L'Isle-Adam/4%20Plan%20du%20centre.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.2%20-%20L'Isle-Adam/5%20Plan%20RDC.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/30.2%20-%20L'Isle-Adam/6%20Plan%20R%2B1.jpg</t>
+  </si>
+  <si>
+    <t>Terrain à vendre dans une zone très qualitative et commerciale (Darty, Décathlon, Naturalia, McDonald's).</t>
+  </si>
+  <si>
+    <t>49.125659</t>
+  </si>
+  <si>
+    <t>2.245342</t>
+  </si>
+  <si>
+    <t>49.125308</t>
+  </si>
+  <si>
+    <t>2.244709</t>
+  </si>
+  <si>
+    <t>150 €/m² = 93 000 €</t>
+  </si>
+  <si>
+    <t>2M €</t>
+  </si>
+  <si>
+    <t>150 €/m² = 94 200 €</t>
   </si>
 </sst>
 </file>
@@ -4892,8 +4922,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU188" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AU188" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU189" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AU189" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="47">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="46" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -5285,7 +5315,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BD204"/>
+  <dimension ref="A1:BD205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -5481,7 +5511,7 @@
         <v>12</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
@@ -5998,7 +6028,7 @@
         <v>9030</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="P5" s="34">
         <v>8628</v>
@@ -12999,7 +13029,7 @@
         <v>308</v>
       </c>
       <c r="AP50" s="35" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="AQ50" s="5" t="s">
         <v>75</v>
@@ -13833,7 +13863,7 @@
         <v>87</v>
       </c>
       <c r="O56" s="10" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="P56" s="34" t="s">
         <v>103</v>
@@ -15624,7 +15654,7 @@
         <v>503</v>
       </c>
       <c r="AP67" s="35" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="AQ67" s="5" t="s">
         <v>75</v>
@@ -15779,7 +15809,7 @@
         <v>504</v>
       </c>
       <c r="AP68" s="35" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="AQ68" s="5" t="s">
         <v>75</v>
@@ -15934,7 +15964,7 @@
         <v>505</v>
       </c>
       <c r="AP69" s="35" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="AQ69" s="5" t="s">
         <v>75</v>
@@ -16089,7 +16119,7 @@
         <v>506</v>
       </c>
       <c r="AP70" s="35" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="AQ70" s="5" t="s">
         <v>75</v>
@@ -16244,7 +16274,7 @@
         <v>507</v>
       </c>
       <c r="AP71" s="35" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="AQ71" s="5" t="s">
         <v>75</v>
@@ -16399,7 +16429,7 @@
         <v>508</v>
       </c>
       <c r="AP72" s="35" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="AQ72" s="5" t="s">
         <v>75</v>
@@ -16554,7 +16584,7 @@
         <v>509</v>
       </c>
       <c r="AP73" s="35" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="AQ73" s="5" t="s">
         <v>75</v>
@@ -16709,7 +16739,7 @@
         <v>510</v>
       </c>
       <c r="AP74" s="35" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="AQ74" s="5" t="s">
         <v>75</v>
@@ -16864,7 +16894,7 @@
         <v>511</v>
       </c>
       <c r="AP75" s="35" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="AQ75" s="5" t="s">
         <v>75</v>
@@ -17019,7 +17049,7 @@
         <v>512</v>
       </c>
       <c r="AP76" s="35" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="AQ76" s="5" t="s">
         <v>75</v>
@@ -17174,7 +17204,7 @@
         <v>513</v>
       </c>
       <c r="AP77" s="35" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="AQ77" s="5" t="s">
         <v>75</v>
@@ -17329,7 +17359,7 @@
         <v>514</v>
       </c>
       <c r="AP78" s="35" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="AQ78" s="5" t="s">
         <v>75</v>
@@ -17484,7 +17514,7 @@
         <v>515</v>
       </c>
       <c r="AP79" s="35" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="AQ79" s="5" t="s">
         <v>75</v>
@@ -17639,7 +17669,7 @@
         <v>516</v>
       </c>
       <c r="AP80" s="35" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="AQ80" s="5" t="s">
         <v>75</v>
@@ -17794,7 +17824,7 @@
         <v>517</v>
       </c>
       <c r="AP81" s="35" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="AQ81" s="5" t="s">
         <v>75</v>
@@ -17949,7 +17979,7 @@
         <v>518</v>
       </c>
       <c r="AP82" s="35" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="AQ82" s="5" t="s">
         <v>75</v>
@@ -18104,7 +18134,7 @@
         <v>519</v>
       </c>
       <c r="AP83" s="35" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="AQ83" s="5" t="s">
         <v>75</v>
@@ -18259,7 +18289,7 @@
         <v>520</v>
       </c>
       <c r="AP84" s="35" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="AQ84" s="5" t="s">
         <v>75</v>
@@ -18414,7 +18444,7 @@
         <v>521</v>
       </c>
       <c r="AP85" s="35" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="AQ85" s="5" t="s">
         <v>75</v>
@@ -18569,7 +18599,7 @@
         <v>522</v>
       </c>
       <c r="AP86" s="35" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="AQ86" s="5" t="s">
         <v>75</v>
@@ -18724,7 +18754,7 @@
         <v>523</v>
       </c>
       <c r="AP87" s="35" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="AQ87" s="5" t="s">
         <v>75</v>
@@ -18879,7 +18909,7 @@
         <v>524</v>
       </c>
       <c r="AP88" s="35" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="AQ88" s="5" t="s">
         <v>75</v>
@@ -19034,7 +19064,7 @@
         <v>525</v>
       </c>
       <c r="AP89" s="35" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="AQ89" s="5" t="s">
         <v>75</v>
@@ -23948,7 +23978,7 @@
         <v>935</v>
       </c>
       <c r="AP121" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ121" s="11" t="s">
         <v>75</v>
@@ -24103,7 +24133,7 @@
         <v>936</v>
       </c>
       <c r="AP122" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ122" s="11" t="s">
         <v>75</v>
@@ -24258,7 +24288,7 @@
         <v>937</v>
       </c>
       <c r="AP123" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ123" s="11" t="s">
         <v>75</v>
@@ -24413,7 +24443,7 @@
         <v>938</v>
       </c>
       <c r="AP124" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ124" s="11" t="s">
         <v>75</v>
@@ -24568,7 +24598,7 @@
         <v>939</v>
       </c>
       <c r="AP125" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ125" s="11" t="s">
         <v>75</v>
@@ -24723,7 +24753,7 @@
         <v>940</v>
       </c>
       <c r="AP126" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ126" s="11" t="s">
         <v>75</v>
@@ -24875,7 +24905,7 @@
         <v>941</v>
       </c>
       <c r="AP127" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ127" s="11" t="s">
         <v>75</v>
@@ -25027,7 +25057,7 @@
         <v>942</v>
       </c>
       <c r="AP128" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ128" s="11" t="s">
         <v>75</v>
@@ -25179,7 +25209,7 @@
         <v>943</v>
       </c>
       <c r="AP129" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ129" s="11" t="s">
         <v>75</v>
@@ -25331,7 +25361,7 @@
         <v>944</v>
       </c>
       <c r="AP130" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ130" s="11" t="s">
         <v>75</v>
@@ -25483,7 +25513,7 @@
         <v>945</v>
       </c>
       <c r="AP131" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ131" s="11" t="s">
         <v>75</v>
@@ -25635,7 +25665,7 @@
         <v>946</v>
       </c>
       <c r="AP132" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ132" s="11" t="s">
         <v>75</v>
@@ -25787,7 +25817,7 @@
         <v>947</v>
       </c>
       <c r="AP133" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ133" s="11" t="s">
         <v>75</v>
@@ -25939,7 +25969,7 @@
         <v>948</v>
       </c>
       <c r="AP134" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ134" s="11" t="s">
         <v>75</v>
@@ -26091,7 +26121,7 @@
         <v>949</v>
       </c>
       <c r="AP135" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ135" s="11" t="s">
         <v>75</v>
@@ -26243,7 +26273,7 @@
         <v>950</v>
       </c>
       <c r="AP136" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ136" s="11" t="s">
         <v>75</v>
@@ -26395,7 +26425,7 @@
         <v>951</v>
       </c>
       <c r="AP137" s="36" t="s">
-        <v>1037</v>
+        <v>1399</v>
       </c>
       <c r="AQ137" s="11" t="s">
         <v>75</v>
@@ -26422,7 +26452,7 @@
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>95</v>
       </c>
-      <c r="D138" s="42" t="s">
+      <c r="D138" s="10" t="s">
         <v>992</v>
       </c>
       <c r="E138" s="26">
@@ -26452,13 +26482,13 @@
         <v>103</v>
       </c>
       <c r="M138" s="36" t="s">
-        <v>994</v>
+        <v>357</v>
       </c>
       <c r="N138" s="34">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>103</v>
+        <v>1402</v>
       </c>
       <c r="P138" s="34" t="s">
         <v>103</v>
@@ -26468,28 +26498,28 @@
       </c>
       <c r="R138" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>48000</v>
+        <v>75150</v>
       </c>
       <c r="S138" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>4000</v>
+        <v>6262.5</v>
       </c>
       <c r="T138" s="12">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="U138" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V138" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>6000</v>
+        <v>17201</v>
       </c>
       <c r="W138" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>500</v>
+        <v>1433.4166666666667</v>
       </c>
       <c r="X138" s="12">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Y138" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
@@ -26507,11 +26537,11 @@
       </c>
       <c r="AC138" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>54000</v>
+        <v>92351</v>
       </c>
       <c r="AD138" s="12" t="str">
         <f>"3 mois = "&amp;TEXT(ROUND(3/12*R138,0),"### ### ##0 €")</f>
-        <v>3 mois = 12 000 €</v>
+        <v>3 mois = 18 788 €</v>
       </c>
       <c r="AE138" s="6" t="s">
         <v>103</v>
@@ -26529,31 +26559,31 @@
         <v>369</v>
       </c>
       <c r="AJ138" s="10" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AK138" s="11" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="AL138" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM138" s="11" t="s">
-        <v>997</v>
+        <v>1409</v>
       </c>
       <c r="AN138" s="11" t="s">
-        <v>998</v>
-      </c>
-      <c r="AO138" s="11">
-        <v>30</v>
+        <v>1410</v>
+      </c>
+      <c r="AO138" s="11" t="s">
+        <v>1400</v>
       </c>
       <c r="AP138" s="36" t="s">
-        <v>1000</v>
+        <v>1404</v>
       </c>
       <c r="AQ138" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR138" s="11" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="AS138" s="13" t="s">
         <v>954</v>
@@ -26574,28 +26604,28 @@
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>95</v>
       </c>
-      <c r="D139" s="42" t="s">
-        <v>1002</v>
+      <c r="D139" s="10" t="s">
+        <v>992</v>
       </c>
       <c r="E139" s="26">
-        <v>95260</v>
+        <v>95290</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="G139" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>Parc d’activités Col’Vert Rue du Kiosque
-95260 - Mours</v>
+        <v>Centre Commercial le Grand Val, Boulevard de Tilsit
+95290 - L'Isle-Adam</v>
       </c>
       <c r="H139" s="15" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="I139" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J139" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K139" s="12" t="s">
         <v>103</v>
@@ -26604,13 +26634,13 @@
         <v>103</v>
       </c>
       <c r="M139" s="36" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="N139" s="34">
-        <v>620</v>
+        <v>124</v>
       </c>
       <c r="O139" s="6" t="s">
-        <v>103</v>
+        <v>1403</v>
       </c>
       <c r="P139" s="34" t="s">
         <v>103</v>
@@ -26620,25 +26650,29 @@
       </c>
       <c r="R139" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="S139" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T139" s="12"/>
+        <v>5166.666666666667</v>
+      </c>
+      <c r="T139" s="12">
+        <v>500</v>
+      </c>
       <c r="U139" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V139" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>12772</v>
       </c>
       <c r="W139" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X139" s="12"/>
+        <v>1064.3333333333333</v>
+      </c>
+      <c r="X139" s="12">
+        <v>103</v>
+      </c>
       <c r="Y139" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -26655,49 +26689,54 @@
       </c>
       <c r="AC139" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD139" s="12"/>
+        <v>74772</v>
+      </c>
+      <c r="AD139" s="12" t="str">
+        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R139,0),"### ### ##0 €")</f>
+        <v>3 mois = 15 500 €</v>
+      </c>
       <c r="AE139" s="6" t="s">
         <v>103</v>
       </c>
       <c r="AF139" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AG139" s="12" t="s">
-        <v>382</v>
+      <c r="AG139" s="6" t="s">
+        <v>363</v>
       </c>
       <c r="AH139" s="10" t="s">
-        <v>377</v>
+        <v>53</v>
       </c>
       <c r="AI139" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AJ139" s="10" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="AK139" s="11" t="s">
-        <v>1010</v>
+        <v>996</v>
       </c>
       <c r="AL139" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM139" s="11" t="s">
-        <v>1011</v>
+        <v>1407</v>
       </c>
       <c r="AN139" s="11" t="s">
-        <v>1012</v>
+        <v>1408</v>
       </c>
       <c r="AO139" s="11" t="s">
-        <v>1003</v>
+        <v>1401</v>
       </c>
       <c r="AP139" s="36" t="s">
-        <v>1038</v>
+        <v>1405</v>
       </c>
       <c r="AQ139" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR139" s="11"/>
+      <c r="AR139" s="11" t="s">
+        <v>995</v>
+      </c>
       <c r="AS139" s="13" t="s">
         <v>954</v>
       </c>
@@ -26717,14 +26756,14 @@
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>95</v>
       </c>
-      <c r="D140" s="42" t="s">
-        <v>1002</v>
+      <c r="D140" s="10" t="s">
+        <v>998</v>
       </c>
       <c r="E140" s="26">
         <v>95260</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G140" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26732,7 +26771,7 @@
 95260 - Mours</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="I140" s="12" t="s">
         <v>47</v>
@@ -26747,7 +26786,7 @@
         <v>103</v>
       </c>
       <c r="M140" s="36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N140" s="34">
         <v>620</v>
@@ -26763,13 +26802,15 @@
       </c>
       <c r="R140" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>124000</v>
       </c>
       <c r="S140" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T140" s="12"/>
+        <v>10333.333333333334</v>
+      </c>
+      <c r="T140" s="12">
+        <v>200</v>
+      </c>
       <c r="U140" s="6" t="s">
         <v>103</v>
       </c>
@@ -26798,9 +26839,12 @@
       </c>
       <c r="AC140" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD140" s="12"/>
+        <v>124000</v>
+      </c>
+      <c r="AD140" s="12" t="str">
+        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R140,0),"### ### ##0 €")</f>
+        <v>3 mois = 31 000 €</v>
+      </c>
       <c r="AE140" s="6" t="s">
         <v>103</v>
       </c>
@@ -26817,30 +26861,32 @@
         <v>370</v>
       </c>
       <c r="AJ140" s="10" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="AK140" s="11" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="AL140" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM140" s="11" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="AN140" s="11" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="AO140" s="11" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="AP140" s="36" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AQ140" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR140" s="11"/>
+      <c r="AR140" s="11" t="s">
+        <v>1411</v>
+      </c>
       <c r="AS140" s="13" t="s">
         <v>954</v>
       </c>
@@ -26860,14 +26906,14 @@
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>95</v>
       </c>
-      <c r="D141" s="42" t="s">
-        <v>1002</v>
+      <c r="D141" s="10" t="s">
+        <v>998</v>
       </c>
       <c r="E141" s="26">
         <v>95260</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G141" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26875,7 +26921,7 @@
 95260 - Mours</v>
       </c>
       <c r="H141" s="15" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="I141" s="12" t="s">
         <v>47</v>
@@ -26890,7 +26936,7 @@
         <v>103</v>
       </c>
       <c r="M141" s="36" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="N141" s="34">
         <v>620</v>
@@ -26906,13 +26952,15 @@
       </c>
       <c r="R141" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>124000</v>
       </c>
       <c r="S141" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T141" s="12"/>
+        <v>10333.333333333334</v>
+      </c>
+      <c r="T141" s="12">
+        <v>200</v>
+      </c>
       <c r="U141" s="6" t="s">
         <v>103</v>
       </c>
@@ -26941,9 +26989,12 @@
       </c>
       <c r="AC141" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD141" s="12"/>
+        <v>124000</v>
+      </c>
+      <c r="AD141" s="12" t="str">
+        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R141,0),"### ### ##0 €")</f>
+        <v>3 mois = 31 000 €</v>
+      </c>
       <c r="AE141" s="6" t="s">
         <v>103</v>
       </c>
@@ -26960,30 +27011,32 @@
         <v>370</v>
       </c>
       <c r="AJ141" s="10" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="AK141" s="11" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="AL141" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM141" s="11" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="AN141" s="11" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="AO141" s="11" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="AP141" s="36" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AQ141" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR141" s="11"/>
+      <c r="AR141" s="11" t="s">
+        <v>1411</v>
+      </c>
       <c r="AS141" s="13" t="s">
         <v>954</v>
       </c>
@@ -27003,14 +27056,14 @@
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>95</v>
       </c>
-      <c r="D142" s="42" t="s">
-        <v>1002</v>
+      <c r="D142" s="10" t="s">
+        <v>998</v>
       </c>
       <c r="E142" s="26">
         <v>95260</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G142" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27018,7 +27071,7 @@
 95260 - Mours</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>47</v>
@@ -27033,10 +27086,10 @@
         <v>103</v>
       </c>
       <c r="M142" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N142" s="34">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>103</v>
@@ -27049,13 +27102,15 @@
       </c>
       <c r="R142" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>124000</v>
       </c>
       <c r="S142" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T142" s="12"/>
+        <v>10333.333333333334</v>
+      </c>
+      <c r="T142" s="12">
+        <v>200</v>
+      </c>
       <c r="U142" s="6" t="s">
         <v>103</v>
       </c>
@@ -27084,9 +27139,12 @@
       </c>
       <c r="AC142" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD142" s="12"/>
+        <v>124000</v>
+      </c>
+      <c r="AD142" s="12" t="str">
+        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R142,0),"### ### ##0 €")</f>
+        <v>3 mois = 31 000 €</v>
+      </c>
       <c r="AE142" s="6" t="s">
         <v>103</v>
       </c>
@@ -27103,30 +27161,32 @@
         <v>370</v>
       </c>
       <c r="AJ142" s="10" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="AK142" s="11" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="AL142" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM142" s="11" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="AN142" s="11" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="AO142" s="11" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="AP142" s="36" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AQ142" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR142" s="11"/>
+      <c r="AR142" s="11" t="s">
+        <v>1411</v>
+      </c>
       <c r="AS142" s="13" t="s">
         <v>954</v>
       </c>
@@ -27146,14 +27206,14 @@
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>95</v>
       </c>
-      <c r="D143" s="42" t="s">
-        <v>1002</v>
+      <c r="D143" s="10" t="s">
+        <v>998</v>
       </c>
       <c r="E143" s="26">
         <v>95260</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G143" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27161,7 +27221,7 @@
 95260 - Mours</v>
       </c>
       <c r="H143" s="15" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>47</v>
@@ -27176,9 +27236,11 @@
         <v>103</v>
       </c>
       <c r="M143" s="36" t="s">
-        <v>359</v>
-      </c>
-      <c r="N143" s="34"/>
+        <v>358</v>
+      </c>
+      <c r="N143" s="34">
+        <v>628</v>
+      </c>
       <c r="O143" s="6" t="s">
         <v>103</v>
       </c>
@@ -27190,13 +27252,15 @@
       </c>
       <c r="R143" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>125600</v>
       </c>
       <c r="S143" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T143" s="12"/>
+        <v>10466.666666666666</v>
+      </c>
+      <c r="T143" s="12">
+        <v>200</v>
+      </c>
       <c r="U143" s="6" t="s">
         <v>103</v>
       </c>
@@ -27225,9 +27289,12 @@
       </c>
       <c r="AC143" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD143" s="12"/>
+        <v>125600</v>
+      </c>
+      <c r="AD143" s="12" t="str">
+        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R143,0),"### ### ##0 €")</f>
+        <v>3 mois = 31 400 €</v>
+      </c>
       <c r="AE143" s="6" t="s">
         <v>103</v>
       </c>
@@ -27244,83 +27311,85 @@
         <v>370</v>
       </c>
       <c r="AJ143" s="10" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="AK143" s="11" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="AL143" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM143" s="11" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="AN143" s="11" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="AO143" s="11" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="AP143" s="36" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="AQ143" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR143" s="11"/>
+      <c r="AR143" s="11" t="s">
+        <v>1413</v>
+      </c>
       <c r="AS143" s="13" t="s">
         <v>954</v>
       </c>
       <c r="AT143" s="14"/>
       <c r="AU143" s="44"/>
     </row>
-    <row r="144" spans="1:47" ht="51">
+    <row r="144" spans="1:47" ht="38.25">
       <c r="A144" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Pays de la Loire</v>
+        <v>Ile-de-France</v>
       </c>
       <c r="B144" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Loire-Atlantique</v>
+        <v>Val-D'Oise</v>
       </c>
       <c r="C144" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>1024</v>
+        <v>998</v>
       </c>
       <c r="E144" s="26">
-        <v>44200</v>
+        <v>95260</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>1025</v>
+        <v>997</v>
       </c>
       <c r="G144" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>15 Boulevard Léon Bureau
-44200 - Nantes</v>
+        <v>Parc d’activités Col’Vert Rue du Kiosque
+95260 - Mours</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>1023</v>
+        <v>1004</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J144" s="12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K144" s="12" t="s">
         <v>103</v>
       </c>
       <c r="L144" s="12" t="s">
-        <v>103</v>
+        <v>1190</v>
       </c>
       <c r="M144" s="36" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="N144" s="34">
-        <v>285</v>
+        <v>4272</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>103</v>
@@ -27333,29 +27402,25 @@
       </c>
       <c r="R144" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>128250</v>
+        <v>0</v>
       </c>
       <c r="S144" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>10687.5</v>
-      </c>
-      <c r="T144" s="12">
-        <v>450</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T144" s="12"/>
       <c r="U144" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V144" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>8550</v>
+        <v>0</v>
       </c>
       <c r="W144" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>712.5</v>
-      </c>
-      <c r="X144" s="12">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X144" s="12"/>
       <c r="Y144" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -27372,12 +27437,9 @@
       </c>
       <c r="AC144" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>136800</v>
-      </c>
-      <c r="AD144" s="12" t="str">
-        <f t="shared" ref="AD144:AD145" si="5">"3 mois = "&amp;TEXT(ROUND(3/12*R144,0),"### ### ##0 €")</f>
-        <v>3 mois = 32 063 €</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD144" s="12"/>
       <c r="AE144" s="6" t="s">
         <v>103</v>
       </c>
@@ -27388,45 +27450,45 @@
         <v>382</v>
       </c>
       <c r="AH144" s="10" t="s">
-        <v>75</v>
+        <v>377</v>
       </c>
       <c r="AI144" s="10" t="s">
         <v>370</v>
       </c>
       <c r="AJ144" s="10" t="s">
-        <v>1032</v>
+        <v>1005</v>
       </c>
       <c r="AK144" s="11" t="s">
-        <v>1190</v>
+        <v>1406</v>
       </c>
       <c r="AL144" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM144" s="11" t="s">
-        <v>1028</v>
+        <v>1015</v>
       </c>
       <c r="AN144" s="11" t="s">
-        <v>1029</v>
+        <v>1016</v>
       </c>
       <c r="AO144" s="11" t="s">
-        <v>1021</v>
+        <v>1003</v>
       </c>
       <c r="AP144" s="36" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AQ144" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR144" s="11" t="s">
-        <v>1026</v>
+        <v>1412</v>
       </c>
       <c r="AS144" s="13" t="s">
-        <v>37</v>
+        <v>954</v>
       </c>
       <c r="AT144" s="14"/>
       <c r="AU144" s="44"/>
     </row>
-    <row r="145" spans="1:47" ht="38.25">
+    <row r="145" spans="1:47" ht="51">
       <c r="A145" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -27440,13 +27502,13 @@
         <v>44</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="E145" s="26">
         <v>44200</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="G145" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27454,7 +27516,7 @@
 44200 - Nantes</v>
       </c>
       <c r="H145" s="15" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="I145" s="12" t="s">
         <v>45</v>
@@ -27469,10 +27531,10 @@
         <v>103</v>
       </c>
       <c r="M145" s="36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N145" s="34">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="O145" s="6" t="s">
         <v>103</v>
@@ -27485,25 +27547,25 @@
       </c>
       <c r="R145" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>78400</v>
+        <v>128250</v>
       </c>
       <c r="S145" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>6533.333333333333</v>
+        <v>10687.5</v>
       </c>
       <c r="T145" s="12">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="U145" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V145" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>6720</v>
+        <v>8550</v>
       </c>
       <c r="W145" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>560</v>
+        <v>712.5</v>
       </c>
       <c r="X145" s="12">
         <v>30</v>
@@ -27524,11 +27586,11 @@
       </c>
       <c r="AC145" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>85120</v>
+        <v>136800</v>
       </c>
       <c r="AD145" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v>3 mois = 19 600 €</v>
+        <f t="shared" ref="AD145:AD146" si="5">"3 mois = "&amp;TEXT(ROUND(3/12*R145,0),"### ### ##0 €")</f>
+        <v>3 mois = 32 063 €</v>
       </c>
       <c r="AE145" s="6" t="s">
         <v>103</v>
@@ -27540,37 +27602,37 @@
         <v>382</v>
       </c>
       <c r="AH145" s="10" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="AI145" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ145" s="10" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="AK145" s="11" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="AL145" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM145" s="11" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="AN145" s="11" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="AO145" s="11" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="AP145" s="36" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="AQ145" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR145" s="11" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="AS145" s="13" t="s">
         <v>37</v>
@@ -27578,209 +27640,224 @@
       <c r="AT145" s="14"/>
       <c r="AU145" s="44"/>
     </row>
-    <row r="146" spans="1:47" ht="25.5">
+    <row r="146" spans="1:47" ht="38.25">
       <c r="A146" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Pays de la Loire</v>
       </c>
       <c r="B146" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Haut-Rhin</v>
+        <v>Loire-Atlantique</v>
       </c>
       <c r="C146" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>44</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E146" s="26">
+        <v>44200</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G146" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>15 Boulevard Léon Bureau
+44200 - Nantes</v>
+      </c>
+      <c r="H146" s="15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J146" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K146" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L146" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M146" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="N146" s="34">
+        <v>224</v>
+      </c>
+      <c r="O146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P146" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R146" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>78400</v>
+      </c>
+      <c r="S146" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>6533.333333333333</v>
+      </c>
+      <c r="T146" s="12">
+        <v>350</v>
+      </c>
+      <c r="U146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V146" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>6720</v>
+      </c>
+      <c r="W146" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>560</v>
+      </c>
+      <c r="X146" s="12">
+        <v>30</v>
+      </c>
+      <c r="Y146" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA146" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC146" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>85120</v>
+      </c>
+      <c r="AD146" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>3 mois = 19 600 €</v>
+      </c>
+      <c r="AE146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG146" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="AH146" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI146" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AJ146" s="10" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AK146" s="11" t="s">
+        <v>1186</v>
+      </c>
+      <c r="AL146" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM146" s="11" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AN146" s="11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AO146" s="11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="AP146" s="36" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AQ146" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR146" s="11" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AS146" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT146" s="14"/>
+      <c r="AU146" s="44"/>
+    </row>
+    <row r="147" spans="1:47" ht="25.5">
+      <c r="A147" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B147" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haut-Rhin</v>
+      </c>
+      <c r="C147" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>68</v>
       </c>
-      <c r="D146" s="42" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E146" s="26">
+      <c r="D147" s="42" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E147" s="26">
         <v>68330</v>
       </c>
-      <c r="F146" s="10" t="s">
+      <c r="F147" s="10" t="s">
         <v>900</v>
       </c>
-      <c r="G146" s="39" t="str">
+      <c r="G147" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>5 avenue d'Alsace
 68330 - Huningue</v>
       </c>
-      <c r="H146" s="15" t="s">
-        <v>1042</v>
-      </c>
-      <c r="I146" s="12" t="s">
+      <c r="H147" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I147" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J146" s="12" t="s">
+      <c r="J147" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K146" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="L146" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M146" s="36" t="s">
-        <v>1041</v>
-      </c>
-      <c r="N146" s="34">
+      <c r="K147" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L147" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M147" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="N147" s="34">
         <v>287</v>
       </c>
-      <c r="O146" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P146" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q146" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R146" s="12">
+      <c r="O147" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P147" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q147" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R147" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>0</v>
       </c>
-      <c r="S146" s="12">
+      <c r="S147" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>0</v>
       </c>
-      <c r="T146" s="12"/>
-      <c r="U146" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V146" s="6">
-        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
-      </c>
-      <c r="W146" s="12">
-        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X146" s="12"/>
-      <c r="Y146" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z146" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA146" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB146" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC146" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AD146" s="12"/>
-      <c r="AE146" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF146" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG146" s="12"/>
-      <c r="AH146" s="10"/>
-      <c r="AI146" s="10"/>
-      <c r="AJ146" s="10"/>
-      <c r="AK146" s="11" t="s">
-        <v>1054</v>
-      </c>
-      <c r="AL146" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="AM146" s="11" t="s">
-        <v>1043</v>
-      </c>
-      <c r="AN146" s="11" t="s">
-        <v>1044</v>
-      </c>
-      <c r="AO146" s="11">
-        <v>33</v>
-      </c>
-      <c r="AP146" s="36" t="s">
-        <v>1055</v>
-      </c>
-      <c r="AQ146" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR146" s="11"/>
-      <c r="AS146" s="13" t="s">
-        <v>1051</v>
-      </c>
-      <c r="AT146" s="14"/>
-      <c r="AU146" s="44"/>
-    </row>
-    <row r="147" spans="1:47" ht="38.25">
-      <c r="A147" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Centre-Val de Loire</v>
-      </c>
-      <c r="B147" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Indre-et-Loire</v>
-      </c>
-      <c r="C147" s="38">
-        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>37</v>
-      </c>
-      <c r="D147" s="10" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E147" s="26">
-        <v>37600</v>
-      </c>
-      <c r="F147" s="10" t="s">
-        <v>901</v>
-      </c>
-      <c r="G147" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>Super U 38 Route de Vauzelles, Rue du Bon Raisin
-37600 - Loches</v>
-      </c>
-      <c r="H147" s="15" t="s">
-        <v>1045</v>
-      </c>
-      <c r="I147" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="J147" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K147" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="L147" s="12">
-        <v>25000</v>
-      </c>
-      <c r="M147" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="N147" s="34">
-        <v>73</v>
-      </c>
-      <c r="O147" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P147" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q147" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R147" s="12">
-        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>25550</v>
-      </c>
-      <c r="S147" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>2129.1666666666665</v>
-      </c>
-      <c r="T147" s="12">
-        <v>350</v>
-      </c>
+      <c r="T147" s="12"/>
       <c r="U147" s="6" t="s">
         <v>103</v>
       </c>
@@ -27809,61 +27886,46 @@
       </c>
       <c r="AC147" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>25550</v>
-      </c>
-      <c r="AD147" s="12" t="str">
-        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R147,0),"### ### ##0 €")</f>
-        <v>3 mois = 6 388 €</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD147" s="12"/>
       <c r="AE147" s="6" t="s">
         <v>103</v>
       </c>
       <c r="AF147" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AG147" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="AH147" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI147" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ147" s="10" t="s">
-        <v>1047</v>
-      </c>
+      <c r="AG147" s="12"/>
+      <c r="AH147" s="10"/>
+      <c r="AI147" s="10"/>
+      <c r="AJ147" s="10"/>
       <c r="AK147" s="11" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="AL147" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM147" s="11" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
       <c r="AN147" s="11" t="s">
-        <v>1049</v>
+        <v>1039</v>
       </c>
       <c r="AO147" s="11">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AP147" s="36" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="AQ147" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR147" s="43" t="s">
-        <v>1052</v>
-      </c>
+      <c r="AR147" s="11"/>
       <c r="AS147" s="13" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="AT147" s="14"/>
-      <c r="AU147" s="44">
-        <v>45999</v>
-      </c>
+      <c r="AU147" s="44"/>
     </row>
     <row r="148" spans="1:47" ht="38.25">
       <c r="A148" s="38" t="str">
@@ -27879,7 +27941,7 @@
         <v>37</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E148" s="26">
         <v>37600</v>
@@ -27893,26 +27955,25 @@
 37600 - Loches</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>1057</v>
+        <v>1040</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J148" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K148" s="12" t="s">
         <v>103</v>
       </c>
       <c r="L148" s="12">
-        <f>100*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M148" s="36" t="s">
         <v>335</v>
       </c>
       <c r="N148" s="34">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>103</v>
@@ -27925,35 +27986,33 @@
       </c>
       <c r="R148" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>40000</v>
+        <v>25550</v>
       </c>
       <c r="S148" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>3333.3333333333335</v>
+        <v>2129.1666666666665</v>
       </c>
       <c r="T148" s="12">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="U148" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V148" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W148" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>833.33333333333337</v>
-      </c>
-      <c r="X148" s="12">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X148" s="12"/>
       <c r="Y148" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>6000</v>
-      </c>
-      <c r="Z148" s="6">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="Z148" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="AA148" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
@@ -27964,11 +28023,11 @@
       </c>
       <c r="AC148" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>56000</v>
+        <v>25550</v>
       </c>
       <c r="AD148" s="12" t="str">
-        <f t="shared" ref="AD148:AD188" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
-        <v>3 mois = 10 000 €</v>
+        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R148,0),"### ### ##0 €")</f>
+        <v>3 mois = 6 388 €</v>
       </c>
       <c r="AE148" s="6" t="s">
         <v>103</v>
@@ -27977,7 +28036,7 @@
         <v>103</v>
       </c>
       <c r="AG148" s="12" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="AH148" s="10" t="s">
         <v>53</v>
@@ -27986,34 +28045,34 @@
         <v>103</v>
       </c>
       <c r="AJ148" s="10" t="s">
-        <v>1061</v>
+        <v>1042</v>
       </c>
       <c r="AK148" s="11" t="s">
-        <v>1058</v>
+        <v>1048</v>
       </c>
       <c r="AL148" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM148" s="11" t="s">
-        <v>1066</v>
+        <v>1043</v>
       </c>
       <c r="AN148" s="11" t="s">
-        <v>1067</v>
-      </c>
-      <c r="AO148" s="11" t="s">
-        <v>1059</v>
+        <v>1044</v>
+      </c>
+      <c r="AO148" s="11">
+        <v>34</v>
       </c>
       <c r="AP148" s="36" t="s">
-        <v>1076</v>
+        <v>1051</v>
       </c>
       <c r="AQ148" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR148" s="11" t="s">
-        <v>1060</v>
+      <c r="AR148" s="43" t="s">
+        <v>1047</v>
       </c>
       <c r="AS148" s="13" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="AT148" s="14"/>
       <c r="AU148" s="44">
@@ -28034,7 +28093,7 @@
         <v>37</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E149" s="26">
         <v>37600</v>
@@ -28048,7 +28107,7 @@
 37600 - Loches</v>
       </c>
       <c r="H149" s="15" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="I149" s="12" t="s">
         <v>47</v>
@@ -28061,13 +28120,13 @@
       </c>
       <c r="L149" s="12">
         <f>100*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="M149" s="36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N149" s="34">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>103</v>
@@ -28080,11 +28139,11 @@
       </c>
       <c r="R149" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="S149" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>8333.3333333333339</v>
+        <v>3333.3333333333335</v>
       </c>
       <c r="T149" s="12">
         <v>200</v>
@@ -28094,18 +28153,18 @@
       </c>
       <c r="V149" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="W149" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>2083.3333333333335</v>
+        <v>833.33333333333337</v>
       </c>
       <c r="X149" s="12">
         <v>50</v>
       </c>
       <c r="Y149" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="Z149" s="6">
         <v>30</v>
@@ -28119,11 +28178,11 @@
       </c>
       <c r="AC149" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>140000</v>
+        <v>56000</v>
       </c>
       <c r="AD149" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>3 mois = 25 000 €</v>
+        <f t="shared" ref="AD149:AD189" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R149,0),"### ### ##0 €")</f>
+        <v>3 mois = 10 000 €</v>
       </c>
       <c r="AE149" s="6" t="s">
         <v>103</v>
@@ -28141,34 +28200,34 @@
         <v>103</v>
       </c>
       <c r="AJ149" s="10" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="AK149" s="11" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="AL149" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM149" s="11" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="AN149" s="11" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="AO149" s="11" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="AP149" s="36" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="AQ149" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR149" s="11" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="AS149" s="13" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="AT149" s="14"/>
       <c r="AU149" s="44">
@@ -28189,7 +28248,7 @@
         <v>37</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E150" s="26">
         <v>37600</v>
@@ -28203,7 +28262,7 @@
 37600 - Loches</v>
       </c>
       <c r="H150" s="15" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="I150" s="12" t="s">
         <v>47</v>
@@ -28216,13 +28275,13 @@
       </c>
       <c r="L150" s="12">
         <f>100*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="M150" s="36" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="N150" s="34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>103</v>
@@ -28235,11 +28294,11 @@
       </c>
       <c r="R150" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="S150" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>16666.666666666668</v>
+        <v>8333.3333333333339</v>
       </c>
       <c r="T150" s="12">
         <v>200</v>
@@ -28249,18 +28308,18 @@
       </c>
       <c r="V150" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="W150" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>4166.666666666667</v>
+        <v>2083.3333333333335</v>
       </c>
       <c r="X150" s="12">
         <v>50</v>
       </c>
       <c r="Y150" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="Z150" s="6">
         <v>30</v>
@@ -28274,11 +28333,11 @@
       </c>
       <c r="AC150" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>280000</v>
+        <v>140000</v>
       </c>
       <c r="AD150" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 50 000 €</v>
+        <v>3 mois = 25 000 €</v>
       </c>
       <c r="AE150" s="6" t="s">
         <v>103</v>
@@ -28296,34 +28355,34 @@
         <v>103</v>
       </c>
       <c r="AJ150" s="10" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="AK150" s="11" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="AL150" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM150" s="11" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="AN150" s="11" t="s">
+        <v>1064</v>
+      </c>
+      <c r="AO150" s="11" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AP150" s="36" t="s">
         <v>1071</v>
-      </c>
-      <c r="AO150" s="11" t="s">
-        <v>1063</v>
-      </c>
-      <c r="AP150" s="36" t="s">
-        <v>1076</v>
       </c>
       <c r="AQ150" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR150" s="11" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="AS150" s="13" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="AT150" s="14"/>
       <c r="AU150" s="44">
@@ -28344,7 +28403,7 @@
         <v>37</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E151" s="26">
         <v>37600</v>
@@ -28358,7 +28417,7 @@
 37600 - Loches</v>
       </c>
       <c r="H151" s="15" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="I151" s="12" t="s">
         <v>47</v>
@@ -28371,13 +28430,13 @@
       </c>
       <c r="L151" s="12">
         <f>100*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="M151" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N151" s="34">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="O151" s="6" t="s">
         <v>103</v>
@@ -28390,11 +28449,11 @@
       </c>
       <c r="R151" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="S151" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>33333.333333333336</v>
+        <v>16666.666666666668</v>
       </c>
       <c r="T151" s="12">
         <v>200</v>
@@ -28404,18 +28463,18 @@
       </c>
       <c r="V151" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="W151" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>8333.3333333333339</v>
+        <v>4166.666666666667</v>
       </c>
       <c r="X151" s="12">
         <v>50</v>
       </c>
       <c r="Y151" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="Z151" s="6">
         <v>30</v>
@@ -28429,11 +28488,11 @@
       </c>
       <c r="AC151" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>560000</v>
+        <v>280000</v>
       </c>
       <c r="AD151" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 100 000 €</v>
+        <v>3 mois = 50 000 €</v>
       </c>
       <c r="AE151" s="6" t="s">
         <v>103</v>
@@ -28451,34 +28510,34 @@
         <v>103</v>
       </c>
       <c r="AJ151" s="10" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="AK151" s="11" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="AL151" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM151" s="11" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="AN151" s="11" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="AO151" s="11" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="AP151" s="36" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="AQ151" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR151" s="11" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="AS151" s="13" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="AT151" s="14"/>
       <c r="AU151" s="44">
@@ -28499,7 +28558,7 @@
         <v>37</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E152" s="26">
         <v>37600</v>
@@ -28513,7 +28572,7 @@
 37600 - Loches</v>
       </c>
       <c r="H152" s="15" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="I152" s="12" t="s">
         <v>47</v>
@@ -28526,13 +28585,13 @@
       </c>
       <c r="L152" s="12">
         <f>100*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="M152" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N152" s="34">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>103</v>
@@ -28545,11 +28604,11 @@
       </c>
       <c r="R152" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="S152" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>83333.333333333328</v>
+        <v>33333.333333333336</v>
       </c>
       <c r="T152" s="12">
         <v>200</v>
@@ -28559,18 +28618,18 @@
       </c>
       <c r="V152" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="W152" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>20833.333333333332</v>
+        <v>8333.3333333333339</v>
       </c>
       <c r="X152" s="12">
         <v>50</v>
       </c>
       <c r="Y152" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>150000</v>
+        <v>60000</v>
       </c>
       <c r="Z152" s="6">
         <v>30</v>
@@ -28584,11 +28643,11 @@
       </c>
       <c r="AC152" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>1400000</v>
+        <v>560000</v>
       </c>
       <c r="AD152" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 250 000 €</v>
+        <v>3 mois = 100 000 €</v>
       </c>
       <c r="AE152" s="6" t="s">
         <v>103</v>
@@ -28606,34 +28665,34 @@
         <v>103</v>
       </c>
       <c r="AJ152" s="10" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="AK152" s="11" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="AL152" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM152" s="11" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="AN152" s="11" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="AO152" s="11" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="AP152" s="36" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="AQ152" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR152" s="11" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="AS152" s="13" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="AT152" s="14"/>
       <c r="AU152" s="44">
@@ -28643,50 +28702,51 @@
     <row r="153" spans="1:47" ht="38.25">
       <c r="A153" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Provence-Alpes-Côte d'Azur</v>
+        <v>Centre-Val de Loire</v>
       </c>
       <c r="B153" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Bouches-du-Rhône</v>
+        <v>Indre-et-Loire</v>
       </c>
       <c r="C153" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>1104</v>
+        <v>1041</v>
       </c>
       <c r="E153" s="26">
-        <v>13127</v>
+        <v>37600</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>1100</v>
+        <v>901</v>
       </c>
       <c r="G153" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>14 Boulevard de l'Europe
-13127 - Vitrolles</v>
+        <v>Super U 38 Route de Vauzelles, Rue du Bon Raisin
+37600 - Loches</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>1105</v>
+        <v>1052</v>
       </c>
       <c r="I153" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J153" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="K153" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L153" s="12" t="s">
-        <v>103</v>
+        <v>50</v>
+      </c>
+      <c r="K153" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L153" s="12">
+        <f>100*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>500000</v>
       </c>
       <c r="M153" s="36" t="s">
-        <v>1204</v>
+        <v>359</v>
       </c>
       <c r="N153" s="34">
-        <v>181</v>
+        <v>5000</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>103</v>
@@ -28699,35 +28759,35 @@
       </c>
       <c r="R153" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>45250</v>
+        <v>1000000</v>
       </c>
       <c r="S153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>3770.8333333333335</v>
+        <v>83333.333333333328</v>
       </c>
       <c r="T153" s="12">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="U153" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V153" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>1306.82</v>
+        <v>250000</v>
       </c>
       <c r="W153" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>108.90166666666666</v>
+        <v>20833.333333333332</v>
       </c>
       <c r="X153" s="12">
-        <v>7.22</v>
+        <v>50</v>
       </c>
       <c r="Y153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>2360.2399999999998</v>
-      </c>
-      <c r="Z153" s="12">
-        <v>13.04</v>
+        <v>150000</v>
+      </c>
+      <c r="Z153" s="6">
+        <v>30</v>
       </c>
       <c r="AA153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
@@ -28738,63 +28798,63 @@
       </c>
       <c r="AC153" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>48917.06</v>
+        <v>1400000</v>
       </c>
       <c r="AD153" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 11 313 €</v>
+        <v>3 mois = 250 000 €</v>
       </c>
       <c r="AE153" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AF153" s="46">
-        <v>0.05</v>
+      <c r="AF153" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="AG153" s="12" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="AH153" s="10" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="AI153" s="10" t="s">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="AJ153" s="10" t="s">
-        <v>1149</v>
+        <v>1056</v>
       </c>
       <c r="AK153" s="11" t="s">
-        <v>1203</v>
+        <v>1053</v>
       </c>
       <c r="AL153" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM153" s="11">
-        <v>43.4393873</v>
-      </c>
-      <c r="AN153" s="11">
-        <v>5.2419589999999996</v>
+      <c r="AM153" s="11" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AN153" s="11" t="s">
+        <v>1070</v>
       </c>
       <c r="AO153" s="11" t="s">
-        <v>1208</v>
+        <v>1060</v>
       </c>
       <c r="AP153" s="36" t="s">
-        <v>1270</v>
+        <v>1071</v>
       </c>
       <c r="AQ153" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR153" s="11" t="s">
-        <v>1202</v>
+        <v>1055</v>
       </c>
       <c r="AS153" s="13" t="s">
-        <v>1146</v>
+        <v>1045</v>
       </c>
       <c r="AT153" s="14"/>
       <c r="AU153" s="44">
-        <v>46003</v>
+        <v>45999</v>
       </c>
     </row>
-    <row r="154" spans="1:47" ht="51">
+    <row r="154" spans="1:47" ht="38.25">
       <c r="A154" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -28808,13 +28868,13 @@
         <v>13</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E154" s="26">
         <v>13127</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="G154" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28822,7 +28882,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="I154" s="12" t="s">
         <v>47</v>
@@ -28831,16 +28891,16 @@
         <v>48</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>1223</v>
+        <v>103</v>
       </c>
       <c r="L154" s="12" t="s">
         <v>103</v>
       </c>
       <c r="M154" s="36" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="N154" s="34">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>103</v>
@@ -28853,32 +28913,32 @@
       </c>
       <c r="R154" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>20000</v>
+        <v>45250</v>
       </c>
       <c r="S154" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>1666.6666666666667</v>
+        <v>3770.8333333333335</v>
       </c>
       <c r="T154" s="12">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U154" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V154" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>722</v>
+        <v>1306.82</v>
       </c>
       <c r="W154" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>60.166666666666664</v>
+        <v>108.90166666666666</v>
       </c>
       <c r="X154" s="12">
         <v>7.22</v>
       </c>
       <c r="Y154" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>1304</v>
+        <v>2360.2399999999998</v>
       </c>
       <c r="Z154" s="12">
         <v>13.04</v>
@@ -28892,11 +28952,11 @@
       </c>
       <c r="AC154" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>22026</v>
+        <v>48917.06</v>
       </c>
       <c r="AD154" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 5 000 €</v>
+        <v>3 mois = 11 313 €</v>
       </c>
       <c r="AE154" s="6" t="s">
         <v>103</v>
@@ -28914,41 +28974,41 @@
         <v>370</v>
       </c>
       <c r="AJ154" s="10" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="AK154" s="11" t="s">
-        <v>1211</v>
+        <v>1198</v>
       </c>
       <c r="AL154" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM154" s="11" t="s">
-        <v>1206</v>
-      </c>
-      <c r="AN154" s="11" t="s">
-        <v>1207</v>
+      <c r="AM154" s="11">
+        <v>43.4393873</v>
+      </c>
+      <c r="AN154" s="11">
+        <v>5.2419589999999996</v>
       </c>
       <c r="AO154" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="AP154" s="36" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
       <c r="AQ154" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR154" s="11" t="s">
-        <v>1212</v>
+        <v>1197</v>
       </c>
       <c r="AS154" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT154" s="14"/>
       <c r="AU154" s="44">
-        <v>46004</v>
+        <v>46003</v>
       </c>
     </row>
-    <row r="155" spans="1:47" ht="38.25">
+    <row r="155" spans="1:47" ht="51">
       <c r="A155" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -28962,13 +29022,13 @@
         <v>13</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E155" s="26">
         <v>13127</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="G155" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28976,7 +29036,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H155" s="15" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>47</v>
@@ -28985,16 +29045,16 @@
         <v>48</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="L155" s="12" t="s">
         <v>103</v>
       </c>
       <c r="M155" s="36" t="s">
-        <v>1216</v>
+        <v>1200</v>
       </c>
       <c r="N155" s="34">
-        <v>446</v>
+        <v>100</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>103</v>
@@ -29007,32 +29067,32 @@
       </c>
       <c r="R155" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>55750</v>
+        <v>20000</v>
       </c>
       <c r="S155" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>4645.833333333333</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="T155" s="12">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="U155" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V155" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>3220.12</v>
+        <v>722</v>
       </c>
       <c r="W155" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>268.34333333333331</v>
+        <v>60.166666666666664</v>
       </c>
       <c r="X155" s="12">
         <v>7.22</v>
       </c>
       <c r="Y155" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>5815.8399999999992</v>
+        <v>1304</v>
       </c>
       <c r="Z155" s="12">
         <v>13.04</v>
@@ -29046,11 +29106,11 @@
       </c>
       <c r="AC155" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>64785.96</v>
+        <v>22026</v>
       </c>
       <c r="AD155" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 13 938 €</v>
+        <v>3 mois = 5 000 €</v>
       </c>
       <c r="AE155" s="6" t="s">
         <v>103</v>
@@ -29062,44 +29122,44 @@
         <v>363</v>
       </c>
       <c r="AH155" s="10" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="AI155" s="10" t="s">
-        <v>103</v>
+        <v>370</v>
       </c>
       <c r="AJ155" s="10" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="AK155" s="11" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="AL155" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM155" s="11" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
       <c r="AN155" s="11" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
       <c r="AO155" s="11" t="s">
-        <v>1218</v>
+        <v>1204</v>
       </c>
       <c r="AP155" s="36" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="AQ155" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR155" s="11" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="AS155" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT155" s="14"/>
       <c r="AU155" s="44">
-        <v>46005</v>
+        <v>46004</v>
       </c>
     </row>
     <row r="156" spans="1:47" ht="38.25">
@@ -29116,13 +29176,13 @@
         <v>13</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E156" s="26">
         <v>13127</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="G156" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29130,7 +29190,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H156" s="15" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="I156" s="12" t="s">
         <v>47</v>
@@ -29139,16 +29199,16 @@
         <v>48</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="L156" s="12" t="s">
         <v>103</v>
       </c>
       <c r="M156" s="36" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="N156" s="34">
-        <v>567</v>
+        <v>446</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>103</v>
@@ -29161,11 +29221,11 @@
       </c>
       <c r="R156" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>70875</v>
+        <v>55750</v>
       </c>
       <c r="S156" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>5906.25</v>
+        <v>4645.833333333333</v>
       </c>
       <c r="T156" s="12">
         <v>125</v>
@@ -29175,18 +29235,18 @@
       </c>
       <c r="V156" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>4093.74</v>
+        <v>3220.12</v>
       </c>
       <c r="W156" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>341.14499999999998</v>
+        <v>268.34333333333331</v>
       </c>
       <c r="X156" s="12">
         <v>7.22</v>
       </c>
       <c r="Y156" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>7393.6799999999994</v>
+        <v>5815.8399999999992</v>
       </c>
       <c r="Z156" s="12">
         <v>13.04</v>
@@ -29200,11 +29260,11 @@
       </c>
       <c r="AC156" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>82362.42</v>
+        <v>64785.96</v>
       </c>
       <c r="AD156" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 17 719 €</v>
+        <v>3 mois = 13 938 €</v>
       </c>
       <c r="AE156" s="6" t="s">
         <v>103</v>
@@ -29222,38 +29282,38 @@
         <v>103</v>
       </c>
       <c r="AJ156" s="10" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="AK156" s="11" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="AL156" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM156" s="11" t="s">
-        <v>1221</v>
+        <v>1208</v>
       </c>
       <c r="AN156" s="11" t="s">
-        <v>1222</v>
+        <v>1209</v>
       </c>
       <c r="AO156" s="11" t="s">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="AP156" s="36" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="AQ156" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR156" s="11" t="s">
-        <v>1219</v>
+        <v>1210</v>
       </c>
       <c r="AS156" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT156" s="14"/>
       <c r="AU156" s="44">
-        <v>46006</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="157" spans="1:47" ht="38.25">
@@ -29270,376 +29330,386 @@
         <v>13</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>1138</v>
+        <v>1099</v>
       </c>
       <c r="E157" s="26">
+        <v>13127</v>
+      </c>
+      <c r="F157" s="10" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G157" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>14 Boulevard de l'Europe
+13127 - Vitrolles</v>
+      </c>
+      <c r="H157" s="15" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K157" s="10" t="s">
+        <v>1218</v>
+      </c>
+      <c r="L157" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M157" s="36" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N157" s="34">
+        <v>567</v>
+      </c>
+      <c r="O157" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P157" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q157" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R157" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>70875</v>
+      </c>
+      <c r="S157" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5906.25</v>
+      </c>
+      <c r="T157" s="12">
+        <v>125</v>
+      </c>
+      <c r="U157" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V157" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>4093.74</v>
+      </c>
+      <c r="W157" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>341.14499999999998</v>
+      </c>
+      <c r="X157" s="12">
+        <v>7.22</v>
+      </c>
+      <c r="Y157" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>7393.6799999999994</v>
+      </c>
+      <c r="Z157" s="12">
+        <v>13.04</v>
+      </c>
+      <c r="AA157" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB157" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC157" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>82362.42</v>
+      </c>
+      <c r="AD157" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 17 719 €</v>
+      </c>
+      <c r="AE157" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF157" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG157" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH157" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI157" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ157" s="10" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AK157" s="11" t="s">
+        <v>1205</v>
+      </c>
+      <c r="AL157" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM157" s="11" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AN157" s="11" t="s">
+        <v>1217</v>
+      </c>
+      <c r="AO157" s="11" t="s">
+        <v>1215</v>
+      </c>
+      <c r="AP157" s="36" t="s">
+        <v>1250</v>
+      </c>
+      <c r="AQ157" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR157" s="11" t="s">
+        <v>1214</v>
+      </c>
+      <c r="AS157" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT157" s="14"/>
+      <c r="AU157" s="44">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="158" spans="1:47" ht="38.25">
+      <c r="A158" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B158" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Bouches-du-Rhône</v>
+      </c>
+      <c r="C158" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>13</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E158" s="26">
         <v>13170</v>
       </c>
-      <c r="F157" s="10" t="s">
-        <v>1126</v>
-      </c>
-      <c r="G157" s="39" t="str">
+      <c r="F158" s="10" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G158" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Plan de Campagne, Chemin des Pennes CD6
 13170 - Les Pennes-Mirabeau</v>
       </c>
-      <c r="H157" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="I157" s="12" t="s">
+      <c r="H158" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I158" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J157" s="12" t="s">
+      <c r="J158" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K157" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L157" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M157" s="36"/>
-      <c r="N157" s="34">
+      <c r="K158" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L158" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M158" s="36"/>
+      <c r="N158" s="34">
         <v>1390</v>
       </c>
-      <c r="O157" s="6" t="s">
-        <v>1225</v>
-      </c>
-      <c r="P157" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q157" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R157" s="12">
+      <c r="O158" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="P158" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q158" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R158" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>312750</v>
       </c>
-      <c r="S157" s="12">
+      <c r="S158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>26062.5</v>
       </c>
-      <c r="T157" s="12">
+      <c r="T158" s="12">
         <v>225</v>
       </c>
-      <c r="U157" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V157" s="6">
+      <c r="U158" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V158" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>9730</v>
       </c>
-      <c r="W157" s="12">
+      <c r="W158" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>810.83333333333337</v>
       </c>
-      <c r="X157" s="12">
+      <c r="X158" s="12">
         <v>7</v>
       </c>
-      <c r="Y157" s="12">
+      <c r="Y158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>20850</v>
       </c>
-      <c r="Z157" s="12">
+      <c r="Z158" s="12">
         <v>15</v>
       </c>
-      <c r="AA157" s="12">
+      <c r="AA158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB157" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC157" s="12">
+      <c r="AB158" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC158" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>343330</v>
       </c>
-      <c r="AD157" s="12" t="str">
+      <c r="AD158" s="12" t="str">
         <f t="shared" si="6"/>
         <v>3 mois = 78 188 €</v>
       </c>
-      <c r="AE157" s="12" t="str">
-        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R157,0),"### ### ##0 €")</f>
+      <c r="AE158" s="12" t="str">
+        <f>"6 mois = "&amp;TEXT(ROUND(6/12*R158,0),"### ### ##0 €")</f>
         <v>6 mois = 156 375 €</v>
       </c>
-      <c r="AF157" s="46">
+      <c r="AF158" s="46">
         <v>0.05</v>
       </c>
-      <c r="AG157" s="12" t="s">
+      <c r="AG158" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AH157" s="10" t="s">
+      <c r="AH158" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="AI157" s="10" t="s">
+      <c r="AI158" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="AJ157" s="10" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AK157" s="11" t="s">
-        <v>1226</v>
-      </c>
-      <c r="AL157" s="5" t="s">
+      <c r="AJ158" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AK158" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AL158" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM157" s="11" t="s">
-        <v>1139</v>
-      </c>
-      <c r="AN157" s="11" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AO157" s="11">
+      <c r="AM158" s="11" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AN158" s="11" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AO158" s="11">
         <v>37</v>
       </c>
-      <c r="AP157" s="36" t="s">
-        <v>1256</v>
-      </c>
-      <c r="AQ157" s="11" t="s">
+      <c r="AP158" s="36" t="s">
+        <v>1251</v>
+      </c>
+      <c r="AQ158" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR157" s="11" t="s">
-        <v>1224</v>
-      </c>
-      <c r="AS157" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT157" s="14"/>
-      <c r="AU157" s="44">
+      <c r="AR158" s="11" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AS158" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT158" s="14"/>
+      <c r="AU158" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="158" spans="1:47" ht="25.5">
-      <c r="A158" s="38" t="str">
+    <row r="159" spans="1:47" ht="25.5">
+      <c r="A159" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
       </c>
-      <c r="B158" s="38" t="str">
+      <c r="B159" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
         <v>Cher</v>
       </c>
-      <c r="C158" s="38">
+      <c r="C159" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>18</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E158" s="26">
+      <c r="D159" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E159" s="26">
         <v>18390</v>
       </c>
-      <c r="F158" s="10" t="s">
-        <v>1128</v>
-      </c>
-      <c r="G158" s="39" t="str">
+      <c r="F159" s="10" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G159" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>8 Rue des Vignes
 18390 - Saint-Germain-du-Puy</v>
       </c>
-      <c r="H158" s="15" t="s">
-        <v>1108</v>
-      </c>
-      <c r="I158" s="12" t="s">
+      <c r="H159" s="15" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I159" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J158" s="12" t="s">
+      <c r="J159" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K158" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L158" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M158" s="36"/>
-      <c r="N158" s="34">
+      <c r="K159" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L159" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M159" s="36"/>
+      <c r="N159" s="34">
         <v>1000</v>
       </c>
-      <c r="O158" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P158" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q158" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R158" s="12">
+      <c r="O159" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P159" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q159" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R159" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>150000</v>
       </c>
-      <c r="S158" s="12">
+      <c r="S159" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>12500</v>
       </c>
-      <c r="T158" s="12">
+      <c r="T159" s="12">
         <v>150</v>
       </c>
-      <c r="U158" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V158" s="6">
+      <c r="U159" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V159" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>3500</v>
       </c>
-      <c r="W158" s="12">
+      <c r="W159" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>291.66666666666669</v>
       </c>
-      <c r="X158" s="12">
+      <c r="X159" s="12">
         <v>3.5</v>
       </c>
-      <c r="Y158" s="12">
+      <c r="Y159" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>12650</v>
       </c>
-      <c r="Z158" s="12">
+      <c r="Z159" s="12">
         <v>12.65</v>
       </c>
-      <c r="AA158" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB158" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC158" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>166150</v>
-      </c>
-      <c r="AD158" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>3 mois = 37 500 €</v>
-      </c>
-      <c r="AE158" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF158" s="46">
-        <v>0.05</v>
-      </c>
-      <c r="AG158" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="AH158" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="AI158" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="AJ158" s="10" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AK158" s="11" t="s">
-        <v>1152</v>
-      </c>
-      <c r="AL158" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="AM158" s="11" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN158" s="11" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AO158" s="11">
-        <v>38</v>
-      </c>
-      <c r="AP158" s="36" t="s">
-        <v>1257</v>
-      </c>
-      <c r="AQ158" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR158" s="11" t="s">
-        <v>1227</v>
-      </c>
-      <c r="AS158" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT158" s="14"/>
-      <c r="AU158" s="44">
-        <v>46003</v>
-      </c>
-    </row>
-    <row r="159" spans="1:47" ht="38.25">
-      <c r="A159" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Centre-Val de Loire</v>
-      </c>
-      <c r="B159" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Cher</v>
-      </c>
-      <c r="C159" s="38">
-        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>18</v>
-      </c>
-      <c r="D159" s="10" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E159" s="26">
-        <v>18230</v>
-      </c>
-      <c r="F159" s="10" t="s">
-        <v>1129</v>
-      </c>
-      <c r="G159" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>Centre Commercial Géant,  548 Route d'Orléans
-18230 -  Saint-Doulchard</v>
-      </c>
-      <c r="H159" s="15" t="s">
-        <v>1109</v>
-      </c>
-      <c r="I159" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="J159" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K159" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L159" s="12"/>
-      <c r="M159" s="36"/>
-      <c r="N159" s="34">
-        <v>5000</v>
-      </c>
-      <c r="O159" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P159" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q159" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R159" s="12">
-        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
-      </c>
-      <c r="S159" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T159" s="12"/>
-      <c r="U159" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V159" s="6">
-        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
-      </c>
-      <c r="W159" s="12">
-        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X159" s="12"/>
-      <c r="Y159" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z159" s="12"/>
       <c r="AA159" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -29649,54 +29719,56 @@
       </c>
       <c r="AC159" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
+        <v>166150</v>
       </c>
       <c r="AD159" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 0 €</v>
+        <v>3 mois = 37 500 €</v>
       </c>
       <c r="AE159" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AF159" s="6" t="s">
-        <v>103</v>
+      <c r="AF159" s="46">
+        <v>0.05</v>
       </c>
       <c r="AG159" s="12" t="s">
         <v>363</v>
       </c>
       <c r="AH159" s="10" t="s">
-        <v>53</v>
+        <v>377</v>
       </c>
       <c r="AI159" s="10" t="s">
-        <v>103</v>
+        <v>370</v>
       </c>
       <c r="AJ159" s="10" t="s">
-        <v>1155</v>
+        <v>1146</v>
       </c>
       <c r="AK159" s="11" t="s">
-        <v>1158</v>
+        <v>1147</v>
       </c>
       <c r="AL159" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM159" s="11" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="AN159" s="11" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
       <c r="AO159" s="11">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AP159" s="36" t="s">
-        <v>1188</v>
+        <v>1252</v>
       </c>
       <c r="AQ159" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR159" s="11"/>
+      <c r="AR159" s="11" t="s">
+        <v>1222</v>
+      </c>
       <c r="AS159" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT159" s="14"/>
       <c r="AU159" s="44">
@@ -29706,51 +29778,49 @@
     <row r="160" spans="1:47" ht="38.25">
       <c r="A160" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Centre-Val de Loire</v>
       </c>
       <c r="B160" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Meurthe-et-Moselle</v>
+        <v>Cher</v>
       </c>
       <c r="C160" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="E160" s="26">
-        <v>54000</v>
+        <v>18230</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>1101</v>
+        <v>1124</v>
       </c>
       <c r="G160" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>50 Rue Saint-Dizier
-54000 - Nancy</v>
+        <v>Centre Commercial Géant,  548 Route d'Orléans
+18230 -  Saint-Doulchard</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K160" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L160" s="12" t="s">
-        <v>103</v>
-      </c>
+      <c r="L160" s="12"/>
       <c r="M160" s="36"/>
       <c r="N160" s="34">
-        <v>550</v>
+        <v>5000</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>1229</v>
+        <v>103</v>
       </c>
       <c r="P160" s="34" t="s">
         <v>103</v>
@@ -29760,36 +29830,30 @@
       </c>
       <c r="R160" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="S160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>27500</v>
-      </c>
-      <c r="T160" s="12">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T160" s="12"/>
       <c r="U160" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V160" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>2750</v>
+        <v>0</v>
       </c>
       <c r="W160" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>229.16666666666666</v>
-      </c>
-      <c r="X160" s="12">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X160" s="12"/>
       <c r="Y160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>8250</v>
-      </c>
-      <c r="Z160" s="12">
-        <v>15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z160" s="12"/>
       <c r="AA160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -29799,56 +29863,54 @@
       </c>
       <c r="AC160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>341000</v>
+        <v>0</v>
       </c>
       <c r="AD160" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 82 500 €</v>
+        <v>3 mois = 0 €</v>
       </c>
       <c r="AE160" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AF160" s="46">
-        <v>0.05</v>
+      <c r="AF160" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="AG160" s="12" t="s">
         <v>363</v>
       </c>
       <c r="AH160" s="10" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="AI160" s="10" t="s">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="AJ160" s="10" t="s">
-        <v>1161</v>
+        <v>1150</v>
       </c>
       <c r="AK160" s="11" t="s">
-        <v>1230</v>
+        <v>1153</v>
       </c>
       <c r="AL160" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM160" s="11" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
       <c r="AN160" s="11" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="AO160" s="11">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP160" s="36" t="s">
-        <v>1258</v>
+        <v>1183</v>
       </c>
       <c r="AQ160" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR160" s="11" t="s">
-        <v>1228</v>
-      </c>
+      <c r="AR160" s="11"/>
       <c r="AS160" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT160" s="14"/>
       <c r="AU160" s="44">
@@ -29858,38 +29920,38 @@
     <row r="161" spans="1:47" ht="38.25">
       <c r="A161" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Hauts-de-France</v>
+        <v>Grand Est</v>
       </c>
       <c r="B161" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Nord</v>
+        <v>Meurthe-et-Moselle</v>
       </c>
       <c r="C161" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="E161" s="26">
-        <v>59300</v>
+        <v>54000</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>1133</v>
+        <v>1096</v>
       </c>
       <c r="G161" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>ZAC D'Aulnoy
-59300 - Aulnoy-lez-Valenciennes</v>
+        <v>50 Rue Saint-Dizier
+54000 - Nancy</v>
       </c>
       <c r="H161" s="15" t="s">
-        <v>1298</v>
+        <v>1105</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J161" s="12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K161" s="10" t="s">
         <v>103</v>
@@ -29899,10 +29961,10 @@
       </c>
       <c r="M161" s="36"/>
       <c r="N161" s="34">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="O161" s="6" t="s">
-        <v>103</v>
+        <v>1224</v>
       </c>
       <c r="P161" s="34" t="s">
         <v>103</v>
@@ -29912,35 +29974,35 @@
       </c>
       <c r="R161" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>144000</v>
+        <v>330000</v>
       </c>
       <c r="S161" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>12000</v>
+        <v>27500</v>
       </c>
       <c r="T161" s="12">
-        <v>300</v>
-      </c>
-      <c r="U161" s="46">
-        <v>0.08</v>
+        <v>600</v>
+      </c>
+      <c r="U161" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="V161" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>32880</v>
+        <v>2750</v>
       </c>
       <c r="W161" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>2740</v>
+        <v>229.16666666666666</v>
       </c>
       <c r="X161" s="12">
-        <v>68.5</v>
+        <v>5</v>
       </c>
       <c r="Y161" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>16800</v>
+        <v>8250</v>
       </c>
       <c r="Z161" s="12">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AA161" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
@@ -29951,11 +30013,11 @@
       </c>
       <c r="AC161" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>193680</v>
+        <v>341000</v>
       </c>
       <c r="AD161" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 36 000 €</v>
+        <v>3 mois = 82 500 €</v>
       </c>
       <c r="AE161" s="6" t="s">
         <v>103</v>
@@ -29967,47 +30029,47 @@
         <v>363</v>
       </c>
       <c r="AH161" s="10" t="s">
-        <v>377</v>
+        <v>75</v>
       </c>
       <c r="AI161" s="10" t="s">
         <v>370</v>
       </c>
       <c r="AJ161" s="10" t="s">
-        <v>1300</v>
+        <v>1156</v>
       </c>
       <c r="AK161" s="11" t="s">
-        <v>1301</v>
+        <v>1225</v>
       </c>
       <c r="AL161" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM161" s="11" t="s">
-        <v>1287</v>
+        <v>1154</v>
       </c>
       <c r="AN161" s="11" t="s">
-        <v>1288</v>
-      </c>
-      <c r="AO161" s="11" t="s">
-        <v>1275</v>
+        <v>1155</v>
+      </c>
+      <c r="AO161" s="11">
+        <v>40</v>
       </c>
       <c r="AP161" s="36" t="s">
-        <v>1303</v>
+        <v>1253</v>
       </c>
       <c r="AQ161" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR161" s="11" t="s">
-        <v>1281</v>
+        <v>1223</v>
       </c>
       <c r="AS161" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT161" s="14"/>
       <c r="AU161" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="162" spans="1:47" ht="25.5">
+    <row r="162" spans="1:47" ht="38.25">
       <c r="A162" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30021,13 +30083,13 @@
         <v>59</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="E162" s="26">
         <v>59300</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="G162" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30035,7 +30097,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="I162" s="12" t="s">
         <v>47</v>
@@ -30051,7 +30113,7 @@
       </c>
       <c r="M162" s="36"/>
       <c r="N162" s="34">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>103</v>
@@ -30064,50 +30126,50 @@
       </c>
       <c r="R162" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>110000</v>
+        <v>144000</v>
       </c>
       <c r="S162" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>9166.6666666666661</v>
+        <v>12000</v>
       </c>
       <c r="T162" s="12">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="U162" s="46">
         <v>0.08</v>
       </c>
       <c r="V162" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>13700</v>
+        <v>32880</v>
       </c>
       <c r="W162" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>1141.6666666666667</v>
+        <v>2740</v>
       </c>
       <c r="X162" s="12">
         <v>68.5</v>
       </c>
       <c r="Y162" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>7000</v>
+        <v>16800</v>
       </c>
       <c r="Z162" s="12">
         <v>35</v>
       </c>
       <c r="AA162" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>5000</v>
-      </c>
-      <c r="AB162" s="6">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="AB162" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="AC162" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>135700</v>
+        <v>193680</v>
       </c>
       <c r="AD162" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 27 500 €</v>
+        <v>3 mois = 36 000 €</v>
       </c>
       <c r="AE162" s="6" t="s">
         <v>103</v>
@@ -30125,37 +30187,39 @@
         <v>370</v>
       </c>
       <c r="AJ162" s="10" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="AK162" s="11" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="AL162" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM162" s="11" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="AN162" s="11" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="AO162" s="11" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="AP162" s="36" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="AQ162" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR162" s="11" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="AS162" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT162" s="14"/>
-      <c r="AU162" s="44"/>
+      <c r="AU162" s="44">
+        <v>46003</v>
+      </c>
     </row>
     <row r="163" spans="1:47" ht="25.5">
       <c r="A163" s="38" t="str">
@@ -30171,13 +30235,13 @@
         <v>59</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="E163" s="26">
         <v>59300</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="G163" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30185,7 +30249,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H163" s="15" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="I163" s="12" t="s">
         <v>47</v>
@@ -30201,7 +30265,7 @@
       </c>
       <c r="M163" s="36"/>
       <c r="N163" s="34">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>103</v>
@@ -30214,50 +30278,50 @@
       </c>
       <c r="R163" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>54000</v>
+        <v>110000</v>
       </c>
       <c r="S163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>4500</v>
+        <v>9166.6666666666661</v>
       </c>
       <c r="T163" s="12">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="U163" s="46">
         <v>0.08</v>
       </c>
       <c r="V163" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>6165</v>
+        <v>13700</v>
       </c>
       <c r="W163" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>513.75</v>
+        <v>1141.6666666666667</v>
       </c>
       <c r="X163" s="12">
         <v>68.5</v>
       </c>
       <c r="Y163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>3150</v>
+        <v>7000</v>
       </c>
       <c r="Z163" s="12">
         <v>35</v>
       </c>
       <c r="AA163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>2250</v>
+        <v>5000</v>
       </c>
       <c r="AB163" s="6">
         <v>25</v>
       </c>
       <c r="AC163" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>65565</v>
+        <v>135700</v>
       </c>
       <c r="AD163" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 13 500 €</v>
+        <v>3 mois = 27 500 €</v>
       </c>
       <c r="AE163" s="6" t="s">
         <v>103</v>
@@ -30275,34 +30339,34 @@
         <v>370</v>
       </c>
       <c r="AJ163" s="10" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="AK163" s="11" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="AL163" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM163" s="11" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="AN163" s="11" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="AO163" s="11" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="AP163" s="36" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="AQ163" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR163" s="11" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="AS163" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT163" s="14"/>
       <c r="AU163" s="44"/>
@@ -30321,13 +30385,13 @@
         <v>59</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="E164" s="26">
         <v>59300</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="G164" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30335,7 +30399,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H164" s="15" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>47</v>
@@ -30351,7 +30415,7 @@
       </c>
       <c r="M164" s="36"/>
       <c r="N164" s="34">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>103</v>
@@ -30364,11 +30428,11 @@
       </c>
       <c r="R164" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>46800</v>
+        <v>54000</v>
       </c>
       <c r="S164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>3900</v>
+        <v>4500</v>
       </c>
       <c r="T164" s="12">
         <v>600</v>
@@ -30378,36 +30442,36 @@
       </c>
       <c r="V164" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>5343</v>
+        <v>6165</v>
       </c>
       <c r="W164" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>445.25</v>
+        <v>513.75</v>
       </c>
       <c r="X164" s="12">
         <v>68.5</v>
       </c>
       <c r="Y164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>2730</v>
+        <v>3150</v>
       </c>
       <c r="Z164" s="12">
         <v>35</v>
       </c>
       <c r="AA164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>1950</v>
+        <v>2250</v>
       </c>
       <c r="AB164" s="6">
         <v>25</v>
       </c>
       <c r="AC164" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>56823</v>
+        <v>65565</v>
       </c>
       <c r="AD164" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 11 700 €</v>
+        <v>3 mois = 13 500 €</v>
       </c>
       <c r="AE164" s="6" t="s">
         <v>103</v>
@@ -30419,40 +30483,40 @@
         <v>363</v>
       </c>
       <c r="AH164" s="10" t="s">
-        <v>53</v>
+        <v>377</v>
       </c>
       <c r="AI164" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ164" s="10" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="AK164" s="11" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="AL164" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM164" s="11" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="AN164" s="11" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="AO164" s="11" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="AP164" s="36" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="AQ164" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR164" s="11" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="AS164" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT164" s="14"/>
       <c r="AU164" s="44"/>
@@ -30471,13 +30535,13 @@
         <v>59</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="E165" s="26">
         <v>59300</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="G165" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30485,7 +30549,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H165" s="15" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="I165" s="12" t="s">
         <v>47</v>
@@ -30501,7 +30565,7 @@
       </c>
       <c r="M165" s="36"/>
       <c r="N165" s="34">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="O165" s="6" t="s">
         <v>103</v>
@@ -30514,50 +30578,50 @@
       </c>
       <c r="R165" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>38500</v>
+        <v>46800</v>
       </c>
       <c r="S165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>3208.3333333333335</v>
+        <v>3900</v>
       </c>
       <c r="T165" s="12">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="U165" s="46">
         <v>0.08</v>
       </c>
       <c r="V165" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>4795</v>
+        <v>5343</v>
       </c>
       <c r="W165" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>399.58333333333331</v>
+        <v>445.25</v>
       </c>
       <c r="X165" s="12">
         <v>68.5</v>
       </c>
       <c r="Y165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>2450</v>
+        <v>2730</v>
       </c>
       <c r="Z165" s="12">
         <v>35</v>
       </c>
       <c r="AA165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>1750</v>
+        <v>1950</v>
       </c>
       <c r="AB165" s="6">
         <v>25</v>
       </c>
       <c r="AC165" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>47495</v>
+        <v>56823</v>
       </c>
       <c r="AD165" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 9 625 €</v>
+        <v>3 mois = 11 700 €</v>
       </c>
       <c r="AE165" s="6" t="s">
         <v>103</v>
@@ -30569,40 +30633,40 @@
         <v>363</v>
       </c>
       <c r="AH165" s="10" t="s">
-        <v>377</v>
+        <v>53</v>
       </c>
       <c r="AI165" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AJ165" s="10" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="AK165" s="11" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="AL165" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM165" s="11" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="AN165" s="11" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="AO165" s="11" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="AP165" s="36" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="AQ165" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR165" s="11" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="AS165" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT165" s="14"/>
       <c r="AU165" s="44"/>
@@ -30621,13 +30685,13 @@
         <v>59</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="E166" s="26">
         <v>59300</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="G166" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30635,7 +30699,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="I166" s="12" t="s">
         <v>47</v>
@@ -30644,14 +30708,14 @@
         <v>49</v>
       </c>
       <c r="K166" s="10" t="s">
-        <v>1309</v>
+        <v>103</v>
       </c>
       <c r="L166" s="12" t="s">
         <v>103</v>
       </c>
       <c r="M166" s="36"/>
       <c r="N166" s="34">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="O166" s="6" t="s">
         <v>103</v>
@@ -30664,50 +30728,50 @@
       </c>
       <c r="R166" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>24000</v>
+        <v>38500</v>
       </c>
       <c r="S166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>2000</v>
+        <v>3208.3333333333335</v>
       </c>
       <c r="T166" s="12">
-        <v>1200</v>
+        <v>550</v>
       </c>
       <c r="U166" s="46">
         <v>0.08</v>
       </c>
       <c r="V166" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>1370</v>
+        <v>4795</v>
       </c>
       <c r="W166" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>114.16666666666667</v>
+        <v>399.58333333333331</v>
       </c>
       <c r="X166" s="12">
         <v>68.5</v>
       </c>
       <c r="Y166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>700</v>
+        <v>2450</v>
       </c>
       <c r="Z166" s="12">
         <v>35</v>
       </c>
       <c r="AA166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="AB166" s="6">
         <v>25</v>
       </c>
       <c r="AC166" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>26570</v>
+        <v>47495</v>
       </c>
       <c r="AD166" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 6 000 €</v>
+        <v>3 mois = 9 625 €</v>
       </c>
       <c r="AE166" s="6" t="s">
         <v>103</v>
@@ -30719,45 +30783,45 @@
         <v>363</v>
       </c>
       <c r="AH166" s="10" t="s">
-        <v>53</v>
+        <v>377</v>
       </c>
       <c r="AI166" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ166" s="10" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="AK166" s="11" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="AL166" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM166" s="11" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="AN166" s="11" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="AO166" s="11" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="AP166" s="36" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="AQ166" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR166" s="11" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="AS166" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT166" s="14"/>
       <c r="AU166" s="44"/>
     </row>
-    <row r="167" spans="1:47" ht="38.25">
+    <row r="167" spans="1:47" ht="25.5">
       <c r="A167" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30771,230 +30835,228 @@
         <v>59</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>1231</v>
+        <v>1127</v>
       </c>
       <c r="E167" s="26">
+        <v>59300</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G167" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>ZAC D'Aulnoy
+59300 - Aulnoy-lez-Valenciennes</v>
+      </c>
+      <c r="H167" s="15" t="s">
+        <v>1293</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J167" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K167" s="10" t="s">
+        <v>1304</v>
+      </c>
+      <c r="L167" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M167" s="36"/>
+      <c r="N167" s="34">
+        <v>20</v>
+      </c>
+      <c r="O167" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P167" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q167" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R167" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>24000</v>
+      </c>
+      <c r="S167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2000</v>
+      </c>
+      <c r="T167" s="12">
+        <v>1200</v>
+      </c>
+      <c r="U167" s="46">
+        <v>0.08</v>
+      </c>
+      <c r="V167" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1370</v>
+      </c>
+      <c r="W167" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>114.16666666666667</v>
+      </c>
+      <c r="X167" s="12">
+        <v>68.5</v>
+      </c>
+      <c r="Y167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>700</v>
+      </c>
+      <c r="Z167" s="12">
+        <v>35</v>
+      </c>
+      <c r="AA167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>500</v>
+      </c>
+      <c r="AB167" s="6">
+        <v>25</v>
+      </c>
+      <c r="AC167" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>26570</v>
+      </c>
+      <c r="AD167" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 6 000 €</v>
+      </c>
+      <c r="AE167" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF167" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG167" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH167" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI167" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AJ167" s="10" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AK167" s="11" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AL167" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM167" s="11" t="s">
+        <v>1291</v>
+      </c>
+      <c r="AN167" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AO167" s="11" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AP167" s="36" t="s">
+        <v>1303</v>
+      </c>
+      <c r="AQ167" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR167" s="11" t="s">
+        <v>1281</v>
+      </c>
+      <c r="AS167" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT167" s="14"/>
+      <c r="AU167" s="44"/>
+    </row>
+    <row r="168" spans="1:47" ht="38.25">
+      <c r="A168" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B168" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Nord</v>
+      </c>
+      <c r="C168" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>59</v>
+      </c>
+      <c r="D168" s="10" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E168" s="26">
         <v>59320</v>
       </c>
-      <c r="F167" s="10" t="s">
-        <v>1134</v>
-      </c>
-      <c r="G167" s="39" t="str">
+      <c r="F168" s="10" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G168" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>5001 Rue des Fusillés de 1940
 59320 - Ennetières-en-Weppes</v>
       </c>
-      <c r="H167" s="15" t="s">
-        <v>1163</v>
-      </c>
-      <c r="I167" s="12" t="s">
+      <c r="H168" s="15" t="s">
+        <v>1158</v>
+      </c>
+      <c r="I168" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J167" s="12" t="s">
+      <c r="J168" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K167" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L167" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M167" s="36"/>
-      <c r="N167" s="34">
+      <c r="K168" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L168" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M168" s="36"/>
+      <c r="N168" s="34">
         <v>750</v>
       </c>
-      <c r="O167" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P167" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q167" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R167" s="12">
+      <c r="O168" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P168" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q168" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R168" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>262500</v>
       </c>
-      <c r="S167" s="12">
+      <c r="S168" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>21875</v>
       </c>
-      <c r="T167" s="12">
+      <c r="T168" s="12">
         <v>350</v>
       </c>
-      <c r="U167" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V167" s="6">
+      <c r="U168" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V168" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>10725</v>
       </c>
-      <c r="W167" s="12">
+      <c r="W168" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>893.75</v>
       </c>
-      <c r="X167" s="12">
+      <c r="X168" s="12">
         <v>14.3</v>
       </c>
-      <c r="Y167" s="12">
+      <c r="Y168" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>13200.000000000002</v>
       </c>
-      <c r="Z167" s="12">
+      <c r="Z168" s="12">
         <v>17.600000000000001</v>
-      </c>
-      <c r="AA167" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB167" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC167" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>286425</v>
-      </c>
-      <c r="AD167" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>3 mois = 65 625 €</v>
-      </c>
-      <c r="AE167" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF167" s="46">
-        <v>0.05</v>
-      </c>
-      <c r="AG167" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="AH167" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI167" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="AJ167" s="10" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AK167" s="11" t="s">
-        <v>1232</v>
-      </c>
-      <c r="AL167" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="AM167" s="11" t="s">
-        <v>1147</v>
-      </c>
-      <c r="AN167" s="11" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO167" s="11">
-        <v>42</v>
-      </c>
-      <c r="AP167" s="36" t="s">
-        <v>1259</v>
-      </c>
-      <c r="AQ167" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR167" s="11" t="s">
-        <v>1272</v>
-      </c>
-      <c r="AS167" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT167" s="14"/>
-      <c r="AU167" s="44">
-        <v>46003</v>
-      </c>
-    </row>
-    <row r="168" spans="1:47" ht="25.5">
-      <c r="A168" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
-      </c>
-      <c r="B168" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Haut-Rhin</v>
-      </c>
-      <c r="C168" s="38">
-        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>68</v>
-      </c>
-      <c r="D168" s="10" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E168" s="26">
-        <v>68270</v>
-      </c>
-      <c r="F168" s="10" t="s">
-        <v>1136</v>
-      </c>
-      <c r="G168" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>11 Rue de Soultz
-68270 - Wittenheim</v>
-      </c>
-      <c r="H168" s="15" t="s">
-        <v>1111</v>
-      </c>
-      <c r="I168" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="J168" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="K168" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L168" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M168" s="36"/>
-      <c r="N168" s="34">
-        <v>930</v>
-      </c>
-      <c r="O168" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P168" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q168" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R168" s="12">
-        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>209250</v>
-      </c>
-      <c r="S168" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>17437.5</v>
-      </c>
-      <c r="T168" s="12">
-        <v>225</v>
-      </c>
-      <c r="U168" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V168" s="6">
-        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>3069</v>
-      </c>
-      <c r="W168" s="12">
-        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>255.75</v>
-      </c>
-      <c r="X168" s="12">
-        <v>3.3</v>
-      </c>
-      <c r="Y168" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>12276</v>
-      </c>
-      <c r="Z168" s="12">
-        <v>13.2</v>
       </c>
       <c r="AA168" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
@@ -31005,11 +31067,11 @@
       </c>
       <c r="AC168" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>224595</v>
+        <v>286425</v>
       </c>
       <c r="AD168" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 52 313 €</v>
+        <v>3 mois = 65 625 €</v>
       </c>
       <c r="AE168" s="6" t="s">
         <v>103</v>
@@ -31021,40 +31083,40 @@
         <v>363</v>
       </c>
       <c r="AH168" s="10" t="s">
-        <v>377</v>
+        <v>75</v>
       </c>
       <c r="AI168" s="10" t="s">
         <v>370</v>
       </c>
       <c r="AJ168" s="10" t="s">
-        <v>1234</v>
+        <v>1157</v>
       </c>
       <c r="AK168" s="11" t="s">
-        <v>1189</v>
+        <v>1227</v>
       </c>
       <c r="AL168" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM168" s="11" t="s">
-        <v>1164</v>
+        <v>1142</v>
       </c>
       <c r="AN168" s="11" t="s">
-        <v>1165</v>
+        <v>1143</v>
       </c>
       <c r="AO168" s="11">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AP168" s="36" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="AQ168" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR168" s="11" t="s">
-        <v>1233</v>
+        <v>1267</v>
       </c>
       <c r="AS168" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT168" s="14"/>
       <c r="AU168" s="44">
@@ -31064,698 +31126,697 @@
     <row r="169" spans="1:47" ht="25.5">
       <c r="A169" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
+        <v>Grand Est</v>
       </c>
       <c r="B169" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Seine-et-Marne</v>
+        <v>Haut-Rhin</v>
       </c>
       <c r="C169" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>68</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E169" s="26">
+        <v>68270</v>
+      </c>
+      <c r="F169" s="10" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G169" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>11 Rue de Soultz
+68270 - Wittenheim</v>
+      </c>
+      <c r="H169" s="15" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K169" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L169" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M169" s="36"/>
+      <c r="N169" s="34">
+        <v>930</v>
+      </c>
+      <c r="O169" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P169" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q169" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R169" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>209250</v>
+      </c>
+      <c r="S169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>17437.5</v>
+      </c>
+      <c r="T169" s="12">
+        <v>225</v>
+      </c>
+      <c r="U169" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V169" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3069</v>
+      </c>
+      <c r="W169" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>255.75</v>
+      </c>
+      <c r="X169" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="Y169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>12276</v>
+      </c>
+      <c r="Z169" s="12">
+        <v>13.2</v>
+      </c>
+      <c r="AA169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB169" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC169" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>224595</v>
+      </c>
+      <c r="AD169" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 52 313 €</v>
+      </c>
+      <c r="AE169" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF169" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG169" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH169" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI169" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ169" s="10" t="s">
+        <v>1229</v>
+      </c>
+      <c r="AK169" s="11" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AL169" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM169" s="11" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AN169" s="11" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AO169" s="11">
+        <v>43</v>
+      </c>
+      <c r="AP169" s="36" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AQ169" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR169" s="11" t="s">
+        <v>1228</v>
+      </c>
+      <c r="AS169" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT169" s="14"/>
+      <c r="AU169" s="44">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="170" spans="1:47" ht="25.5">
+      <c r="A170" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B170" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Seine-et-Marne</v>
+      </c>
+      <c r="C170" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>77</v>
       </c>
-      <c r="D169" s="10" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E169" s="26">
+      <c r="D170" s="10" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E170" s="26">
         <v>77140</v>
       </c>
-      <c r="F169" s="10" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G169" s="39" t="str">
+      <c r="F170" s="10" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G170" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>31 Rue de Montargis
 77140 - Nemours</v>
       </c>
-      <c r="H169" s="15" t="s">
-        <v>1112</v>
-      </c>
-      <c r="I169" s="12" t="s">
+      <c r="H170" s="15" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I170" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J169" s="12" t="s">
+      <c r="J170" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K169" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L169" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M169" s="36"/>
-      <c r="N169" s="34">
+      <c r="K170" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L170" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M170" s="36"/>
+      <c r="N170" s="34">
         <v>760</v>
       </c>
-      <c r="O169" s="6" t="s">
-        <v>1236</v>
-      </c>
-      <c r="P169" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q169" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R169" s="12">
+      <c r="O170" s="6" t="s">
+        <v>1231</v>
+      </c>
+      <c r="P170" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q170" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R170" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>95000</v>
       </c>
-      <c r="S169" s="12">
+      <c r="S170" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>7916.666666666667</v>
       </c>
-      <c r="T169" s="12">
+      <c r="T170" s="12">
         <v>125</v>
       </c>
-      <c r="U169" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V169" s="6">
+      <c r="U170" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V170" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>3800</v>
       </c>
-      <c r="W169" s="12">
+      <c r="W170" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>316.66666666666669</v>
       </c>
-      <c r="X169" s="12">
+      <c r="X170" s="12">
         <v>5</v>
       </c>
-      <c r="Y169" s="12">
+      <c r="Y170" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>17480</v>
       </c>
-      <c r="Z169" s="12">
+      <c r="Z170" s="12">
         <v>23</v>
       </c>
-      <c r="AA169" s="12">
+      <c r="AA170" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB169" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC169" s="12">
+      <c r="AB170" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC170" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>116280</v>
       </c>
-      <c r="AD169" s="12" t="str">
+      <c r="AD170" s="12" t="str">
         <f t="shared" si="6"/>
         <v>3 mois = 23 750 €</v>
       </c>
-      <c r="AE169" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF169" s="46">
+      <c r="AE170" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF170" s="46">
         <v>0.05</v>
       </c>
-      <c r="AG169" s="12" t="s">
+      <c r="AG170" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AH169" s="10" t="s">
+      <c r="AH170" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="AI169" s="10" t="s">
+      <c r="AI170" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="AJ169" s="10" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AK169" s="11" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AL169" s="5" t="s">
+      <c r="AJ170" s="10" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AK170" s="11" t="s">
+        <v>1232</v>
+      </c>
+      <c r="AL170" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM169" s="11" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AN169" s="11" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AO169" s="11">
+      <c r="AM170" s="11" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AN170" s="11" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AO170" s="11">
         <v>44</v>
       </c>
-      <c r="AP169" s="36" t="s">
-        <v>1261</v>
-      </c>
-      <c r="AQ169" s="11" t="s">
+      <c r="AP170" s="36" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AQ170" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR169" s="11" t="s">
-        <v>1235</v>
-      </c>
-      <c r="AS169" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT169" s="14"/>
-      <c r="AU169" s="44">
+      <c r="AR170" s="11" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AS170" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT170" s="14"/>
+      <c r="AU170" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="170" spans="1:47" ht="38.25">
-      <c r="A170" s="38" t="str">
+    <row r="171" spans="1:47" ht="38.25">
+      <c r="A171" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
       </c>
-      <c r="B170" s="38" t="str">
+      <c r="B171" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
         <v>Var</v>
       </c>
-      <c r="C170" s="38">
+      <c r="C171" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>83</v>
       </c>
-      <c r="D170" s="10" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E170" s="26">
+      <c r="D171" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E171" s="26">
         <v>83160</v>
       </c>
-      <c r="F170" s="10" t="s">
-        <v>1118</v>
-      </c>
-      <c r="G170" s="39" t="str">
+      <c r="F171" s="10" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G171" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>23 Avenue des Frères Lumière
 83160 - La Valette-du-Var</v>
       </c>
-      <c r="H170" s="15" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I170" s="12" t="s">
+      <c r="H171" s="15" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I171" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J170" s="12" t="s">
+      <c r="J171" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K170" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L170" s="12"/>
-      <c r="M170" s="36"/>
-      <c r="N170" s="34">
+      <c r="K171" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L171" s="12"/>
+      <c r="M171" s="36"/>
+      <c r="N171" s="34">
         <v>276</v>
       </c>
-      <c r="O170" s="6" t="s">
-        <v>1238</v>
-      </c>
-      <c r="P170" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q170" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R170" s="12">
+      <c r="O171" s="6" t="s">
+        <v>1233</v>
+      </c>
+      <c r="P171" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q171" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R171" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>151800</v>
       </c>
-      <c r="S170" s="12">
+      <c r="S171" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>12650</v>
       </c>
-      <c r="T170" s="12">
+      <c r="T171" s="12">
         <v>550</v>
       </c>
-      <c r="U170" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V170" s="6">
+      <c r="U171" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V171" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>2760</v>
       </c>
-      <c r="W170" s="12">
+      <c r="W171" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>230</v>
       </c>
-      <c r="X170" s="12">
+      <c r="X171" s="12">
         <v>10</v>
       </c>
-      <c r="Y170" s="12">
+      <c r="Y171" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>6348</v>
       </c>
-      <c r="Z170" s="12">
+      <c r="Z171" s="12">
         <v>23</v>
       </c>
-      <c r="AA170" s="12">
+      <c r="AA171" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB170" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC170" s="12">
+      <c r="AB171" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC171" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>160908</v>
       </c>
-      <c r="AD170" s="12" t="str">
+      <c r="AD171" s="12" t="str">
         <f t="shared" si="6"/>
         <v>3 mois = 37 950 €</v>
       </c>
-      <c r="AE170" s="12" t="str">
-        <f t="shared" ref="AE170:AE176" si="7">"6 mois = "&amp;TEXT(ROUND(6/12*R170,0),"### ### ##0 €")</f>
+      <c r="AE171" s="12" t="str">
+        <f t="shared" ref="AE171:AE177" si="7">"6 mois = "&amp;TEXT(ROUND(6/12*R171,0),"### ### ##0 €")</f>
         <v>6 mois = 75 900 €</v>
       </c>
-      <c r="AF170" s="46">
+      <c r="AF171" s="46">
         <v>0.05</v>
       </c>
-      <c r="AG170" s="12" t="s">
+      <c r="AG171" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AH170" s="10" t="s">
+      <c r="AH171" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="AI170" s="10" t="s">
+      <c r="AI171" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="AJ170" s="10" t="s">
-        <v>1171</v>
-      </c>
-      <c r="AK170" s="11" t="s">
-        <v>1299</v>
-      </c>
-      <c r="AL170" s="5" t="s">
+      <c r="AJ171" s="10" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AK171" s="11" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AL171" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM170" s="11" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AN170" s="11" t="s">
-        <v>1170</v>
-      </c>
-      <c r="AO170" s="11" t="s">
-        <v>1142</v>
-      </c>
-      <c r="AP170" s="36" t="s">
-        <v>1262</v>
-      </c>
-      <c r="AQ170" s="11" t="s">
+      <c r="AM171" s="11" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AN171" s="11" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AO171" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AP171" s="36" t="s">
+        <v>1257</v>
+      </c>
+      <c r="AQ171" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR170" s="11" t="s">
-        <v>1273</v>
-      </c>
-      <c r="AS170" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT170" s="14"/>
-      <c r="AU170" s="44">
+      <c r="AR171" s="11" t="s">
+        <v>1268</v>
+      </c>
+      <c r="AS171" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT171" s="14"/>
+      <c r="AU171" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="171" spans="1:47" ht="25.5">
-      <c r="A171" s="38" t="str">
+    <row r="172" spans="1:47" ht="25.5">
+      <c r="A172" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
       </c>
-      <c r="B171" s="38" t="str">
+      <c r="B172" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
         <v>Var</v>
       </c>
-      <c r="C171" s="38">
+      <c r="C172" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>83</v>
       </c>
-      <c r="D171" s="10" t="s">
-        <v>1239</v>
-      </c>
-      <c r="E171" s="26">
+      <c r="D172" s="10" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E172" s="26">
         <v>83160</v>
       </c>
-      <c r="F171" s="10" t="s">
-        <v>1118</v>
-      </c>
-      <c r="G171" s="39" t="str">
+      <c r="F172" s="10" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G172" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>83 Avenue de l'Université
 83160 - La Valette-du-Var</v>
       </c>
-      <c r="H171" s="15" t="s">
-        <v>1114</v>
-      </c>
-      <c r="I171" s="12" t="s">
+      <c r="H172" s="15" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I172" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J171" s="12" t="s">
+      <c r="J172" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K171" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L171" s="12">
+      <c r="K172" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L172" s="12">
         <v>60000</v>
       </c>
-      <c r="M171" s="36"/>
-      <c r="N171" s="34">
+      <c r="M172" s="36"/>
+      <c r="N172" s="34">
         <v>470</v>
       </c>
-      <c r="O171" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P171" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q171" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R171" s="12">
+      <c r="O172" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P172" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q172" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R172" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>188000</v>
       </c>
-      <c r="S171" s="12">
+      <c r="S172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>15666.666666666666</v>
       </c>
-      <c r="T171" s="12">
+      <c r="T172" s="12">
         <v>400</v>
       </c>
-      <c r="U171" s="46">
+      <c r="U172" s="46">
         <v>0.08</v>
       </c>
-      <c r="V171" s="6">
+      <c r="V172" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>2350</v>
       </c>
-      <c r="W171" s="12">
+      <c r="W172" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>195.83333333333334</v>
       </c>
-      <c r="X171" s="12">
+      <c r="X172" s="12">
         <v>5</v>
       </c>
-      <c r="Y171" s="12">
+      <c r="Y172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>16450</v>
       </c>
-      <c r="Z171" s="12">
+      <c r="Z172" s="12">
         <v>35</v>
       </c>
-      <c r="AA171" s="12">
+      <c r="AA172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB171" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC171" s="12">
+      <c r="AB172" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC172" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>206800</v>
       </c>
-      <c r="AD171" s="12" t="str">
+      <c r="AD172" s="12" t="str">
         <f t="shared" si="6"/>
         <v>3 mois = 47 000 €</v>
       </c>
-      <c r="AE171" s="12" t="str">
+      <c r="AE172" s="12" t="str">
         <f t="shared" si="7"/>
         <v>6 mois = 94 000 €</v>
       </c>
-      <c r="AF171" s="46">
+      <c r="AF172" s="46">
         <v>0.05</v>
       </c>
-      <c r="AG171" s="12" t="s">
+      <c r="AG172" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AH171" s="10" t="s">
+      <c r="AH172" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="AI171" s="10" t="s">
+      <c r="AI172" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="AJ171" s="10" t="s">
-        <v>1172</v>
-      </c>
-      <c r="AK171" s="11" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AL171" s="5" t="s">
+      <c r="AJ172" s="10" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AK172" s="11" t="s">
+        <v>1236</v>
+      </c>
+      <c r="AL172" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM171" s="11" t="s">
-        <v>1173</v>
-      </c>
-      <c r="AN171" s="11" t="s">
-        <v>1174</v>
-      </c>
-      <c r="AO171" s="11" t="s">
+      <c r="AM172" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AN172" s="11" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO172" s="11" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AP172" s="36" t="s">
+        <v>1258</v>
+      </c>
+      <c r="AQ172" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR172" s="11" t="s">
+        <v>1235</v>
+      </c>
+      <c r="AS172" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AP171" s="36" t="s">
-        <v>1263</v>
-      </c>
-      <c r="AQ171" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR171" s="11" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AS171" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT171" s="14"/>
-      <c r="AU171" s="44">
+      <c r="AT172" s="14"/>
+      <c r="AU172" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="172" spans="1:47" ht="51">
-      <c r="A172" s="38" t="str">
+    <row r="173" spans="1:47" ht="51">
+      <c r="A173" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
       </c>
-      <c r="B172" s="38" t="str">
+      <c r="B173" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
         <v>Vaucluse</v>
       </c>
-      <c r="C172" s="38">
+      <c r="C173" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>84</v>
       </c>
-      <c r="D172" s="10" t="s">
-        <v>1120</v>
-      </c>
-      <c r="E172" s="26">
+      <c r="D173" s="10" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E173" s="26">
         <v>84140</v>
       </c>
-      <c r="F172" s="10" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G172" s="39" t="str">
+      <c r="F173" s="10" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G173" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>330 Avenue Marcou Delanglade
 84140 - Avignon</v>
       </c>
-      <c r="H172" s="15" t="s">
-        <v>1178</v>
-      </c>
-      <c r="I172" s="12" t="s">
+      <c r="H173" s="15" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I173" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J172" s="12" t="s">
+      <c r="J173" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K172" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L172" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M172" s="36"/>
-      <c r="N172" s="34">
+      <c r="K173" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L173" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M173" s="36"/>
+      <c r="N173" s="34">
         <v>616</v>
       </c>
-      <c r="O172" s="6" t="s">
-        <v>1243</v>
-      </c>
-      <c r="P172" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q172" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R172" s="12">
+      <c r="O173" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="P173" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q173" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R173" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>123200</v>
       </c>
-      <c r="S172" s="12">
+      <c r="S173" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>10266.666666666666</v>
       </c>
-      <c r="T172" s="12">
+      <c r="T173" s="12">
         <v>200</v>
       </c>
-      <c r="U172" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V172" s="6">
+      <c r="U173" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V173" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>11088</v>
       </c>
-      <c r="W172" s="12">
+      <c r="W173" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>924</v>
       </c>
-      <c r="X172" s="12">
+      <c r="X173" s="12">
         <v>18</v>
       </c>
-      <c r="Y172" s="12">
+      <c r="Y173" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>8624</v>
       </c>
-      <c r="Z172" s="12">
+      <c r="Z173" s="12">
         <v>14</v>
-      </c>
-      <c r="AA172" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB172" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC172" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>142912</v>
-      </c>
-      <c r="AD172" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>3 mois = 30 800 €</v>
-      </c>
-      <c r="AE172" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v>6 mois = 61 600 €</v>
-      </c>
-      <c r="AF172" s="46">
-        <v>0.05</v>
-      </c>
-      <c r="AG172" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="AH172" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI172" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="AJ172" s="10" t="s">
-        <v>1177</v>
-      </c>
-      <c r="AK172" s="11" t="s">
-        <v>1244</v>
-      </c>
-      <c r="AL172" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="AM172" s="11" t="s">
-        <v>1175</v>
-      </c>
-      <c r="AN172" s="11" t="s">
-        <v>1176</v>
-      </c>
-      <c r="AO172" s="11">
-        <v>46</v>
-      </c>
-      <c r="AP172" s="45" t="s">
-        <v>1264</v>
-      </c>
-      <c r="AQ172" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR172" s="11" t="s">
-        <v>1242</v>
-      </c>
-      <c r="AS172" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT172" s="14"/>
-      <c r="AU172" s="44">
-        <v>46003</v>
-      </c>
-    </row>
-    <row r="173" spans="1:47" ht="38.25">
-      <c r="A173" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
-      </c>
-      <c r="B173" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Val-de-Marne</v>
-      </c>
-      <c r="C173" s="38">
-        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>94</v>
-      </c>
-      <c r="D173" s="10" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E173" s="26">
-        <v>94500</v>
-      </c>
-      <c r="F173" s="10" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G173" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>14 Rue Serpente
-94500 - Champigny-sur-Marne</v>
-      </c>
-      <c r="H173" s="15" t="s">
-        <v>1117</v>
-      </c>
-      <c r="I173" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J173" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="K173" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L173" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M173" s="36"/>
-      <c r="N173" s="34">
-        <v>875</v>
-      </c>
-      <c r="O173" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P173" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q173" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R173" s="12">
-        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>196875</v>
-      </c>
-      <c r="S173" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>16406.25</v>
-      </c>
-      <c r="T173" s="12">
-        <v>225</v>
-      </c>
-      <c r="U173" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V173" s="6">
-        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>5250</v>
-      </c>
-      <c r="W173" s="12">
-        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>437.5</v>
-      </c>
-      <c r="X173" s="12">
-        <v>6</v>
-      </c>
-      <c r="Y173" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>11375</v>
-      </c>
-      <c r="Z173" s="12">
-        <v>13</v>
       </c>
       <c r="AA173" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
@@ -31766,15 +31827,15 @@
       </c>
       <c r="AC173" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>213500</v>
+        <v>142912</v>
       </c>
       <c r="AD173" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 49 219 €</v>
+        <v>3 mois = 30 800 €</v>
       </c>
       <c r="AE173" s="12" t="str">
         <f t="shared" si="7"/>
-        <v>6 mois = 98 438 €</v>
+        <v>6 mois = 61 600 €</v>
       </c>
       <c r="AF173" s="46">
         <v>0.05</v>
@@ -31783,40 +31844,40 @@
         <v>363</v>
       </c>
       <c r="AH173" s="10" t="s">
-        <v>377</v>
+        <v>75</v>
       </c>
       <c r="AI173" s="10" t="s">
         <v>370</v>
       </c>
       <c r="AJ173" s="10" t="s">
-        <v>1183</v>
+        <v>1172</v>
       </c>
       <c r="AK173" s="11" t="s">
-        <v>1250</v>
+        <v>1239</v>
       </c>
       <c r="AL173" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM173" s="11" t="s">
-        <v>1179</v>
+        <v>1170</v>
       </c>
       <c r="AN173" s="11" t="s">
-        <v>1180</v>
-      </c>
-      <c r="AO173" s="11" t="s">
-        <v>1143</v>
+        <v>1171</v>
+      </c>
+      <c r="AO173" s="11">
+        <v>46</v>
       </c>
       <c r="AP173" s="45" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="AQ173" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR173" s="11" t="s">
-        <v>1274</v>
+        <v>1237</v>
       </c>
       <c r="AS173" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT173" s="14"/>
       <c r="AU173" s="44">
@@ -31837,21 +31898,21 @@
         <v>94</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="E174" s="26">
         <v>94500</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G174" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>13 Rue Serpente
+        <v>14 Rue Serpente
 94500 - Champigny-sur-Marne</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="I174" s="12" t="s">
         <v>45</v>
@@ -31867,7 +31928,7 @@
       </c>
       <c r="M174" s="36"/>
       <c r="N174" s="34">
-        <v>387</v>
+        <v>875</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>103</v>
@@ -31880,35 +31941,35 @@
       </c>
       <c r="R174" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>96750</v>
+        <v>196875</v>
       </c>
       <c r="S174" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>8062.5</v>
+        <v>16406.25</v>
       </c>
       <c r="T174" s="12">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U174" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V174" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>2322</v>
+        <v>5250</v>
       </c>
       <c r="W174" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>193.5</v>
+        <v>437.5</v>
       </c>
       <c r="X174" s="12">
         <v>6</v>
       </c>
       <c r="Y174" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>5418</v>
+        <v>11375</v>
       </c>
       <c r="Z174" s="12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA174" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
@@ -31919,15 +31980,15 @@
       </c>
       <c r="AC174" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>104490</v>
+        <v>213500</v>
       </c>
       <c r="AD174" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 24 188 €</v>
+        <v>3 mois = 49 219 €</v>
       </c>
       <c r="AE174" s="12" t="str">
         <f t="shared" si="7"/>
-        <v>6 mois = 48 375 €</v>
+        <v>6 mois = 98 438 €</v>
       </c>
       <c r="AF174" s="46">
         <v>0.05</v>
@@ -31942,34 +32003,34 @@
         <v>370</v>
       </c>
       <c r="AJ174" s="10" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="AK174" s="11" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="AL174" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM174" s="11" t="s">
-        <v>1246</v>
+        <v>1174</v>
       </c>
       <c r="AN174" s="11" t="s">
-        <v>1247</v>
+        <v>1175</v>
       </c>
       <c r="AO174" s="11" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AP174" s="36" t="s">
-        <v>1266</v>
+        <v>1138</v>
+      </c>
+      <c r="AP174" s="45" t="s">
+        <v>1260</v>
       </c>
       <c r="AQ174" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR174" s="11" t="s">
-        <v>1245</v>
+        <v>1269</v>
       </c>
       <c r="AS174" s="13" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="AT174" s="14"/>
       <c r="AU174" s="44">
@@ -31990,532 +32051,539 @@
         <v>94</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="E175" s="26">
         <v>94500</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G175" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>13 Rue Serpente
+94500 - Champigny-sur-Marne</v>
+      </c>
+      <c r="H175" s="15" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J175" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K175" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L175" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M175" s="36"/>
+      <c r="N175" s="34">
+        <v>387</v>
+      </c>
+      <c r="O175" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P175" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q175" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R175" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>96750</v>
+      </c>
+      <c r="S175" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>8062.5</v>
+      </c>
+      <c r="T175" s="12">
+        <v>250</v>
+      </c>
+      <c r="U175" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V175" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2322</v>
+      </c>
+      <c r="W175" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>193.5</v>
+      </c>
+      <c r="X175" s="12">
+        <v>6</v>
+      </c>
+      <c r="Y175" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>5418</v>
+      </c>
+      <c r="Z175" s="12">
+        <v>14</v>
+      </c>
+      <c r="AA175" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB175" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC175" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>104490</v>
+      </c>
+      <c r="AD175" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 24 188 €</v>
+      </c>
+      <c r="AE175" s="12" t="str">
+        <f t="shared" si="7"/>
+        <v>6 mois = 48 375 €</v>
+      </c>
+      <c r="AF175" s="46">
+        <v>0.05</v>
+      </c>
+      <c r="AG175" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH175" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI175" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ175" s="10" t="s">
+        <v>1178</v>
+      </c>
+      <c r="AK175" s="11" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AL175" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM175" s="11" t="s">
+        <v>1241</v>
+      </c>
+      <c r="AN175" s="11" t="s">
+        <v>1242</v>
+      </c>
+      <c r="AO175" s="11" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AP175" s="36" t="s">
+        <v>1261</v>
+      </c>
+      <c r="AQ175" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR175" s="11" t="s">
+        <v>1240</v>
+      </c>
+      <c r="AS175" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT175" s="14"/>
+      <c r="AU175" s="44">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="176" spans="1:47" ht="38.25">
+      <c r="A176" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B176" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C176" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E176" s="26">
+        <v>94500</v>
+      </c>
+      <c r="F176" s="10" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G176" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>14 Rue Serpente
 94500 - Champigny-sur-Marne</v>
       </c>
-      <c r="H175" s="15" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I175" s="12" t="s">
+      <c r="H176" s="15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I176" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J175" s="12" t="s">
+      <c r="J176" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K175" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L175" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M175" s="36"/>
-      <c r="N175" s="34">
+      <c r="K176" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L176" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M176" s="36"/>
+      <c r="N176" s="34">
         <v>723</v>
       </c>
-      <c r="O175" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P175" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q175" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R175" s="12">
+      <c r="O176" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P176" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q176" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R176" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>162675</v>
       </c>
-      <c r="S175" s="12">
+      <c r="S176" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>13556.25</v>
       </c>
-      <c r="T175" s="12">
+      <c r="T176" s="12">
         <v>225</v>
       </c>
-      <c r="U175" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V175" s="6">
+      <c r="U176" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V176" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>4338</v>
       </c>
-      <c r="W175" s="12">
+      <c r="W176" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>361.5</v>
       </c>
-      <c r="X175" s="12">
+      <c r="X176" s="12">
         <v>6</v>
       </c>
-      <c r="Y175" s="12">
+      <c r="Y176" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>9399</v>
       </c>
-      <c r="Z175" s="12">
+      <c r="Z176" s="12">
         <v>13</v>
       </c>
-      <c r="AA175" s="12">
+      <c r="AA176" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB175" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC175" s="12">
+      <c r="AB176" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC176" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>176412</v>
       </c>
-      <c r="AD175" s="12" t="str">
+      <c r="AD176" s="12" t="str">
         <f t="shared" si="6"/>
         <v>3 mois = 40 669 €</v>
       </c>
-      <c r="AE175" s="12" t="str">
+      <c r="AE176" s="12" t="str">
         <f t="shared" si="7"/>
         <v>6 mois = 81 338 €</v>
       </c>
-      <c r="AF175" s="46">
+      <c r="AF176" s="46">
         <v>0.05</v>
       </c>
-      <c r="AG175" s="12" t="s">
+      <c r="AG176" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AH175" s="10" t="s">
+      <c r="AH176" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="AI175" s="10" t="s">
+      <c r="AI176" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="AJ175" s="10" t="s">
-        <v>1183</v>
-      </c>
-      <c r="AK175" s="11" t="s">
-        <v>1250</v>
-      </c>
-      <c r="AL175" s="5" t="s">
+      <c r="AJ176" s="10" t="s">
+        <v>1178</v>
+      </c>
+      <c r="AK176" s="11" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AL176" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM175" s="11" t="s">
-        <v>1181</v>
-      </c>
-      <c r="AN175" s="11" t="s">
-        <v>1182</v>
-      </c>
-      <c r="AO175" s="11" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AP175" s="36" t="s">
-        <v>1267</v>
-      </c>
-      <c r="AQ175" s="11" t="s">
+      <c r="AM176" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="AN176" s="11" t="s">
+        <v>1177</v>
+      </c>
+      <c r="AO176" s="11" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AP176" s="36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="AQ176" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR175" s="11" t="s">
-        <v>1248</v>
-      </c>
-      <c r="AS175" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT175" s="14"/>
-      <c r="AU175" s="44">
+      <c r="AR176" s="11" t="s">
+        <v>1243</v>
+      </c>
+      <c r="AS176" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT176" s="14"/>
+      <c r="AU176" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="176" spans="1:47" ht="25.5">
-      <c r="A176" s="38" t="str">
+    <row r="177" spans="1:47" ht="25.5">
+      <c r="A177" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
       </c>
-      <c r="B176" s="38" t="str">
+      <c r="B177" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
         <v>Val-D'Oise</v>
       </c>
-      <c r="C176" s="38">
+      <c r="C177" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>95</v>
       </c>
-      <c r="D176" s="10" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E176" s="26">
+      <c r="D177" s="10" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E177" s="26">
         <v>95220</v>
       </c>
-      <c r="F176" s="10" t="s">
-        <v>1124</v>
-      </c>
-      <c r="G176" s="39" t="str">
+      <c r="F177" s="10" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G177" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>8 Avenue Paul Langevin
 95220 - Herblay-sur-Seine</v>
       </c>
-      <c r="H176" s="15" t="s">
-        <v>1184</v>
-      </c>
-      <c r="I176" s="12" t="s">
+      <c r="H177" s="15" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I177" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J176" s="12" t="s">
+      <c r="J177" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K176" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L176" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M176" s="36"/>
-      <c r="N176" s="34">
+      <c r="K177" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L177" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M177" s="36"/>
+      <c r="N177" s="34">
         <v>402</v>
       </c>
-      <c r="O176" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P176" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q176" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R176" s="12">
+      <c r="O177" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P177" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q177" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R177" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>180900</v>
       </c>
-      <c r="S176" s="12">
+      <c r="S177" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>15075</v>
       </c>
-      <c r="T176" s="12">
+      <c r="T177" s="12">
         <v>450</v>
       </c>
-      <c r="U176" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V176" s="6">
+      <c r="U177" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V177" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>3618</v>
       </c>
-      <c r="W176" s="12">
+      <c r="W177" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>301.5</v>
       </c>
-      <c r="X176" s="12">
+      <c r="X177" s="12">
         <v>9</v>
       </c>
-      <c r="Y176" s="12">
+      <c r="Y177" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>5226</v>
       </c>
-      <c r="Z176" s="12">
+      <c r="Z177" s="12">
         <v>13</v>
       </c>
-      <c r="AA176" s="12">
+      <c r="AA177" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB176" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC176" s="12">
+      <c r="AB177" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC177" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>189744</v>
       </c>
-      <c r="AD176" s="12" t="str">
+      <c r="AD177" s="12" t="str">
         <f t="shared" si="6"/>
         <v>3 mois = 45 225 €</v>
       </c>
-      <c r="AE176" s="12" t="str">
+      <c r="AE177" s="12" t="str">
         <f t="shared" si="7"/>
         <v>6 mois = 90 450 €</v>
       </c>
-      <c r="AF176" s="46">
+      <c r="AF177" s="46">
         <v>0.05</v>
       </c>
-      <c r="AG176" s="12" t="s">
+      <c r="AG177" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AH176" s="10" t="s">
+      <c r="AH177" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="AI176" s="10" t="s">
+      <c r="AI177" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="AJ176" s="10" t="s">
-        <v>1187</v>
-      </c>
-      <c r="AK176" s="11" t="s">
-        <v>1251</v>
-      </c>
-      <c r="AL176" s="5" t="s">
+      <c r="AJ177" s="10" t="s">
+        <v>1182</v>
+      </c>
+      <c r="AK177" s="11" t="s">
+        <v>1246</v>
+      </c>
+      <c r="AL177" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM176" s="11" t="s">
-        <v>1185</v>
-      </c>
-      <c r="AN176" s="11" t="s">
-        <v>1186</v>
-      </c>
-      <c r="AO176" s="11">
+      <c r="AM177" s="11" t="s">
+        <v>1180</v>
+      </c>
+      <c r="AN177" s="11" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AO177" s="11">
         <v>48</v>
       </c>
-      <c r="AP176" s="36" t="s">
-        <v>1268</v>
-      </c>
-      <c r="AQ176" s="11" t="s">
+      <c r="AP177" s="36" t="s">
+        <v>1263</v>
+      </c>
+      <c r="AQ177" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR176" s="11" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AS176" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AT176" s="14"/>
-      <c r="AU176" s="44">
+      <c r="AR177" s="11" t="s">
+        <v>1244</v>
+      </c>
+      <c r="AS177" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AT177" s="14"/>
+      <c r="AU177" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="177" spans="1:47" ht="38.25">
-      <c r="A177" s="38" t="str">
+    <row r="178" spans="1:47" ht="38.25">
+      <c r="A178" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
       </c>
-      <c r="B177" s="38" t="str">
+      <c r="B178" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
         <v>Alpes-Maritimes</v>
       </c>
-      <c r="C177" s="38">
+      <c r="C178" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>6</v>
       </c>
-      <c r="D177" s="11" t="s">
-        <v>1193</v>
-      </c>
-      <c r="E177" s="48" t="s">
-        <v>1393</v>
-      </c>
-      <c r="F177" s="10" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G177" s="47" t="str">
+      <c r="D178" s="11" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E178" s="48" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F178" s="10" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G178" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>CAP 3000
 217 Av. Eugène Donadeï
 06 700 - Saint-Laurent-du-Var</v>
       </c>
-      <c r="H177" s="15" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I177" s="12" t="s">
+      <c r="H178" s="15" t="s">
+        <v>1189</v>
+      </c>
+      <c r="I178" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J177" s="12" t="s">
+      <c r="J178" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K177" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L177" s="12" t="s">
-        <v>1195</v>
-      </c>
-      <c r="M177" s="36"/>
-      <c r="N177" s="34">
+      <c r="K178" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L178" s="12" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M178" s="36"/>
+      <c r="N178" s="34">
         <v>126</v>
       </c>
-      <c r="O177" s="6" t="s">
-        <v>1252</v>
-      </c>
-      <c r="P177" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q177" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R177" s="12">
+      <c r="O178" s="6" t="s">
+        <v>1247</v>
+      </c>
+      <c r="P178" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q178" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R178" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>139986</v>
       </c>
-      <c r="S177" s="12">
+      <c r="S178" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>11665.5</v>
       </c>
-      <c r="T177" s="12">
+      <c r="T178" s="12">
         <v>1111</v>
       </c>
-      <c r="U177" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V177" s="6">
+      <c r="U178" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V178" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>20790</v>
       </c>
-      <c r="W177" s="12">
+      <c r="W178" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>1732.5</v>
       </c>
-      <c r="X177" s="12">
+      <c r="X178" s="12">
         <v>165</v>
       </c>
-      <c r="Y177" s="12">
+      <c r="Y178" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>4536</v>
       </c>
-      <c r="Z177" s="12">
+      <c r="Z178" s="12">
         <v>36</v>
       </c>
-      <c r="AA177" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB177" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC177" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>165312</v>
-      </c>
-      <c r="AD177" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>3 mois = 34 997 €</v>
-      </c>
-      <c r="AE177" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF177" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG177" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="AH177" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI177" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ177" s="10" t="s">
-        <v>1197</v>
-      </c>
-      <c r="AK177" s="11" t="s">
-        <v>1196</v>
-      </c>
-      <c r="AL177" s="5" t="s">
-        <v>1201</v>
-      </c>
-      <c r="AM177" s="11" t="s">
-        <v>1198</v>
-      </c>
-      <c r="AN177" s="11" t="s">
-        <v>1199</v>
-      </c>
-      <c r="AO177" s="11">
-        <v>49</v>
-      </c>
-      <c r="AP177" s="36" t="s">
-        <v>1269</v>
-      </c>
-      <c r="AQ177" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR177" s="11"/>
-      <c r="AS177" s="13" t="s">
-        <v>1200</v>
-      </c>
-      <c r="AT177" s="14"/>
-      <c r="AU177" s="44">
-        <v>46010</v>
-      </c>
-    </row>
-    <row r="178" spans="1:47" ht="25.5">
-      <c r="A178" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
-      </c>
-      <c r="B178" s="38" t="str">
-        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Seine-et-Marne</v>
-      </c>
-      <c r="C178" s="38">
-        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>77</v>
-      </c>
-      <c r="D178" s="10" t="s">
-        <v>1312</v>
-      </c>
-      <c r="E178" s="26">
-        <v>77000</v>
-      </c>
-      <c r="F178" s="10" t="s">
-        <v>1313</v>
-      </c>
-      <c r="G178" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>23 avenue Paul Doumer
-77000 - Melun</v>
-      </c>
-      <c r="H178" s="15" t="s">
-        <v>1314</v>
-      </c>
-      <c r="I178" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J178" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="K178" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L178" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M178" s="36"/>
-      <c r="N178" s="34">
-        <v>530</v>
-      </c>
-      <c r="O178" s="12" t="s">
-        <v>1315</v>
-      </c>
-      <c r="P178" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q178" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R178" s="12">
-        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>132500</v>
-      </c>
-      <c r="S178" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>11041.666666666666</v>
-      </c>
-      <c r="T178" s="12">
-        <v>250</v>
-      </c>
-      <c r="U178" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V178" s="6">
-        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
-      </c>
-      <c r="W178" s="12">
-        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="X178" s="12"/>
-      <c r="Y178" s="12">
-        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="Z178" s="12"/>
       <c r="AA178" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -32525,11 +32593,11 @@
       </c>
       <c r="AC178" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>132500</v>
+        <v>165312</v>
       </c>
       <c r="AD178" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 33 125 €</v>
+        <v>3 mois = 34 997 €</v>
       </c>
       <c r="AE178" s="6" t="s">
         <v>103</v>
@@ -32541,42 +32609,42 @@
         <v>363</v>
       </c>
       <c r="AH178" s="10" t="s">
-        <v>377</v>
+        <v>53</v>
       </c>
       <c r="AI178" s="10" t="s">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="AJ178" s="10" t="s">
-        <v>1317</v>
+        <v>1192</v>
       </c>
       <c r="AK178" s="11" t="s">
-        <v>1316</v>
+        <v>1191</v>
       </c>
       <c r="AL178" s="5" t="s">
-        <v>368</v>
+        <v>1196</v>
       </c>
       <c r="AM178" s="11" t="s">
-        <v>1318</v>
+        <v>1193</v>
       </c>
       <c r="AN178" s="11" t="s">
-        <v>1319</v>
+        <v>1194</v>
       </c>
       <c r="AO178" s="11">
-        <v>50</v>
-      </c>
-      <c r="AP178" s="36"/>
+        <v>49</v>
+      </c>
+      <c r="AP178" s="36" t="s">
+        <v>1264</v>
+      </c>
       <c r="AQ178" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR178" s="11" t="s">
-        <v>1320</v>
-      </c>
+      <c r="AR178" s="11"/>
       <c r="AS178" s="13" t="s">
-        <v>1321</v>
+        <v>1195</v>
       </c>
       <c r="AT178" s="14"/>
       <c r="AU178" s="44">
-        <v>46042</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="179" spans="1:47" ht="25.5">
@@ -32586,28 +32654,28 @@
       </c>
       <c r="B179" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Paris</v>
+        <v>Seine-et-Marne</v>
       </c>
       <c r="C179" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1322</v>
+        <v>1307</v>
       </c>
       <c r="E179" s="26">
-        <v>75016</v>
+        <v>77000</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>92</v>
+        <v>1308</v>
       </c>
       <c r="G179" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>1 boulevard Exelmans
-75016 - Paris</v>
+        <v>23 avenue Paul Doumer
+77000 - Melun</v>
       </c>
       <c r="H179" s="15" t="s">
-        <v>1323</v>
+        <v>1309</v>
       </c>
       <c r="I179" s="12" t="s">
         <v>45</v>
@@ -32623,10 +32691,10 @@
       </c>
       <c r="M179" s="36"/>
       <c r="N179" s="34">
-        <v>187</v>
+        <v>530</v>
       </c>
       <c r="O179" s="12" t="s">
-        <v>1324</v>
+        <v>1310</v>
       </c>
       <c r="P179" s="34" t="s">
         <v>103</v>
@@ -32636,14 +32704,14 @@
       </c>
       <c r="R179" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>112200</v>
+        <v>132500</v>
       </c>
       <c r="S179" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>9350</v>
+        <v>11041.666666666666</v>
       </c>
       <c r="T179" s="12">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="U179" s="6" t="s">
         <v>103</v>
@@ -32671,11 +32739,11 @@
       </c>
       <c r="AC179" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>112200</v>
+        <v>132500</v>
       </c>
       <c r="AD179" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 28 050 €</v>
+        <v>3 mois = 33 125 €</v>
       </c>
       <c r="AE179" s="6" t="s">
         <v>103</v>
@@ -32693,35 +32761,37 @@
         <v>370</v>
       </c>
       <c r="AJ179" s="10" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
       <c r="AK179" s="11" t="s">
-        <v>1382</v>
+        <v>1311</v>
       </c>
       <c r="AL179" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM179" s="11" t="s">
-        <v>1326</v>
+        <v>1313</v>
       </c>
       <c r="AN179" s="11" t="s">
-        <v>1327</v>
+        <v>1314</v>
       </c>
       <c r="AO179" s="11">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AP179" s="36"/>
       <c r="AQ179" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR179" s="11" t="s">
-        <v>1325</v>
+        <v>1315</v>
       </c>
       <c r="AS179" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT179" s="14"/>
-      <c r="AU179" s="44"/>
+      <c r="AU179" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="180" spans="1:47" ht="25.5">
       <c r="A180" s="38" t="str">
@@ -32737,21 +32807,21 @@
         <v>75</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>1329</v>
+        <v>1317</v>
       </c>
       <c r="E180" s="26">
-        <v>75014</v>
+        <v>75016</v>
       </c>
       <c r="F180" s="10" t="s">
         <v>92</v>
       </c>
       <c r="G180" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>90 rue d'Alésia
-75014 - Paris</v>
+        <v>1 boulevard Exelmans
+75016 - Paris</v>
       </c>
       <c r="H180" s="15" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="I180" s="12" t="s">
         <v>45</v>
@@ -32767,10 +32837,10 @@
       </c>
       <c r="M180" s="36"/>
       <c r="N180" s="34">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="O180" s="12" t="s">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="P180" s="34" t="s">
         <v>103</v>
@@ -32780,14 +32850,14 @@
       </c>
       <c r="R180" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>53100</v>
+        <v>112200</v>
       </c>
       <c r="S180" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>4425</v>
+        <v>9350</v>
       </c>
       <c r="T180" s="12">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="U180" s="6" t="s">
         <v>103</v>
@@ -32815,11 +32885,11 @@
       </c>
       <c r="AC180" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>53100</v>
+        <v>112200</v>
       </c>
       <c r="AD180" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 13 275 €</v>
+        <v>3 mois = 28 050 €</v>
       </c>
       <c r="AE180" s="6" t="s">
         <v>103</v>
@@ -32833,37 +32903,41 @@
       <c r="AH180" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="AI180" s="10"/>
+      <c r="AI180" s="10" t="s">
+        <v>370</v>
+      </c>
       <c r="AJ180" s="10" t="s">
-        <v>1335</v>
+        <v>1323</v>
       </c>
       <c r="AK180" s="11" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="AL180" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM180" s="11" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
       <c r="AN180" s="11" t="s">
-        <v>1334</v>
+        <v>1322</v>
       </c>
       <c r="AO180" s="11">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AP180" s="36"/>
       <c r="AQ180" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR180" s="11" t="s">
-        <v>1332</v>
+        <v>1320</v>
       </c>
       <c r="AS180" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT180" s="14"/>
-      <c r="AU180" s="44"/>
+      <c r="AU180" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="181" spans="1:47" ht="25.5">
       <c r="A181" s="38" t="str">
@@ -32879,21 +32953,21 @@
         <v>75</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>1336</v>
+        <v>1324</v>
       </c>
       <c r="E181" s="26">
-        <v>75020</v>
+        <v>75014</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>92</v>
       </c>
       <c r="G181" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>356 rue des Pyrénées
-75020 - Paris</v>
+        <v>90 rue d'Alésia
+75014 - Paris</v>
       </c>
       <c r="H181" s="15" t="s">
-        <v>1337</v>
+        <v>1325</v>
       </c>
       <c r="I181" s="12" t="s">
         <v>45</v>
@@ -32909,29 +32983,29 @@
       </c>
       <c r="M181" s="36"/>
       <c r="N181" s="34">
-        <v>39</v>
-      </c>
-      <c r="O181" s="34" t="s">
-        <v>103</v>
+        <v>59</v>
+      </c>
+      <c r="O181" s="12" t="s">
+        <v>1326</v>
       </c>
       <c r="P181" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="Q181" s="34" t="s">
+      <c r="Q181" s="6" t="s">
         <v>103</v>
       </c>
       <c r="R181" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>42900</v>
+        <v>53100</v>
       </c>
       <c r="S181" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>3575</v>
+        <v>4425</v>
       </c>
       <c r="T181" s="12">
-        <v>1100</v>
-      </c>
-      <c r="U181" s="34" t="s">
+        <v>900</v>
+      </c>
+      <c r="U181" s="6" t="s">
         <v>103</v>
       </c>
       <c r="V181" s="6">
@@ -32952,16 +33026,16 @@
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AB181" s="34" t="s">
+      <c r="AB181" s="6" t="s">
         <v>103</v>
       </c>
       <c r="AC181" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>42900</v>
+        <v>53100</v>
       </c>
       <c r="AD181" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 10 725 €</v>
+        <v>3 mois = 13 275 €</v>
       </c>
       <c r="AE181" s="6" t="s">
         <v>103</v>
@@ -32977,33 +33051,37 @@
       </c>
       <c r="AI181" s="10"/>
       <c r="AJ181" s="10" t="s">
-        <v>1341</v>
-      </c>
-      <c r="AK181" s="11"/>
+        <v>1330</v>
+      </c>
+      <c r="AK181" s="11" t="s">
+        <v>1378</v>
+      </c>
       <c r="AL181" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM181" s="11" t="s">
-        <v>1340</v>
+        <v>1328</v>
       </c>
       <c r="AN181" s="11" t="s">
-        <v>1339</v>
+        <v>1329</v>
       </c>
       <c r="AO181" s="11">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AP181" s="36"/>
       <c r="AQ181" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR181" s="11" t="s">
-        <v>1338</v>
+        <v>1327</v>
       </c>
       <c r="AS181" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT181" s="14"/>
-      <c r="AU181" s="44"/>
+      <c r="AU181" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="182" spans="1:47" ht="25.5">
       <c r="A182" s="38" t="str">
@@ -33019,21 +33097,21 @@
         <v>75</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>1342</v>
+        <v>1331</v>
       </c>
       <c r="E182" s="26">
-        <v>75017</v>
+        <v>75020</v>
       </c>
       <c r="F182" s="10" t="s">
         <v>92</v>
       </c>
       <c r="G182" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>103 rue Legendre
-75017 - Paris</v>
+        <v>356 rue des Pyrénées
+75020 - Paris</v>
       </c>
       <c r="H182" s="15" t="s">
-        <v>1343</v>
+        <v>1332</v>
       </c>
       <c r="I182" s="12" t="s">
         <v>45</v>
@@ -33049,7 +33127,7 @@
       </c>
       <c r="M182" s="36"/>
       <c r="N182" s="34">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="O182" s="34" t="s">
         <v>103</v>
@@ -33062,14 +33140,14 @@
       </c>
       <c r="R182" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>74400</v>
+        <v>42900</v>
       </c>
       <c r="S182" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>6200</v>
+        <v>3575</v>
       </c>
       <c r="T182" s="12">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="U182" s="34" t="s">
         <v>103</v>
@@ -33097,11 +33175,11 @@
       </c>
       <c r="AC182" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>74400</v>
+        <v>42900</v>
       </c>
       <c r="AD182" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 18 600 €</v>
+        <v>3 mois = 10 725 €</v>
       </c>
       <c r="AE182" s="6" t="s">
         <v>103</v>
@@ -33117,35 +33195,35 @@
       </c>
       <c r="AI182" s="10"/>
       <c r="AJ182" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="AK182" s="11" t="s">
-        <v>1345</v>
-      </c>
+        <v>1336</v>
+      </c>
+      <c r="AK182" s="11"/>
       <c r="AL182" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM182" s="11" t="s">
-        <v>1367</v>
+        <v>1335</v>
       </c>
       <c r="AN182" s="11" t="s">
-        <v>1368</v>
+        <v>1334</v>
       </c>
       <c r="AO182" s="11">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AP182" s="36"/>
       <c r="AQ182" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR182" s="11" t="s">
-        <v>1344</v>
+        <v>1333</v>
       </c>
       <c r="AS182" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT182" s="14"/>
-      <c r="AU182" s="44"/>
+      <c r="AU182" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="183" spans="1:47" ht="25.5">
       <c r="A183" s="38" t="str">
@@ -33154,28 +33232,28 @@
       </c>
       <c r="B183" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Hauts-de-Seine</v>
+        <v>Paris</v>
       </c>
       <c r="C183" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>75</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E183" s="26">
+        <v>75017</v>
+      </c>
+      <c r="F183" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D183" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E183" s="26">
-        <v>92100</v>
-      </c>
-      <c r="F183" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="G183" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>86 avenue Edouard Vaillant
-92100 - Boulogne-Billancourt</v>
+        <v>103 rue Legendre
+75017 - Paris</v>
       </c>
       <c r="H183" s="15" t="s">
-        <v>1348</v>
+        <v>1338</v>
       </c>
       <c r="I183" s="12" t="s">
         <v>45</v>
@@ -33191,10 +33269,10 @@
       </c>
       <c r="M183" s="36"/>
       <c r="N183" s="34">
-        <v>141</v>
-      </c>
-      <c r="O183" s="12" t="s">
-        <v>1354</v>
+        <v>93</v>
+      </c>
+      <c r="O183" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="P183" s="34" t="s">
         <v>103</v>
@@ -33204,11 +33282,11 @@
       </c>
       <c r="R183" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>112800</v>
+        <v>74400</v>
       </c>
       <c r="S183" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>9400</v>
+        <v>6200</v>
       </c>
       <c r="T183" s="12">
         <v>800</v>
@@ -33239,11 +33317,11 @@
       </c>
       <c r="AC183" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>112800</v>
+        <v>74400</v>
       </c>
       <c r="AD183" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 28 200 €</v>
+        <v>3 mois = 18 600 €</v>
       </c>
       <c r="AE183" s="6" t="s">
         <v>103</v>
@@ -33255,71 +33333,71 @@
         <v>363</v>
       </c>
       <c r="AH183" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI183" s="10" t="s">
-        <v>369</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AI183" s="10"/>
       <c r="AJ183" s="10" t="s">
-        <v>1387</v>
+        <v>1341</v>
       </c>
       <c r="AK183" s="11" t="s">
-        <v>1386</v>
+        <v>1340</v>
       </c>
       <c r="AL183" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM183" s="11" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="AN183" s="11" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="AO183" s="11">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AP183" s="36"/>
       <c r="AQ183" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR183" s="11" t="s">
-        <v>1349</v>
+        <v>1339</v>
       </c>
       <c r="AS183" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT183" s="14"/>
-      <c r="AU183" s="44"/>
+      <c r="AU183" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="184" spans="1:47" ht="25.5">
       <c r="A184" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Hauts-de-France</v>
+        <v>Ile-de-France</v>
       </c>
       <c r="B184" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Pas-de-Calais</v>
+        <v>Hauts-de-Seine</v>
       </c>
       <c r="C184" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>1351</v>
+        <v>1342</v>
       </c>
       <c r="E184" s="26">
-        <v>62520</v>
+        <v>92100</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>1352</v>
+        <v>93</v>
       </c>
       <c r="G184" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>73 bis rue Saint-Jean
-62520 - Le Touquet-Paris-Plage</v>
+        <v>86 avenue Edouard Vaillant
+92100 - Boulogne-Billancourt</v>
       </c>
       <c r="H184" s="15" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
       <c r="I184" s="12" t="s">
         <v>45</v>
@@ -33335,10 +33413,10 @@
       </c>
       <c r="M184" s="36"/>
       <c r="N184" s="34">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="O184" s="12" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="P184" s="34" t="s">
         <v>103</v>
@@ -33348,14 +33426,14 @@
       </c>
       <c r="R184" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>60200</v>
+        <v>112800</v>
       </c>
       <c r="S184" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>5016.666666666667</v>
+        <v>9400</v>
       </c>
       <c r="T184" s="12">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="U184" s="34" t="s">
         <v>103</v>
@@ -33383,11 +33461,11 @@
       </c>
       <c r="AC184" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>60200</v>
+        <v>112800</v>
       </c>
       <c r="AD184" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 15 050 €</v>
+        <v>3 mois = 28 200 €</v>
       </c>
       <c r="AE184" s="6" t="s">
         <v>103</v>
@@ -33399,71 +33477,73 @@
         <v>363</v>
       </c>
       <c r="AH184" s="10" t="s">
-        <v>377</v>
+        <v>53</v>
       </c>
       <c r="AI184" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AJ184" s="10" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
       <c r="AK184" s="11" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="AL184" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM184" s="11" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="AN184" s="11" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="AO184" s="11">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AP184" s="36"/>
       <c r="AQ184" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR184" s="11" t="s">
-        <v>1355</v>
+        <v>1344</v>
       </c>
       <c r="AS184" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT184" s="14"/>
-      <c r="AU184" s="44"/>
+      <c r="AU184" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="185" spans="1:47" ht="25.5">
       <c r="A185" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Bourgogne-Franche-Comté</v>
+        <v>Hauts-de-France</v>
       </c>
       <c r="B185" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Côte-d'Or</v>
+        <v>Pas-de-Calais</v>
       </c>
       <c r="C185" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>1358</v>
+        <v>1346</v>
       </c>
       <c r="E185" s="26">
-        <v>21000</v>
+        <v>62520</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>1359</v>
+        <v>1347</v>
       </c>
       <c r="G185" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>65 rue du Bourg
-21000 - Dijon</v>
+        <v>73 bis rue Saint-Jean
+62520 - Le Touquet-Paris-Plage</v>
       </c>
       <c r="H185" s="15" t="s">
-        <v>1360</v>
+        <v>1345</v>
       </c>
       <c r="I185" s="12" t="s">
         <v>45</v>
@@ -33479,10 +33559,10 @@
       </c>
       <c r="M185" s="36"/>
       <c r="N185" s="34">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="O185" s="12" t="s">
-        <v>1361</v>
+        <v>1348</v>
       </c>
       <c r="P185" s="34" t="s">
         <v>103</v>
@@ -33492,14 +33572,14 @@
       </c>
       <c r="R185" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>134000</v>
+        <v>60200</v>
       </c>
       <c r="S185" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>11166.666666666666</v>
+        <v>5016.666666666667</v>
       </c>
       <c r="T185" s="12">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="U185" s="34" t="s">
         <v>103</v>
@@ -33527,11 +33607,11 @@
       </c>
       <c r="AC185" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>134000</v>
+        <v>60200</v>
       </c>
       <c r="AD185" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 33 500 €</v>
+        <v>3 mois = 15 050 €</v>
       </c>
       <c r="AE185" s="6" t="s">
         <v>103</v>
@@ -33549,65 +33629,67 @@
         <v>370</v>
       </c>
       <c r="AJ185" s="10" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
       <c r="AK185" s="11" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="AL185" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM185" s="11" t="s">
-        <v>1364</v>
+        <v>1351</v>
       </c>
       <c r="AN185" s="11" t="s">
-        <v>1363</v>
+        <v>1352</v>
       </c>
       <c r="AO185" s="11">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AP185" s="36"/>
       <c r="AQ185" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR185" s="11" t="s">
-        <v>1362</v>
+        <v>1350</v>
       </c>
       <c r="AS185" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT185" s="14"/>
-      <c r="AU185" s="44"/>
+      <c r="AU185" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="186" spans="1:47" ht="25.5">
       <c r="A186" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Bourgogne-Franche-Comté</v>
       </c>
       <c r="B186" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Aube</v>
+        <v>Côte-d'Or</v>
       </c>
       <c r="C186" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>1369</v>
+        <v>1353</v>
       </c>
       <c r="E186" s="26">
-        <v>10000</v>
+        <v>21000</v>
       </c>
       <c r="F186" s="10" t="s">
-        <v>1370</v>
+        <v>1354</v>
       </c>
       <c r="G186" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>97 rue Emile Zola
-10000 - Troyes</v>
+        <v>65 rue du Bourg
+21000 - Dijon</v>
       </c>
       <c r="H186" s="15" t="s">
-        <v>1371</v>
+        <v>1355</v>
       </c>
       <c r="I186" s="12" t="s">
         <v>45</v>
@@ -33623,10 +33705,10 @@
       </c>
       <c r="M186" s="36"/>
       <c r="N186" s="34">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="O186" s="12" t="s">
-        <v>1372</v>
+        <v>1356</v>
       </c>
       <c r="P186" s="34" t="s">
         <v>103</v>
@@ -33636,14 +33718,14 @@
       </c>
       <c r="R186" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>113400</v>
+        <v>134000</v>
       </c>
       <c r="S186" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>9450</v>
+        <v>11166.666666666666</v>
       </c>
       <c r="T186" s="12">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U186" s="34" t="s">
         <v>103</v>
@@ -33671,11 +33753,11 @@
       </c>
       <c r="AC186" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>113400</v>
+        <v>134000</v>
       </c>
       <c r="AD186" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 28 350 €</v>
+        <v>3 mois = 33 500 €</v>
       </c>
       <c r="AE186" s="6" t="s">
         <v>103</v>
@@ -33693,65 +33775,67 @@
         <v>370</v>
       </c>
       <c r="AJ186" s="10" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="AK186" s="11" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="AL186" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM186" s="11" t="s">
-        <v>1374</v>
+        <v>1359</v>
       </c>
       <c r="AN186" s="11" t="s">
-        <v>1375</v>
+        <v>1358</v>
       </c>
       <c r="AO186" s="11">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AP186" s="36"/>
       <c r="AQ186" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR186" s="11" t="s">
-        <v>1373</v>
+        <v>1357</v>
       </c>
       <c r="AS186" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT186" s="14"/>
-      <c r="AU186" s="44"/>
+      <c r="AU186" s="44">
+        <v>46042</v>
+      </c>
     </row>
     <row r="187" spans="1:47" ht="25.5">
       <c r="A187" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Ile-de-France</v>
+        <v>Grand Est</v>
       </c>
       <c r="B187" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Paris</v>
+        <v>Aube</v>
       </c>
       <c r="C187" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D187" s="10" t="s">
-        <v>1376</v>
+        <v>1364</v>
       </c>
       <c r="E187" s="26">
-        <v>75001</v>
+        <v>10000</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>92</v>
+        <v>1365</v>
       </c>
       <c r="G187" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>9 Rue du Marché Saint-Honoré
-75001 - Paris</v>
+        <v>97 rue Emile Zola
+10000 - Troyes</v>
       </c>
       <c r="H187" s="15" t="s">
-        <v>1377</v>
+        <v>1366</v>
       </c>
       <c r="I187" s="12" t="s">
         <v>45</v>
@@ -33767,10 +33851,10 @@
       </c>
       <c r="M187" s="36"/>
       <c r="N187" s="34">
-        <v>48</v>
+        <v>378</v>
       </c>
       <c r="O187" s="12" t="s">
-        <v>1378</v>
+        <v>1367</v>
       </c>
       <c r="P187" s="34" t="s">
         <v>103</v>
@@ -33780,14 +33864,14 @@
       </c>
       <c r="R187" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>134400</v>
+        <v>113400</v>
       </c>
       <c r="S187" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>11200</v>
+        <v>9450</v>
       </c>
       <c r="T187" s="12">
-        <v>2800</v>
+        <v>300</v>
       </c>
       <c r="U187" s="34" t="s">
         <v>103</v>
@@ -33815,11 +33899,11 @@
       </c>
       <c r="AC187" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>134400</v>
+        <v>113400</v>
       </c>
       <c r="AD187" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>3 mois = 33 600 €</v>
+        <v>3 mois = 28 350 €</v>
       </c>
       <c r="AE187" s="6" t="s">
         <v>103</v>
@@ -33831,196 +33915,346 @@
         <v>363</v>
       </c>
       <c r="AH187" s="10" t="s">
-        <v>53</v>
+        <v>377</v>
       </c>
       <c r="AI187" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ187" s="10" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="AK187" s="11" t="s">
-        <v>1392</v>
+        <v>1379</v>
       </c>
       <c r="AL187" s="5" t="s">
         <v>368</v>
       </c>
       <c r="AM187" s="11" t="s">
-        <v>1380</v>
+        <v>1369</v>
       </c>
       <c r="AN187" s="11" t="s">
-        <v>1381</v>
+        <v>1370</v>
       </c>
       <c r="AO187" s="11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AP187" s="36"/>
       <c r="AQ187" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AR187" s="11" t="s">
-        <v>1379</v>
+        <v>1368</v>
       </c>
       <c r="AS187" s="13" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="AT187" s="14"/>
-      <c r="AU187" s="44"/>
+      <c r="AU187" s="44">
+        <v>46042</v>
+      </c>
     </row>
-    <row r="188" spans="1:47" ht="38.25">
+    <row r="188" spans="1:47" ht="25.5">
       <c r="A188" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Auvergne-Rhône-Alpes</v>
+        <v>Ile-de-France</v>
       </c>
       <c r="B188" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Ain</v>
+        <v>Paris</v>
       </c>
       <c r="C188" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>75</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E188" s="26">
+        <v>75001</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G188" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>9 Rue du Marché Saint-Honoré
+75001 - Paris</v>
+      </c>
+      <c r="H188" s="15" t="s">
+        <v>1372</v>
+      </c>
+      <c r="I188" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J188" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K188" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L188" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M188" s="36"/>
+      <c r="N188" s="34">
+        <v>48</v>
+      </c>
+      <c r="O188" s="12" t="s">
+        <v>1373</v>
+      </c>
+      <c r="P188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R188" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>134400</v>
+      </c>
+      <c r="S188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>11200</v>
+      </c>
+      <c r="T188" s="12">
+        <v>2800</v>
+      </c>
+      <c r="U188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V188" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="W188" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="X188" s="12"/>
+      <c r="Y188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="Z188" s="12"/>
+      <c r="AA188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC188" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>134400</v>
+      </c>
+      <c r="AD188" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>3 mois = 33 600 €</v>
+      </c>
+      <c r="AE188" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF188" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG188" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH188" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI188" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AJ188" s="10" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AK188" s="11" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AL188" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM188" s="11" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AN188" s="11" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AO188" s="11">
+        <v>59</v>
+      </c>
+      <c r="AP188" s="36"/>
+      <c r="AQ188" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR188" s="11" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AS188" s="13" t="s">
+        <v>1316</v>
+      </c>
+      <c r="AT188" s="14"/>
+      <c r="AU188" s="44">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="189" spans="1:47" ht="38.25">
+      <c r="A189" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B189" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Ain</v>
+      </c>
+      <c r="C189" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>1</v>
       </c>
-      <c r="D188" s="11" t="s">
-        <v>1397</v>
-      </c>
-      <c r="E188" s="49" t="s">
-        <v>1395</v>
-      </c>
-      <c r="F188" s="10" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G188" s="39" t="str">
+      <c r="D189" s="11" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E189" s="49" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G189" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;Tableau1[[#This Row],[Code Postal]]&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Cap Émeraude
 Avenue du Capitaine Dhonne01 000Bourg-en-Bresse</v>
       </c>
-      <c r="H188" s="15" t="s">
-        <v>1394</v>
-      </c>
-      <c r="I188" s="12" t="s">
+      <c r="H189" s="15" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I189" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J188" s="12" t="s">
+      <c r="J189" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K188" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L188" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M188" s="36"/>
-      <c r="N188" s="34">
+      <c r="K189" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L189" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M189" s="36"/>
+      <c r="N189" s="34">
         <v>196</v>
       </c>
-      <c r="O188" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="P188" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q188" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="R188" s="12">
+      <c r="O189" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="P189" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q189" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R189" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>113680</v>
       </c>
-      <c r="S188" s="12">
+      <c r="S189" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
         <v>9473.3333333333339</v>
       </c>
-      <c r="T188" s="12">
+      <c r="T189" s="12">
         <v>580</v>
       </c>
-      <c r="U188" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="V188" s="6">
+      <c r="U189" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V189" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>11172</v>
       </c>
-      <c r="W188" s="12">
+      <c r="W189" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>931</v>
       </c>
-      <c r="X188" s="12">
+      <c r="X189" s="12">
         <v>57</v>
       </c>
-      <c r="Y188" s="12">
+      <c r="Y189" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>6468</v>
       </c>
-      <c r="Z188" s="12">
+      <c r="Z189" s="12">
         <v>33</v>
       </c>
-      <c r="AA188" s="12">
+      <c r="AA189" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>3920</v>
       </c>
-      <c r="AB188" s="12">
+      <c r="AB189" s="12">
         <v>20</v>
       </c>
-      <c r="AC188" s="12">
+      <c r="AC189" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
         <v>135240</v>
       </c>
-      <c r="AD188" s="12" t="str">
+      <c r="AD189" s="12" t="str">
         <f t="shared" si="6"/>
         <v>3 mois = 28 420 €</v>
       </c>
-      <c r="AE188" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF188" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG188" s="12" t="s">
+      <c r="AE189" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF189" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG189" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AH188" s="10"/>
-      <c r="AI188" s="10"/>
-      <c r="AJ188" s="10" t="s">
-        <v>1401</v>
-      </c>
-      <c r="AK188" s="11" t="s">
-        <v>1400</v>
-      </c>
-      <c r="AL188" s="5" t="s">
+      <c r="AH189" s="10"/>
+      <c r="AI189" s="10"/>
+      <c r="AJ189" s="10" t="s">
+        <v>1396</v>
+      </c>
+      <c r="AK189" s="11" t="s">
+        <v>1395</v>
+      </c>
+      <c r="AL189" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM188" s="11" t="s">
+      <c r="AM189" s="11" t="s">
+        <v>1393</v>
+      </c>
+      <c r="AN189" s="11" t="s">
+        <v>1394</v>
+      </c>
+      <c r="AO189" s="11">
+        <v>60</v>
+      </c>
+      <c r="AP189" s="36" t="s">
         <v>1398</v>
       </c>
-      <c r="AN188" s="11" t="s">
-        <v>1399</v>
-      </c>
-      <c r="AO188" s="11">
-        <v>60</v>
-      </c>
-      <c r="AP188" s="36" t="s">
-        <v>1402</v>
-      </c>
-      <c r="AQ188" s="11" t="s">
+      <c r="AQ189" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR188" s="11" t="s">
+      <c r="AR189" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS188" s="13" t="s">
-        <v>1403</v>
-      </c>
-      <c r="AT188" s="14"/>
-      <c r="AU188" s="44"/>
-    </row>
-    <row r="203" spans="6:6">
-      <c r="F203" s="1" t="s">
-        <v>1034</v>
+      <c r="AS189" s="13" t="s">
+        <v>1397</v>
+      </c>
+      <c r="AT189" s="14"/>
+      <c r="AU189" s="44">
+        <v>46042</v>
       </c>
     </row>
     <row r="204" spans="6:6">
       <c r="F204" s="1" t="s">
-        <v>1035</v>
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="205" spans="6:6">
+      <c r="F205" s="1" t="s">
+        <v>1031</v>
       </c>
     </row>
   </sheetData>
@@ -34114,7 +34348,7 @@
     <hyperlink ref="H120" r:id="rId86" xr:uid="{B7CDE0FD-8A09-4174-932D-FE6101C452B5}"/>
     <hyperlink ref="H121" r:id="rId87" xr:uid="{6971848A-A988-4DBF-9D23-FFFD48C1E6CD}"/>
     <hyperlink ref="H138" r:id="rId88" xr:uid="{080B1A9F-E5F0-49E3-97CD-6FCCA68308F4}"/>
-    <hyperlink ref="H139" r:id="rId89" xr:uid="{60277B5C-FF5B-46B3-BBF6-66AFD5E516D1}"/>
+    <hyperlink ref="H140" r:id="rId89" xr:uid="{60277B5C-FF5B-46B3-BBF6-66AFD5E516D1}"/>
     <hyperlink ref="H122" r:id="rId90" xr:uid="{62405CFE-5DA9-4596-886C-3ACF426D9309}"/>
     <hyperlink ref="H123" r:id="rId91" xr:uid="{B587046D-852F-4EB8-948D-F8411549618B}"/>
     <hyperlink ref="H125" r:id="rId92" xr:uid="{399D402E-7B20-4D08-860B-714F86DCE34E}"/>
@@ -34131,50 +34365,51 @@
     <hyperlink ref="H132" r:id="rId103" xr:uid="{DBAA1B38-C94A-4F88-A4D2-2B9015202629}"/>
     <hyperlink ref="H134" r:id="rId104" xr:uid="{CAD15A8F-0FDF-468F-841D-5DB3005468A0}"/>
     <hyperlink ref="H136" r:id="rId105" xr:uid="{56259A3A-CABA-4CC7-8994-C525611F5A2A}"/>
-    <hyperlink ref="H140" r:id="rId106" xr:uid="{54D9C84A-9E79-4E6C-94AD-0B1E658B9727}"/>
-    <hyperlink ref="H141" r:id="rId107" xr:uid="{03D798D2-CCD2-4F77-BE5B-6E2A2FE47845}"/>
-    <hyperlink ref="H143" r:id="rId108" xr:uid="{0816FF13-6441-462C-A055-21680CDF255C}"/>
-    <hyperlink ref="H142" r:id="rId109" xr:uid="{01C599EF-C1DF-4C31-ADC2-E79CCD9D3420}"/>
-    <hyperlink ref="H144" r:id="rId110" xr:uid="{48DF072A-5724-4516-9EB9-B2B092F9ECBF}"/>
-    <hyperlink ref="H145" r:id="rId111" xr:uid="{2D52890D-990D-499F-92B9-790A6B56B2C1}"/>
-    <hyperlink ref="H146" r:id="rId112" xr:uid="{D89787FE-D414-4ADC-AC02-C8B9D2520919}"/>
-    <hyperlink ref="H147" r:id="rId113" xr:uid="{83F81C45-2D7B-4019-9457-DB12A08DE525}"/>
-    <hyperlink ref="H148" r:id="rId114" xr:uid="{5DD490B2-A51A-488D-BCDE-B83932141509}"/>
-    <hyperlink ref="H149" r:id="rId115" xr:uid="{8FDF2590-E1B8-4CE8-9753-7BFB747102D3}"/>
-    <hyperlink ref="H150" r:id="rId116" xr:uid="{F9E1A7BC-0810-451D-AAC4-F0BE420D1B9F}"/>
-    <hyperlink ref="H151" r:id="rId117" xr:uid="{6B38E304-7485-42E7-9EFC-3CDA0B79C692}"/>
-    <hyperlink ref="H152" r:id="rId118" xr:uid="{9BAD643D-2774-4811-AF7F-3253EB54E8FC}"/>
-    <hyperlink ref="H153" r:id="rId119" xr:uid="{8C4EE05C-7B50-4EF6-B2F7-FACAB92DA663}"/>
-    <hyperlink ref="H157" r:id="rId120" xr:uid="{0D1E98E9-4BCF-4406-AFDA-600010FB176B}"/>
-    <hyperlink ref="H158" r:id="rId121" xr:uid="{580F9DBE-E800-4F84-BEDC-E8B38FD61F7A}"/>
-    <hyperlink ref="H159" r:id="rId122" xr:uid="{372123E9-8C5B-4111-8443-C1645E86AD4D}"/>
-    <hyperlink ref="H160" r:id="rId123" xr:uid="{CC20D8BA-62C0-4205-8CD5-E236C90A7669}"/>
-    <hyperlink ref="H167" r:id="rId124" xr:uid="{D9CEB66C-2A2B-4C50-90E4-25DDB2866B82}"/>
-    <hyperlink ref="H168" r:id="rId125" xr:uid="{77194CDF-321B-4F1D-8892-C65AB2918B74}"/>
-    <hyperlink ref="H169" r:id="rId126" xr:uid="{A510C509-E61B-4228-AC93-D0093532C7D2}"/>
-    <hyperlink ref="H170" r:id="rId127" xr:uid="{13D66F57-470F-41F4-93A6-03D5A2A4CCDB}"/>
-    <hyperlink ref="H171" r:id="rId128" xr:uid="{5B7EA501-9646-45C8-A6A4-6075F4FADE70}"/>
-    <hyperlink ref="H172" r:id="rId129" xr:uid="{6D822EC9-F492-4D93-A1BA-8FA65E1327B7}"/>
-    <hyperlink ref="H174" r:id="rId130" xr:uid="{3C8BCE0A-AAD1-4E3F-915C-B7BFA9B07703}"/>
-    <hyperlink ref="H175" r:id="rId131" xr:uid="{EB1761D0-DA2C-4FCB-8A87-DC3BF56A199A}"/>
-    <hyperlink ref="H173" r:id="rId132" xr:uid="{AC7B9731-155A-409D-B7DE-6A2C81027D18}"/>
-    <hyperlink ref="H176" r:id="rId133" xr:uid="{ED7C6A33-7CA0-4B59-BFC3-713467DF5837}"/>
-    <hyperlink ref="H154" r:id="rId134" xr:uid="{84DBA056-5C11-4ECE-9D32-78D0DE5AACCA}"/>
-    <hyperlink ref="H155" r:id="rId135" xr:uid="{3F6F7192-2423-4CFD-AC54-5D69482DCDAA}"/>
-    <hyperlink ref="H156" r:id="rId136" xr:uid="{34F05E83-B67A-4D2E-97A2-715EF4DB16F0}"/>
-    <hyperlink ref="H177" r:id="rId137" xr:uid="{0DCDD234-61DD-4535-96A0-1CB0ED1C39E2}"/>
-    <hyperlink ref="H161" r:id="rId138" xr:uid="{69AC0ECC-2E2A-4A8B-BC81-EF4428A37640}"/>
-    <hyperlink ref="H162:H166" r:id="rId139" display="https://maps.app.goo.gl/jjHUN2H4tKUGyBEQ7" xr:uid="{2DDA41A9-46D6-46F1-BFA4-95D30FE59882}"/>
-    <hyperlink ref="H178" r:id="rId140" xr:uid="{F6366A42-B67C-40CD-AFBC-6C8424BEB013}"/>
-    <hyperlink ref="H180" r:id="rId141" xr:uid="{AC4BD242-08DC-4A93-AF73-32CF15E14420}"/>
-    <hyperlink ref="H181" r:id="rId142" xr:uid="{3FEF2131-529B-4B74-9649-3B4B1CFC2613}"/>
-    <hyperlink ref="H182" r:id="rId143" xr:uid="{3F02EB48-A165-461F-8BAF-AC050FE23690}"/>
-    <hyperlink ref="H183" r:id="rId144" xr:uid="{145A22A7-33A1-43C0-A440-9E0FD9BB1AD1}"/>
-    <hyperlink ref="H184" r:id="rId145" xr:uid="{A5000FCA-4DF3-47B7-97D9-DAAC213C360B}"/>
-    <hyperlink ref="H185" r:id="rId146" xr:uid="{9FF463BE-AA91-4BC5-AE7D-4936D1C6D265}"/>
-    <hyperlink ref="H186" r:id="rId147" xr:uid="{EED7450E-F5F5-483A-B269-54C932486E0F}"/>
-    <hyperlink ref="H187" r:id="rId148" xr:uid="{B52E97C0-A3E5-471B-BD01-7BEB96586BB6}"/>
-    <hyperlink ref="H188" r:id="rId149" xr:uid="{6D139DEB-1BCB-45F1-9FA5-40A114985687}"/>
+    <hyperlink ref="H141" r:id="rId106" xr:uid="{54D9C84A-9E79-4E6C-94AD-0B1E658B9727}"/>
+    <hyperlink ref="H142" r:id="rId107" xr:uid="{03D798D2-CCD2-4F77-BE5B-6E2A2FE47845}"/>
+    <hyperlink ref="H144" r:id="rId108" xr:uid="{0816FF13-6441-462C-A055-21680CDF255C}"/>
+    <hyperlink ref="H143" r:id="rId109" xr:uid="{01C599EF-C1DF-4C31-ADC2-E79CCD9D3420}"/>
+    <hyperlink ref="H145" r:id="rId110" xr:uid="{48DF072A-5724-4516-9EB9-B2B092F9ECBF}"/>
+    <hyperlink ref="H146" r:id="rId111" xr:uid="{2D52890D-990D-499F-92B9-790A6B56B2C1}"/>
+    <hyperlink ref="H147" r:id="rId112" xr:uid="{D89787FE-D414-4ADC-AC02-C8B9D2520919}"/>
+    <hyperlink ref="H148" r:id="rId113" xr:uid="{83F81C45-2D7B-4019-9457-DB12A08DE525}"/>
+    <hyperlink ref="H149" r:id="rId114" xr:uid="{5DD490B2-A51A-488D-BCDE-B83932141509}"/>
+    <hyperlink ref="H150" r:id="rId115" xr:uid="{8FDF2590-E1B8-4CE8-9753-7BFB747102D3}"/>
+    <hyperlink ref="H151" r:id="rId116" xr:uid="{F9E1A7BC-0810-451D-AAC4-F0BE420D1B9F}"/>
+    <hyperlink ref="H152" r:id="rId117" xr:uid="{6B38E304-7485-42E7-9EFC-3CDA0B79C692}"/>
+    <hyperlink ref="H153" r:id="rId118" xr:uid="{9BAD643D-2774-4811-AF7F-3253EB54E8FC}"/>
+    <hyperlink ref="H154" r:id="rId119" xr:uid="{8C4EE05C-7B50-4EF6-B2F7-FACAB92DA663}"/>
+    <hyperlink ref="H158" r:id="rId120" xr:uid="{0D1E98E9-4BCF-4406-AFDA-600010FB176B}"/>
+    <hyperlink ref="H159" r:id="rId121" xr:uid="{580F9DBE-E800-4F84-BEDC-E8B38FD61F7A}"/>
+    <hyperlink ref="H160" r:id="rId122" xr:uid="{372123E9-8C5B-4111-8443-C1645E86AD4D}"/>
+    <hyperlink ref="H161" r:id="rId123" xr:uid="{CC20D8BA-62C0-4205-8CD5-E236C90A7669}"/>
+    <hyperlink ref="H168" r:id="rId124" xr:uid="{D9CEB66C-2A2B-4C50-90E4-25DDB2866B82}"/>
+    <hyperlink ref="H169" r:id="rId125" xr:uid="{77194CDF-321B-4F1D-8892-C65AB2918B74}"/>
+    <hyperlink ref="H170" r:id="rId126" xr:uid="{A510C509-E61B-4228-AC93-D0093532C7D2}"/>
+    <hyperlink ref="H171" r:id="rId127" xr:uid="{13D66F57-470F-41F4-93A6-03D5A2A4CCDB}"/>
+    <hyperlink ref="H172" r:id="rId128" xr:uid="{5B7EA501-9646-45C8-A6A4-6075F4FADE70}"/>
+    <hyperlink ref="H173" r:id="rId129" xr:uid="{6D822EC9-F492-4D93-A1BA-8FA65E1327B7}"/>
+    <hyperlink ref="H175" r:id="rId130" xr:uid="{3C8BCE0A-AAD1-4E3F-915C-B7BFA9B07703}"/>
+    <hyperlink ref="H176" r:id="rId131" xr:uid="{EB1761D0-DA2C-4FCB-8A87-DC3BF56A199A}"/>
+    <hyperlink ref="H174" r:id="rId132" xr:uid="{AC7B9731-155A-409D-B7DE-6A2C81027D18}"/>
+    <hyperlink ref="H177" r:id="rId133" xr:uid="{ED7C6A33-7CA0-4B59-BFC3-713467DF5837}"/>
+    <hyperlink ref="H155" r:id="rId134" xr:uid="{84DBA056-5C11-4ECE-9D32-78D0DE5AACCA}"/>
+    <hyperlink ref="H156" r:id="rId135" xr:uid="{3F6F7192-2423-4CFD-AC54-5D69482DCDAA}"/>
+    <hyperlink ref="H157" r:id="rId136" xr:uid="{34F05E83-B67A-4D2E-97A2-715EF4DB16F0}"/>
+    <hyperlink ref="H178" r:id="rId137" xr:uid="{0DCDD234-61DD-4535-96A0-1CB0ED1C39E2}"/>
+    <hyperlink ref="H162" r:id="rId138" xr:uid="{69AC0ECC-2E2A-4A8B-BC81-EF4428A37640}"/>
+    <hyperlink ref="H163:H167" r:id="rId139" display="https://maps.app.goo.gl/jjHUN2H4tKUGyBEQ7" xr:uid="{2DDA41A9-46D6-46F1-BFA4-95D30FE59882}"/>
+    <hyperlink ref="H179" r:id="rId140" xr:uid="{F6366A42-B67C-40CD-AFBC-6C8424BEB013}"/>
+    <hyperlink ref="H181" r:id="rId141" xr:uid="{AC4BD242-08DC-4A93-AF73-32CF15E14420}"/>
+    <hyperlink ref="H182" r:id="rId142" xr:uid="{3FEF2131-529B-4B74-9649-3B4B1CFC2613}"/>
+    <hyperlink ref="H183" r:id="rId143" xr:uid="{3F02EB48-A165-461F-8BAF-AC050FE23690}"/>
+    <hyperlink ref="H184" r:id="rId144" xr:uid="{145A22A7-33A1-43C0-A440-9E0FD9BB1AD1}"/>
+    <hyperlink ref="H185" r:id="rId145" xr:uid="{A5000FCA-4DF3-47B7-97D9-DAAC213C360B}"/>
+    <hyperlink ref="H186" r:id="rId146" xr:uid="{9FF463BE-AA91-4BC5-AE7D-4936D1C6D265}"/>
+    <hyperlink ref="H187" r:id="rId147" xr:uid="{EED7450E-F5F5-483A-B269-54C932486E0F}"/>
+    <hyperlink ref="H188" r:id="rId148" xr:uid="{B52E97C0-A3E5-471B-BD01-7BEB96586BB6}"/>
+    <hyperlink ref="H189" r:id="rId149" xr:uid="{6D139DEB-1BCB-45F1-9FA5-40A114985687}"/>
+    <hyperlink ref="H139" r:id="rId150" xr:uid="{069CCB02-48CE-4D86-8BBE-DFAEAC941704}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -34183,7 +34418,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId150"/>
+    <tablePart r:id="rId151"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1CA2A9-8711-4DB2-830F-1B1728B2872E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CEC251-BB05-4697-B78C-FA27B6BD2875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5509" uniqueCount="1414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5519" uniqueCount="1424">
   <si>
     <t>Contact</t>
   </si>
@@ -4289,6 +4289,36 @@
   </si>
   <si>
     <t>150 €/m² = 94 200 €</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/50%20-%20Melun/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/50%20-%20Melun/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/50%20-%20Melun/3.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/51%20-%20Paris%20Exelmans/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/51%20-%20Paris%20Exelmans/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/51%20-%20Paris%20Exelmans/3.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/52%20-%20Paris%20Al%C3%A9sia/1.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/53%20-%20Paris%20Pyr%C3%A9n%C3%A9es/1.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/54%20-%20Paris%20Legendre/1.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/55%20-%20Boulogne-Billancourt/1.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/56%20-%20Le%20Touquet-Paris-Plage/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/56%20-%20Le%20Touquet-Paris-Plage/2.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/57%20-%20Dijon/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/57%20-%20Dijon/2.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/58%20-%20Troyes/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/58%20-%20Troyes/2.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/59%20-%20Paris%20March%C3%A9%20St-Honor%C3%A9/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/59%20-%20Paris%20March%C3%A9%20St-Honor%C3%A9/2.jpg</t>
   </si>
 </sst>
 </file>
@@ -32778,7 +32808,9 @@
       <c r="AO179" s="11">
         <v>50</v>
       </c>
-      <c r="AP179" s="36"/>
+      <c r="AP179" s="36" t="s">
+        <v>1414</v>
+      </c>
       <c r="AQ179" s="11" t="s">
         <v>75</v>
       </c>
@@ -32924,7 +32956,9 @@
       <c r="AO180" s="11">
         <v>51</v>
       </c>
-      <c r="AP180" s="36"/>
+      <c r="AP180" s="36" t="s">
+        <v>1415</v>
+      </c>
       <c r="AQ180" s="11" t="s">
         <v>75</v>
       </c>
@@ -33068,7 +33102,9 @@
       <c r="AO181" s="11">
         <v>52</v>
       </c>
-      <c r="AP181" s="36"/>
+      <c r="AP181" s="36" t="s">
+        <v>1416</v>
+      </c>
       <c r="AQ181" s="11" t="s">
         <v>75</v>
       </c>
@@ -33210,7 +33246,9 @@
       <c r="AO182" s="11">
         <v>53</v>
       </c>
-      <c r="AP182" s="36"/>
+      <c r="AP182" s="36" t="s">
+        <v>1417</v>
+      </c>
       <c r="AQ182" s="11" t="s">
         <v>75</v>
       </c>
@@ -33354,7 +33392,9 @@
       <c r="AO183" s="11">
         <v>54</v>
       </c>
-      <c r="AP183" s="36"/>
+      <c r="AP183" s="36" t="s">
+        <v>1418</v>
+      </c>
       <c r="AQ183" s="11" t="s">
         <v>75</v>
       </c>
@@ -33500,7 +33540,9 @@
       <c r="AO184" s="11">
         <v>55</v>
       </c>
-      <c r="AP184" s="36"/>
+      <c r="AP184" s="36" t="s">
+        <v>1419</v>
+      </c>
       <c r="AQ184" s="11" t="s">
         <v>75</v>
       </c>
@@ -33646,7 +33688,9 @@
       <c r="AO185" s="11">
         <v>56</v>
       </c>
-      <c r="AP185" s="36"/>
+      <c r="AP185" s="36" t="s">
+        <v>1420</v>
+      </c>
       <c r="AQ185" s="11" t="s">
         <v>75</v>
       </c>
@@ -33792,7 +33836,9 @@
       <c r="AO186" s="11">
         <v>57</v>
       </c>
-      <c r="AP186" s="36"/>
+      <c r="AP186" s="36" t="s">
+        <v>1421</v>
+      </c>
       <c r="AQ186" s="11" t="s">
         <v>75</v>
       </c>
@@ -33938,7 +33984,9 @@
       <c r="AO187" s="11">
         <v>58</v>
       </c>
-      <c r="AP187" s="36"/>
+      <c r="AP187" s="36" t="s">
+        <v>1422</v>
+      </c>
       <c r="AQ187" s="11" t="s">
         <v>75</v>
       </c>
@@ -34084,7 +34132,9 @@
       <c r="AO188" s="11">
         <v>59</v>
       </c>
-      <c r="AP188" s="36"/>
+      <c r="AP188" s="36" t="s">
+        <v>1423</v>
+      </c>
       <c r="AQ188" s="11" t="s">
         <v>75</v>
       </c>
@@ -34410,6 +34460,7 @@
     <hyperlink ref="H188" r:id="rId148" xr:uid="{B52E97C0-A3E5-471B-BD01-7BEB96586BB6}"/>
     <hyperlink ref="H189" r:id="rId149" xr:uid="{6D139DEB-1BCB-45F1-9FA5-40A114985687}"/>
     <hyperlink ref="H139" r:id="rId150" xr:uid="{069CCB02-48CE-4D86-8BBE-DFAEAC941704}"/>
+    <hyperlink ref="H180" r:id="rId151" xr:uid="{3FF7903C-E5BA-4ED9-88DD-9F4AF755FB57}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -34418,7 +34469,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId151"/>
+    <tablePart r:id="rId152"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CEC251-BB05-4697-B78C-FA27B6BD2875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1C864F-E223-429F-867B-C53E5BDF5988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5519" uniqueCount="1424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5519" uniqueCount="1425">
   <si>
     <t>Contact</t>
   </si>
@@ -4319,6 +4319,9 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/59%20-%20Paris%20March%C3%A9%20St-Honor%C3%A9/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/59%20-%20Paris%20March%C3%A9%20St-Honor%C3%A9/2.jpg</t>
+  </si>
+  <si>
+    <t>Nature</t>
   </si>
 </sst>
 </file>
@@ -4953,7 +4956,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU189" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AU189" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+  <autoFilter ref="A1:AU189" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="/"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="47">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="46" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -4975,7 +4984,7 @@
     </tableColumn>
     <tableColumn id="15" xr3:uid="{172E07C4-0318-49AC-A621-9C0E3C5C5B5D}" name="Emplacement" dataDxfId="38" dataCellStyle="Normal 2"/>
     <tableColumn id="14" xr3:uid="{95EAECC7-A016-42C4-9C47-2CABFEAEC577}" name="Typologie" dataDxfId="37" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{8C8D77C7-8B55-471A-B479-215BC0D77604}" name="Type" dataDxfId="36" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{8C8D77C7-8B55-471A-B479-215BC0D77604}" name="Nature" dataDxfId="36" dataCellStyle="Normal 2"/>
     <tableColumn id="4" xr3:uid="{87D84239-5323-4A47-9424-F0CADB050723}" name="Cession / Droit au bail" dataDxfId="35" dataCellStyle="Normal 2"/>
     <tableColumn id="31" xr3:uid="{86770348-6586-45F2-A401-94B68504976F}" name="Numéro de lot" dataDxfId="34" dataCellStyle="Normal 2"/>
     <tableColumn id="1" xr3:uid="{3888DEAC-D743-4A06-B622-0805DADF7B24}" name="Surface GLA" dataDxfId="33" dataCellStyle="Normal 2"/>
@@ -5433,7 +5442,7 @@
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>6</v>
+        <v>1424</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>10</v>
@@ -26570,7 +26579,7 @@
         <v>92351</v>
       </c>
       <c r="AD138" s="12" t="str">
-        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R138,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AD138:AD143" si="5">"3 mois = "&amp;TEXT(ROUND(3/12*R138,0),"### ### ##0 €")</f>
         <v>3 mois = 18 788 €</v>
       </c>
       <c r="AE138" s="6" t="s">
@@ -26722,7 +26731,7 @@
         <v>74772</v>
       </c>
       <c r="AD139" s="12" t="str">
-        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R139,0),"### ### ##0 €")</f>
+        <f t="shared" si="5"/>
         <v>3 mois = 15 500 €</v>
       </c>
       <c r="AE139" s="6" t="s">
@@ -26872,7 +26881,7 @@
         <v>124000</v>
       </c>
       <c r="AD140" s="12" t="str">
-        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R140,0),"### ### ##0 €")</f>
+        <f t="shared" si="5"/>
         <v>3 mois = 31 000 €</v>
       </c>
       <c r="AE140" s="6" t="s">
@@ -27022,7 +27031,7 @@
         <v>124000</v>
       </c>
       <c r="AD141" s="12" t="str">
-        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R141,0),"### ### ##0 €")</f>
+        <f t="shared" si="5"/>
         <v>3 mois = 31 000 €</v>
       </c>
       <c r="AE141" s="6" t="s">
@@ -27172,7 +27181,7 @@
         <v>124000</v>
       </c>
       <c r="AD142" s="12" t="str">
-        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R142,0),"### ### ##0 €")</f>
+        <f t="shared" si="5"/>
         <v>3 mois = 31 000 €</v>
       </c>
       <c r="AE142" s="6" t="s">
@@ -27322,7 +27331,7 @@
         <v>125600</v>
       </c>
       <c r="AD143" s="12" t="str">
-        <f>"3 mois = "&amp;TEXT(ROUND(3/12*R143,0),"### ### ##0 €")</f>
+        <f t="shared" si="5"/>
         <v>3 mois = 31 400 €</v>
       </c>
       <c r="AE143" s="6" t="s">
@@ -27619,7 +27628,7 @@
         <v>136800</v>
       </c>
       <c r="AD145" s="12" t="str">
-        <f t="shared" ref="AD145:AD146" si="5">"3 mois = "&amp;TEXT(ROUND(3/12*R145,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AD145:AD146" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R145,0),"### ### ##0 €")</f>
         <v>3 mois = 32 063 €</v>
       </c>
       <c r="AE145" s="6" t="s">
@@ -27771,7 +27780,7 @@
         <v>85120</v>
       </c>
       <c r="AD146" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3 mois = 19 600 €</v>
       </c>
       <c r="AE146" s="6" t="s">
@@ -28211,7 +28220,7 @@
         <v>56000</v>
       </c>
       <c r="AD149" s="12" t="str">
-        <f t="shared" ref="AD149:AD189" si="6">"3 mois = "&amp;TEXT(ROUND(3/12*R149,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AD149:AD189" si="7">"3 mois = "&amp;TEXT(ROUND(3/12*R149,0),"### ### ##0 €")</f>
         <v>3 mois = 10 000 €</v>
       </c>
       <c r="AE149" s="6" t="s">
@@ -28366,7 +28375,7 @@
         <v>140000</v>
       </c>
       <c r="AD150" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 25 000 €</v>
       </c>
       <c r="AE150" s="6" t="s">
@@ -28521,7 +28530,7 @@
         <v>280000</v>
       </c>
       <c r="AD151" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 50 000 €</v>
       </c>
       <c r="AE151" s="6" t="s">
@@ -28676,7 +28685,7 @@
         <v>560000</v>
       </c>
       <c r="AD152" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 100 000 €</v>
       </c>
       <c r="AE152" s="6" t="s">
@@ -28831,7 +28840,7 @@
         <v>1400000</v>
       </c>
       <c r="AD153" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 250 000 €</v>
       </c>
       <c r="AE153" s="6" t="s">
@@ -28985,7 +28994,7 @@
         <v>48917.06</v>
       </c>
       <c r="AD154" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 11 313 €</v>
       </c>
       <c r="AE154" s="6" t="s">
@@ -29038,7 +29047,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="155" spans="1:47" ht="51">
+    <row r="155" spans="1:47" ht="51" hidden="1">
       <c r="A155" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29139,7 +29148,7 @@
         <v>22026</v>
       </c>
       <c r="AD155" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 5 000 €</v>
       </c>
       <c r="AE155" s="6" t="s">
@@ -29192,7 +29201,7 @@
         <v>46004</v>
       </c>
     </row>
-    <row r="156" spans="1:47" ht="38.25">
+    <row r="156" spans="1:47" ht="38.25" hidden="1">
       <c r="A156" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29293,7 +29302,7 @@
         <v>64785.96</v>
       </c>
       <c r="AD156" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 13 938 €</v>
       </c>
       <c r="AE156" s="6" t="s">
@@ -29346,7 +29355,7 @@
         <v>46005</v>
       </c>
     </row>
-    <row r="157" spans="1:47" ht="38.25">
+    <row r="157" spans="1:47" ht="38.25" hidden="1">
       <c r="A157" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29447,7 +29456,7 @@
         <v>82362.42</v>
       </c>
       <c r="AD157" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 17 719 €</v>
       </c>
       <c r="AE157" s="6" t="s">
@@ -29599,7 +29608,7 @@
         <v>343330</v>
       </c>
       <c r="AD158" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 78 188 €</v>
       </c>
       <c r="AE158" s="12" t="str">
@@ -29752,7 +29761,7 @@
         <v>166150</v>
       </c>
       <c r="AD159" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 37 500 €</v>
       </c>
       <c r="AE159" s="6" t="s">
@@ -29896,7 +29905,7 @@
         <v>0</v>
       </c>
       <c r="AD160" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 0 €</v>
       </c>
       <c r="AE160" s="6" t="s">
@@ -30046,7 +30055,7 @@
         <v>341000</v>
       </c>
       <c r="AD161" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 82 500 €</v>
       </c>
       <c r="AE161" s="6" t="s">
@@ -30198,7 +30207,7 @@
         <v>193680</v>
       </c>
       <c r="AD162" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 36 000 €</v>
       </c>
       <c r="AE162" s="6" t="s">
@@ -30350,7 +30359,7 @@
         <v>135700</v>
       </c>
       <c r="AD163" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 27 500 €</v>
       </c>
       <c r="AE163" s="6" t="s">
@@ -30500,7 +30509,7 @@
         <v>65565</v>
       </c>
       <c r="AD164" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 13 500 €</v>
       </c>
       <c r="AE164" s="6" t="s">
@@ -30650,7 +30659,7 @@
         <v>56823</v>
       </c>
       <c r="AD165" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 11 700 €</v>
       </c>
       <c r="AE165" s="6" t="s">
@@ -30800,7 +30809,7 @@
         <v>47495</v>
       </c>
       <c r="AD166" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 9 625 €</v>
       </c>
       <c r="AE166" s="6" t="s">
@@ -30851,7 +30860,7 @@
       <c r="AT166" s="14"/>
       <c r="AU166" s="44"/>
     </row>
-    <row r="167" spans="1:47" ht="25.5">
+    <row r="167" spans="1:47" ht="25.5" hidden="1">
       <c r="A167" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30950,7 +30959,7 @@
         <v>26570</v>
       </c>
       <c r="AD167" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 6 000 €</v>
       </c>
       <c r="AE167" s="6" t="s">
@@ -31100,7 +31109,7 @@
         <v>286425</v>
       </c>
       <c r="AD168" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 65 625 €</v>
       </c>
       <c r="AE168" s="6" t="s">
@@ -31252,7 +31261,7 @@
         <v>224595</v>
       </c>
       <c r="AD169" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 52 313 €</v>
       </c>
       <c r="AE169" s="6" t="s">
@@ -31404,7 +31413,7 @@
         <v>116280</v>
       </c>
       <c r="AD170" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 23 750 €</v>
       </c>
       <c r="AE170" s="6" t="s">
@@ -31554,11 +31563,11 @@
         <v>160908</v>
       </c>
       <c r="AD171" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 37 950 €</v>
       </c>
       <c r="AE171" s="12" t="str">
-        <f t="shared" ref="AE171:AE177" si="7">"6 mois = "&amp;TEXT(ROUND(6/12*R171,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AE171:AE177" si="8">"6 mois = "&amp;TEXT(ROUND(6/12*R171,0),"### ### ##0 €")</f>
         <v>6 mois = 75 900 €</v>
       </c>
       <c r="AF171" s="46">
@@ -31707,11 +31716,11 @@
         <v>206800</v>
       </c>
       <c r="AD172" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 47 000 €</v>
       </c>
       <c r="AE172" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6 mois = 94 000 €</v>
       </c>
       <c r="AF172" s="46">
@@ -31860,11 +31869,11 @@
         <v>142912</v>
       </c>
       <c r="AD173" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 30 800 €</v>
       </c>
       <c r="AE173" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6 mois = 61 600 €</v>
       </c>
       <c r="AF173" s="46">
@@ -32013,11 +32022,11 @@
         <v>213500</v>
       </c>
       <c r="AD174" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 49 219 €</v>
       </c>
       <c r="AE174" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6 mois = 98 438 €</v>
       </c>
       <c r="AF174" s="46">
@@ -32166,11 +32175,11 @@
         <v>104490</v>
       </c>
       <c r="AD175" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 24 188 €</v>
       </c>
       <c r="AE175" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6 mois = 48 375 €</v>
       </c>
       <c r="AF175" s="46">
@@ -32319,11 +32328,11 @@
         <v>176412</v>
       </c>
       <c r="AD176" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 40 669 €</v>
       </c>
       <c r="AE176" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6 mois = 81 338 €</v>
       </c>
       <c r="AF176" s="46">
@@ -32472,11 +32481,11 @@
         <v>189744</v>
       </c>
       <c r="AD177" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 45 225 €</v>
       </c>
       <c r="AE177" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6 mois = 90 450 €</v>
       </c>
       <c r="AF177" s="46">
@@ -32626,7 +32635,7 @@
         <v>165312</v>
       </c>
       <c r="AD178" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 34 997 €</v>
       </c>
       <c r="AE178" s="6" t="s">
@@ -32772,7 +32781,7 @@
         <v>132500</v>
       </c>
       <c r="AD179" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 33 125 €</v>
       </c>
       <c r="AE179" s="6" t="s">
@@ -32920,7 +32929,7 @@
         <v>112200</v>
       </c>
       <c r="AD180" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 28 050 €</v>
       </c>
       <c r="AE180" s="6" t="s">
@@ -33068,7 +33077,7 @@
         <v>53100</v>
       </c>
       <c r="AD181" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 13 275 €</v>
       </c>
       <c r="AE181" s="6" t="s">
@@ -33214,7 +33223,7 @@
         <v>42900</v>
       </c>
       <c r="AD182" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 10 725 €</v>
       </c>
       <c r="AE182" s="6" t="s">
@@ -33358,7 +33367,7 @@
         <v>74400</v>
       </c>
       <c r="AD183" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 18 600 €</v>
       </c>
       <c r="AE183" s="6" t="s">
@@ -33504,7 +33513,7 @@
         <v>112800</v>
       </c>
       <c r="AD184" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 28 200 €</v>
       </c>
       <c r="AE184" s="6" t="s">
@@ -33652,7 +33661,7 @@
         <v>60200</v>
       </c>
       <c r="AD185" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 15 050 €</v>
       </c>
       <c r="AE185" s="6" t="s">
@@ -33800,7 +33809,7 @@
         <v>134000</v>
       </c>
       <c r="AD186" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 33 500 €</v>
       </c>
       <c r="AE186" s="6" t="s">
@@ -33948,7 +33957,7 @@
         <v>113400</v>
       </c>
       <c r="AD187" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 28 350 €</v>
       </c>
       <c r="AE187" s="6" t="s">
@@ -34096,7 +34105,7 @@
         <v>134400</v>
       </c>
       <c r="AD188" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 33 600 €</v>
       </c>
       <c r="AE188" s="6" t="s">
@@ -34248,7 +34257,7 @@
         <v>135240</v>
       </c>
       <c r="AD189" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3 mois = 28 420 €</v>
       </c>
       <c r="AE189" s="6" t="s">

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1C864F-E223-429F-867B-C53E5BDF5988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C701B71-F278-48CA-AE70-3F1FE5A7A388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5519" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5540" uniqueCount="1427">
   <si>
     <t>Contact</t>
   </si>
@@ -4322,6 +4322,12 @@
   </si>
   <si>
     <t>Nature</t>
+  </si>
+  <si>
+    <t>Frais de rédaction</t>
+  </si>
+  <si>
+    <t>2 000 € HT</t>
   </si>
 </sst>
 </file>
@@ -4592,7 +4598,16 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{4EE763AE-B02B-43D6-BC8E-83B5996D9CAB}"/>
     <cellStyle name="Pourcentage" xfId="3" builtinId="5"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="48">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
@@ -4955,82 +4970,83 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AU189" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AU189" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AV189" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AV189" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}">
     <filterColumn colId="10">
       <filters>
         <filter val="/"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="47">
-    <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="46" dataCellStyle="Normal 2">
+  <tableColumns count="48">
+    <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="47" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{EA09E10C-F31A-414B-B7AE-01100FDFFB35}" name="Département" dataDxfId="45" dataCellStyle="Normal 2">
+    <tableColumn id="45" xr3:uid="{EA09E10C-F31A-414B-B7AE-01100FDFFB35}" name="Département" dataDxfId="46" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{B8B116FD-A2D6-4640-B53A-B27BF55F77D2}" name="N° Département" dataDxfId="44" dataCellStyle="Normal 2">
+    <tableColumn id="44" xr3:uid="{B8B116FD-A2D6-4640-B53A-B27BF55F77D2}" name="N° Département" dataDxfId="45" dataCellStyle="Normal 2">
       <calculatedColumnFormula>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{807881FC-FCFC-4E58-94E6-974968140DE0}" name="Rue" dataDxfId="43" dataCellStyle="Normal 2"/>
-    <tableColumn id="24" xr3:uid="{5BC55846-88AA-4EB3-AA6F-8E4CFB785641}" name="Code Postal" dataDxfId="42" dataCellStyle="Normal 2"/>
-    <tableColumn id="17" xr3:uid="{35EE7115-51F8-4E1F-AD3E-33A05B4BE6AA}" name="Ville" dataDxfId="41" dataCellStyle="Normal 2"/>
-    <tableColumn id="34" xr3:uid="{BCDF1767-53B8-4755-BA69-6972BF82336C}" name="Adresse" dataDxfId="40" dataCellStyle="Normal 2">
+    <tableColumn id="22" xr3:uid="{807881FC-FCFC-4E58-94E6-974968140DE0}" name="Rue" dataDxfId="44" dataCellStyle="Normal 2"/>
+    <tableColumn id="24" xr3:uid="{5BC55846-88AA-4EB3-AA6F-8E4CFB785641}" name="Code Postal" dataDxfId="43" dataCellStyle="Normal 2"/>
+    <tableColumn id="17" xr3:uid="{35EE7115-51F8-4E1F-AD3E-33A05B4BE6AA}" name="Ville" dataDxfId="42" dataCellStyle="Normal 2"/>
+    <tableColumn id="34" xr3:uid="{BCDF1767-53B8-4755-BA69-6972BF82336C}" name="Adresse" dataDxfId="41" dataCellStyle="Normal 2">
       <calculatedColumnFormula>Tableau1[[#This Row],[Rue]]&amp;Tableau1[[#This Row],[Code Postal]]&amp;Tableau1[[#This Row],[Ville]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{F16F96D2-ED03-45AB-90ED-8D480A7B0261}" name="Lien Google Maps" dataDxfId="39" dataCellStyle="Normal 2">
+    <tableColumn id="18" xr3:uid="{F16F96D2-ED03-45AB-90ED-8D480A7B0261}" name="Lien Google Maps" dataDxfId="40" dataCellStyle="Normal 2">
       <calculatedColumnFormula array="1">Extrait_hyperlien(#REF!)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{172E07C4-0318-49AC-A621-9C0E3C5C5B5D}" name="Emplacement" dataDxfId="38" dataCellStyle="Normal 2"/>
-    <tableColumn id="14" xr3:uid="{95EAECC7-A016-42C4-9C47-2CABFEAEC577}" name="Typologie" dataDxfId="37" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{8C8D77C7-8B55-471A-B479-215BC0D77604}" name="Nature" dataDxfId="36" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{87D84239-5323-4A47-9424-F0CADB050723}" name="Cession / Droit au bail" dataDxfId="35" dataCellStyle="Normal 2"/>
-    <tableColumn id="31" xr3:uid="{86770348-6586-45F2-A401-94B68504976F}" name="Numéro de lot" dataDxfId="34" dataCellStyle="Normal 2"/>
-    <tableColumn id="1" xr3:uid="{3888DEAC-D743-4A06-B622-0805DADF7B24}" name="Surface GLA" dataDxfId="33" dataCellStyle="Normal 2"/>
-    <tableColumn id="9" xr3:uid="{0D61162C-F920-419C-993E-EDC2DF105B61}" name="Répartition surface GLA" dataDxfId="32" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{9969DD5B-5EA2-4595-B887-2E9B21053A55}" name="Surface utile" dataDxfId="31" dataCellStyle="Normal 2"/>
-    <tableColumn id="21" xr3:uid="{3DFB9473-7064-409A-A47B-5544538EC4AE}" name="Répartition surface utile" dataDxfId="30" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{A744513A-B9BE-426C-9A67-F73FDBDA82D8}" name="Loyer annuel" dataDxfId="29" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{356A37C1-BF3E-4357-A954-82A182007A4A}" name="Loyer Mensuel" dataDxfId="28" dataCellStyle="Normal 2">
+    <tableColumn id="15" xr3:uid="{172E07C4-0318-49AC-A621-9C0E3C5C5B5D}" name="Emplacement" dataDxfId="39" dataCellStyle="Normal 2"/>
+    <tableColumn id="14" xr3:uid="{95EAECC7-A016-42C4-9C47-2CABFEAEC577}" name="Typologie" dataDxfId="38" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{8C8D77C7-8B55-471A-B479-215BC0D77604}" name="Nature" dataDxfId="37" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{87D84239-5323-4A47-9424-F0CADB050723}" name="Cession / Droit au bail" dataDxfId="36" dataCellStyle="Normal 2"/>
+    <tableColumn id="31" xr3:uid="{86770348-6586-45F2-A401-94B68504976F}" name="Numéro de lot" dataDxfId="35" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{3888DEAC-D743-4A06-B622-0805DADF7B24}" name="Surface GLA" dataDxfId="34" dataCellStyle="Normal 2"/>
+    <tableColumn id="9" xr3:uid="{0D61162C-F920-419C-993E-EDC2DF105B61}" name="Répartition surface GLA" dataDxfId="33" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{9969DD5B-5EA2-4595-B887-2E9B21053A55}" name="Surface utile" dataDxfId="32" dataCellStyle="Normal 2"/>
+    <tableColumn id="21" xr3:uid="{3DFB9473-7064-409A-A47B-5544538EC4AE}" name="Répartition surface utile" dataDxfId="31" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{A744513A-B9BE-426C-9A67-F73FDBDA82D8}" name="Loyer annuel" dataDxfId="30" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{356A37C1-BF3E-4357-A954-82A182007A4A}" name="Loyer Mensuel" dataDxfId="29" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{767012B1-AABD-475A-8A4D-3B7DA0A65895}" name="Loyer €/m²" dataDxfId="27" dataCellStyle="Normal 2"/>
-    <tableColumn id="30" xr3:uid="{1B20B1A4-ACFD-45E3-955E-514E88115368}" name="Loyer variable" dataDxfId="26" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{2A7DA589-64F1-4CF6-8C82-38781BD9EC1D}" name="Charges annuelles" dataDxfId="25" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{440DF5B1-3CC3-4785-9C23-94B007AF5E1B}" name="Charges Mensuelles" dataDxfId="24" dataCellStyle="Normal 2">
+    <tableColumn id="11" xr3:uid="{767012B1-AABD-475A-8A4D-3B7DA0A65895}" name="Loyer €/m²" dataDxfId="28" dataCellStyle="Normal 2"/>
+    <tableColumn id="30" xr3:uid="{1B20B1A4-ACFD-45E3-955E-514E88115368}" name="Loyer variable" dataDxfId="27" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{2A7DA589-64F1-4CF6-8C82-38781BD9EC1D}" name="Charges annuelles" dataDxfId="26" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{440DF5B1-3CC3-4785-9C23-94B007AF5E1B}" name="Charges Mensuelles" dataDxfId="25" dataCellStyle="Normal 2">
       <calculatedColumnFormula>Tableau1[[#This Row],[Charges annuelles]]/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{4129B281-2FE2-4CF1-9B2A-1383495B75F8}" name="Charges €/m²" dataDxfId="23" dataCellStyle="Normal 2"/>
-    <tableColumn id="23" xr3:uid="{8D958AF5-4590-4B2C-91C7-84AA83299F72}" name="Taxe foncière" dataDxfId="22" dataCellStyle="Normal 2">
+    <tableColumn id="19" xr3:uid="{4129B281-2FE2-4CF1-9B2A-1383495B75F8}" name="Charges €/m²" dataDxfId="24" dataCellStyle="Normal 2"/>
+    <tableColumn id="23" xr3:uid="{8D958AF5-4590-4B2C-91C7-84AA83299F72}" name="Taxe foncière" dataDxfId="23" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{3ED0377F-0AC3-483C-A382-DCE0304838BB}" name="Taxe foncière €/m²" dataDxfId="21" dataCellStyle="Normal 2"/>
-    <tableColumn id="37" xr3:uid="{DCF6EDF6-4C11-48C1-B6A2-F68E6553ECAE}" name="Marketing" dataDxfId="20" dataCellStyle="Normal 2">
+    <tableColumn id="25" xr3:uid="{3ED0377F-0AC3-483C-A382-DCE0304838BB}" name="Taxe foncière €/m²" dataDxfId="22" dataCellStyle="Normal 2"/>
+    <tableColumn id="37" xr3:uid="{DCF6EDF6-4C11-48C1-B6A2-F68E6553ECAE}" name="Marketing" dataDxfId="21" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{0670F3CF-44F2-4728-8A06-52C034D6BD30}" name="Marketing €/m²" dataDxfId="19" dataCellStyle="Normal 2"/>
-    <tableColumn id="39" xr3:uid="{5F4F5D62-4EE8-4561-AFC9-FBA26AD0FEB9}" name="Total (L+C+M)" dataDxfId="18" dataCellStyle="Normal 2">
+    <tableColumn id="26" xr3:uid="{0670F3CF-44F2-4728-8A06-52C034D6BD30}" name="Marketing €/m²" dataDxfId="20" dataCellStyle="Normal 2"/>
+    <tableColumn id="39" xr3:uid="{5F4F5D62-4EE8-4561-AFC9-FBA26AD0FEB9}" name="Total (L+C+M)" dataDxfId="19" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{95C0AA56-6C81-4449-BBAF-48D6559B29F4}" name="Dépôt de garantie" dataDxfId="17" dataCellStyle="Normal 2"/>
-    <tableColumn id="33" xr3:uid="{5D2CDDBF-0016-4D42-9FA2-C6BE7187A781}" name="GAPD" dataDxfId="16" dataCellStyle="Normal 2"/>
-    <tableColumn id="27" xr3:uid="{AE6532DB-DF7C-4137-958E-CF0878BAF4EA}" name="Gestion" dataDxfId="15" dataCellStyle="Normal 2"/>
-    <tableColumn id="29" xr3:uid="{C7D740EB-05A5-4C80-B626-4AE327C99B0E}" name="Etat de livraison" dataDxfId="14" dataCellStyle="Normal 2"/>
-    <tableColumn id="10" xr3:uid="{F202F9CF-E361-49F7-BCB2-41601DB0A090}" name="Extraction" dataDxfId="13" dataCellStyle="Normal 2"/>
-    <tableColumn id="38" xr3:uid="{1E22D9C1-89FA-49FF-9893-8AC79191E4A6}" name="Restauration" dataDxfId="12" dataCellStyle="Normal 2"/>
-    <tableColumn id="28" xr3:uid="{BF030FEC-E7AF-42C6-AC39-B670759A4BC7}" name="Environnement Commercial" dataDxfId="11" dataCellStyle="Normal 2"/>
-    <tableColumn id="16" xr3:uid="{D3CC4D5A-911C-4939-9024-731260442272}" name="Commentaires" dataDxfId="10" dataCellStyle="Normal 2"/>
-    <tableColumn id="40" xr3:uid="{5463AA4C-3D9C-45CF-B81C-A3755D028F2B}" name="Honoraires" dataDxfId="9" dataCellStyle="Normal 2"/>
-    <tableColumn id="36" xr3:uid="{EBABBF90-FEC0-4C48-8EB4-A8DB85141CEF}" name="Latitude" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="35" xr3:uid="{FDA62BB3-971D-4771-BFF4-42A78D749576}" name="Longitude" dataDxfId="7" dataCellStyle="Normal 2"/>
-    <tableColumn id="41" xr3:uid="{0B5CFD66-9BAF-42E4-85BA-98CEF40CC994}" name="Référence annonce" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="46" xr3:uid="{ED041E73-B65A-464D-8E38-4CD520F93F57}" name="Photos annonce" dataDxfId="5" dataCellStyle="Normal 2"/>
-    <tableColumn id="42" xr3:uid="{31DE41E2-CE5A-45AD-B999-11A9307EA50B}" name="Actif" dataDxfId="4" dataCellStyle="Normal 2"/>
-    <tableColumn id="20" xr3:uid="{D2AE6F16-4821-49DE-B56C-155BB51A6204}" name="Valeur BP" dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{80CF5A8D-23B2-4B36-80CB-91ECBC7FF3FE}" name="Contact" dataDxfId="2" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{E28C924B-61DC-4BBD-ABE7-33B29A5037B4}" name="Page Web" dataDxfId="1" dataCellStyle="Normal 2"/>
-    <tableColumn id="47" xr3:uid="{6D70689D-C350-4037-8D03-D9E5646BA26C}" name="Date d'ajout" dataDxfId="0" dataCellStyle="Normal 2"/>
+    <tableColumn id="32" xr3:uid="{95C0AA56-6C81-4449-BBAF-48D6559B29F4}" name="Dépôt de garantie" dataDxfId="18" dataCellStyle="Normal 2"/>
+    <tableColumn id="33" xr3:uid="{5D2CDDBF-0016-4D42-9FA2-C6BE7187A781}" name="GAPD" dataDxfId="17" dataCellStyle="Normal 2"/>
+    <tableColumn id="27" xr3:uid="{AE6532DB-DF7C-4137-958E-CF0878BAF4EA}" name="Gestion" dataDxfId="16" dataCellStyle="Normal 2"/>
+    <tableColumn id="29" xr3:uid="{C7D740EB-05A5-4C80-B626-4AE327C99B0E}" name="Etat de livraison" dataDxfId="15" dataCellStyle="Normal 2"/>
+    <tableColumn id="10" xr3:uid="{F202F9CF-E361-49F7-BCB2-41601DB0A090}" name="Extraction" dataDxfId="14" dataCellStyle="Normal 2"/>
+    <tableColumn id="38" xr3:uid="{1E22D9C1-89FA-49FF-9893-8AC79191E4A6}" name="Restauration" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="28" xr3:uid="{BF030FEC-E7AF-42C6-AC39-B670759A4BC7}" name="Environnement Commercial" dataDxfId="12" dataCellStyle="Normal 2"/>
+    <tableColumn id="16" xr3:uid="{D3CC4D5A-911C-4939-9024-731260442272}" name="Commentaires" dataDxfId="11" dataCellStyle="Normal 2"/>
+    <tableColumn id="48" xr3:uid="{251DE01D-1A11-497D-9729-BA9E0EB06C60}" name="Frais de rédaction" dataDxfId="0" dataCellStyle="Normal 2"/>
+    <tableColumn id="40" xr3:uid="{5463AA4C-3D9C-45CF-B81C-A3755D028F2B}" name="Honoraires" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="36" xr3:uid="{EBABBF90-FEC0-4C48-8EB4-A8DB85141CEF}" name="Latitude" dataDxfId="9" dataCellStyle="Normal 2"/>
+    <tableColumn id="35" xr3:uid="{FDA62BB3-971D-4771-BFF4-42A78D749576}" name="Longitude" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="41" xr3:uid="{0B5CFD66-9BAF-42E4-85BA-98CEF40CC994}" name="Référence annonce" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="46" xr3:uid="{ED041E73-B65A-464D-8E38-4CD520F93F57}" name="Photos annonce" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="42" xr3:uid="{31DE41E2-CE5A-45AD-B999-11A9307EA50B}" name="Actif" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="20" xr3:uid="{D2AE6F16-4821-49DE-B56C-155BB51A6204}" name="Valeur BP" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{80CF5A8D-23B2-4B36-80CB-91ECBC7FF3FE}" name="Contact" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{E28C924B-61DC-4BBD-ABE7-33B29A5037B4}" name="Page Web" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="47" xr3:uid="{6D70689D-C350-4037-8D03-D9E5646BA26C}" name="Date d'ajout" dataDxfId="1" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5354,7 +5370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BD205"/>
+  <dimension ref="A1:BE205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -5389,28 +5405,28 @@
     <col min="34" max="34" width="11.25" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="9.625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="53.875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="41.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="18.5" style="1" customWidth="1"/>
-    <col min="43" max="43" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="25.75" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="28" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="40.625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="27.75" style="1" customWidth="1"/>
-    <col min="52" max="53" width="44.25" style="1" customWidth="1"/>
-    <col min="54" max="54" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="93.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="16384" width="11.625" style="1"/>
+    <col min="37" max="38" width="53.875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="41.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18.5" style="1" customWidth="1"/>
+    <col min="44" max="44" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="13.375" style="1" customWidth="1"/>
+    <col min="48" max="48" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="28" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="40.625" style="1" customWidth="1"/>
+    <col min="52" max="52" width="27.75" style="1" customWidth="1"/>
+    <col min="53" max="54" width="44.25" style="1" customWidth="1"/>
+    <col min="55" max="55" width="33" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="93.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="11.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" ht="12.75">
+    <row r="1" spans="1:57" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>255</v>
       </c>
@@ -5523,40 +5539,43 @@
         <v>1</v>
       </c>
       <c r="AL1" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>1101</v>
       </c>
-      <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
-      <c r="BD1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="BE1" s="1"/>
     </row>
-    <row r="2" spans="1:56" ht="25.5">
+    <row r="2" spans="1:57" ht="25.5">
       <c r="A2" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Nouvelle-Aquitaine</v>
@@ -5680,37 +5699,38 @@
       <c r="AK2" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="AL2" s="5" t="s">
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM2" s="5" t="s">
+      <c r="AN2" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="AN2" s="5" t="s">
+      <c r="AO2" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="AO2" s="32" t="s">
+      <c r="AP2" s="32" t="s">
         <v>335</v>
       </c>
-      <c r="AP2" s="35" t="s">
+      <c r="AQ2" s="35" t="s">
         <v>750</v>
       </c>
-      <c r="AQ2" s="5" t="s">
+      <c r="AR2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR2" s="5" t="s">
+      <c r="AS2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AS2" s="7" t="s">
+      <c r="AT2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="7"/>
-      <c r="AU2" s="44"/>
-      <c r="AV2" s="1"/>
+      <c r="AU2" s="7"/>
+      <c r="AV2" s="44"/>
       <c r="AW2" s="1"/>
-      <c r="BD2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="BE2" s="1"/>
     </row>
-    <row r="3" spans="1:56" ht="25.5">
+    <row r="3" spans="1:57" ht="25.5">
       <c r="A3" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -5834,37 +5854,38 @@
       <c r="AK3" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="AL3" s="5" t="s">
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM3" s="5">
+      <c r="AN3" s="5">
         <v>47.238161699999999</v>
       </c>
-      <c r="AN3" s="5">
+      <c r="AO3" s="5">
         <v>6.0234543</v>
       </c>
-      <c r="AO3" s="32" t="s">
+      <c r="AP3" s="32" t="s">
         <v>336</v>
       </c>
-      <c r="AP3" s="35" t="s">
+      <c r="AQ3" s="35" t="s">
         <v>751</v>
       </c>
-      <c r="AQ3" s="5" t="s">
+      <c r="AR3" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR3" s="5" t="s">
+      <c r="AS3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AT3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT3" s="9"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="1"/>
+      <c r="AU3" s="9"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="1"/>
-      <c r="BD3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="BE3" s="1"/>
     </row>
-    <row r="4" spans="1:56" ht="25.5">
+    <row r="4" spans="1:57" ht="25.5">
       <c r="A4" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -5988,37 +6009,38 @@
       <c r="AK4" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="AL4" s="5" t="s">
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM4" s="5" t="s">
+      <c r="AN4" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="AN4" s="5" t="s">
+      <c r="AO4" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AP4" s="32" t="s">
         <v>357</v>
       </c>
-      <c r="AP4" s="35" t="s">
+      <c r="AQ4" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="AQ4" s="5" t="s">
+      <c r="AR4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR4" s="5" t="s">
+      <c r="AS4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AS4" s="7" t="s">
+      <c r="AT4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT4" s="8"/>
-      <c r="AU4" s="44"/>
-      <c r="AV4" s="1"/>
+      <c r="AU4" s="8"/>
+      <c r="AV4" s="44"/>
       <c r="AW4" s="1"/>
-      <c r="BD4" s="1"/>
+      <c r="AX4" s="1"/>
+      <c r="BE4" s="1"/>
     </row>
-    <row r="5" spans="1:56" ht="25.5">
+    <row r="5" spans="1:57" ht="25.5">
       <c r="A5" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -6142,37 +6164,38 @@
       <c r="AK5" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="AL5" s="5" t="s">
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM5" s="5" t="s">
+      <c r="AN5" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="AN5" s="5" t="s">
+      <c r="AO5" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="AO5" s="32" t="s">
+      <c r="AP5" s="32" t="s">
         <v>358</v>
       </c>
-      <c r="AP5" s="35" t="s">
+      <c r="AQ5" s="35" t="s">
         <v>753</v>
       </c>
-      <c r="AQ5" s="5" t="s">
+      <c r="AR5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR5" s="5" t="s">
+      <c r="AS5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AS5" s="7" t="s">
+      <c r="AT5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT5" s="8"/>
-      <c r="AU5" s="44"/>
-      <c r="AV5" s="1"/>
+      <c r="AU5" s="8"/>
+      <c r="AV5" s="44"/>
       <c r="AW5" s="1"/>
-      <c r="BD5" s="1"/>
+      <c r="AX5" s="1"/>
+      <c r="BE5" s="1"/>
     </row>
-    <row r="6" spans="1:56" ht="25.5">
+    <row r="6" spans="1:57" ht="25.5">
       <c r="A6" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6296,37 +6319,38 @@
       <c r="AK6" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL6" s="5" t="s">
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM6" s="11" t="s">
+      <c r="AN6" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="AN6" s="11" t="s">
+      <c r="AO6" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="AO6" s="32" t="s">
+      <c r="AP6" s="32" t="s">
         <v>444</v>
       </c>
-      <c r="AP6" s="35" t="s">
+      <c r="AQ6" s="35" t="s">
         <v>754</v>
       </c>
-      <c r="AQ6" s="5" t="s">
+      <c r="AR6" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR6" s="11" t="s">
+      <c r="AS6" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS6" s="13" t="s">
+      <c r="AT6" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT6" s="14"/>
-      <c r="AU6" s="44"/>
-      <c r="AV6" s="1"/>
+      <c r="AU6" s="14"/>
+      <c r="AV6" s="44"/>
       <c r="AW6" s="1"/>
-      <c r="BD6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="BE6" s="1"/>
     </row>
-    <row r="7" spans="1:56" ht="25.5">
+    <row r="7" spans="1:57" ht="25.5">
       <c r="A7" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6450,37 +6474,38 @@
       <c r="AK7" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL7" s="5" t="s">
+      <c r="AL7" s="11"/>
+      <c r="AM7" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM7" s="11" t="s">
+      <c r="AN7" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="AN7" s="11" t="s">
+      <c r="AO7" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="AO7" s="32" t="s">
+      <c r="AP7" s="32" t="s">
         <v>445</v>
       </c>
-      <c r="AP7" s="35" t="s">
+      <c r="AQ7" s="35" t="s">
         <v>755</v>
       </c>
-      <c r="AQ7" s="5" t="s">
+      <c r="AR7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR7" s="11" t="s">
+      <c r="AS7" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS7" s="13" t="s">
+      <c r="AT7" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT7" s="14"/>
-      <c r="AU7" s="44"/>
-      <c r="AV7" s="1"/>
+      <c r="AU7" s="14"/>
+      <c r="AV7" s="44"/>
       <c r="AW7" s="1"/>
-      <c r="BD7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="BE7" s="1"/>
     </row>
-    <row r="8" spans="1:56" ht="25.5">
+    <row r="8" spans="1:57" ht="25.5">
       <c r="A8" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6604,37 +6629,38 @@
       <c r="AK8" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL8" s="5" t="s">
+      <c r="AL8" s="11"/>
+      <c r="AM8" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM8" s="11" t="s">
+      <c r="AN8" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="AN8" s="11" t="s">
+      <c r="AO8" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="AO8" s="32" t="s">
+      <c r="AP8" s="32" t="s">
         <v>446</v>
       </c>
-      <c r="AP8" s="35" t="s">
+      <c r="AQ8" s="35" t="s">
         <v>756</v>
       </c>
-      <c r="AQ8" s="5" t="s">
+      <c r="AR8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR8" s="11" t="s">
+      <c r="AS8" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS8" s="13" t="s">
+      <c r="AT8" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT8" s="14"/>
-      <c r="AU8" s="44"/>
-      <c r="AV8" s="1"/>
+      <c r="AU8" s="14"/>
+      <c r="AV8" s="44"/>
       <c r="AW8" s="1"/>
-      <c r="BD8" s="1"/>
+      <c r="AX8" s="1"/>
+      <c r="BE8" s="1"/>
     </row>
-    <row r="9" spans="1:56" ht="25.5">
+    <row r="9" spans="1:57" ht="25.5">
       <c r="A9" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6758,37 +6784,38 @@
       <c r="AK9" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL9" s="5" t="s">
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM9" s="11" t="s">
+      <c r="AN9" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="AN9" s="11" t="s">
+      <c r="AO9" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="AO9" s="32" t="s">
+      <c r="AP9" s="32" t="s">
         <v>447</v>
       </c>
-      <c r="AP9" s="35" t="s">
+      <c r="AQ9" s="35" t="s">
         <v>757</v>
       </c>
-      <c r="AQ9" s="5" t="s">
+      <c r="AR9" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR9" s="11" t="s">
+      <c r="AS9" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS9" s="13" t="s">
+      <c r="AT9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT9" s="14"/>
-      <c r="AU9" s="44"/>
-      <c r="AV9" s="1"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="44"/>
       <c r="AW9" s="1"/>
-      <c r="BD9" s="1"/>
+      <c r="AX9" s="1"/>
+      <c r="BE9" s="1"/>
     </row>
-    <row r="10" spans="1:56" ht="25.5">
+    <row r="10" spans="1:57" ht="25.5">
       <c r="A10" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6912,37 +6939,38 @@
       <c r="AK10" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL10" s="5" t="s">
+      <c r="AL10" s="11"/>
+      <c r="AM10" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM10" s="11" t="s">
+      <c r="AN10" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="AN10" s="11" t="s">
+      <c r="AO10" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="AO10" s="32" t="s">
+      <c r="AP10" s="32" t="s">
         <v>448</v>
       </c>
-      <c r="AP10" s="35" t="s">
+      <c r="AQ10" s="35" t="s">
         <v>758</v>
       </c>
-      <c r="AQ10" s="5" t="s">
+      <c r="AR10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR10" s="11" t="s">
+      <c r="AS10" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS10" s="13" t="s">
+      <c r="AT10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT10" s="14"/>
-      <c r="AU10" s="44"/>
-      <c r="AV10" s="1"/>
+      <c r="AU10" s="14"/>
+      <c r="AV10" s="44"/>
       <c r="AW10" s="1"/>
-      <c r="BD10" s="1"/>
+      <c r="AX10" s="1"/>
+      <c r="BE10" s="1"/>
     </row>
-    <row r="11" spans="1:56" ht="25.5">
+    <row r="11" spans="1:57" ht="25.5">
       <c r="A11" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7066,37 +7094,38 @@
       <c r="AK11" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL11" s="5" t="s">
+      <c r="AL11" s="11"/>
+      <c r="AM11" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM11" s="11" t="s">
+      <c r="AN11" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="AN11" s="11" t="s">
+      <c r="AO11" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="AO11" s="32" t="s">
+      <c r="AP11" s="32" t="s">
         <v>449</v>
       </c>
-      <c r="AP11" s="35" t="s">
+      <c r="AQ11" s="35" t="s">
         <v>759</v>
       </c>
-      <c r="AQ11" s="5" t="s">
+      <c r="AR11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR11" s="11" t="s">
+      <c r="AS11" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS11" s="13" t="s">
+      <c r="AT11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT11" s="14"/>
-      <c r="AU11" s="44"/>
-      <c r="AV11" s="1"/>
+      <c r="AU11" s="14"/>
+      <c r="AV11" s="44"/>
       <c r="AW11" s="1"/>
-      <c r="BD11" s="1"/>
+      <c r="AX11" s="1"/>
+      <c r="BE11" s="1"/>
     </row>
-    <row r="12" spans="1:56" ht="25.5">
+    <row r="12" spans="1:57" ht="25.5">
       <c r="A12" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7220,37 +7249,38 @@
       <c r="AK12" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL12" s="5" t="s">
+      <c r="AL12" s="11"/>
+      <c r="AM12" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM12" s="11" t="s">
+      <c r="AN12" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="AN12" s="11" t="s">
+      <c r="AO12" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="AO12" s="32" t="s">
+      <c r="AP12" s="32" t="s">
         <v>450</v>
       </c>
-      <c r="AP12" s="35" t="s">
+      <c r="AQ12" s="35" t="s">
         <v>760</v>
       </c>
-      <c r="AQ12" s="5" t="s">
+      <c r="AR12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR12" s="11" t="s">
+      <c r="AS12" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS12" s="13" t="s">
+      <c r="AT12" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT12" s="14"/>
-      <c r="AU12" s="44"/>
-      <c r="AV12" s="1"/>
+      <c r="AU12" s="14"/>
+      <c r="AV12" s="44"/>
       <c r="AW12" s="1"/>
-      <c r="BD12" s="1"/>
+      <c r="AX12" s="1"/>
+      <c r="BE12" s="1"/>
     </row>
-    <row r="13" spans="1:56" ht="25.5">
+    <row r="13" spans="1:57" ht="25.5">
       <c r="A13" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7374,37 +7404,38 @@
       <c r="AK13" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL13" s="5" t="s">
+      <c r="AL13" s="11"/>
+      <c r="AM13" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM13" s="11" t="s">
+      <c r="AN13" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="AN13" s="11" t="s">
+      <c r="AO13" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="AO13" s="32" t="s">
+      <c r="AP13" s="32" t="s">
         <v>451</v>
       </c>
-      <c r="AP13" s="35" t="s">
+      <c r="AQ13" s="35" t="s">
         <v>761</v>
       </c>
-      <c r="AQ13" s="5" t="s">
+      <c r="AR13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR13" s="11" t="s">
+      <c r="AS13" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS13" s="13" t="s">
+      <c r="AT13" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT13" s="14"/>
-      <c r="AU13" s="44"/>
-      <c r="AV13" s="1"/>
+      <c r="AU13" s="14"/>
+      <c r="AV13" s="44"/>
       <c r="AW13" s="1"/>
-      <c r="BD13" s="1"/>
+      <c r="AX13" s="1"/>
+      <c r="BE13" s="1"/>
     </row>
-    <row r="14" spans="1:56" ht="25.5">
+    <row r="14" spans="1:57" ht="25.5">
       <c r="A14" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7528,37 +7559,38 @@
       <c r="AK14" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL14" s="5" t="s">
+      <c r="AL14" s="11"/>
+      <c r="AM14" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM14" s="11" t="s">
+      <c r="AN14" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="AN14" s="11" t="s">
+      <c r="AO14" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="AO14" s="32" t="s">
+      <c r="AP14" s="32" t="s">
         <v>452</v>
       </c>
-      <c r="AP14" s="35" t="s">
+      <c r="AQ14" s="35" t="s">
         <v>762</v>
       </c>
-      <c r="AQ14" s="5" t="s">
+      <c r="AR14" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR14" s="11" t="s">
+      <c r="AS14" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS14" s="13" t="s">
+      <c r="AT14" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT14" s="14"/>
-      <c r="AU14" s="44"/>
-      <c r="AV14" s="1"/>
+      <c r="AU14" s="14"/>
+      <c r="AV14" s="44"/>
       <c r="AW14" s="1"/>
-      <c r="BD14" s="1"/>
+      <c r="AX14" s="1"/>
+      <c r="BE14" s="1"/>
     </row>
-    <row r="15" spans="1:56" ht="25.5">
+    <row r="15" spans="1:57" ht="25.5">
       <c r="A15" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7682,37 +7714,38 @@
       <c r="AK15" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL15" s="5" t="s">
+      <c r="AL15" s="11"/>
+      <c r="AM15" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM15" s="11" t="s">
+      <c r="AN15" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="AN15" s="11" t="s">
+      <c r="AO15" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="AO15" s="32" t="s">
+      <c r="AP15" s="32" t="s">
         <v>453</v>
       </c>
-      <c r="AP15" s="35" t="s">
+      <c r="AQ15" s="35" t="s">
         <v>763</v>
       </c>
-      <c r="AQ15" s="5" t="s">
+      <c r="AR15" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR15" s="11" t="s">
+      <c r="AS15" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS15" s="13" t="s">
+      <c r="AT15" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT15" s="14"/>
-      <c r="AU15" s="44"/>
-      <c r="AV15" s="1"/>
+      <c r="AU15" s="14"/>
+      <c r="AV15" s="44"/>
       <c r="AW15" s="1"/>
-      <c r="BD15" s="1"/>
+      <c r="AX15" s="1"/>
+      <c r="BE15" s="1"/>
     </row>
-    <row r="16" spans="1:56" ht="25.5">
+    <row r="16" spans="1:57" ht="25.5">
       <c r="A16" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7836,37 +7869,38 @@
       <c r="AK16" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL16" s="5" t="s">
+      <c r="AL16" s="11"/>
+      <c r="AM16" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM16" s="11" t="s">
+      <c r="AN16" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="AN16" s="11" t="s">
+      <c r="AO16" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="AO16" s="32" t="s">
+      <c r="AP16" s="32" t="s">
         <v>454</v>
       </c>
-      <c r="AP16" s="35" t="s">
+      <c r="AQ16" s="35" t="s">
         <v>764</v>
       </c>
-      <c r="AQ16" s="5" t="s">
+      <c r="AR16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR16" s="11" t="s">
+      <c r="AS16" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS16" s="13" t="s">
+      <c r="AT16" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT16" s="14"/>
-      <c r="AU16" s="44"/>
-      <c r="AV16" s="1"/>
+      <c r="AU16" s="14"/>
+      <c r="AV16" s="44"/>
       <c r="AW16" s="1"/>
-      <c r="BD16" s="1"/>
+      <c r="AX16" s="1"/>
+      <c r="BE16" s="1"/>
     </row>
-    <row r="17" spans="1:56" ht="25.5">
+    <row r="17" spans="1:57" ht="25.5">
       <c r="A17" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7990,37 +8024,38 @@
       <c r="AK17" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL17" s="5" t="s">
+      <c r="AL17" s="11"/>
+      <c r="AM17" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM17" s="11" t="s">
+      <c r="AN17" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="AN17" s="11" t="s">
+      <c r="AO17" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="AO17" s="32" t="s">
+      <c r="AP17" s="32" t="s">
         <v>455</v>
       </c>
-      <c r="AP17" s="35" t="s">
+      <c r="AQ17" s="35" t="s">
         <v>765</v>
       </c>
-      <c r="AQ17" s="5" t="s">
+      <c r="AR17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR17" s="11" t="s">
+      <c r="AS17" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS17" s="13" t="s">
+      <c r="AT17" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT17" s="14"/>
-      <c r="AU17" s="44"/>
-      <c r="AV17" s="1"/>
+      <c r="AU17" s="14"/>
+      <c r="AV17" s="44"/>
       <c r="AW17" s="1"/>
-      <c r="BD17" s="1"/>
+      <c r="AX17" s="1"/>
+      <c r="BE17" s="1"/>
     </row>
-    <row r="18" spans="1:56" ht="25.5">
+    <row r="18" spans="1:57" ht="25.5">
       <c r="A18" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -8144,37 +8179,38 @@
       <c r="AK18" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="AL18" s="5" t="s">
+      <c r="AL18" s="11"/>
+      <c r="AM18" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM18" s="11" t="s">
+      <c r="AN18" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="AN18" s="11" t="s">
+      <c r="AO18" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="AO18" s="32" t="s">
+      <c r="AP18" s="32" t="s">
         <v>456</v>
       </c>
-      <c r="AP18" s="35" t="s">
+      <c r="AQ18" s="35" t="s">
         <v>766</v>
       </c>
-      <c r="AQ18" s="5" t="s">
+      <c r="AR18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR18" s="11" t="s">
+      <c r="AS18" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS18" s="13" t="s">
+      <c r="AT18" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT18" s="14"/>
-      <c r="AU18" s="44"/>
-      <c r="AV18" s="1"/>
+      <c r="AU18" s="14"/>
+      <c r="AV18" s="44"/>
       <c r="AW18" s="1"/>
-      <c r="BD18" s="1"/>
+      <c r="AX18" s="1"/>
+      <c r="BE18" s="1"/>
     </row>
-    <row r="19" spans="1:56" ht="25.5">
+    <row r="19" spans="1:57" ht="25.5">
       <c r="A19" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8298,37 +8334,38 @@
       <c r="AK19" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL19" s="5" t="s">
+      <c r="AL19" s="11"/>
+      <c r="AM19" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM19" s="11" t="s">
+      <c r="AN19" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="AN19" s="11" t="s">
+      <c r="AO19" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="AO19" s="32" t="s">
+      <c r="AP19" s="32" t="s">
         <v>457</v>
       </c>
-      <c r="AP19" s="35" t="s">
+      <c r="AQ19" s="35" t="s">
         <v>767</v>
       </c>
-      <c r="AQ19" s="5" t="s">
+      <c r="AR19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR19" s="11" t="s">
+      <c r="AS19" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS19" s="13" t="s">
+      <c r="AT19" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT19" s="14"/>
-      <c r="AU19" s="44"/>
-      <c r="AV19" s="1"/>
+      <c r="AU19" s="14"/>
+      <c r="AV19" s="44"/>
       <c r="AW19" s="1"/>
-      <c r="BD19" s="1"/>
+      <c r="AX19" s="1"/>
+      <c r="BE19" s="1"/>
     </row>
-    <row r="20" spans="1:56" ht="25.5">
+    <row r="20" spans="1:57" ht="25.5">
       <c r="A20" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8452,37 +8489,38 @@
       <c r="AK20" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL20" s="5" t="s">
+      <c r="AL20" s="11"/>
+      <c r="AM20" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM20" s="11" t="s">
+      <c r="AN20" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="AN20" s="11" t="s">
+      <c r="AO20" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="AO20" s="32" t="s">
+      <c r="AP20" s="32" t="s">
         <v>458</v>
       </c>
-      <c r="AP20" s="36" t="s">
+      <c r="AQ20" s="36" t="s">
         <v>768</v>
       </c>
-      <c r="AQ20" s="5" t="s">
+      <c r="AR20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR20" s="11" t="s">
+      <c r="AS20" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS20" s="13" t="s">
+      <c r="AT20" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT20" s="14"/>
-      <c r="AU20" s="44"/>
-      <c r="AV20" s="1"/>
+      <c r="AU20" s="14"/>
+      <c r="AV20" s="44"/>
       <c r="AW20" s="1"/>
-      <c r="BD20" s="1"/>
+      <c r="AX20" s="1"/>
+      <c r="BE20" s="1"/>
     </row>
-    <row r="21" spans="1:56" ht="25.5">
+    <row r="21" spans="1:57" ht="25.5">
       <c r="A21" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8606,37 +8644,38 @@
       <c r="AK21" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL21" s="5" t="s">
+      <c r="AL21" s="11"/>
+      <c r="AM21" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM21" s="11" t="s">
+      <c r="AN21" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="AN21" s="11" t="s">
+      <c r="AO21" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="AO21" s="32" t="s">
+      <c r="AP21" s="32" t="s">
         <v>459</v>
       </c>
-      <c r="AP21" s="36" t="s">
+      <c r="AQ21" s="36" t="s">
         <v>769</v>
       </c>
-      <c r="AQ21" s="5" t="s">
+      <c r="AR21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR21" s="11" t="s">
+      <c r="AS21" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS21" s="13" t="s">
+      <c r="AT21" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT21" s="14"/>
-      <c r="AU21" s="44"/>
-      <c r="AV21" s="1"/>
+      <c r="AU21" s="14"/>
+      <c r="AV21" s="44"/>
       <c r="AW21" s="1"/>
-      <c r="BD21" s="1"/>
+      <c r="AX21" s="1"/>
+      <c r="BE21" s="1"/>
     </row>
-    <row r="22" spans="1:56" ht="25.5">
+    <row r="22" spans="1:57" ht="25.5">
       <c r="A22" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8760,37 +8799,38 @@
       <c r="AK22" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL22" s="5" t="s">
+      <c r="AL22" s="11"/>
+      <c r="AM22" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM22" s="11" t="s">
+      <c r="AN22" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="AN22" s="11" t="s">
+      <c r="AO22" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="AO22" s="32" t="s">
+      <c r="AP22" s="32" t="s">
         <v>460</v>
       </c>
-      <c r="AP22" s="36" t="s">
+      <c r="AQ22" s="36" t="s">
         <v>770</v>
       </c>
-      <c r="AQ22" s="5" t="s">
+      <c r="AR22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR22" s="11" t="s">
+      <c r="AS22" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS22" s="13" t="s">
+      <c r="AT22" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT22" s="14"/>
-      <c r="AU22" s="44"/>
-      <c r="AV22" s="1"/>
+      <c r="AU22" s="14"/>
+      <c r="AV22" s="44"/>
       <c r="AW22" s="1"/>
-      <c r="BD22" s="1"/>
+      <c r="AX22" s="1"/>
+      <c r="BE22" s="1"/>
     </row>
-    <row r="23" spans="1:56" ht="25.5">
+    <row r="23" spans="1:57" ht="25.5">
       <c r="A23" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8914,37 +8954,38 @@
       <c r="AK23" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL23" s="5" t="s">
+      <c r="AL23" s="11"/>
+      <c r="AM23" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM23" s="11" t="s">
+      <c r="AN23" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="AN23" s="11" t="s">
+      <c r="AO23" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="AO23" s="32" t="s">
+      <c r="AP23" s="32" t="s">
         <v>461</v>
       </c>
-      <c r="AP23" s="36" t="s">
+      <c r="AQ23" s="36" t="s">
         <v>771</v>
       </c>
-      <c r="AQ23" s="5" t="s">
+      <c r="AR23" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR23" s="11" t="s">
+      <c r="AS23" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS23" s="13" t="s">
+      <c r="AT23" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT23" s="14"/>
-      <c r="AU23" s="44"/>
-      <c r="AV23" s="1"/>
+      <c r="AU23" s="14"/>
+      <c r="AV23" s="44"/>
       <c r="AW23" s="1"/>
-      <c r="BD23" s="1"/>
+      <c r="AX23" s="1"/>
+      <c r="BE23" s="1"/>
     </row>
-    <row r="24" spans="1:56" ht="25.5">
+    <row r="24" spans="1:57" ht="25.5">
       <c r="A24" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9068,37 +9109,38 @@
       <c r="AK24" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL24" s="5" t="s">
+      <c r="AL24" s="11"/>
+      <c r="AM24" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM24" s="11" t="s">
+      <c r="AN24" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="AN24" s="11" t="s">
+      <c r="AO24" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="AO24" s="32" t="s">
+      <c r="AP24" s="32" t="s">
         <v>462</v>
       </c>
-      <c r="AP24" s="36" t="s">
+      <c r="AQ24" s="36" t="s">
         <v>772</v>
       </c>
-      <c r="AQ24" s="5" t="s">
+      <c r="AR24" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR24" s="11" t="s">
+      <c r="AS24" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS24" s="13" t="s">
+      <c r="AT24" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT24" s="14"/>
-      <c r="AU24" s="44"/>
-      <c r="AV24" s="1"/>
+      <c r="AU24" s="14"/>
+      <c r="AV24" s="44"/>
       <c r="AW24" s="1"/>
-      <c r="BD24" s="1"/>
+      <c r="AX24" s="1"/>
+      <c r="BE24" s="1"/>
     </row>
-    <row r="25" spans="1:56" ht="25.5">
+    <row r="25" spans="1:57" ht="25.5">
       <c r="A25" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9222,37 +9264,38 @@
       <c r="AK25" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL25" s="5" t="s">
+      <c r="AL25" s="11"/>
+      <c r="AM25" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM25" s="11" t="s">
+      <c r="AN25" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="AN25" s="11" t="s">
+      <c r="AO25" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="AO25" s="32" t="s">
+      <c r="AP25" s="32" t="s">
         <v>463</v>
       </c>
-      <c r="AP25" s="36" t="s">
+      <c r="AQ25" s="36" t="s">
         <v>773</v>
       </c>
-      <c r="AQ25" s="5" t="s">
+      <c r="AR25" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR25" s="11" t="s">
+      <c r="AS25" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS25" s="13" t="s">
+      <c r="AT25" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT25" s="14"/>
-      <c r="AU25" s="44"/>
-      <c r="AV25" s="1"/>
+      <c r="AU25" s="14"/>
+      <c r="AV25" s="44"/>
       <c r="AW25" s="1"/>
-      <c r="BD25" s="1"/>
+      <c r="AX25" s="1"/>
+      <c r="BE25" s="1"/>
     </row>
-    <row r="26" spans="1:56" ht="25.5">
+    <row r="26" spans="1:57" ht="25.5">
       <c r="A26" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9376,37 +9419,38 @@
       <c r="AK26" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL26" s="5" t="s">
+      <c r="AL26" s="11"/>
+      <c r="AM26" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM26" s="11" t="s">
+      <c r="AN26" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="AN26" s="11" t="s">
+      <c r="AO26" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="AO26" s="32" t="s">
+      <c r="AP26" s="32" t="s">
         <v>464</v>
       </c>
-      <c r="AP26" s="36" t="s">
+      <c r="AQ26" s="36" t="s">
         <v>774</v>
       </c>
-      <c r="AQ26" s="5" t="s">
+      <c r="AR26" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR26" s="11" t="s">
+      <c r="AS26" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS26" s="13" t="s">
+      <c r="AT26" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT26" s="14"/>
-      <c r="AU26" s="44"/>
-      <c r="AV26" s="1"/>
+      <c r="AU26" s="14"/>
+      <c r="AV26" s="44"/>
       <c r="AW26" s="1"/>
-      <c r="BD26" s="1"/>
+      <c r="AX26" s="1"/>
+      <c r="BE26" s="1"/>
     </row>
-    <row r="27" spans="1:56" ht="25.5">
+    <row r="27" spans="1:57" ht="25.5">
       <c r="A27" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9530,37 +9574,38 @@
       <c r="AK27" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL27" s="5" t="s">
+      <c r="AL27" s="11"/>
+      <c r="AM27" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM27" s="11" t="s">
+      <c r="AN27" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="AN27" s="11" t="s">
+      <c r="AO27" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="AO27" s="32" t="s">
+      <c r="AP27" s="32" t="s">
         <v>465</v>
       </c>
-      <c r="AP27" s="36" t="s">
+      <c r="AQ27" s="36" t="s">
         <v>775</v>
       </c>
-      <c r="AQ27" s="5" t="s">
+      <c r="AR27" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR27" s="11" t="s">
+      <c r="AS27" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS27" s="13" t="s">
+      <c r="AT27" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT27" s="14"/>
-      <c r="AU27" s="44"/>
-      <c r="AV27" s="1"/>
+      <c r="AU27" s="14"/>
+      <c r="AV27" s="44"/>
       <c r="AW27" s="1"/>
-      <c r="BD27" s="1"/>
+      <c r="AX27" s="1"/>
+      <c r="BE27" s="1"/>
     </row>
-    <row r="28" spans="1:56" ht="25.5">
+    <row r="28" spans="1:57" ht="25.5">
       <c r="A28" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9684,37 +9729,38 @@
       <c r="AK28" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL28" s="5" t="s">
+      <c r="AL28" s="11"/>
+      <c r="AM28" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM28" s="11" t="s">
+      <c r="AN28" s="11" t="s">
         <v>601</v>
       </c>
-      <c r="AN28" s="11" t="s">
+      <c r="AO28" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="AO28" s="32" t="s">
+      <c r="AP28" s="32" t="s">
         <v>466</v>
       </c>
-      <c r="AP28" s="36" t="s">
+      <c r="AQ28" s="36" t="s">
         <v>776</v>
       </c>
-      <c r="AQ28" s="5" t="s">
+      <c r="AR28" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR28" s="11" t="s">
+      <c r="AS28" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS28" s="13" t="s">
+      <c r="AT28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT28" s="14"/>
-      <c r="AU28" s="44"/>
-      <c r="AV28" s="1"/>
+      <c r="AU28" s="14"/>
+      <c r="AV28" s="44"/>
       <c r="AW28" s="1"/>
-      <c r="BD28" s="1"/>
+      <c r="AX28" s="1"/>
+      <c r="BE28" s="1"/>
     </row>
-    <row r="29" spans="1:56" ht="25.5">
+    <row r="29" spans="1:57" ht="25.5">
       <c r="A29" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9838,37 +9884,38 @@
       <c r="AK29" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL29" s="5" t="s">
+      <c r="AL29" s="11"/>
+      <c r="AM29" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM29" s="11" t="s">
+      <c r="AN29" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="AN29" s="11" t="s">
+      <c r="AO29" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="AO29" s="32" t="s">
+      <c r="AP29" s="32" t="s">
         <v>467</v>
       </c>
-      <c r="AP29" s="36" t="s">
+      <c r="AQ29" s="36" t="s">
         <v>777</v>
       </c>
-      <c r="AQ29" s="5" t="s">
+      <c r="AR29" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR29" s="11" t="s">
+      <c r="AS29" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS29" s="13" t="s">
+      <c r="AT29" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT29" s="14"/>
-      <c r="AU29" s="44"/>
-      <c r="AV29" s="1"/>
+      <c r="AU29" s="14"/>
+      <c r="AV29" s="44"/>
       <c r="AW29" s="1"/>
-      <c r="BD29" s="1"/>
+      <c r="AX29" s="1"/>
+      <c r="BE29" s="1"/>
     </row>
-    <row r="30" spans="1:56" ht="25.5">
+    <row r="30" spans="1:57" ht="25.5">
       <c r="A30" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9992,37 +10039,38 @@
       <c r="AK30" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="AL30" s="5" t="s">
+      <c r="AL30" s="11"/>
+      <c r="AM30" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM30" s="11" t="s">
+      <c r="AN30" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="AN30" s="11" t="s">
+      <c r="AO30" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="AO30" s="32" t="s">
+      <c r="AP30" s="32" t="s">
         <v>468</v>
       </c>
-      <c r="AP30" s="36" t="s">
+      <c r="AQ30" s="36" t="s">
         <v>778</v>
       </c>
-      <c r="AQ30" s="5" t="s">
+      <c r="AR30" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR30" s="11" t="s">
+      <c r="AS30" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS30" s="13" t="s">
+      <c r="AT30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AT30" s="14"/>
-      <c r="AU30" s="44"/>
-      <c r="AV30" s="1"/>
+      <c r="AU30" s="14"/>
+      <c r="AV30" s="44"/>
       <c r="AW30" s="1"/>
-      <c r="BD30" s="1"/>
+      <c r="AX30" s="1"/>
+      <c r="BE30" s="1"/>
     </row>
-    <row r="31" spans="1:56" ht="25.5">
+    <row r="31" spans="1:57" ht="25.5">
       <c r="A31" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10146,37 +10194,38 @@
       <c r="AK31" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="AL31" s="5" t="s">
+      <c r="AL31" s="11"/>
+      <c r="AM31" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM31" s="11" t="s">
+      <c r="AN31" s="11" t="s">
         <v>614</v>
       </c>
-      <c r="AN31" s="11" t="s">
+      <c r="AO31" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="AO31" s="32" t="s">
+      <c r="AP31" s="32" t="s">
         <v>469</v>
       </c>
-      <c r="AP31" s="35" t="s">
+      <c r="AQ31" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ31" s="5" t="s">
+      <c r="AR31" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR31" s="11" t="s">
+      <c r="AS31" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS31" s="13" t="s">
+      <c r="AT31" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT31" s="14"/>
-      <c r="AU31" s="44"/>
-      <c r="AV31" s="1"/>
+      <c r="AU31" s="14"/>
+      <c r="AV31" s="44"/>
       <c r="AW31" s="1"/>
-      <c r="BD31" s="1"/>
+      <c r="AX31" s="1"/>
+      <c r="BE31" s="1"/>
     </row>
-    <row r="32" spans="1:56" ht="25.5">
+    <row r="32" spans="1:57" ht="25.5">
       <c r="A32" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10298,37 +10347,38 @@
       <c r="AK32" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="AL32" s="5" t="s">
+      <c r="AL32" s="11"/>
+      <c r="AM32" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM32" s="11" t="s">
+      <c r="AN32" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="AN32" s="11" t="s">
+      <c r="AO32" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="AO32" s="11" t="s">
+      <c r="AP32" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="AP32" s="35" t="s">
+      <c r="AQ32" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ32" s="5" t="s">
+      <c r="AR32" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR32" s="11" t="s">
+      <c r="AS32" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS32" s="13" t="s">
+      <c r="AT32" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT32" s="14"/>
-      <c r="AU32" s="44"/>
-      <c r="AV32" s="1"/>
+      <c r="AU32" s="14"/>
+      <c r="AV32" s="44"/>
       <c r="AW32" s="1"/>
-      <c r="BD32" s="1"/>
+      <c r="AX32" s="1"/>
+      <c r="BE32" s="1"/>
     </row>
-    <row r="33" spans="1:56" ht="25.5">
+    <row r="33" spans="1:57" ht="25.5">
       <c r="A33" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10452,37 +10502,38 @@
       <c r="AK33" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="AL33" s="5" t="s">
+      <c r="AL33" s="11"/>
+      <c r="AM33" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM33" s="11" t="s">
+      <c r="AN33" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="AN33" s="11" t="s">
+      <c r="AO33" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="AO33" s="32" t="s">
+      <c r="AP33" s="32" t="s">
         <v>471</v>
       </c>
-      <c r="AP33" s="35" t="s">
+      <c r="AQ33" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ33" s="5" t="s">
+      <c r="AR33" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR33" s="11" t="s">
+      <c r="AS33" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS33" s="13" t="s">
+      <c r="AT33" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT33" s="14"/>
-      <c r="AU33" s="44"/>
-      <c r="AV33" s="1"/>
+      <c r="AU33" s="14"/>
+      <c r="AV33" s="44"/>
       <c r="AW33" s="1"/>
-      <c r="BD33" s="1"/>
+      <c r="AX33" s="1"/>
+      <c r="BE33" s="1"/>
     </row>
-    <row r="34" spans="1:56" ht="25.5">
+    <row r="34" spans="1:57" ht="25.5">
       <c r="A34" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10606,37 +10657,38 @@
       <c r="AK34" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="AL34" s="5" t="s">
+      <c r="AL34" s="11"/>
+      <c r="AM34" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM34" s="11" t="s">
+      <c r="AN34" s="11" t="s">
         <v>620</v>
       </c>
-      <c r="AN34" s="11" t="s">
+      <c r="AO34" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="AO34" s="11" t="s">
+      <c r="AP34" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="AP34" s="35" t="s">
+      <c r="AQ34" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ34" s="5" t="s">
+      <c r="AR34" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR34" s="11" t="s">
+      <c r="AS34" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS34" s="13" t="s">
+      <c r="AT34" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT34" s="14"/>
-      <c r="AU34" s="44"/>
-      <c r="AV34" s="1"/>
+      <c r="AU34" s="14"/>
+      <c r="AV34" s="44"/>
       <c r="AW34" s="1"/>
-      <c r="BD34" s="1"/>
+      <c r="AX34" s="1"/>
+      <c r="BE34" s="1"/>
     </row>
-    <row r="35" spans="1:56" ht="25.5">
+    <row r="35" spans="1:57" ht="25.5">
       <c r="A35" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10760,37 +10812,38 @@
       <c r="AK35" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="AL35" s="5" t="s">
+      <c r="AL35" s="11"/>
+      <c r="AM35" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM35" s="11" t="s">
+      <c r="AN35" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="AN35" s="11" t="s">
+      <c r="AO35" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="AO35" s="32" t="s">
+      <c r="AP35" s="32" t="s">
         <v>473</v>
       </c>
-      <c r="AP35" s="35" t="s">
+      <c r="AQ35" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ35" s="5" t="s">
+      <c r="AR35" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR35" s="11" t="s">
+      <c r="AS35" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS35" s="13" t="s">
+      <c r="AT35" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT35" s="14"/>
-      <c r="AU35" s="44"/>
-      <c r="AV35" s="1"/>
+      <c r="AU35" s="14"/>
+      <c r="AV35" s="44"/>
       <c r="AW35" s="1"/>
-      <c r="BD35" s="1"/>
+      <c r="AX35" s="1"/>
+      <c r="BE35" s="1"/>
     </row>
-    <row r="36" spans="1:56" ht="25.5">
+    <row r="36" spans="1:57" ht="25.5">
       <c r="A36" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10914,37 +10967,38 @@
       <c r="AK36" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="AL36" s="5" t="s">
+      <c r="AL36" s="11"/>
+      <c r="AM36" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM36" s="11" t="s">
+      <c r="AN36" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="AN36" s="11" t="s">
+      <c r="AO36" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="AO36" s="11" t="s">
+      <c r="AP36" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="AP36" s="35" t="s">
+      <c r="AQ36" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ36" s="5" t="s">
+      <c r="AR36" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR36" s="11" t="s">
+      <c r="AS36" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS36" s="13" t="s">
+      <c r="AT36" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT36" s="14"/>
-      <c r="AU36" s="44"/>
-      <c r="AV36" s="1"/>
+      <c r="AU36" s="14"/>
+      <c r="AV36" s="44"/>
       <c r="AW36" s="1"/>
-      <c r="BD36" s="1"/>
+      <c r="AX36" s="1"/>
+      <c r="BE36" s="1"/>
     </row>
-    <row r="37" spans="1:56" ht="25.5">
+    <row r="37" spans="1:57" ht="25.5">
       <c r="A37" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -11068,37 +11122,38 @@
       <c r="AK37" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="AL37" s="5" t="s">
+      <c r="AL37" s="11"/>
+      <c r="AM37" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM37" s="11" t="s">
+      <c r="AN37" s="11" t="s">
         <v>626</v>
       </c>
-      <c r="AN37" s="11" t="s">
+      <c r="AO37" s="11" t="s">
         <v>627</v>
       </c>
-      <c r="AO37" s="32" t="s">
+      <c r="AP37" s="32" t="s">
         <v>475</v>
       </c>
-      <c r="AP37" s="35" t="s">
+      <c r="AQ37" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ37" s="5" t="s">
+      <c r="AR37" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR37" s="11" t="s">
+      <c r="AS37" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS37" s="13" t="s">
+      <c r="AT37" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT37" s="14"/>
-      <c r="AU37" s="44"/>
-      <c r="AV37" s="1"/>
+      <c r="AU37" s="14"/>
+      <c r="AV37" s="44"/>
       <c r="AW37" s="1"/>
-      <c r="BD37" s="1"/>
+      <c r="AX37" s="1"/>
+      <c r="BE37" s="1"/>
     </row>
-    <row r="38" spans="1:56" ht="25.5">
+    <row r="38" spans="1:57" ht="25.5">
       <c r="A38" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -11222,37 +11277,38 @@
       <c r="AK38" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="AL38" s="5" t="s">
+      <c r="AL38" s="11"/>
+      <c r="AM38" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM38" s="11" t="s">
+      <c r="AN38" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="AN38" s="11" t="s">
+      <c r="AO38" s="11" t="s">
         <v>629</v>
       </c>
-      <c r="AO38" s="11" t="s">
+      <c r="AP38" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="AP38" s="35" t="s">
+      <c r="AQ38" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ38" s="5" t="s">
+      <c r="AR38" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR38" s="11" t="s">
+      <c r="AS38" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS38" s="13" t="s">
+      <c r="AT38" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT38" s="14"/>
-      <c r="AU38" s="44"/>
-      <c r="AV38" s="1"/>
+      <c r="AU38" s="14"/>
+      <c r="AV38" s="44"/>
       <c r="AW38" s="1"/>
-      <c r="BD38" s="1"/>
+      <c r="AX38" s="1"/>
+      <c r="BE38" s="1"/>
     </row>
-    <row r="39" spans="1:56" ht="25.5">
+    <row r="39" spans="1:57" ht="25.5">
       <c r="A39" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -11376,37 +11432,38 @@
       <c r="AK39" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="AL39" s="5" t="s">
+      <c r="AL39" s="11"/>
+      <c r="AM39" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM39" s="11" t="s">
+      <c r="AN39" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="AN39" s="11" t="s">
+      <c r="AO39" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="AO39" s="32" t="s">
+      <c r="AP39" s="32" t="s">
         <v>613</v>
       </c>
-      <c r="AP39" s="35" t="s">
+      <c r="AQ39" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="AQ39" s="5" t="s">
+      <c r="AR39" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR39" s="11" t="s">
+      <c r="AS39" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AS39" s="13" t="s">
+      <c r="AT39" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AT39" s="14"/>
-      <c r="AU39" s="44"/>
-      <c r="AV39" s="1"/>
+      <c r="AU39" s="14"/>
+      <c r="AV39" s="44"/>
       <c r="AW39" s="1"/>
-      <c r="BD39" s="1"/>
+      <c r="AX39" s="1"/>
+      <c r="BE39" s="1"/>
     </row>
-    <row r="40" spans="1:56" ht="25.5">
+    <row r="40" spans="1:57" ht="25.5">
       <c r="A40" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Auvergne-Rhône-Alpes</v>
@@ -11530,37 +11587,38 @@
       <c r="AK40" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="AL40" s="5" t="s">
+      <c r="AL40" s="5"/>
+      <c r="AM40" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM40" s="5" t="s">
+      <c r="AN40" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="AN40" s="5" t="s">
+      <c r="AO40" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="AO40" s="32" t="s">
+      <c r="AP40" s="32" t="s">
         <v>477</v>
       </c>
-      <c r="AP40" s="35" t="s">
+      <c r="AQ40" s="35" t="s">
         <v>780</v>
       </c>
-      <c r="AQ40" s="5" t="s">
+      <c r="AR40" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR40" s="11" t="s">
+      <c r="AS40" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="AS40" s="13" t="s">
+      <c r="AT40" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT40" s="14"/>
-      <c r="AU40" s="44"/>
-      <c r="AV40" s="1"/>
+      <c r="AU40" s="14"/>
+      <c r="AV40" s="44"/>
       <c r="AW40" s="1"/>
-      <c r="BD40" s="1"/>
+      <c r="AX40" s="1"/>
+      <c r="BE40" s="1"/>
     </row>
-    <row r="41" spans="1:56" ht="25.5">
+    <row r="41" spans="1:57" ht="25.5">
       <c r="A41" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -11684,37 +11742,38 @@
       <c r="AK41" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="AL41" s="5" t="s">
+      <c r="AL41" s="5"/>
+      <c r="AM41" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM41" s="5" t="s">
+      <c r="AN41" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="AN41" s="5" t="s">
+      <c r="AO41" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="AO41" s="32" t="s">
+      <c r="AP41" s="32" t="s">
         <v>478</v>
       </c>
-      <c r="AP41" s="35" t="s">
+      <c r="AQ41" s="35" t="s">
         <v>781</v>
       </c>
-      <c r="AQ41" s="5" t="s">
+      <c r="AR41" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR41" s="5" t="s">
+      <c r="AS41" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AS41" s="7" t="s">
+      <c r="AT41" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT41" s="9"/>
-      <c r="AU41" s="44"/>
-      <c r="AV41" s="1"/>
+      <c r="AU41" s="9"/>
+      <c r="AV41" s="44"/>
       <c r="AW41" s="1"/>
-      <c r="BD41" s="1"/>
+      <c r="AX41" s="1"/>
+      <c r="BE41" s="1"/>
     </row>
-    <row r="42" spans="1:56" ht="25.5">
+    <row r="42" spans="1:57" ht="25.5">
       <c r="A42" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -11834,37 +11893,38 @@
       <c r="AK42" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="AL42" s="5" t="s">
+      <c r="AL42" s="5"/>
+      <c r="AM42" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM42" s="11" t="s">
+      <c r="AN42" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="AN42" s="11" t="s">
+      <c r="AO42" s="11" t="s">
         <v>637</v>
       </c>
-      <c r="AO42" s="32" t="s">
+      <c r="AP42" s="32" t="s">
         <v>479</v>
       </c>
-      <c r="AP42" s="35" t="s">
+      <c r="AQ42" s="35" t="s">
         <v>782</v>
       </c>
-      <c r="AQ42" s="5" t="s">
+      <c r="AR42" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR42" s="5" t="s">
+      <c r="AS42" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AS42" s="7" t="s">
+      <c r="AT42" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT42" s="14"/>
-      <c r="AU42" s="44"/>
-      <c r="AV42" s="1"/>
+      <c r="AU42" s="14"/>
+      <c r="AV42" s="44"/>
       <c r="AW42" s="1"/>
-      <c r="BD42" s="1"/>
+      <c r="AX42" s="1"/>
+      <c r="BE42" s="1"/>
     </row>
-    <row r="43" spans="1:56" ht="25.5">
+    <row r="43" spans="1:57" ht="25.5">
       <c r="A43" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -11984,37 +12044,38 @@
       <c r="AK43" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="AL43" s="5" t="s">
+      <c r="AL43" s="5"/>
+      <c r="AM43" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM43" s="11" t="s">
+      <c r="AN43" s="11" t="s">
         <v>638</v>
       </c>
-      <c r="AN43" s="11" t="s">
+      <c r="AO43" s="11" t="s">
         <v>639</v>
       </c>
-      <c r="AO43" s="32" t="s">
+      <c r="AP43" s="32" t="s">
         <v>480</v>
       </c>
-      <c r="AP43" s="35" t="s">
+      <c r="AQ43" s="35" t="s">
         <v>783</v>
       </c>
-      <c r="AQ43" s="5" t="s">
+      <c r="AR43" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR43" s="5" t="s">
+      <c r="AS43" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AS43" s="7" t="s">
+      <c r="AT43" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT43" s="14"/>
-      <c r="AU43" s="44"/>
-      <c r="AV43" s="1"/>
+      <c r="AU43" s="14"/>
+      <c r="AV43" s="44"/>
       <c r="AW43" s="1"/>
-      <c r="BD43" s="1"/>
+      <c r="AX43" s="1"/>
+      <c r="BE43" s="1"/>
     </row>
-    <row r="44" spans="1:56" ht="25.5">
+    <row r="44" spans="1:57" ht="25.5">
       <c r="A44" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12134,37 +12195,38 @@
       <c r="AK44" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="AL44" s="5" t="s">
+      <c r="AL44" s="5"/>
+      <c r="AM44" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM44" s="11" t="s">
+      <c r="AN44" s="11" t="s">
         <v>640</v>
       </c>
-      <c r="AN44" s="11" t="s">
+      <c r="AO44" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="AO44" s="32" t="s">
+      <c r="AP44" s="32" t="s">
         <v>481</v>
       </c>
-      <c r="AP44" s="35" t="s">
+      <c r="AQ44" s="35" t="s">
         <v>784</v>
       </c>
-      <c r="AQ44" s="5" t="s">
+      <c r="AR44" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR44" s="5" t="s">
+      <c r="AS44" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AS44" s="7" t="s">
+      <c r="AT44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT44" s="14"/>
-      <c r="AU44" s="44"/>
-      <c r="AV44" s="1"/>
+      <c r="AU44" s="14"/>
+      <c r="AV44" s="44"/>
       <c r="AW44" s="1"/>
-      <c r="BD44" s="1"/>
+      <c r="AX44" s="1"/>
+      <c r="BE44" s="1"/>
     </row>
-    <row r="45" spans="1:56" ht="25.5">
+    <row r="45" spans="1:57" ht="25.5">
       <c r="A45" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12288,37 +12350,38 @@
       <c r="AK45" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="AL45" s="5" t="s">
+      <c r="AL45" s="5"/>
+      <c r="AM45" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM45" s="11" t="s">
+      <c r="AN45" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="AN45" s="11" t="s">
+      <c r="AO45" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="AO45" s="32" t="s">
+      <c r="AP45" s="32" t="s">
         <v>482</v>
       </c>
-      <c r="AP45" s="35" t="s">
+      <c r="AQ45" s="35" t="s">
         <v>785</v>
       </c>
-      <c r="AQ45" s="5" t="s">
+      <c r="AR45" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR45" s="5" t="s">
+      <c r="AS45" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AS45" s="7" t="s">
+      <c r="AT45" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT45" s="14"/>
-      <c r="AU45" s="44"/>
-      <c r="AV45" s="1"/>
+      <c r="AU45" s="14"/>
+      <c r="AV45" s="44"/>
       <c r="AW45" s="1"/>
-      <c r="BD45" s="1"/>
+      <c r="AX45" s="1"/>
+      <c r="BE45" s="1"/>
     </row>
-    <row r="46" spans="1:56" ht="25.5">
+    <row r="46" spans="1:57" ht="25.5">
       <c r="A46" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12442,37 +12505,38 @@
       <c r="AK46" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="AL46" s="5" t="s">
+      <c r="AL46" s="5"/>
+      <c r="AM46" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM46" s="11" t="s">
+      <c r="AN46" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="AN46" s="11" t="s">
+      <c r="AO46" s="11" t="s">
         <v>645</v>
       </c>
-      <c r="AO46" s="32" t="s">
+      <c r="AP46" s="32" t="s">
         <v>483</v>
       </c>
-      <c r="AP46" s="35" t="s">
+      <c r="AQ46" s="35" t="s">
         <v>786</v>
       </c>
-      <c r="AQ46" s="11" t="s">
+      <c r="AR46" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="AR46" s="5" t="s">
+      <c r="AS46" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AS46" s="7" t="s">
+      <c r="AT46" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT46" s="14"/>
-      <c r="AU46" s="44"/>
-      <c r="AV46" s="1"/>
+      <c r="AU46" s="14"/>
+      <c r="AV46" s="44"/>
       <c r="AW46" s="1"/>
-      <c r="BD46" s="1"/>
+      <c r="AX46" s="1"/>
+      <c r="BE46" s="1"/>
     </row>
-    <row r="47" spans="1:56" ht="25.5">
+    <row r="47" spans="1:57" ht="25.5">
       <c r="A47" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -12596,37 +12660,38 @@
       <c r="AK47" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="AL47" s="5" t="s">
+      <c r="AL47" s="5"/>
+      <c r="AM47" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM47" s="5" t="s">
+      <c r="AN47" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="AN47" s="5" t="s">
+      <c r="AO47" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="AO47" s="32" t="s">
+      <c r="AP47" s="32" t="s">
         <v>484</v>
       </c>
-      <c r="AP47" s="35" t="s">
+      <c r="AQ47" s="35" t="s">
         <v>787</v>
       </c>
-      <c r="AQ47" s="5" t="s">
+      <c r="AR47" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR47" s="5" t="s">
+      <c r="AS47" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AS47" s="7" t="s">
+      <c r="AT47" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT47" s="8"/>
-      <c r="AU47" s="44"/>
-      <c r="AV47" s="1"/>
+      <c r="AU47" s="8"/>
+      <c r="AV47" s="44"/>
       <c r="AW47" s="1"/>
-      <c r="BD47" s="1"/>
+      <c r="AX47" s="1"/>
+      <c r="BE47" s="1"/>
     </row>
-    <row r="48" spans="1:56" ht="25.5">
+    <row r="48" spans="1:57" ht="25.5">
       <c r="A48" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -12750,37 +12815,38 @@
       <c r="AK48" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="AL48" s="5" t="s">
+      <c r="AL48" s="11"/>
+      <c r="AM48" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM48" s="11" t="s">
+      <c r="AN48" s="11" t="s">
         <v>648</v>
       </c>
-      <c r="AN48" s="11" t="s">
+      <c r="AO48" s="11" t="s">
         <v>649</v>
       </c>
-      <c r="AO48" s="32" t="s">
+      <c r="AP48" s="32" t="s">
         <v>485</v>
       </c>
-      <c r="AP48" s="35" t="s">
+      <c r="AQ48" s="35" t="s">
         <v>788</v>
       </c>
-      <c r="AQ48" s="5" t="s">
+      <c r="AR48" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR48" s="11" t="s">
+      <c r="AS48" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AS48" s="7" t="s">
+      <c r="AT48" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT48" s="14"/>
-      <c r="AU48" s="44"/>
-      <c r="AV48" s="1"/>
+      <c r="AU48" s="14"/>
+      <c r="AV48" s="44"/>
       <c r="AW48" s="1"/>
-      <c r="BD48" s="1"/>
+      <c r="AX48" s="1"/>
+      <c r="BE48" s="1"/>
     </row>
-    <row r="49" spans="1:56" ht="25.5">
+    <row r="49" spans="1:57" ht="25.5">
       <c r="A49" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12904,37 +12970,38 @@
       <c r="AK49" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="AL49" s="5" t="s">
+      <c r="AL49" s="11"/>
+      <c r="AM49" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM49" s="11" t="s">
+      <c r="AN49" s="11" t="s">
         <v>650</v>
       </c>
-      <c r="AN49" s="11" t="s">
+      <c r="AO49" s="11" t="s">
         <v>651</v>
       </c>
-      <c r="AO49" s="32" t="s">
+      <c r="AP49" s="32" t="s">
         <v>486</v>
       </c>
-      <c r="AP49" s="35" t="s">
+      <c r="AQ49" s="35" t="s">
         <v>789</v>
       </c>
-      <c r="AQ49" s="5" t="s">
+      <c r="AR49" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR49" s="11" t="s">
+      <c r="AS49" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS49" s="13" t="s">
+      <c r="AT49" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT49" s="14"/>
-      <c r="AU49" s="44"/>
-      <c r="AV49" s="1"/>
+      <c r="AU49" s="14"/>
+      <c r="AV49" s="44"/>
       <c r="AW49" s="1"/>
-      <c r="BD49" s="1"/>
+      <c r="AX49" s="1"/>
+      <c r="BE49" s="1"/>
     </row>
-    <row r="50" spans="1:56" ht="25.5">
+    <row r="50" spans="1:57" ht="25.5">
       <c r="A50" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13055,37 +13122,38 @@
       <c r="AK50" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="AL50" s="5" t="s">
+      <c r="AL50" s="11"/>
+      <c r="AM50" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM50" s="11" t="s">
+      <c r="AN50" s="11" t="s">
         <v>652</v>
       </c>
-      <c r="AN50" s="11" t="s">
+      <c r="AO50" s="11" t="s">
         <v>653</v>
       </c>
-      <c r="AO50" s="32" t="s">
+      <c r="AP50" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="AP50" s="35" t="s">
+      <c r="AQ50" s="35" t="s">
         <v>1266</v>
       </c>
-      <c r="AQ50" s="5" t="s">
+      <c r="AR50" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR50" s="11" t="s">
+      <c r="AS50" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AS50" s="13" t="s">
+      <c r="AT50" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT50" s="14"/>
-      <c r="AU50" s="44"/>
-      <c r="AV50" s="1"/>
+      <c r="AU50" s="14"/>
+      <c r="AV50" s="44"/>
       <c r="AW50" s="1"/>
-      <c r="BD50" s="1"/>
+      <c r="AX50" s="1"/>
+      <c r="BE50" s="1"/>
     </row>
-    <row r="51" spans="1:56" ht="25.5">
+    <row r="51" spans="1:57" ht="25.5">
       <c r="A51" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13209,35 +13277,36 @@
       <c r="AK51" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="AL51" s="5" t="s">
+      <c r="AL51" s="11"/>
+      <c r="AM51" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM51" s="11" t="s">
+      <c r="AN51" s="11" t="s">
         <v>654</v>
       </c>
-      <c r="AN51" s="11" t="s">
+      <c r="AO51" s="11" t="s">
         <v>655</v>
       </c>
-      <c r="AO51" s="32" t="s">
+      <c r="AP51" s="32" t="s">
         <v>487</v>
       </c>
-      <c r="AP51" s="35"/>
-      <c r="AQ51" s="5" t="s">
+      <c r="AQ51" s="35"/>
+      <c r="AR51" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AR51" s="11" t="s">
+      <c r="AS51" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="AS51" s="13" t="s">
+      <c r="AT51" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT51" s="14"/>
-      <c r="AU51" s="44"/>
-      <c r="AV51" s="1"/>
+      <c r="AU51" s="14"/>
+      <c r="AV51" s="44"/>
       <c r="AW51" s="1"/>
-      <c r="BD51" s="1"/>
+      <c r="AX51" s="1"/>
+      <c r="BE51" s="1"/>
     </row>
-    <row r="52" spans="1:56" ht="25.5">
+    <row r="52" spans="1:57" ht="25.5">
       <c r="A52" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13361,37 +13430,38 @@
       <c r="AK52" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="AL52" s="5" t="s">
+      <c r="AL52" s="11"/>
+      <c r="AM52" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM52" s="11" t="s">
+      <c r="AN52" s="11" t="s">
         <v>656</v>
       </c>
-      <c r="AN52" s="11" t="s">
+      <c r="AO52" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="AO52" s="32" t="s">
+      <c r="AP52" s="32" t="s">
         <v>488</v>
       </c>
-      <c r="AP52" s="35" t="s">
+      <c r="AQ52" s="35" t="s">
         <v>790</v>
       </c>
-      <c r="AQ52" s="5" t="s">
+      <c r="AR52" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR52" s="11" t="s">
+      <c r="AS52" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="AS52" s="13" t="s">
+      <c r="AT52" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT52" s="14"/>
-      <c r="AU52" s="44"/>
-      <c r="AV52" s="1"/>
+      <c r="AU52" s="14"/>
+      <c r="AV52" s="44"/>
       <c r="AW52" s="1"/>
-      <c r="BD52" s="1"/>
+      <c r="AX52" s="1"/>
+      <c r="BE52" s="1"/>
     </row>
-    <row r="53" spans="1:56" ht="25.5">
+    <row r="53" spans="1:57" ht="25.5">
       <c r="A53" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13515,37 +13585,38 @@
       <c r="AK53" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="AL53" s="5" t="s">
+      <c r="AL53" s="11"/>
+      <c r="AM53" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM53" s="11" t="s">
+      <c r="AN53" s="11" t="s">
         <v>658</v>
       </c>
-      <c r="AN53" s="11" t="s">
+      <c r="AO53" s="11" t="s">
         <v>659</v>
       </c>
-      <c r="AO53" s="32" t="s">
+      <c r="AP53" s="32" t="s">
         <v>489</v>
       </c>
-      <c r="AP53" s="35" t="s">
+      <c r="AQ53" s="35" t="s">
         <v>791</v>
       </c>
-      <c r="AQ53" s="5" t="s">
+      <c r="AR53" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR53" s="11" t="s">
+      <c r="AS53" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AS53" s="13" t="s">
+      <c r="AT53" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT53" s="14"/>
-      <c r="AU53" s="44"/>
-      <c r="AV53" s="1"/>
+      <c r="AU53" s="14"/>
+      <c r="AV53" s="44"/>
       <c r="AW53" s="1"/>
-      <c r="BD53" s="1"/>
+      <c r="AX53" s="1"/>
+      <c r="BE53" s="1"/>
     </row>
-    <row r="54" spans="1:56" ht="25.5">
+    <row r="54" spans="1:57" ht="25.5">
       <c r="A54" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13669,37 +13740,38 @@
       <c r="AK54" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="AL54" s="5" t="s">
+      <c r="AL54" s="11"/>
+      <c r="AM54" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM54" s="11" t="s">
+      <c r="AN54" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="AN54" s="11" t="s">
+      <c r="AO54" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="AO54" s="32" t="s">
+      <c r="AP54" s="32" t="s">
         <v>490</v>
       </c>
-      <c r="AP54" s="35" t="s">
+      <c r="AQ54" s="35" t="s">
         <v>792</v>
       </c>
-      <c r="AQ54" s="5" t="s">
+      <c r="AR54" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR54" s="11" t="s">
+      <c r="AS54" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AS54" s="13" t="s">
+      <c r="AT54" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT54" s="14"/>
-      <c r="AU54" s="44"/>
-      <c r="AV54" s="1"/>
+      <c r="AU54" s="14"/>
+      <c r="AV54" s="44"/>
       <c r="AW54" s="1"/>
-      <c r="BD54" s="1"/>
+      <c r="AX54" s="1"/>
+      <c r="BE54" s="1"/>
     </row>
-    <row r="55" spans="1:56" ht="25.5">
+    <row r="55" spans="1:57" ht="25.5">
       <c r="A55" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13823,37 +13895,38 @@
       <c r="AK55" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AL55" s="5" t="s">
+      <c r="AL55" s="11"/>
+      <c r="AM55" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM55" s="11" t="s">
+      <c r="AN55" s="11" t="s">
         <v>662</v>
       </c>
-      <c r="AN55" s="11" t="s">
+      <c r="AO55" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="AO55" s="32" t="s">
+      <c r="AP55" s="32" t="s">
         <v>491</v>
       </c>
-      <c r="AP55" s="35" t="s">
+      <c r="AQ55" s="35" t="s">
         <v>793</v>
       </c>
-      <c r="AQ55" s="5" t="s">
+      <c r="AR55" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR55" s="11" t="s">
+      <c r="AS55" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AS55" s="13" t="s">
+      <c r="AT55" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AT55" s="14"/>
-      <c r="AU55" s="44"/>
-      <c r="AV55" s="1"/>
+      <c r="AU55" s="14"/>
+      <c r="AV55" s="44"/>
       <c r="AW55" s="1"/>
-      <c r="BD55" s="1"/>
+      <c r="AX55" s="1"/>
+      <c r="BE55" s="1"/>
     </row>
-    <row r="56" spans="1:56" ht="25.5">
+    <row r="56" spans="1:57" ht="25.5">
       <c r="A56" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13977,37 +14050,38 @@
       <c r="AK56" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="AL56" s="5" t="s">
+      <c r="AL56" s="11"/>
+      <c r="AM56" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM56" s="11" t="s">
+      <c r="AN56" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="AN56" s="11" t="s">
+      <c r="AO56" s="11" t="s">
         <v>665</v>
       </c>
-      <c r="AO56" s="32" t="s">
+      <c r="AP56" s="32" t="s">
         <v>492</v>
       </c>
-      <c r="AP56" s="35" t="s">
+      <c r="AQ56" s="35" t="s">
         <v>794</v>
       </c>
-      <c r="AQ56" s="5" t="s">
+      <c r="AR56" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR56" s="11" t="s">
+      <c r="AS56" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="AS56" s="13" t="s">
+      <c r="AT56" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT56" s="14"/>
-      <c r="AU56" s="44"/>
-      <c r="AV56" s="1"/>
+      <c r="AU56" s="14"/>
+      <c r="AV56" s="44"/>
       <c r="AW56" s="1"/>
-      <c r="BD56" s="1"/>
+      <c r="AX56" s="1"/>
+      <c r="BE56" s="1"/>
     </row>
-    <row r="57" spans="1:56" ht="25.5">
+    <row r="57" spans="1:57" ht="25.5">
       <c r="A57" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14132,37 +14206,38 @@
       <c r="AK57" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL57" s="5" t="s">
+      <c r="AL57" s="5"/>
+      <c r="AM57" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM57" s="5" t="s">
+      <c r="AN57" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="AN57" s="5" t="s">
+      <c r="AO57" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="AO57" s="32" t="s">
+      <c r="AP57" s="32" t="s">
         <v>493</v>
       </c>
-      <c r="AP57" s="35" t="s">
+      <c r="AQ57" s="35" t="s">
         <v>795</v>
       </c>
-      <c r="AQ57" s="5" t="s">
+      <c r="AR57" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR57" s="11" t="s">
+      <c r="AS57" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS57" s="13" t="s">
+      <c r="AT57" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT57" s="14"/>
-      <c r="AU57" s="44"/>
-      <c r="AV57" s="1"/>
+      <c r="AU57" s="14"/>
+      <c r="AV57" s="44"/>
       <c r="AW57" s="1"/>
-      <c r="BD57" s="1"/>
+      <c r="AX57" s="1"/>
+      <c r="BE57" s="1"/>
     </row>
-    <row r="58" spans="1:56" ht="25.5">
+    <row r="58" spans="1:57" ht="25.5">
       <c r="A58" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14287,37 +14362,38 @@
       <c r="AK58" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL58" s="5" t="s">
+      <c r="AL58" s="5"/>
+      <c r="AM58" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM58" s="11" t="s">
+      <c r="AN58" s="11" t="s">
         <v>668</v>
       </c>
-      <c r="AN58" s="11" t="s">
+      <c r="AO58" s="11" t="s">
         <v>669</v>
       </c>
-      <c r="AO58" s="32" t="s">
+      <c r="AP58" s="32" t="s">
         <v>494</v>
       </c>
-      <c r="AP58" s="35" t="s">
+      <c r="AQ58" s="35" t="s">
         <v>796</v>
       </c>
-      <c r="AQ58" s="5" t="s">
+      <c r="AR58" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR58" s="11" t="s">
+      <c r="AS58" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS58" s="13" t="s">
+      <c r="AT58" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT58" s="14"/>
-      <c r="AU58" s="44"/>
-      <c r="AV58" s="1"/>
+      <c r="AU58" s="14"/>
+      <c r="AV58" s="44"/>
       <c r="AW58" s="1"/>
-      <c r="BD58" s="1"/>
+      <c r="AX58" s="1"/>
+      <c r="BE58" s="1"/>
     </row>
-    <row r="59" spans="1:56" ht="25.5">
+    <row r="59" spans="1:57" ht="25.5">
       <c r="A59" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14442,37 +14518,38 @@
       <c r="AK59" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL59" s="5" t="s">
+      <c r="AL59" s="5"/>
+      <c r="AM59" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM59" s="11" t="s">
+      <c r="AN59" s="11" t="s">
         <v>670</v>
       </c>
-      <c r="AN59" s="11" t="s">
+      <c r="AO59" s="11" t="s">
         <v>671</v>
       </c>
-      <c r="AO59" s="32" t="s">
+      <c r="AP59" s="32" t="s">
         <v>495</v>
       </c>
-      <c r="AP59" s="35" t="s">
+      <c r="AQ59" s="35" t="s">
         <v>797</v>
       </c>
-      <c r="AQ59" s="5" t="s">
+      <c r="AR59" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR59" s="11" t="s">
+      <c r="AS59" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS59" s="13" t="s">
+      <c r="AT59" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT59" s="14"/>
-      <c r="AU59" s="44"/>
-      <c r="AV59" s="1"/>
+      <c r="AU59" s="14"/>
+      <c r="AV59" s="44"/>
       <c r="AW59" s="1"/>
-      <c r="BD59" s="1"/>
+      <c r="AX59" s="1"/>
+      <c r="BE59" s="1"/>
     </row>
-    <row r="60" spans="1:56" ht="25.5">
+    <row r="60" spans="1:57" ht="25.5">
       <c r="A60" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14597,37 +14674,38 @@
       <c r="AK60" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL60" s="5" t="s">
+      <c r="AL60" s="5"/>
+      <c r="AM60" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM60" s="11" t="s">
+      <c r="AN60" s="11" t="s">
         <v>672</v>
       </c>
-      <c r="AN60" s="11" t="s">
+      <c r="AO60" s="11" t="s">
         <v>673</v>
       </c>
-      <c r="AO60" s="32" t="s">
+      <c r="AP60" s="32" t="s">
         <v>496</v>
       </c>
-      <c r="AP60" s="35" t="s">
+      <c r="AQ60" s="35" t="s">
         <v>798</v>
       </c>
-      <c r="AQ60" s="5" t="s">
+      <c r="AR60" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR60" s="11" t="s">
+      <c r="AS60" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS60" s="13" t="s">
+      <c r="AT60" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT60" s="14"/>
-      <c r="AU60" s="44"/>
-      <c r="AV60" s="1"/>
+      <c r="AU60" s="14"/>
+      <c r="AV60" s="44"/>
       <c r="AW60" s="1"/>
-      <c r="BD60" s="1"/>
+      <c r="AX60" s="1"/>
+      <c r="BE60" s="1"/>
     </row>
-    <row r="61" spans="1:56" ht="25.5">
+    <row r="61" spans="1:57" ht="25.5">
       <c r="A61" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14752,37 +14830,38 @@
       <c r="AK61" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL61" s="5" t="s">
+      <c r="AL61" s="5"/>
+      <c r="AM61" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM61" s="11" t="s">
+      <c r="AN61" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="AN61" s="11" t="s">
+      <c r="AO61" s="11" t="s">
         <v>675</v>
       </c>
-      <c r="AO61" s="32" t="s">
+      <c r="AP61" s="32" t="s">
         <v>497</v>
       </c>
-      <c r="AP61" s="35" t="s">
+      <c r="AQ61" s="35" t="s">
         <v>799</v>
       </c>
-      <c r="AQ61" s="5" t="s">
+      <c r="AR61" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR61" s="11" t="s">
+      <c r="AS61" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS61" s="13" t="s">
+      <c r="AT61" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT61" s="14"/>
-      <c r="AU61" s="44"/>
-      <c r="AV61" s="1"/>
+      <c r="AU61" s="14"/>
+      <c r="AV61" s="44"/>
       <c r="AW61" s="1"/>
-      <c r="BD61" s="1"/>
+      <c r="AX61" s="1"/>
+      <c r="BE61" s="1"/>
     </row>
-    <row r="62" spans="1:56" ht="25.5">
+    <row r="62" spans="1:57" ht="25.5">
       <c r="A62" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14907,37 +14986,38 @@
       <c r="AK62" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL62" s="5" t="s">
+      <c r="AL62" s="5"/>
+      <c r="AM62" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM62" s="11" t="s">
+      <c r="AN62" s="11" t="s">
         <v>676</v>
       </c>
-      <c r="AN62" s="11" t="s">
+      <c r="AO62" s="11" t="s">
         <v>675</v>
       </c>
-      <c r="AO62" s="32" t="s">
+      <c r="AP62" s="32" t="s">
         <v>498</v>
       </c>
-      <c r="AP62" s="35" t="s">
+      <c r="AQ62" s="35" t="s">
         <v>800</v>
       </c>
-      <c r="AQ62" s="5" t="s">
+      <c r="AR62" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR62" s="11" t="s">
+      <c r="AS62" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS62" s="13" t="s">
+      <c r="AT62" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT62" s="14"/>
-      <c r="AU62" s="44"/>
-      <c r="AV62" s="1"/>
+      <c r="AU62" s="14"/>
+      <c r="AV62" s="44"/>
       <c r="AW62" s="1"/>
-      <c r="BD62" s="1"/>
+      <c r="AX62" s="1"/>
+      <c r="BE62" s="1"/>
     </row>
-    <row r="63" spans="1:56" ht="25.5">
+    <row r="63" spans="1:57" ht="25.5">
       <c r="A63" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15062,37 +15142,38 @@
       <c r="AK63" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL63" s="5" t="s">
+      <c r="AL63" s="5"/>
+      <c r="AM63" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM63" s="11" t="s">
+      <c r="AN63" s="11" t="s">
         <v>677</v>
       </c>
-      <c r="AN63" s="11" t="s">
+      <c r="AO63" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="AO63" s="32" t="s">
+      <c r="AP63" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="AP63" s="35" t="s">
+      <c r="AQ63" s="35" t="s">
         <v>801</v>
       </c>
-      <c r="AQ63" s="5" t="s">
+      <c r="AR63" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR63" s="11" t="s">
+      <c r="AS63" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS63" s="13" t="s">
+      <c r="AT63" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT63" s="14"/>
-      <c r="AU63" s="44"/>
-      <c r="AV63" s="1"/>
+      <c r="AU63" s="14"/>
+      <c r="AV63" s="44"/>
       <c r="AW63" s="1"/>
-      <c r="BD63" s="1"/>
+      <c r="AX63" s="1"/>
+      <c r="BE63" s="1"/>
     </row>
-    <row r="64" spans="1:56" ht="25.5">
+    <row r="64" spans="1:57" ht="25.5">
       <c r="A64" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15217,37 +15298,38 @@
       <c r="AK64" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="AL64" s="5" t="s">
+      <c r="AL64" s="5"/>
+      <c r="AM64" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM64" s="11" t="s">
+      <c r="AN64" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="AN64" s="11" t="s">
+      <c r="AO64" s="11" t="s">
         <v>680</v>
       </c>
-      <c r="AO64" s="32" t="s">
+      <c r="AP64" s="32" t="s">
         <v>500</v>
       </c>
-      <c r="AP64" s="35" t="s">
+      <c r="AQ64" s="35" t="s">
         <v>802</v>
       </c>
-      <c r="AQ64" s="5" t="s">
+      <c r="AR64" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR64" s="11" t="s">
+      <c r="AS64" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS64" s="13" t="s">
+      <c r="AT64" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT64" s="14"/>
-      <c r="AU64" s="44"/>
-      <c r="AV64" s="1"/>
+      <c r="AU64" s="14"/>
+      <c r="AV64" s="44"/>
       <c r="AW64" s="1"/>
-      <c r="BD64" s="1"/>
+      <c r="AX64" s="1"/>
+      <c r="BE64" s="1"/>
     </row>
-    <row r="65" spans="1:56" ht="25.5">
+    <row r="65" spans="1:57" ht="25.5">
       <c r="A65" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15371,37 +15453,38 @@
       <c r="AK65" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="AL65" s="5" t="s">
+      <c r="AL65" s="5"/>
+      <c r="AM65" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM65" s="5" t="s">
+      <c r="AN65" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="AN65" s="5" t="s">
+      <c r="AO65" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="AO65" s="32" t="s">
+      <c r="AP65" s="32" t="s">
         <v>501</v>
       </c>
-      <c r="AP65" s="35" t="s">
+      <c r="AQ65" s="35" t="s">
         <v>803</v>
       </c>
-      <c r="AQ65" s="5" t="s">
+      <c r="AR65" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR65" s="11" t="s">
+      <c r="AS65" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="AS65" s="13" t="s">
+      <c r="AT65" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT65" s="14"/>
-      <c r="AU65" s="44"/>
-      <c r="AV65" s="1"/>
+      <c r="AU65" s="14"/>
+      <c r="AV65" s="44"/>
       <c r="AW65" s="1"/>
-      <c r="BD65" s="1"/>
+      <c r="AX65" s="1"/>
+      <c r="BE65" s="1"/>
     </row>
-    <row r="66" spans="1:56" ht="25.5">
+    <row r="66" spans="1:57" ht="25.5">
       <c r="A66" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15525,37 +15608,38 @@
       <c r="AK66" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="AL66" s="5" t="s">
+      <c r="AL66" s="5"/>
+      <c r="AM66" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM66" s="11" t="s">
+      <c r="AN66" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="AN66" s="11" t="s">
+      <c r="AO66" s="11" t="s">
         <v>684</v>
       </c>
-      <c r="AO66" s="32" t="s">
+      <c r="AP66" s="32" t="s">
         <v>502</v>
       </c>
-      <c r="AP66" s="36" t="s">
+      <c r="AQ66" s="36" t="s">
         <v>804</v>
       </c>
-      <c r="AQ66" s="5" t="s">
+      <c r="AR66" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR66" s="11" t="s">
+      <c r="AS66" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="AS66" s="13" t="s">
+      <c r="AT66" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT66" s="14"/>
-      <c r="AU66" s="44"/>
-      <c r="AV66" s="1"/>
+      <c r="AU66" s="14"/>
+      <c r="AV66" s="44"/>
       <c r="AW66" s="1"/>
-      <c r="BD66" s="1"/>
+      <c r="AX66" s="1"/>
+      <c r="BE66" s="1"/>
     </row>
-    <row r="67" spans="1:56" ht="25.5">
+    <row r="67" spans="1:57" ht="25.5">
       <c r="A67" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15680,37 +15764,38 @@
       <c r="AK67" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL67" s="5" t="s">
+      <c r="AL67" s="5"/>
+      <c r="AM67" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM67" s="5" t="s">
+      <c r="AN67" s="5" t="s">
         <v>861</v>
       </c>
-      <c r="AN67" s="5" t="s">
+      <c r="AO67" s="5" t="s">
         <v>862</v>
       </c>
-      <c r="AO67" s="32" t="s">
+      <c r="AP67" s="32" t="s">
         <v>503</v>
       </c>
-      <c r="AP67" s="35" t="s">
+      <c r="AQ67" s="35" t="s">
         <v>1072</v>
       </c>
-      <c r="AQ67" s="5" t="s">
+      <c r="AR67" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR67" s="11" t="s">
+      <c r="AS67" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS67" s="13" t="s">
+      <c r="AT67" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT67" s="14"/>
-      <c r="AU67" s="44"/>
-      <c r="AV67" s="1"/>
+      <c r="AU67" s="14"/>
+      <c r="AV67" s="44"/>
       <c r="AW67" s="1"/>
-      <c r="BD67" s="1"/>
+      <c r="AX67" s="1"/>
+      <c r="BE67" s="1"/>
     </row>
-    <row r="68" spans="1:56" ht="25.5">
+    <row r="68" spans="1:57" ht="25.5">
       <c r="A68" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15835,37 +15920,38 @@
       <c r="AK68" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL68" s="5" t="s">
+      <c r="AL68" s="5"/>
+      <c r="AM68" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM68" s="11" t="s">
+      <c r="AN68" s="11" t="s">
         <v>863</v>
       </c>
-      <c r="AN68" s="11" t="s">
+      <c r="AO68" s="11" t="s">
         <v>864</v>
       </c>
-      <c r="AO68" s="32" t="s">
+      <c r="AP68" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="AP68" s="35" t="s">
+      <c r="AQ68" s="35" t="s">
         <v>1073</v>
       </c>
-      <c r="AQ68" s="5" t="s">
+      <c r="AR68" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR68" s="11" t="s">
+      <c r="AS68" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS68" s="13" t="s">
+      <c r="AT68" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT68" s="14"/>
-      <c r="AU68" s="44"/>
-      <c r="AV68" s="1"/>
+      <c r="AU68" s="14"/>
+      <c r="AV68" s="44"/>
       <c r="AW68" s="1"/>
-      <c r="BD68" s="1"/>
+      <c r="AX68" s="1"/>
+      <c r="BE68" s="1"/>
     </row>
-    <row r="69" spans="1:56" ht="25.5">
+    <row r="69" spans="1:57" ht="25.5">
       <c r="A69" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15990,37 +16076,38 @@
       <c r="AK69" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL69" s="5" t="s">
+      <c r="AL69" s="5"/>
+      <c r="AM69" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM69" s="11" t="s">
+      <c r="AN69" s="11" t="s">
         <v>865</v>
       </c>
-      <c r="AN69" s="11" t="s">
+      <c r="AO69" s="11" t="s">
         <v>866</v>
       </c>
-      <c r="AO69" s="32" t="s">
+      <c r="AP69" s="32" t="s">
         <v>505</v>
       </c>
-      <c r="AP69" s="35" t="s">
+      <c r="AQ69" s="35" t="s">
         <v>1074</v>
       </c>
-      <c r="AQ69" s="5" t="s">
+      <c r="AR69" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR69" s="11" t="s">
+      <c r="AS69" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS69" s="13" t="s">
+      <c r="AT69" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT69" s="14"/>
-      <c r="AU69" s="44"/>
-      <c r="AV69" s="1"/>
+      <c r="AU69" s="14"/>
+      <c r="AV69" s="44"/>
       <c r="AW69" s="1"/>
-      <c r="BD69" s="1"/>
+      <c r="AX69" s="1"/>
+      <c r="BE69" s="1"/>
     </row>
-    <row r="70" spans="1:56" ht="25.5">
+    <row r="70" spans="1:57" ht="25.5">
       <c r="A70" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16145,37 +16232,38 @@
       <c r="AK70" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL70" s="5" t="s">
+      <c r="AL70" s="5"/>
+      <c r="AM70" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM70" s="11" t="s">
+      <c r="AN70" s="11" t="s">
         <v>867</v>
       </c>
-      <c r="AN70" s="11" t="s">
+      <c r="AO70" s="11" t="s">
         <v>868</v>
       </c>
-      <c r="AO70" s="32" t="s">
+      <c r="AP70" s="32" t="s">
         <v>506</v>
       </c>
-      <c r="AP70" s="35" t="s">
+      <c r="AQ70" s="35" t="s">
         <v>1075</v>
       </c>
-      <c r="AQ70" s="5" t="s">
+      <c r="AR70" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR70" s="11" t="s">
+      <c r="AS70" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS70" s="13" t="s">
+      <c r="AT70" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT70" s="14"/>
-      <c r="AU70" s="44"/>
-      <c r="AV70" s="1"/>
+      <c r="AU70" s="14"/>
+      <c r="AV70" s="44"/>
       <c r="AW70" s="1"/>
-      <c r="BD70" s="1"/>
+      <c r="AX70" s="1"/>
+      <c r="BE70" s="1"/>
     </row>
-    <row r="71" spans="1:56" ht="25.5">
+    <row r="71" spans="1:57" ht="25.5">
       <c r="A71" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16300,37 +16388,38 @@
       <c r="AK71" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL71" s="5" t="s">
+      <c r="AL71" s="5"/>
+      <c r="AM71" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM71" s="11" t="s">
+      <c r="AN71" s="11" t="s">
         <v>845</v>
       </c>
-      <c r="AN71" s="11" t="s">
+      <c r="AO71" s="11" t="s">
         <v>846</v>
       </c>
-      <c r="AO71" s="32" t="s">
+      <c r="AP71" s="32" t="s">
         <v>507</v>
       </c>
-      <c r="AP71" s="35" t="s">
+      <c r="AQ71" s="35" t="s">
         <v>1076</v>
       </c>
-      <c r="AQ71" s="5" t="s">
+      <c r="AR71" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR71" s="11" t="s">
+      <c r="AS71" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS71" s="13" t="s">
+      <c r="AT71" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT71" s="14"/>
-      <c r="AU71" s="44"/>
-      <c r="AV71" s="1"/>
+      <c r="AU71" s="14"/>
+      <c r="AV71" s="44"/>
       <c r="AW71" s="1"/>
-      <c r="BD71" s="1"/>
+      <c r="AX71" s="1"/>
+      <c r="BE71" s="1"/>
     </row>
-    <row r="72" spans="1:56" ht="25.5">
+    <row r="72" spans="1:57" ht="25.5">
       <c r="A72" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16455,37 +16544,38 @@
       <c r="AK72" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL72" s="5" t="s">
+      <c r="AL72" s="5"/>
+      <c r="AM72" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM72" s="11" t="s">
+      <c r="AN72" s="11" t="s">
         <v>847</v>
       </c>
-      <c r="AN72" s="11" t="s">
+      <c r="AO72" s="11" t="s">
         <v>848</v>
       </c>
-      <c r="AO72" s="32" t="s">
+      <c r="AP72" s="32" t="s">
         <v>508</v>
       </c>
-      <c r="AP72" s="35" t="s">
+      <c r="AQ72" s="35" t="s">
         <v>1077</v>
       </c>
-      <c r="AQ72" s="5" t="s">
+      <c r="AR72" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR72" s="11" t="s">
+      <c r="AS72" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS72" s="13" t="s">
+      <c r="AT72" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT72" s="14"/>
-      <c r="AU72" s="44"/>
-      <c r="AV72" s="1"/>
+      <c r="AU72" s="14"/>
+      <c r="AV72" s="44"/>
       <c r="AW72" s="1"/>
-      <c r="BD72" s="1"/>
+      <c r="AX72" s="1"/>
+      <c r="BE72" s="1"/>
     </row>
-    <row r="73" spans="1:56" ht="25.5">
+    <row r="73" spans="1:57" ht="25.5">
       <c r="A73" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16610,37 +16700,38 @@
       <c r="AK73" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL73" s="5" t="s">
+      <c r="AL73" s="5"/>
+      <c r="AM73" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM73" s="11" t="s">
+      <c r="AN73" s="11" t="s">
         <v>843</v>
       </c>
-      <c r="AN73" s="11" t="s">
+      <c r="AO73" s="11" t="s">
         <v>844</v>
       </c>
-      <c r="AO73" s="32" t="s">
+      <c r="AP73" s="32" t="s">
         <v>509</v>
       </c>
-      <c r="AP73" s="35" t="s">
+      <c r="AQ73" s="35" t="s">
         <v>1078</v>
       </c>
-      <c r="AQ73" s="5" t="s">
+      <c r="AR73" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR73" s="11" t="s">
+      <c r="AS73" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS73" s="13" t="s">
+      <c r="AT73" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT73" s="14"/>
-      <c r="AU73" s="44"/>
-      <c r="AV73" s="1"/>
+      <c r="AU73" s="14"/>
+      <c r="AV73" s="44"/>
       <c r="AW73" s="1"/>
-      <c r="BD73" s="1"/>
+      <c r="AX73" s="1"/>
+      <c r="BE73" s="1"/>
     </row>
-    <row r="74" spans="1:56" ht="25.5">
+    <row r="74" spans="1:57" ht="25.5">
       <c r="A74" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16765,37 +16856,38 @@
       <c r="AK74" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL74" s="5" t="s">
+      <c r="AL74" s="5"/>
+      <c r="AM74" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM74" s="11" t="s">
+      <c r="AN74" s="11" t="s">
         <v>849</v>
       </c>
-      <c r="AN74" s="11" t="s">
+      <c r="AO74" s="11" t="s">
         <v>850</v>
       </c>
-      <c r="AO74" s="32" t="s">
+      <c r="AP74" s="32" t="s">
         <v>510</v>
       </c>
-      <c r="AP74" s="35" t="s">
+      <c r="AQ74" s="35" t="s">
         <v>1079</v>
       </c>
-      <c r="AQ74" s="5" t="s">
+      <c r="AR74" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR74" s="11" t="s">
+      <c r="AS74" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS74" s="13" t="s">
+      <c r="AT74" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT74" s="14"/>
-      <c r="AU74" s="44"/>
-      <c r="AV74" s="1"/>
+      <c r="AU74" s="14"/>
+      <c r="AV74" s="44"/>
       <c r="AW74" s="1"/>
-      <c r="BD74" s="1"/>
+      <c r="AX74" s="1"/>
+      <c r="BE74" s="1"/>
     </row>
-    <row r="75" spans="1:56" ht="25.5">
+    <row r="75" spans="1:57" ht="25.5">
       <c r="A75" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16920,37 +17012,38 @@
       <c r="AK75" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL75" s="5" t="s">
+      <c r="AL75" s="5"/>
+      <c r="AM75" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM75" s="11" t="s">
+      <c r="AN75" s="11" t="s">
         <v>851</v>
       </c>
-      <c r="AN75" s="11" t="s">
+      <c r="AO75" s="11" t="s">
         <v>852</v>
       </c>
-      <c r="AO75" s="32" t="s">
+      <c r="AP75" s="32" t="s">
         <v>511</v>
       </c>
-      <c r="AP75" s="35" t="s">
+      <c r="AQ75" s="35" t="s">
         <v>1080</v>
       </c>
-      <c r="AQ75" s="5" t="s">
+      <c r="AR75" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR75" s="11" t="s">
+      <c r="AS75" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS75" s="13" t="s">
+      <c r="AT75" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT75" s="14"/>
-      <c r="AU75" s="44"/>
-      <c r="AV75" s="1"/>
+      <c r="AU75" s="14"/>
+      <c r="AV75" s="44"/>
       <c r="AW75" s="1"/>
-      <c r="BD75" s="1"/>
+      <c r="AX75" s="1"/>
+      <c r="BE75" s="1"/>
     </row>
-    <row r="76" spans="1:56" ht="25.5">
+    <row r="76" spans="1:57" ht="25.5">
       <c r="A76" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17075,37 +17168,38 @@
       <c r="AK76" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL76" s="5" t="s">
+      <c r="AL76" s="5"/>
+      <c r="AM76" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM76" s="11" t="s">
+      <c r="AN76" s="11" t="s">
         <v>853</v>
       </c>
-      <c r="AN76" s="11" t="s">
+      <c r="AO76" s="11" t="s">
         <v>854</v>
       </c>
-      <c r="AO76" s="32" t="s">
+      <c r="AP76" s="32" t="s">
         <v>512</v>
       </c>
-      <c r="AP76" s="35" t="s">
+      <c r="AQ76" s="35" t="s">
         <v>1081</v>
       </c>
-      <c r="AQ76" s="5" t="s">
+      <c r="AR76" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR76" s="11" t="s">
+      <c r="AS76" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS76" s="13" t="s">
+      <c r="AT76" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT76" s="14"/>
-      <c r="AU76" s="44"/>
-      <c r="AV76" s="1"/>
+      <c r="AU76" s="14"/>
+      <c r="AV76" s="44"/>
       <c r="AW76" s="1"/>
-      <c r="BD76" s="1"/>
+      <c r="AX76" s="1"/>
+      <c r="BE76" s="1"/>
     </row>
-    <row r="77" spans="1:56" ht="25.5">
+    <row r="77" spans="1:57" ht="25.5">
       <c r="A77" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17230,37 +17324,38 @@
       <c r="AK77" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL77" s="5" t="s">
+      <c r="AL77" s="5"/>
+      <c r="AM77" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM77" s="11" t="s">
+      <c r="AN77" s="11" t="s">
         <v>855</v>
       </c>
-      <c r="AN77" s="11" t="s">
+      <c r="AO77" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="AO77" s="32" t="s">
+      <c r="AP77" s="32" t="s">
         <v>513</v>
       </c>
-      <c r="AP77" s="35" t="s">
+      <c r="AQ77" s="35" t="s">
         <v>1082</v>
       </c>
-      <c r="AQ77" s="5" t="s">
+      <c r="AR77" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR77" s="11" t="s">
+      <c r="AS77" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS77" s="13" t="s">
+      <c r="AT77" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT77" s="14"/>
-      <c r="AU77" s="44"/>
-      <c r="AV77" s="1"/>
+      <c r="AU77" s="14"/>
+      <c r="AV77" s="44"/>
       <c r="AW77" s="1"/>
-      <c r="BD77" s="1"/>
+      <c r="AX77" s="1"/>
+      <c r="BE77" s="1"/>
     </row>
-    <row r="78" spans="1:56" ht="25.5">
+    <row r="78" spans="1:57" ht="25.5">
       <c r="A78" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17385,37 +17480,38 @@
       <c r="AK78" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL78" s="5" t="s">
+      <c r="AL78" s="5"/>
+      <c r="AM78" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM78" s="11" t="s">
+      <c r="AN78" s="11" t="s">
         <v>819</v>
       </c>
-      <c r="AN78" s="11" t="s">
+      <c r="AO78" s="11" t="s">
         <v>820</v>
       </c>
-      <c r="AO78" s="32" t="s">
+      <c r="AP78" s="32" t="s">
         <v>514</v>
       </c>
-      <c r="AP78" s="35" t="s">
+      <c r="AQ78" s="35" t="s">
         <v>1083</v>
       </c>
-      <c r="AQ78" s="5" t="s">
+      <c r="AR78" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR78" s="11" t="s">
+      <c r="AS78" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS78" s="13" t="s">
+      <c r="AT78" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT78" s="14"/>
-      <c r="AU78" s="44"/>
-      <c r="AV78" s="1"/>
+      <c r="AU78" s="14"/>
+      <c r="AV78" s="44"/>
       <c r="AW78" s="1"/>
-      <c r="BD78" s="1"/>
+      <c r="AX78" s="1"/>
+      <c r="BE78" s="1"/>
     </row>
-    <row r="79" spans="1:56" ht="25.5">
+    <row r="79" spans="1:57" ht="25.5">
       <c r="A79" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17540,37 +17636,38 @@
       <c r="AK79" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL79" s="5" t="s">
+      <c r="AL79" s="5"/>
+      <c r="AM79" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM79" s="11" t="s">
+      <c r="AN79" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="AN79" s="11" t="s">
+      <c r="AO79" s="11" t="s">
         <v>822</v>
       </c>
-      <c r="AO79" s="32" t="s">
+      <c r="AP79" s="32" t="s">
         <v>515</v>
       </c>
-      <c r="AP79" s="35" t="s">
+      <c r="AQ79" s="35" t="s">
         <v>1084</v>
       </c>
-      <c r="AQ79" s="5" t="s">
+      <c r="AR79" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR79" s="11" t="s">
+      <c r="AS79" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS79" s="13" t="s">
+      <c r="AT79" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT79" s="14"/>
-      <c r="AU79" s="44"/>
-      <c r="AV79" s="1"/>
+      <c r="AU79" s="14"/>
+      <c r="AV79" s="44"/>
       <c r="AW79" s="1"/>
-      <c r="BD79" s="1"/>
+      <c r="AX79" s="1"/>
+      <c r="BE79" s="1"/>
     </row>
-    <row r="80" spans="1:56" ht="25.5">
+    <row r="80" spans="1:57" ht="25.5">
       <c r="A80" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17695,37 +17792,38 @@
       <c r="AK80" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL80" s="5" t="s">
+      <c r="AL80" s="5"/>
+      <c r="AM80" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM80" s="11" t="s">
+      <c r="AN80" s="11" t="s">
         <v>823</v>
       </c>
-      <c r="AN80" s="11" t="s">
+      <c r="AO80" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="AO80" s="32" t="s">
+      <c r="AP80" s="32" t="s">
         <v>516</v>
       </c>
-      <c r="AP80" s="35" t="s">
+      <c r="AQ80" s="35" t="s">
         <v>1085</v>
       </c>
-      <c r="AQ80" s="5" t="s">
+      <c r="AR80" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR80" s="11" t="s">
+      <c r="AS80" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS80" s="13" t="s">
+      <c r="AT80" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT80" s="14"/>
-      <c r="AU80" s="44"/>
-      <c r="AV80" s="1"/>
+      <c r="AU80" s="14"/>
+      <c r="AV80" s="44"/>
       <c r="AW80" s="1"/>
-      <c r="BD80" s="1"/>
+      <c r="AX80" s="1"/>
+      <c r="BE80" s="1"/>
     </row>
-    <row r="81" spans="1:56" ht="25.5">
+    <row r="81" spans="1:57" ht="25.5">
       <c r="A81" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17850,37 +17948,38 @@
       <c r="AK81" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL81" s="5" t="s">
+      <c r="AL81" s="5"/>
+      <c r="AM81" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM81" s="11" t="s">
+      <c r="AN81" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="AN81" s="11" t="s">
+      <c r="AO81" s="11" t="s">
         <v>826</v>
       </c>
-      <c r="AO81" s="32" t="s">
+      <c r="AP81" s="32" t="s">
         <v>517</v>
       </c>
-      <c r="AP81" s="35" t="s">
+      <c r="AQ81" s="35" t="s">
         <v>1086</v>
       </c>
-      <c r="AQ81" s="5" t="s">
+      <c r="AR81" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR81" s="11" t="s">
+      <c r="AS81" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS81" s="13" t="s">
+      <c r="AT81" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT81" s="14"/>
-      <c r="AU81" s="44"/>
-      <c r="AV81" s="1"/>
+      <c r="AU81" s="14"/>
+      <c r="AV81" s="44"/>
       <c r="AW81" s="1"/>
-      <c r="BD81" s="1"/>
+      <c r="AX81" s="1"/>
+      <c r="BE81" s="1"/>
     </row>
-    <row r="82" spans="1:56" ht="25.5">
+    <row r="82" spans="1:57" ht="25.5">
       <c r="A82" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18005,37 +18104,38 @@
       <c r="AK82" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL82" s="5" t="s">
+      <c r="AL82" s="5"/>
+      <c r="AM82" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM82" s="11" t="s">
+      <c r="AN82" s="11" t="s">
         <v>827</v>
       </c>
-      <c r="AN82" s="11" t="s">
+      <c r="AO82" s="11" t="s">
         <v>828</v>
       </c>
-      <c r="AO82" s="32" t="s">
+      <c r="AP82" s="32" t="s">
         <v>518</v>
       </c>
-      <c r="AP82" s="35" t="s">
+      <c r="AQ82" s="35" t="s">
         <v>1087</v>
       </c>
-      <c r="AQ82" s="5" t="s">
+      <c r="AR82" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR82" s="11" t="s">
+      <c r="AS82" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS82" s="13" t="s">
+      <c r="AT82" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT82" s="14"/>
-      <c r="AU82" s="44"/>
-      <c r="AV82" s="1"/>
+      <c r="AU82" s="14"/>
+      <c r="AV82" s="44"/>
       <c r="AW82" s="1"/>
-      <c r="BD82" s="1"/>
+      <c r="AX82" s="1"/>
+      <c r="BE82" s="1"/>
     </row>
-    <row r="83" spans="1:56" ht="25.5">
+    <row r="83" spans="1:57" ht="25.5">
       <c r="A83" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18160,37 +18260,38 @@
       <c r="AK83" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL83" s="5" t="s">
+      <c r="AL83" s="5"/>
+      <c r="AM83" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM83" s="11" t="s">
+      <c r="AN83" s="11" t="s">
         <v>829</v>
       </c>
-      <c r="AN83" s="11" t="s">
+      <c r="AO83" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="AO83" s="32" t="s">
+      <c r="AP83" s="32" t="s">
         <v>519</v>
       </c>
-      <c r="AP83" s="35" t="s">
+      <c r="AQ83" s="35" t="s">
         <v>1088</v>
       </c>
-      <c r="AQ83" s="5" t="s">
+      <c r="AR83" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR83" s="11" t="s">
+      <c r="AS83" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS83" s="13" t="s">
+      <c r="AT83" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT83" s="14"/>
-      <c r="AU83" s="44"/>
-      <c r="AV83" s="1"/>
+      <c r="AU83" s="14"/>
+      <c r="AV83" s="44"/>
       <c r="AW83" s="1"/>
-      <c r="BD83" s="1"/>
+      <c r="AX83" s="1"/>
+      <c r="BE83" s="1"/>
     </row>
-    <row r="84" spans="1:56" ht="25.5">
+    <row r="84" spans="1:57" ht="25.5">
       <c r="A84" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18315,37 +18416,38 @@
       <c r="AK84" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL84" s="5" t="s">
+      <c r="AL84" s="5"/>
+      <c r="AM84" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM84" s="11" t="s">
+      <c r="AN84" s="11" t="s">
         <v>831</v>
       </c>
-      <c r="AN84" s="11" t="s">
+      <c r="AO84" s="11" t="s">
         <v>832</v>
       </c>
-      <c r="AO84" s="32" t="s">
+      <c r="AP84" s="32" t="s">
         <v>520</v>
       </c>
-      <c r="AP84" s="35" t="s">
+      <c r="AQ84" s="35" t="s">
         <v>1089</v>
       </c>
-      <c r="AQ84" s="5" t="s">
+      <c r="AR84" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR84" s="11" t="s">
+      <c r="AS84" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS84" s="13" t="s">
+      <c r="AT84" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT84" s="14"/>
-      <c r="AU84" s="44"/>
-      <c r="AV84" s="1"/>
+      <c r="AU84" s="14"/>
+      <c r="AV84" s="44"/>
       <c r="AW84" s="1"/>
-      <c r="BD84" s="1"/>
+      <c r="AX84" s="1"/>
+      <c r="BE84" s="1"/>
     </row>
-    <row r="85" spans="1:56" ht="25.5">
+    <row r="85" spans="1:57" ht="25.5">
       <c r="A85" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18470,37 +18572,38 @@
       <c r="AK85" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL85" s="5" t="s">
+      <c r="AL85" s="5"/>
+      <c r="AM85" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM85" s="11" t="s">
+      <c r="AN85" s="11" t="s">
         <v>833</v>
       </c>
-      <c r="AN85" s="11" t="s">
+      <c r="AO85" s="11" t="s">
         <v>834</v>
       </c>
-      <c r="AO85" s="32" t="s">
+      <c r="AP85" s="32" t="s">
         <v>521</v>
       </c>
-      <c r="AP85" s="35" t="s">
+      <c r="AQ85" s="35" t="s">
         <v>1090</v>
       </c>
-      <c r="AQ85" s="5" t="s">
+      <c r="AR85" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR85" s="11" t="s">
+      <c r="AS85" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS85" s="13" t="s">
+      <c r="AT85" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT85" s="14"/>
-      <c r="AU85" s="44"/>
-      <c r="AV85" s="1"/>
+      <c r="AU85" s="14"/>
+      <c r="AV85" s="44"/>
       <c r="AW85" s="1"/>
-      <c r="BD85" s="1"/>
+      <c r="AX85" s="1"/>
+      <c r="BE85" s="1"/>
     </row>
-    <row r="86" spans="1:56" ht="25.5">
+    <row r="86" spans="1:57" ht="25.5">
       <c r="A86" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18625,37 +18728,38 @@
       <c r="AK86" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL86" s="5" t="s">
+      <c r="AL86" s="5"/>
+      <c r="AM86" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM86" s="11" t="s">
+      <c r="AN86" s="11" t="s">
         <v>835</v>
       </c>
-      <c r="AN86" s="11" t="s">
+      <c r="AO86" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="AO86" s="32" t="s">
+      <c r="AP86" s="32" t="s">
         <v>522</v>
       </c>
-      <c r="AP86" s="35" t="s">
+      <c r="AQ86" s="35" t="s">
         <v>1091</v>
       </c>
-      <c r="AQ86" s="5" t="s">
+      <c r="AR86" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR86" s="11" t="s">
+      <c r="AS86" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS86" s="13" t="s">
+      <c r="AT86" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT86" s="14"/>
-      <c r="AU86" s="44"/>
-      <c r="AV86" s="1"/>
+      <c r="AU86" s="14"/>
+      <c r="AV86" s="44"/>
       <c r="AW86" s="1"/>
-      <c r="BD86" s="1"/>
+      <c r="AX86" s="1"/>
+      <c r="BE86" s="1"/>
     </row>
-    <row r="87" spans="1:56" ht="25.5">
+    <row r="87" spans="1:57" ht="25.5">
       <c r="A87" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18780,37 +18884,38 @@
       <c r="AK87" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL87" s="5" t="s">
+      <c r="AL87" s="5"/>
+      <c r="AM87" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM87" s="11" t="s">
+      <c r="AN87" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="AN87" s="11" t="s">
+      <c r="AO87" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="AO87" s="32" t="s">
+      <c r="AP87" s="32" t="s">
         <v>523</v>
       </c>
-      <c r="AP87" s="35" t="s">
+      <c r="AQ87" s="35" t="s">
         <v>1092</v>
       </c>
-      <c r="AQ87" s="5" t="s">
+      <c r="AR87" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR87" s="11" t="s">
+      <c r="AS87" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS87" s="13" t="s">
+      <c r="AT87" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT87" s="14"/>
-      <c r="AU87" s="44"/>
-      <c r="AV87" s="1"/>
+      <c r="AU87" s="14"/>
+      <c r="AV87" s="44"/>
       <c r="AW87" s="1"/>
-      <c r="BD87" s="1"/>
+      <c r="AX87" s="1"/>
+      <c r="BE87" s="1"/>
     </row>
-    <row r="88" spans="1:56" ht="25.5">
+    <row r="88" spans="1:57" ht="25.5">
       <c r="A88" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18935,37 +19040,38 @@
       <c r="AK88" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL88" s="5" t="s">
+      <c r="AL88" s="5"/>
+      <c r="AM88" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM88" s="11" t="s">
+      <c r="AN88" s="11" t="s">
         <v>839</v>
       </c>
-      <c r="AN88" s="11" t="s">
+      <c r="AO88" s="11" t="s">
         <v>840</v>
       </c>
-      <c r="AO88" s="32" t="s">
+      <c r="AP88" s="32" t="s">
         <v>524</v>
       </c>
-      <c r="AP88" s="35" t="s">
+      <c r="AQ88" s="35" t="s">
         <v>1093</v>
       </c>
-      <c r="AQ88" s="5" t="s">
+      <c r="AR88" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR88" s="11" t="s">
+      <c r="AS88" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS88" s="13" t="s">
+      <c r="AT88" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT88" s="14"/>
-      <c r="AU88" s="44"/>
-      <c r="AV88" s="1"/>
+      <c r="AU88" s="14"/>
+      <c r="AV88" s="44"/>
       <c r="AW88" s="1"/>
-      <c r="BD88" s="1"/>
+      <c r="AX88" s="1"/>
+      <c r="BE88" s="1"/>
     </row>
-    <row r="89" spans="1:56" ht="25.5">
+    <row r="89" spans="1:57" ht="25.5">
       <c r="A89" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19090,37 +19196,38 @@
       <c r="AK89" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AL89" s="5" t="s">
+      <c r="AL89" s="5"/>
+      <c r="AM89" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM89" s="11" t="s">
+      <c r="AN89" s="11" t="s">
         <v>841</v>
       </c>
-      <c r="AN89" s="11" t="s">
+      <c r="AO89" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="AO89" s="32" t="s">
+      <c r="AP89" s="32" t="s">
         <v>525</v>
       </c>
-      <c r="AP89" s="35" t="s">
+      <c r="AQ89" s="35" t="s">
         <v>1094</v>
       </c>
-      <c r="AQ89" s="5" t="s">
+      <c r="AR89" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR89" s="11" t="s">
+      <c r="AS89" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS89" s="13" t="s">
+      <c r="AT89" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT89" s="14"/>
-      <c r="AU89" s="44"/>
-      <c r="AV89" s="1"/>
+      <c r="AU89" s="14"/>
+      <c r="AV89" s="44"/>
       <c r="AW89" s="1"/>
-      <c r="BD89" s="1"/>
+      <c r="AX89" s="1"/>
+      <c r="BE89" s="1"/>
     </row>
-    <row r="90" spans="1:56" ht="25.5">
+    <row r="90" spans="1:57" ht="25.5">
       <c r="A90" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19244,37 +19351,38 @@
       <c r="AK90" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="AL90" s="5" t="s">
+      <c r="AL90" s="5"/>
+      <c r="AM90" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM90" s="5" t="s">
+      <c r="AN90" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="AN90" s="5" t="s">
+      <c r="AO90" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="AO90" s="32" t="s">
+      <c r="AP90" s="32" t="s">
         <v>526</v>
       </c>
-      <c r="AP90" s="35" t="s">
+      <c r="AQ90" s="35" t="s">
         <v>805</v>
       </c>
-      <c r="AQ90" s="5" t="s">
+      <c r="AR90" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR90" s="11" t="s">
+      <c r="AS90" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="AS90" s="13" t="s">
+      <c r="AT90" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT90" s="14"/>
-      <c r="AU90" s="44"/>
-      <c r="AV90" s="1"/>
+      <c r="AU90" s="14"/>
+      <c r="AV90" s="44"/>
       <c r="AW90" s="1"/>
-      <c r="BD90" s="1"/>
+      <c r="AX90" s="1"/>
+      <c r="BE90" s="1"/>
     </row>
-    <row r="91" spans="1:56" ht="25.5">
+    <row r="91" spans="1:57" ht="25.5">
       <c r="A91" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19398,37 +19506,38 @@
       <c r="AK91" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="AL91" s="5" t="s">
+      <c r="AL91" s="5"/>
+      <c r="AM91" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM91" s="11" t="s">
+      <c r="AN91" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="AN91" s="11" t="s">
+      <c r="AO91" s="11" t="s">
         <v>698</v>
       </c>
-      <c r="AO91" s="32" t="s">
+      <c r="AP91" s="32" t="s">
         <v>527</v>
       </c>
-      <c r="AP91" s="35" t="s">
+      <c r="AQ91" s="35" t="s">
         <v>806</v>
       </c>
-      <c r="AQ91" s="5" t="s">
+      <c r="AR91" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR91" s="11" t="s">
+      <c r="AS91" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="AS91" s="13" t="s">
+      <c r="AT91" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT91" s="14"/>
-      <c r="AU91" s="44"/>
-      <c r="AV91" s="1"/>
+      <c r="AU91" s="14"/>
+      <c r="AV91" s="44"/>
       <c r="AW91" s="1"/>
-      <c r="BD91" s="1"/>
+      <c r="AX91" s="1"/>
+      <c r="BE91" s="1"/>
     </row>
-    <row r="92" spans="1:56" ht="25.5">
+    <row r="92" spans="1:57" ht="25.5">
       <c r="A92" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19552,37 +19661,38 @@
       <c r="AK92" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="AL92" s="5" t="s">
+      <c r="AL92" s="5"/>
+      <c r="AM92" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM92" s="11" t="s">
+      <c r="AN92" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="AN92" s="11" t="s">
+      <c r="AO92" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="AO92" s="32" t="s">
+      <c r="AP92" s="32" t="s">
         <v>528</v>
       </c>
-      <c r="AP92" s="35" t="s">
+      <c r="AQ92" s="35" t="s">
         <v>807</v>
       </c>
-      <c r="AQ92" s="5" t="s">
+      <c r="AR92" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR92" s="11" t="s">
+      <c r="AS92" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="AS92" s="13" t="s">
+      <c r="AT92" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT92" s="14"/>
-      <c r="AU92" s="44"/>
-      <c r="AV92" s="1"/>
+      <c r="AU92" s="14"/>
+      <c r="AV92" s="44"/>
       <c r="AW92" s="1"/>
-      <c r="BD92" s="1"/>
+      <c r="AX92" s="1"/>
+      <c r="BE92" s="1"/>
     </row>
-    <row r="93" spans="1:56" ht="25.5">
+    <row r="93" spans="1:57" ht="25.5">
       <c r="A93" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19706,37 +19816,38 @@
       <c r="AK93" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="AL93" s="5" t="s">
+      <c r="AL93" s="5"/>
+      <c r="AM93" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM93" s="11" t="s">
+      <c r="AN93" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="AN93" s="11" t="s">
+      <c r="AO93" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="AO93" s="32" t="s">
+      <c r="AP93" s="32" t="s">
         <v>529</v>
       </c>
-      <c r="AP93" s="36" t="s">
+      <c r="AQ93" s="36" t="s">
         <v>808</v>
       </c>
-      <c r="AQ93" s="5" t="s">
+      <c r="AR93" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR93" s="11" t="s">
+      <c r="AS93" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="AS93" s="13" t="s">
+      <c r="AT93" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT93" s="14"/>
-      <c r="AU93" s="44"/>
-      <c r="AV93" s="1"/>
+      <c r="AU93" s="14"/>
+      <c r="AV93" s="44"/>
       <c r="AW93" s="1"/>
-      <c r="BD93" s="1"/>
+      <c r="AX93" s="1"/>
+      <c r="BE93" s="1"/>
     </row>
-    <row r="94" spans="1:56" ht="25.5">
+    <row r="94" spans="1:57" ht="25.5">
       <c r="A94" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19860,37 +19971,38 @@
       <c r="AK94" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="AL94" s="5" t="s">
+      <c r="AL94" s="5"/>
+      <c r="AM94" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM94" s="11" t="s">
+      <c r="AN94" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="AN94" s="11" t="s">
+      <c r="AO94" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="AO94" s="32" t="s">
+      <c r="AP94" s="32" t="s">
         <v>530</v>
       </c>
-      <c r="AP94" s="36" t="s">
+      <c r="AQ94" s="36" t="s">
         <v>809</v>
       </c>
-      <c r="AQ94" s="5" t="s">
+      <c r="AR94" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR94" s="11" t="s">
+      <c r="AS94" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="AS94" s="13" t="s">
+      <c r="AT94" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT94" s="14"/>
-      <c r="AU94" s="44"/>
-      <c r="AV94" s="1"/>
+      <c r="AU94" s="14"/>
+      <c r="AV94" s="44"/>
       <c r="AW94" s="1"/>
-      <c r="BD94" s="1"/>
+      <c r="AX94" s="1"/>
+      <c r="BE94" s="1"/>
     </row>
-    <row r="95" spans="1:56" ht="25.5">
+    <row r="95" spans="1:57" ht="25.5">
       <c r="A95" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20014,37 +20126,38 @@
       <c r="AK95" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="AL95" s="5" t="s">
+      <c r="AL95" s="5"/>
+      <c r="AM95" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM95" s="11" t="s">
+      <c r="AN95" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="AN95" s="11" t="s">
+      <c r="AO95" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="AO95" s="32" t="s">
+      <c r="AP95" s="32" t="s">
         <v>531</v>
       </c>
-      <c r="AP95" s="36" t="s">
+      <c r="AQ95" s="36" t="s">
         <v>810</v>
       </c>
-      <c r="AQ95" s="5" t="s">
+      <c r="AR95" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR95" s="11" t="s">
+      <c r="AS95" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="AS95" s="13" t="s">
+      <c r="AT95" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT95" s="14"/>
-      <c r="AU95" s="44"/>
-      <c r="AV95" s="1"/>
+      <c r="AU95" s="14"/>
+      <c r="AV95" s="44"/>
       <c r="AW95" s="1"/>
-      <c r="BD95" s="1"/>
+      <c r="AX95" s="1"/>
+      <c r="BE95" s="1"/>
     </row>
-    <row r="96" spans="1:56" ht="25.5">
+    <row r="96" spans="1:57" ht="25.5">
       <c r="A96" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20168,37 +20281,38 @@
       <c r="AK96" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="AL96" s="5" t="s">
+      <c r="AL96" s="5"/>
+      <c r="AM96" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM96" s="11" t="s">
+      <c r="AN96" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="AN96" s="11" t="s">
+      <c r="AO96" s="11" t="s">
         <v>707</v>
       </c>
-      <c r="AO96" s="32" t="s">
+      <c r="AP96" s="32" t="s">
         <v>532</v>
       </c>
-      <c r="AP96" s="36" t="s">
+      <c r="AQ96" s="36" t="s">
         <v>811</v>
       </c>
-      <c r="AQ96" s="5" t="s">
+      <c r="AR96" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR96" s="11" t="s">
+      <c r="AS96" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="AS96" s="13" t="s">
+      <c r="AT96" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT96" s="14"/>
-      <c r="AU96" s="44"/>
-      <c r="AV96" s="1"/>
+      <c r="AU96" s="14"/>
+      <c r="AV96" s="44"/>
       <c r="AW96" s="1"/>
-      <c r="BD96" s="1"/>
+      <c r="AX96" s="1"/>
+      <c r="BE96" s="1"/>
     </row>
-    <row r="97" spans="1:56" ht="25.5">
+    <row r="97" spans="1:57" ht="25.5">
       <c r="A97" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20322,37 +20436,38 @@
       <c r="AK97" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="AL97" s="5" t="s">
+      <c r="AL97" s="5"/>
+      <c r="AM97" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM97" s="11" t="s">
+      <c r="AN97" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="AN97" s="11" t="s">
+      <c r="AO97" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="AO97" s="32" t="s">
+      <c r="AP97" s="32" t="s">
         <v>710</v>
       </c>
-      <c r="AP97" s="36" t="s">
+      <c r="AQ97" s="36" t="s">
         <v>812</v>
       </c>
-      <c r="AQ97" s="5" t="s">
+      <c r="AR97" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR97" s="11" t="s">
+      <c r="AS97" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="AS97" s="13" t="s">
+      <c r="AT97" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT97" s="14"/>
-      <c r="AU97" s="44"/>
-      <c r="AV97" s="1"/>
+      <c r="AU97" s="14"/>
+      <c r="AV97" s="44"/>
       <c r="AW97" s="1"/>
-      <c r="BD97" s="1"/>
+      <c r="AX97" s="1"/>
+      <c r="BE97" s="1"/>
     </row>
-    <row r="98" spans="1:56" ht="25.5">
+    <row r="98" spans="1:57" ht="25.5">
       <c r="A98" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20477,37 +20592,38 @@
       <c r="AK98" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="AL98" s="5" t="s">
+      <c r="AL98" s="5"/>
+      <c r="AM98" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM98" s="5" t="s">
+      <c r="AN98" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="AN98" s="5" t="s">
+      <c r="AO98" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="AO98" s="32" t="s">
+      <c r="AP98" s="32" t="s">
         <v>533</v>
       </c>
-      <c r="AP98" s="35" t="s">
+      <c r="AQ98" s="35" t="s">
         <v>813</v>
       </c>
-      <c r="AQ98" s="5" t="s">
+      <c r="AR98" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR98" s="11" t="s">
+      <c r="AS98" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="AS98" s="13" t="s">
+      <c r="AT98" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT98" s="14"/>
-      <c r="AU98" s="44"/>
-      <c r="AV98" s="1"/>
+      <c r="AU98" s="14"/>
+      <c r="AV98" s="44"/>
       <c r="AW98" s="1"/>
-      <c r="BD98" s="1"/>
+      <c r="AX98" s="1"/>
+      <c r="BE98" s="1"/>
     </row>
-    <row r="99" spans="1:56" ht="25.5">
+    <row r="99" spans="1:57" ht="25.5">
       <c r="A99" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20632,37 +20748,38 @@
       <c r="AK99" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="AL99" s="5" t="s">
+      <c r="AL99" s="5"/>
+      <c r="AM99" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM99" s="11" t="s">
+      <c r="AN99" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="AN99" s="11" t="s">
+      <c r="AO99" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="AO99" s="32" t="s">
+      <c r="AP99" s="32" t="s">
         <v>534</v>
       </c>
-      <c r="AP99" s="35" t="s">
+      <c r="AQ99" s="35" t="s">
         <v>814</v>
       </c>
-      <c r="AQ99" s="5" t="s">
+      <c r="AR99" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR99" s="11" t="s">
+      <c r="AS99" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="AS99" s="13" t="s">
+      <c r="AT99" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT99" s="14"/>
-      <c r="AU99" s="44"/>
-      <c r="AV99" s="1"/>
+      <c r="AU99" s="14"/>
+      <c r="AV99" s="44"/>
       <c r="AW99" s="1"/>
-      <c r="BD99" s="1"/>
+      <c r="AX99" s="1"/>
+      <c r="BE99" s="1"/>
     </row>
-    <row r="100" spans="1:56" ht="25.5">
+    <row r="100" spans="1:57" ht="25.5">
       <c r="A100" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20787,37 +20904,38 @@
       <c r="AK100" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="AL100" s="5" t="s">
+      <c r="AL100" s="5"/>
+      <c r="AM100" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM100" s="11" t="s">
+      <c r="AN100" s="11" t="s">
         <v>712</v>
       </c>
-      <c r="AN100" s="11" t="s">
+      <c r="AO100" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="AO100" s="32" t="s">
+      <c r="AP100" s="32" t="s">
         <v>535</v>
       </c>
-      <c r="AP100" s="35" t="s">
+      <c r="AQ100" s="35" t="s">
         <v>815</v>
       </c>
-      <c r="AQ100" s="5" t="s">
+      <c r="AR100" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR100" s="11" t="s">
+      <c r="AS100" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="AS100" s="13" t="s">
+      <c r="AT100" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT100" s="14"/>
-      <c r="AU100" s="44"/>
-      <c r="AV100" s="1"/>
+      <c r="AU100" s="14"/>
+      <c r="AV100" s="44"/>
       <c r="AW100" s="1"/>
-      <c r="BD100" s="1"/>
+      <c r="AX100" s="1"/>
+      <c r="BE100" s="1"/>
     </row>
-    <row r="101" spans="1:56" ht="25.5">
+    <row r="101" spans="1:57" ht="25.5">
       <c r="A101" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20942,37 +21060,38 @@
       <c r="AK101" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="AL101" s="5" t="s">
+      <c r="AL101" s="5"/>
+      <c r="AM101" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM101" s="11" t="s">
+      <c r="AN101" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="AN101" s="11" t="s">
+      <c r="AO101" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="AO101" s="32" t="s">
+      <c r="AP101" s="32" t="s">
         <v>536</v>
       </c>
-      <c r="AP101" s="35" t="s">
+      <c r="AQ101" s="35" t="s">
         <v>816</v>
       </c>
-      <c r="AQ101" s="5" t="s">
+      <c r="AR101" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR101" s="11" t="s">
+      <c r="AS101" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="AS101" s="13" t="s">
+      <c r="AT101" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT101" s="14"/>
-      <c r="AU101" s="44"/>
-      <c r="AV101" s="1"/>
+      <c r="AU101" s="14"/>
+      <c r="AV101" s="44"/>
       <c r="AW101" s="1"/>
-      <c r="BD101" s="1"/>
+      <c r="AX101" s="1"/>
+      <c r="BE101" s="1"/>
     </row>
-    <row r="102" spans="1:56" ht="25.5">
+    <row r="102" spans="1:57" ht="25.5">
       <c r="A102" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -21097,37 +21216,38 @@
       <c r="AK102" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="AL102" s="5" t="s">
+      <c r="AL102" s="5"/>
+      <c r="AM102" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM102" s="11" t="s">
+      <c r="AN102" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="AN102" s="11" t="s">
+      <c r="AO102" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="AO102" s="32" t="s">
+      <c r="AP102" s="32" t="s">
         <v>537</v>
       </c>
-      <c r="AP102" s="35" t="s">
+      <c r="AQ102" s="35" t="s">
         <v>817</v>
       </c>
-      <c r="AQ102" s="5" t="s">
+      <c r="AR102" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR102" s="11" t="s">
+      <c r="AS102" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="AS102" s="13" t="s">
+      <c r="AT102" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT102" s="14"/>
-      <c r="AU102" s="44"/>
-      <c r="AV102" s="1"/>
+      <c r="AU102" s="14"/>
+      <c r="AV102" s="44"/>
       <c r="AW102" s="1"/>
-      <c r="BD102" s="1"/>
+      <c r="AX102" s="1"/>
+      <c r="BE102" s="1"/>
     </row>
-    <row r="103" spans="1:56" ht="25.5">
+    <row r="103" spans="1:57" ht="25.5">
       <c r="A103" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21251,37 +21371,38 @@
       <c r="AK103" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL103" s="5" t="s">
+      <c r="AL103" s="11"/>
+      <c r="AM103" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM103" s="11" t="s">
+      <c r="AN103" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="AN103" s="11" t="s">
+      <c r="AO103" s="11" t="s">
         <v>723</v>
       </c>
-      <c r="AO103" s="32" t="s">
+      <c r="AP103" s="32" t="s">
         <v>538</v>
       </c>
-      <c r="AP103" s="35" t="s">
+      <c r="AQ103" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ103" s="5" t="s">
+      <c r="AR103" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR103" s="11" t="s">
+      <c r="AS103" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS103" s="7" t="s">
+      <c r="AT103" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT103" s="16"/>
-      <c r="AU103" s="44"/>
-      <c r="AV103" s="1"/>
+      <c r="AU103" s="16"/>
+      <c r="AV103" s="44"/>
       <c r="AW103" s="1"/>
-      <c r="BD103" s="1"/>
+      <c r="AX103" s="1"/>
+      <c r="BE103" s="1"/>
     </row>
-    <row r="104" spans="1:56" ht="25.5">
+    <row r="104" spans="1:57" ht="25.5">
       <c r="A104" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21405,40 +21526,41 @@
       <c r="AK104" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL104" s="5" t="s">
+      <c r="AL104" s="11"/>
+      <c r="AM104" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM104" s="11" t="s">
+      <c r="AN104" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="AN104" s="11" t="s">
+      <c r="AO104" s="11" t="s">
         <v>725</v>
       </c>
-      <c r="AO104" s="32" t="s">
+      <c r="AP104" s="32" t="s">
         <v>539</v>
       </c>
-      <c r="AP104" s="35" t="s">
+      <c r="AQ104" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ104" s="5" t="s">
+      <c r="AR104" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR104" s="11" t="s">
+      <c r="AS104" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS104" s="7" t="s">
+      <c r="AT104" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT104" s="14"/>
-      <c r="AU104" s="44"/>
-      <c r="AX104" s="10"/>
+      <c r="AU104" s="14"/>
+      <c r="AV104" s="44"/>
       <c r="AY104" s="10"/>
-      <c r="AZ104" s="11"/>
+      <c r="AZ104" s="10"/>
       <c r="BA104" s="11"/>
-      <c r="BB104" s="13"/>
-      <c r="BC104" s="16"/>
+      <c r="BB104" s="11"/>
+      <c r="BC104" s="13"/>
+      <c r="BD104" s="16"/>
     </row>
-    <row r="105" spans="1:56" ht="25.5">
+    <row r="105" spans="1:57" ht="25.5">
       <c r="A105" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21562,34 +21684,35 @@
       <c r="AK105" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL105" s="5" t="s">
+      <c r="AL105" s="11"/>
+      <c r="AM105" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM105" s="11" t="s">
+      <c r="AN105" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="AN105" s="11" t="s">
+      <c r="AO105" s="11" t="s">
         <v>727</v>
       </c>
-      <c r="AO105" s="32" t="s">
+      <c r="AP105" s="32" t="s">
         <v>540</v>
       </c>
-      <c r="AP105" s="35" t="s">
+      <c r="AQ105" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ105" s="5" t="s">
+      <c r="AR105" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR105" s="11" t="s">
+      <c r="AS105" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS105" s="7" t="s">
+      <c r="AT105" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT105" s="14"/>
-      <c r="AU105" s="44"/>
+      <c r="AU105" s="14"/>
+      <c r="AV105" s="44"/>
     </row>
-    <row r="106" spans="1:56" ht="25.5">
+    <row r="106" spans="1:57" ht="25.5">
       <c r="A106" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21711,34 +21834,35 @@
       <c r="AK106" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL106" s="5" t="s">
+      <c r="AL106" s="11"/>
+      <c r="AM106" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM106" s="11" t="s">
+      <c r="AN106" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="AN106" s="11" t="s">
+      <c r="AO106" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="AO106" s="32" t="s">
+      <c r="AP106" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="AP106" s="35" t="s">
+      <c r="AQ106" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ106" s="5" t="s">
+      <c r="AR106" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR106" s="11" t="s">
+      <c r="AS106" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS106" s="7" t="s">
+      <c r="AT106" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT106" s="14"/>
-      <c r="AU106" s="44"/>
+      <c r="AU106" s="14"/>
+      <c r="AV106" s="44"/>
     </row>
-    <row r="107" spans="1:56" ht="25.5">
+    <row r="107" spans="1:57" ht="25.5">
       <c r="A107" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21862,34 +21986,35 @@
       <c r="AK107" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL107" s="5" t="s">
+      <c r="AL107" s="11"/>
+      <c r="AM107" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM107" s="11" t="s">
+      <c r="AN107" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="AN107" s="11" t="s">
+      <c r="AO107" s="11" t="s">
         <v>731</v>
       </c>
-      <c r="AO107" s="32" t="s">
+      <c r="AP107" s="32" t="s">
         <v>542</v>
       </c>
-      <c r="AP107" s="35" t="s">
+      <c r="AQ107" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ107" s="5" t="s">
+      <c r="AR107" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR107" s="11" t="s">
+      <c r="AS107" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS107" s="7" t="s">
+      <c r="AT107" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT107" s="14"/>
-      <c r="AU107" s="44"/>
+      <c r="AU107" s="14"/>
+      <c r="AV107" s="44"/>
     </row>
-    <row r="108" spans="1:56" ht="25.5">
+    <row r="108" spans="1:57" ht="25.5">
       <c r="A108" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22013,34 +22138,35 @@
       <c r="AK108" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL108" s="5" t="s">
+      <c r="AL108" s="11"/>
+      <c r="AM108" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM108" s="11" t="s">
+      <c r="AN108" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="AN108" s="11" t="s">
+      <c r="AO108" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="AO108" s="32" t="s">
+      <c r="AP108" s="32" t="s">
         <v>543</v>
       </c>
-      <c r="AP108" s="35" t="s">
+      <c r="AQ108" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ108" s="5" t="s">
+      <c r="AR108" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR108" s="11" t="s">
+      <c r="AS108" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS108" s="7" t="s">
+      <c r="AT108" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT108" s="14"/>
-      <c r="AU108" s="44"/>
+      <c r="AU108" s="14"/>
+      <c r="AV108" s="44"/>
     </row>
-    <row r="109" spans="1:56" ht="25.5">
+    <row r="109" spans="1:57" ht="25.5">
       <c r="A109" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22164,34 +22290,35 @@
       <c r="AK109" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL109" s="5" t="s">
+      <c r="AL109" s="11"/>
+      <c r="AM109" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM109" s="11" t="s">
+      <c r="AN109" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="AN109" s="11" t="s">
+      <c r="AO109" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="AO109" s="32" t="s">
+      <c r="AP109" s="32" t="s">
         <v>544</v>
       </c>
-      <c r="AP109" s="35" t="s">
+      <c r="AQ109" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ109" s="5" t="s">
+      <c r="AR109" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR109" s="11" t="s">
+      <c r="AS109" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS109" s="7" t="s">
+      <c r="AT109" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT109" s="14"/>
-      <c r="AU109" s="44"/>
+      <c r="AU109" s="14"/>
+      <c r="AV109" s="44"/>
     </row>
-    <row r="110" spans="1:56" ht="25.5">
+    <row r="110" spans="1:57" ht="25.5">
       <c r="A110" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22315,34 +22442,35 @@
       <c r="AK110" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL110" s="5" t="s">
+      <c r="AL110" s="11"/>
+      <c r="AM110" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM110" s="11" t="s">
+      <c r="AN110" s="11" t="s">
         <v>736</v>
       </c>
-      <c r="AN110" s="11" t="s">
+      <c r="AO110" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="AO110" s="32" t="s">
+      <c r="AP110" s="32" t="s">
         <v>545</v>
       </c>
-      <c r="AP110" s="35" t="s">
+      <c r="AQ110" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ110" s="5" t="s">
+      <c r="AR110" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR110" s="11" t="s">
+      <c r="AS110" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS110" s="7" t="s">
+      <c r="AT110" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT110" s="14"/>
-      <c r="AU110" s="44"/>
+      <c r="AU110" s="14"/>
+      <c r="AV110" s="44"/>
     </row>
-    <row r="111" spans="1:56" ht="25.5">
+    <row r="111" spans="1:57" ht="25.5">
       <c r="A111" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22466,34 +22594,35 @@
       <c r="AK111" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL111" s="5" t="s">
+      <c r="AL111" s="11"/>
+      <c r="AM111" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM111" s="11" t="s">
+      <c r="AN111" s="11" t="s">
         <v>738</v>
       </c>
-      <c r="AN111" s="11" t="s">
+      <c r="AO111" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="AO111" s="32" t="s">
+      <c r="AP111" s="32" t="s">
         <v>546</v>
       </c>
-      <c r="AP111" s="35" t="s">
+      <c r="AQ111" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ111" s="5" t="s">
+      <c r="AR111" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR111" s="11" t="s">
+      <c r="AS111" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS111" s="7" t="s">
+      <c r="AT111" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT111" s="14"/>
-      <c r="AU111" s="44"/>
+      <c r="AU111" s="14"/>
+      <c r="AV111" s="44"/>
     </row>
-    <row r="112" spans="1:56" ht="25.5">
+    <row r="112" spans="1:57" ht="25.5">
       <c r="A112" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22617,37 +22746,38 @@
       <c r="AK112" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL112" s="5" t="s">
+      <c r="AL112" s="11"/>
+      <c r="AM112" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM112" s="11" t="s">
+      <c r="AN112" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="AN112" s="11" t="s">
+      <c r="AO112" s="11" t="s">
         <v>741</v>
       </c>
-      <c r="AO112" s="32" t="s">
+      <c r="AP112" s="32" t="s">
         <v>547</v>
       </c>
-      <c r="AP112" s="35" t="s">
+      <c r="AQ112" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ112" s="5" t="s">
+      <c r="AR112" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR112" s="11" t="s">
+      <c r="AS112" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS112" s="7" t="s">
+      <c r="AT112" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT112" s="14"/>
-      <c r="AU112" s="44"/>
-      <c r="AW112" s="1"/>
-      <c r="BC112"/>
-      <c r="BD112" s="1"/>
+      <c r="AU112" s="14"/>
+      <c r="AV112" s="44"/>
+      <c r="AX112" s="1"/>
+      <c r="BD112"/>
+      <c r="BE112" s="1"/>
     </row>
-    <row r="113" spans="1:56" ht="25.5">
+    <row r="113" spans="1:57" ht="25.5">
       <c r="A113" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22771,37 +22901,38 @@
       <c r="AK113" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL113" s="5" t="s">
+      <c r="AL113" s="11"/>
+      <c r="AM113" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM113" s="11" t="s">
+      <c r="AN113" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="AN113" s="11" t="s">
+      <c r="AO113" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="AO113" s="32" t="s">
+      <c r="AP113" s="32" t="s">
         <v>548</v>
       </c>
-      <c r="AP113" s="35" t="s">
+      <c r="AQ113" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ113" s="5" t="s">
+      <c r="AR113" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR113" s="11" t="s">
+      <c r="AS113" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS113" s="7" t="s">
+      <c r="AT113" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT113" s="14"/>
-      <c r="AU113" s="44"/>
-      <c r="AW113" s="1"/>
-      <c r="BC113"/>
-      <c r="BD113" s="1"/>
+      <c r="AU113" s="14"/>
+      <c r="AV113" s="44"/>
+      <c r="AX113" s="1"/>
+      <c r="BD113"/>
+      <c r="BE113" s="1"/>
     </row>
-    <row r="114" spans="1:56" ht="25.5">
+    <row r="114" spans="1:57" ht="25.5">
       <c r="A114" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22925,37 +23056,38 @@
       <c r="AK114" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL114" s="5" t="s">
+      <c r="AL114" s="11"/>
+      <c r="AM114" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM114" s="11" t="s">
+      <c r="AN114" s="11" t="s">
         <v>744</v>
       </c>
-      <c r="AN114" s="11" t="s">
+      <c r="AO114" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="AO114" s="32" t="s">
+      <c r="AP114" s="32" t="s">
         <v>549</v>
       </c>
-      <c r="AP114" s="35" t="s">
+      <c r="AQ114" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ114" s="5" t="s">
+      <c r="AR114" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR114" s="11" t="s">
+      <c r="AS114" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS114" s="7" t="s">
+      <c r="AT114" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT114" s="14"/>
-      <c r="AU114" s="44"/>
-      <c r="AW114" s="1"/>
-      <c r="BC114"/>
-      <c r="BD114" s="1"/>
+      <c r="AU114" s="14"/>
+      <c r="AV114" s="44"/>
+      <c r="AX114" s="1"/>
+      <c r="BD114"/>
+      <c r="BE114" s="1"/>
     </row>
-    <row r="115" spans="1:56" ht="25.5">
+    <row r="115" spans="1:57" ht="25.5">
       <c r="A115" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -23079,37 +23211,38 @@
       <c r="AK115" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL115" s="5" t="s">
+      <c r="AL115" s="11"/>
+      <c r="AM115" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM115" s="11" t="s">
+      <c r="AN115" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="AN115" s="11" t="s">
+      <c r="AO115" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="AO115" s="32" t="s">
+      <c r="AP115" s="32" t="s">
         <v>550</v>
       </c>
-      <c r="AP115" s="35" t="s">
+      <c r="AQ115" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ115" s="5" t="s">
+      <c r="AR115" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR115" s="11" t="s">
+      <c r="AS115" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS115" s="7" t="s">
+      <c r="AT115" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT115" s="14"/>
-      <c r="AU115" s="44"/>
-      <c r="AW115" s="1"/>
-      <c r="BC115"/>
-      <c r="BD115" s="1"/>
+      <c r="AU115" s="14"/>
+      <c r="AV115" s="44"/>
+      <c r="AX115" s="1"/>
+      <c r="BD115"/>
+      <c r="BE115" s="1"/>
     </row>
-    <row r="116" spans="1:56" ht="25.5">
+    <row r="116" spans="1:57" ht="25.5">
       <c r="A116" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -23233,37 +23366,38 @@
       <c r="AK116" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="AL116" s="5" t="s">
+      <c r="AL116" s="11"/>
+      <c r="AM116" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM116" s="11" t="s">
+      <c r="AN116" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="AN116" s="11" t="s">
+      <c r="AO116" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="AO116" s="32" t="s">
+      <c r="AP116" s="32" t="s">
         <v>551</v>
       </c>
-      <c r="AP116" s="35" t="s">
+      <c r="AQ116" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="AQ116" s="5" t="s">
+      <c r="AR116" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AR116" s="11" t="s">
+      <c r="AS116" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AS116" s="7" t="s">
+      <c r="AT116" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AT116" s="14"/>
-      <c r="AU116" s="44"/>
-      <c r="AW116" s="1"/>
-      <c r="BC116"/>
-      <c r="BD116" s="1"/>
+      <c r="AU116" s="14"/>
+      <c r="AV116" s="44"/>
+      <c r="AX116" s="1"/>
+      <c r="BD116"/>
+      <c r="BE116" s="1"/>
     </row>
-    <row r="117" spans="1:56" ht="38.25">
+    <row r="117" spans="1:57" ht="38.25">
       <c r="A117" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -23388,37 +23522,38 @@
       <c r="AK117" s="11" t="s">
         <v>894</v>
       </c>
-      <c r="AL117" s="5" t="s">
+      <c r="AL117" s="11"/>
+      <c r="AM117" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM117" s="11" t="s">
+      <c r="AN117" s="11" t="s">
         <v>895</v>
       </c>
-      <c r="AN117" s="11" t="s">
+      <c r="AO117" s="11" t="s">
         <v>896</v>
       </c>
-      <c r="AO117" s="11">
+      <c r="AP117" s="11">
         <v>25</v>
       </c>
-      <c r="AP117" s="36" t="s">
+      <c r="AQ117" s="36" t="s">
         <v>899</v>
       </c>
-      <c r="AQ117" s="11" t="s">
+      <c r="AR117" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR117" s="11" t="s">
+      <c r="AS117" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS117" s="13" t="s">
+      <c r="AT117" s="13" t="s">
         <v>897</v>
       </c>
-      <c r="AT117" s="14"/>
-      <c r="AU117" s="44"/>
-      <c r="AW117" s="1"/>
-      <c r="BC117"/>
-      <c r="BD117" s="1"/>
+      <c r="AU117" s="14"/>
+      <c r="AV117" s="44"/>
+      <c r="AX117" s="1"/>
+      <c r="BD117"/>
+      <c r="BE117" s="1"/>
     </row>
-    <row r="118" spans="1:56" ht="38.25">
+    <row r="118" spans="1:57" ht="38.25">
       <c r="A118" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -23543,37 +23678,38 @@
       <c r="AK118" s="11" t="s">
         <v>907</v>
       </c>
-      <c r="AL118" s="5" t="s">
+      <c r="AL118" s="11"/>
+      <c r="AM118" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM118" s="11" t="s">
+      <c r="AN118" s="11" t="s">
         <v>908</v>
       </c>
-      <c r="AN118" s="11" t="s">
+      <c r="AO118" s="11" t="s">
         <v>909</v>
       </c>
-      <c r="AO118" s="11">
+      <c r="AP118" s="11">
         <v>26</v>
       </c>
-      <c r="AP118" s="36" t="s">
+      <c r="AQ118" s="36" t="s">
         <v>911</v>
       </c>
-      <c r="AQ118" s="11" t="s">
+      <c r="AR118" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR118" s="11" t="s">
+      <c r="AS118" s="11" t="s">
         <v>910</v>
       </c>
-      <c r="AS118" s="13" t="s">
+      <c r="AT118" s="13" t="s">
         <v>897</v>
       </c>
-      <c r="AT118" s="14"/>
-      <c r="AU118" s="44"/>
-      <c r="AW118" s="1"/>
-      <c r="BC118"/>
-      <c r="BD118" s="1"/>
+      <c r="AU118" s="14"/>
+      <c r="AV118" s="44"/>
+      <c r="AX118" s="1"/>
+      <c r="BD118"/>
+      <c r="BE118" s="1"/>
     </row>
-    <row r="119" spans="1:56" ht="25.5">
+    <row r="119" spans="1:57" ht="25.5">
       <c r="A119" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -23695,37 +23831,38 @@
       <c r="AK119" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="AL119" s="5" t="s">
+      <c r="AL119" s="11"/>
+      <c r="AM119" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM119" s="11" t="s">
+      <c r="AN119" s="11" t="s">
         <v>916</v>
       </c>
-      <c r="AN119" s="11" t="s">
+      <c r="AO119" s="11" t="s">
         <v>917</v>
       </c>
-      <c r="AO119" s="11">
+      <c r="AP119" s="11">
         <v>27</v>
       </c>
-      <c r="AP119" s="36" t="s">
+      <c r="AQ119" s="36" t="s">
         <v>924</v>
       </c>
-      <c r="AQ119" s="11" t="s">
+      <c r="AR119" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR119" s="11" t="s">
+      <c r="AS119" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS119" s="13" t="s">
+      <c r="AT119" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT119" s="14"/>
-      <c r="AU119" s="44"/>
-      <c r="AW119" s="1"/>
-      <c r="BC119"/>
-      <c r="BD119" s="1"/>
+      <c r="AU119" s="14"/>
+      <c r="AV119" s="44"/>
+      <c r="AX119" s="1"/>
+      <c r="BD119"/>
+      <c r="BE119" s="1"/>
     </row>
-    <row r="120" spans="1:56" ht="25.5">
+    <row r="120" spans="1:57" ht="25.5">
       <c r="A120" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -23849,37 +23986,38 @@
       <c r="AK120" s="11" t="s">
         <v>926</v>
       </c>
-      <c r="AL120" s="5" t="s">
+      <c r="AL120" s="11"/>
+      <c r="AM120" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM120" s="11" t="s">
+      <c r="AN120" s="11" t="s">
         <v>921</v>
       </c>
-      <c r="AN120" s="11" t="s">
+      <c r="AO120" s="11" t="s">
         <v>922</v>
       </c>
-      <c r="AO120" s="11">
+      <c r="AP120" s="11">
         <v>28</v>
       </c>
-      <c r="AP120" s="36" t="s">
+      <c r="AQ120" s="36" t="s">
         <v>925</v>
       </c>
-      <c r="AQ120" s="11" t="s">
+      <c r="AR120" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR120" s="11" t="s">
+      <c r="AS120" s="11" t="s">
         <v>923</v>
       </c>
-      <c r="AS120" s="13" t="s">
+      <c r="AT120" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AT120" s="14"/>
-      <c r="AU120" s="44"/>
-      <c r="AW120" s="1"/>
-      <c r="BC120"/>
-      <c r="BD120" s="1"/>
+      <c r="AU120" s="14"/>
+      <c r="AV120" s="44"/>
+      <c r="AX120" s="1"/>
+      <c r="BD120"/>
+      <c r="BE120" s="1"/>
     </row>
-    <row r="121" spans="1:56" ht="25.5">
+    <row r="121" spans="1:57" ht="25.5">
       <c r="A121" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24004,37 +24142,38 @@
       <c r="AK121" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL121" s="5" t="s">
+      <c r="AL121" s="11"/>
+      <c r="AM121" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM121" s="11" t="s">
+      <c r="AN121" s="11" t="s">
         <v>955</v>
       </c>
-      <c r="AN121" s="11" t="s">
+      <c r="AO121" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="AO121" s="11" t="s">
+      <c r="AP121" s="11" t="s">
         <v>935</v>
       </c>
-      <c r="AP121" s="36" t="s">
+      <c r="AQ121" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ121" s="11" t="s">
+      <c r="AR121" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR121" s="11" t="s">
+      <c r="AS121" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS121" s="13" t="s">
+      <c r="AT121" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT121" s="14"/>
-      <c r="AU121" s="44"/>
-      <c r="AW121" s="1"/>
-      <c r="BC121"/>
-      <c r="BD121" s="1"/>
+      <c r="AU121" s="14"/>
+      <c r="AV121" s="44"/>
+      <c r="AX121" s="1"/>
+      <c r="BD121"/>
+      <c r="BE121" s="1"/>
     </row>
-    <row r="122" spans="1:56" ht="25.5">
+    <row r="122" spans="1:57" ht="25.5">
       <c r="A122" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24159,37 +24298,38 @@
       <c r="AK122" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL122" s="5" t="s">
+      <c r="AL122" s="11"/>
+      <c r="AM122" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM122" s="11" t="s">
+      <c r="AN122" s="11" t="s">
         <v>957</v>
       </c>
-      <c r="AN122" s="11" t="s">
+      <c r="AO122" s="11" t="s">
         <v>958</v>
       </c>
-      <c r="AO122" s="11" t="s">
+      <c r="AP122" s="11" t="s">
         <v>936</v>
       </c>
-      <c r="AP122" s="36" t="s">
+      <c r="AQ122" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ122" s="11" t="s">
+      <c r="AR122" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR122" s="11" t="s">
+      <c r="AS122" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS122" s="13" t="s">
+      <c r="AT122" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT122" s="14"/>
-      <c r="AU122" s="44"/>
-      <c r="AW122" s="1"/>
-      <c r="BC122"/>
-      <c r="BD122" s="1"/>
+      <c r="AU122" s="14"/>
+      <c r="AV122" s="44"/>
+      <c r="AX122" s="1"/>
+      <c r="BD122"/>
+      <c r="BE122" s="1"/>
     </row>
-    <row r="123" spans="1:56" ht="25.5">
+    <row r="123" spans="1:57" ht="25.5">
       <c r="A123" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24314,37 +24454,38 @@
       <c r="AK123" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL123" s="5" t="s">
+      <c r="AL123" s="11"/>
+      <c r="AM123" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM123" s="11" t="s">
+      <c r="AN123" s="11" t="s">
         <v>959</v>
       </c>
-      <c r="AN123" s="11" t="s">
+      <c r="AO123" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="AO123" s="11" t="s">
+      <c r="AP123" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AP123" s="36" t="s">
+      <c r="AQ123" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ123" s="11" t="s">
+      <c r="AR123" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR123" s="11" t="s">
+      <c r="AS123" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS123" s="13" t="s">
+      <c r="AT123" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT123" s="14"/>
-      <c r="AU123" s="44"/>
-      <c r="AW123" s="1"/>
-      <c r="BC123"/>
-      <c r="BD123" s="1"/>
+      <c r="AU123" s="14"/>
+      <c r="AV123" s="44"/>
+      <c r="AX123" s="1"/>
+      <c r="BD123"/>
+      <c r="BE123" s="1"/>
     </row>
-    <row r="124" spans="1:56" ht="38.25">
+    <row r="124" spans="1:57" ht="38.25">
       <c r="A124" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24469,37 +24610,38 @@
       <c r="AK124" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="AL124" s="5" t="s">
+      <c r="AL124" s="11"/>
+      <c r="AM124" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM124" s="11" t="s">
+      <c r="AN124" s="11" t="s">
         <v>961</v>
       </c>
-      <c r="AN124" s="11" t="s">
+      <c r="AO124" s="11" t="s">
         <v>962</v>
       </c>
-      <c r="AO124" s="11" t="s">
+      <c r="AP124" s="11" t="s">
         <v>938</v>
       </c>
-      <c r="AP124" s="36" t="s">
+      <c r="AQ124" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ124" s="11" t="s">
+      <c r="AR124" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR124" s="11" t="s">
+      <c r="AS124" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS124" s="13" t="s">
+      <c r="AT124" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT124" s="14"/>
-      <c r="AU124" s="44"/>
-      <c r="AW124" s="1"/>
-      <c r="BC124"/>
-      <c r="BD124" s="1"/>
+      <c r="AU124" s="14"/>
+      <c r="AV124" s="44"/>
+      <c r="AX124" s="1"/>
+      <c r="BD124"/>
+      <c r="BE124" s="1"/>
     </row>
-    <row r="125" spans="1:56" ht="25.5">
+    <row r="125" spans="1:57" ht="25.5">
       <c r="A125" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24624,37 +24766,38 @@
       <c r="AK125" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL125" s="5" t="s">
+      <c r="AL125" s="11"/>
+      <c r="AM125" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM125" s="11" t="s">
+      <c r="AN125" s="11" t="s">
         <v>963</v>
       </c>
-      <c r="AN125" s="11" t="s">
+      <c r="AO125" s="11" t="s">
         <v>964</v>
       </c>
-      <c r="AO125" s="11" t="s">
+      <c r="AP125" s="11" t="s">
         <v>939</v>
       </c>
-      <c r="AP125" s="36" t="s">
+      <c r="AQ125" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ125" s="11" t="s">
+      <c r="AR125" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR125" s="11" t="s">
+      <c r="AS125" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS125" s="13" t="s">
+      <c r="AT125" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT125" s="14"/>
-      <c r="AU125" s="44"/>
-      <c r="AW125" s="1"/>
-      <c r="BC125"/>
-      <c r="BD125" s="1"/>
+      <c r="AU125" s="14"/>
+      <c r="AV125" s="44"/>
+      <c r="AX125" s="1"/>
+      <c r="BD125"/>
+      <c r="BE125" s="1"/>
     </row>
-    <row r="126" spans="1:56" ht="25.5">
+    <row r="126" spans="1:57" ht="25.5">
       <c r="A126" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24779,34 +24922,35 @@
       <c r="AK126" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL126" s="5" t="s">
+      <c r="AL126" s="11"/>
+      <c r="AM126" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM126" s="11" t="s">
+      <c r="AN126" s="11" t="s">
         <v>971</v>
       </c>
-      <c r="AN126" s="11" t="s">
+      <c r="AO126" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="AO126" s="11" t="s">
+      <c r="AP126" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="AP126" s="36" t="s">
+      <c r="AQ126" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ126" s="11" t="s">
+      <c r="AR126" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR126" s="11" t="s">
+      <c r="AS126" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS126" s="13" t="s">
+      <c r="AT126" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT126" s="14"/>
-      <c r="AU126" s="44"/>
+      <c r="AU126" s="14"/>
+      <c r="AV126" s="44"/>
     </row>
-    <row r="127" spans="1:56" ht="25.5">
+    <row r="127" spans="1:57" ht="25.5">
       <c r="A127" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24931,34 +25075,35 @@
       <c r="AK127" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL127" s="5" t="s">
+      <c r="AL127" s="11"/>
+      <c r="AM127" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM127" s="11" t="s">
+      <c r="AN127" s="11" t="s">
         <v>969</v>
       </c>
-      <c r="AN127" s="11" t="s">
+      <c r="AO127" s="11" t="s">
         <v>970</v>
       </c>
-      <c r="AO127" s="11" t="s">
+      <c r="AP127" s="11" t="s">
         <v>941</v>
       </c>
-      <c r="AP127" s="36" t="s">
+      <c r="AQ127" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ127" s="11" t="s">
+      <c r="AR127" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR127" s="11" t="s">
+      <c r="AS127" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS127" s="13" t="s">
+      <c r="AT127" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT127" s="14"/>
-      <c r="AU127" s="44"/>
+      <c r="AU127" s="14"/>
+      <c r="AV127" s="44"/>
     </row>
-    <row r="128" spans="1:56" ht="25.5">
+    <row r="128" spans="1:57" ht="25.5">
       <c r="A128" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25083,34 +25228,35 @@
       <c r="AK128" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL128" s="5" t="s">
+      <c r="AL128" s="11"/>
+      <c r="AM128" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM128" s="11" t="s">
+      <c r="AN128" s="11" t="s">
         <v>967</v>
       </c>
-      <c r="AN128" s="11" t="s">
+      <c r="AO128" s="11" t="s">
         <v>968</v>
       </c>
-      <c r="AO128" s="11" t="s">
+      <c r="AP128" s="11" t="s">
         <v>942</v>
       </c>
-      <c r="AP128" s="36" t="s">
+      <c r="AQ128" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ128" s="11" t="s">
+      <c r="AR128" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR128" s="11" t="s">
+      <c r="AS128" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS128" s="13" t="s">
+      <c r="AT128" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT128" s="14"/>
-      <c r="AU128" s="44"/>
+      <c r="AU128" s="14"/>
+      <c r="AV128" s="44"/>
     </row>
-    <row r="129" spans="1:47" ht="25.5">
+    <row r="129" spans="1:48" ht="25.5">
       <c r="A129" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25235,34 +25381,35 @@
       <c r="AK129" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL129" s="5" t="s">
+      <c r="AL129" s="11"/>
+      <c r="AM129" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM129" s="11" t="s">
+      <c r="AN129" s="11" t="s">
         <v>965</v>
       </c>
-      <c r="AN129" s="11" t="s">
+      <c r="AO129" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="AO129" s="11" t="s">
+      <c r="AP129" s="11" t="s">
         <v>943</v>
       </c>
-      <c r="AP129" s="36" t="s">
+      <c r="AQ129" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ129" s="11" t="s">
+      <c r="AR129" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR129" s="11" t="s">
+      <c r="AS129" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS129" s="13" t="s">
+      <c r="AT129" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT129" s="14"/>
-      <c r="AU129" s="44"/>
+      <c r="AU129" s="14"/>
+      <c r="AV129" s="44"/>
     </row>
-    <row r="130" spans="1:47" ht="25.5">
+    <row r="130" spans="1:48" ht="25.5">
       <c r="A130" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25387,34 +25534,35 @@
       <c r="AK130" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL130" s="5" t="s">
+      <c r="AL130" s="11"/>
+      <c r="AM130" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM130" s="11" t="s">
+      <c r="AN130" s="11" t="s">
         <v>973</v>
       </c>
-      <c r="AN130" s="11" t="s">
+      <c r="AO130" s="11" t="s">
         <v>974</v>
       </c>
-      <c r="AO130" s="11" t="s">
+      <c r="AP130" s="11" t="s">
         <v>944</v>
       </c>
-      <c r="AP130" s="36" t="s">
+      <c r="AQ130" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ130" s="11" t="s">
+      <c r="AR130" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR130" s="11" t="s">
+      <c r="AS130" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS130" s="13" t="s">
+      <c r="AT130" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT130" s="14"/>
-      <c r="AU130" s="44"/>
+      <c r="AU130" s="14"/>
+      <c r="AV130" s="44"/>
     </row>
-    <row r="131" spans="1:47" ht="25.5">
+    <row r="131" spans="1:48" ht="25.5">
       <c r="A131" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25539,34 +25687,35 @@
       <c r="AK131" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL131" s="5" t="s">
+      <c r="AL131" s="11"/>
+      <c r="AM131" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM131" s="11" t="s">
+      <c r="AN131" s="11" t="s">
         <v>975</v>
       </c>
-      <c r="AN131" s="11" t="s">
+      <c r="AO131" s="11" t="s">
         <v>976</v>
       </c>
-      <c r="AO131" s="11" t="s">
+      <c r="AP131" s="11" t="s">
         <v>945</v>
       </c>
-      <c r="AP131" s="36" t="s">
+      <c r="AQ131" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ131" s="11" t="s">
+      <c r="AR131" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR131" s="11" t="s">
+      <c r="AS131" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS131" s="13" t="s">
+      <c r="AT131" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT131" s="14"/>
-      <c r="AU131" s="44"/>
+      <c r="AU131" s="14"/>
+      <c r="AV131" s="44"/>
     </row>
-    <row r="132" spans="1:47" ht="25.5">
+    <row r="132" spans="1:48" ht="25.5">
       <c r="A132" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25691,34 +25840,35 @@
       <c r="AK132" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL132" s="5" t="s">
+      <c r="AL132" s="11"/>
+      <c r="AM132" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM132" s="11" t="s">
+      <c r="AN132" s="11" t="s">
         <v>977</v>
       </c>
-      <c r="AN132" s="11" t="s">
+      <c r="AO132" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="AO132" s="11" t="s">
+      <c r="AP132" s="11" t="s">
         <v>946</v>
       </c>
-      <c r="AP132" s="36" t="s">
+      <c r="AQ132" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ132" s="11" t="s">
+      <c r="AR132" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR132" s="11" t="s">
+      <c r="AS132" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS132" s="13" t="s">
+      <c r="AT132" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT132" s="14"/>
-      <c r="AU132" s="44"/>
+      <c r="AU132" s="14"/>
+      <c r="AV132" s="44"/>
     </row>
-    <row r="133" spans="1:47" ht="25.5">
+    <row r="133" spans="1:48" ht="25.5">
       <c r="A133" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25843,34 +25993,35 @@
       <c r="AK133" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL133" s="5" t="s">
+      <c r="AL133" s="11"/>
+      <c r="AM133" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM133" s="11" t="s">
+      <c r="AN133" s="11" t="s">
         <v>979</v>
       </c>
-      <c r="AN133" s="11" t="s">
+      <c r="AO133" s="11" t="s">
         <v>980</v>
       </c>
-      <c r="AO133" s="11" t="s">
+      <c r="AP133" s="11" t="s">
         <v>947</v>
       </c>
-      <c r="AP133" s="36" t="s">
+      <c r="AQ133" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ133" s="11" t="s">
+      <c r="AR133" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR133" s="11" t="s">
+      <c r="AS133" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS133" s="13" t="s">
+      <c r="AT133" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT133" s="14"/>
-      <c r="AU133" s="44"/>
+      <c r="AU133" s="14"/>
+      <c r="AV133" s="44"/>
     </row>
-    <row r="134" spans="1:47" ht="25.5">
+    <row r="134" spans="1:48" ht="25.5">
       <c r="A134" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25995,34 +26146,35 @@
       <c r="AK134" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL134" s="5" t="s">
+      <c r="AL134" s="11"/>
+      <c r="AM134" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM134" s="11" t="s">
+      <c r="AN134" s="11" t="s">
         <v>981</v>
       </c>
-      <c r="AN134" s="11" t="s">
+      <c r="AO134" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="AO134" s="11" t="s">
+      <c r="AP134" s="11" t="s">
         <v>948</v>
       </c>
-      <c r="AP134" s="36" t="s">
+      <c r="AQ134" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ134" s="11" t="s">
+      <c r="AR134" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR134" s="11" t="s">
+      <c r="AS134" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS134" s="13" t="s">
+      <c r="AT134" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT134" s="14"/>
-      <c r="AU134" s="44"/>
+      <c r="AU134" s="14"/>
+      <c r="AV134" s="44"/>
     </row>
-    <row r="135" spans="1:47" ht="25.5">
+    <row r="135" spans="1:48" ht="25.5">
       <c r="A135" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26147,34 +26299,35 @@
       <c r="AK135" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL135" s="5" t="s">
+      <c r="AL135" s="11"/>
+      <c r="AM135" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM135" s="11" t="s">
+      <c r="AN135" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="AN135" s="11" t="s">
+      <c r="AO135" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="AO135" s="11" t="s">
+      <c r="AP135" s="11" t="s">
         <v>949</v>
       </c>
-      <c r="AP135" s="36" t="s">
+      <c r="AQ135" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ135" s="11" t="s">
+      <c r="AR135" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR135" s="11" t="s">
+      <c r="AS135" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS135" s="13" t="s">
+      <c r="AT135" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT135" s="14"/>
-      <c r="AU135" s="44"/>
+      <c r="AU135" s="14"/>
+      <c r="AV135" s="44"/>
     </row>
-    <row r="136" spans="1:47" ht="25.5">
+    <row r="136" spans="1:48" ht="25.5">
       <c r="A136" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26299,34 +26452,35 @@
       <c r="AK136" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL136" s="5" t="s">
+      <c r="AL136" s="11"/>
+      <c r="AM136" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM136" s="11" t="s">
+      <c r="AN136" s="11" t="s">
         <v>985</v>
       </c>
-      <c r="AN136" s="11" t="s">
+      <c r="AO136" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="AO136" s="11" t="s">
+      <c r="AP136" s="11" t="s">
         <v>950</v>
       </c>
-      <c r="AP136" s="36" t="s">
+      <c r="AQ136" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ136" s="11" t="s">
+      <c r="AR136" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR136" s="11" t="s">
+      <c r="AS136" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS136" s="13" t="s">
+      <c r="AT136" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT136" s="14"/>
-      <c r="AU136" s="44"/>
+      <c r="AU136" s="14"/>
+      <c r="AV136" s="44"/>
     </row>
-    <row r="137" spans="1:47" ht="25.5">
+    <row r="137" spans="1:48" ht="25.5">
       <c r="A137" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26451,34 +26605,35 @@
       <c r="AK137" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="AL137" s="5" t="s">
+      <c r="AL137" s="11"/>
+      <c r="AM137" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM137" s="11" t="s">
+      <c r="AN137" s="11" t="s">
         <v>987</v>
       </c>
-      <c r="AN137" s="11" t="s">
+      <c r="AO137" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="AO137" s="11" t="s">
+      <c r="AP137" s="11" t="s">
         <v>951</v>
       </c>
-      <c r="AP137" s="36" t="s">
+      <c r="AQ137" s="36" t="s">
         <v>1399</v>
       </c>
-      <c r="AQ137" s="11" t="s">
+      <c r="AR137" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR137" s="11" t="s">
+      <c r="AS137" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="AS137" s="13" t="s">
+      <c r="AT137" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT137" s="14"/>
-      <c r="AU137" s="44"/>
+      <c r="AU137" s="14"/>
+      <c r="AV137" s="44"/>
     </row>
-    <row r="138" spans="1:47" ht="38.25">
+    <row r="138" spans="1:48" ht="38.25">
       <c r="A138" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26603,34 +26758,35 @@
       <c r="AK138" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="AL138" s="5" t="s">
+      <c r="AL138" s="11"/>
+      <c r="AM138" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM138" s="11" t="s">
+      <c r="AN138" s="11" t="s">
         <v>1409</v>
       </c>
-      <c r="AN138" s="11" t="s">
+      <c r="AO138" s="11" t="s">
         <v>1410</v>
       </c>
-      <c r="AO138" s="11" t="s">
+      <c r="AP138" s="11" t="s">
         <v>1400</v>
       </c>
-      <c r="AP138" s="36" t="s">
+      <c r="AQ138" s="36" t="s">
         <v>1404</v>
       </c>
-      <c r="AQ138" s="11" t="s">
+      <c r="AR138" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR138" s="11" t="s">
+      <c r="AS138" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="AS138" s="13" t="s">
+      <c r="AT138" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT138" s="14"/>
-      <c r="AU138" s="44"/>
+      <c r="AU138" s="14"/>
+      <c r="AV138" s="44"/>
     </row>
-    <row r="139" spans="1:47" ht="38.25">
+    <row r="139" spans="1:48" ht="38.25">
       <c r="A139" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26755,34 +26911,35 @@
       <c r="AK139" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="AL139" s="5" t="s">
+      <c r="AL139" s="11"/>
+      <c r="AM139" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM139" s="11" t="s">
+      <c r="AN139" s="11" t="s">
         <v>1407</v>
       </c>
-      <c r="AN139" s="11" t="s">
+      <c r="AO139" s="11" t="s">
         <v>1408</v>
       </c>
-      <c r="AO139" s="11" t="s">
+      <c r="AP139" s="11" t="s">
         <v>1401</v>
       </c>
-      <c r="AP139" s="36" t="s">
+      <c r="AQ139" s="36" t="s">
         <v>1405</v>
       </c>
-      <c r="AQ139" s="11" t="s">
+      <c r="AR139" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR139" s="11" t="s">
+      <c r="AS139" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="AS139" s="13" t="s">
+      <c r="AT139" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT139" s="14"/>
-      <c r="AU139" s="44"/>
+      <c r="AU139" s="14"/>
+      <c r="AV139" s="44"/>
     </row>
-    <row r="140" spans="1:47" ht="38.25">
+    <row r="140" spans="1:48" ht="38.25">
       <c r="A140" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26905,34 +27062,35 @@
       <c r="AK140" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="AL140" s="5" t="s">
+      <c r="AL140" s="11"/>
+      <c r="AM140" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM140" s="11" t="s">
+      <c r="AN140" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="AN140" s="11" t="s">
+      <c r="AO140" s="11" t="s">
         <v>1008</v>
       </c>
-      <c r="AO140" s="11" t="s">
+      <c r="AP140" s="11" t="s">
         <v>999</v>
       </c>
-      <c r="AP140" s="36" t="s">
+      <c r="AQ140" s="36" t="s">
         <v>1033</v>
       </c>
-      <c r="AQ140" s="11" t="s">
+      <c r="AR140" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR140" s="11" t="s">
+      <c r="AS140" s="11" t="s">
         <v>1411</v>
       </c>
-      <c r="AS140" s="13" t="s">
+      <c r="AT140" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT140" s="14"/>
-      <c r="AU140" s="44"/>
+      <c r="AU140" s="14"/>
+      <c r="AV140" s="44"/>
     </row>
-    <row r="141" spans="1:47" ht="38.25">
+    <row r="141" spans="1:48" ht="38.25">
       <c r="A141" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27055,34 +27213,35 @@
       <c r="AK141" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="AL141" s="5" t="s">
+      <c r="AL141" s="11"/>
+      <c r="AM141" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM141" s="11" t="s">
+      <c r="AN141" s="11" t="s">
         <v>1009</v>
       </c>
-      <c r="AN141" s="11" t="s">
+      <c r="AO141" s="11" t="s">
         <v>1010</v>
       </c>
-      <c r="AO141" s="11" t="s">
+      <c r="AP141" s="11" t="s">
         <v>1000</v>
       </c>
-      <c r="AP141" s="36" t="s">
+      <c r="AQ141" s="36" t="s">
         <v>1033</v>
       </c>
-      <c r="AQ141" s="11" t="s">
+      <c r="AR141" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR141" s="11" t="s">
+      <c r="AS141" s="11" t="s">
         <v>1411</v>
       </c>
-      <c r="AS141" s="13" t="s">
+      <c r="AT141" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT141" s="14"/>
-      <c r="AU141" s="44"/>
+      <c r="AU141" s="14"/>
+      <c r="AV141" s="44"/>
     </row>
-    <row r="142" spans="1:47" ht="38.25">
+    <row r="142" spans="1:48" ht="38.25">
       <c r="A142" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27205,34 +27364,35 @@
       <c r="AK142" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="AL142" s="5" t="s">
+      <c r="AL142" s="11"/>
+      <c r="AM142" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM142" s="11" t="s">
+      <c r="AN142" s="11" t="s">
         <v>1011</v>
       </c>
-      <c r="AN142" s="11" t="s">
+      <c r="AO142" s="11" t="s">
         <v>1012</v>
       </c>
-      <c r="AO142" s="11" t="s">
+      <c r="AP142" s="11" t="s">
         <v>1001</v>
       </c>
-      <c r="AP142" s="36" t="s">
+      <c r="AQ142" s="36" t="s">
         <v>1033</v>
       </c>
-      <c r="AQ142" s="11" t="s">
+      <c r="AR142" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR142" s="11" t="s">
+      <c r="AS142" s="11" t="s">
         <v>1411</v>
       </c>
-      <c r="AS142" s="13" t="s">
+      <c r="AT142" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT142" s="14"/>
-      <c r="AU142" s="44"/>
+      <c r="AU142" s="14"/>
+      <c r="AV142" s="44"/>
     </row>
-    <row r="143" spans="1:47" ht="38.25">
+    <row r="143" spans="1:48" ht="38.25">
       <c r="A143" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27355,34 +27515,35 @@
       <c r="AK143" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="AL143" s="5" t="s">
+      <c r="AL143" s="11"/>
+      <c r="AM143" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM143" s="11" t="s">
+      <c r="AN143" s="11" t="s">
         <v>1013</v>
       </c>
-      <c r="AN143" s="11" t="s">
+      <c r="AO143" s="11" t="s">
         <v>1014</v>
       </c>
-      <c r="AO143" s="11" t="s">
+      <c r="AP143" s="11" t="s">
         <v>1002</v>
       </c>
-      <c r="AP143" s="36" t="s">
+      <c r="AQ143" s="36" t="s">
         <v>1033</v>
       </c>
-      <c r="AQ143" s="11" t="s">
+      <c r="AR143" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR143" s="11" t="s">
+      <c r="AS143" s="11" t="s">
         <v>1413</v>
       </c>
-      <c r="AS143" s="13" t="s">
+      <c r="AT143" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT143" s="14"/>
-      <c r="AU143" s="44"/>
+      <c r="AU143" s="14"/>
+      <c r="AV143" s="44"/>
     </row>
-    <row r="144" spans="1:47" ht="38.25">
+    <row r="144" spans="1:48" ht="38.25">
       <c r="A144" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27500,34 +27661,35 @@
       <c r="AK144" s="11" t="s">
         <v>1406</v>
       </c>
-      <c r="AL144" s="5" t="s">
+      <c r="AL144" s="11"/>
+      <c r="AM144" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM144" s="11" t="s">
+      <c r="AN144" s="11" t="s">
         <v>1015</v>
       </c>
-      <c r="AN144" s="11" t="s">
+      <c r="AO144" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="AO144" s="11" t="s">
+      <c r="AP144" s="11" t="s">
         <v>1003</v>
       </c>
-      <c r="AP144" s="36" t="s">
+      <c r="AQ144" s="36" t="s">
         <v>1034</v>
       </c>
-      <c r="AQ144" s="11" t="s">
+      <c r="AR144" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR144" s="11" t="s">
+      <c r="AS144" s="11" t="s">
         <v>1412</v>
       </c>
-      <c r="AS144" s="13" t="s">
+      <c r="AT144" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AT144" s="14"/>
-      <c r="AU144" s="44"/>
+      <c r="AU144" s="14"/>
+      <c r="AV144" s="44"/>
     </row>
-    <row r="145" spans="1:47" ht="51">
+    <row r="145" spans="1:48" ht="51">
       <c r="A145" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -27652,34 +27814,35 @@
       <c r="AK145" s="11" t="s">
         <v>1185</v>
       </c>
-      <c r="AL145" s="5" t="s">
+      <c r="AL145" s="11"/>
+      <c r="AM145" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM145" s="11" t="s">
+      <c r="AN145" s="11" t="s">
         <v>1024</v>
       </c>
-      <c r="AN145" s="11" t="s">
+      <c r="AO145" s="11" t="s">
         <v>1025</v>
       </c>
-      <c r="AO145" s="11" t="s">
+      <c r="AP145" s="11" t="s">
         <v>1017</v>
       </c>
-      <c r="AP145" s="36" t="s">
+      <c r="AQ145" s="36" t="s">
         <v>1032</v>
       </c>
-      <c r="AQ145" s="11" t="s">
+      <c r="AR145" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR145" s="11" t="s">
+      <c r="AS145" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="AS145" s="13" t="s">
+      <c r="AT145" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT145" s="14"/>
-      <c r="AU145" s="44"/>
+      <c r="AU145" s="14"/>
+      <c r="AV145" s="44"/>
     </row>
-    <row r="146" spans="1:47" ht="38.25">
+    <row r="146" spans="1:48" ht="38.25">
       <c r="A146" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -27804,34 +27967,35 @@
       <c r="AK146" s="11" t="s">
         <v>1186</v>
       </c>
-      <c r="AL146" s="5" t="s">
+      <c r="AL146" s="11"/>
+      <c r="AM146" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM146" s="11" t="s">
+      <c r="AN146" s="11" t="s">
         <v>1026</v>
       </c>
-      <c r="AN146" s="11" t="s">
+      <c r="AO146" s="11" t="s">
         <v>1027</v>
       </c>
-      <c r="AO146" s="11" t="s">
+      <c r="AP146" s="11" t="s">
         <v>1018</v>
       </c>
-      <c r="AP146" s="36" t="s">
+      <c r="AQ146" s="36" t="s">
         <v>1029</v>
       </c>
-      <c r="AQ146" s="11" t="s">
+      <c r="AR146" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR146" s="11" t="s">
+      <c r="AS146" s="11" t="s">
         <v>1023</v>
       </c>
-      <c r="AS146" s="13" t="s">
+      <c r="AT146" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AT146" s="14"/>
-      <c r="AU146" s="44"/>
+      <c r="AU146" s="14"/>
+      <c r="AV146" s="44"/>
     </row>
-    <row r="147" spans="1:47" ht="25.5">
+    <row r="147" spans="1:48" ht="25.5">
       <c r="A147" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -27941,32 +28105,33 @@
       <c r="AK147" s="11" t="s">
         <v>1049</v>
       </c>
-      <c r="AL147" s="5" t="s">
+      <c r="AL147" s="11"/>
+      <c r="AM147" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM147" s="11" t="s">
+      <c r="AN147" s="11" t="s">
         <v>1038</v>
       </c>
-      <c r="AN147" s="11" t="s">
+      <c r="AO147" s="11" t="s">
         <v>1039</v>
       </c>
-      <c r="AO147" s="11">
+      <c r="AP147" s="11">
         <v>33</v>
       </c>
-      <c r="AP147" s="36" t="s">
+      <c r="AQ147" s="36" t="s">
         <v>1050</v>
       </c>
-      <c r="AQ147" s="11" t="s">
+      <c r="AR147" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR147" s="11"/>
-      <c r="AS147" s="13" t="s">
+      <c r="AS147" s="11"/>
+      <c r="AT147" s="13" t="s">
         <v>1046</v>
       </c>
-      <c r="AT147" s="14"/>
-      <c r="AU147" s="44"/>
+      <c r="AU147" s="14"/>
+      <c r="AV147" s="44"/>
     </row>
-    <row r="148" spans="1:47" ht="38.25">
+    <row r="148" spans="1:48" ht="38.25">
       <c r="A148" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28089,36 +28254,37 @@
       <c r="AK148" s="11" t="s">
         <v>1048</v>
       </c>
-      <c r="AL148" s="5" t="s">
+      <c r="AL148" s="11"/>
+      <c r="AM148" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM148" s="11" t="s">
+      <c r="AN148" s="11" t="s">
         <v>1043</v>
       </c>
-      <c r="AN148" s="11" t="s">
+      <c r="AO148" s="11" t="s">
         <v>1044</v>
       </c>
-      <c r="AO148" s="11">
+      <c r="AP148" s="11">
         <v>34</v>
       </c>
-      <c r="AP148" s="36" t="s">
+      <c r="AQ148" s="36" t="s">
         <v>1051</v>
       </c>
-      <c r="AQ148" s="11" t="s">
+      <c r="AR148" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR148" s="43" t="s">
+      <c r="AS148" s="43" t="s">
         <v>1047</v>
       </c>
-      <c r="AS148" s="13" t="s">
+      <c r="AT148" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="AT148" s="14"/>
-      <c r="AU148" s="44">
+      <c r="AU148" s="14"/>
+      <c r="AV148" s="44">
         <v>45999</v>
       </c>
     </row>
-    <row r="149" spans="1:47" ht="38.25">
+    <row r="149" spans="1:48" ht="38.25">
       <c r="A149" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28244,36 +28410,37 @@
       <c r="AK149" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="AL149" s="5" t="s">
+      <c r="AL149" s="11"/>
+      <c r="AM149" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM149" s="11" t="s">
+      <c r="AN149" s="11" t="s">
         <v>1061</v>
       </c>
-      <c r="AN149" s="11" t="s">
+      <c r="AO149" s="11" t="s">
         <v>1062</v>
       </c>
-      <c r="AO149" s="11" t="s">
+      <c r="AP149" s="11" t="s">
         <v>1054</v>
       </c>
-      <c r="AP149" s="36" t="s">
+      <c r="AQ149" s="36" t="s">
         <v>1071</v>
       </c>
-      <c r="AQ149" s="11" t="s">
+      <c r="AR149" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR149" s="11" t="s">
+      <c r="AS149" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="AS149" s="13" t="s">
+      <c r="AT149" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="AT149" s="14"/>
-      <c r="AU149" s="44">
+      <c r="AU149" s="14"/>
+      <c r="AV149" s="44">
         <v>45999</v>
       </c>
     </row>
-    <row r="150" spans="1:47" ht="38.25">
+    <row r="150" spans="1:48" ht="38.25">
       <c r="A150" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28399,36 +28566,37 @@
       <c r="AK150" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="AL150" s="5" t="s">
+      <c r="AL150" s="11"/>
+      <c r="AM150" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM150" s="11" t="s">
+      <c r="AN150" s="11" t="s">
         <v>1063</v>
       </c>
-      <c r="AN150" s="11" t="s">
+      <c r="AO150" s="11" t="s">
         <v>1064</v>
       </c>
-      <c r="AO150" s="11" t="s">
+      <c r="AP150" s="11" t="s">
         <v>1057</v>
       </c>
-      <c r="AP150" s="36" t="s">
+      <c r="AQ150" s="36" t="s">
         <v>1071</v>
       </c>
-      <c r="AQ150" s="11" t="s">
+      <c r="AR150" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR150" s="11" t="s">
+      <c r="AS150" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="AS150" s="13" t="s">
+      <c r="AT150" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="AT150" s="14"/>
-      <c r="AU150" s="44">
+      <c r="AU150" s="14"/>
+      <c r="AV150" s="44">
         <v>45999</v>
       </c>
     </row>
-    <row r="151" spans="1:47" ht="38.25">
+    <row r="151" spans="1:48" ht="38.25">
       <c r="A151" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28554,36 +28722,37 @@
       <c r="AK151" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="AL151" s="5" t="s">
+      <c r="AL151" s="11"/>
+      <c r="AM151" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM151" s="11" t="s">
+      <c r="AN151" s="11" t="s">
         <v>1065</v>
       </c>
-      <c r="AN151" s="11" t="s">
+      <c r="AO151" s="11" t="s">
         <v>1066</v>
       </c>
-      <c r="AO151" s="11" t="s">
+      <c r="AP151" s="11" t="s">
         <v>1058</v>
       </c>
-      <c r="AP151" s="36" t="s">
+      <c r="AQ151" s="36" t="s">
         <v>1071</v>
       </c>
-      <c r="AQ151" s="11" t="s">
+      <c r="AR151" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR151" s="11" t="s">
+      <c r="AS151" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="AS151" s="13" t="s">
+      <c r="AT151" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="AT151" s="14"/>
-      <c r="AU151" s="44">
+      <c r="AU151" s="14"/>
+      <c r="AV151" s="44">
         <v>45999</v>
       </c>
     </row>
-    <row r="152" spans="1:47" ht="38.25">
+    <row r="152" spans="1:48" ht="38.25">
       <c r="A152" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28709,36 +28878,37 @@
       <c r="AK152" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="AL152" s="5" t="s">
+      <c r="AL152" s="11"/>
+      <c r="AM152" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM152" s="11" t="s">
+      <c r="AN152" s="11" t="s">
         <v>1067</v>
       </c>
-      <c r="AN152" s="11" t="s">
+      <c r="AO152" s="11" t="s">
         <v>1068</v>
       </c>
-      <c r="AO152" s="11" t="s">
+      <c r="AP152" s="11" t="s">
         <v>1059</v>
       </c>
-      <c r="AP152" s="36" t="s">
+      <c r="AQ152" s="36" t="s">
         <v>1071</v>
       </c>
-      <c r="AQ152" s="11" t="s">
+      <c r="AR152" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR152" s="11" t="s">
+      <c r="AS152" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="AS152" s="13" t="s">
+      <c r="AT152" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="AT152" s="14"/>
-      <c r="AU152" s="44">
+      <c r="AU152" s="14"/>
+      <c r="AV152" s="44">
         <v>45999</v>
       </c>
     </row>
-    <row r="153" spans="1:47" ht="38.25">
+    <row r="153" spans="1:48" ht="38.25">
       <c r="A153" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28864,36 +29034,37 @@
       <c r="AK153" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="AL153" s="5" t="s">
+      <c r="AL153" s="11"/>
+      <c r="AM153" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM153" s="11" t="s">
+      <c r="AN153" s="11" t="s">
         <v>1069</v>
       </c>
-      <c r="AN153" s="11" t="s">
+      <c r="AO153" s="11" t="s">
         <v>1070</v>
       </c>
-      <c r="AO153" s="11" t="s">
+      <c r="AP153" s="11" t="s">
         <v>1060</v>
       </c>
-      <c r="AP153" s="36" t="s">
+      <c r="AQ153" s="36" t="s">
         <v>1071</v>
       </c>
-      <c r="AQ153" s="11" t="s">
+      <c r="AR153" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR153" s="11" t="s">
+      <c r="AS153" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="AS153" s="13" t="s">
+      <c r="AT153" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="AT153" s="14"/>
-      <c r="AU153" s="44">
+      <c r="AU153" s="14"/>
+      <c r="AV153" s="44">
         <v>45999</v>
       </c>
     </row>
-    <row r="154" spans="1:47" ht="38.25">
+    <row r="154" spans="1:48" ht="38.25">
       <c r="A154" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29018,36 +29189,39 @@
       <c r="AK154" s="11" t="s">
         <v>1198</v>
       </c>
-      <c r="AL154" s="5" t="s">
+      <c r="AL154" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM154" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM154" s="11">
+      <c r="AN154" s="11">
         <v>43.4393873</v>
       </c>
-      <c r="AN154" s="11">
+      <c r="AO154" s="11">
         <v>5.2419589999999996</v>
       </c>
-      <c r="AO154" s="11" t="s">
+      <c r="AP154" s="11" t="s">
         <v>1203</v>
       </c>
-      <c r="AP154" s="36" t="s">
+      <c r="AQ154" s="36" t="s">
         <v>1265</v>
       </c>
-      <c r="AQ154" s="11" t="s">
+      <c r="AR154" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR154" s="11" t="s">
+      <c r="AS154" s="11" t="s">
         <v>1197</v>
       </c>
-      <c r="AS154" s="13" t="s">
+      <c r="AT154" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT154" s="14"/>
-      <c r="AU154" s="44">
+      <c r="AU154" s="14"/>
+      <c r="AV154" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="155" spans="1:47" ht="51" hidden="1">
+    <row r="155" spans="1:48" ht="51" hidden="1">
       <c r="A155" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29172,36 +29346,37 @@
       <c r="AK155" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="AL155" s="5" t="s">
+      <c r="AL155" s="11"/>
+      <c r="AM155" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM155" s="11" t="s">
+      <c r="AN155" s="11" t="s">
         <v>1201</v>
       </c>
-      <c r="AN155" s="11" t="s">
+      <c r="AO155" s="11" t="s">
         <v>1202</v>
       </c>
-      <c r="AO155" s="11" t="s">
+      <c r="AP155" s="11" t="s">
         <v>1204</v>
       </c>
-      <c r="AP155" s="36" t="s">
+      <c r="AQ155" s="36" t="s">
         <v>1248</v>
       </c>
-      <c r="AQ155" s="11" t="s">
+      <c r="AR155" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR155" s="11" t="s">
+      <c r="AS155" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="AS155" s="13" t="s">
+      <c r="AT155" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT155" s="14"/>
-      <c r="AU155" s="44">
+      <c r="AU155" s="14"/>
+      <c r="AV155" s="44">
         <v>46004</v>
       </c>
     </row>
-    <row r="156" spans="1:47" ht="38.25" hidden="1">
+    <row r="156" spans="1:48" ht="38.25" hidden="1">
       <c r="A156" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29326,36 +29501,37 @@
       <c r="AK156" s="11" t="s">
         <v>1205</v>
       </c>
-      <c r="AL156" s="5" t="s">
+      <c r="AL156" s="11"/>
+      <c r="AM156" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM156" s="11" t="s">
+      <c r="AN156" s="11" t="s">
         <v>1208</v>
       </c>
-      <c r="AN156" s="11" t="s">
+      <c r="AO156" s="11" t="s">
         <v>1209</v>
       </c>
-      <c r="AO156" s="11" t="s">
+      <c r="AP156" s="11" t="s">
         <v>1213</v>
       </c>
-      <c r="AP156" s="36" t="s">
+      <c r="AQ156" s="36" t="s">
         <v>1249</v>
       </c>
-      <c r="AQ156" s="11" t="s">
+      <c r="AR156" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR156" s="11" t="s">
+      <c r="AS156" s="11" t="s">
         <v>1210</v>
       </c>
-      <c r="AS156" s="13" t="s">
+      <c r="AT156" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT156" s="14"/>
-      <c r="AU156" s="44">
+      <c r="AU156" s="14"/>
+      <c r="AV156" s="44">
         <v>46005</v>
       </c>
     </row>
-    <row r="157" spans="1:47" ht="38.25" hidden="1">
+    <row r="157" spans="1:48" ht="38.25" hidden="1">
       <c r="A157" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29480,36 +29656,37 @@
       <c r="AK157" s="11" t="s">
         <v>1205</v>
       </c>
-      <c r="AL157" s="5" t="s">
+      <c r="AL157" s="11"/>
+      <c r="AM157" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM157" s="11" t="s">
+      <c r="AN157" s="11" t="s">
         <v>1216</v>
       </c>
-      <c r="AN157" s="11" t="s">
+      <c r="AO157" s="11" t="s">
         <v>1217</v>
       </c>
-      <c r="AO157" s="11" t="s">
+      <c r="AP157" s="11" t="s">
         <v>1215</v>
       </c>
-      <c r="AP157" s="36" t="s">
+      <c r="AQ157" s="36" t="s">
         <v>1250</v>
       </c>
-      <c r="AQ157" s="11" t="s">
+      <c r="AR157" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR157" s="11" t="s">
+      <c r="AS157" s="11" t="s">
         <v>1214</v>
       </c>
-      <c r="AS157" s="13" t="s">
+      <c r="AT157" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT157" s="14"/>
-      <c r="AU157" s="44">
+      <c r="AU157" s="14"/>
+      <c r="AV157" s="44">
         <v>46006</v>
       </c>
     </row>
-    <row r="158" spans="1:47" ht="38.25">
+    <row r="158" spans="1:48" ht="38.25">
       <c r="A158" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29633,36 +29810,39 @@
       <c r="AK158" s="11" t="s">
         <v>1221</v>
       </c>
-      <c r="AL158" s="5" t="s">
+      <c r="AL158" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM158" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM158" s="11" t="s">
+      <c r="AN158" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AN158" s="11" t="s">
+      <c r="AO158" s="11" t="s">
         <v>1135</v>
       </c>
-      <c r="AO158" s="11">
+      <c r="AP158" s="11">
         <v>37</v>
       </c>
-      <c r="AP158" s="36" t="s">
+      <c r="AQ158" s="36" t="s">
         <v>1251</v>
       </c>
-      <c r="AQ158" s="11" t="s">
+      <c r="AR158" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR158" s="11" t="s">
+      <c r="AS158" s="11" t="s">
         <v>1219</v>
       </c>
-      <c r="AS158" s="13" t="s">
+      <c r="AT158" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT158" s="14"/>
-      <c r="AU158" s="44">
+      <c r="AU158" s="14"/>
+      <c r="AV158" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="159" spans="1:47" ht="25.5">
+    <row r="159" spans="1:48" ht="25.5">
       <c r="A159" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -29785,36 +29965,39 @@
       <c r="AK159" s="11" t="s">
         <v>1147</v>
       </c>
-      <c r="AL159" s="5" t="s">
+      <c r="AL159" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM159" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM159" s="11" t="s">
+      <c r="AN159" s="11" t="s">
         <v>1148</v>
       </c>
-      <c r="AN159" s="11" t="s">
+      <c r="AO159" s="11" t="s">
         <v>1149</v>
       </c>
-      <c r="AO159" s="11">
+      <c r="AP159" s="11">
         <v>38</v>
       </c>
-      <c r="AP159" s="36" t="s">
+      <c r="AQ159" s="36" t="s">
         <v>1252</v>
       </c>
-      <c r="AQ159" s="11" t="s">
+      <c r="AR159" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR159" s="11" t="s">
+      <c r="AS159" s="11" t="s">
         <v>1222</v>
       </c>
-      <c r="AS159" s="13" t="s">
+      <c r="AT159" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT159" s="14"/>
-      <c r="AU159" s="44">
+      <c r="AU159" s="14"/>
+      <c r="AV159" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="160" spans="1:47" ht="38.25">
+    <row r="160" spans="1:48" ht="38.25">
       <c r="A160" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -29929,34 +30112,37 @@
       <c r="AK160" s="11" t="s">
         <v>1153</v>
       </c>
-      <c r="AL160" s="5" t="s">
+      <c r="AL160" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM160" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM160" s="11" t="s">
+      <c r="AN160" s="11" t="s">
         <v>1151</v>
       </c>
-      <c r="AN160" s="11" t="s">
+      <c r="AO160" s="11" t="s">
         <v>1152</v>
       </c>
-      <c r="AO160" s="11">
+      <c r="AP160" s="11">
         <v>39</v>
       </c>
-      <c r="AP160" s="36" t="s">
+      <c r="AQ160" s="36" t="s">
         <v>1183</v>
       </c>
-      <c r="AQ160" s="11" t="s">
+      <c r="AR160" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR160" s="11"/>
-      <c r="AS160" s="13" t="s">
+      <c r="AS160" s="11"/>
+      <c r="AT160" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT160" s="14"/>
-      <c r="AU160" s="44">
+      <c r="AU160" s="14"/>
+      <c r="AV160" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="161" spans="1:47" ht="38.25">
+    <row r="161" spans="1:48" ht="38.25">
       <c r="A161" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -30079,36 +30265,39 @@
       <c r="AK161" s="11" t="s">
         <v>1225</v>
       </c>
-      <c r="AL161" s="5" t="s">
+      <c r="AL161" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM161" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM161" s="11" t="s">
+      <c r="AN161" s="11" t="s">
         <v>1154</v>
       </c>
-      <c r="AN161" s="11" t="s">
+      <c r="AO161" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="AO161" s="11">
+      <c r="AP161" s="11">
         <v>40</v>
       </c>
-      <c r="AP161" s="36" t="s">
+      <c r="AQ161" s="36" t="s">
         <v>1253</v>
       </c>
-      <c r="AQ161" s="11" t="s">
+      <c r="AR161" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR161" s="11" t="s">
+      <c r="AS161" s="11" t="s">
         <v>1223</v>
       </c>
-      <c r="AS161" s="13" t="s">
+      <c r="AT161" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT161" s="14"/>
-      <c r="AU161" s="44">
+      <c r="AU161" s="14"/>
+      <c r="AV161" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="162" spans="1:47" ht="38.25">
+    <row r="162" spans="1:48" ht="38.25">
       <c r="A162" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30231,36 +30420,39 @@
       <c r="AK162" s="11" t="s">
         <v>1296</v>
       </c>
-      <c r="AL162" s="5" t="s">
+      <c r="AL162" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM162" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM162" s="11" t="s">
+      <c r="AN162" s="11" t="s">
         <v>1282</v>
       </c>
-      <c r="AN162" s="11" t="s">
+      <c r="AO162" s="11" t="s">
         <v>1283</v>
       </c>
-      <c r="AO162" s="11" t="s">
+      <c r="AP162" s="11" t="s">
         <v>1270</v>
       </c>
-      <c r="AP162" s="36" t="s">
+      <c r="AQ162" s="36" t="s">
         <v>1298</v>
       </c>
-      <c r="AQ162" s="11" t="s">
+      <c r="AR162" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR162" s="11" t="s">
+      <c r="AS162" s="11" t="s">
         <v>1276</v>
       </c>
-      <c r="AS162" s="13" t="s">
+      <c r="AT162" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT162" s="14"/>
-      <c r="AU162" s="44">
+      <c r="AU162" s="14"/>
+      <c r="AV162" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="163" spans="1:47" ht="25.5">
+    <row r="163" spans="1:48" ht="25.5">
       <c r="A163" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30383,34 +30575,37 @@
       <c r="AK163" s="11" t="s">
         <v>1297</v>
       </c>
-      <c r="AL163" s="5" t="s">
+      <c r="AL163" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM163" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM163" s="11" t="s">
+      <c r="AN163" s="11" t="s">
         <v>1284</v>
       </c>
-      <c r="AN163" s="11" t="s">
+      <c r="AO163" s="11" t="s">
         <v>1285</v>
       </c>
-      <c r="AO163" s="11" t="s">
+      <c r="AP163" s="11" t="s">
         <v>1271</v>
       </c>
-      <c r="AP163" s="36" t="s">
+      <c r="AQ163" s="36" t="s">
         <v>1299</v>
       </c>
-      <c r="AQ163" s="11" t="s">
+      <c r="AR163" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR163" s="11" t="s">
+      <c r="AS163" s="11" t="s">
         <v>1277</v>
       </c>
-      <c r="AS163" s="13" t="s">
+      <c r="AT163" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT163" s="14"/>
-      <c r="AU163" s="44"/>
+      <c r="AU163" s="14"/>
+      <c r="AV163" s="44"/>
     </row>
-    <row r="164" spans="1:47" ht="25.5">
+    <row r="164" spans="1:48" ht="25.5">
       <c r="A164" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30533,34 +30728,37 @@
       <c r="AK164" s="11" t="s">
         <v>1297</v>
       </c>
-      <c r="AL164" s="5" t="s">
+      <c r="AL164" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM164" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM164" s="11" t="s">
+      <c r="AN164" s="11" t="s">
         <v>1284</v>
       </c>
-      <c r="AN164" s="11" t="s">
+      <c r="AO164" s="11" t="s">
         <v>1286</v>
       </c>
-      <c r="AO164" s="11" t="s">
+      <c r="AP164" s="11" t="s">
         <v>1272</v>
       </c>
-      <c r="AP164" s="36" t="s">
+      <c r="AQ164" s="36" t="s">
         <v>1300</v>
       </c>
-      <c r="AQ164" s="11" t="s">
+      <c r="AR164" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR164" s="11" t="s">
+      <c r="AS164" s="11" t="s">
         <v>1278</v>
       </c>
-      <c r="AS164" s="13" t="s">
+      <c r="AT164" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT164" s="14"/>
-      <c r="AU164" s="44"/>
+      <c r="AU164" s="14"/>
+      <c r="AV164" s="44"/>
     </row>
-    <row r="165" spans="1:47" ht="25.5">
+    <row r="165" spans="1:48" ht="25.5">
       <c r="A165" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30683,34 +30881,37 @@
       <c r="AK165" s="11" t="s">
         <v>1297</v>
       </c>
-      <c r="AL165" s="5" t="s">
+      <c r="AL165" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM165" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM165" s="11" t="s">
+      <c r="AN165" s="11" t="s">
         <v>1287</v>
       </c>
-      <c r="AN165" s="11" t="s">
+      <c r="AO165" s="11" t="s">
         <v>1288</v>
       </c>
-      <c r="AO165" s="11" t="s">
+      <c r="AP165" s="11" t="s">
         <v>1273</v>
       </c>
-      <c r="AP165" s="36" t="s">
+      <c r="AQ165" s="36" t="s">
         <v>1301</v>
       </c>
-      <c r="AQ165" s="11" t="s">
+      <c r="AR165" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR165" s="11" t="s">
+      <c r="AS165" s="11" t="s">
         <v>1279</v>
       </c>
-      <c r="AS165" s="13" t="s">
+      <c r="AT165" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT165" s="14"/>
-      <c r="AU165" s="44"/>
+      <c r="AU165" s="14"/>
+      <c r="AV165" s="44"/>
     </row>
-    <row r="166" spans="1:47" ht="25.5">
+    <row r="166" spans="1:48" ht="25.5">
       <c r="A166" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30833,34 +31034,37 @@
       <c r="AK166" s="11" t="s">
         <v>1297</v>
       </c>
-      <c r="AL166" s="5" t="s">
+      <c r="AL166" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM166" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM166" s="11" t="s">
+      <c r="AN166" s="11" t="s">
         <v>1289</v>
       </c>
-      <c r="AN166" s="11" t="s">
+      <c r="AO166" s="11" t="s">
         <v>1290</v>
       </c>
-      <c r="AO166" s="11" t="s">
+      <c r="AP166" s="11" t="s">
         <v>1274</v>
       </c>
-      <c r="AP166" s="36" t="s">
+      <c r="AQ166" s="36" t="s">
         <v>1302</v>
       </c>
-      <c r="AQ166" s="11" t="s">
+      <c r="AR166" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR166" s="11" t="s">
+      <c r="AS166" s="11" t="s">
         <v>1280</v>
       </c>
-      <c r="AS166" s="13" t="s">
+      <c r="AT166" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT166" s="14"/>
-      <c r="AU166" s="44"/>
+      <c r="AU166" s="14"/>
+      <c r="AV166" s="44"/>
     </row>
-    <row r="167" spans="1:47" ht="25.5" hidden="1">
+    <row r="167" spans="1:48" ht="25.5" hidden="1">
       <c r="A167" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30983,34 +31187,35 @@
       <c r="AK167" s="11" t="s">
         <v>1297</v>
       </c>
-      <c r="AL167" s="5" t="s">
+      <c r="AL167" s="11"/>
+      <c r="AM167" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM167" s="11" t="s">
+      <c r="AN167" s="11" t="s">
         <v>1291</v>
       </c>
-      <c r="AN167" s="11" t="s">
+      <c r="AO167" s="11" t="s">
         <v>1292</v>
       </c>
-      <c r="AO167" s="11" t="s">
+      <c r="AP167" s="11" t="s">
         <v>1275</v>
       </c>
-      <c r="AP167" s="36" t="s">
+      <c r="AQ167" s="36" t="s">
         <v>1303</v>
       </c>
-      <c r="AQ167" s="11" t="s">
+      <c r="AR167" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR167" s="11" t="s">
+      <c r="AS167" s="11" t="s">
         <v>1281</v>
       </c>
-      <c r="AS167" s="13" t="s">
+      <c r="AT167" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT167" s="14"/>
-      <c r="AU167" s="44"/>
+      <c r="AU167" s="14"/>
+      <c r="AV167" s="44"/>
     </row>
-    <row r="168" spans="1:47" ht="38.25">
+    <row r="168" spans="1:48" ht="38.25">
       <c r="A168" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -31133,36 +31338,39 @@
       <c r="AK168" s="11" t="s">
         <v>1227</v>
       </c>
-      <c r="AL168" s="5" t="s">
+      <c r="AL168" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM168" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM168" s="11" t="s">
+      <c r="AN168" s="11" t="s">
         <v>1142</v>
       </c>
-      <c r="AN168" s="11" t="s">
+      <c r="AO168" s="11" t="s">
         <v>1143</v>
       </c>
-      <c r="AO168" s="11">
+      <c r="AP168" s="11">
         <v>42</v>
       </c>
-      <c r="AP168" s="36" t="s">
+      <c r="AQ168" s="36" t="s">
         <v>1254</v>
       </c>
-      <c r="AQ168" s="11" t="s">
+      <c r="AR168" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR168" s="11" t="s">
+      <c r="AS168" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="AS168" s="13" t="s">
+      <c r="AT168" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT168" s="14"/>
-      <c r="AU168" s="44">
+      <c r="AU168" s="14"/>
+      <c r="AV168" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="169" spans="1:47" ht="25.5">
+    <row r="169" spans="1:48" ht="25.5">
       <c r="A169" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -31285,36 +31493,39 @@
       <c r="AK169" s="11" t="s">
         <v>1184</v>
       </c>
-      <c r="AL169" s="5" t="s">
+      <c r="AL169" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM169" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM169" s="11" t="s">
+      <c r="AN169" s="11" t="s">
         <v>1159</v>
       </c>
-      <c r="AN169" s="11" t="s">
+      <c r="AO169" s="11" t="s">
         <v>1160</v>
       </c>
-      <c r="AO169" s="11">
+      <c r="AP169" s="11">
         <v>43</v>
       </c>
-      <c r="AP169" s="36" t="s">
+      <c r="AQ169" s="36" t="s">
         <v>1255</v>
       </c>
-      <c r="AQ169" s="11" t="s">
+      <c r="AR169" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR169" s="11" t="s">
+      <c r="AS169" s="11" t="s">
         <v>1228</v>
       </c>
-      <c r="AS169" s="13" t="s">
+      <c r="AT169" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT169" s="14"/>
-      <c r="AU169" s="44">
+      <c r="AU169" s="14"/>
+      <c r="AV169" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="170" spans="1:47" ht="25.5">
+    <row r="170" spans="1:48" ht="25.5">
       <c r="A170" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -31437,36 +31648,39 @@
       <c r="AK170" s="11" t="s">
         <v>1232</v>
       </c>
-      <c r="AL170" s="5" t="s">
+      <c r="AL170" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM170" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM170" s="11" t="s">
+      <c r="AN170" s="11" t="s">
         <v>1161</v>
       </c>
-      <c r="AN170" s="11" t="s">
+      <c r="AO170" s="11" t="s">
         <v>1162</v>
       </c>
-      <c r="AO170" s="11">
+      <c r="AP170" s="11">
         <v>44</v>
       </c>
-      <c r="AP170" s="36" t="s">
+      <c r="AQ170" s="36" t="s">
         <v>1256</v>
       </c>
-      <c r="AQ170" s="11" t="s">
+      <c r="AR170" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR170" s="11" t="s">
+      <c r="AS170" s="11" t="s">
         <v>1230</v>
       </c>
-      <c r="AS170" s="13" t="s">
+      <c r="AT170" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT170" s="14"/>
-      <c r="AU170" s="44">
+      <c r="AU170" s="14"/>
+      <c r="AV170" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="171" spans="1:47" ht="38.25">
+    <row r="171" spans="1:48" ht="38.25">
       <c r="A171" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -31588,36 +31802,39 @@
       <c r="AK171" s="11" t="s">
         <v>1294</v>
       </c>
-      <c r="AL171" s="5" t="s">
+      <c r="AL171" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM171" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM171" s="11" t="s">
+      <c r="AN171" s="11" t="s">
         <v>1164</v>
       </c>
-      <c r="AN171" s="11" t="s">
+      <c r="AO171" s="11" t="s">
         <v>1165</v>
       </c>
-      <c r="AO171" s="11" t="s">
+      <c r="AP171" s="11" t="s">
         <v>1137</v>
       </c>
-      <c r="AP171" s="36" t="s">
+      <c r="AQ171" s="36" t="s">
         <v>1257</v>
       </c>
-      <c r="AQ171" s="11" t="s">
+      <c r="AR171" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR171" s="11" t="s">
+      <c r="AS171" s="11" t="s">
         <v>1268</v>
       </c>
-      <c r="AS171" s="13" t="s">
+      <c r="AT171" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT171" s="14"/>
-      <c r="AU171" s="44">
+      <c r="AU171" s="14"/>
+      <c r="AV171" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="172" spans="1:47" ht="25.5">
+    <row r="172" spans="1:48" ht="25.5">
       <c r="A172" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -31741,36 +31958,39 @@
       <c r="AK172" s="11" t="s">
         <v>1236</v>
       </c>
-      <c r="AL172" s="5" t="s">
+      <c r="AL172" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM172" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM172" s="11" t="s">
+      <c r="AN172" s="11" t="s">
         <v>1168</v>
       </c>
-      <c r="AN172" s="11" t="s">
+      <c r="AO172" s="11" t="s">
         <v>1169</v>
       </c>
-      <c r="AO172" s="11" t="s">
+      <c r="AP172" s="11" t="s">
         <v>1136</v>
       </c>
-      <c r="AP172" s="36" t="s">
+      <c r="AQ172" s="36" t="s">
         <v>1258</v>
       </c>
-      <c r="AQ172" s="11" t="s">
+      <c r="AR172" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR172" s="11" t="s">
+      <c r="AS172" s="11" t="s">
         <v>1235</v>
       </c>
-      <c r="AS172" s="13" t="s">
+      <c r="AT172" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT172" s="14"/>
-      <c r="AU172" s="44">
+      <c r="AU172" s="14"/>
+      <c r="AV172" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="173" spans="1:47" ht="51">
+    <row r="173" spans="1:48" ht="51">
       <c r="A173" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -31894,36 +32114,39 @@
       <c r="AK173" s="11" t="s">
         <v>1239</v>
       </c>
-      <c r="AL173" s="5" t="s">
+      <c r="AL173" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM173" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM173" s="11" t="s">
+      <c r="AN173" s="11" t="s">
         <v>1170</v>
       </c>
-      <c r="AN173" s="11" t="s">
+      <c r="AO173" s="11" t="s">
         <v>1171</v>
       </c>
-      <c r="AO173" s="11">
+      <c r="AP173" s="11">
         <v>46</v>
       </c>
-      <c r="AP173" s="45" t="s">
+      <c r="AQ173" s="45" t="s">
         <v>1259</v>
       </c>
-      <c r="AQ173" s="11" t="s">
+      <c r="AR173" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR173" s="11" t="s">
+      <c r="AS173" s="11" t="s">
         <v>1237</v>
       </c>
-      <c r="AS173" s="13" t="s">
+      <c r="AT173" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT173" s="14"/>
-      <c r="AU173" s="44">
+      <c r="AU173" s="14"/>
+      <c r="AV173" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="174" spans="1:47" ht="38.25">
+    <row r="174" spans="1:48" ht="38.25">
       <c r="A174" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32047,36 +32270,39 @@
       <c r="AK174" s="11" t="s">
         <v>1245</v>
       </c>
-      <c r="AL174" s="5" t="s">
+      <c r="AL174" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM174" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM174" s="11" t="s">
+      <c r="AN174" s="11" t="s">
         <v>1174</v>
       </c>
-      <c r="AN174" s="11" t="s">
+      <c r="AO174" s="11" t="s">
         <v>1175</v>
       </c>
-      <c r="AO174" s="11" t="s">
+      <c r="AP174" s="11" t="s">
         <v>1138</v>
       </c>
-      <c r="AP174" s="45" t="s">
+      <c r="AQ174" s="45" t="s">
         <v>1260</v>
       </c>
-      <c r="AQ174" s="11" t="s">
+      <c r="AR174" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR174" s="11" t="s">
+      <c r="AS174" s="11" t="s">
         <v>1269</v>
       </c>
-      <c r="AS174" s="13" t="s">
+      <c r="AT174" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT174" s="14"/>
-      <c r="AU174" s="44">
+      <c r="AU174" s="14"/>
+      <c r="AV174" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="175" spans="1:47" ht="38.25">
+    <row r="175" spans="1:48" ht="38.25">
       <c r="A175" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32200,36 +32426,39 @@
       <c r="AK175" s="11" t="s">
         <v>1245</v>
       </c>
-      <c r="AL175" s="5" t="s">
+      <c r="AL175" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM175" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM175" s="11" t="s">
+      <c r="AN175" s="11" t="s">
         <v>1241</v>
       </c>
-      <c r="AN175" s="11" t="s">
+      <c r="AO175" s="11" t="s">
         <v>1242</v>
       </c>
-      <c r="AO175" s="11" t="s">
+      <c r="AP175" s="11" t="s">
         <v>1139</v>
       </c>
-      <c r="AP175" s="36" t="s">
+      <c r="AQ175" s="36" t="s">
         <v>1261</v>
       </c>
-      <c r="AQ175" s="11" t="s">
+      <c r="AR175" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR175" s="11" t="s">
+      <c r="AS175" s="11" t="s">
         <v>1240</v>
       </c>
-      <c r="AS175" s="13" t="s">
+      <c r="AT175" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT175" s="14"/>
-      <c r="AU175" s="44">
+      <c r="AU175" s="14"/>
+      <c r="AV175" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="176" spans="1:47" ht="38.25">
+    <row r="176" spans="1:48" ht="38.25">
       <c r="A176" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32353,36 +32582,39 @@
       <c r="AK176" s="11" t="s">
         <v>1245</v>
       </c>
-      <c r="AL176" s="5" t="s">
+      <c r="AL176" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM176" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM176" s="11" t="s">
+      <c r="AN176" s="11" t="s">
         <v>1176</v>
       </c>
-      <c r="AN176" s="11" t="s">
+      <c r="AO176" s="11" t="s">
         <v>1177</v>
       </c>
-      <c r="AO176" s="11" t="s">
+      <c r="AP176" s="11" t="s">
         <v>1140</v>
       </c>
-      <c r="AP176" s="36" t="s">
+      <c r="AQ176" s="36" t="s">
         <v>1262</v>
       </c>
-      <c r="AQ176" s="11" t="s">
+      <c r="AR176" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR176" s="11" t="s">
+      <c r="AS176" s="11" t="s">
         <v>1243</v>
       </c>
-      <c r="AS176" s="13" t="s">
+      <c r="AT176" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT176" s="14"/>
-      <c r="AU176" s="44">
+      <c r="AU176" s="14"/>
+      <c r="AV176" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="177" spans="1:47" ht="25.5">
+    <row r="177" spans="1:48" ht="25.5">
       <c r="A177" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32506,36 +32738,39 @@
       <c r="AK177" s="11" t="s">
         <v>1246</v>
       </c>
-      <c r="AL177" s="5" t="s">
+      <c r="AL177" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AM177" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM177" s="11" t="s">
+      <c r="AN177" s="11" t="s">
         <v>1180</v>
       </c>
-      <c r="AN177" s="11" t="s">
+      <c r="AO177" s="11" t="s">
         <v>1181</v>
       </c>
-      <c r="AO177" s="11">
+      <c r="AP177" s="11">
         <v>48</v>
       </c>
-      <c r="AP177" s="36" t="s">
+      <c r="AQ177" s="36" t="s">
         <v>1263</v>
       </c>
-      <c r="AQ177" s="11" t="s">
+      <c r="AR177" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR177" s="11" t="s">
+      <c r="AS177" s="11" t="s">
         <v>1244</v>
       </c>
-      <c r="AS177" s="13" t="s">
+      <c r="AT177" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="AT177" s="14"/>
-      <c r="AU177" s="44">
+      <c r="AU177" s="14"/>
+      <c r="AV177" s="44">
         <v>46003</v>
       </c>
     </row>
-    <row r="178" spans="1:47" ht="38.25">
+    <row r="178" spans="1:48" ht="38.25">
       <c r="A178" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -32659,34 +32894,35 @@
       <c r="AK178" s="11" t="s">
         <v>1191</v>
       </c>
-      <c r="AL178" s="5" t="s">
+      <c r="AL178" s="11"/>
+      <c r="AM178" s="5" t="s">
         <v>1196</v>
       </c>
-      <c r="AM178" s="11" t="s">
+      <c r="AN178" s="11" t="s">
         <v>1193</v>
       </c>
-      <c r="AN178" s="11" t="s">
+      <c r="AO178" s="11" t="s">
         <v>1194</v>
       </c>
-      <c r="AO178" s="11">
+      <c r="AP178" s="11">
         <v>49</v>
       </c>
-      <c r="AP178" s="36" t="s">
+      <c r="AQ178" s="36" t="s">
         <v>1264</v>
       </c>
-      <c r="AQ178" s="11" t="s">
+      <c r="AR178" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR178" s="11"/>
-      <c r="AS178" s="13" t="s">
+      <c r="AS178" s="11"/>
+      <c r="AT178" s="13" t="s">
         <v>1195</v>
       </c>
-      <c r="AT178" s="14"/>
-      <c r="AU178" s="44">
+      <c r="AU178" s="14"/>
+      <c r="AV178" s="44">
         <v>46010</v>
       </c>
     </row>
-    <row r="179" spans="1:47" ht="25.5">
+    <row r="179" spans="1:48" ht="25.5">
       <c r="A179" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32805,36 +33041,37 @@
       <c r="AK179" s="11" t="s">
         <v>1311</v>
       </c>
-      <c r="AL179" s="5" t="s">
+      <c r="AL179" s="11"/>
+      <c r="AM179" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM179" s="11" t="s">
+      <c r="AN179" s="11" t="s">
         <v>1313</v>
       </c>
-      <c r="AN179" s="11" t="s">
+      <c r="AO179" s="11" t="s">
         <v>1314</v>
       </c>
-      <c r="AO179" s="11">
+      <c r="AP179" s="11">
         <v>50</v>
       </c>
-      <c r="AP179" s="36" t="s">
+      <c r="AQ179" s="36" t="s">
         <v>1414</v>
       </c>
-      <c r="AQ179" s="11" t="s">
+      <c r="AR179" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR179" s="11" t="s">
+      <c r="AS179" s="11" t="s">
         <v>1315</v>
       </c>
-      <c r="AS179" s="13" t="s">
+      <c r="AT179" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT179" s="14"/>
-      <c r="AU179" s="44">
+      <c r="AU179" s="14"/>
+      <c r="AV179" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="180" spans="1:47" ht="25.5">
+    <row r="180" spans="1:48" ht="25.5">
       <c r="A180" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32953,36 +33190,37 @@
       <c r="AK180" s="11" t="s">
         <v>1377</v>
       </c>
-      <c r="AL180" s="5" t="s">
+      <c r="AL180" s="11"/>
+      <c r="AM180" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM180" s="11" t="s">
+      <c r="AN180" s="11" t="s">
         <v>1321</v>
       </c>
-      <c r="AN180" s="11" t="s">
+      <c r="AO180" s="11" t="s">
         <v>1322</v>
       </c>
-      <c r="AO180" s="11">
+      <c r="AP180" s="11">
         <v>51</v>
       </c>
-      <c r="AP180" s="36" t="s">
+      <c r="AQ180" s="36" t="s">
         <v>1415</v>
       </c>
-      <c r="AQ180" s="11" t="s">
+      <c r="AR180" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR180" s="11" t="s">
+      <c r="AS180" s="11" t="s">
         <v>1320</v>
       </c>
-      <c r="AS180" s="13" t="s">
+      <c r="AT180" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT180" s="14"/>
-      <c r="AU180" s="44">
+      <c r="AU180" s="14"/>
+      <c r="AV180" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="181" spans="1:47" ht="25.5">
+    <row r="181" spans="1:48" ht="25.5">
       <c r="A181" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33099,36 +33337,37 @@
       <c r="AK181" s="11" t="s">
         <v>1378</v>
       </c>
-      <c r="AL181" s="5" t="s">
+      <c r="AL181" s="11"/>
+      <c r="AM181" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM181" s="11" t="s">
+      <c r="AN181" s="11" t="s">
         <v>1328</v>
       </c>
-      <c r="AN181" s="11" t="s">
+      <c r="AO181" s="11" t="s">
         <v>1329</v>
       </c>
-      <c r="AO181" s="11">
+      <c r="AP181" s="11">
         <v>52</v>
       </c>
-      <c r="AP181" s="36" t="s">
+      <c r="AQ181" s="36" t="s">
         <v>1416</v>
       </c>
-      <c r="AQ181" s="11" t="s">
+      <c r="AR181" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR181" s="11" t="s">
+      <c r="AS181" s="11" t="s">
         <v>1327</v>
       </c>
-      <c r="AS181" s="13" t="s">
+      <c r="AT181" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT181" s="14"/>
-      <c r="AU181" s="44">
+      <c r="AU181" s="14"/>
+      <c r="AV181" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="182" spans="1:47" ht="25.5">
+    <row r="182" spans="1:48" ht="25.5">
       <c r="A182" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33243,36 +33482,37 @@
         <v>1336</v>
       </c>
       <c r="AK182" s="11"/>
-      <c r="AL182" s="5" t="s">
+      <c r="AL182" s="11"/>
+      <c r="AM182" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM182" s="11" t="s">
+      <c r="AN182" s="11" t="s">
         <v>1335</v>
       </c>
-      <c r="AN182" s="11" t="s">
+      <c r="AO182" s="11" t="s">
         <v>1334</v>
       </c>
-      <c r="AO182" s="11">
+      <c r="AP182" s="11">
         <v>53</v>
       </c>
-      <c r="AP182" s="36" t="s">
+      <c r="AQ182" s="36" t="s">
         <v>1417</v>
       </c>
-      <c r="AQ182" s="11" t="s">
+      <c r="AR182" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR182" s="11" t="s">
+      <c r="AS182" s="11" t="s">
         <v>1333</v>
       </c>
-      <c r="AS182" s="13" t="s">
+      <c r="AT182" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT182" s="14"/>
-      <c r="AU182" s="44">
+      <c r="AU182" s="14"/>
+      <c r="AV182" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="183" spans="1:47" ht="25.5">
+    <row r="183" spans="1:48" ht="25.5">
       <c r="A183" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33389,36 +33629,37 @@
       <c r="AK183" s="11" t="s">
         <v>1340</v>
       </c>
-      <c r="AL183" s="5" t="s">
+      <c r="AL183" s="11"/>
+      <c r="AM183" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM183" s="11" t="s">
+      <c r="AN183" s="11" t="s">
         <v>1362</v>
       </c>
-      <c r="AN183" s="11" t="s">
+      <c r="AO183" s="11" t="s">
         <v>1363</v>
       </c>
-      <c r="AO183" s="11">
+      <c r="AP183" s="11">
         <v>54</v>
       </c>
-      <c r="AP183" s="36" t="s">
+      <c r="AQ183" s="36" t="s">
         <v>1418</v>
       </c>
-      <c r="AQ183" s="11" t="s">
+      <c r="AR183" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR183" s="11" t="s">
+      <c r="AS183" s="11" t="s">
         <v>1339</v>
       </c>
-      <c r="AS183" s="13" t="s">
+      <c r="AT183" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT183" s="14"/>
-      <c r="AU183" s="44">
+      <c r="AU183" s="14"/>
+      <c r="AV183" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="184" spans="1:47" ht="25.5">
+    <row r="184" spans="1:48" ht="25.5">
       <c r="A184" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33537,36 +33778,37 @@
       <c r="AK184" s="11" t="s">
         <v>1381</v>
       </c>
-      <c r="AL184" s="5" t="s">
+      <c r="AL184" s="11"/>
+      <c r="AM184" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM184" s="11" t="s">
+      <c r="AN184" s="11" t="s">
         <v>1361</v>
       </c>
-      <c r="AN184" s="11" t="s">
+      <c r="AO184" s="11" t="s">
         <v>1360</v>
       </c>
-      <c r="AO184" s="11">
+      <c r="AP184" s="11">
         <v>55</v>
       </c>
-      <c r="AP184" s="36" t="s">
+      <c r="AQ184" s="36" t="s">
         <v>1419</v>
       </c>
-      <c r="AQ184" s="11" t="s">
+      <c r="AR184" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR184" s="11" t="s">
+      <c r="AS184" s="11" t="s">
         <v>1344</v>
       </c>
-      <c r="AS184" s="13" t="s">
+      <c r="AT184" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT184" s="14"/>
-      <c r="AU184" s="44">
+      <c r="AU184" s="14"/>
+      <c r="AV184" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="185" spans="1:47" ht="25.5">
+    <row r="185" spans="1:48" ht="25.5">
       <c r="A185" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -33685,36 +33927,37 @@
       <c r="AK185" s="11" t="s">
         <v>1379</v>
       </c>
-      <c r="AL185" s="5" t="s">
+      <c r="AL185" s="11"/>
+      <c r="AM185" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM185" s="11" t="s">
+      <c r="AN185" s="11" t="s">
         <v>1351</v>
       </c>
-      <c r="AN185" s="11" t="s">
+      <c r="AO185" s="11" t="s">
         <v>1352</v>
       </c>
-      <c r="AO185" s="11">
+      <c r="AP185" s="11">
         <v>56</v>
       </c>
-      <c r="AP185" s="36" t="s">
+      <c r="AQ185" s="36" t="s">
         <v>1420</v>
       </c>
-      <c r="AQ185" s="11" t="s">
+      <c r="AR185" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR185" s="11" t="s">
+      <c r="AS185" s="11" t="s">
         <v>1350</v>
       </c>
-      <c r="AS185" s="13" t="s">
+      <c r="AT185" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT185" s="14"/>
-      <c r="AU185" s="44">
+      <c r="AU185" s="14"/>
+      <c r="AV185" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="186" spans="1:47" ht="25.5">
+    <row r="186" spans="1:48" ht="25.5">
       <c r="A186" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -33833,36 +34076,37 @@
       <c r="AK186" s="11" t="s">
         <v>1380</v>
       </c>
-      <c r="AL186" s="5" t="s">
+      <c r="AL186" s="11"/>
+      <c r="AM186" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM186" s="11" t="s">
+      <c r="AN186" s="11" t="s">
         <v>1359</v>
       </c>
-      <c r="AN186" s="11" t="s">
+      <c r="AO186" s="11" t="s">
         <v>1358</v>
       </c>
-      <c r="AO186" s="11">
+      <c r="AP186" s="11">
         <v>57</v>
       </c>
-      <c r="AP186" s="36" t="s">
+      <c r="AQ186" s="36" t="s">
         <v>1421</v>
       </c>
-      <c r="AQ186" s="11" t="s">
+      <c r="AR186" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR186" s="11" t="s">
+      <c r="AS186" s="11" t="s">
         <v>1357</v>
       </c>
-      <c r="AS186" s="13" t="s">
+      <c r="AT186" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT186" s="14"/>
-      <c r="AU186" s="44">
+      <c r="AU186" s="14"/>
+      <c r="AV186" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="187" spans="1:47" ht="25.5">
+    <row r="187" spans="1:48" ht="25.5">
       <c r="A187" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -33981,36 +34225,37 @@
       <c r="AK187" s="11" t="s">
         <v>1379</v>
       </c>
-      <c r="AL187" s="5" t="s">
+      <c r="AL187" s="11"/>
+      <c r="AM187" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM187" s="11" t="s">
+      <c r="AN187" s="11" t="s">
         <v>1369</v>
       </c>
-      <c r="AN187" s="11" t="s">
+      <c r="AO187" s="11" t="s">
         <v>1370</v>
       </c>
-      <c r="AO187" s="11">
+      <c r="AP187" s="11">
         <v>58</v>
       </c>
-      <c r="AP187" s="36" t="s">
+      <c r="AQ187" s="36" t="s">
         <v>1422</v>
       </c>
-      <c r="AQ187" s="11" t="s">
+      <c r="AR187" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR187" s="11" t="s">
+      <c r="AS187" s="11" t="s">
         <v>1368</v>
       </c>
-      <c r="AS187" s="13" t="s">
+      <c r="AT187" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT187" s="14"/>
-      <c r="AU187" s="44">
+      <c r="AU187" s="14"/>
+      <c r="AV187" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="188" spans="1:47" ht="25.5">
+    <row r="188" spans="1:48" ht="25.5">
       <c r="A188" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -34129,36 +34374,37 @@
       <c r="AK188" s="11" t="s">
         <v>1387</v>
       </c>
-      <c r="AL188" s="5" t="s">
+      <c r="AL188" s="11"/>
+      <c r="AM188" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM188" s="11" t="s">
+      <c r="AN188" s="11" t="s">
         <v>1375</v>
       </c>
-      <c r="AN188" s="11" t="s">
+      <c r="AO188" s="11" t="s">
         <v>1376</v>
       </c>
-      <c r="AO188" s="11">
+      <c r="AP188" s="11">
         <v>59</v>
       </c>
-      <c r="AP188" s="36" t="s">
+      <c r="AQ188" s="36" t="s">
         <v>1423</v>
       </c>
-      <c r="AQ188" s="11" t="s">
+      <c r="AR188" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR188" s="11" t="s">
+      <c r="AS188" s="11" t="s">
         <v>1374</v>
       </c>
-      <c r="AS188" s="13" t="s">
+      <c r="AT188" s="13" t="s">
         <v>1316</v>
       </c>
-      <c r="AT188" s="14"/>
-      <c r="AU188" s="44">
+      <c r="AU188" s="14"/>
+      <c r="AV188" s="44">
         <v>46042</v>
       </c>
     </row>
-    <row r="189" spans="1:47" ht="38.25">
+    <row r="189" spans="1:48" ht="38.25">
       <c r="A189" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Auvergne-Rhône-Alpes</v>
@@ -34277,32 +34523,33 @@
       <c r="AK189" s="11" t="s">
         <v>1395</v>
       </c>
-      <c r="AL189" s="5" t="s">
+      <c r="AL189" s="11"/>
+      <c r="AM189" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="AM189" s="11" t="s">
+      <c r="AN189" s="11" t="s">
         <v>1393</v>
       </c>
-      <c r="AN189" s="11" t="s">
+      <c r="AO189" s="11" t="s">
         <v>1394</v>
       </c>
-      <c r="AO189" s="11">
+      <c r="AP189" s="11">
         <v>60</v>
       </c>
-      <c r="AP189" s="36" t="s">
+      <c r="AQ189" s="36" t="s">
         <v>1398</v>
       </c>
-      <c r="AQ189" s="11" t="s">
+      <c r="AR189" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR189" s="11" t="s">
+      <c r="AS189" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="AS189" s="13" t="s">
+      <c r="AT189" s="13" t="s">
         <v>1397</v>
       </c>
-      <c r="AT189" s="14"/>
-      <c r="AU189" s="44">
+      <c r="AU189" s="14"/>
+      <c r="AV189" s="44">
         <v>46042</v>
       </c>
     </row>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AECFD9C-2904-4A52-A162-E5A6A3243C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F86D9B1-F7A2-4682-9C4D-CCD785B84027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -4609,7 +4609,7 @@
   </cellStyles>
   <dxfs count="50">
     <dxf>
-      <numFmt numFmtId="166" formatCode="General&quot; m²&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0\ [$€-40C];[Red]\-#,##0\ [$€-40C]"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -4855,7 +4855,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0\ [$€-40C];[Red]\-#,##0\ [$€-40C]"/>
+      <numFmt numFmtId="166" formatCode="General&quot; m²&quot;"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -5032,8 +5032,8 @@
     <tableColumn id="4" xr3:uid="{87D84239-5323-4A47-9424-F0CADB050723}" name="Cession / Droit au bail" dataDxfId="37" dataCellStyle="Normal 2"/>
     <tableColumn id="31" xr3:uid="{86770348-6586-45F2-A401-94B68504976F}" name="Numéro de lot" dataDxfId="36" dataCellStyle="Normal 2"/>
     <tableColumn id="1" xr3:uid="{3888DEAC-D743-4A06-B622-0805DADF7B24}" name="Surface GLA" dataDxfId="35" dataCellStyle="Normal 2"/>
-    <tableColumn id="50" xr3:uid="{647D7D49-7B6F-4747-BFFF-85889E08899D}" name="Surface maximale" dataDxfId="0" dataCellStyle="Normal 2"/>
-    <tableColumn id="9" xr3:uid="{0D61162C-F920-419C-993E-EDC2DF105B61}" name="Répartition surface GLA" dataDxfId="34" dataCellStyle="Normal 2"/>
+    <tableColumn id="9" xr3:uid="{0D61162C-F920-419C-993E-EDC2DF105B61}" name="Répartition surface GLA" dataDxfId="0" dataCellStyle="Normal 2"/>
+    <tableColumn id="50" xr3:uid="{647D7D49-7B6F-4747-BFFF-85889E08899D}" name="Surface maximale" dataDxfId="34" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{9969DD5B-5EA2-4595-B887-2E9B21053A55}" name="Surface utile" dataDxfId="33" dataCellStyle="Normal 2"/>
     <tableColumn id="21" xr3:uid="{3DFB9473-7064-409A-A47B-5544538EC4AE}" name="Répartition surface utile" dataDxfId="32" dataCellStyle="Normal 2"/>
     <tableColumn id="5" xr3:uid="{A744513A-B9BE-426C-9A67-F73FDBDA82D8}" name="Loyer annuel" dataDxfId="31" dataCellStyle="Normal 2"/>
@@ -5400,7 +5400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BG205"/>
+  <dimension ref="A1:BH205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -5416,49 +5416,49 @@
     <col min="12" max="12" width="17.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="15.625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.75" style="1" customWidth="1"/>
-    <col min="25" max="25" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.75" customWidth="1"/>
-    <col min="28" max="28" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.25" style="1" customWidth="1"/>
-    <col min="30" max="30" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.25" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="53.875" style="1" customWidth="1"/>
-    <col min="41" max="41" width="41.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.5" style="1" customWidth="1"/>
-    <col min="46" max="46" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="13.375" style="1" customWidth="1"/>
-    <col min="50" max="50" width="25.75" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="28" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="40.625" style="1" customWidth="1"/>
-    <col min="54" max="54" width="27.75" style="1" customWidth="1"/>
-    <col min="55" max="56" width="44.25" style="1" customWidth="1"/>
-    <col min="57" max="57" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="93.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="16384" width="11.625" style="1"/>
+    <col min="16" max="16" width="10.875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.75" style="1" customWidth="1"/>
+    <col min="26" max="26" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.75" customWidth="1"/>
+    <col min="29" max="29" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.25" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.25" style="1" customWidth="1"/>
+    <col min="33" max="33" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="64.5" style="1" customWidth="1"/>
+    <col min="40" max="41" width="53.875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="41.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.5" style="1" customWidth="1"/>
+    <col min="47" max="47" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.375" style="1" customWidth="1"/>
+    <col min="51" max="51" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="28" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="40.625" style="1" customWidth="1"/>
+    <col min="55" max="55" width="27.75" style="1" customWidth="1"/>
+    <col min="56" max="57" width="44.25" style="1" customWidth="1"/>
+    <col min="58" max="58" width="33" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="93.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="11.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="12.75">
+    <row r="1" spans="1:60" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>255</v>
       </c>
@@ -5505,10 +5505,10 @@
         <v>19</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>1429</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>260</v>
@@ -5611,9 +5611,10 @@
       </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
-      <c r="BG1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BH1" s="1"/>
     </row>
-    <row r="2" spans="1:59" ht="25.5">
+    <row r="2" spans="1:60" ht="25.5">
       <c r="A2" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Nouvelle-Aquitaine</v>
@@ -5662,10 +5663,10 @@
       <c r="O2" s="33">
         <v>451</v>
       </c>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>262</v>
       </c>
+      <c r="Q2" s="33"/>
       <c r="R2" s="34">
         <v>423</v>
       </c>
@@ -5768,9 +5769,10 @@
       <c r="AX2" s="44"/>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
-      <c r="BG2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BH2" s="1"/>
     </row>
-    <row r="3" spans="1:59" ht="25.5">
+    <row r="3" spans="1:60" ht="25.5">
       <c r="A3" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -5819,10 +5821,10 @@
       <c r="O3" s="33">
         <v>325</v>
       </c>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>263</v>
       </c>
+      <c r="Q3" s="33"/>
       <c r="R3" s="34" t="s">
         <v>103</v>
       </c>
@@ -5925,9 +5927,10 @@
       <c r="AX3" s="44"/>
       <c r="AY3" s="1"/>
       <c r="AZ3" s="1"/>
-      <c r="BG3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BH3" s="1"/>
     </row>
-    <row r="4" spans="1:59" ht="25.5">
+    <row r="4" spans="1:60" ht="25.5">
       <c r="A4" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -5976,10 +5979,10 @@
       <c r="O4" s="33">
         <v>264</v>
       </c>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>264</v>
       </c>
+      <c r="Q4" s="33"/>
       <c r="R4" s="34">
         <v>244</v>
       </c>
@@ -6082,9 +6085,10 @@
       <c r="AX4" s="44"/>
       <c r="AY4" s="1"/>
       <c r="AZ4" s="1"/>
-      <c r="BG4" s="1"/>
+      <c r="BA4" s="1"/>
+      <c r="BH4" s="1"/>
     </row>
-    <row r="5" spans="1:59" ht="25.5">
+    <row r="5" spans="1:60" ht="25.5">
       <c r="A5" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -6133,10 +6137,10 @@
       <c r="O5" s="33">
         <v>9030</v>
       </c>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>1304</v>
       </c>
+      <c r="Q5" s="33"/>
       <c r="R5" s="34">
         <v>8628</v>
       </c>
@@ -6239,9 +6243,10 @@
       <c r="AX5" s="44"/>
       <c r="AY5" s="1"/>
       <c r="AZ5" s="1"/>
-      <c r="BG5" s="1"/>
+      <c r="BA5" s="1"/>
+      <c r="BH5" s="1"/>
     </row>
-    <row r="6" spans="1:59" ht="25.5">
+    <row r="6" spans="1:60" ht="25.5">
       <c r="A6" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6290,10 +6295,10 @@
       <c r="O6" s="34">
         <v>179</v>
       </c>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q6" s="34"/>
       <c r="R6" s="34" t="s">
         <v>103</v>
       </c>
@@ -6396,9 +6401,10 @@
       <c r="AX6" s="44"/>
       <c r="AY6" s="1"/>
       <c r="AZ6" s="1"/>
-      <c r="BG6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BH6" s="1"/>
     </row>
-    <row r="7" spans="1:59" ht="25.5">
+    <row r="7" spans="1:60" ht="25.5">
       <c r="A7" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6447,10 +6453,10 @@
       <c r="O7" s="34">
         <v>159</v>
       </c>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P7" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q7" s="34"/>
       <c r="R7" s="34" t="s">
         <v>103</v>
       </c>
@@ -6553,9 +6559,10 @@
       <c r="AX7" s="44"/>
       <c r="AY7" s="1"/>
       <c r="AZ7" s="1"/>
-      <c r="BG7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BH7" s="1"/>
     </row>
-    <row r="8" spans="1:59" ht="25.5">
+    <row r="8" spans="1:60" ht="25.5">
       <c r="A8" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6604,10 +6611,10 @@
       <c r="O8" s="34">
         <v>125</v>
       </c>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q8" s="34"/>
       <c r="R8" s="34" t="s">
         <v>103</v>
       </c>
@@ -6710,9 +6717,10 @@
       <c r="AX8" s="44"/>
       <c r="AY8" s="1"/>
       <c r="AZ8" s="1"/>
-      <c r="BG8" s="1"/>
+      <c r="BA8" s="1"/>
+      <c r="BH8" s="1"/>
     </row>
-    <row r="9" spans="1:59" ht="25.5">
+    <row r="9" spans="1:60" ht="25.5">
       <c r="A9" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6761,11 +6769,11 @@
       <c r="O9" s="34">
         <v>156</v>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q9" s="34">
         <v>758</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R9" s="34" t="s">
         <v>103</v>
@@ -6869,9 +6877,10 @@
       <c r="AX9" s="44"/>
       <c r="AY9" s="1"/>
       <c r="AZ9" s="1"/>
-      <c r="BG9" s="1"/>
+      <c r="BA9" s="1"/>
+      <c r="BH9" s="1"/>
     </row>
-    <row r="10" spans="1:59" ht="25.5">
+    <row r="10" spans="1:60" ht="25.5">
       <c r="A10" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -6920,11 +6929,11 @@
       <c r="O10" s="34">
         <v>178</v>
       </c>
-      <c r="P10" s="34">
+      <c r="P10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10" s="34">
         <v>758</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R10" s="34" t="s">
         <v>103</v>
@@ -7028,9 +7037,10 @@
       <c r="AX10" s="44"/>
       <c r="AY10" s="1"/>
       <c r="AZ10" s="1"/>
-      <c r="BG10" s="1"/>
+      <c r="BA10" s="1"/>
+      <c r="BH10" s="1"/>
     </row>
-    <row r="11" spans="1:59" ht="25.5">
+    <row r="11" spans="1:60" ht="25.5">
       <c r="A11" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7079,11 +7089,11 @@
       <c r="O11" s="34">
         <v>253</v>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q11" s="34">
         <v>758</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R11" s="34" t="s">
         <v>103</v>
@@ -7187,9 +7197,10 @@
       <c r="AX11" s="44"/>
       <c r="AY11" s="1"/>
       <c r="AZ11" s="1"/>
-      <c r="BG11" s="1"/>
+      <c r="BA11" s="1"/>
+      <c r="BH11" s="1"/>
     </row>
-    <row r="12" spans="1:59" ht="25.5">
+    <row r="12" spans="1:60" ht="25.5">
       <c r="A12" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7238,11 +7249,11 @@
       <c r="O12" s="34">
         <v>171</v>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q12" s="34">
         <v>758</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R12" s="34" t="s">
         <v>103</v>
@@ -7346,9 +7357,10 @@
       <c r="AX12" s="44"/>
       <c r="AY12" s="1"/>
       <c r="AZ12" s="1"/>
-      <c r="BG12" s="1"/>
+      <c r="BA12" s="1"/>
+      <c r="BH12" s="1"/>
     </row>
-    <row r="13" spans="1:59" ht="25.5">
+    <row r="13" spans="1:60" ht="25.5">
       <c r="A13" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7397,11 +7409,11 @@
       <c r="O13" s="34">
         <v>200</v>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13" s="34">
         <v>305</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R13" s="34" t="s">
         <v>103</v>
@@ -7505,9 +7517,10 @@
       <c r="AX13" s="44"/>
       <c r="AY13" s="1"/>
       <c r="AZ13" s="1"/>
-      <c r="BG13" s="1"/>
+      <c r="BA13" s="1"/>
+      <c r="BH13" s="1"/>
     </row>
-    <row r="14" spans="1:59" ht="25.5">
+    <row r="14" spans="1:60" ht="25.5">
       <c r="A14" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7556,11 +7569,11 @@
       <c r="O14" s="34">
         <v>105</v>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q14" s="34">
         <v>305</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R14" s="34" t="s">
         <v>103</v>
@@ -7664,9 +7677,10 @@
       <c r="AX14" s="44"/>
       <c r="AY14" s="1"/>
       <c r="AZ14" s="1"/>
-      <c r="BG14" s="1"/>
+      <c r="BA14" s="1"/>
+      <c r="BH14" s="1"/>
     </row>
-    <row r="15" spans="1:59" ht="25.5">
+    <row r="15" spans="1:60" ht="25.5">
       <c r="A15" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7715,11 +7729,11 @@
       <c r="O15" s="34">
         <v>51</v>
       </c>
-      <c r="P15" s="34">
+      <c r="P15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q15" s="34">
         <v>166</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R15" s="34" t="s">
         <v>103</v>
@@ -7823,9 +7837,10 @@
       <c r="AX15" s="44"/>
       <c r="AY15" s="1"/>
       <c r="AZ15" s="1"/>
-      <c r="BG15" s="1"/>
+      <c r="BA15" s="1"/>
+      <c r="BH15" s="1"/>
     </row>
-    <row r="16" spans="1:59" ht="25.5">
+    <row r="16" spans="1:60" ht="25.5">
       <c r="A16" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -7874,11 +7889,11 @@
       <c r="O16" s="34">
         <v>115</v>
       </c>
-      <c r="P16" s="34">
+      <c r="P16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q16" s="34">
         <v>166</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="R16" s="34" t="s">
         <v>103</v>
@@ -7982,9 +7997,10 @@
       <c r="AX16" s="44"/>
       <c r="AY16" s="1"/>
       <c r="AZ16" s="1"/>
-      <c r="BG16" s="1"/>
+      <c r="BA16" s="1"/>
+      <c r="BH16" s="1"/>
     </row>
-    <row r="17" spans="1:59" ht="25.5">
+    <row r="17" spans="1:60" ht="25.5">
       <c r="A17" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -8033,10 +8049,10 @@
       <c r="O17" s="34">
         <v>210</v>
       </c>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q17" s="34"/>
       <c r="R17" s="34" t="s">
         <v>103</v>
       </c>
@@ -8139,9 +8155,10 @@
       <c r="AX17" s="44"/>
       <c r="AY17" s="1"/>
       <c r="AZ17" s="1"/>
-      <c r="BG17" s="1"/>
+      <c r="BA17" s="1"/>
+      <c r="BH17" s="1"/>
     </row>
-    <row r="18" spans="1:59" ht="25.5">
+    <row r="18" spans="1:60" ht="25.5">
       <c r="A18" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Normandie</v>
@@ -8190,10 +8207,10 @@
       <c r="O18" s="34">
         <v>30</v>
       </c>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" s="34"/>
       <c r="R18" s="34" t="s">
         <v>103</v>
       </c>
@@ -8296,9 +8313,10 @@
       <c r="AX18" s="44"/>
       <c r="AY18" s="1"/>
       <c r="AZ18" s="1"/>
-      <c r="BG18" s="1"/>
+      <c r="BA18" s="1"/>
+      <c r="BH18" s="1"/>
     </row>
-    <row r="19" spans="1:59" ht="25.5">
+    <row r="19" spans="1:60" ht="25.5">
       <c r="A19" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8347,10 +8365,10 @@
       <c r="O19" s="34">
         <v>1200</v>
       </c>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P19" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q19" s="34"/>
       <c r="R19" s="34" t="s">
         <v>103</v>
       </c>
@@ -8453,9 +8471,10 @@
       <c r="AX19" s="44"/>
       <c r="AY19" s="1"/>
       <c r="AZ19" s="1"/>
-      <c r="BG19" s="1"/>
+      <c r="BA19" s="1"/>
+      <c r="BH19" s="1"/>
     </row>
-    <row r="20" spans="1:59" ht="25.5">
+    <row r="20" spans="1:60" ht="25.5">
       <c r="A20" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8504,10 +8523,10 @@
       <c r="O20" s="34">
         <v>1200</v>
       </c>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P20" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q20" s="34"/>
       <c r="R20" s="34" t="s">
         <v>103</v>
       </c>
@@ -8610,9 +8629,10 @@
       <c r="AX20" s="44"/>
       <c r="AY20" s="1"/>
       <c r="AZ20" s="1"/>
-      <c r="BG20" s="1"/>
+      <c r="BA20" s="1"/>
+      <c r="BH20" s="1"/>
     </row>
-    <row r="21" spans="1:59" ht="25.5">
+    <row r="21" spans="1:60" ht="25.5">
       <c r="A21" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8661,10 +8681,10 @@
       <c r="O21" s="34">
         <v>549</v>
       </c>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q21" s="34"/>
       <c r="R21" s="34" t="s">
         <v>103</v>
       </c>
@@ -8767,9 +8787,10 @@
       <c r="AX21" s="44"/>
       <c r="AY21" s="1"/>
       <c r="AZ21" s="1"/>
-      <c r="BG21" s="1"/>
+      <c r="BA21" s="1"/>
+      <c r="BH21" s="1"/>
     </row>
-    <row r="22" spans="1:59" ht="25.5">
+    <row r="22" spans="1:60" ht="25.5">
       <c r="A22" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8818,10 +8839,10 @@
       <c r="O22" s="34">
         <v>502</v>
       </c>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q22" s="34"/>
       <c r="R22" s="34" t="s">
         <v>103</v>
       </c>
@@ -8924,9 +8945,10 @@
       <c r="AX22" s="44"/>
       <c r="AY22" s="1"/>
       <c r="AZ22" s="1"/>
-      <c r="BG22" s="1"/>
+      <c r="BA22" s="1"/>
+      <c r="BH22" s="1"/>
     </row>
-    <row r="23" spans="1:59" ht="25.5">
+    <row r="23" spans="1:60" ht="25.5">
       <c r="A23" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -8975,10 +8997,10 @@
       <c r="O23" s="34">
         <v>250</v>
       </c>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P23" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q23" s="34"/>
       <c r="R23" s="34" t="s">
         <v>103</v>
       </c>
@@ -9081,9 +9103,10 @@
       <c r="AX23" s="44"/>
       <c r="AY23" s="1"/>
       <c r="AZ23" s="1"/>
-      <c r="BG23" s="1"/>
+      <c r="BA23" s="1"/>
+      <c r="BH23" s="1"/>
     </row>
-    <row r="24" spans="1:59" ht="25.5">
+    <row r="24" spans="1:60" ht="25.5">
       <c r="A24" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9132,10 +9155,10 @@
       <c r="O24" s="34">
         <v>264</v>
       </c>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P24" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q24" s="34"/>
       <c r="R24" s="34" t="s">
         <v>103</v>
       </c>
@@ -9238,9 +9261,10 @@
       <c r="AX24" s="44"/>
       <c r="AY24" s="1"/>
       <c r="AZ24" s="1"/>
-      <c r="BG24" s="1"/>
+      <c r="BA24" s="1"/>
+      <c r="BH24" s="1"/>
     </row>
-    <row r="25" spans="1:59" ht="25.5">
+    <row r="25" spans="1:60" ht="25.5">
       <c r="A25" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9289,10 +9313,10 @@
       <c r="O25" s="34">
         <v>486</v>
       </c>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q25" s="34"/>
       <c r="R25" s="34" t="s">
         <v>103</v>
       </c>
@@ -9395,9 +9419,10 @@
       <c r="AX25" s="44"/>
       <c r="AY25" s="1"/>
       <c r="AZ25" s="1"/>
-      <c r="BG25" s="1"/>
+      <c r="BA25" s="1"/>
+      <c r="BH25" s="1"/>
     </row>
-    <row r="26" spans="1:59" ht="25.5">
+    <row r="26" spans="1:60" ht="25.5">
       <c r="A26" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9446,10 +9471,10 @@
       <c r="O26" s="34">
         <v>267</v>
       </c>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q26" s="34"/>
       <c r="R26" s="34" t="s">
         <v>103</v>
       </c>
@@ -9552,9 +9577,10 @@
       <c r="AX26" s="44"/>
       <c r="AY26" s="1"/>
       <c r="AZ26" s="1"/>
-      <c r="BG26" s="1"/>
+      <c r="BA26" s="1"/>
+      <c r="BH26" s="1"/>
     </row>
-    <row r="27" spans="1:59" ht="25.5">
+    <row r="27" spans="1:60" ht="25.5">
       <c r="A27" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9603,10 +9629,10 @@
       <c r="O27" s="34">
         <v>321</v>
       </c>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P27" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q27" s="34"/>
       <c r="R27" s="34" t="s">
         <v>103</v>
       </c>
@@ -9709,9 +9735,10 @@
       <c r="AX27" s="44"/>
       <c r="AY27" s="1"/>
       <c r="AZ27" s="1"/>
-      <c r="BG27" s="1"/>
+      <c r="BA27" s="1"/>
+      <c r="BH27" s="1"/>
     </row>
-    <row r="28" spans="1:59" ht="25.5">
+    <row r="28" spans="1:60" ht="25.5">
       <c r="A28" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9760,10 +9787,10 @@
       <c r="O28" s="34">
         <v>472</v>
       </c>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P28" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q28" s="34"/>
       <c r="R28" s="34" t="s">
         <v>103</v>
       </c>
@@ -9866,9 +9893,10 @@
       <c r="AX28" s="44"/>
       <c r="AY28" s="1"/>
       <c r="AZ28" s="1"/>
-      <c r="BG28" s="1"/>
+      <c r="BA28" s="1"/>
+      <c r="BH28" s="1"/>
     </row>
-    <row r="29" spans="1:59" ht="25.5">
+    <row r="29" spans="1:60" ht="25.5">
       <c r="A29" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -9917,10 +9945,10 @@
       <c r="O29" s="34">
         <v>1195</v>
       </c>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P29" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q29" s="34"/>
       <c r="R29" s="34" t="s">
         <v>103</v>
       </c>
@@ -10023,9 +10051,10 @@
       <c r="AX29" s="44"/>
       <c r="AY29" s="1"/>
       <c r="AZ29" s="1"/>
-      <c r="BG29" s="1"/>
+      <c r="BA29" s="1"/>
+      <c r="BH29" s="1"/>
     </row>
-    <row r="30" spans="1:59" ht="25.5">
+    <row r="30" spans="1:60" ht="25.5">
       <c r="A30" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bretagne</v>
@@ -10074,10 +10103,10 @@
       <c r="O30" s="34">
         <v>170</v>
       </c>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P30" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q30" s="34"/>
       <c r="R30" s="34" t="s">
         <v>103</v>
       </c>
@@ -10180,9 +10209,10 @@
       <c r="AX30" s="44"/>
       <c r="AY30" s="1"/>
       <c r="AZ30" s="1"/>
-      <c r="BG30" s="1"/>
+      <c r="BA30" s="1"/>
+      <c r="BH30" s="1"/>
     </row>
-    <row r="31" spans="1:59" ht="25.5">
+    <row r="31" spans="1:60" ht="25.5">
       <c r="A31" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10231,10 +10261,10 @@
       <c r="O31" s="34">
         <v>61</v>
       </c>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P31" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q31" s="34"/>
       <c r="R31" s="34" t="s">
         <v>103</v>
       </c>
@@ -10337,9 +10367,10 @@
       <c r="AX31" s="44"/>
       <c r="AY31" s="1"/>
       <c r="AZ31" s="1"/>
-      <c r="BG31" s="1"/>
+      <c r="BA31" s="1"/>
+      <c r="BH31" s="1"/>
     </row>
-    <row r="32" spans="1:59" ht="25.5">
+    <row r="32" spans="1:60" ht="25.5">
       <c r="A32" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10388,10 +10419,10 @@
       <c r="O32" s="34">
         <v>10</v>
       </c>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q32" s="34"/>
       <c r="R32" s="34" t="s">
         <v>103</v>
       </c>
@@ -10492,9 +10523,10 @@
       <c r="AX32" s="44"/>
       <c r="AY32" s="1"/>
       <c r="AZ32" s="1"/>
-      <c r="BG32" s="1"/>
+      <c r="BA32" s="1"/>
+      <c r="BH32" s="1"/>
     </row>
-    <row r="33" spans="1:59" ht="25.5">
+    <row r="33" spans="1:60" ht="25.5">
       <c r="A33" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10543,10 +10575,10 @@
       <c r="O33" s="34">
         <v>227</v>
       </c>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P33" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q33" s="34"/>
       <c r="R33" s="34" t="s">
         <v>103</v>
       </c>
@@ -10649,9 +10681,10 @@
       <c r="AX33" s="44"/>
       <c r="AY33" s="1"/>
       <c r="AZ33" s="1"/>
-      <c r="BG33" s="1"/>
+      <c r="BA33" s="1"/>
+      <c r="BH33" s="1"/>
     </row>
-    <row r="34" spans="1:59" ht="25.5">
+    <row r="34" spans="1:60" ht="25.5">
       <c r="A34" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10700,10 +10733,10 @@
       <c r="O34" s="34">
         <v>102</v>
       </c>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q34" s="34"/>
       <c r="R34" s="34" t="s">
         <v>103</v>
       </c>
@@ -10806,9 +10839,10 @@
       <c r="AX34" s="44"/>
       <c r="AY34" s="1"/>
       <c r="AZ34" s="1"/>
-      <c r="BG34" s="1"/>
+      <c r="BA34" s="1"/>
+      <c r="BH34" s="1"/>
     </row>
-    <row r="35" spans="1:59" ht="25.5">
+    <row r="35" spans="1:60" ht="25.5">
       <c r="A35" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -10857,10 +10891,10 @@
       <c r="O35" s="34">
         <v>62</v>
       </c>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P35" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q35" s="34"/>
       <c r="R35" s="34" t="s">
         <v>103</v>
       </c>
@@ -10963,9 +10997,10 @@
       <c r="AX35" s="44"/>
       <c r="AY35" s="1"/>
       <c r="AZ35" s="1"/>
-      <c r="BG35" s="1"/>
+      <c r="BA35" s="1"/>
+      <c r="BH35" s="1"/>
     </row>
-    <row r="36" spans="1:59" ht="25.5">
+    <row r="36" spans="1:60" ht="25.5">
       <c r="A36" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -11014,10 +11049,10 @@
       <c r="O36" s="34">
         <v>22</v>
       </c>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P36" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q36" s="34"/>
       <c r="R36" s="34" t="s">
         <v>103</v>
       </c>
@@ -11120,9 +11155,10 @@
       <c r="AX36" s="44"/>
       <c r="AY36" s="1"/>
       <c r="AZ36" s="1"/>
-      <c r="BG36" s="1"/>
+      <c r="BA36" s="1"/>
+      <c r="BH36" s="1"/>
     </row>
-    <row r="37" spans="1:59" ht="25.5">
+    <row r="37" spans="1:60" ht="25.5">
       <c r="A37" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -11171,10 +11207,10 @@
       <c r="O37" s="34">
         <v>9</v>
       </c>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P37" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q37" s="34"/>
       <c r="R37" s="34" t="s">
         <v>103</v>
       </c>
@@ -11277,9 +11313,10 @@
       <c r="AX37" s="44"/>
       <c r="AY37" s="1"/>
       <c r="AZ37" s="1"/>
-      <c r="BG37" s="1"/>
+      <c r="BA37" s="1"/>
+      <c r="BH37" s="1"/>
     </row>
-    <row r="38" spans="1:59" ht="25.5">
+    <row r="38" spans="1:60" ht="25.5">
       <c r="A38" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -11328,10 +11365,10 @@
       <c r="O38" s="34">
         <v>71</v>
       </c>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P38" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q38" s="34"/>
       <c r="R38" s="34" t="s">
         <v>103</v>
       </c>
@@ -11434,9 +11471,10 @@
       <c r="AX38" s="44"/>
       <c r="AY38" s="1"/>
       <c r="AZ38" s="1"/>
-      <c r="BG38" s="1"/>
+      <c r="BA38" s="1"/>
+      <c r="BH38" s="1"/>
     </row>
-    <row r="39" spans="1:59" ht="25.5">
+    <row r="39" spans="1:60" ht="25.5">
       <c r="A39" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -11485,10 +11523,10 @@
       <c r="O39" s="34">
         <v>45</v>
       </c>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P39" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q39" s="34"/>
       <c r="R39" s="34" t="s">
         <v>103</v>
       </c>
@@ -11591,9 +11629,10 @@
       <c r="AX39" s="44"/>
       <c r="AY39" s="1"/>
       <c r="AZ39" s="1"/>
-      <c r="BG39" s="1"/>
+      <c r="BA39" s="1"/>
+      <c r="BH39" s="1"/>
     </row>
-    <row r="40" spans="1:59" ht="25.5">
+    <row r="40" spans="1:60" ht="25.5">
       <c r="A40" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Auvergne-Rhône-Alpes</v>
@@ -11642,10 +11681,10 @@
       <c r="O40" s="34">
         <v>238</v>
       </c>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P40" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q40" s="34"/>
       <c r="R40" s="34">
         <v>200</v>
       </c>
@@ -11748,9 +11787,10 @@
       <c r="AX40" s="44"/>
       <c r="AY40" s="1"/>
       <c r="AZ40" s="1"/>
-      <c r="BG40" s="1"/>
+      <c r="BA40" s="1"/>
+      <c r="BH40" s="1"/>
     </row>
-    <row r="41" spans="1:59" ht="25.5">
+    <row r="41" spans="1:60" ht="25.5">
       <c r="A41" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -11799,10 +11839,10 @@
       <c r="O41" s="33">
         <v>168</v>
       </c>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="6" t="s">
+      <c r="P41" s="6" t="s">
         <v>317</v>
       </c>
+      <c r="Q41" s="33"/>
       <c r="R41" s="34">
         <v>156</v>
       </c>
@@ -11905,9 +11945,10 @@
       <c r="AX41" s="44"/>
       <c r="AY41" s="1"/>
       <c r="AZ41" s="1"/>
-      <c r="BG41" s="1"/>
+      <c r="BA41" s="1"/>
+      <c r="BH41" s="1"/>
     </row>
-    <row r="42" spans="1:59" ht="25.5">
+    <row r="42" spans="1:60" ht="25.5">
       <c r="A42" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -11956,8 +11997,8 @@
       <c r="O42" s="34">
         <v>87</v>
       </c>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="12"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="34"/>
       <c r="R42" s="34">
         <v>82</v>
       </c>
@@ -12058,9 +12099,10 @@
       <c r="AX42" s="44"/>
       <c r="AY42" s="1"/>
       <c r="AZ42" s="1"/>
-      <c r="BG42" s="1"/>
+      <c r="BA42" s="1"/>
+      <c r="BH42" s="1"/>
     </row>
-    <row r="43" spans="1:59" ht="25.5">
+    <row r="43" spans="1:60" ht="25.5">
       <c r="A43" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12109,8 +12151,8 @@
       <c r="O43" s="34">
         <v>197</v>
       </c>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="12"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="34"/>
       <c r="R43" s="34">
         <v>182</v>
       </c>
@@ -12211,9 +12253,10 @@
       <c r="AX43" s="44"/>
       <c r="AY43" s="1"/>
       <c r="AZ43" s="1"/>
-      <c r="BG43" s="1"/>
+      <c r="BA43" s="1"/>
+      <c r="BH43" s="1"/>
     </row>
-    <row r="44" spans="1:59" ht="25.5">
+    <row r="44" spans="1:60" ht="25.5">
       <c r="A44" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12262,8 +12305,8 @@
       <c r="O44" s="34">
         <v>576</v>
       </c>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="12"/>
+      <c r="P44" s="12"/>
+      <c r="Q44" s="34"/>
       <c r="R44" s="34">
         <v>543</v>
       </c>
@@ -12364,9 +12407,10 @@
       <c r="AX44" s="44"/>
       <c r="AY44" s="1"/>
       <c r="AZ44" s="1"/>
-      <c r="BG44" s="1"/>
+      <c r="BA44" s="1"/>
+      <c r="BH44" s="1"/>
     </row>
-    <row r="45" spans="1:59" ht="25.5">
+    <row r="45" spans="1:60" ht="25.5">
       <c r="A45" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12415,10 +12459,10 @@
       <c r="O45" s="34">
         <v>237</v>
       </c>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="12" t="s">
+      <c r="P45" s="12" t="s">
         <v>323</v>
       </c>
+      <c r="Q45" s="34"/>
       <c r="R45" s="34">
         <v>221</v>
       </c>
@@ -12521,9 +12565,10 @@
       <c r="AX45" s="44"/>
       <c r="AY45" s="1"/>
       <c r="AZ45" s="1"/>
-      <c r="BG45" s="1"/>
+      <c r="BA45" s="1"/>
+      <c r="BH45" s="1"/>
     </row>
-    <row r="46" spans="1:59" ht="25.5">
+    <row r="46" spans="1:60" ht="25.5">
       <c r="A46" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -12572,10 +12617,10 @@
       <c r="O46" s="34">
         <v>236</v>
       </c>
-      <c r="P46" s="34"/>
-      <c r="Q46" s="12" t="s">
+      <c r="P46" s="12" t="s">
         <v>325</v>
       </c>
+      <c r="Q46" s="34"/>
       <c r="R46" s="34">
         <v>218</v>
       </c>
@@ -12678,9 +12723,10 @@
       <c r="AX46" s="44"/>
       <c r="AY46" s="1"/>
       <c r="AZ46" s="1"/>
-      <c r="BG46" s="1"/>
+      <c r="BA46" s="1"/>
+      <c r="BH46" s="1"/>
     </row>
-    <row r="47" spans="1:59" ht="25.5">
+    <row r="47" spans="1:60" ht="25.5">
       <c r="A47" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -12729,10 +12775,10 @@
       <c r="O47" s="33">
         <v>370</v>
       </c>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="4" t="s">
+      <c r="P47" s="4" t="s">
         <v>265</v>
       </c>
+      <c r="Q47" s="33"/>
       <c r="R47" s="34" t="s">
         <v>103</v>
       </c>
@@ -12835,9 +12881,10 @@
       <c r="AX47" s="44"/>
       <c r="AY47" s="1"/>
       <c r="AZ47" s="1"/>
-      <c r="BG47" s="1"/>
+      <c r="BA47" s="1"/>
+      <c r="BH47" s="1"/>
     </row>
-    <row r="48" spans="1:59" ht="25.5">
+    <row r="48" spans="1:60" ht="25.5">
       <c r="A48" s="4" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -12886,10 +12933,10 @@
       <c r="O48" s="33">
         <v>486</v>
       </c>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="10" t="s">
+      <c r="P48" s="10" t="s">
         <v>266</v>
       </c>
+      <c r="Q48" s="33"/>
       <c r="R48" s="34" t="s">
         <v>103</v>
       </c>
@@ -12992,9 +13039,10 @@
       <c r="AX48" s="44"/>
       <c r="AY48" s="1"/>
       <c r="AZ48" s="1"/>
-      <c r="BG48" s="1"/>
+      <c r="BA48" s="1"/>
+      <c r="BH48" s="1"/>
     </row>
-    <row r="49" spans="1:59" ht="25.5">
+    <row r="49" spans="1:60" ht="25.5">
       <c r="A49" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13043,10 +13091,10 @@
       <c r="O49" s="33">
         <v>681</v>
       </c>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="10" t="s">
+      <c r="P49" s="10" t="s">
         <v>267</v>
       </c>
+      <c r="Q49" s="33"/>
       <c r="R49" s="34" t="s">
         <v>103</v>
       </c>
@@ -13149,9 +13197,10 @@
       <c r="AX49" s="44"/>
       <c r="AY49" s="1"/>
       <c r="AZ49" s="1"/>
-      <c r="BG49" s="1"/>
+      <c r="BA49" s="1"/>
+      <c r="BH49" s="1"/>
     </row>
-    <row r="50" spans="1:59" ht="25.5">
+    <row r="50" spans="1:60" ht="25.5">
       <c r="A50" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13200,10 +13249,10 @@
       <c r="O50" s="34">
         <v>672</v>
       </c>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="6" t="s">
+      <c r="P50" s="6" t="s">
         <v>66</v>
       </c>
+      <c r="Q50" s="34"/>
       <c r="R50" s="34" t="s">
         <v>103</v>
       </c>
@@ -13303,9 +13352,10 @@
       <c r="AX50" s="44"/>
       <c r="AY50" s="1"/>
       <c r="AZ50" s="1"/>
-      <c r="BG50" s="1"/>
+      <c r="BA50" s="1"/>
+      <c r="BH50" s="1"/>
     </row>
-    <row r="51" spans="1:59" ht="25.5">
+    <row r="51" spans="1:60" ht="25.5">
       <c r="A51" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13354,10 +13404,10 @@
       <c r="O51" s="33">
         <v>115</v>
       </c>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="10" t="s">
+      <c r="P51" s="10" t="s">
         <v>268</v>
       </c>
+      <c r="Q51" s="33"/>
       <c r="R51" s="34" t="s">
         <v>103</v>
       </c>
@@ -13458,9 +13508,10 @@
       <c r="AX51" s="44"/>
       <c r="AY51" s="1"/>
       <c r="AZ51" s="1"/>
-      <c r="BG51" s="1"/>
+      <c r="BA51" s="1"/>
+      <c r="BH51" s="1"/>
     </row>
-    <row r="52" spans="1:59" ht="25.5">
+    <row r="52" spans="1:60" ht="25.5">
       <c r="A52" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13509,10 +13560,10 @@
       <c r="O52" s="33">
         <v>189</v>
       </c>
-      <c r="P52" s="33"/>
-      <c r="Q52" s="10" t="s">
+      <c r="P52" s="10" t="s">
         <v>269</v>
       </c>
+      <c r="Q52" s="33"/>
       <c r="R52" s="34" t="s">
         <v>103</v>
       </c>
@@ -13615,9 +13666,10 @@
       <c r="AX52" s="44"/>
       <c r="AY52" s="1"/>
       <c r="AZ52" s="1"/>
-      <c r="BG52" s="1"/>
+      <c r="BA52" s="1"/>
+      <c r="BH52" s="1"/>
     </row>
-    <row r="53" spans="1:59" ht="25.5">
+    <row r="53" spans="1:60" ht="25.5">
       <c r="A53" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13666,10 +13718,10 @@
       <c r="O53" s="33">
         <v>177</v>
       </c>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="10" t="s">
+      <c r="P53" s="10" t="s">
         <v>270</v>
       </c>
+      <c r="Q53" s="33"/>
       <c r="R53" s="34" t="s">
         <v>103</v>
       </c>
@@ -13772,9 +13824,10 @@
       <c r="AX53" s="44"/>
       <c r="AY53" s="1"/>
       <c r="AZ53" s="1"/>
-      <c r="BG53" s="1"/>
+      <c r="BA53" s="1"/>
+      <c r="BH53" s="1"/>
     </row>
-    <row r="54" spans="1:59" ht="25.5">
+    <row r="54" spans="1:60" ht="25.5">
       <c r="A54" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13823,10 +13876,10 @@
       <c r="O54" s="34">
         <v>85</v>
       </c>
-      <c r="P54" s="34"/>
-      <c r="Q54" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P54" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q54" s="34"/>
       <c r="R54" s="34" t="s">
         <v>103</v>
       </c>
@@ -13929,9 +13982,10 @@
       <c r="AX54" s="44"/>
       <c r="AY54" s="1"/>
       <c r="AZ54" s="1"/>
-      <c r="BG54" s="1"/>
+      <c r="BA54" s="1"/>
+      <c r="BH54" s="1"/>
     </row>
-    <row r="55" spans="1:59" ht="25.5">
+    <row r="55" spans="1:60" ht="25.5">
       <c r="A55" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -13980,10 +14034,10 @@
       <c r="O55" s="33">
         <v>26</v>
       </c>
-      <c r="P55" s="33"/>
-      <c r="Q55" s="10" t="s">
+      <c r="P55" s="10" t="s">
         <v>271</v>
       </c>
+      <c r="Q55" s="33"/>
       <c r="R55" s="34" t="s">
         <v>103</v>
       </c>
@@ -14086,9 +14140,10 @@
       <c r="AX55" s="44"/>
       <c r="AY55" s="1"/>
       <c r="AZ55" s="1"/>
-      <c r="BG55" s="1"/>
+      <c r="BA55" s="1"/>
+      <c r="BH55" s="1"/>
     </row>
-    <row r="56" spans="1:59" ht="25.5">
+    <row r="56" spans="1:60" ht="25.5">
       <c r="A56" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14137,10 +14192,10 @@
       <c r="O56" s="33">
         <v>87</v>
       </c>
-      <c r="P56" s="33"/>
-      <c r="Q56" s="10" t="s">
+      <c r="P56" s="10" t="s">
         <v>1305</v>
       </c>
+      <c r="Q56" s="33"/>
       <c r="R56" s="34" t="s">
         <v>103</v>
       </c>
@@ -14243,9 +14298,10 @@
       <c r="AX56" s="44"/>
       <c r="AY56" s="1"/>
       <c r="AZ56" s="1"/>
-      <c r="BG56" s="1"/>
+      <c r="BA56" s="1"/>
+      <c r="BH56" s="1"/>
     </row>
-    <row r="57" spans="1:59" ht="25.5">
+    <row r="57" spans="1:60" ht="25.5">
       <c r="A57" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14294,10 +14350,10 @@
       <c r="O57" s="34">
         <v>110</v>
       </c>
-      <c r="P57" s="34"/>
-      <c r="Q57" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P57" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q57" s="34"/>
       <c r="R57" s="34" t="s">
         <v>103</v>
       </c>
@@ -14401,9 +14457,10 @@
       <c r="AX57" s="44"/>
       <c r="AY57" s="1"/>
       <c r="AZ57" s="1"/>
-      <c r="BG57" s="1"/>
+      <c r="BA57" s="1"/>
+      <c r="BH57" s="1"/>
     </row>
-    <row r="58" spans="1:59" ht="25.5">
+    <row r="58" spans="1:60" ht="25.5">
       <c r="A58" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14452,10 +14509,10 @@
       <c r="O58" s="34">
         <v>66</v>
       </c>
-      <c r="P58" s="34"/>
-      <c r="Q58" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P58" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q58" s="34"/>
       <c r="R58" s="34" t="s">
         <v>103</v>
       </c>
@@ -14559,9 +14616,10 @@
       <c r="AX58" s="44"/>
       <c r="AY58" s="1"/>
       <c r="AZ58" s="1"/>
-      <c r="BG58" s="1"/>
+      <c r="BA58" s="1"/>
+      <c r="BH58" s="1"/>
     </row>
-    <row r="59" spans="1:59" ht="25.5">
+    <row r="59" spans="1:60" ht="25.5">
       <c r="A59" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14610,10 +14668,10 @@
       <c r="O59" s="34">
         <v>79</v>
       </c>
-      <c r="P59" s="34"/>
-      <c r="Q59" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P59" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q59" s="34"/>
       <c r="R59" s="34" t="s">
         <v>103</v>
       </c>
@@ -14717,9 +14775,10 @@
       <c r="AX59" s="44"/>
       <c r="AY59" s="1"/>
       <c r="AZ59" s="1"/>
-      <c r="BG59" s="1"/>
+      <c r="BA59" s="1"/>
+      <c r="BH59" s="1"/>
     </row>
-    <row r="60" spans="1:59" ht="25.5">
+    <row r="60" spans="1:60" ht="25.5">
       <c r="A60" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14768,10 +14827,10 @@
       <c r="O60" s="34">
         <v>47</v>
       </c>
-      <c r="P60" s="34"/>
-      <c r="Q60" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P60" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q60" s="34"/>
       <c r="R60" s="34" t="s">
         <v>103</v>
       </c>
@@ -14875,9 +14934,10 @@
       <c r="AX60" s="44"/>
       <c r="AY60" s="1"/>
       <c r="AZ60" s="1"/>
-      <c r="BG60" s="1"/>
+      <c r="BA60" s="1"/>
+      <c r="BH60" s="1"/>
     </row>
-    <row r="61" spans="1:59" ht="25.5">
+    <row r="61" spans="1:60" ht="25.5">
       <c r="A61" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -14926,10 +14986,10 @@
       <c r="O61" s="34">
         <v>60</v>
       </c>
-      <c r="P61" s="34"/>
-      <c r="Q61" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P61" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q61" s="34"/>
       <c r="R61" s="34" t="s">
         <v>103</v>
       </c>
@@ -15033,9 +15093,10 @@
       <c r="AX61" s="44"/>
       <c r="AY61" s="1"/>
       <c r="AZ61" s="1"/>
-      <c r="BG61" s="1"/>
+      <c r="BA61" s="1"/>
+      <c r="BH61" s="1"/>
     </row>
-    <row r="62" spans="1:59" ht="25.5">
+    <row r="62" spans="1:60" ht="25.5">
       <c r="A62" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15084,10 +15145,10 @@
       <c r="O62" s="34">
         <v>81</v>
       </c>
-      <c r="P62" s="34"/>
-      <c r="Q62" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P62" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q62" s="34"/>
       <c r="R62" s="34" t="s">
         <v>103</v>
       </c>
@@ -15191,9 +15252,10 @@
       <c r="AX62" s="44"/>
       <c r="AY62" s="1"/>
       <c r="AZ62" s="1"/>
-      <c r="BG62" s="1"/>
+      <c r="BA62" s="1"/>
+      <c r="BH62" s="1"/>
     </row>
-    <row r="63" spans="1:59" ht="25.5">
+    <row r="63" spans="1:60" ht="25.5">
       <c r="A63" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15242,10 +15304,10 @@
       <c r="O63" s="34">
         <v>45</v>
       </c>
-      <c r="P63" s="34"/>
-      <c r="Q63" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P63" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q63" s="34"/>
       <c r="R63" s="34" t="s">
         <v>103</v>
       </c>
@@ -15349,9 +15411,10 @@
       <c r="AX63" s="44"/>
       <c r="AY63" s="1"/>
       <c r="AZ63" s="1"/>
-      <c r="BG63" s="1"/>
+      <c r="BA63" s="1"/>
+      <c r="BH63" s="1"/>
     </row>
-    <row r="64" spans="1:59" ht="25.5">
+    <row r="64" spans="1:60" ht="25.5">
       <c r="A64" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15400,10 +15463,10 @@
       <c r="O64" s="34">
         <v>73</v>
       </c>
-      <c r="P64" s="34"/>
-      <c r="Q64" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P64" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q64" s="34"/>
       <c r="R64" s="34" t="s">
         <v>103</v>
       </c>
@@ -15507,9 +15570,10 @@
       <c r="AX64" s="44"/>
       <c r="AY64" s="1"/>
       <c r="AZ64" s="1"/>
-      <c r="BG64" s="1"/>
+      <c r="BA64" s="1"/>
+      <c r="BH64" s="1"/>
     </row>
-    <row r="65" spans="1:59" ht="25.5">
+    <row r="65" spans="1:60" ht="25.5">
       <c r="A65" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15558,10 +15622,10 @@
       <c r="O65" s="34">
         <v>80</v>
       </c>
-      <c r="P65" s="34"/>
-      <c r="Q65" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P65" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q65" s="34"/>
       <c r="R65" s="34" t="s">
         <v>103</v>
       </c>
@@ -15664,9 +15728,10 @@
       <c r="AX65" s="44"/>
       <c r="AY65" s="1"/>
       <c r="AZ65" s="1"/>
-      <c r="BG65" s="1"/>
+      <c r="BA65" s="1"/>
+      <c r="BH65" s="1"/>
     </row>
-    <row r="66" spans="1:59" ht="25.5">
+    <row r="66" spans="1:60" ht="25.5">
       <c r="A66" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15715,10 +15780,10 @@
       <c r="O66" s="34">
         <v>110</v>
       </c>
-      <c r="P66" s="34"/>
-      <c r="Q66" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P66" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q66" s="34"/>
       <c r="R66" s="34" t="s">
         <v>103</v>
       </c>
@@ -15821,9 +15886,10 @@
       <c r="AX66" s="44"/>
       <c r="AY66" s="1"/>
       <c r="AZ66" s="1"/>
-      <c r="BG66" s="1"/>
+      <c r="BA66" s="1"/>
+      <c r="BH66" s="1"/>
     </row>
-    <row r="67" spans="1:59" ht="25.5">
+    <row r="67" spans="1:60" ht="25.5">
       <c r="A67" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -15872,10 +15938,10 @@
       <c r="O67" s="34">
         <v>321</v>
       </c>
-      <c r="P67" s="34"/>
-      <c r="Q67" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P67" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q67" s="34"/>
       <c r="R67" s="34" t="s">
         <v>103</v>
       </c>
@@ -15979,9 +16045,10 @@
       <c r="AX67" s="44"/>
       <c r="AY67" s="1"/>
       <c r="AZ67" s="1"/>
-      <c r="BG67" s="1"/>
+      <c r="BA67" s="1"/>
+      <c r="BH67" s="1"/>
     </row>
-    <row r="68" spans="1:59" ht="25.5">
+    <row r="68" spans="1:60" ht="25.5">
       <c r="A68" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16030,10 +16097,10 @@
       <c r="O68" s="34">
         <v>159</v>
       </c>
-      <c r="P68" s="34"/>
-      <c r="Q68" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P68" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q68" s="34"/>
       <c r="R68" s="34" t="s">
         <v>103</v>
       </c>
@@ -16137,9 +16204,10 @@
       <c r="AX68" s="44"/>
       <c r="AY68" s="1"/>
       <c r="AZ68" s="1"/>
-      <c r="BG68" s="1"/>
+      <c r="BA68" s="1"/>
+      <c r="BH68" s="1"/>
     </row>
-    <row r="69" spans="1:59" ht="25.5">
+    <row r="69" spans="1:60" ht="25.5">
       <c r="A69" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16188,10 +16256,10 @@
       <c r="O69" s="34">
         <v>281</v>
       </c>
-      <c r="P69" s="34"/>
-      <c r="Q69" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P69" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q69" s="34"/>
       <c r="R69" s="34" t="s">
         <v>103</v>
       </c>
@@ -16295,9 +16363,10 @@
       <c r="AX69" s="44"/>
       <c r="AY69" s="1"/>
       <c r="AZ69" s="1"/>
-      <c r="BG69" s="1"/>
+      <c r="BA69" s="1"/>
+      <c r="BH69" s="1"/>
     </row>
-    <row r="70" spans="1:59" ht="25.5">
+    <row r="70" spans="1:60" ht="25.5">
       <c r="A70" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16346,10 +16415,10 @@
       <c r="O70" s="34">
         <v>168</v>
       </c>
-      <c r="P70" s="34"/>
-      <c r="Q70" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P70" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q70" s="34"/>
       <c r="R70" s="34" t="s">
         <v>103</v>
       </c>
@@ -16453,9 +16522,10 @@
       <c r="AX70" s="44"/>
       <c r="AY70" s="1"/>
       <c r="AZ70" s="1"/>
-      <c r="BG70" s="1"/>
+      <c r="BA70" s="1"/>
+      <c r="BH70" s="1"/>
     </row>
-    <row r="71" spans="1:59" ht="25.5">
+    <row r="71" spans="1:60" ht="25.5">
       <c r="A71" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16504,10 +16574,10 @@
       <c r="O71" s="34">
         <v>228</v>
       </c>
-      <c r="P71" s="34"/>
-      <c r="Q71" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P71" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q71" s="34"/>
       <c r="R71" s="34" t="s">
         <v>103</v>
       </c>
@@ -16611,9 +16681,10 @@
       <c r="AX71" s="44"/>
       <c r="AY71" s="1"/>
       <c r="AZ71" s="1"/>
-      <c r="BG71" s="1"/>
+      <c r="BA71" s="1"/>
+      <c r="BH71" s="1"/>
     </row>
-    <row r="72" spans="1:59" ht="25.5">
+    <row r="72" spans="1:60" ht="25.5">
       <c r="A72" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16662,10 +16733,10 @@
       <c r="O72" s="34">
         <v>133</v>
       </c>
-      <c r="P72" s="34"/>
-      <c r="Q72" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P72" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q72" s="34"/>
       <c r="R72" s="34" t="s">
         <v>103</v>
       </c>
@@ -16769,9 +16840,10 @@
       <c r="AX72" s="44"/>
       <c r="AY72" s="1"/>
       <c r="AZ72" s="1"/>
-      <c r="BG72" s="1"/>
+      <c r="BA72" s="1"/>
+      <c r="BH72" s="1"/>
     </row>
-    <row r="73" spans="1:59" ht="25.5">
+    <row r="73" spans="1:60" ht="25.5">
       <c r="A73" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16820,10 +16892,10 @@
       <c r="O73" s="34">
         <v>341</v>
       </c>
-      <c r="P73" s="34"/>
-      <c r="Q73" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P73" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q73" s="34"/>
       <c r="R73" s="34" t="s">
         <v>103</v>
       </c>
@@ -16927,9 +16999,10 @@
       <c r="AX73" s="44"/>
       <c r="AY73" s="1"/>
       <c r="AZ73" s="1"/>
-      <c r="BG73" s="1"/>
+      <c r="BA73" s="1"/>
+      <c r="BH73" s="1"/>
     </row>
-    <row r="74" spans="1:59" ht="25.5">
+    <row r="74" spans="1:60" ht="25.5">
       <c r="A74" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -16978,10 +17051,10 @@
       <c r="O74" s="34">
         <v>444</v>
       </c>
-      <c r="P74" s="34"/>
-      <c r="Q74" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P74" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q74" s="34"/>
       <c r="R74" s="34" t="s">
         <v>103</v>
       </c>
@@ -17085,9 +17158,10 @@
       <c r="AX74" s="44"/>
       <c r="AY74" s="1"/>
       <c r="AZ74" s="1"/>
-      <c r="BG74" s="1"/>
+      <c r="BA74" s="1"/>
+      <c r="BH74" s="1"/>
     </row>
-    <row r="75" spans="1:59" ht="25.5">
+    <row r="75" spans="1:60" ht="25.5">
       <c r="A75" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17136,10 +17210,10 @@
       <c r="O75" s="34">
         <v>206</v>
       </c>
-      <c r="P75" s="34"/>
-      <c r="Q75" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P75" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q75" s="34"/>
       <c r="R75" s="34" t="s">
         <v>103</v>
       </c>
@@ -17243,9 +17317,10 @@
       <c r="AX75" s="44"/>
       <c r="AY75" s="1"/>
       <c r="AZ75" s="1"/>
-      <c r="BG75" s="1"/>
+      <c r="BA75" s="1"/>
+      <c r="BH75" s="1"/>
     </row>
-    <row r="76" spans="1:59" ht="25.5">
+    <row r="76" spans="1:60" ht="25.5">
       <c r="A76" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17294,10 +17369,10 @@
       <c r="O76" s="34">
         <v>231</v>
       </c>
-      <c r="P76" s="34"/>
-      <c r="Q76" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P76" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q76" s="34"/>
       <c r="R76" s="34" t="s">
         <v>103</v>
       </c>
@@ -17401,9 +17476,10 @@
       <c r="AX76" s="44"/>
       <c r="AY76" s="1"/>
       <c r="AZ76" s="1"/>
-      <c r="BG76" s="1"/>
+      <c r="BA76" s="1"/>
+      <c r="BH76" s="1"/>
     </row>
-    <row r="77" spans="1:59" ht="25.5">
+    <row r="77" spans="1:60" ht="25.5">
       <c r="A77" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17452,10 +17528,10 @@
       <c r="O77" s="34">
         <v>235</v>
       </c>
-      <c r="P77" s="34"/>
-      <c r="Q77" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P77" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q77" s="34"/>
       <c r="R77" s="34" t="s">
         <v>103</v>
       </c>
@@ -17559,9 +17635,10 @@
       <c r="AX77" s="44"/>
       <c r="AY77" s="1"/>
       <c r="AZ77" s="1"/>
-      <c r="BG77" s="1"/>
+      <c r="BA77" s="1"/>
+      <c r="BH77" s="1"/>
     </row>
-    <row r="78" spans="1:59" ht="25.5">
+    <row r="78" spans="1:60" ht="25.5">
       <c r="A78" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17610,10 +17687,10 @@
       <c r="O78" s="34">
         <v>333</v>
       </c>
-      <c r="P78" s="34"/>
-      <c r="Q78" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P78" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q78" s="34"/>
       <c r="R78" s="34" t="s">
         <v>103</v>
       </c>
@@ -17717,9 +17794,10 @@
       <c r="AX78" s="44"/>
       <c r="AY78" s="1"/>
       <c r="AZ78" s="1"/>
-      <c r="BG78" s="1"/>
+      <c r="BA78" s="1"/>
+      <c r="BH78" s="1"/>
     </row>
-    <row r="79" spans="1:59" ht="25.5">
+    <row r="79" spans="1:60" ht="25.5">
       <c r="A79" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17768,10 +17846,10 @@
       <c r="O79" s="34">
         <v>177</v>
       </c>
-      <c r="P79" s="34"/>
-      <c r="Q79" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P79" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q79" s="34"/>
       <c r="R79" s="34" t="s">
         <v>103</v>
       </c>
@@ -17875,9 +17953,10 @@
       <c r="AX79" s="44"/>
       <c r="AY79" s="1"/>
       <c r="AZ79" s="1"/>
-      <c r="BG79" s="1"/>
+      <c r="BA79" s="1"/>
+      <c r="BH79" s="1"/>
     </row>
-    <row r="80" spans="1:59" ht="25.5">
+    <row r="80" spans="1:60" ht="25.5">
       <c r="A80" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -17926,10 +18005,10 @@
       <c r="O80" s="34">
         <v>99</v>
       </c>
-      <c r="P80" s="34"/>
-      <c r="Q80" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P80" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q80" s="34"/>
       <c r="R80" s="34" t="s">
         <v>103</v>
       </c>
@@ -18033,9 +18112,10 @@
       <c r="AX80" s="44"/>
       <c r="AY80" s="1"/>
       <c r="AZ80" s="1"/>
-      <c r="BG80" s="1"/>
+      <c r="BA80" s="1"/>
+      <c r="BH80" s="1"/>
     </row>
-    <row r="81" spans="1:59" ht="25.5">
+    <row r="81" spans="1:60" ht="25.5">
       <c r="A81" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18084,10 +18164,10 @@
       <c r="O81" s="34">
         <v>169</v>
       </c>
-      <c r="P81" s="34"/>
-      <c r="Q81" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P81" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q81" s="34"/>
       <c r="R81" s="34" t="s">
         <v>103</v>
       </c>
@@ -18191,9 +18271,10 @@
       <c r="AX81" s="44"/>
       <c r="AY81" s="1"/>
       <c r="AZ81" s="1"/>
-      <c r="BG81" s="1"/>
+      <c r="BA81" s="1"/>
+      <c r="BH81" s="1"/>
     </row>
-    <row r="82" spans="1:59" ht="25.5">
+    <row r="82" spans="1:60" ht="25.5">
       <c r="A82" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18242,10 +18323,10 @@
       <c r="O82" s="34">
         <v>196</v>
       </c>
-      <c r="P82" s="34"/>
-      <c r="Q82" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P82" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q82" s="34"/>
       <c r="R82" s="34" t="s">
         <v>103</v>
       </c>
@@ -18349,9 +18430,10 @@
       <c r="AX82" s="44"/>
       <c r="AY82" s="1"/>
       <c r="AZ82" s="1"/>
-      <c r="BG82" s="1"/>
+      <c r="BA82" s="1"/>
+      <c r="BH82" s="1"/>
     </row>
-    <row r="83" spans="1:59" ht="25.5">
+    <row r="83" spans="1:60" ht="25.5">
       <c r="A83" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18400,10 +18482,10 @@
       <c r="O83" s="34">
         <v>195</v>
       </c>
-      <c r="P83" s="34"/>
-      <c r="Q83" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P83" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q83" s="34"/>
       <c r="R83" s="34" t="s">
         <v>103</v>
       </c>
@@ -18507,9 +18589,10 @@
       <c r="AX83" s="44"/>
       <c r="AY83" s="1"/>
       <c r="AZ83" s="1"/>
-      <c r="BG83" s="1"/>
+      <c r="BA83" s="1"/>
+      <c r="BH83" s="1"/>
     </row>
-    <row r="84" spans="1:59" ht="25.5">
+    <row r="84" spans="1:60" ht="25.5">
       <c r="A84" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18558,10 +18641,10 @@
       <c r="O84" s="34">
         <v>181</v>
       </c>
-      <c r="P84" s="34"/>
-      <c r="Q84" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P84" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q84" s="34"/>
       <c r="R84" s="34" t="s">
         <v>103</v>
       </c>
@@ -18665,9 +18748,10 @@
       <c r="AX84" s="44"/>
       <c r="AY84" s="1"/>
       <c r="AZ84" s="1"/>
-      <c r="BG84" s="1"/>
+      <c r="BA84" s="1"/>
+      <c r="BH84" s="1"/>
     </row>
-    <row r="85" spans="1:59" ht="25.5">
+    <row r="85" spans="1:60" ht="25.5">
       <c r="A85" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18716,10 +18800,10 @@
       <c r="O85" s="34">
         <v>277</v>
       </c>
-      <c r="P85" s="34"/>
-      <c r="Q85" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P85" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q85" s="34"/>
       <c r="R85" s="34" t="s">
         <v>103</v>
       </c>
@@ -18823,9 +18907,10 @@
       <c r="AX85" s="44"/>
       <c r="AY85" s="1"/>
       <c r="AZ85" s="1"/>
-      <c r="BG85" s="1"/>
+      <c r="BA85" s="1"/>
+      <c r="BH85" s="1"/>
     </row>
-    <row r="86" spans="1:59" ht="25.5">
+    <row r="86" spans="1:60" ht="25.5">
       <c r="A86" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -18874,10 +18959,10 @@
       <c r="O86" s="34">
         <v>142</v>
       </c>
-      <c r="P86" s="34"/>
-      <c r="Q86" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P86" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q86" s="34"/>
       <c r="R86" s="34" t="s">
         <v>103</v>
       </c>
@@ -18981,9 +19066,10 @@
       <c r="AX86" s="44"/>
       <c r="AY86" s="1"/>
       <c r="AZ86" s="1"/>
-      <c r="BG86" s="1"/>
+      <c r="BA86" s="1"/>
+      <c r="BH86" s="1"/>
     </row>
-    <row r="87" spans="1:59" ht="25.5">
+    <row r="87" spans="1:60" ht="25.5">
       <c r="A87" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19032,10 +19118,10 @@
       <c r="O87" s="34">
         <v>114</v>
       </c>
-      <c r="P87" s="34"/>
-      <c r="Q87" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P87" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q87" s="34"/>
       <c r="R87" s="34" t="s">
         <v>103</v>
       </c>
@@ -19139,9 +19225,10 @@
       <c r="AX87" s="44"/>
       <c r="AY87" s="1"/>
       <c r="AZ87" s="1"/>
-      <c r="BG87" s="1"/>
+      <c r="BA87" s="1"/>
+      <c r="BH87" s="1"/>
     </row>
-    <row r="88" spans="1:59" ht="25.5">
+    <row r="88" spans="1:60" ht="25.5">
       <c r="A88" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19190,10 +19277,10 @@
       <c r="O88" s="34">
         <v>167</v>
       </c>
-      <c r="P88" s="34"/>
-      <c r="Q88" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P88" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q88" s="34"/>
       <c r="R88" s="34" t="s">
         <v>103</v>
       </c>
@@ -19297,9 +19384,10 @@
       <c r="AX88" s="44"/>
       <c r="AY88" s="1"/>
       <c r="AZ88" s="1"/>
-      <c r="BG88" s="1"/>
+      <c r="BA88" s="1"/>
+      <c r="BH88" s="1"/>
     </row>
-    <row r="89" spans="1:59" ht="25.5">
+    <row r="89" spans="1:60" ht="25.5">
       <c r="A89" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19348,10 +19436,10 @@
       <c r="O89" s="34">
         <v>88</v>
       </c>
-      <c r="P89" s="34"/>
-      <c r="Q89" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P89" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q89" s="34"/>
       <c r="R89" s="34" t="s">
         <v>103</v>
       </c>
@@ -19455,9 +19543,10 @@
       <c r="AX89" s="44"/>
       <c r="AY89" s="1"/>
       <c r="AZ89" s="1"/>
-      <c r="BG89" s="1"/>
+      <c r="BA89" s="1"/>
+      <c r="BH89" s="1"/>
     </row>
-    <row r="90" spans="1:59" ht="25.5">
+    <row r="90" spans="1:60" ht="25.5">
       <c r="A90" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19506,10 +19595,10 @@
       <c r="O90" s="34">
         <v>372</v>
       </c>
-      <c r="P90" s="34"/>
-      <c r="Q90" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P90" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q90" s="34"/>
       <c r="R90" s="34" t="s">
         <v>103</v>
       </c>
@@ -19612,9 +19701,10 @@
       <c r="AX90" s="44"/>
       <c r="AY90" s="1"/>
       <c r="AZ90" s="1"/>
-      <c r="BG90" s="1"/>
+      <c r="BA90" s="1"/>
+      <c r="BH90" s="1"/>
     </row>
-    <row r="91" spans="1:59" ht="25.5">
+    <row r="91" spans="1:60" ht="25.5">
       <c r="A91" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19663,10 +19753,10 @@
       <c r="O91" s="34">
         <v>106</v>
       </c>
-      <c r="P91" s="34"/>
-      <c r="Q91" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P91" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q91" s="34"/>
       <c r="R91" s="34" t="s">
         <v>103</v>
       </c>
@@ -19769,9 +19859,10 @@
       <c r="AX91" s="44"/>
       <c r="AY91" s="1"/>
       <c r="AZ91" s="1"/>
-      <c r="BG91" s="1"/>
+      <c r="BA91" s="1"/>
+      <c r="BH91" s="1"/>
     </row>
-    <row r="92" spans="1:59" ht="25.5">
+    <row r="92" spans="1:60" ht="25.5">
       <c r="A92" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19820,10 +19911,10 @@
       <c r="O92" s="34">
         <v>108</v>
       </c>
-      <c r="P92" s="34"/>
-      <c r="Q92" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P92" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q92" s="34"/>
       <c r="R92" s="34" t="s">
         <v>103</v>
       </c>
@@ -19926,9 +20017,10 @@
       <c r="AX92" s="44"/>
       <c r="AY92" s="1"/>
       <c r="AZ92" s="1"/>
-      <c r="BG92" s="1"/>
+      <c r="BA92" s="1"/>
+      <c r="BH92" s="1"/>
     </row>
-    <row r="93" spans="1:59" ht="25.5">
+    <row r="93" spans="1:60" ht="25.5">
       <c r="A93" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -19977,10 +20069,10 @@
       <c r="O93" s="34">
         <v>424</v>
       </c>
-      <c r="P93" s="34"/>
-      <c r="Q93" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P93" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q93" s="34"/>
       <c r="R93" s="34" t="s">
         <v>103</v>
       </c>
@@ -20083,9 +20175,10 @@
       <c r="AX93" s="44"/>
       <c r="AY93" s="1"/>
       <c r="AZ93" s="1"/>
-      <c r="BG93" s="1"/>
+      <c r="BA93" s="1"/>
+      <c r="BH93" s="1"/>
     </row>
-    <row r="94" spans="1:59" ht="25.5">
+    <row r="94" spans="1:60" ht="25.5">
       <c r="A94" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20134,10 +20227,10 @@
       <c r="O94" s="34">
         <v>258</v>
       </c>
-      <c r="P94" s="34"/>
-      <c r="Q94" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P94" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q94" s="34"/>
       <c r="R94" s="34" t="s">
         <v>103</v>
       </c>
@@ -20240,9 +20333,10 @@
       <c r="AX94" s="44"/>
       <c r="AY94" s="1"/>
       <c r="AZ94" s="1"/>
-      <c r="BG94" s="1"/>
+      <c r="BA94" s="1"/>
+      <c r="BH94" s="1"/>
     </row>
-    <row r="95" spans="1:59" ht="25.5">
+    <row r="95" spans="1:60" ht="25.5">
       <c r="A95" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20291,10 +20385,10 @@
       <c r="O95" s="34">
         <v>152</v>
       </c>
-      <c r="P95" s="34"/>
-      <c r="Q95" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P95" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q95" s="34"/>
       <c r="R95" s="34" t="s">
         <v>103</v>
       </c>
@@ -20397,9 +20491,10 @@
       <c r="AX95" s="44"/>
       <c r="AY95" s="1"/>
       <c r="AZ95" s="1"/>
-      <c r="BG95" s="1"/>
+      <c r="BA95" s="1"/>
+      <c r="BH95" s="1"/>
     </row>
-    <row r="96" spans="1:59" ht="25.5">
+    <row r="96" spans="1:60" ht="25.5">
       <c r="A96" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20448,10 +20543,10 @@
       <c r="O96" s="34">
         <v>105</v>
       </c>
-      <c r="P96" s="34"/>
-      <c r="Q96" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P96" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q96" s="34"/>
       <c r="R96" s="34" t="s">
         <v>103</v>
       </c>
@@ -20554,9 +20649,10 @@
       <c r="AX96" s="44"/>
       <c r="AY96" s="1"/>
       <c r="AZ96" s="1"/>
-      <c r="BG96" s="1"/>
+      <c r="BA96" s="1"/>
+      <c r="BH96" s="1"/>
     </row>
-    <row r="97" spans="1:59" ht="25.5">
+    <row r="97" spans="1:60" ht="25.5">
       <c r="A97" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20605,10 +20701,10 @@
       <c r="O97" s="34">
         <v>547</v>
       </c>
-      <c r="P97" s="34"/>
-      <c r="Q97" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P97" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q97" s="34"/>
       <c r="R97" s="34" t="s">
         <v>103</v>
       </c>
@@ -20711,9 +20807,10 @@
       <c r="AX97" s="44"/>
       <c r="AY97" s="1"/>
       <c r="AZ97" s="1"/>
-      <c r="BG97" s="1"/>
+      <c r="BA97" s="1"/>
+      <c r="BH97" s="1"/>
     </row>
-    <row r="98" spans="1:59" ht="25.5">
+    <row r="98" spans="1:60" ht="25.5">
       <c r="A98" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20762,10 +20859,10 @@
       <c r="O98" s="34">
         <v>286</v>
       </c>
-      <c r="P98" s="34"/>
-      <c r="Q98" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P98" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q98" s="34"/>
       <c r="R98" s="34" t="s">
         <v>103</v>
       </c>
@@ -20869,9 +20966,10 @@
       <c r="AX98" s="44"/>
       <c r="AY98" s="1"/>
       <c r="AZ98" s="1"/>
-      <c r="BG98" s="1"/>
+      <c r="BA98" s="1"/>
+      <c r="BH98" s="1"/>
     </row>
-    <row r="99" spans="1:59" ht="25.5">
+    <row r="99" spans="1:60" ht="25.5">
       <c r="A99" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -20920,10 +21018,10 @@
       <c r="O99" s="34">
         <v>84</v>
       </c>
-      <c r="P99" s="34"/>
-      <c r="Q99" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P99" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q99" s="34"/>
       <c r="R99" s="34" t="s">
         <v>103</v>
       </c>
@@ -21027,9 +21125,10 @@
       <c r="AX99" s="44"/>
       <c r="AY99" s="1"/>
       <c r="AZ99" s="1"/>
-      <c r="BG99" s="1"/>
+      <c r="BA99" s="1"/>
+      <c r="BH99" s="1"/>
     </row>
-    <row r="100" spans="1:59" ht="25.5">
+    <row r="100" spans="1:60" ht="25.5">
       <c r="A100" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -21078,10 +21177,10 @@
       <c r="O100" s="34">
         <v>272</v>
       </c>
-      <c r="P100" s="34"/>
-      <c r="Q100" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P100" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q100" s="34"/>
       <c r="R100" s="34" t="s">
         <v>103</v>
       </c>
@@ -21185,9 +21284,10 @@
       <c r="AX100" s="44"/>
       <c r="AY100" s="1"/>
       <c r="AZ100" s="1"/>
-      <c r="BG100" s="1"/>
+      <c r="BA100" s="1"/>
+      <c r="BH100" s="1"/>
     </row>
-    <row r="101" spans="1:59" ht="25.5">
+    <row r="101" spans="1:60" ht="25.5">
       <c r="A101" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -21236,10 +21336,10 @@
       <c r="O101" s="34">
         <v>162</v>
       </c>
-      <c r="P101" s="34"/>
-      <c r="Q101" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P101" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q101" s="34"/>
       <c r="R101" s="34" t="s">
         <v>103</v>
       </c>
@@ -21343,9 +21443,10 @@
       <c r="AX101" s="44"/>
       <c r="AY101" s="1"/>
       <c r="AZ101" s="1"/>
-      <c r="BG101" s="1"/>
+      <c r="BA101" s="1"/>
+      <c r="BH101" s="1"/>
     </row>
-    <row r="102" spans="1:59" ht="25.5">
+    <row r="102" spans="1:60" ht="25.5">
       <c r="A102" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -21394,10 +21495,10 @@
       <c r="O102" s="34">
         <v>271</v>
       </c>
-      <c r="P102" s="34"/>
-      <c r="Q102" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P102" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q102" s="34"/>
       <c r="R102" s="34" t="s">
         <v>103</v>
       </c>
@@ -21501,9 +21602,10 @@
       <c r="AX102" s="44"/>
       <c r="AY102" s="1"/>
       <c r="AZ102" s="1"/>
-      <c r="BG102" s="1"/>
+      <c r="BA102" s="1"/>
+      <c r="BH102" s="1"/>
     </row>
-    <row r="103" spans="1:59" ht="25.5">
+    <row r="103" spans="1:60" ht="25.5">
       <c r="A103" s="10" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21552,10 +21654,10 @@
       <c r="O103" s="34">
         <v>144</v>
       </c>
-      <c r="P103" s="34"/>
-      <c r="Q103" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P103" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q103" s="34"/>
       <c r="R103" s="34" t="s">
         <v>103</v>
       </c>
@@ -21658,9 +21760,10 @@
       <c r="AX103" s="44"/>
       <c r="AY103" s="1"/>
       <c r="AZ103" s="1"/>
-      <c r="BG103" s="1"/>
+      <c r="BA103" s="1"/>
+      <c r="BH103" s="1"/>
     </row>
-    <row r="104" spans="1:59" ht="25.5">
+    <row r="104" spans="1:60" ht="25.5">
       <c r="A104" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21709,10 +21812,10 @@
       <c r="O104" s="34">
         <v>133</v>
       </c>
-      <c r="P104" s="34"/>
-      <c r="Q104" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P104" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q104" s="34"/>
       <c r="R104" s="34" t="s">
         <v>103</v>
       </c>
@@ -21819,8 +21922,10 @@
       <c r="BD104" s="11"/>
       <c r="BE104" s="13"/>
       <c r="BF104" s="16"/>
+      <c r="BG104"/>
+      <c r="BH104" s="1"/>
     </row>
-    <row r="105" spans="1:59" ht="25.5">
+    <row r="105" spans="1:60" ht="25.5">
       <c r="A105" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -21869,10 +21974,10 @@
       <c r="O105" s="34">
         <v>114</v>
       </c>
-      <c r="P105" s="34"/>
-      <c r="Q105" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P105" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q105" s="34"/>
       <c r="R105" s="34" t="s">
         <v>103</v>
       </c>
@@ -21973,8 +22078,11 @@
       </c>
       <c r="AW105" s="14"/>
       <c r="AX105" s="44"/>
+      <c r="BA105" s="1"/>
+      <c r="BG105"/>
+      <c r="BH105" s="1"/>
     </row>
-    <row r="106" spans="1:59" ht="25.5">
+    <row r="106" spans="1:60" ht="25.5">
       <c r="A106" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22021,10 +22129,10 @@
       <c r="O106" s="34">
         <v>36</v>
       </c>
-      <c r="P106" s="34"/>
-      <c r="Q106" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P106" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q106" s="34"/>
       <c r="R106" s="34" t="s">
         <v>103</v>
       </c>
@@ -22125,8 +22233,11 @@
       </c>
       <c r="AW106" s="14"/>
       <c r="AX106" s="44"/>
+      <c r="BA106" s="1"/>
+      <c r="BG106"/>
+      <c r="BH106" s="1"/>
     </row>
-    <row r="107" spans="1:59" ht="25.5">
+    <row r="107" spans="1:60" ht="25.5">
       <c r="A107" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22175,10 +22286,10 @@
       <c r="O107" s="34">
         <v>60</v>
       </c>
-      <c r="P107" s="34"/>
-      <c r="Q107" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P107" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q107" s="34"/>
       <c r="R107" s="34" t="s">
         <v>103</v>
       </c>
@@ -22279,8 +22390,11 @@
       </c>
       <c r="AW107" s="14"/>
       <c r="AX107" s="44"/>
+      <c r="BA107" s="1"/>
+      <c r="BG107"/>
+      <c r="BH107" s="1"/>
     </row>
-    <row r="108" spans="1:59" ht="25.5">
+    <row r="108" spans="1:60" ht="25.5">
       <c r="A108" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22329,10 +22443,10 @@
       <c r="O108" s="34">
         <v>60</v>
       </c>
-      <c r="P108" s="34"/>
-      <c r="Q108" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P108" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q108" s="34"/>
       <c r="R108" s="34" t="s">
         <v>103</v>
       </c>
@@ -22433,8 +22547,11 @@
       </c>
       <c r="AW108" s="14"/>
       <c r="AX108" s="44"/>
+      <c r="BA108" s="1"/>
+      <c r="BG108"/>
+      <c r="BH108" s="1"/>
     </row>
-    <row r="109" spans="1:59" ht="25.5">
+    <row r="109" spans="1:60" ht="25.5">
       <c r="A109" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22483,10 +22600,10 @@
       <c r="O109" s="34">
         <v>96</v>
       </c>
-      <c r="P109" s="34"/>
-      <c r="Q109" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P109" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q109" s="34"/>
       <c r="R109" s="34" t="s">
         <v>103</v>
       </c>
@@ -22587,8 +22704,11 @@
       </c>
       <c r="AW109" s="14"/>
       <c r="AX109" s="44"/>
+      <c r="BA109" s="1"/>
+      <c r="BG109"/>
+      <c r="BH109" s="1"/>
     </row>
-    <row r="110" spans="1:59" ht="25.5">
+    <row r="110" spans="1:60" ht="25.5">
       <c r="A110" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22637,10 +22757,10 @@
       <c r="O110" s="34">
         <v>265</v>
       </c>
-      <c r="P110" s="34"/>
-      <c r="Q110" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P110" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q110" s="34"/>
       <c r="R110" s="34" t="s">
         <v>103</v>
       </c>
@@ -22741,8 +22861,11 @@
       </c>
       <c r="AW110" s="14"/>
       <c r="AX110" s="44"/>
+      <c r="BA110" s="1"/>
+      <c r="BG110"/>
+      <c r="BH110" s="1"/>
     </row>
-    <row r="111" spans="1:59" ht="25.5">
+    <row r="111" spans="1:60" ht="25.5">
       <c r="A111" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22791,10 +22914,10 @@
       <c r="O111" s="34">
         <v>63</v>
       </c>
-      <c r="P111" s="34"/>
-      <c r="Q111" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P111" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q111" s="34"/>
       <c r="R111" s="34" t="s">
         <v>103</v>
       </c>
@@ -22895,8 +23018,11 @@
       </c>
       <c r="AW111" s="14"/>
       <c r="AX111" s="44"/>
+      <c r="BA111" s="1"/>
+      <c r="BG111"/>
+      <c r="BH111" s="1"/>
     </row>
-    <row r="112" spans="1:59" ht="25.5">
+    <row r="112" spans="1:60" ht="25.5">
       <c r="A112" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -22945,10 +23071,10 @@
       <c r="O112" s="34">
         <v>120</v>
       </c>
-      <c r="P112" s="34"/>
-      <c r="Q112" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P112" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q112" s="34"/>
       <c r="R112" s="34" t="s">
         <v>103</v>
       </c>
@@ -23050,10 +23176,11 @@
       <c r="AW112" s="14"/>
       <c r="AX112" s="44"/>
       <c r="AZ112" s="1"/>
+      <c r="BA112" s="1"/>
       <c r="BF112"/>
-      <c r="BG112" s="1"/>
+      <c r="BH112" s="1"/>
     </row>
-    <row r="113" spans="1:59" ht="25.5">
+    <row r="113" spans="1:60" ht="25.5">
       <c r="A113" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -23102,10 +23229,10 @@
       <c r="O113" s="34">
         <v>176</v>
       </c>
-      <c r="P113" s="34"/>
-      <c r="Q113" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P113" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q113" s="34"/>
       <c r="R113" s="34" t="s">
         <v>103</v>
       </c>
@@ -23207,10 +23334,11 @@
       <c r="AW113" s="14"/>
       <c r="AX113" s="44"/>
       <c r="AZ113" s="1"/>
+      <c r="BA113" s="1"/>
       <c r="BF113"/>
-      <c r="BG113" s="1"/>
+      <c r="BH113" s="1"/>
     </row>
-    <row r="114" spans="1:59" ht="25.5">
+    <row r="114" spans="1:60" ht="25.5">
       <c r="A114" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -23259,10 +23387,10 @@
       <c r="O114" s="34">
         <v>86</v>
       </c>
-      <c r="P114" s="34"/>
-      <c r="Q114" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P114" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q114" s="34"/>
       <c r="R114" s="34" t="s">
         <v>103</v>
       </c>
@@ -23364,10 +23492,11 @@
       <c r="AW114" s="14"/>
       <c r="AX114" s="44"/>
       <c r="AZ114" s="1"/>
+      <c r="BA114" s="1"/>
       <c r="BF114"/>
-      <c r="BG114" s="1"/>
+      <c r="BH114" s="1"/>
     </row>
-    <row r="115" spans="1:59" ht="25.5">
+    <row r="115" spans="1:60" ht="25.5">
       <c r="A115" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -23416,10 +23545,10 @@
       <c r="O115" s="34">
         <v>86</v>
       </c>
-      <c r="P115" s="34"/>
-      <c r="Q115" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P115" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q115" s="34"/>
       <c r="R115" s="34" t="s">
         <v>103</v>
       </c>
@@ -23521,10 +23650,11 @@
       <c r="AW115" s="14"/>
       <c r="AX115" s="44"/>
       <c r="AZ115" s="1"/>
+      <c r="BA115" s="1"/>
       <c r="BF115"/>
-      <c r="BG115" s="1"/>
+      <c r="BH115" s="1"/>
     </row>
-    <row r="116" spans="1:59" ht="25.5">
+    <row r="116" spans="1:60" ht="25.5">
       <c r="A116" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Occitanie</v>
@@ -23573,10 +23703,10 @@
       <c r="O116" s="34">
         <v>90</v>
       </c>
-      <c r="P116" s="34"/>
-      <c r="Q116" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P116" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q116" s="34"/>
       <c r="R116" s="34" t="s">
         <v>103</v>
       </c>
@@ -23678,10 +23808,11 @@
       <c r="AW116" s="14"/>
       <c r="AX116" s="44"/>
       <c r="AZ116" s="1"/>
+      <c r="BA116" s="1"/>
       <c r="BF116"/>
-      <c r="BG116" s="1"/>
+      <c r="BH116" s="1"/>
     </row>
-    <row r="117" spans="1:59" ht="38.25">
+    <row r="117" spans="1:60" ht="38.25">
       <c r="A117" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -23730,10 +23861,10 @@
       <c r="O117" s="34">
         <v>98</v>
       </c>
-      <c r="P117" s="34"/>
-      <c r="Q117" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P117" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q117" s="34"/>
       <c r="R117" s="34" t="s">
         <v>103</v>
       </c>
@@ -23836,10 +23967,11 @@
       <c r="AW117" s="14"/>
       <c r="AX117" s="44"/>
       <c r="AZ117" s="1"/>
+      <c r="BA117" s="1"/>
       <c r="BF117"/>
-      <c r="BG117" s="1"/>
+      <c r="BH117" s="1"/>
     </row>
-    <row r="118" spans="1:59" ht="38.25">
+    <row r="118" spans="1:60" ht="38.25">
       <c r="A118" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -23888,10 +24020,10 @@
       <c r="O118" s="34">
         <v>1118</v>
       </c>
-      <c r="P118" s="34"/>
-      <c r="Q118" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P118" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q118" s="34"/>
       <c r="R118" s="34" t="s">
         <v>103</v>
       </c>
@@ -23994,10 +24126,11 @@
       <c r="AW118" s="14"/>
       <c r="AX118" s="44"/>
       <c r="AZ118" s="1"/>
+      <c r="BA118" s="1"/>
       <c r="BF118"/>
-      <c r="BG118" s="1"/>
+      <c r="BH118" s="1"/>
     </row>
-    <row r="119" spans="1:59" ht="25.5">
+    <row r="119" spans="1:60" ht="25.5">
       <c r="A119" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24046,10 +24179,10 @@
       <c r="O119" s="34">
         <v>254</v>
       </c>
-      <c r="P119" s="34"/>
-      <c r="Q119" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P119" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q119" s="34"/>
       <c r="R119" s="34" t="s">
         <v>103</v>
       </c>
@@ -24149,10 +24282,11 @@
       <c r="AW119" s="14"/>
       <c r="AX119" s="44"/>
       <c r="AZ119" s="1"/>
+      <c r="BA119" s="1"/>
       <c r="BF119"/>
-      <c r="BG119" s="1"/>
+      <c r="BH119" s="1"/>
     </row>
-    <row r="120" spans="1:59" ht="25.5">
+    <row r="120" spans="1:60" ht="25.5">
       <c r="A120" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24201,10 +24335,10 @@
       <c r="O120" s="34">
         <v>99</v>
       </c>
-      <c r="P120" s="34"/>
-      <c r="Q120" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P120" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q120" s="34"/>
       <c r="R120" s="34" t="s">
         <v>103</v>
       </c>
@@ -24306,10 +24440,11 @@
       <c r="AW120" s="14"/>
       <c r="AX120" s="44"/>
       <c r="AZ120" s="1"/>
+      <c r="BA120" s="1"/>
       <c r="BF120"/>
-      <c r="BG120" s="1"/>
+      <c r="BH120" s="1"/>
     </row>
-    <row r="121" spans="1:59" ht="25.5">
+    <row r="121" spans="1:60" ht="25.5">
       <c r="A121" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24358,10 +24493,10 @@
       <c r="O121" s="34">
         <v>163</v>
       </c>
-      <c r="P121" s="34"/>
-      <c r="Q121" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P121" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q121" s="34"/>
       <c r="R121" s="34" t="s">
         <v>103</v>
       </c>
@@ -24464,10 +24599,11 @@
       <c r="AW121" s="14"/>
       <c r="AX121" s="44"/>
       <c r="AZ121" s="1"/>
+      <c r="BA121" s="1"/>
       <c r="BF121"/>
-      <c r="BG121" s="1"/>
+      <c r="BH121" s="1"/>
     </row>
-    <row r="122" spans="1:59" ht="25.5">
+    <row r="122" spans="1:60" ht="25.5">
       <c r="A122" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24516,10 +24652,10 @@
       <c r="O122" s="34">
         <v>102</v>
       </c>
-      <c r="P122" s="34"/>
-      <c r="Q122" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P122" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q122" s="34"/>
       <c r="R122" s="34" t="s">
         <v>103</v>
       </c>
@@ -24622,10 +24758,11 @@
       <c r="AW122" s="14"/>
       <c r="AX122" s="44"/>
       <c r="AZ122" s="1"/>
+      <c r="BA122" s="1"/>
       <c r="BF122"/>
-      <c r="BG122" s="1"/>
+      <c r="BH122" s="1"/>
     </row>
-    <row r="123" spans="1:59" ht="25.5">
+    <row r="123" spans="1:60" ht="25.5">
       <c r="A123" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24674,10 +24811,10 @@
       <c r="O123" s="34">
         <v>87</v>
       </c>
-      <c r="P123" s="34"/>
-      <c r="Q123" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P123" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q123" s="34"/>
       <c r="R123" s="34" t="s">
         <v>103</v>
       </c>
@@ -24780,10 +24917,11 @@
       <c r="AW123" s="14"/>
       <c r="AX123" s="44"/>
       <c r="AZ123" s="1"/>
+      <c r="BA123" s="1"/>
       <c r="BF123"/>
-      <c r="BG123" s="1"/>
+      <c r="BH123" s="1"/>
     </row>
-    <row r="124" spans="1:59" ht="38.25">
+    <row r="124" spans="1:60" ht="25.5">
       <c r="A124" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24832,10 +24970,10 @@
       <c r="O124" s="34">
         <v>438</v>
       </c>
-      <c r="P124" s="34"/>
-      <c r="Q124" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P124" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q124" s="34"/>
       <c r="R124" s="34" t="s">
         <v>103</v>
       </c>
@@ -24938,10 +25076,11 @@
       <c r="AW124" s="14"/>
       <c r="AX124" s="44"/>
       <c r="AZ124" s="1"/>
+      <c r="BA124" s="1"/>
       <c r="BF124"/>
-      <c r="BG124" s="1"/>
+      <c r="BH124" s="1"/>
     </row>
-    <row r="125" spans="1:59" ht="25.5">
+    <row r="125" spans="1:60" ht="25.5">
       <c r="A125" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -24990,10 +25129,10 @@
       <c r="O125" s="34">
         <v>97</v>
       </c>
-      <c r="P125" s="34"/>
-      <c r="Q125" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P125" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q125" s="34"/>
       <c r="R125" s="34" t="s">
         <v>103</v>
       </c>
@@ -25096,10 +25235,11 @@
       <c r="AW125" s="14"/>
       <c r="AX125" s="44"/>
       <c r="AZ125" s="1"/>
+      <c r="BA125" s="1"/>
       <c r="BF125"/>
-      <c r="BG125" s="1"/>
+      <c r="BH125" s="1"/>
     </row>
-    <row r="126" spans="1:59" ht="25.5">
+    <row r="126" spans="1:60" ht="25.5">
       <c r="A126" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25148,10 +25288,10 @@
       <c r="O126" s="34">
         <v>75</v>
       </c>
-      <c r="P126" s="34"/>
-      <c r="Q126" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P126" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q126" s="34"/>
       <c r="R126" s="34" t="s">
         <v>103</v>
       </c>
@@ -25253,8 +25393,11 @@
       </c>
       <c r="AW126" s="14"/>
       <c r="AX126" s="44"/>
+      <c r="BA126" s="1"/>
+      <c r="BG126"/>
+      <c r="BH126" s="1"/>
     </row>
-    <row r="127" spans="1:59" ht="25.5">
+    <row r="127" spans="1:60" ht="25.5">
       <c r="A127" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25303,10 +25446,10 @@
       <c r="O127" s="34">
         <v>125</v>
       </c>
-      <c r="P127" s="34"/>
-      <c r="Q127" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P127" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q127" s="34"/>
       <c r="R127" s="34" t="s">
         <v>103</v>
       </c>
@@ -25408,8 +25551,11 @@
       </c>
       <c r="AW127" s="14"/>
       <c r="AX127" s="44"/>
+      <c r="BA127" s="1"/>
+      <c r="BG127"/>
+      <c r="BH127" s="1"/>
     </row>
-    <row r="128" spans="1:59" ht="25.5">
+    <row r="128" spans="1:60" ht="25.5">
       <c r="A128" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25458,10 +25604,10 @@
       <c r="O128" s="34">
         <v>69</v>
       </c>
-      <c r="P128" s="34"/>
-      <c r="Q128" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P128" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q128" s="34"/>
       <c r="R128" s="34" t="s">
         <v>103</v>
       </c>
@@ -25563,8 +25709,11 @@
       </c>
       <c r="AW128" s="14"/>
       <c r="AX128" s="44"/>
+      <c r="BA128" s="1"/>
+      <c r="BG128"/>
+      <c r="BH128" s="1"/>
     </row>
-    <row r="129" spans="1:50" ht="25.5">
+    <row r="129" spans="1:60" ht="25.5">
       <c r="A129" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25613,10 +25762,10 @@
       <c r="O129" s="34">
         <v>65</v>
       </c>
-      <c r="P129" s="34"/>
-      <c r="Q129" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P129" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q129" s="34"/>
       <c r="R129" s="34" t="s">
         <v>103</v>
       </c>
@@ -25718,8 +25867,11 @@
       </c>
       <c r="AW129" s="14"/>
       <c r="AX129" s="44"/>
+      <c r="BA129" s="1"/>
+      <c r="BG129"/>
+      <c r="BH129" s="1"/>
     </row>
-    <row r="130" spans="1:50" ht="25.5">
+    <row r="130" spans="1:60" ht="25.5">
       <c r="A130" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25768,10 +25920,10 @@
       <c r="O130" s="34">
         <v>73</v>
       </c>
-      <c r="P130" s="34"/>
-      <c r="Q130" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P130" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q130" s="34"/>
       <c r="R130" s="34" t="s">
         <v>103</v>
       </c>
@@ -25873,8 +26025,11 @@
       </c>
       <c r="AW130" s="14"/>
       <c r="AX130" s="44"/>
+      <c r="BA130" s="1"/>
+      <c r="BG130"/>
+      <c r="BH130" s="1"/>
     </row>
-    <row r="131" spans="1:50" ht="25.5">
+    <row r="131" spans="1:60" ht="25.5">
       <c r="A131" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -25923,10 +26078,10 @@
       <c r="O131" s="34">
         <v>75</v>
       </c>
-      <c r="P131" s="34"/>
-      <c r="Q131" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P131" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q131" s="34"/>
       <c r="R131" s="34" t="s">
         <v>103</v>
       </c>
@@ -26028,8 +26183,11 @@
       </c>
       <c r="AW131" s="14"/>
       <c r="AX131" s="44"/>
+      <c r="BA131" s="1"/>
+      <c r="BG131"/>
+      <c r="BH131" s="1"/>
     </row>
-    <row r="132" spans="1:50" ht="25.5">
+    <row r="132" spans="1:60" ht="25.5">
       <c r="A132" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26078,10 +26236,10 @@
       <c r="O132" s="34">
         <v>57</v>
       </c>
-      <c r="P132" s="34"/>
-      <c r="Q132" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P132" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q132" s="34"/>
       <c r="R132" s="34" t="s">
         <v>103</v>
       </c>
@@ -26183,8 +26341,11 @@
       </c>
       <c r="AW132" s="14"/>
       <c r="AX132" s="44"/>
+      <c r="BA132" s="1"/>
+      <c r="BG132"/>
+      <c r="BH132" s="1"/>
     </row>
-    <row r="133" spans="1:50" ht="25.5">
+    <row r="133" spans="1:60" ht="25.5">
       <c r="A133" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26233,10 +26394,10 @@
       <c r="O133" s="34">
         <v>58</v>
       </c>
-      <c r="P133" s="34"/>
-      <c r="Q133" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P133" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q133" s="34"/>
       <c r="R133" s="34" t="s">
         <v>103</v>
       </c>
@@ -26338,8 +26499,11 @@
       </c>
       <c r="AW133" s="14"/>
       <c r="AX133" s="44"/>
+      <c r="BA133" s="1"/>
+      <c r="BG133"/>
+      <c r="BH133" s="1"/>
     </row>
-    <row r="134" spans="1:50" ht="25.5">
+    <row r="134" spans="1:60" ht="25.5">
       <c r="A134" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26388,10 +26552,10 @@
       <c r="O134" s="34">
         <v>63</v>
       </c>
-      <c r="P134" s="34"/>
-      <c r="Q134" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P134" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q134" s="34"/>
       <c r="R134" s="34" t="s">
         <v>103</v>
       </c>
@@ -26493,8 +26657,11 @@
       </c>
       <c r="AW134" s="14"/>
       <c r="AX134" s="44"/>
+      <c r="BA134" s="1"/>
+      <c r="BG134"/>
+      <c r="BH134" s="1"/>
     </row>
-    <row r="135" spans="1:50" ht="25.5">
+    <row r="135" spans="1:60" ht="25.5">
       <c r="A135" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26543,10 +26710,10 @@
       <c r="O135" s="34">
         <v>84</v>
       </c>
-      <c r="P135" s="34"/>
-      <c r="Q135" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P135" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q135" s="34"/>
       <c r="R135" s="34" t="s">
         <v>103</v>
       </c>
@@ -26648,8 +26815,11 @@
       </c>
       <c r="AW135" s="14"/>
       <c r="AX135" s="44"/>
+      <c r="BA135" s="1"/>
+      <c r="BG135"/>
+      <c r="BH135" s="1"/>
     </row>
-    <row r="136" spans="1:50" ht="25.5">
+    <row r="136" spans="1:60" ht="25.5">
       <c r="A136" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26698,10 +26868,10 @@
       <c r="O136" s="34">
         <v>94</v>
       </c>
-      <c r="P136" s="34"/>
-      <c r="Q136" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P136" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q136" s="34"/>
       <c r="R136" s="34" t="s">
         <v>103</v>
       </c>
@@ -26803,8 +26973,11 @@
       </c>
       <c r="AW136" s="14"/>
       <c r="AX136" s="44"/>
+      <c r="BA136" s="1"/>
+      <c r="BG136"/>
+      <c r="BH136" s="1"/>
     </row>
-    <row r="137" spans="1:50" ht="25.5">
+    <row r="137" spans="1:60" ht="25.5">
       <c r="A137" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -26853,10 +27026,10 @@
       <c r="O137" s="34">
         <v>62</v>
       </c>
-      <c r="P137" s="34"/>
-      <c r="Q137" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P137" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q137" s="34"/>
       <c r="R137" s="34" t="s">
         <v>103</v>
       </c>
@@ -26958,8 +27131,11 @@
       </c>
       <c r="AW137" s="14"/>
       <c r="AX137" s="44"/>
+      <c r="BA137" s="1"/>
+      <c r="BG137"/>
+      <c r="BH137" s="1"/>
     </row>
-    <row r="138" spans="1:50" ht="38.25">
+    <row r="138" spans="1:60" ht="38.25">
       <c r="A138" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27008,10 +27184,10 @@
       <c r="O138" s="34">
         <v>167</v>
       </c>
-      <c r="P138" s="34"/>
-      <c r="Q138" s="6" t="s">
+      <c r="P138" s="6" t="s">
         <v>1401</v>
       </c>
+      <c r="Q138" s="34"/>
       <c r="R138" s="34" t="s">
         <v>103</v>
       </c>
@@ -27113,8 +27289,11 @@
       </c>
       <c r="AW138" s="14"/>
       <c r="AX138" s="44"/>
+      <c r="BA138" s="1"/>
+      <c r="BG138"/>
+      <c r="BH138" s="1"/>
     </row>
-    <row r="139" spans="1:50" ht="38.25">
+    <row r="139" spans="1:60" ht="38.25">
       <c r="A139" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27163,10 +27342,10 @@
       <c r="O139" s="34">
         <v>124</v>
       </c>
-      <c r="P139" s="34"/>
-      <c r="Q139" s="6" t="s">
+      <c r="P139" s="6" t="s">
         <v>1402</v>
       </c>
+      <c r="Q139" s="34"/>
       <c r="R139" s="34" t="s">
         <v>103</v>
       </c>
@@ -27268,8 +27447,11 @@
       </c>
       <c r="AW139" s="14"/>
       <c r="AX139" s="44"/>
+      <c r="BA139" s="1"/>
+      <c r="BG139"/>
+      <c r="BH139" s="1"/>
     </row>
-    <row r="140" spans="1:50" ht="38.25">
+    <row r="140" spans="1:60" ht="38.25">
       <c r="A140" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27318,10 +27500,10 @@
       <c r="O140" s="34">
         <v>620</v>
       </c>
-      <c r="P140" s="34"/>
-      <c r="Q140" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P140" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q140" s="34"/>
       <c r="R140" s="34" t="s">
         <v>103</v>
       </c>
@@ -27421,8 +27603,11 @@
       </c>
       <c r="AW140" s="14"/>
       <c r="AX140" s="44"/>
+      <c r="BA140" s="1"/>
+      <c r="BG140"/>
+      <c r="BH140" s="1"/>
     </row>
-    <row r="141" spans="1:50" ht="38.25">
+    <row r="141" spans="1:60" ht="38.25">
       <c r="A141" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27471,10 +27656,10 @@
       <c r="O141" s="34">
         <v>620</v>
       </c>
-      <c r="P141" s="34"/>
-      <c r="Q141" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P141" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q141" s="34"/>
       <c r="R141" s="34" t="s">
         <v>103</v>
       </c>
@@ -27574,8 +27759,11 @@
       </c>
       <c r="AW141" s="14"/>
       <c r="AX141" s="44"/>
+      <c r="BA141" s="1"/>
+      <c r="BG141"/>
+      <c r="BH141" s="1"/>
     </row>
-    <row r="142" spans="1:50" ht="38.25">
+    <row r="142" spans="1:60" ht="38.25">
       <c r="A142" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27624,10 +27812,10 @@
       <c r="O142" s="34">
         <v>620</v>
       </c>
-      <c r="P142" s="34"/>
-      <c r="Q142" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P142" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q142" s="34"/>
       <c r="R142" s="34" t="s">
         <v>103</v>
       </c>
@@ -27727,8 +27915,11 @@
       </c>
       <c r="AW142" s="14"/>
       <c r="AX142" s="44"/>
+      <c r="BA142" s="1"/>
+      <c r="BG142"/>
+      <c r="BH142" s="1"/>
     </row>
-    <row r="143" spans="1:50" ht="38.25">
+    <row r="143" spans="1:60" ht="38.25">
       <c r="A143" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27777,10 +27968,10 @@
       <c r="O143" s="34">
         <v>628</v>
       </c>
-      <c r="P143" s="34"/>
-      <c r="Q143" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P143" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q143" s="34"/>
       <c r="R143" s="34" t="s">
         <v>103</v>
       </c>
@@ -27880,8 +28071,11 @@
       </c>
       <c r="AW143" s="14"/>
       <c r="AX143" s="44"/>
+      <c r="BA143" s="1"/>
+      <c r="BG143"/>
+      <c r="BH143" s="1"/>
     </row>
-    <row r="144" spans="1:50" ht="38.25">
+    <row r="144" spans="1:60" ht="38.25">
       <c r="A144" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -27930,10 +28124,10 @@
       <c r="O144" s="34">
         <v>4272</v>
       </c>
-      <c r="P144" s="34"/>
-      <c r="Q144" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P144" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q144" s="34"/>
       <c r="R144" s="34" t="s">
         <v>103</v>
       </c>
@@ -28028,8 +28222,11 @@
       </c>
       <c r="AW144" s="14"/>
       <c r="AX144" s="44"/>
+      <c r="BA144" s="1"/>
+      <c r="BG144"/>
+      <c r="BH144" s="1"/>
     </row>
-    <row r="145" spans="1:50" ht="51">
+    <row r="145" spans="1:60" ht="38.25">
       <c r="A145" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -28078,10 +28275,10 @@
       <c r="O145" s="34">
         <v>285</v>
       </c>
-      <c r="P145" s="34"/>
-      <c r="Q145" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P145" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q145" s="34"/>
       <c r="R145" s="34" t="s">
         <v>103</v>
       </c>
@@ -28183,8 +28380,11 @@
       </c>
       <c r="AW145" s="14"/>
       <c r="AX145" s="44"/>
+      <c r="BA145" s="1"/>
+      <c r="BG145"/>
+      <c r="BH145" s="1"/>
     </row>
-    <row r="146" spans="1:50" ht="38.25">
+    <row r="146" spans="1:60" ht="38.25">
       <c r="A146" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Pays de la Loire</v>
@@ -28233,10 +28433,10 @@
       <c r="O146" s="34">
         <v>224</v>
       </c>
-      <c r="P146" s="34"/>
-      <c r="Q146" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P146" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q146" s="34"/>
       <c r="R146" s="34" t="s">
         <v>103</v>
       </c>
@@ -28338,8 +28538,11 @@
       </c>
       <c r="AW146" s="14"/>
       <c r="AX146" s="44"/>
+      <c r="BA146" s="1"/>
+      <c r="BG146"/>
+      <c r="BH146" s="1"/>
     </row>
-    <row r="147" spans="1:50" ht="25.5">
+    <row r="147" spans="1:60" ht="25.5">
       <c r="A147" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -28388,10 +28591,10 @@
       <c r="O147" s="34">
         <v>287</v>
       </c>
-      <c r="P147" s="34"/>
-      <c r="Q147" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P147" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q147" s="34"/>
       <c r="R147" s="34" t="s">
         <v>103</v>
       </c>
@@ -28476,8 +28679,11 @@
       </c>
       <c r="AW147" s="14"/>
       <c r="AX147" s="44"/>
+      <c r="BA147" s="1"/>
+      <c r="BG147"/>
+      <c r="BH147" s="1"/>
     </row>
-    <row r="148" spans="1:50" ht="38.25">
+    <row r="148" spans="1:60" ht="38.25">
       <c r="A148" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28526,10 +28732,10 @@
       <c r="O148" s="34">
         <v>73</v>
       </c>
-      <c r="P148" s="34"/>
-      <c r="Q148" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P148" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q148" s="34"/>
       <c r="R148" s="34" t="s">
         <v>103</v>
       </c>
@@ -28631,8 +28837,11 @@
       <c r="AX148" s="44">
         <v>45999</v>
       </c>
+      <c r="BA148" s="1"/>
+      <c r="BG148"/>
+      <c r="BH148" s="1"/>
     </row>
-    <row r="149" spans="1:50" ht="38.25">
+    <row r="149" spans="1:60" ht="38.25">
       <c r="A149" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28682,10 +28891,10 @@
       <c r="O149" s="34">
         <v>200</v>
       </c>
-      <c r="P149" s="34"/>
-      <c r="Q149" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P149" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q149" s="34"/>
       <c r="R149" s="34" t="s">
         <v>103</v>
       </c>
@@ -28789,8 +28998,11 @@
       <c r="AX149" s="44">
         <v>45999</v>
       </c>
+      <c r="BA149" s="1"/>
+      <c r="BG149"/>
+      <c r="BH149" s="1"/>
     </row>
-    <row r="150" spans="1:50" ht="38.25">
+    <row r="150" spans="1:60" ht="38.25">
       <c r="A150" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28840,10 +29052,10 @@
       <c r="O150" s="34">
         <v>500</v>
       </c>
-      <c r="P150" s="34"/>
-      <c r="Q150" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P150" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q150" s="34"/>
       <c r="R150" s="34" t="s">
         <v>103</v>
       </c>
@@ -28947,8 +29159,11 @@
       <c r="AX150" s="44">
         <v>45999</v>
       </c>
+      <c r="BA150" s="1"/>
+      <c r="BG150"/>
+      <c r="BH150" s="1"/>
     </row>
-    <row r="151" spans="1:50" ht="38.25">
+    <row r="151" spans="1:60" ht="38.25">
       <c r="A151" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -28998,10 +29213,10 @@
       <c r="O151" s="34">
         <v>1000</v>
       </c>
-      <c r="P151" s="34"/>
-      <c r="Q151" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P151" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q151" s="34"/>
       <c r="R151" s="34" t="s">
         <v>103</v>
       </c>
@@ -29105,8 +29320,11 @@
       <c r="AX151" s="44">
         <v>45999</v>
       </c>
+      <c r="BA151" s="1"/>
+      <c r="BG151"/>
+      <c r="BH151" s="1"/>
     </row>
-    <row r="152" spans="1:50" ht="38.25">
+    <row r="152" spans="1:60" ht="38.25">
       <c r="A152" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -29156,10 +29374,10 @@
       <c r="O152" s="34">
         <v>2000</v>
       </c>
-      <c r="P152" s="34"/>
-      <c r="Q152" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P152" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q152" s="34"/>
       <c r="R152" s="34" t="s">
         <v>103</v>
       </c>
@@ -29263,8 +29481,11 @@
       <c r="AX152" s="44">
         <v>45999</v>
       </c>
+      <c r="BA152" s="1"/>
+      <c r="BG152"/>
+      <c r="BH152" s="1"/>
     </row>
-    <row r="153" spans="1:50" ht="38.25">
+    <row r="153" spans="1:60" ht="38.25">
       <c r="A153" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -29314,10 +29535,10 @@
       <c r="O153" s="34">
         <v>5000</v>
       </c>
-      <c r="P153" s="34"/>
-      <c r="Q153" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P153" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q153" s="34"/>
       <c r="R153" s="34" t="s">
         <v>103</v>
       </c>
@@ -29421,8 +29642,11 @@
       <c r="AX153" s="44">
         <v>45999</v>
       </c>
+      <c r="BA153" s="1"/>
+      <c r="BG153"/>
+      <c r="BH153" s="1"/>
     </row>
-    <row r="154" spans="1:50" ht="38.25">
+    <row r="154" spans="1:60" ht="25.5">
       <c r="A154" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29473,10 +29697,10 @@
       <c r="O154" s="34">
         <v>181</v>
       </c>
-      <c r="P154" s="34"/>
-      <c r="Q154" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P154" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q154" s="34"/>
       <c r="R154" s="34" t="s">
         <v>103</v>
       </c>
@@ -29582,8 +29806,11 @@
       <c r="AX154" s="44">
         <v>46003</v>
       </c>
+      <c r="BA154" s="1"/>
+      <c r="BG154"/>
+      <c r="BH154" s="1"/>
     </row>
-    <row r="155" spans="1:50" ht="51" hidden="1">
+    <row r="155" spans="1:60" ht="165.75" hidden="1">
       <c r="A155" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29632,10 +29859,10 @@
       <c r="O155" s="34">
         <v>100</v>
       </c>
-      <c r="P155" s="34"/>
-      <c r="Q155" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P155" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q155" s="34"/>
       <c r="R155" s="34" t="s">
         <v>103</v>
       </c>
@@ -29739,8 +29966,11 @@
       <c r="AX155" s="44">
         <v>46004</v>
       </c>
+      <c r="BA155" s="1"/>
+      <c r="BG155"/>
+      <c r="BH155" s="1"/>
     </row>
-    <row r="156" spans="1:50" ht="38.25" hidden="1">
+    <row r="156" spans="1:60" ht="140.25" hidden="1">
       <c r="A156" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29789,10 +30019,10 @@
       <c r="O156" s="34">
         <v>446</v>
       </c>
-      <c r="P156" s="34"/>
-      <c r="Q156" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P156" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q156" s="34"/>
       <c r="R156" s="34" t="s">
         <v>103</v>
       </c>
@@ -29896,8 +30126,11 @@
       <c r="AX156" s="44">
         <v>46005</v>
       </c>
+      <c r="BA156" s="1"/>
+      <c r="BG156"/>
+      <c r="BH156" s="1"/>
     </row>
-    <row r="157" spans="1:50" ht="38.25" hidden="1">
+    <row r="157" spans="1:60" ht="140.25" hidden="1">
       <c r="A157" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -29946,10 +30179,10 @@
       <c r="O157" s="34">
         <v>567</v>
       </c>
-      <c r="P157" s="34"/>
-      <c r="Q157" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P157" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q157" s="34"/>
       <c r="R157" s="34" t="s">
         <v>103</v>
       </c>
@@ -30053,8 +30286,11 @@
       <c r="AX157" s="44">
         <v>46006</v>
       </c>
+      <c r="BA157" s="1"/>
+      <c r="BG157"/>
+      <c r="BH157" s="1"/>
     </row>
-    <row r="158" spans="1:50" ht="38.25">
+    <row r="158" spans="1:60" ht="38.25">
       <c r="A158" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -30103,10 +30339,10 @@
       <c r="O158" s="34">
         <v>1390</v>
       </c>
-      <c r="P158" s="34"/>
-      <c r="Q158" s="6" t="s">
+      <c r="P158" s="6" t="s">
         <v>1219</v>
       </c>
+      <c r="Q158" s="34"/>
       <c r="R158" s="34" t="s">
         <v>103</v>
       </c>
@@ -30213,8 +30449,11 @@
       <c r="AX158" s="44">
         <v>46003</v>
       </c>
+      <c r="BA158" s="1"/>
+      <c r="BG158"/>
+      <c r="BH158" s="1"/>
     </row>
-    <row r="159" spans="1:50" ht="25.5">
+    <row r="159" spans="1:60" ht="25.5">
       <c r="A159" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -30263,10 +30502,10 @@
       <c r="O159" s="34">
         <v>1000</v>
       </c>
-      <c r="P159" s="34"/>
-      <c r="Q159" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P159" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q159" s="34"/>
       <c r="R159" s="34" t="s">
         <v>103</v>
       </c>
@@ -30372,8 +30611,11 @@
       <c r="AX159" s="44">
         <v>46003</v>
       </c>
+      <c r="BA159" s="1"/>
+      <c r="BG159"/>
+      <c r="BH159" s="1"/>
     </row>
-    <row r="160" spans="1:50" ht="38.25">
+    <row r="160" spans="1:60" ht="38.25">
       <c r="A160" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Centre-Val de Loire</v>
@@ -30420,10 +30662,10 @@
       <c r="O160" s="34">
         <v>5000</v>
       </c>
-      <c r="P160" s="34"/>
-      <c r="Q160" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P160" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q160" s="34"/>
       <c r="R160" s="34" t="s">
         <v>103</v>
       </c>
@@ -30521,8 +30763,11 @@
       <c r="AX160" s="44">
         <v>46003</v>
       </c>
+      <c r="BA160" s="1"/>
+      <c r="BG160"/>
+      <c r="BH160" s="1"/>
     </row>
-    <row r="161" spans="1:50" ht="38.25">
+    <row r="161" spans="1:60" ht="25.5">
       <c r="A161" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -30571,10 +30816,10 @@
       <c r="O161" s="34">
         <v>550</v>
       </c>
-      <c r="P161" s="34"/>
-      <c r="Q161" s="6" t="s">
+      <c r="P161" s="6" t="s">
         <v>1223</v>
       </c>
+      <c r="Q161" s="34"/>
       <c r="R161" s="34" t="s">
         <v>103</v>
       </c>
@@ -30680,8 +30925,11 @@
       <c r="AX161" s="44">
         <v>46003</v>
       </c>
+      <c r="BA161" s="1"/>
+      <c r="BG161"/>
+      <c r="BH161" s="1"/>
     </row>
-    <row r="162" spans="1:50" ht="38.25">
+    <row r="162" spans="1:60" ht="25.5">
       <c r="A162" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30730,10 +30978,10 @@
       <c r="O162" s="34">
         <v>480</v>
       </c>
-      <c r="P162" s="34"/>
-      <c r="Q162" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P162" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q162" s="34"/>
       <c r="R162" s="34" t="s">
         <v>103</v>
       </c>
@@ -30839,8 +31087,11 @@
       <c r="AX162" s="44">
         <v>46003</v>
       </c>
+      <c r="BA162" s="1"/>
+      <c r="BG162"/>
+      <c r="BH162" s="1"/>
     </row>
-    <row r="163" spans="1:50" ht="25.5">
+    <row r="163" spans="1:60" ht="25.5">
       <c r="A163" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -30889,10 +31140,10 @@
       <c r="O163" s="34">
         <v>200</v>
       </c>
-      <c r="P163" s="34"/>
-      <c r="Q163" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P163" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q163" s="34"/>
       <c r="R163" s="34" t="s">
         <v>103</v>
       </c>
@@ -30996,8 +31247,11 @@
       </c>
       <c r="AW163" s="14"/>
       <c r="AX163" s="44"/>
+      <c r="BA163" s="1"/>
+      <c r="BG163"/>
+      <c r="BH163" s="1"/>
     </row>
-    <row r="164" spans="1:50" ht="25.5">
+    <row r="164" spans="1:60" ht="25.5">
       <c r="A164" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -31046,10 +31300,10 @@
       <c r="O164" s="34">
         <v>90</v>
       </c>
-      <c r="P164" s="34"/>
-      <c r="Q164" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P164" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q164" s="34"/>
       <c r="R164" s="34" t="s">
         <v>103</v>
       </c>
@@ -31153,8 +31407,11 @@
       </c>
       <c r="AW164" s="14"/>
       <c r="AX164" s="44"/>
+      <c r="BA164" s="1"/>
+      <c r="BG164"/>
+      <c r="BH164" s="1"/>
     </row>
-    <row r="165" spans="1:50" ht="25.5">
+    <row r="165" spans="1:60" ht="25.5">
       <c r="A165" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -31203,10 +31460,10 @@
       <c r="O165" s="34">
         <v>78</v>
       </c>
-      <c r="P165" s="34"/>
-      <c r="Q165" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P165" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q165" s="34"/>
       <c r="R165" s="34" t="s">
         <v>103</v>
       </c>
@@ -31310,8 +31567,11 @@
       </c>
       <c r="AW165" s="14"/>
       <c r="AX165" s="44"/>
+      <c r="BA165" s="1"/>
+      <c r="BG165"/>
+      <c r="BH165" s="1"/>
     </row>
-    <row r="166" spans="1:50" ht="25.5">
+    <row r="166" spans="1:60" ht="25.5">
       <c r="A166" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -31360,10 +31620,10 @@
       <c r="O166" s="34">
         <v>70</v>
       </c>
-      <c r="P166" s="34"/>
-      <c r="Q166" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P166" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q166" s="34"/>
       <c r="R166" s="34" t="s">
         <v>103</v>
       </c>
@@ -31467,8 +31727,11 @@
       </c>
       <c r="AW166" s="14"/>
       <c r="AX166" s="44"/>
+      <c r="BA166" s="1"/>
+      <c r="BG166"/>
+      <c r="BH166" s="1"/>
     </row>
-    <row r="167" spans="1:50" ht="25.5">
+    <row r="167" spans="1:60" ht="25.5">
       <c r="A167" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -31515,10 +31778,10 @@
       <c r="O167" s="34">
         <v>20</v>
       </c>
-      <c r="P167" s="34"/>
-      <c r="Q167" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P167" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q167" s="34"/>
       <c r="R167" s="34" t="s">
         <v>103</v>
       </c>
@@ -31622,8 +31885,11 @@
       </c>
       <c r="AW167" s="14"/>
       <c r="AX167" s="44"/>
+      <c r="BA167" s="1"/>
+      <c r="BG167"/>
+      <c r="BH167" s="1"/>
     </row>
-    <row r="168" spans="1:50" ht="38.25">
+    <row r="168" spans="1:60" ht="25.5">
       <c r="A168" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -31672,10 +31938,10 @@
       <c r="O168" s="34">
         <v>750</v>
       </c>
-      <c r="P168" s="34"/>
-      <c r="Q168" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P168" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q168" s="34"/>
       <c r="R168" s="34" t="s">
         <v>103</v>
       </c>
@@ -31781,8 +32047,11 @@
       <c r="AX168" s="44">
         <v>46003</v>
       </c>
+      <c r="BA168" s="1"/>
+      <c r="BG168"/>
+      <c r="BH168" s="1"/>
     </row>
-    <row r="169" spans="1:50" ht="25.5">
+    <row r="169" spans="1:60" ht="25.5">
       <c r="A169" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -31831,10 +32100,10 @@
       <c r="O169" s="34">
         <v>930</v>
       </c>
-      <c r="P169" s="34"/>
-      <c r="Q169" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P169" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q169" s="34"/>
       <c r="R169" s="34" t="s">
         <v>103</v>
       </c>
@@ -31940,8 +32209,11 @@
       <c r="AX169" s="44">
         <v>46003</v>
       </c>
+      <c r="BA169" s="1"/>
+      <c r="BG169"/>
+      <c r="BH169" s="1"/>
     </row>
-    <row r="170" spans="1:50" ht="25.5">
+    <row r="170" spans="1:60" ht="25.5">
       <c r="A170" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -31990,10 +32262,10 @@
       <c r="O170" s="34">
         <v>760</v>
       </c>
-      <c r="P170" s="34"/>
-      <c r="Q170" s="6" t="s">
+      <c r="P170" s="6" t="s">
         <v>1230</v>
       </c>
+      <c r="Q170" s="34"/>
       <c r="R170" s="34" t="s">
         <v>103</v>
       </c>
@@ -32099,8 +32371,11 @@
       <c r="AX170" s="44">
         <v>46003</v>
       </c>
+      <c r="BA170" s="1"/>
+      <c r="BG170"/>
+      <c r="BH170" s="1"/>
     </row>
-    <row r="171" spans="1:50" ht="38.25">
+    <row r="171" spans="1:60" ht="38.25">
       <c r="A171" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -32147,10 +32422,10 @@
       <c r="O171" s="34">
         <v>276</v>
       </c>
-      <c r="P171" s="34"/>
-      <c r="Q171" s="6" t="s">
+      <c r="P171" s="6" t="s">
         <v>1232</v>
       </c>
+      <c r="Q171" s="34"/>
       <c r="R171" s="34" t="s">
         <v>103</v>
       </c>
@@ -32257,8 +32532,11 @@
       <c r="AX171" s="44">
         <v>46003</v>
       </c>
+      <c r="BA171" s="1"/>
+      <c r="BG171"/>
+      <c r="BH171" s="1"/>
     </row>
-    <row r="172" spans="1:50" ht="25.5">
+    <row r="172" spans="1:60" ht="25.5">
       <c r="A172" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -32307,10 +32585,10 @@
       <c r="O172" s="34">
         <v>470</v>
       </c>
-      <c r="P172" s="34"/>
-      <c r="Q172" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P172" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q172" s="34"/>
       <c r="R172" s="34" t="s">
         <v>103</v>
       </c>
@@ -32417,8 +32695,11 @@
       <c r="AX172" s="44">
         <v>46003</v>
       </c>
+      <c r="BA172" s="1"/>
+      <c r="BG172"/>
+      <c r="BH172" s="1"/>
     </row>
-    <row r="173" spans="1:50" ht="51">
+    <row r="173" spans="1:60" ht="38.25">
       <c r="A173" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -32467,10 +32748,10 @@
       <c r="O173" s="34">
         <v>616</v>
       </c>
-      <c r="P173" s="34"/>
-      <c r="Q173" s="6" t="s">
+      <c r="P173" s="6" t="s">
         <v>1237</v>
       </c>
+      <c r="Q173" s="34"/>
       <c r="R173" s="34" t="s">
         <v>103</v>
       </c>
@@ -32577,8 +32858,11 @@
       <c r="AX173" s="44">
         <v>46003</v>
       </c>
+      <c r="BA173" s="1"/>
+      <c r="BG173"/>
+      <c r="BH173" s="1"/>
     </row>
-    <row r="174" spans="1:50" ht="38.25">
+    <row r="174" spans="1:60" ht="25.5">
       <c r="A174" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32627,10 +32911,10 @@
       <c r="O174" s="34">
         <v>875</v>
       </c>
-      <c r="P174" s="34"/>
-      <c r="Q174" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P174" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q174" s="34"/>
       <c r="R174" s="34" t="s">
         <v>103</v>
       </c>
@@ -32737,8 +33021,11 @@
       <c r="AX174" s="44">
         <v>46003</v>
       </c>
+      <c r="BA174" s="1"/>
+      <c r="BG174"/>
+      <c r="BH174" s="1"/>
     </row>
-    <row r="175" spans="1:50" ht="38.25">
+    <row r="175" spans="1:60" ht="25.5">
       <c r="A175" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32787,10 +33074,10 @@
       <c r="O175" s="34">
         <v>387</v>
       </c>
-      <c r="P175" s="34"/>
-      <c r="Q175" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P175" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q175" s="34"/>
       <c r="R175" s="34" t="s">
         <v>103</v>
       </c>
@@ -32897,8 +33184,11 @@
       <c r="AX175" s="44">
         <v>46003</v>
       </c>
+      <c r="BA175" s="1"/>
+      <c r="BG175"/>
+      <c r="BH175" s="1"/>
     </row>
-    <row r="176" spans="1:50" ht="38.25">
+    <row r="176" spans="1:60" ht="25.5">
       <c r="A176" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -32947,10 +33237,10 @@
       <c r="O176" s="34">
         <v>723</v>
       </c>
-      <c r="P176" s="34"/>
-      <c r="Q176" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P176" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q176" s="34"/>
       <c r="R176" s="34" t="s">
         <v>103</v>
       </c>
@@ -33057,8 +33347,11 @@
       <c r="AX176" s="44">
         <v>46003</v>
       </c>
+      <c r="BA176" s="1"/>
+      <c r="BG176"/>
+      <c r="BH176" s="1"/>
     </row>
-    <row r="177" spans="1:50" ht="25.5">
+    <row r="177" spans="1:60" ht="25.5">
       <c r="A177" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33107,10 +33400,10 @@
       <c r="O177" s="34">
         <v>402</v>
       </c>
-      <c r="P177" s="34"/>
-      <c r="Q177" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="P177" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q177" s="34"/>
       <c r="R177" s="34" t="s">
         <v>103</v>
       </c>
@@ -33217,8 +33510,11 @@
       <c r="AX177" s="44">
         <v>46003</v>
       </c>
+      <c r="BA177" s="1"/>
+      <c r="BG177"/>
+      <c r="BH177" s="1"/>
     </row>
-    <row r="178" spans="1:50" ht="38.25">
+    <row r="178" spans="1:60" ht="38.25">
       <c r="A178" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -33266,10 +33562,10 @@
       <c r="O178" s="34">
         <v>126</v>
       </c>
-      <c r="P178" s="34"/>
-      <c r="Q178" s="6" t="s">
+      <c r="P178" s="6" t="s">
         <v>1246</v>
       </c>
+      <c r="Q178" s="34"/>
       <c r="R178" s="34" t="s">
         <v>103</v>
       </c>
@@ -33371,8 +33667,11 @@
       <c r="AX178" s="44">
         <v>46010</v>
       </c>
+      <c r="BA178" s="1"/>
+      <c r="BG178"/>
+      <c r="BH178" s="1"/>
     </row>
-    <row r="179" spans="1:50" ht="25.5">
+    <row r="179" spans="1:60" ht="25.5">
       <c r="A179" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33419,10 +33718,10 @@
       <c r="O179" s="34">
         <v>530</v>
       </c>
-      <c r="P179" s="34"/>
-      <c r="Q179" s="12" t="s">
+      <c r="P179" s="12" t="s">
         <v>1309</v>
       </c>
+      <c r="Q179" s="34"/>
       <c r="R179" s="34" t="s">
         <v>103</v>
       </c>
@@ -33522,8 +33821,11 @@
       <c r="AX179" s="44">
         <v>46042</v>
       </c>
+      <c r="BA179" s="1"/>
+      <c r="BG179"/>
+      <c r="BH179" s="1"/>
     </row>
-    <row r="180" spans="1:50" ht="25.5">
+    <row r="180" spans="1:60" ht="25.5">
       <c r="A180" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33570,10 +33872,10 @@
       <c r="O180" s="34">
         <v>187</v>
       </c>
-      <c r="P180" s="34"/>
-      <c r="Q180" s="12" t="s">
+      <c r="P180" s="12" t="s">
         <v>1318</v>
       </c>
+      <c r="Q180" s="34"/>
       <c r="R180" s="34" t="s">
         <v>103</v>
       </c>
@@ -33673,8 +33975,11 @@
       <c r="AX180" s="44">
         <v>46042</v>
       </c>
+      <c r="BA180" s="1"/>
+      <c r="BG180"/>
+      <c r="BH180" s="1"/>
     </row>
-    <row r="181" spans="1:50" ht="25.5">
+    <row r="181" spans="1:60" ht="25.5">
       <c r="A181" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33721,10 +34026,10 @@
       <c r="O181" s="34">
         <v>59</v>
       </c>
-      <c r="P181" s="34"/>
-      <c r="Q181" s="12" t="s">
+      <c r="P181" s="12" t="s">
         <v>1325</v>
       </c>
+      <c r="Q181" s="34"/>
       <c r="R181" s="34" t="s">
         <v>103</v>
       </c>
@@ -33822,8 +34127,11 @@
       <c r="AX181" s="44">
         <v>46042</v>
       </c>
+      <c r="BA181" s="1"/>
+      <c r="BG181"/>
+      <c r="BH181" s="1"/>
     </row>
-    <row r="182" spans="1:50" ht="25.5">
+    <row r="182" spans="1:60" ht="25.5">
       <c r="A182" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -33870,10 +34178,10 @@
       <c r="O182" s="34">
         <v>39</v>
       </c>
-      <c r="P182" s="34"/>
-      <c r="Q182" s="34" t="s">
-        <v>103</v>
-      </c>
+      <c r="P182" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q182" s="34"/>
       <c r="R182" s="34" t="s">
         <v>103</v>
       </c>
@@ -33969,8 +34277,11 @@
       <c r="AX182" s="44">
         <v>46042</v>
       </c>
+      <c r="BA182" s="1"/>
+      <c r="BG182"/>
+      <c r="BH182" s="1"/>
     </row>
-    <row r="183" spans="1:50" ht="25.5">
+    <row r="183" spans="1:60" ht="25.5">
       <c r="A183" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -34017,10 +34328,10 @@
       <c r="O183" s="34">
         <v>93</v>
       </c>
-      <c r="P183" s="34"/>
-      <c r="Q183" s="34" t="s">
-        <v>103</v>
-      </c>
+      <c r="P183" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q183" s="34"/>
       <c r="R183" s="34" t="s">
         <v>103</v>
       </c>
@@ -34118,8 +34429,11 @@
       <c r="AX183" s="44">
         <v>46042</v>
       </c>
+      <c r="BA183" s="1"/>
+      <c r="BG183"/>
+      <c r="BH183" s="1"/>
     </row>
-    <row r="184" spans="1:50" ht="25.5">
+    <row r="184" spans="1:60" ht="25.5">
       <c r="A184" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -34166,10 +34480,10 @@
       <c r="O184" s="34">
         <v>141</v>
       </c>
-      <c r="P184" s="34"/>
-      <c r="Q184" s="12" t="s">
+      <c r="P184" s="12" t="s">
         <v>1348</v>
       </c>
+      <c r="Q184" s="34"/>
       <c r="R184" s="34" t="s">
         <v>103</v>
       </c>
@@ -34269,8 +34583,11 @@
       <c r="AX184" s="44">
         <v>46042</v>
       </c>
+      <c r="BA184" s="1"/>
+      <c r="BG184"/>
+      <c r="BH184" s="1"/>
     </row>
-    <row r="185" spans="1:50" ht="25.5">
+    <row r="185" spans="1:60" ht="25.5">
       <c r="A185" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Hauts-de-France</v>
@@ -34317,10 +34634,10 @@
       <c r="O185" s="34">
         <v>86</v>
       </c>
-      <c r="P185" s="34"/>
-      <c r="Q185" s="12" t="s">
+      <c r="P185" s="12" t="s">
         <v>1347</v>
       </c>
+      <c r="Q185" s="34"/>
       <c r="R185" s="34" t="s">
         <v>103</v>
       </c>
@@ -34420,8 +34737,11 @@
       <c r="AX185" s="44">
         <v>46042</v>
       </c>
+      <c r="BA185" s="1"/>
+      <c r="BG185"/>
+      <c r="BH185" s="1"/>
     </row>
-    <row r="186" spans="1:50" ht="25.5">
+    <row r="186" spans="1:60" ht="25.5">
       <c r="A186" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -34468,10 +34788,10 @@
       <c r="O186" s="34">
         <v>335</v>
       </c>
-      <c r="P186" s="34"/>
-      <c r="Q186" s="12" t="s">
+      <c r="P186" s="12" t="s">
         <v>1355</v>
       </c>
+      <c r="Q186" s="34"/>
       <c r="R186" s="34" t="s">
         <v>103</v>
       </c>
@@ -34571,8 +34891,11 @@
       <c r="AX186" s="44">
         <v>46042</v>
       </c>
+      <c r="BA186" s="1"/>
+      <c r="BG186"/>
+      <c r="BH186" s="1"/>
     </row>
-    <row r="187" spans="1:50" ht="25.5">
+    <row r="187" spans="1:60" ht="25.5">
       <c r="A187" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -34619,10 +34942,10 @@
       <c r="O187" s="34">
         <v>378</v>
       </c>
-      <c r="P187" s="34"/>
-      <c r="Q187" s="12" t="s">
+      <c r="P187" s="12" t="s">
         <v>1366</v>
       </c>
+      <c r="Q187" s="34"/>
       <c r="R187" s="34" t="s">
         <v>103</v>
       </c>
@@ -34722,8 +35045,11 @@
       <c r="AX187" s="44">
         <v>46042</v>
       </c>
+      <c r="BA187" s="1"/>
+      <c r="BG187"/>
+      <c r="BH187" s="1"/>
     </row>
-    <row r="188" spans="1:50" ht="25.5">
+    <row r="188" spans="1:60" ht="25.5">
       <c r="A188" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Ile-de-France</v>
@@ -34770,10 +35096,10 @@
       <c r="O188" s="34">
         <v>48</v>
       </c>
-      <c r="P188" s="34"/>
-      <c r="Q188" s="12" t="s">
+      <c r="P188" s="12" t="s">
         <v>1372</v>
       </c>
+      <c r="Q188" s="34"/>
       <c r="R188" s="34" t="s">
         <v>103</v>
       </c>
@@ -34873,8 +35199,11 @@
       <c r="AX188" s="44">
         <v>46042</v>
       </c>
+      <c r="BA188" s="1"/>
+      <c r="BG188"/>
+      <c r="BH188" s="1"/>
     </row>
-    <row r="189" spans="1:50" ht="38.25">
+    <row r="189" spans="1:60" ht="38.25">
       <c r="A189" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Auvergne-Rhône-Alpes</v>
@@ -34921,10 +35250,10 @@
       <c r="O189" s="34">
         <v>196</v>
       </c>
-      <c r="P189" s="34"/>
-      <c r="Q189" s="34" t="s">
-        <v>103</v>
-      </c>
+      <c r="P189" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q189" s="34"/>
       <c r="R189" s="34" t="s">
         <v>103</v>
       </c>
@@ -35024,6 +35353,9 @@
       <c r="AX189" s="44">
         <v>46042</v>
       </c>
+      <c r="BA189" s="1"/>
+      <c r="BG189"/>
+      <c r="BH189" s="1"/>
     </row>
     <row r="204" spans="6:6">
       <c r="F204" s="1" t="s">

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF14FAC9-06F5-42CE-AC32-A41287563E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EF4A99-C005-42E2-A1BA-892473E4438F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5563" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5767" uniqueCount="1451">
   <si>
     <t>Contact</t>
   </si>
@@ -2100,30 +2100,6 @@
   </si>
   <si>
     <t>Boulangerie, Franprix</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 10</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 11</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 12</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 13</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 14</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 15</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 16</t>
-  </si>
-  <si>
-    <t>Quartier réaménagé. Les 1,2,3 sont fusionnables, ainsi que 4, 5, 6 et 17</t>
   </si>
   <si>
     <t>48.822274</t>
@@ -3633,9 +3609,6 @@
     <t>221 €/m² = 40 000 €</t>
   </si>
   <si>
-    <t>Restaurant en pied d'un batiment autonome dans une zone d'activité et d'entreprises (22 000 emplois). Proximité de l'A7 et de l'aéroport de Marseille. Baill 6/9/10 ans</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
@@ -3702,9 +3675,6 @@
     <t>700 + 690</t>
   </si>
   <si>
-    <t>Local dans l'une des principales zones commerciales de France (+40M de flux annuel). Environ une cinquantaine de places de parking. Bail 6/9/10 ans. Frais de rédaction d'acte 2 000 €HT</t>
-  </si>
-  <si>
     <t>90 €/m² = 90 000 €</t>
   </si>
   <si>
@@ -3714,9 +3684,6 @@
     <t>100 (SS) + 155 + 295</t>
   </si>
   <si>
-    <t>Ancien Five Guys. Emplacement exceptionnel en angle et en cœur de ville de Nancy avec 70 m² de terrasse. 16M de flux annuel. Bail 6/9/10 ans</t>
-  </si>
-  <si>
     <t>5001 Rue des Fusillés de 1940</t>
   </si>
   <si>
@@ -3744,18 +3711,12 @@
     <t>298 €/m² = 140 000 €</t>
   </si>
   <si>
-    <t>Ancien Casa dans une zone commerciale forte à proximité d'Avenue 83 et Toulon Grand Var. Frais de rédaction : 2 000 € HT. Bail 6/9/10 ans.</t>
-  </si>
-  <si>
     <t>145 €/m² = 90 000 €</t>
   </si>
   <si>
     <t>420 + 196</t>
   </si>
   <si>
-    <t>Ancien Point B (burger) dans une zone commercial à proximité du centre Auchan Mistral 7 au sud d'Avignon. 15M de flux annuel. Avec mezzanine et terrasse. Frais de rédaction d'acte : 2 000 € HT. Bail 6/9/10 ans.</t>
-  </si>
-  <si>
     <t>180 €/m² = 70 000 €</t>
   </si>
   <si>
@@ -3771,12 +3732,6 @@
     <t>375 €/m² = 150 000 €</t>
   </si>
   <si>
-    <t>Zone commerciale à côté du Leclerc de Champigny. Proximité directe avec les habitations. Frais de rédaction d'acte : 2 500 € HT. Bail 6/9/10 ans.</t>
-  </si>
-  <si>
-    <t>Local situé dans la Patte d'Oie d'Herblay. 60M de flux annuel. Frais de rédaction d'acte : 2 500 € HT. Bail 6/9/10 ans.</t>
-  </si>
-  <si>
     <t>74 + 52 (mezz)</t>
   </si>
   <si>
@@ -3916,9 +3871,6 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/jjHUN2H4tKUGyBEQ7</t>
-  </si>
-  <si>
-    <t>Sous CS de libération du local. Boulangerie dans une zone commerciale forte à proximité d'avenue 83 et Toulon Grand Var. Frais de rédaction : 2 000 € HT. Terrasse de 100 m². Bail 9/10 ans.</t>
   </si>
   <si>
     <t xml:space="preserve">Nocibé, Léonidas, Okaïdi, Krys, KFC,… </t>
@@ -4340,6 +4292,115 @@
   </si>
   <si>
     <t>Ancien Cuisine Plus à proximité du Carrefour Wittenheim.</t>
+  </si>
+  <si>
+    <t>120 €/m²</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/aBGTEuZJUKzAi2NE7</t>
+  </si>
+  <si>
+    <t>Rivières</t>
+  </si>
+  <si>
+    <t>McDonald’s, Action, Zeeman, E.Leclerc</t>
+  </si>
+  <si>
+    <t>Terrain à construire dans un bon environnement commercial</t>
+  </si>
+  <si>
+    <t>1 500 € HT</t>
+  </si>
+  <si>
+    <t>45.751593</t>
+  </si>
+  <si>
+    <t>0.383593</t>
+  </si>
+  <si>
+    <t>62.2</t>
+  </si>
+  <si>
+    <t>110 €/m² = 77 000 €</t>
+  </si>
+  <si>
+    <t>Sogenial</t>
+  </si>
+  <si>
+    <t>Boréal Parc
+rue de Bleuets</t>
+  </si>
+  <si>
+    <t>Beaurains</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LrXvSy35NAUmoadS8</t>
+  </si>
+  <si>
+    <t>Local disposant de 3 gaines d'extraction : 2 x 100 mm et 1 x 200 mm. Possibilité de terrasse extérieur</t>
+  </si>
+  <si>
+    <t>62.1</t>
+  </si>
+  <si>
+    <t>2.797706</t>
+  </si>
+  <si>
+    <t>50.262432</t>
+  </si>
+  <si>
+    <t>50.262627</t>
+  </si>
+  <si>
+    <t>2.798029</t>
+  </si>
+  <si>
+    <t>218 €/m² = 28 000 € HT</t>
+  </si>
+  <si>
+    <t>Carrefour Market, Chaussea, Zeeman, Cerntrakor, Gamm vert, restaurants</t>
+  </si>
+  <si>
+    <t>Local traversant en face caisse</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/61%20-%20Rivi%C3%A8res/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/61%20-%20Rivi%C3%A8res/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/61%20-%20Rivi%C3%A8res/3%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/61%20-%20Rivi%C3%A8res/3%20Plan.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/62.1%20-%20Beaurains/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/62.1%20-%20Beaurains/3%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/62.2%20-%20Beaurains/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/62.2%20-%20Beaurains/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/62.2%20-%20Beaurains/3.jpg</t>
+  </si>
+  <si>
+    <t>Quartier réaménagé. 2 200 logements privés à proximité.</t>
+  </si>
+  <si>
+    <t>Restaurant en pied d'un batiment autonome dans une zone d'activité et d'entreprises (22 000 emplois). Proximité de l'A7 et de l'aéroport de Marseille.</t>
+  </si>
+  <si>
+    <t>Local dans l'une des principales zones commerciales de France (+40M de flux annuel). Environ une cinquantaine de places de parking.</t>
+  </si>
+  <si>
+    <t>Ancien Five Guys. Emplacement exceptionnel en angle et en cœur de ville de Nancy avec 70 m² de terrasse. 16M de flux annuel.</t>
+  </si>
+  <si>
+    <t>Sous CS de libération du local. Boulangerie dans une zone commerciale forte à proximité d'avenue 83 et Toulon Grand Var. Terrasse de 100 m².</t>
+  </si>
+  <si>
+    <t>9/10 ans</t>
+  </si>
+  <si>
+    <t>Ancien Casa dans une zone commerciale forte à proximité d'Avenue 83 et Toulon Grand Var.</t>
+  </si>
+  <si>
+    <t>Ancien Point B (burger) dans une zone commercial à proximité du centre Auchan Mistral 7 au sud d'Avignon. 15M de flux annuel. Avec mezzanine et terrasse.</t>
+  </si>
+  <si>
+    <t>Zone commerciale à côté du Leclerc de Champigny. Proximité directe avec les habitations.</t>
+  </si>
+  <si>
+    <t>Local situé dans la Patte d'Oie d'Herblay. 60M de flux annuel.</t>
   </si>
 </sst>
 </file>
@@ -5001,8 +5062,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX189" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AX189" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX192" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AX192" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}">
     <filterColumn colId="10">
       <filters>
         <filter val="/"/>
@@ -5493,10 +5554,10 @@
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1420</v>
+        <v>1404</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -5511,7 +5572,7 @@
         <v>259</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1426</v>
+        <v>1410</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>260</v>
@@ -5580,10 +5641,10 @@
         <v>1</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>1422</v>
+        <v>1406</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>1423</v>
+        <v>1407</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>106</v>
@@ -5610,7 +5671,7 @@
         <v>12</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
@@ -5669,7 +5730,9 @@
       <c r="P2" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="Q2" s="33"/>
+      <c r="Q2" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R2" s="34">
         <v>423</v>
       </c>
@@ -5757,7 +5820,7 @@
         <v>335</v>
       </c>
       <c r="AS2" s="35" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="AT2" s="5" t="s">
         <v>75</v>
@@ -5827,7 +5890,9 @@
       <c r="P3" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="Q3" s="33"/>
+      <c r="Q3" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R3" s="34" t="s">
         <v>103</v>
       </c>
@@ -5915,7 +5980,7 @@
         <v>336</v>
       </c>
       <c r="AS3" s="35" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="AT3" s="5" t="s">
         <v>75</v>
@@ -5985,7 +6050,9 @@
       <c r="P4" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="Q4" s="33"/>
+      <c r="Q4" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R4" s="34">
         <v>244</v>
       </c>
@@ -6073,7 +6140,7 @@
         <v>357</v>
       </c>
       <c r="AS4" s="35" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="AT4" s="5" t="s">
         <v>75</v>
@@ -6141,9 +6208,11 @@
         <v>9030</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="Q5" s="33"/>
+        <v>1285</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R5" s="34">
         <v>8628</v>
       </c>
@@ -6231,7 +6300,7 @@
         <v>358</v>
       </c>
       <c r="AS5" s="35" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="AT5" s="5" t="s">
         <v>75</v>
@@ -6301,7 +6370,9 @@
       <c r="P6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q6" s="34"/>
+      <c r="Q6" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R6" s="34" t="s">
         <v>103</v>
       </c>
@@ -6373,7 +6444,7 @@
         <v>374</v>
       </c>
       <c r="AM6" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN6" s="11"/>
       <c r="AO6" s="5" t="s">
@@ -6389,7 +6460,7 @@
         <v>442</v>
       </c>
       <c r="AS6" s="35" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="AT6" s="5" t="s">
         <v>75</v>
@@ -6459,7 +6530,9 @@
       <c r="P7" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q7" s="34"/>
+      <c r="Q7" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R7" s="34" t="s">
         <v>103</v>
       </c>
@@ -6531,7 +6604,7 @@
         <v>374</v>
       </c>
       <c r="AM7" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN7" s="11"/>
       <c r="AO7" s="5" t="s">
@@ -6547,7 +6620,7 @@
         <v>443</v>
       </c>
       <c r="AS7" s="35" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="AT7" s="5" t="s">
         <v>75</v>
@@ -6617,7 +6690,9 @@
       <c r="P8" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q8" s="34"/>
+      <c r="Q8" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R8" s="34" t="s">
         <v>103</v>
       </c>
@@ -6689,7 +6764,7 @@
         <v>374</v>
       </c>
       <c r="AM8" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN8" s="11"/>
       <c r="AO8" s="5" t="s">
@@ -6705,7 +6780,7 @@
         <v>444</v>
       </c>
       <c r="AS8" s="35" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="AT8" s="5" t="s">
         <v>75</v>
@@ -6849,7 +6924,7 @@
         <v>374</v>
       </c>
       <c r="AM9" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN9" s="11"/>
       <c r="AO9" s="5" t="s">
@@ -6865,7 +6940,7 @@
         <v>445</v>
       </c>
       <c r="AS9" s="35" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="AT9" s="5" t="s">
         <v>75</v>
@@ -7009,7 +7084,7 @@
         <v>374</v>
       </c>
       <c r="AM10" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN10" s="11"/>
       <c r="AO10" s="5" t="s">
@@ -7025,7 +7100,7 @@
         <v>446</v>
       </c>
       <c r="AS10" s="35" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="AT10" s="5" t="s">
         <v>75</v>
@@ -7169,7 +7244,7 @@
         <v>374</v>
       </c>
       <c r="AM11" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN11" s="11"/>
       <c r="AO11" s="5" t="s">
@@ -7185,7 +7260,7 @@
         <v>447</v>
       </c>
       <c r="AS11" s="35" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="AT11" s="5" t="s">
         <v>75</v>
@@ -7329,7 +7404,7 @@
         <v>374</v>
       </c>
       <c r="AM12" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN12" s="11"/>
       <c r="AO12" s="5" t="s">
@@ -7345,7 +7420,7 @@
         <v>448</v>
       </c>
       <c r="AS12" s="35" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="AT12" s="5" t="s">
         <v>75</v>
@@ -7489,7 +7564,7 @@
         <v>374</v>
       </c>
       <c r="AM13" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN13" s="11"/>
       <c r="AO13" s="5" t="s">
@@ -7505,7 +7580,7 @@
         <v>449</v>
       </c>
       <c r="AS13" s="35" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="AT13" s="5" t="s">
         <v>75</v>
@@ -7649,7 +7724,7 @@
         <v>374</v>
       </c>
       <c r="AM14" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN14" s="11"/>
       <c r="AO14" s="5" t="s">
@@ -7665,7 +7740,7 @@
         <v>450</v>
       </c>
       <c r="AS14" s="35" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="AT14" s="5" t="s">
         <v>75</v>
@@ -7809,7 +7884,7 @@
         <v>374</v>
       </c>
       <c r="AM15" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN15" s="11"/>
       <c r="AO15" s="5" t="s">
@@ -7825,7 +7900,7 @@
         <v>451</v>
       </c>
       <c r="AS15" s="35" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="AT15" s="5" t="s">
         <v>75</v>
@@ -7969,7 +8044,7 @@
         <v>374</v>
       </c>
       <c r="AM16" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN16" s="11"/>
       <c r="AO16" s="5" t="s">
@@ -7985,7 +8060,7 @@
         <v>452</v>
       </c>
       <c r="AS16" s="35" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="AT16" s="5" t="s">
         <v>75</v>
@@ -8055,7 +8130,9 @@
       <c r="P17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q17" s="34"/>
+      <c r="Q17" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R17" s="34" t="s">
         <v>103</v>
       </c>
@@ -8127,7 +8204,7 @@
         <v>374</v>
       </c>
       <c r="AM17" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN17" s="11"/>
       <c r="AO17" s="5" t="s">
@@ -8143,7 +8220,7 @@
         <v>453</v>
       </c>
       <c r="AS17" s="35" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="AT17" s="5" t="s">
         <v>75</v>
@@ -8213,7 +8290,9 @@
       <c r="P18" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q18" s="34"/>
+      <c r="Q18" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R18" s="34" t="s">
         <v>103</v>
       </c>
@@ -8285,7 +8364,7 @@
         <v>374</v>
       </c>
       <c r="AM18" s="11" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
       <c r="AN18" s="11"/>
       <c r="AO18" s="5" t="s">
@@ -8301,7 +8380,7 @@
         <v>454</v>
       </c>
       <c r="AS18" s="35" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="AT18" s="5" t="s">
         <v>75</v>
@@ -8461,7 +8540,7 @@
         <v>455</v>
       </c>
       <c r="AS19" s="35" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="AT19" s="5" t="s">
         <v>75</v>
@@ -8621,7 +8700,7 @@
         <v>456</v>
       </c>
       <c r="AS20" s="36" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="AT20" s="5" t="s">
         <v>75</v>
@@ -8781,7 +8860,7 @@
         <v>457</v>
       </c>
       <c r="AS21" s="36" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="AT21" s="5" t="s">
         <v>75</v>
@@ -8941,7 +9020,7 @@
         <v>458</v>
       </c>
       <c r="AS22" s="36" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="AT22" s="5" t="s">
         <v>75</v>
@@ -9101,7 +9180,7 @@
         <v>459</v>
       </c>
       <c r="AS23" s="36" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="AT23" s="5" t="s">
         <v>75</v>
@@ -9261,7 +9340,7 @@
         <v>460</v>
       </c>
       <c r="AS24" s="36" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="AT24" s="5" t="s">
         <v>75</v>
@@ -9331,7 +9410,9 @@
       <c r="P25" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q25" s="34"/>
+      <c r="Q25" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R25" s="34" t="s">
         <v>103</v>
       </c>
@@ -9419,7 +9500,7 @@
         <v>461</v>
       </c>
       <c r="AS25" s="36" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="AT25" s="5" t="s">
         <v>75</v>
@@ -9579,7 +9660,7 @@
         <v>462</v>
       </c>
       <c r="AS26" s="36" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="AT26" s="5" t="s">
         <v>75</v>
@@ -9739,7 +9820,7 @@
         <v>463</v>
       </c>
       <c r="AS27" s="36" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="AT27" s="5" t="s">
         <v>75</v>
@@ -9899,7 +9980,7 @@
         <v>464</v>
       </c>
       <c r="AS28" s="36" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="AT28" s="5" t="s">
         <v>75</v>
@@ -10059,7 +10140,7 @@
         <v>465</v>
       </c>
       <c r="AS29" s="36" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="AT29" s="5" t="s">
         <v>75</v>
@@ -10219,7 +10300,7 @@
         <v>466</v>
       </c>
       <c r="AS30" s="36" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="AT30" s="5" t="s">
         <v>75</v>
@@ -10289,7 +10370,9 @@
       <c r="P31" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q31" s="34"/>
+      <c r="Q31" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R31" s="34" t="s">
         <v>103</v>
       </c>
@@ -10377,7 +10460,7 @@
         <v>467</v>
       </c>
       <c r="AS31" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT31" s="5" t="s">
         <v>75</v>
@@ -10447,7 +10530,9 @@
       <c r="P32" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q32" s="34"/>
+      <c r="Q32" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R32" s="34" t="s">
         <v>103</v>
       </c>
@@ -10533,7 +10618,7 @@
         <v>468</v>
       </c>
       <c r="AS32" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT32" s="5" t="s">
         <v>75</v>
@@ -10603,7 +10688,9 @@
       <c r="P33" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q33" s="34"/>
+      <c r="Q33" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R33" s="34" t="s">
         <v>103</v>
       </c>
@@ -10691,7 +10778,7 @@
         <v>469</v>
       </c>
       <c r="AS33" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT33" s="5" t="s">
         <v>75</v>
@@ -10761,7 +10848,9 @@
       <c r="P34" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q34" s="34"/>
+      <c r="Q34" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="34" t="s">
         <v>103</v>
       </c>
@@ -10849,7 +10938,7 @@
         <v>470</v>
       </c>
       <c r="AS34" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT34" s="5" t="s">
         <v>75</v>
@@ -10919,7 +11008,9 @@
       <c r="P35" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q35" s="34"/>
+      <c r="Q35" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R35" s="34" t="s">
         <v>103</v>
       </c>
@@ -11007,7 +11098,7 @@
         <v>471</v>
       </c>
       <c r="AS35" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT35" s="5" t="s">
         <v>75</v>
@@ -11077,7 +11168,9 @@
       <c r="P36" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q36" s="34"/>
+      <c r="Q36" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R36" s="34" t="s">
         <v>103</v>
       </c>
@@ -11165,7 +11258,7 @@
         <v>472</v>
       </c>
       <c r="AS36" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT36" s="5" t="s">
         <v>75</v>
@@ -11235,7 +11328,9 @@
       <c r="P37" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q37" s="34"/>
+      <c r="Q37" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R37" s="34" t="s">
         <v>103</v>
       </c>
@@ -11323,7 +11418,7 @@
         <v>473</v>
       </c>
       <c r="AS37" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT37" s="5" t="s">
         <v>75</v>
@@ -11393,7 +11488,9 @@
       <c r="P38" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q38" s="34"/>
+      <c r="Q38" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R38" s="34" t="s">
         <v>103</v>
       </c>
@@ -11481,7 +11578,7 @@
         <v>474</v>
       </c>
       <c r="AS38" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT38" s="5" t="s">
         <v>75</v>
@@ -11551,7 +11648,9 @@
       <c r="P39" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q39" s="34"/>
+      <c r="Q39" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R39" s="34" t="s">
         <v>103</v>
       </c>
@@ -11639,7 +11738,7 @@
         <v>611</v>
       </c>
       <c r="AS39" s="35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="AT39" s="5" t="s">
         <v>75</v>
@@ -11709,7 +11808,9 @@
       <c r="P40" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q40" s="34"/>
+      <c r="Q40" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R40" s="34">
         <v>200</v>
       </c>
@@ -11797,7 +11898,7 @@
         <v>475</v>
       </c>
       <c r="AS40" s="35" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="AT40" s="5" t="s">
         <v>75</v>
@@ -11867,7 +11968,9 @@
       <c r="P41" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="Q41" s="33"/>
+      <c r="Q41" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R41" s="34">
         <v>156</v>
       </c>
@@ -11955,7 +12058,7 @@
         <v>476</v>
       </c>
       <c r="AS41" s="35" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="AT41" s="5" t="s">
         <v>75</v>
@@ -12023,7 +12126,9 @@
         <v>87</v>
       </c>
       <c r="P42" s="12"/>
-      <c r="Q42" s="34"/>
+      <c r="Q42" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="34">
         <v>82</v>
       </c>
@@ -12109,7 +12214,7 @@
         <v>477</v>
       </c>
       <c r="AS42" s="35" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="AT42" s="5" t="s">
         <v>75</v>
@@ -12177,7 +12282,9 @@
         <v>197</v>
       </c>
       <c r="P43" s="12"/>
-      <c r="Q43" s="34"/>
+      <c r="Q43" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R43" s="34">
         <v>182</v>
       </c>
@@ -12263,7 +12370,7 @@
         <v>478</v>
       </c>
       <c r="AS43" s="35" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="AT43" s="5" t="s">
         <v>75</v>
@@ -12333,7 +12440,9 @@
       <c r="P44" s="12">
         <v>1257</v>
       </c>
-      <c r="Q44" s="34"/>
+      <c r="Q44" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R44" s="34">
         <v>543</v>
       </c>
@@ -12419,7 +12528,7 @@
         <v>479</v>
       </c>
       <c r="AS44" s="35" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="AT44" s="5" t="s">
         <v>75</v>
@@ -12489,7 +12598,9 @@
       <c r="P45" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="Q45" s="34"/>
+      <c r="Q45" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R45" s="34">
         <v>221</v>
       </c>
@@ -12577,7 +12688,7 @@
         <v>480</v>
       </c>
       <c r="AS45" s="35" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="AT45" s="5" t="s">
         <v>75</v>
@@ -12647,7 +12758,9 @@
       <c r="P46" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="Q46" s="34"/>
+      <c r="Q46" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R46" s="34">
         <v>218</v>
       </c>
@@ -12735,7 +12848,7 @@
         <v>481</v>
       </c>
       <c r="AS46" s="35" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="AT46" s="11" t="s">
         <v>53</v>
@@ -12805,7 +12918,9 @@
       <c r="P47" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="Q47" s="33"/>
+      <c r="Q47" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R47" s="34" t="s">
         <v>103</v>
       </c>
@@ -12893,7 +13008,7 @@
         <v>482</v>
       </c>
       <c r="AS47" s="35" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="AT47" s="5" t="s">
         <v>75</v>
@@ -12963,7 +13078,9 @@
       <c r="P48" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="Q48" s="33"/>
+      <c r="Q48" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R48" s="34" t="s">
         <v>103</v>
       </c>
@@ -13051,7 +13168,7 @@
         <v>483</v>
       </c>
       <c r="AS48" s="35" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="AT48" s="5" t="s">
         <v>75</v>
@@ -13121,7 +13238,9 @@
       <c r="P49" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="Q49" s="33"/>
+      <c r="Q49" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R49" s="34" t="s">
         <v>103</v>
       </c>
@@ -13209,7 +13328,7 @@
         <v>484</v>
       </c>
       <c r="AS49" s="35" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="AT49" s="5" t="s">
         <v>75</v>
@@ -13279,7 +13398,9 @@
       <c r="P50" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Q50" s="34"/>
+      <c r="Q50" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R50" s="34" t="s">
         <v>103</v>
       </c>
@@ -13364,7 +13485,7 @@
         <v>308</v>
       </c>
       <c r="AS50" s="35" t="s">
-        <v>1262</v>
+        <v>1247</v>
       </c>
       <c r="AT50" s="5" t="s">
         <v>75</v>
@@ -13434,7 +13555,9 @@
       <c r="P51" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="Q51" s="33"/>
+      <c r="Q51" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R51" s="34" t="s">
         <v>103</v>
       </c>
@@ -13590,7 +13713,9 @@
       <c r="P52" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="Q52" s="33"/>
+      <c r="Q52" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R52" s="34" t="s">
         <v>103</v>
       </c>
@@ -13678,7 +13803,7 @@
         <v>486</v>
       </c>
       <c r="AS52" s="35" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="AT52" s="5" t="s">
         <v>75</v>
@@ -13748,7 +13873,9 @@
       <c r="P53" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="Q53" s="33"/>
+      <c r="Q53" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R53" s="34" t="s">
         <v>103</v>
       </c>
@@ -13836,7 +13963,7 @@
         <v>487</v>
       </c>
       <c r="AS53" s="35" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="AT53" s="5" t="s">
         <v>75</v>
@@ -13906,7 +14033,9 @@
       <c r="P54" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q54" s="34"/>
+      <c r="Q54" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R54" s="34" t="s">
         <v>103</v>
       </c>
@@ -13994,7 +14123,7 @@
         <v>488</v>
       </c>
       <c r="AS54" s="35" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="AT54" s="5" t="s">
         <v>75</v>
@@ -14064,7 +14193,9 @@
       <c r="P55" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="Q55" s="33"/>
+      <c r="Q55" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R55" s="34" t="s">
         <v>103</v>
       </c>
@@ -14152,7 +14283,7 @@
         <v>489</v>
       </c>
       <c r="AS55" s="35" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="AT55" s="5" t="s">
         <v>75</v>
@@ -14220,9 +14351,11 @@
         <v>87</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>1302</v>
-      </c>
-      <c r="Q56" s="33"/>
+        <v>1286</v>
+      </c>
+      <c r="Q56" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R56" s="34" t="s">
         <v>103</v>
       </c>
@@ -14310,7 +14443,7 @@
         <v>490</v>
       </c>
       <c r="AS56" s="35" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="AT56" s="5" t="s">
         <v>75</v>
@@ -14380,7 +14513,9 @@
       <c r="P57" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q57" s="34"/>
+      <c r="Q57" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R57" s="34" t="s">
         <v>103</v>
       </c>
@@ -14469,7 +14604,7 @@
         <v>491</v>
       </c>
       <c r="AS57" s="35" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="AT57" s="5" t="s">
         <v>75</v>
@@ -14539,7 +14674,9 @@
       <c r="P58" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q58" s="34"/>
+      <c r="Q58" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R58" s="34" t="s">
         <v>103</v>
       </c>
@@ -14628,7 +14765,7 @@
         <v>492</v>
       </c>
       <c r="AS58" s="35" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="AT58" s="5" t="s">
         <v>75</v>
@@ -14698,7 +14835,9 @@
       <c r="P59" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q59" s="34"/>
+      <c r="Q59" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R59" s="34" t="s">
         <v>103</v>
       </c>
@@ -14787,7 +14926,7 @@
         <v>493</v>
       </c>
       <c r="AS59" s="35" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AT59" s="5" t="s">
         <v>75</v>
@@ -14948,7 +15087,7 @@
         <v>494</v>
       </c>
       <c r="AS60" s="35" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="AT60" s="5" t="s">
         <v>75</v>
@@ -15109,7 +15248,7 @@
         <v>495</v>
       </c>
       <c r="AS61" s="35" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="AT61" s="5" t="s">
         <v>75</v>
@@ -15270,7 +15409,7 @@
         <v>496</v>
       </c>
       <c r="AS62" s="35" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="AT62" s="5" t="s">
         <v>75</v>
@@ -15340,7 +15479,9 @@
       <c r="P63" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q63" s="34"/>
+      <c r="Q63" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R63" s="34" t="s">
         <v>103</v>
       </c>
@@ -15429,7 +15570,7 @@
         <v>497</v>
       </c>
       <c r="AS63" s="35" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="AT63" s="5" t="s">
         <v>75</v>
@@ -15499,7 +15640,9 @@
       <c r="P64" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q64" s="34"/>
+      <c r="Q64" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R64" s="34" t="s">
         <v>103</v>
       </c>
@@ -15588,7 +15731,7 @@
         <v>498</v>
       </c>
       <c r="AS64" s="35" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AT64" s="5" t="s">
         <v>75</v>
@@ -15658,7 +15801,9 @@
       <c r="P65" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q65" s="34"/>
+      <c r="Q65" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R65" s="34" t="s">
         <v>103</v>
       </c>
@@ -15746,7 +15891,7 @@
         <v>499</v>
       </c>
       <c r="AS65" s="35" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="AT65" s="5" t="s">
         <v>75</v>
@@ -15816,7 +15961,9 @@
       <c r="P66" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q66" s="34"/>
+      <c r="Q66" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R66" s="34" t="s">
         <v>103</v>
       </c>
@@ -15904,7 +16051,7 @@
         <v>500</v>
       </c>
       <c r="AS66" s="36" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="AT66" s="5" t="s">
         <v>75</v>
@@ -15950,7 +16097,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>45</v>
@@ -15966,7 +16113,7 @@
         <v>103</v>
       </c>
       <c r="N67" s="35" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="O67" s="34">
         <v>321</v>
@@ -15974,7 +16121,9 @@
       <c r="P67" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q67" s="34"/>
+      <c r="Q67" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R67" s="34" t="s">
         <v>103</v>
       </c>
@@ -16044,7 +16193,7 @@
         <v>369</v>
       </c>
       <c r="AL67" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM67" s="5" t="s">
         <v>356</v>
@@ -16054,16 +16203,16 @@
         <v>367</v>
       </c>
       <c r="AP67" s="5" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="AQ67" s="5" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="AR67" s="32" t="s">
         <v>501</v>
       </c>
       <c r="AS67" s="35" t="s">
-        <v>1070</v>
+        <v>1062</v>
       </c>
       <c r="AT67" s="5" t="s">
         <v>75</v>
@@ -16109,7 +16258,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>45</v>
@@ -16125,7 +16274,7 @@
         <v>103</v>
       </c>
       <c r="N68" s="36" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="O68" s="34">
         <v>159</v>
@@ -16133,7 +16282,9 @@
       <c r="P68" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q68" s="34"/>
+      <c r="Q68" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R68" s="34" t="s">
         <v>103</v>
       </c>
@@ -16203,7 +16354,7 @@
         <v>369</v>
       </c>
       <c r="AL68" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM68" s="5" t="s">
         <v>356</v>
@@ -16213,16 +16364,16 @@
         <v>367</v>
       </c>
       <c r="AP68" s="11" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="AQ68" s="11" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="AR68" s="32" t="s">
         <v>502</v>
       </c>
       <c r="AS68" s="35" t="s">
-        <v>1071</v>
+        <v>1063</v>
       </c>
       <c r="AT68" s="5" t="s">
         <v>75</v>
@@ -16268,7 +16419,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>45</v>
@@ -16284,7 +16435,7 @@
         <v>103</v>
       </c>
       <c r="N69" s="36" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="O69" s="34">
         <v>281</v>
@@ -16292,7 +16443,9 @@
       <c r="P69" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q69" s="34"/>
+      <c r="Q69" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R69" s="34" t="s">
         <v>103</v>
       </c>
@@ -16362,7 +16515,7 @@
         <v>369</v>
       </c>
       <c r="AL69" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM69" s="5" t="s">
         <v>356</v>
@@ -16372,16 +16525,16 @@
         <v>367</v>
       </c>
       <c r="AP69" s="11" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="AQ69" s="11" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="AR69" s="32" t="s">
         <v>503</v>
       </c>
       <c r="AS69" s="35" t="s">
-        <v>1072</v>
+        <v>1064</v>
       </c>
       <c r="AT69" s="5" t="s">
         <v>75</v>
@@ -16427,7 +16580,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>45</v>
@@ -16443,7 +16596,7 @@
         <v>103</v>
       </c>
       <c r="N70" s="36" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="O70" s="34">
         <v>168</v>
@@ -16451,7 +16604,9 @@
       <c r="P70" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q70" s="34"/>
+      <c r="Q70" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R70" s="34" t="s">
         <v>103</v>
       </c>
@@ -16521,7 +16676,7 @@
         <v>369</v>
       </c>
       <c r="AL70" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM70" s="5" t="s">
         <v>356</v>
@@ -16531,16 +16686,16 @@
         <v>367</v>
       </c>
       <c r="AP70" s="11" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="AQ70" s="11" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AR70" s="32" t="s">
         <v>504</v>
       </c>
       <c r="AS70" s="35" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
       <c r="AT70" s="5" t="s">
         <v>75</v>
@@ -16586,7 +16741,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>45</v>
@@ -16610,7 +16765,9 @@
       <c r="P71" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q71" s="34"/>
+      <c r="Q71" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R71" s="34" t="s">
         <v>103</v>
       </c>
@@ -16680,7 +16837,7 @@
         <v>369</v>
       </c>
       <c r="AL71" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM71" s="5" t="s">
         <v>356</v>
@@ -16690,16 +16847,16 @@
         <v>367</v>
       </c>
       <c r="AP71" s="11" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="AQ71" s="11" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="AR71" s="32" t="s">
         <v>505</v>
       </c>
       <c r="AS71" s="35" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
       <c r="AT71" s="5" t="s">
         <v>75</v>
@@ -16745,7 +16902,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>45</v>
@@ -16769,7 +16926,9 @@
       <c r="P72" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q72" s="34"/>
+      <c r="Q72" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R72" s="34" t="s">
         <v>103</v>
       </c>
@@ -16839,7 +16998,7 @@
         <v>369</v>
       </c>
       <c r="AL72" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM72" s="5" t="s">
         <v>356</v>
@@ -16849,16 +17008,16 @@
         <v>367</v>
       </c>
       <c r="AP72" s="11" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="AQ72" s="11" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="AR72" s="32" t="s">
         <v>506</v>
       </c>
       <c r="AS72" s="35" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
       <c r="AT72" s="5" t="s">
         <v>75</v>
@@ -16904,7 +17063,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>45</v>
@@ -16928,7 +17087,9 @@
       <c r="P73" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q73" s="34"/>
+      <c r="Q73" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R73" s="34" t="s">
         <v>103</v>
       </c>
@@ -16998,7 +17159,7 @@
         <v>369</v>
       </c>
       <c r="AL73" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM73" s="5" t="s">
         <v>356</v>
@@ -17008,16 +17169,16 @@
         <v>367</v>
       </c>
       <c r="AP73" s="11" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="AQ73" s="11" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="AR73" s="32" t="s">
         <v>507</v>
       </c>
       <c r="AS73" s="35" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
       <c r="AT73" s="5" t="s">
         <v>75</v>
@@ -17063,7 +17224,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>45</v>
@@ -17087,7 +17248,9 @@
       <c r="P74" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q74" s="34"/>
+      <c r="Q74" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R74" s="34" t="s">
         <v>103</v>
       </c>
@@ -17157,7 +17320,7 @@
         <v>369</v>
       </c>
       <c r="AL74" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM74" s="5" t="s">
         <v>356</v>
@@ -17167,16 +17330,16 @@
         <v>367</v>
       </c>
       <c r="AP74" s="11" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="AQ74" s="11" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="AR74" s="32" t="s">
         <v>508</v>
       </c>
       <c r="AS74" s="35" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
       <c r="AT74" s="5" t="s">
         <v>75</v>
@@ -17222,7 +17385,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>45</v>
@@ -17246,7 +17409,9 @@
       <c r="P75" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q75" s="34"/>
+      <c r="Q75" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R75" s="34" t="s">
         <v>103</v>
       </c>
@@ -17316,7 +17481,7 @@
         <v>369</v>
       </c>
       <c r="AL75" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM75" s="5" t="s">
         <v>356</v>
@@ -17326,16 +17491,16 @@
         <v>367</v>
       </c>
       <c r="AP75" s="11" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="AQ75" s="11" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="AR75" s="32" t="s">
         <v>509</v>
       </c>
       <c r="AS75" s="35" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="AT75" s="5" t="s">
         <v>75</v>
@@ -17381,7 +17546,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>45</v>
@@ -17405,7 +17570,9 @@
       <c r="P76" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q76" s="34"/>
+      <c r="Q76" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R76" s="34" t="s">
         <v>103</v>
       </c>
@@ -17475,7 +17642,7 @@
         <v>369</v>
       </c>
       <c r="AL76" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM76" s="5" t="s">
         <v>356</v>
@@ -17485,16 +17652,16 @@
         <v>367</v>
       </c>
       <c r="AP76" s="11" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="AQ76" s="11" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="AR76" s="32" t="s">
         <v>510</v>
       </c>
       <c r="AS76" s="35" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
       <c r="AT76" s="5" t="s">
         <v>75</v>
@@ -17540,7 +17707,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H77" s="15" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>45</v>
@@ -17564,7 +17731,9 @@
       <c r="P77" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q77" s="34"/>
+      <c r="Q77" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R77" s="34" t="s">
         <v>103</v>
       </c>
@@ -17634,7 +17803,7 @@
         <v>369</v>
       </c>
       <c r="AL77" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM77" s="5" t="s">
         <v>356</v>
@@ -17644,16 +17813,16 @@
         <v>367</v>
       </c>
       <c r="AP77" s="11" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="AQ77" s="11" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="AR77" s="32" t="s">
         <v>511</v>
       </c>
       <c r="AS77" s="35" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
       <c r="AT77" s="5" t="s">
         <v>75</v>
@@ -17699,7 +17868,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>45</v>
@@ -17723,7 +17892,9 @@
       <c r="P78" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q78" s="34"/>
+      <c r="Q78" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R78" s="34" t="s">
         <v>103</v>
       </c>
@@ -17793,7 +17964,7 @@
         <v>369</v>
       </c>
       <c r="AL78" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM78" s="5" t="s">
         <v>356</v>
@@ -17803,16 +17974,16 @@
         <v>367</v>
       </c>
       <c r="AP78" s="11" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="AQ78" s="11" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="AR78" s="32" t="s">
         <v>512</v>
       </c>
       <c r="AS78" s="35" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
       <c r="AT78" s="5" t="s">
         <v>75</v>
@@ -17858,7 +18029,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>45</v>
@@ -17882,7 +18053,9 @@
       <c r="P79" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q79" s="34"/>
+      <c r="Q79" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R79" s="34" t="s">
         <v>103</v>
       </c>
@@ -17952,7 +18125,7 @@
         <v>369</v>
       </c>
       <c r="AL79" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM79" s="5" t="s">
         <v>356</v>
@@ -17962,16 +18135,16 @@
         <v>367</v>
       </c>
       <c r="AP79" s="11" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="AQ79" s="11" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="AR79" s="32" t="s">
         <v>513</v>
       </c>
       <c r="AS79" s="35" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="AT79" s="5" t="s">
         <v>75</v>
@@ -18017,7 +18190,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>45</v>
@@ -18041,7 +18214,9 @@
       <c r="P80" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q80" s="34"/>
+      <c r="Q80" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R80" s="34" t="s">
         <v>103</v>
       </c>
@@ -18111,7 +18286,7 @@
         <v>369</v>
       </c>
       <c r="AL80" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM80" s="5" t="s">
         <v>356</v>
@@ -18121,16 +18296,16 @@
         <v>367</v>
       </c>
       <c r="AP80" s="11" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="AQ80" s="11" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="AR80" s="32" t="s">
         <v>514</v>
       </c>
       <c r="AS80" s="35" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="AT80" s="5" t="s">
         <v>75</v>
@@ -18176,7 +18351,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H81" s="15" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>45</v>
@@ -18200,7 +18375,9 @@
       <c r="P81" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q81" s="34"/>
+      <c r="Q81" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R81" s="34" t="s">
         <v>103</v>
       </c>
@@ -18270,7 +18447,7 @@
         <v>369</v>
       </c>
       <c r="AL81" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM81" s="5" t="s">
         <v>356</v>
@@ -18280,16 +18457,16 @@
         <v>367</v>
       </c>
       <c r="AP81" s="11" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="AQ81" s="11" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="AR81" s="32" t="s">
         <v>515</v>
       </c>
       <c r="AS81" s="35" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="AT81" s="5" t="s">
         <v>75</v>
@@ -18335,7 +18512,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>45</v>
@@ -18359,7 +18536,9 @@
       <c r="P82" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q82" s="34"/>
+      <c r="Q82" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R82" s="34" t="s">
         <v>103</v>
       </c>
@@ -18429,7 +18608,7 @@
         <v>369</v>
       </c>
       <c r="AL82" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM82" s="5" t="s">
         <v>356</v>
@@ -18439,16 +18618,16 @@
         <v>367</v>
       </c>
       <c r="AP82" s="11" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="AQ82" s="11" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="AR82" s="32" t="s">
         <v>516</v>
       </c>
       <c r="AS82" s="35" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="AT82" s="5" t="s">
         <v>75</v>
@@ -18494,7 +18673,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>45</v>
@@ -18518,7 +18697,9 @@
       <c r="P83" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q83" s="34"/>
+      <c r="Q83" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R83" s="34" t="s">
         <v>103</v>
       </c>
@@ -18588,7 +18769,7 @@
         <v>369</v>
       </c>
       <c r="AL83" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM83" s="5" t="s">
         <v>356</v>
@@ -18598,16 +18779,16 @@
         <v>367</v>
       </c>
       <c r="AP83" s="11" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="AQ83" s="11" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="AR83" s="32" t="s">
         <v>517</v>
       </c>
       <c r="AS83" s="35" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="AT83" s="5" t="s">
         <v>75</v>
@@ -18653,7 +18834,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>45</v>
@@ -18677,7 +18858,9 @@
       <c r="P84" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q84" s="34"/>
+      <c r="Q84" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R84" s="34" t="s">
         <v>103</v>
       </c>
@@ -18747,7 +18930,7 @@
         <v>369</v>
       </c>
       <c r="AL84" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM84" s="5" t="s">
         <v>356</v>
@@ -18757,16 +18940,16 @@
         <v>367</v>
       </c>
       <c r="AP84" s="11" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="AQ84" s="11" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="AR84" s="32" t="s">
         <v>518</v>
       </c>
       <c r="AS84" s="35" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="AT84" s="5" t="s">
         <v>75</v>
@@ -18812,7 +18995,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H85" s="15" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>45</v>
@@ -18836,7 +19019,9 @@
       <c r="P85" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q85" s="34"/>
+      <c r="Q85" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R85" s="34" t="s">
         <v>103</v>
       </c>
@@ -18906,7 +19091,7 @@
         <v>369</v>
       </c>
       <c r="AL85" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM85" s="5" t="s">
         <v>356</v>
@@ -18916,16 +19101,16 @@
         <v>367</v>
       </c>
       <c r="AP85" s="11" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="AQ85" s="11" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="AR85" s="32" t="s">
         <v>519</v>
       </c>
       <c r="AS85" s="35" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
       <c r="AT85" s="5" t="s">
         <v>75</v>
@@ -18971,7 +19156,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>45</v>
@@ -18995,7 +19180,9 @@
       <c r="P86" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q86" s="34"/>
+      <c r="Q86" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R86" s="34" t="s">
         <v>103</v>
       </c>
@@ -19065,7 +19252,7 @@
         <v>369</v>
       </c>
       <c r="AL86" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM86" s="5" t="s">
         <v>356</v>
@@ -19075,16 +19262,16 @@
         <v>367</v>
       </c>
       <c r="AP86" s="11" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="AQ86" s="11" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="AR86" s="32" t="s">
         <v>520</v>
       </c>
       <c r="AS86" s="35" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="AT86" s="5" t="s">
         <v>75</v>
@@ -19130,7 +19317,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>45</v>
@@ -19154,7 +19341,9 @@
       <c r="P87" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q87" s="34"/>
+      <c r="Q87" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R87" s="34" t="s">
         <v>103</v>
       </c>
@@ -19224,7 +19413,7 @@
         <v>369</v>
       </c>
       <c r="AL87" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM87" s="5" t="s">
         <v>356</v>
@@ -19234,16 +19423,16 @@
         <v>367</v>
       </c>
       <c r="AP87" s="11" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="AQ87" s="11" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="AR87" s="32" t="s">
         <v>521</v>
       </c>
       <c r="AS87" s="35" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="AT87" s="5" t="s">
         <v>75</v>
@@ -19289,7 +19478,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>45</v>
@@ -19313,7 +19502,9 @@
       <c r="P88" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q88" s="34"/>
+      <c r="Q88" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R88" s="34" t="s">
         <v>103</v>
       </c>
@@ -19383,7 +19574,7 @@
         <v>369</v>
       </c>
       <c r="AL88" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM88" s="5" t="s">
         <v>356</v>
@@ -19393,16 +19584,16 @@
         <v>367</v>
       </c>
       <c r="AP88" s="11" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="AQ88" s="11" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="AR88" s="32" t="s">
         <v>522</v>
       </c>
       <c r="AS88" s="35" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="AT88" s="5" t="s">
         <v>75</v>
@@ -19448,7 +19639,7 @@
 92290 - Châtenay-Malabry</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>45</v>
@@ -19472,7 +19663,9 @@
       <c r="P89" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q89" s="34"/>
+      <c r="Q89" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R89" s="34" t="s">
         <v>103</v>
       </c>
@@ -19542,7 +19735,7 @@
         <v>369</v>
       </c>
       <c r="AL89" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AM89" s="5" t="s">
         <v>356</v>
@@ -19552,16 +19745,16 @@
         <v>367</v>
       </c>
       <c r="AP89" s="11" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="AQ89" s="11" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="AR89" s="32" t="s">
         <v>523</v>
       </c>
       <c r="AS89" s="35" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
       <c r="AT89" s="5" t="s">
         <v>75</v>
@@ -19705,23 +19898,23 @@
         <v>684</v>
       </c>
       <c r="AM90" s="5" t="s">
-        <v>685</v>
+        <v>1441</v>
       </c>
       <c r="AN90" s="5"/>
       <c r="AO90" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP90" s="5" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="AQ90" s="5" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="AR90" s="32" t="s">
         <v>524</v>
       </c>
       <c r="AS90" s="35" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="AT90" s="5" t="s">
         <v>75</v>
@@ -19865,23 +20058,23 @@
         <v>684</v>
       </c>
       <c r="AM91" s="5" t="s">
-        <v>686</v>
+        <v>1441</v>
       </c>
       <c r="AN91" s="5"/>
       <c r="AO91" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP91" s="11" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="AQ91" s="11" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="AR91" s="32" t="s">
         <v>525</v>
       </c>
       <c r="AS91" s="35" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="AT91" s="5" t="s">
         <v>75</v>
@@ -20025,23 +20218,23 @@
         <v>684</v>
       </c>
       <c r="AM92" s="5" t="s">
-        <v>687</v>
+        <v>1441</v>
       </c>
       <c r="AN92" s="5"/>
       <c r="AO92" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP92" s="11" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="AQ92" s="11" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="AR92" s="32" t="s">
         <v>526</v>
       </c>
       <c r="AS92" s="35" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="AT92" s="5" t="s">
         <v>75</v>
@@ -20185,23 +20378,23 @@
         <v>684</v>
       </c>
       <c r="AM93" s="5" t="s">
-        <v>688</v>
+        <v>1441</v>
       </c>
       <c r="AN93" s="5"/>
       <c r="AO93" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP93" s="11" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="AQ93" s="11" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="AR93" s="32" t="s">
         <v>527</v>
       </c>
       <c r="AS93" s="36" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="AT93" s="5" t="s">
         <v>75</v>
@@ -20345,23 +20538,23 @@
         <v>684</v>
       </c>
       <c r="AM94" s="5" t="s">
-        <v>689</v>
+        <v>1441</v>
       </c>
       <c r="AN94" s="5"/>
       <c r="AO94" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP94" s="11" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="AQ94" s="11" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="AR94" s="32" t="s">
         <v>528</v>
       </c>
       <c r="AS94" s="36" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="AT94" s="5" t="s">
         <v>75</v>
@@ -20505,23 +20698,23 @@
         <v>684</v>
       </c>
       <c r="AM95" s="5" t="s">
-        <v>690</v>
+        <v>1441</v>
       </c>
       <c r="AN95" s="5"/>
       <c r="AO95" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP95" s="11" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="AQ95" s="11" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="AR95" s="32" t="s">
         <v>529</v>
       </c>
       <c r="AS95" s="36" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="AT95" s="5" t="s">
         <v>75</v>
@@ -20591,7 +20784,9 @@
       <c r="P96" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q96" s="34"/>
+      <c r="Q96" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R96" s="34" t="s">
         <v>103</v>
       </c>
@@ -20663,23 +20858,23 @@
         <v>684</v>
       </c>
       <c r="AM96" s="5" t="s">
-        <v>691</v>
+        <v>1441</v>
       </c>
       <c r="AN96" s="5"/>
       <c r="AO96" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP96" s="11" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="AQ96" s="11" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="AR96" s="32" t="s">
         <v>530</v>
       </c>
       <c r="AS96" s="36" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="AT96" s="5" t="s">
         <v>75</v>
@@ -20823,29 +21018,29 @@
         <v>684</v>
       </c>
       <c r="AM97" s="5" t="s">
-        <v>692</v>
+        <v>1441</v>
       </c>
       <c r="AN97" s="5"/>
       <c r="AO97" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP97" s="11" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="AQ97" s="11" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="AR97" s="32" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="AS97" s="36" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="AT97" s="5" t="s">
         <v>75</v>
       </c>
       <c r="AU97" s="11" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="AV97" s="13" t="s">
         <v>31</v>
@@ -20909,7 +21104,9 @@
       <c r="P98" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q98" s="34"/>
+      <c r="Q98" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R98" s="34" t="s">
         <v>103</v>
       </c>
@@ -20989,16 +21186,16 @@
         <v>367</v>
       </c>
       <c r="AP98" s="5" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="AQ98" s="5" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="AR98" s="32" t="s">
         <v>531</v>
       </c>
       <c r="AS98" s="35" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="AT98" s="5" t="s">
         <v>75</v>
@@ -21068,7 +21265,9 @@
       <c r="P99" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q99" s="34"/>
+      <c r="Q99" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R99" s="34" t="s">
         <v>103</v>
       </c>
@@ -21148,16 +21347,16 @@
         <v>367</v>
       </c>
       <c r="AP99" s="11" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="AQ99" s="11" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="AR99" s="32" t="s">
         <v>532</v>
       </c>
       <c r="AS99" s="35" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="AT99" s="5" t="s">
         <v>75</v>
@@ -21227,7 +21426,9 @@
       <c r="P100" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q100" s="34"/>
+      <c r="Q100" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R100" s="34" t="s">
         <v>103</v>
       </c>
@@ -21307,16 +21508,16 @@
         <v>367</v>
       </c>
       <c r="AP100" s="11" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="AQ100" s="11" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="AR100" s="32" t="s">
         <v>533</v>
       </c>
       <c r="AS100" s="35" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="AT100" s="5" t="s">
         <v>75</v>
@@ -21386,7 +21587,9 @@
       <c r="P101" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q101" s="34"/>
+      <c r="Q101" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R101" s="34" t="s">
         <v>103</v>
       </c>
@@ -21466,16 +21669,16 @@
         <v>367</v>
       </c>
       <c r="AP101" s="11" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="AQ101" s="11" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="AR101" s="32" t="s">
         <v>534</v>
       </c>
       <c r="AS101" s="35" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="AT101" s="5" t="s">
         <v>75</v>
@@ -21545,7 +21748,9 @@
       <c r="P102" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q102" s="34"/>
+      <c r="Q102" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R102" s="34" t="s">
         <v>103</v>
       </c>
@@ -21625,16 +21830,16 @@
         <v>367</v>
       </c>
       <c r="AP102" s="11" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="AQ102" s="11" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="AR102" s="32" t="s">
         <v>535</v>
       </c>
       <c r="AS102" s="35" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="AT102" s="5" t="s">
         <v>75</v>
@@ -21704,7 +21909,9 @@
       <c r="P103" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q103" s="34"/>
+      <c r="Q103" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R103" s="34" t="s">
         <v>103</v>
       </c>
@@ -21783,16 +21990,16 @@
         <v>367</v>
       </c>
       <c r="AP103" s="11" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="AQ103" s="11" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="AR103" s="32" t="s">
         <v>536</v>
       </c>
       <c r="AS103" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT103" s="5" t="s">
         <v>75</v>
@@ -21862,7 +22069,9 @@
       <c r="P104" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q104" s="34"/>
+      <c r="Q104" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R104" s="34" t="s">
         <v>103</v>
       </c>
@@ -21941,16 +22150,16 @@
         <v>367</v>
       </c>
       <c r="AP104" s="11" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="AQ104" s="11" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="AR104" s="32" t="s">
         <v>537</v>
       </c>
       <c r="AS104" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT104" s="5" t="s">
         <v>75</v>
@@ -22024,7 +22233,9 @@
       <c r="P105" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q105" s="34"/>
+      <c r="Q105" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R105" s="34" t="s">
         <v>103</v>
       </c>
@@ -22103,16 +22314,16 @@
         <v>367</v>
       </c>
       <c r="AP105" s="11" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="AQ105" s="11" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="AR105" s="32" t="s">
         <v>538</v>
       </c>
       <c r="AS105" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT105" s="5" t="s">
         <v>75</v>
@@ -22179,7 +22390,9 @@
       <c r="P106" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q106" s="34"/>
+      <c r="Q106" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R106" s="34" t="s">
         <v>103</v>
       </c>
@@ -22258,16 +22471,16 @@
         <v>367</v>
       </c>
       <c r="AP106" s="11" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="AQ106" s="11" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="AR106" s="32" t="s">
         <v>539</v>
       </c>
       <c r="AS106" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT106" s="5" t="s">
         <v>75</v>
@@ -22417,16 +22630,16 @@
         <v>367</v>
       </c>
       <c r="AP107" s="11" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="AQ107" s="11" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="AR107" s="32" t="s">
         <v>540</v>
       </c>
       <c r="AS107" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT107" s="5" t="s">
         <v>75</v>
@@ -22576,16 +22789,16 @@
         <v>367</v>
       </c>
       <c r="AP108" s="11" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="AQ108" s="11" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="AR108" s="32" t="s">
         <v>541</v>
       </c>
       <c r="AS108" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT108" s="5" t="s">
         <v>75</v>
@@ -22654,7 +22867,9 @@
       <c r="P109" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q109" s="34"/>
+      <c r="Q109" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R109" s="34" t="s">
         <v>103</v>
       </c>
@@ -22733,16 +22948,16 @@
         <v>367</v>
       </c>
       <c r="AP109" s="11" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="AQ109" s="11" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="AR109" s="32" t="s">
         <v>542</v>
       </c>
       <c r="AS109" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT109" s="5" t="s">
         <v>75</v>
@@ -22892,16 +23107,16 @@
         <v>367</v>
       </c>
       <c r="AP110" s="11" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="AQ110" s="11" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="AR110" s="32" t="s">
         <v>543</v>
       </c>
       <c r="AS110" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT110" s="5" t="s">
         <v>75</v>
@@ -23051,16 +23266,16 @@
         <v>367</v>
       </c>
       <c r="AP111" s="11" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="AQ111" s="11" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="AR111" s="32" t="s">
         <v>544</v>
       </c>
       <c r="AS111" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT111" s="5" t="s">
         <v>75</v>
@@ -23210,16 +23425,16 @@
         <v>367</v>
       </c>
       <c r="AP112" s="11" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="AQ112" s="11" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="AR112" s="32" t="s">
         <v>545</v>
       </c>
       <c r="AS112" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT112" s="5" t="s">
         <v>75</v>
@@ -23370,16 +23585,16 @@
         <v>367</v>
       </c>
       <c r="AP113" s="11" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="AQ113" s="11" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="AR113" s="32" t="s">
         <v>546</v>
       </c>
       <c r="AS113" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT113" s="5" t="s">
         <v>75</v>
@@ -23530,16 +23745,16 @@
         <v>367</v>
       </c>
       <c r="AP114" s="11" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="AQ114" s="11" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="AR114" s="32" t="s">
         <v>547</v>
       </c>
       <c r="AS114" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT114" s="5" t="s">
         <v>75</v>
@@ -23690,16 +23905,16 @@
         <v>367</v>
       </c>
       <c r="AP115" s="11" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="AQ115" s="11" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="AR115" s="32" t="s">
         <v>548</v>
       </c>
       <c r="AS115" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT115" s="5" t="s">
         <v>75</v>
@@ -23769,7 +23984,9 @@
       <c r="P116" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q116" s="34"/>
+      <c r="Q116" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R116" s="34" t="s">
         <v>103</v>
       </c>
@@ -23848,16 +24065,16 @@
         <v>367</v>
       </c>
       <c r="AP116" s="11" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="AQ116" s="11" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="AR116" s="32" t="s">
         <v>549</v>
       </c>
       <c r="AS116" s="35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AT116" s="5" t="s">
         <v>75</v>
@@ -23889,13 +24106,13 @@
         <v>67</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="E117" s="26">
         <v>67600</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="G117" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -23903,7 +24120,7 @@
 67600 - Sélestat</v>
       </c>
       <c r="H117" s="15" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>45</v>
@@ -23919,7 +24136,7 @@
         <v>7500</v>
       </c>
       <c r="N117" s="36" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="O117" s="34">
         <v>98</v>
@@ -23927,7 +24144,9 @@
       <c r="P117" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q117" s="34"/>
+      <c r="Q117" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R117" s="34" t="s">
         <v>103</v>
       </c>
@@ -23997,26 +24216,26 @@
         <v>368</v>
       </c>
       <c r="AL117" s="10" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="AM117" s="11" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="AN117" s="11"/>
       <c r="AO117" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP117" s="11" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="AQ117" s="11" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="AR117" s="11">
         <v>25</v>
       </c>
       <c r="AS117" s="36" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="AT117" s="11" t="s">
         <v>75</v>
@@ -24025,7 +24244,7 @@
         <v>376</v>
       </c>
       <c r="AV117" s="13" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="AW117" s="14"/>
       <c r="AX117" s="44"/>
@@ -24048,13 +24267,13 @@
         <v>84</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="E118" s="26">
         <v>84507</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="G118" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24062,7 +24281,7 @@
 84507 - Bollène</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="I118" s="12" t="s">
         <v>47</v>
@@ -24086,7 +24305,9 @@
       <c r="P118" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q118" s="34"/>
+      <c r="Q118" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R118" s="34" t="s">
         <v>103</v>
       </c>
@@ -24156,35 +24377,35 @@
         <v>369</v>
       </c>
       <c r="AL118" s="10" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="AM118" s="11" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="AN118" s="11"/>
       <c r="AO118" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP118" s="11" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="AQ118" s="11" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="AR118" s="11">
         <v>26</v>
       </c>
       <c r="AS118" s="36" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="AT118" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU118" s="11" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="AV118" s="13" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="AW118" s="14"/>
       <c r="AX118" s="44"/>
@@ -24207,7 +24428,7 @@
         <v>92</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="E119" s="26">
         <v>92100</v>
@@ -24221,7 +24442,7 @@
 92100 - Boulogne-Billancourt</v>
       </c>
       <c r="H119" s="15" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="I119" s="12" t="s">
         <v>45</v>
@@ -24237,7 +24458,7 @@
         <v>103</v>
       </c>
       <c r="N119" s="36" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="O119" s="34">
         <v>254</v>
@@ -24245,7 +24466,9 @@
       <c r="P119" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q119" s="34"/>
+      <c r="Q119" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R119" s="34" t="s">
         <v>103</v>
       </c>
@@ -24315,23 +24538,23 @@
       </c>
       <c r="AL119" s="10"/>
       <c r="AM119" s="11" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="AN119" s="11"/>
       <c r="AO119" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP119" s="11" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="AQ119" s="11" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="AR119" s="11">
         <v>27</v>
       </c>
       <c r="AS119" s="36" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="AT119" s="11" t="s">
         <v>75</v>
@@ -24363,7 +24586,7 @@
         <v>75</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="E120" s="26">
         <v>75020</v>
@@ -24377,7 +24600,7 @@
 75020 - Paris</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="I120" s="12" t="s">
         <v>45</v>
@@ -24401,7 +24624,9 @@
       <c r="P120" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q120" s="34"/>
+      <c r="Q120" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R120" s="34" t="s">
         <v>103</v>
       </c>
@@ -24470,32 +24695,32 @@
         <v>368</v>
       </c>
       <c r="AL120" s="10" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="AM120" s="11" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="AN120" s="11"/>
       <c r="AO120" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP120" s="11" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AQ120" s="11" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="AR120" s="11">
         <v>28</v>
       </c>
       <c r="AS120" s="36" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="AT120" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU120" s="11" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AV120" s="13" t="s">
         <v>31</v>
@@ -24521,13 +24746,13 @@
         <v>93</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E121" s="26">
         <v>93430</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G121" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24535,7 +24760,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H121" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I121" s="12" t="s">
         <v>45</v>
@@ -24551,7 +24776,7 @@
         <v>103</v>
       </c>
       <c r="N121" s="36" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="O121" s="34">
         <v>163</v>
@@ -24559,7 +24784,9 @@
       <c r="P121" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q121" s="34"/>
+      <c r="Q121" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R121" s="34" t="s">
         <v>103</v>
       </c>
@@ -24629,35 +24856,35 @@
         <v>369</v>
       </c>
       <c r="AL121" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM121" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN121" s="11"/>
       <c r="AO121" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP121" s="11" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="AQ121" s="11" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="AR121" s="11" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="AS121" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT121" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU121" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV121" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW121" s="14"/>
       <c r="AX121" s="44"/>
@@ -24680,13 +24907,13 @@
         <v>93</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E122" s="26">
         <v>93430</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G122" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24694,7 +24921,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H122" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I122" s="12" t="s">
         <v>45</v>
@@ -24790,35 +25017,35 @@
         <v>368</v>
       </c>
       <c r="AL122" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM122" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN122" s="11"/>
       <c r="AO122" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP122" s="11" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="AQ122" s="11" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="AR122" s="11" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="AS122" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT122" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU122" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV122" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW122" s="14"/>
       <c r="AX122" s="44"/>
@@ -24841,13 +25068,13 @@
         <v>93</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E123" s="26">
         <v>93430</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G123" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -24855,7 +25082,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H123" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I123" s="12" t="s">
         <v>45</v>
@@ -24951,35 +25178,35 @@
         <v>368</v>
       </c>
       <c r="AL123" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM123" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN123" s="11"/>
       <c r="AO123" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP123" s="11" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="AQ123" s="11" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="AR123" s="11" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="AS123" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT123" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU123" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV123" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW123" s="14"/>
       <c r="AX123" s="44"/>
@@ -25002,13 +25229,13 @@
         <v>93</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E124" s="26">
         <v>93430</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G124" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25016,7 +25243,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I124" s="12" t="s">
         <v>45</v>
@@ -25032,7 +25259,7 @@
         <v>103</v>
       </c>
       <c r="N124" s="36" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="O124" s="34">
         <v>438</v>
@@ -25040,7 +25267,9 @@
       <c r="P124" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q124" s="34"/>
+      <c r="Q124" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R124" s="34" t="s">
         <v>103</v>
       </c>
@@ -25110,35 +25339,35 @@
         <v>369</v>
       </c>
       <c r="AL124" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM124" s="11" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="AN124" s="11"/>
       <c r="AO124" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP124" s="11" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="AQ124" s="11" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="AR124" s="11" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="AS124" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT124" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU124" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV124" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW124" s="14"/>
       <c r="AX124" s="44"/>
@@ -25161,13 +25390,13 @@
         <v>93</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E125" s="26">
         <v>93430</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G125" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25175,7 +25404,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H125" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I125" s="12" t="s">
         <v>45</v>
@@ -25191,7 +25420,7 @@
         <v>103</v>
       </c>
       <c r="N125" s="36" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="O125" s="34">
         <v>97</v>
@@ -25199,7 +25428,9 @@
       <c r="P125" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q125" s="34"/>
+      <c r="Q125" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R125" s="34" t="s">
         <v>103</v>
       </c>
@@ -25269,35 +25500,35 @@
         <v>368</v>
       </c>
       <c r="AL125" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM125" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN125" s="11"/>
       <c r="AO125" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP125" s="11" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="AQ125" s="11" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="AR125" s="11" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="AS125" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT125" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU125" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV125" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW125" s="14"/>
       <c r="AX125" s="44"/>
@@ -25320,13 +25551,13 @@
         <v>93</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E126" s="26">
         <v>93430</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G126" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25334,7 +25565,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I126" s="12" t="s">
         <v>45</v>
@@ -25430,35 +25661,35 @@
         <v>368</v>
       </c>
       <c r="AL126" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM126" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN126" s="11"/>
       <c r="AO126" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP126" s="11" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="AQ126" s="11" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="AR126" s="11" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="AS126" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT126" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU126" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV126" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW126" s="14"/>
       <c r="AX126" s="44"/>
@@ -25480,13 +25711,13 @@
         <v>93</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E127" s="26">
         <v>93430</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G127" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25494,7 +25725,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H127" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I127" s="12" t="s">
         <v>45</v>
@@ -25510,7 +25741,7 @@
         <v>103</v>
       </c>
       <c r="N127" s="36" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="O127" s="34">
         <v>125</v>
@@ -25590,35 +25821,35 @@
         <v>368</v>
       </c>
       <c r="AL127" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM127" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN127" s="11"/>
       <c r="AO127" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP127" s="11" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="AQ127" s="11" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="AR127" s="11" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="AS127" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT127" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU127" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV127" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW127" s="14"/>
       <c r="AX127" s="44"/>
@@ -25640,13 +25871,13 @@
         <v>93</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E128" s="26">
         <v>93430</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G128" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25654,7 +25885,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H128" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I128" s="12" t="s">
         <v>45</v>
@@ -25750,35 +25981,35 @@
         <v>368</v>
       </c>
       <c r="AL128" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM128" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN128" s="11"/>
       <c r="AO128" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP128" s="11" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="AQ128" s="11" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="AR128" s="11" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="AS128" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT128" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU128" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV128" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW128" s="14"/>
       <c r="AX128" s="44"/>
@@ -25800,13 +26031,13 @@
         <v>93</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E129" s="26">
         <v>93430</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G129" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25814,7 +26045,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H129" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I129" s="12" t="s">
         <v>45</v>
@@ -25910,35 +26141,35 @@
         <v>368</v>
       </c>
       <c r="AL129" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM129" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN129" s="11"/>
       <c r="AO129" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP129" s="11" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="AQ129" s="11" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="AR129" s="11" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="AS129" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT129" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU129" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV129" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW129" s="14"/>
       <c r="AX129" s="44"/>
@@ -25960,13 +26191,13 @@
         <v>93</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E130" s="26">
         <v>93430</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G130" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -25974,7 +26205,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H130" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I130" s="12" t="s">
         <v>45</v>
@@ -26070,35 +26301,35 @@
         <v>368</v>
       </c>
       <c r="AL130" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM130" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN130" s="11"/>
       <c r="AO130" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP130" s="11" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="AQ130" s="11" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="AR130" s="11" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="AS130" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT130" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU130" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV130" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW130" s="14"/>
       <c r="AX130" s="44"/>
@@ -26120,13 +26351,13 @@
         <v>93</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E131" s="26">
         <v>93430</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G131" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26134,7 +26365,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H131" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I131" s="12" t="s">
         <v>45</v>
@@ -26230,35 +26461,35 @@
         <v>368</v>
       </c>
       <c r="AL131" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM131" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN131" s="11"/>
       <c r="AO131" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP131" s="11" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="AQ131" s="11" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="AR131" s="11" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="AS131" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT131" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU131" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV131" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW131" s="14"/>
       <c r="AX131" s="44"/>
@@ -26280,13 +26511,13 @@
         <v>93</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E132" s="26">
         <v>93430</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G132" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26294,7 +26525,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H132" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I132" s="12" t="s">
         <v>45</v>
@@ -26390,35 +26621,35 @@
         <v>368</v>
       </c>
       <c r="AL132" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM132" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN132" s="11"/>
       <c r="AO132" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP132" s="11" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="AQ132" s="11" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="AR132" s="11" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="AS132" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT132" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU132" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV132" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW132" s="14"/>
       <c r="AX132" s="44"/>
@@ -26440,13 +26671,13 @@
         <v>93</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E133" s="26">
         <v>93430</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G133" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26454,7 +26685,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H133" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I133" s="12" t="s">
         <v>45</v>
@@ -26550,35 +26781,35 @@
         <v>368</v>
       </c>
       <c r="AL133" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM133" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN133" s="11"/>
       <c r="AO133" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP133" s="11" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="AQ133" s="11" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="AR133" s="11" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="AS133" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT133" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU133" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV133" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW133" s="14"/>
       <c r="AX133" s="44"/>
@@ -26600,13 +26831,13 @@
         <v>93</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E134" s="26">
         <v>93430</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G134" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26614,7 +26845,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I134" s="12" t="s">
         <v>45</v>
@@ -26710,35 +26941,35 @@
         <v>368</v>
       </c>
       <c r="AL134" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM134" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN134" s="11"/>
       <c r="AO134" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP134" s="11" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="AQ134" s="11" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="AR134" s="11" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="AS134" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT134" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU134" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV134" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW134" s="14"/>
       <c r="AX134" s="44"/>
@@ -26760,13 +26991,13 @@
         <v>93</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E135" s="26">
         <v>93430</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G135" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26774,7 +27005,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H135" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I135" s="12" t="s">
         <v>45</v>
@@ -26870,35 +27101,35 @@
         <v>368</v>
       </c>
       <c r="AL135" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM135" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN135" s="11"/>
       <c r="AO135" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP135" s="11" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="AQ135" s="11" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="AR135" s="11" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="AS135" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT135" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU135" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV135" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW135" s="14"/>
       <c r="AX135" s="44"/>
@@ -26920,13 +27151,13 @@
         <v>93</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E136" s="26">
         <v>93430</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G136" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -26934,7 +27165,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H136" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I136" s="12" t="s">
         <v>45</v>
@@ -26958,7 +27189,9 @@
       <c r="P136" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q136" s="34"/>
+      <c r="Q136" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R136" s="34" t="s">
         <v>103</v>
       </c>
@@ -27028,35 +27261,35 @@
         <v>368</v>
       </c>
       <c r="AL136" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM136" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN136" s="11"/>
       <c r="AO136" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP136" s="11" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="AQ136" s="11" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="AR136" s="11" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="AS136" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT136" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU136" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV136" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW136" s="14"/>
       <c r="AX136" s="44"/>
@@ -27078,13 +27311,13 @@
         <v>93</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E137" s="26">
         <v>93430</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G137" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27092,7 +27325,7 @@
 93430 - Villetaneuse</v>
       </c>
       <c r="H137" s="15" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I137" s="12" t="s">
         <v>45</v>
@@ -27108,7 +27341,7 @@
         <v>103</v>
       </c>
       <c r="N137" s="36" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="O137" s="34">
         <v>62</v>
@@ -27116,7 +27349,9 @@
       <c r="P137" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q137" s="34"/>
+      <c r="Q137" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R137" s="34" t="s">
         <v>103</v>
       </c>
@@ -27186,35 +27421,35 @@
         <v>368</v>
       </c>
       <c r="AL137" s="10" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AM137" s="11" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="AN137" s="11"/>
       <c r="AO137" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP137" s="11" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="AQ137" s="11" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="AR137" s="11" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="AS137" s="36" t="s">
-        <v>1395</v>
+        <v>1379</v>
       </c>
       <c r="AT137" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU137" s="11" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AV137" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW137" s="14"/>
       <c r="AX137" s="44"/>
@@ -27236,13 +27471,13 @@
         <v>95</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="E138" s="26">
         <v>95290</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="G138" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27250,7 +27485,7 @@
 95290 - L'Isle-Adam</v>
       </c>
       <c r="H138" s="15" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="I138" s="12" t="s">
         <v>47</v>
@@ -27272,9 +27507,11 @@
         <v>167</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>1398</v>
-      </c>
-      <c r="Q138" s="34"/>
+        <v>1382</v>
+      </c>
+      <c r="Q138" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R138" s="34" t="s">
         <v>103</v>
       </c>
@@ -27344,35 +27581,35 @@
         <v>368</v>
       </c>
       <c r="AL138" s="10" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="AM138" s="11" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="AN138" s="11"/>
       <c r="AO138" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP138" s="11" t="s">
-        <v>1405</v>
+        <v>1389</v>
       </c>
       <c r="AQ138" s="11" t="s">
-        <v>1406</v>
+        <v>1390</v>
       </c>
       <c r="AR138" s="11" t="s">
-        <v>1396</v>
+        <v>1380</v>
       </c>
       <c r="AS138" s="36" t="s">
-        <v>1400</v>
+        <v>1384</v>
       </c>
       <c r="AT138" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU138" s="11" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="AV138" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW138" s="14"/>
       <c r="AX138" s="44"/>
@@ -27394,13 +27631,13 @@
         <v>95</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="E139" s="26">
         <v>95290</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="G139" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27408,7 +27645,7 @@
 95290 - L'Isle-Adam</v>
       </c>
       <c r="H139" s="15" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="I139" s="12" t="s">
         <v>47</v>
@@ -27430,9 +27667,11 @@
         <v>124</v>
       </c>
       <c r="P139" s="6" t="s">
-        <v>1399</v>
-      </c>
-      <c r="Q139" s="34"/>
+        <v>1383</v>
+      </c>
+      <c r="Q139" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R139" s="34" t="s">
         <v>103</v>
       </c>
@@ -27502,35 +27741,35 @@
         <v>368</v>
       </c>
       <c r="AL139" s="10" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="AM139" s="11" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="AN139" s="11"/>
       <c r="AO139" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP139" s="11" t="s">
-        <v>1403</v>
+        <v>1387</v>
       </c>
       <c r="AQ139" s="11" t="s">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="AR139" s="11" t="s">
-        <v>1397</v>
+        <v>1381</v>
       </c>
       <c r="AS139" s="36" t="s">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="AT139" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU139" s="11" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="AV139" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW139" s="14"/>
       <c r="AX139" s="44"/>
@@ -27552,13 +27791,13 @@
         <v>95</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="E140" s="26">
         <v>95260</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="G140" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27566,7 +27805,7 @@
 95260 - Mours</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="I140" s="12" t="s">
         <v>47</v>
@@ -27660,35 +27899,35 @@
         <v>369</v>
       </c>
       <c r="AL140" s="10" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="AM140" s="11" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="AN140" s="11"/>
       <c r="AO140" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP140" s="11" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="AQ140" s="11" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="AR140" s="11" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="AS140" s="36" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="AT140" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU140" s="11" t="s">
-        <v>1407</v>
+        <v>1391</v>
       </c>
       <c r="AV140" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW140" s="14"/>
       <c r="AX140" s="44"/>
@@ -27710,13 +27949,13 @@
         <v>95</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="E141" s="26">
         <v>95260</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="G141" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27724,7 +27963,7 @@
 95260 - Mours</v>
       </c>
       <c r="H141" s="15" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="I141" s="12" t="s">
         <v>47</v>
@@ -27818,35 +28057,35 @@
         <v>369</v>
       </c>
       <c r="AL141" s="10" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="AM141" s="11" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="AN141" s="11"/>
       <c r="AO141" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP141" s="11" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="AQ141" s="11" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="AR141" s="11" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="AS141" s="36" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="AT141" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU141" s="11" t="s">
-        <v>1407</v>
+        <v>1391</v>
       </c>
       <c r="AV141" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW141" s="14"/>
       <c r="AX141" s="44"/>
@@ -27868,13 +28107,13 @@
         <v>95</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="E142" s="26">
         <v>95260</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="G142" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -27882,7 +28121,7 @@
 95260 - Mours</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>47</v>
@@ -27976,35 +28215,35 @@
         <v>369</v>
       </c>
       <c r="AL142" s="10" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="AM142" s="11" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="AN142" s="11"/>
       <c r="AO142" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP142" s="11" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="AQ142" s="11" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="AR142" s="11" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="AS142" s="36" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="AT142" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU142" s="11" t="s">
-        <v>1407</v>
+        <v>1391</v>
       </c>
       <c r="AV142" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW142" s="14"/>
       <c r="AX142" s="44"/>
@@ -28026,13 +28265,13 @@
         <v>95</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="E143" s="26">
         <v>95260</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="G143" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28040,7 +28279,7 @@
 95260 - Mours</v>
       </c>
       <c r="H143" s="15" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>47</v>
@@ -28134,35 +28373,35 @@
         <v>369</v>
       </c>
       <c r="AL143" s="10" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="AM143" s="11" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="AN143" s="11"/>
       <c r="AO143" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP143" s="11" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="AQ143" s="11" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="AR143" s="11" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="AS143" s="36" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="AT143" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU143" s="11" t="s">
-        <v>1409</v>
+        <v>1393</v>
       </c>
       <c r="AV143" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW143" s="14"/>
       <c r="AX143" s="44"/>
@@ -28184,13 +28423,13 @@
         <v>95</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="E144" s="26">
         <v>95260</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="G144" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28198,7 +28437,7 @@
 95260 - Mours</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="I144" s="12" t="s">
         <v>47</v>
@@ -28207,11 +28446,11 @@
         <v>50</v>
       </c>
       <c r="K144" s="12" t="s">
-        <v>1428</v>
+        <v>1412</v>
       </c>
       <c r="L144" s="12"/>
       <c r="M144" s="12" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
       <c r="N144" s="36" t="s">
         <v>359</v>
@@ -28222,7 +28461,9 @@
       <c r="P144" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q144" s="34"/>
+      <c r="Q144" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R144" s="34" t="s">
         <v>103</v>
       </c>
@@ -28285,35 +28526,35 @@
         <v>369</v>
       </c>
       <c r="AL144" s="10" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="AM144" s="11" t="s">
-        <v>1402</v>
+        <v>1386</v>
       </c>
       <c r="AN144" s="11"/>
       <c r="AO144" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP144" s="11" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="AQ144" s="11" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="AR144" s="11" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="AS144" s="36" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="AT144" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU144" s="11" t="s">
-        <v>1408</v>
+        <v>1392</v>
       </c>
       <c r="AV144" s="13" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AW144" s="14"/>
       <c r="AX144" s="44"/>
@@ -28335,13 +28576,13 @@
         <v>44</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="E145" s="26">
         <v>44200</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="G145" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28349,7 +28590,7 @@
 44200 - Nantes</v>
       </c>
       <c r="H145" s="15" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="I145" s="12" t="s">
         <v>45</v>
@@ -28373,7 +28614,9 @@
       <c r="P145" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q145" s="34"/>
+      <c r="Q145" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R145" s="34" t="s">
         <v>103</v>
       </c>
@@ -28443,32 +28686,32 @@
         <v>369</v>
       </c>
       <c r="AL145" s="10" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="AM145" s="11" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
       <c r="AN145" s="11"/>
       <c r="AO145" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP145" s="11" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AQ145" s="11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AR145" s="11" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AS145" s="36" t="s">
         <v>1022</v>
-      </c>
-      <c r="AQ145" s="11" t="s">
-        <v>1023</v>
-      </c>
-      <c r="AR145" s="11" t="s">
-        <v>1015</v>
-      </c>
-      <c r="AS145" s="36" t="s">
-        <v>1030</v>
       </c>
       <c r="AT145" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU145" s="11" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="AV145" s="13" t="s">
         <v>37</v>
@@ -28493,13 +28736,13 @@
         <v>44</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="E146" s="26">
         <v>44200</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="G146" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28507,7 +28750,7 @@
 44200 - Nantes</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="I146" s="12" t="s">
         <v>45</v>
@@ -28531,7 +28774,9 @@
       <c r="P146" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q146" s="34"/>
+      <c r="Q146" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R146" s="34" t="s">
         <v>103</v>
       </c>
@@ -28601,32 +28846,32 @@
         <v>368</v>
       </c>
       <c r="AL146" s="10" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="AM146" s="11" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="AN146" s="11"/>
       <c r="AO146" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP146" s="11" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="AQ146" s="11" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="AR146" s="11" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="AS146" s="36" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="AT146" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU146" s="11" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="AV146" s="13" t="s">
         <v>37</v>
@@ -28650,14 +28895,14 @@
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
         <v>68</v>
       </c>
-      <c r="D147" s="42" t="s">
-        <v>1033</v>
+      <c r="D147" s="10" t="s">
+        <v>1025</v>
       </c>
       <c r="E147" s="26">
         <v>68330</v>
       </c>
-      <c r="F147" s="10" t="s">
-        <v>898</v>
+      <c r="F147" s="42" t="s">
+        <v>890</v>
       </c>
       <c r="G147" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28665,7 +28910,7 @@
 68330 - Huningue</v>
       </c>
       <c r="H147" s="15" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="I147" s="12" t="s">
         <v>45</v>
@@ -28681,7 +28926,7 @@
         <v>103</v>
       </c>
       <c r="N147" s="36" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="O147" s="34">
         <v>287</v>
@@ -28689,7 +28934,9 @@
       <c r="P147" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q147" s="34"/>
+      <c r="Q147" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R147" s="34" t="s">
         <v>103</v>
       </c>
@@ -28747,30 +28994,30 @@
       <c r="AK147" s="10"/>
       <c r="AL147" s="10"/>
       <c r="AM147" s="11" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="AN147" s="11"/>
       <c r="AO147" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP147" s="11" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="AQ147" s="11" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="AR147" s="11">
         <v>33</v>
       </c>
       <c r="AS147" s="36" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="AT147" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU147" s="11"/>
       <c r="AV147" s="13" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="AW147" s="14"/>
       <c r="AX147" s="44"/>
@@ -28792,13 +29039,13 @@
         <v>37</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="E148" s="26">
         <v>37600</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G148" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28806,7 +29053,7 @@
 37600 - Loches</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>47</v>
@@ -28830,7 +29077,9 @@
       <c r="P148" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q148" s="34"/>
+      <c r="Q148" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R148" s="34" t="s">
         <v>103</v>
       </c>
@@ -28898,35 +29147,35 @@
         <v>103</v>
       </c>
       <c r="AL148" s="10" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="AM148" s="11" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
       <c r="AN148" s="11"/>
       <c r="AO148" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP148" s="11" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="AQ148" s="11" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="AR148" s="11">
         <v>34</v>
       </c>
       <c r="AS148" s="36" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="AT148" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU148" s="43" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="AV148" s="13" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="AW148" s="14"/>
       <c r="AX148" s="44">
@@ -28950,13 +29199,13 @@
         <v>37</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="E149" s="26">
         <v>37600</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G149" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -28964,7 +29213,7 @@
 37600 - Loches</v>
       </c>
       <c r="H149" s="15" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="I149" s="12" t="s">
         <v>47</v>
@@ -29042,7 +29291,7 @@
         <v>56000</v>
       </c>
       <c r="AF149" s="12" t="str">
-        <f t="shared" ref="AF149:AF189" si="7">"3 mois = "&amp;TEXT(ROUND(3/12*T149,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AF149:AF190" si="7">"3 mois = "&amp;TEXT(ROUND(3/12*T149,0),"### ### ##0 €")</f>
         <v>3 mois = 10 000 €</v>
       </c>
       <c r="AG149" s="6" t="s">
@@ -29061,35 +29310,35 @@
         <v>103</v>
       </c>
       <c r="AL149" s="10" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="AM149" s="11" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="AN149" s="11"/>
       <c r="AO149" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP149" s="11" t="s">
-        <v>1059</v>
+        <v>1051</v>
       </c>
       <c r="AQ149" s="11" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="AR149" s="11" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="AS149" s="36" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="AT149" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU149" s="11" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="AV149" s="13" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="AW149" s="14"/>
       <c r="AX149" s="44">
@@ -29113,13 +29362,13 @@
         <v>37</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="E150" s="26">
         <v>37600</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G150" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29127,7 +29376,7 @@
 37600 - Loches</v>
       </c>
       <c r="H150" s="15" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="I150" s="12" t="s">
         <v>47</v>
@@ -29224,35 +29473,35 @@
         <v>103</v>
       </c>
       <c r="AL150" s="10" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="AM150" s="11" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="AN150" s="11"/>
       <c r="AO150" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP150" s="11" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AQ150" s="11" t="s">
+        <v>1054</v>
+      </c>
+      <c r="AR150" s="11" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AS150" s="36" t="s">
         <v>1061</v>
-      </c>
-      <c r="AQ150" s="11" t="s">
-        <v>1062</v>
-      </c>
-      <c r="AR150" s="11" t="s">
-        <v>1055</v>
-      </c>
-      <c r="AS150" s="36" t="s">
-        <v>1069</v>
       </c>
       <c r="AT150" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU150" s="11" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="AV150" s="13" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="AW150" s="14"/>
       <c r="AX150" s="44">
@@ -29276,13 +29525,13 @@
         <v>37</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="E151" s="26">
         <v>37600</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G151" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29290,7 +29539,7 @@
 37600 - Loches</v>
       </c>
       <c r="H151" s="15" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="I151" s="12" t="s">
         <v>47</v>
@@ -29387,35 +29636,35 @@
         <v>103</v>
       </c>
       <c r="AL151" s="10" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="AM151" s="11" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="AN151" s="11"/>
       <c r="AO151" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP151" s="11" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
       <c r="AQ151" s="11" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
       <c r="AR151" s="11" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="AS151" s="36" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="AT151" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU151" s="11" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="AV151" s="13" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="AW151" s="14"/>
       <c r="AX151" s="44">
@@ -29439,13 +29688,13 @@
         <v>37</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="E152" s="26">
         <v>37600</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G152" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29453,7 +29702,7 @@
 37600 - Loches</v>
       </c>
       <c r="H152" s="15" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="I152" s="12" t="s">
         <v>47</v>
@@ -29550,35 +29799,35 @@
         <v>103</v>
       </c>
       <c r="AL152" s="10" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="AM152" s="11" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="AN152" s="11"/>
       <c r="AO152" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP152" s="11" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
       <c r="AQ152" s="11" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="AR152" s="11" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
       <c r="AS152" s="36" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="AT152" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU152" s="11" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="AV152" s="13" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="AW152" s="14"/>
       <c r="AX152" s="44">
@@ -29602,13 +29851,13 @@
         <v>37</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="E153" s="26">
         <v>37600</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G153" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29616,7 +29865,7 @@
 37600 - Loches</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="I153" s="12" t="s">
         <v>47</v>
@@ -29713,35 +29962,35 @@
         <v>103</v>
       </c>
       <c r="AL153" s="10" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="AM153" s="11" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="AN153" s="11"/>
       <c r="AO153" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP153" s="11" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
       <c r="AQ153" s="11" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="AR153" s="11" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
       <c r="AS153" s="36" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="AT153" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU153" s="11" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="AV153" s="13" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="AW153" s="14"/>
       <c r="AX153" s="44">
@@ -29765,13 +30014,13 @@
         <v>13</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="E154" s="26">
         <v>13127</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="G154" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29779,7 +30028,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="I154" s="12" t="s">
         <v>47</v>
@@ -29791,13 +30040,13 @@
         <v>103</v>
       </c>
       <c r="L154" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M154" s="12" t="s">
         <v>103</v>
       </c>
       <c r="N154" s="36" t="s">
-        <v>1196</v>
+        <v>1187</v>
       </c>
       <c r="O154" s="34">
         <v>181</v>
@@ -29805,7 +30054,9 @@
       <c r="P154" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q154" s="34"/>
+      <c r="Q154" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R154" s="34" t="s">
         <v>103</v>
       </c>
@@ -29875,13 +30126,13 @@
         <v>369</v>
       </c>
       <c r="AL154" s="10" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="AM154" s="11" t="s">
-        <v>1195</v>
+        <v>1442</v>
       </c>
       <c r="AN154" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO154" s="5" t="s">
         <v>367</v>
@@ -29893,19 +30144,19 @@
         <v>5.2419589999999996</v>
       </c>
       <c r="AR154" s="11" t="s">
-        <v>1200</v>
+        <v>1191</v>
       </c>
       <c r="AS154" s="36" t="s">
-        <v>1261</v>
+        <v>1246</v>
       </c>
       <c r="AT154" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU154" s="11" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="AV154" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW154" s="14"/>
       <c r="AX154" s="44">
@@ -29929,13 +30180,13 @@
         <v>13</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="E155" s="26">
         <v>13127</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="G155" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -29943,7 +30194,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H155" s="15" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>47</v>
@@ -29952,14 +30203,14 @@
         <v>48</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>1215</v>
+        <v>1206</v>
       </c>
       <c r="L155" s="10"/>
       <c r="M155" s="12" t="s">
         <v>103</v>
       </c>
       <c r="N155" s="36" t="s">
-        <v>1197</v>
+        <v>1188</v>
       </c>
       <c r="O155" s="34">
         <v>100</v>
@@ -30037,35 +30288,35 @@
         <v>369</v>
       </c>
       <c r="AL155" s="10" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="AM155" s="11" t="s">
-        <v>1203</v>
+        <v>1194</v>
       </c>
       <c r="AN155" s="11"/>
       <c r="AO155" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP155" s="11" t="s">
-        <v>1198</v>
+        <v>1189</v>
       </c>
       <c r="AQ155" s="11" t="s">
-        <v>1199</v>
+        <v>1190</v>
       </c>
       <c r="AR155" s="11" t="s">
-        <v>1201</v>
+        <v>1192</v>
       </c>
       <c r="AS155" s="36" t="s">
-        <v>1244</v>
+        <v>1229</v>
       </c>
       <c r="AT155" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU155" s="11" t="s">
-        <v>1204</v>
+        <v>1195</v>
       </c>
       <c r="AV155" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW155" s="14"/>
       <c r="AX155" s="44">
@@ -30089,13 +30340,13 @@
         <v>13</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="E156" s="26">
         <v>13127</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="G156" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30103,7 +30354,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H156" s="15" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="I156" s="12" t="s">
         <v>47</v>
@@ -30112,14 +30363,14 @@
         <v>48</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>1215</v>
+        <v>1206</v>
       </c>
       <c r="L156" s="10"/>
       <c r="M156" s="12" t="s">
         <v>103</v>
       </c>
       <c r="N156" s="36" t="s">
-        <v>1208</v>
+        <v>1199</v>
       </c>
       <c r="O156" s="34">
         <v>446</v>
@@ -30197,35 +30448,35 @@
         <v>103</v>
       </c>
       <c r="AL156" s="10" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="AM156" s="11" t="s">
-        <v>1202</v>
+        <v>1193</v>
       </c>
       <c r="AN156" s="11"/>
       <c r="AO156" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP156" s="11" t="s">
-        <v>1205</v>
+        <v>1196</v>
       </c>
       <c r="AQ156" s="11" t="s">
-        <v>1206</v>
+        <v>1197</v>
       </c>
       <c r="AR156" s="11" t="s">
-        <v>1210</v>
+        <v>1201</v>
       </c>
       <c r="AS156" s="36" t="s">
-        <v>1245</v>
+        <v>1230</v>
       </c>
       <c r="AT156" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU156" s="11" t="s">
-        <v>1207</v>
+        <v>1198</v>
       </c>
       <c r="AV156" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW156" s="14"/>
       <c r="AX156" s="44">
@@ -30249,13 +30500,13 @@
         <v>13</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="E157" s="26">
         <v>13127</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="G157" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30263,7 +30514,7 @@
 13127 - Vitrolles</v>
       </c>
       <c r="H157" s="15" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="I157" s="12" t="s">
         <v>47</v>
@@ -30272,14 +30523,14 @@
         <v>48</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>1215</v>
+        <v>1206</v>
       </c>
       <c r="L157" s="10"/>
       <c r="M157" s="12" t="s">
         <v>103</v>
       </c>
       <c r="N157" s="36" t="s">
-        <v>1209</v>
+        <v>1200</v>
       </c>
       <c r="O157" s="34">
         <v>567</v>
@@ -30357,35 +30608,35 @@
         <v>103</v>
       </c>
       <c r="AL157" s="10" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="AM157" s="11" t="s">
-        <v>1202</v>
+        <v>1193</v>
       </c>
       <c r="AN157" s="11"/>
       <c r="AO157" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP157" s="11" t="s">
-        <v>1213</v>
+        <v>1204</v>
       </c>
       <c r="AQ157" s="11" t="s">
-        <v>1214</v>
+        <v>1205</v>
       </c>
       <c r="AR157" s="11" t="s">
-        <v>1212</v>
+        <v>1203</v>
       </c>
       <c r="AS157" s="36" t="s">
-        <v>1246</v>
+        <v>1231</v>
       </c>
       <c r="AT157" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU157" s="11" t="s">
-        <v>1211</v>
+        <v>1202</v>
       </c>
       <c r="AV157" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW157" s="14"/>
       <c r="AX157" s="44">
@@ -30409,13 +30660,13 @@
         <v>13</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
       <c r="E158" s="26">
         <v>13170</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
       <c r="G158" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30423,7 +30674,7 @@
 13170 - Les Pennes-Mirabeau</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="I158" s="12" t="s">
         <v>47</v>
@@ -30435,7 +30686,7 @@
         <v>103</v>
       </c>
       <c r="L158" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M158" s="12" t="s">
         <v>103</v>
@@ -30445,9 +30696,11 @@
         <v>1390</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>1217</v>
-      </c>
-      <c r="Q158" s="34"/>
+        <v>1208</v>
+      </c>
+      <c r="Q158" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R158" s="34" t="s">
         <v>103</v>
       </c>
@@ -30518,37 +30771,37 @@
         <v>369</v>
       </c>
       <c r="AL158" s="10" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
       <c r="AM158" s="11" t="s">
-        <v>1218</v>
+        <v>1443</v>
       </c>
       <c r="AN158" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO158" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP158" s="11" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="AQ158" s="11" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="AR158" s="11">
         <v>37</v>
       </c>
       <c r="AS158" s="36" t="s">
-        <v>1247</v>
+        <v>1232</v>
       </c>
       <c r="AT158" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU158" s="11" t="s">
-        <v>1216</v>
+        <v>1207</v>
       </c>
       <c r="AV158" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW158" s="14"/>
       <c r="AX158" s="44">
@@ -30572,13 +30825,13 @@
         <v>18</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
       <c r="E159" s="26">
         <v>18390</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
       <c r="G159" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30586,7 +30839,7 @@
 18390 - Saint-Germain-du-Puy</v>
       </c>
       <c r="H159" s="15" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
       <c r="I159" s="12" t="s">
         <v>47</v>
@@ -30598,7 +30851,7 @@
         <v>103</v>
       </c>
       <c r="L159" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M159" s="12" t="s">
         <v>103</v>
@@ -30610,7 +30863,9 @@
       <c r="P159" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q159" s="34"/>
+      <c r="Q159" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R159" s="34" t="s">
         <v>103</v>
       </c>
@@ -30680,37 +30935,37 @@
         <v>369</v>
       </c>
       <c r="AL159" s="10" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
       <c r="AM159" s="11" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
       <c r="AN159" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO159" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP159" s="11" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
       <c r="AQ159" s="11" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="AR159" s="11">
         <v>38</v>
       </c>
       <c r="AS159" s="36" t="s">
-        <v>1248</v>
+        <v>1233</v>
       </c>
       <c r="AT159" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU159" s="11" t="s">
-        <v>1219</v>
+        <v>1209</v>
       </c>
       <c r="AV159" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW159" s="14"/>
       <c r="AX159" s="44">
@@ -30734,13 +30989,13 @@
         <v>18</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
       <c r="E160" s="26">
         <v>18230</v>
       </c>
-      <c r="F160" s="42" t="s">
-        <v>1122</v>
+      <c r="F160" s="10" t="s">
+        <v>1114</v>
       </c>
       <c r="G160" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30748,7 +31003,7 @@
 18230 -  Saint-Doulchard</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
       <c r="I160" s="12" t="s">
         <v>47</v>
@@ -30760,9 +31015,11 @@
         <v>103</v>
       </c>
       <c r="L160" s="10" t="s">
-        <v>1425</v>
-      </c>
-      <c r="M160" s="12"/>
+        <v>1409</v>
+      </c>
+      <c r="M160" s="12" t="s">
+        <v>103</v>
+      </c>
       <c r="N160" s="36"/>
       <c r="O160" s="34">
         <v>600</v>
@@ -30781,30 +31038,36 @@
       </c>
       <c r="T160" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="U160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V160" s="12"/>
+        <v>7500</v>
+      </c>
+      <c r="V160" s="12">
+        <v>150</v>
+      </c>
       <c r="W160" s="6" t="s">
         <v>103</v>
       </c>
       <c r="X160" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="Y160" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z160" s="12"/>
+        <v>1300</v>
+      </c>
+      <c r="Z160" s="12">
+        <v>26</v>
+      </c>
       <c r="AA160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB160" s="12"/>
+        <v>8400</v>
+      </c>
+      <c r="AB160" s="12">
+        <v>14</v>
+      </c>
       <c r="AC160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -30814,17 +31077,17 @@
       </c>
       <c r="AE160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
+        <v>114000</v>
       </c>
       <c r="AF160" s="12" t="str">
         <f t="shared" si="7"/>
-        <v>3 mois = 0 €</v>
+        <v>3 mois = 22 500 €</v>
       </c>
       <c r="AG160" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH160" s="6" t="s">
-        <v>103</v>
+      <c r="AH160" s="46">
+        <v>0.05</v>
       </c>
       <c r="AI160" s="12" t="s">
         <v>363</v>
@@ -30833,38 +31096,40 @@
         <v>53</v>
       </c>
       <c r="AK160" s="10" t="s">
-        <v>103</v>
+        <v>368</v>
       </c>
       <c r="AL160" s="10" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
       <c r="AM160" s="11" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="AN160" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO160" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP160" s="11" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
       <c r="AQ160" s="11" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
       <c r="AR160" s="11">
         <v>39</v>
       </c>
       <c r="AS160" s="36" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="AT160" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AU160" s="11"/>
+      <c r="AU160" s="11" t="s">
+        <v>1415</v>
+      </c>
       <c r="AV160" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW160" s="14"/>
       <c r="AX160" s="44">
@@ -30888,13 +31153,13 @@
         <v>54</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
       <c r="E161" s="26">
         <v>54000</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="G161" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -30902,7 +31167,7 @@
 54000 - Nancy</v>
       </c>
       <c r="H161" s="15" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
       <c r="I161" s="12" t="s">
         <v>45</v>
@@ -30914,7 +31179,7 @@
         <v>103</v>
       </c>
       <c r="L161" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M161" s="12" t="s">
         <v>103</v>
@@ -30924,9 +31189,11 @@
         <v>550</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>1221</v>
-      </c>
-      <c r="Q161" s="34"/>
+        <v>1211</v>
+      </c>
+      <c r="Q161" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R161" s="34" t="s">
         <v>103</v>
       </c>
@@ -30996,37 +31263,37 @@
         <v>369</v>
       </c>
       <c r="AL161" s="10" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="AM161" s="11" t="s">
-        <v>1222</v>
+        <v>1444</v>
       </c>
       <c r="AN161" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO161" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP161" s="11" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
       <c r="AQ161" s="11" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
       <c r="AR161" s="11">
         <v>40</v>
       </c>
       <c r="AS161" s="36" t="s">
-        <v>1249</v>
+        <v>1234</v>
       </c>
       <c r="AT161" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU161" s="11" t="s">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="AV161" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW161" s="14"/>
       <c r="AX161" s="44">
@@ -31050,13 +31317,13 @@
         <v>59</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="E162" s="26">
         <v>59300</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="G162" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -31064,7 +31331,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="I162" s="12" t="s">
         <v>47</v>
@@ -31076,7 +31343,7 @@
         <v>103</v>
       </c>
       <c r="L162" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M162" s="12" t="s">
         <v>103</v>
@@ -31160,37 +31427,37 @@
         <v>369</v>
       </c>
       <c r="AL162" s="10" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="AM162" s="11" t="s">
-        <v>1292</v>
+        <v>1276</v>
       </c>
       <c r="AN162" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO162" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP162" s="11" t="s">
+        <v>1263</v>
+      </c>
+      <c r="AQ162" s="11" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AR162" s="11" t="s">
+        <v>1251</v>
+      </c>
+      <c r="AS162" s="36" t="s">
         <v>1278</v>
-      </c>
-      <c r="AQ162" s="11" t="s">
-        <v>1279</v>
-      </c>
-      <c r="AR162" s="11" t="s">
-        <v>1266</v>
-      </c>
-      <c r="AS162" s="36" t="s">
-        <v>1294</v>
       </c>
       <c r="AT162" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU162" s="11" t="s">
-        <v>1272</v>
+        <v>1257</v>
       </c>
       <c r="AV162" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW162" s="14"/>
       <c r="AX162" s="44">
@@ -31214,13 +31481,13 @@
         <v>59</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="E163" s="26">
         <v>59300</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="G163" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -31228,7 +31495,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H163" s="15" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="I163" s="12" t="s">
         <v>47</v>
@@ -31240,7 +31507,7 @@
         <v>103</v>
       </c>
       <c r="L163" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M163" s="12" t="s">
         <v>103</v>
@@ -31324,37 +31591,37 @@
         <v>369</v>
       </c>
       <c r="AL163" s="10" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="AM163" s="11" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="AN163" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO163" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP163" s="11" t="s">
-        <v>1280</v>
+        <v>1265</v>
       </c>
       <c r="AQ163" s="11" t="s">
-        <v>1281</v>
+        <v>1266</v>
       </c>
       <c r="AR163" s="11" t="s">
-        <v>1267</v>
+        <v>1252</v>
       </c>
       <c r="AS163" s="36" t="s">
-        <v>1295</v>
+        <v>1279</v>
       </c>
       <c r="AT163" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU163" s="11" t="s">
-        <v>1273</v>
+        <v>1258</v>
       </c>
       <c r="AV163" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW163" s="14"/>
       <c r="AX163" s="44"/>
@@ -31376,13 +31643,13 @@
         <v>59</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="E164" s="26">
         <v>59300</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="G164" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -31390,7 +31657,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H164" s="15" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>47</v>
@@ -31402,7 +31669,7 @@
         <v>103</v>
       </c>
       <c r="L164" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M164" s="12" t="s">
         <v>103</v>
@@ -31486,37 +31753,37 @@
         <v>369</v>
       </c>
       <c r="AL164" s="10" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="AM164" s="11" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="AN164" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO164" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP164" s="11" t="s">
+        <v>1265</v>
+      </c>
+      <c r="AQ164" s="11" t="s">
+        <v>1267</v>
+      </c>
+      <c r="AR164" s="11" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AS164" s="36" t="s">
         <v>1280</v>
-      </c>
-      <c r="AQ164" s="11" t="s">
-        <v>1282</v>
-      </c>
-      <c r="AR164" s="11" t="s">
-        <v>1268</v>
-      </c>
-      <c r="AS164" s="36" t="s">
-        <v>1296</v>
       </c>
       <c r="AT164" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU164" s="11" t="s">
-        <v>1274</v>
+        <v>1259</v>
       </c>
       <c r="AV164" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW164" s="14"/>
       <c r="AX164" s="44"/>
@@ -31538,13 +31805,13 @@
         <v>59</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="E165" s="26">
         <v>59300</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="G165" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -31552,7 +31819,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H165" s="15" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="I165" s="12" t="s">
         <v>47</v>
@@ -31564,7 +31831,7 @@
         <v>103</v>
       </c>
       <c r="L165" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M165" s="12" t="s">
         <v>103</v>
@@ -31576,7 +31843,9 @@
       <c r="P165" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q165" s="34"/>
+      <c r="Q165" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R165" s="34" t="s">
         <v>103</v>
       </c>
@@ -31646,37 +31915,37 @@
         <v>368</v>
       </c>
       <c r="AL165" s="10" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="AM165" s="11" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="AN165" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO165" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP165" s="11" t="s">
-        <v>1283</v>
+        <v>1268</v>
       </c>
       <c r="AQ165" s="11" t="s">
-        <v>1284</v>
+        <v>1269</v>
       </c>
       <c r="AR165" s="11" t="s">
-        <v>1269</v>
+        <v>1254</v>
       </c>
       <c r="AS165" s="36" t="s">
-        <v>1297</v>
+        <v>1281</v>
       </c>
       <c r="AT165" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU165" s="11" t="s">
-        <v>1275</v>
+        <v>1260</v>
       </c>
       <c r="AV165" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW165" s="14"/>
       <c r="AX165" s="44"/>
@@ -31698,13 +31967,13 @@
         <v>59</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="E166" s="26">
         <v>59300</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="G166" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -31712,7 +31981,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="I166" s="12" t="s">
         <v>47</v>
@@ -31724,7 +31993,7 @@
         <v>103</v>
       </c>
       <c r="L166" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M166" s="12" t="s">
         <v>103</v>
@@ -31736,7 +32005,9 @@
       <c r="P166" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q166" s="34"/>
+      <c r="Q166" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R166" s="34" t="s">
         <v>103</v>
       </c>
@@ -31806,37 +32077,37 @@
         <v>369</v>
       </c>
       <c r="AL166" s="10" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="AM166" s="11" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="AN166" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO166" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP166" s="11" t="s">
-        <v>1285</v>
+        <v>1270</v>
       </c>
       <c r="AQ166" s="11" t="s">
-        <v>1286</v>
+        <v>1271</v>
       </c>
       <c r="AR166" s="11" t="s">
-        <v>1270</v>
+        <v>1255</v>
       </c>
       <c r="AS166" s="36" t="s">
-        <v>1298</v>
+        <v>1282</v>
       </c>
       <c r="AT166" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU166" s="11" t="s">
-        <v>1276</v>
+        <v>1261</v>
       </c>
       <c r="AV166" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW166" s="14"/>
       <c r="AX166" s="44"/>
@@ -31858,13 +32129,13 @@
         <v>59</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="E167" s="26">
         <v>59300</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="G167" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -31872,7 +32143,7 @@
 59300 - Aulnoy-lez-Valenciennes</v>
       </c>
       <c r="H167" s="15" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="I167" s="12" t="s">
         <v>47</v>
@@ -31881,9 +32152,11 @@
         <v>49</v>
       </c>
       <c r="K167" s="10" t="s">
-        <v>1300</v>
-      </c>
-      <c r="L167" s="10"/>
+        <v>1284</v>
+      </c>
+      <c r="L167" s="10" t="s">
+        <v>1409</v>
+      </c>
       <c r="M167" s="12" t="s">
         <v>103</v>
       </c>
@@ -31894,7 +32167,9 @@
       <c r="P167" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q167" s="34"/>
+      <c r="Q167" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R167" s="34" t="s">
         <v>103</v>
       </c>
@@ -31964,37 +32239,37 @@
         <v>368</v>
       </c>
       <c r="AL167" s="10" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="AM167" s="11" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="AN167" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO167" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP167" s="11" t="s">
-        <v>1287</v>
+        <v>1272</v>
       </c>
       <c r="AQ167" s="11" t="s">
-        <v>1288</v>
+        <v>1273</v>
       </c>
       <c r="AR167" s="11" t="s">
-        <v>1271</v>
+        <v>1256</v>
       </c>
       <c r="AS167" s="36" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="AT167" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU167" s="11" t="s">
-        <v>1277</v>
+        <v>1262</v>
       </c>
       <c r="AV167" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW167" s="14"/>
       <c r="AX167" s="44"/>
@@ -32016,13 +32291,13 @@
         <v>59</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>1223</v>
+        <v>1212</v>
       </c>
       <c r="E168" s="26">
         <v>59320</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="G168" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -32030,7 +32305,7 @@
 59320 - Ennetières-en-Weppes</v>
       </c>
       <c r="H168" s="15" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="I168" s="12" t="s">
         <v>47</v>
@@ -32042,7 +32317,7 @@
         <v>103</v>
       </c>
       <c r="L168" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M168" s="12" t="s">
         <v>103</v>
@@ -32126,37 +32401,37 @@
         <v>369</v>
       </c>
       <c r="AL168" s="10" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
       <c r="AM168" s="11" t="s">
-        <v>1429</v>
+        <v>1413</v>
       </c>
       <c r="AN168" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO168" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP168" s="11" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
       <c r="AQ168" s="11" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
       <c r="AR168" s="11">
         <v>42</v>
       </c>
       <c r="AS168" s="36" t="s">
-        <v>1250</v>
+        <v>1235</v>
       </c>
       <c r="AT168" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU168" s="11" t="s">
-        <v>1263</v>
+        <v>1248</v>
       </c>
       <c r="AV168" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW168" s="14"/>
       <c r="AX168" s="44">
@@ -32180,13 +32455,13 @@
         <v>68</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="E169" s="26">
         <v>68270</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="G169" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -32194,7 +32469,7 @@
 68270 - Wittenheim</v>
       </c>
       <c r="H169" s="15" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
       <c r="I169" s="12" t="s">
         <v>47</v>
@@ -32206,7 +32481,7 @@
         <v>103</v>
       </c>
       <c r="L169" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M169" s="12" t="s">
         <v>103</v>
@@ -32290,37 +32565,37 @@
         <v>369</v>
       </c>
       <c r="AL169" s="10" t="s">
-        <v>1225</v>
+        <v>1214</v>
       </c>
       <c r="AM169" s="11" t="s">
-        <v>1430</v>
+        <v>1414</v>
       </c>
       <c r="AN169" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO169" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP169" s="11" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
       <c r="AQ169" s="11" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="AR169" s="11">
         <v>43</v>
       </c>
       <c r="AS169" s="36" t="s">
-        <v>1251</v>
+        <v>1236</v>
       </c>
       <c r="AT169" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU169" s="11" t="s">
-        <v>1224</v>
+        <v>1213</v>
       </c>
       <c r="AV169" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW169" s="14"/>
       <c r="AX169" s="44">
@@ -32344,13 +32619,13 @@
         <v>77</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
       <c r="E170" s="26">
         <v>77140</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="G170" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -32358,7 +32633,7 @@
 77140 - Nemours</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
       <c r="I170" s="12" t="s">
         <v>47</v>
@@ -32370,7 +32645,7 @@
         <v>103</v>
       </c>
       <c r="L170" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M170" s="12" t="s">
         <v>103</v>
@@ -32380,9 +32655,11 @@
         <v>760</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>1227</v>
-      </c>
-      <c r="Q170" s="34"/>
+        <v>1216</v>
+      </c>
+      <c r="Q170" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R170" s="34" t="s">
         <v>103</v>
       </c>
@@ -32452,37 +32729,37 @@
         <v>369</v>
       </c>
       <c r="AL170" s="10" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
       <c r="AM170" s="11" t="s">
-        <v>1228</v>
+        <v>1217</v>
       </c>
       <c r="AN170" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO170" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP170" s="11" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
       <c r="AQ170" s="11" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="AR170" s="11">
         <v>44</v>
       </c>
       <c r="AS170" s="36" t="s">
-        <v>1252</v>
+        <v>1237</v>
       </c>
       <c r="AT170" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU170" s="11" t="s">
-        <v>1226</v>
+        <v>1215</v>
       </c>
       <c r="AV170" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW170" s="14"/>
       <c r="AX170" s="44">
@@ -32492,7 +32769,7 @@
       <c r="BG170"/>
       <c r="BH170" s="1"/>
     </row>
-    <row r="171" spans="1:60" ht="38.25">
+    <row r="171" spans="1:60" ht="25.5">
       <c r="A171" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -32506,13 +32783,13 @@
         <v>83</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
       <c r="E171" s="26">
         <v>83160</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="G171" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -32520,7 +32797,7 @@
 83160 - La Valette-du-Var</v>
       </c>
       <c r="H171" s="15" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="I171" s="12" t="s">
         <v>45</v>
@@ -32532,7 +32809,7 @@
         <v>103</v>
       </c>
       <c r="L171" s="10" t="s">
-        <v>1425</v>
+        <v>1446</v>
       </c>
       <c r="M171" s="12"/>
       <c r="N171" s="36"/>
@@ -32540,9 +32817,11 @@
         <v>276</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>1229</v>
-      </c>
-      <c r="Q171" s="34"/>
+        <v>1218</v>
+      </c>
+      <c r="Q171" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R171" s="34" t="s">
         <v>103</v>
       </c>
@@ -32613,37 +32892,37 @@
         <v>369</v>
       </c>
       <c r="AL171" s="10" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="AM171" s="11" t="s">
-        <v>1290</v>
+        <v>1445</v>
       </c>
       <c r="AN171" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO171" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP171" s="11" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="AQ171" s="11" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="AR171" s="11" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
       <c r="AS171" s="36" t="s">
-        <v>1253</v>
+        <v>1238</v>
       </c>
       <c r="AT171" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU171" s="11" t="s">
-        <v>1264</v>
+        <v>1249</v>
       </c>
       <c r="AV171" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW171" s="14"/>
       <c r="AX171" s="44">
@@ -32667,13 +32946,13 @@
         <v>83</v>
       </c>
       <c r="D172" s="10" t="s">
-        <v>1230</v>
+        <v>1219</v>
       </c>
       <c r="E172" s="26">
         <v>83160</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="G172" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -32681,7 +32960,7 @@
 83160 - La Valette-du-Var</v>
       </c>
       <c r="H172" s="15" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
       <c r="I172" s="12" t="s">
         <v>45</v>
@@ -32693,7 +32972,7 @@
         <v>103</v>
       </c>
       <c r="L172" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M172" s="12">
         <v>60000</v>
@@ -32705,7 +32984,9 @@
       <c r="P172" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q172" s="34"/>
+      <c r="Q172" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R172" s="34" t="s">
         <v>103</v>
       </c>
@@ -32776,37 +33057,37 @@
         <v>369</v>
       </c>
       <c r="AL172" s="10" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
       <c r="AM172" s="11" t="s">
-        <v>1232</v>
+        <v>1447</v>
       </c>
       <c r="AN172" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO172" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP172" s="11" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
       <c r="AQ172" s="11" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
       <c r="AR172" s="11" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="AS172" s="36" t="s">
-        <v>1254</v>
+        <v>1239</v>
       </c>
       <c r="AT172" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU172" s="11" t="s">
-        <v>1231</v>
+        <v>1220</v>
       </c>
       <c r="AV172" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW172" s="14"/>
       <c r="AX172" s="44">
@@ -32816,7 +33097,7 @@
       <c r="BG172"/>
       <c r="BH172" s="1"/>
     </row>
-    <row r="173" spans="1:60" ht="38.25">
+    <row r="173" spans="1:60" ht="25.5">
       <c r="A173" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -32830,13 +33111,13 @@
         <v>84</v>
       </c>
       <c r="D173" s="10" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
       <c r="E173" s="26">
         <v>84140</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
       <c r="G173" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -32844,7 +33125,7 @@
 84140 - Avignon</v>
       </c>
       <c r="H173" s="15" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="I173" s="12" t="s">
         <v>47</v>
@@ -32856,7 +33137,7 @@
         <v>103</v>
       </c>
       <c r="L173" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M173" s="12" t="s">
         <v>103</v>
@@ -32866,9 +33147,11 @@
         <v>616</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>1234</v>
-      </c>
-      <c r="Q173" s="34"/>
+        <v>1222</v>
+      </c>
+      <c r="Q173" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R173" s="34" t="s">
         <v>103</v>
       </c>
@@ -32939,37 +33222,37 @@
         <v>369</v>
       </c>
       <c r="AL173" s="10" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
       <c r="AM173" s="11" t="s">
-        <v>1235</v>
+        <v>1448</v>
       </c>
       <c r="AN173" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO173" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP173" s="11" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
       <c r="AQ173" s="11" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="AR173" s="11">
         <v>46</v>
       </c>
       <c r="AS173" s="45" t="s">
-        <v>1255</v>
+        <v>1240</v>
       </c>
       <c r="AT173" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU173" s="11" t="s">
-        <v>1233</v>
+        <v>1221</v>
       </c>
       <c r="AV173" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW173" s="14"/>
       <c r="AX173" s="44">
@@ -32993,13 +33276,13 @@
         <v>94</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="E174" s="26">
         <v>94500</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="G174" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -33007,7 +33290,7 @@
 94500 - Champigny-sur-Marne</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="I174" s="12" t="s">
         <v>45</v>
@@ -33019,7 +33302,7 @@
         <v>103</v>
       </c>
       <c r="L174" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M174" s="12" t="s">
         <v>103</v>
@@ -33104,37 +33387,37 @@
         <v>369</v>
       </c>
       <c r="AL174" s="10" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="AM174" s="11" t="s">
-        <v>1241</v>
+        <v>1449</v>
       </c>
       <c r="AN174" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO174" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP174" s="11" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
       <c r="AQ174" s="11" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
       <c r="AR174" s="11" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="AS174" s="45" t="s">
-        <v>1256</v>
+        <v>1241</v>
       </c>
       <c r="AT174" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU174" s="11" t="s">
-        <v>1265</v>
+        <v>1250</v>
       </c>
       <c r="AV174" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW174" s="14"/>
       <c r="AX174" s="44">
@@ -33158,13 +33441,13 @@
         <v>94</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
       <c r="E175" s="26">
         <v>94500</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="G175" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -33172,7 +33455,7 @@
 94500 - Champigny-sur-Marne</v>
       </c>
       <c r="H175" s="15" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="I175" s="12" t="s">
         <v>45</v>
@@ -33184,7 +33467,7 @@
         <v>103</v>
       </c>
       <c r="L175" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M175" s="12" t="s">
         <v>103</v>
@@ -33196,7 +33479,9 @@
       <c r="P175" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q175" s="34"/>
+      <c r="Q175" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R175" s="34" t="s">
         <v>103</v>
       </c>
@@ -33267,37 +33552,37 @@
         <v>369</v>
       </c>
       <c r="AL175" s="10" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="AM175" s="11" t="s">
-        <v>1241</v>
+        <v>1449</v>
       </c>
       <c r="AN175" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO175" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP175" s="11" t="s">
-        <v>1237</v>
+        <v>1224</v>
       </c>
       <c r="AQ175" s="11" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
       <c r="AR175" s="11" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
       <c r="AS175" s="36" t="s">
-        <v>1257</v>
+        <v>1242</v>
       </c>
       <c r="AT175" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU175" s="11" t="s">
-        <v>1236</v>
+        <v>1223</v>
       </c>
       <c r="AV175" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW175" s="14"/>
       <c r="AX175" s="44">
@@ -33321,13 +33606,13 @@
         <v>94</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="E176" s="26">
         <v>94500</v>
       </c>
       <c r="F176" s="10" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="G176" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -33335,7 +33620,7 @@
 94500 - Champigny-sur-Marne</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="I176" s="12" t="s">
         <v>45</v>
@@ -33347,7 +33632,7 @@
         <v>103</v>
       </c>
       <c r="L176" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M176" s="12" t="s">
         <v>103</v>
@@ -33432,37 +33717,37 @@
         <v>369</v>
       </c>
       <c r="AL176" s="10" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="AM176" s="11" t="s">
-        <v>1241</v>
+        <v>1449</v>
       </c>
       <c r="AN176" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO176" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP176" s="11" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
       <c r="AQ176" s="11" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
       <c r="AR176" s="11" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="AS176" s="36" t="s">
-        <v>1258</v>
+        <v>1243</v>
       </c>
       <c r="AT176" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU176" s="11" t="s">
-        <v>1239</v>
+        <v>1226</v>
       </c>
       <c r="AV176" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW176" s="14"/>
       <c r="AX176" s="44">
@@ -33486,13 +33771,13 @@
         <v>95</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
       <c r="E177" s="26">
         <v>95220</v>
       </c>
       <c r="F177" s="10" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
       <c r="G177" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -33500,7 +33785,7 @@
 95220 - Herblay-sur-Seine</v>
       </c>
       <c r="H177" s="15" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
       <c r="I177" s="12" t="s">
         <v>47</v>
@@ -33512,7 +33797,7 @@
         <v>103</v>
       </c>
       <c r="L177" s="10" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="M177" s="12" t="s">
         <v>103</v>
@@ -33524,7 +33809,9 @@
       <c r="P177" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q177" s="34"/>
+      <c r="Q177" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R177" s="34" t="s">
         <v>103</v>
       </c>
@@ -33595,37 +33882,37 @@
         <v>369</v>
       </c>
       <c r="AL177" s="10" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
       <c r="AM177" s="11" t="s">
-        <v>1242</v>
+        <v>1450</v>
       </c>
       <c r="AN177" s="11" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="AO177" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP177" s="11" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
       <c r="AQ177" s="11" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
       <c r="AR177" s="11">
         <v>48</v>
       </c>
       <c r="AS177" s="36" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="AT177" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU177" s="11" t="s">
-        <v>1240</v>
+        <v>1227</v>
       </c>
       <c r="AV177" s="13" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="AW177" s="14"/>
       <c r="AX177" s="44">
@@ -33649,13 +33936,13 @@
         <v>6</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
       <c r="E178" s="48" t="s">
-        <v>1384</v>
+        <v>1368</v>
       </c>
       <c r="F178" s="10" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="G178" s="47" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -33664,7 +33951,7 @@
 06 700 - Saint-Laurent-du-Var</v>
       </c>
       <c r="H178" s="15" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
       <c r="I178" s="12" t="s">
         <v>47</v>
@@ -33677,16 +33964,18 @@
       </c>
       <c r="L178" s="10"/>
       <c r="M178" s="12" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
       <c r="N178" s="36"/>
       <c r="O178" s="34">
         <v>126</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>1243</v>
-      </c>
-      <c r="Q178" s="34"/>
+        <v>1228</v>
+      </c>
+      <c r="Q178" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R178" s="34" t="s">
         <v>103</v>
       </c>
@@ -33756,33 +34045,33 @@
         <v>103</v>
       </c>
       <c r="AL178" s="10" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
       <c r="AM178" s="11" t="s">
-        <v>1188</v>
+        <v>1180</v>
       </c>
       <c r="AN178" s="11"/>
       <c r="AO178" s="5" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="AP178" s="11" t="s">
-        <v>1190</v>
+        <v>1182</v>
       </c>
       <c r="AQ178" s="11" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
       <c r="AR178" s="11">
         <v>49</v>
       </c>
       <c r="AS178" s="36" t="s">
-        <v>1260</v>
+        <v>1245</v>
       </c>
       <c r="AT178" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU178" s="11"/>
       <c r="AV178" s="13" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
       <c r="AW178" s="14"/>
       <c r="AX178" s="44">
@@ -33806,13 +34095,13 @@
         <v>77</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1303</v>
+        <v>1287</v>
       </c>
       <c r="E179" s="26">
         <v>77000</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
       <c r="G179" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -33820,7 +34109,7 @@
 77000 - Melun</v>
       </c>
       <c r="H179" s="15" t="s">
-        <v>1305</v>
+        <v>1289</v>
       </c>
       <c r="I179" s="12" t="s">
         <v>45</v>
@@ -33840,9 +34129,11 @@
         <v>530</v>
       </c>
       <c r="P179" s="12" t="s">
-        <v>1306</v>
-      </c>
-      <c r="Q179" s="34"/>
+        <v>1290</v>
+      </c>
+      <c r="Q179" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R179" s="34" t="s">
         <v>103</v>
       </c>
@@ -33908,35 +34199,35 @@
         <v>369</v>
       </c>
       <c r="AL179" s="10" t="s">
-        <v>1308</v>
+        <v>1292</v>
       </c>
       <c r="AM179" s="11" t="s">
-        <v>1307</v>
+        <v>1291</v>
       </c>
       <c r="AN179" s="11"/>
       <c r="AO179" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP179" s="11" t="s">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="AQ179" s="11" t="s">
-        <v>1310</v>
+        <v>1294</v>
       </c>
       <c r="AR179" s="11">
         <v>50</v>
       </c>
       <c r="AS179" s="36" t="s">
-        <v>1410</v>
+        <v>1394</v>
       </c>
       <c r="AT179" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU179" s="11" t="s">
-        <v>1311</v>
+        <v>1295</v>
       </c>
       <c r="AV179" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW179" s="14"/>
       <c r="AX179" s="44">
@@ -33960,7 +34251,7 @@
         <v>75</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>1313</v>
+        <v>1297</v>
       </c>
       <c r="E180" s="26">
         <v>75016</v>
@@ -33974,7 +34265,7 @@
 75016 - Paris</v>
       </c>
       <c r="H180" s="15" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
       <c r="I180" s="12" t="s">
         <v>45</v>
@@ -33994,9 +34285,11 @@
         <v>187</v>
       </c>
       <c r="P180" s="12" t="s">
-        <v>1315</v>
-      </c>
-      <c r="Q180" s="34"/>
+        <v>1299</v>
+      </c>
+      <c r="Q180" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R180" s="34" t="s">
         <v>103</v>
       </c>
@@ -34062,35 +34355,35 @@
         <v>369</v>
       </c>
       <c r="AL180" s="10" t="s">
-        <v>1319</v>
+        <v>1303</v>
       </c>
       <c r="AM180" s="11" t="s">
-        <v>1373</v>
+        <v>1357</v>
       </c>
       <c r="AN180" s="11"/>
       <c r="AO180" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP180" s="11" t="s">
-        <v>1317</v>
+        <v>1301</v>
       </c>
       <c r="AQ180" s="11" t="s">
-        <v>1318</v>
+        <v>1302</v>
       </c>
       <c r="AR180" s="11">
         <v>51</v>
       </c>
       <c r="AS180" s="36" t="s">
-        <v>1411</v>
+        <v>1395</v>
       </c>
       <c r="AT180" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU180" s="11" t="s">
-        <v>1316</v>
+        <v>1300</v>
       </c>
       <c r="AV180" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW180" s="14"/>
       <c r="AX180" s="44">
@@ -34114,7 +34407,7 @@
         <v>75</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>1320</v>
+        <v>1304</v>
       </c>
       <c r="E181" s="26">
         <v>75014</v>
@@ -34128,7 +34421,7 @@
 75014 - Paris</v>
       </c>
       <c r="H181" s="15" t="s">
-        <v>1321</v>
+        <v>1305</v>
       </c>
       <c r="I181" s="12" t="s">
         <v>45</v>
@@ -34148,9 +34441,11 @@
         <v>59</v>
       </c>
       <c r="P181" s="12" t="s">
-        <v>1322</v>
-      </c>
-      <c r="Q181" s="34"/>
+        <v>1306</v>
+      </c>
+      <c r="Q181" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R181" s="34" t="s">
         <v>103</v>
       </c>
@@ -34214,35 +34509,35 @@
       </c>
       <c r="AK181" s="10"/>
       <c r="AL181" s="10" t="s">
-        <v>1326</v>
+        <v>1310</v>
       </c>
       <c r="AM181" s="11" t="s">
-        <v>1374</v>
+        <v>1358</v>
       </c>
       <c r="AN181" s="11"/>
       <c r="AO181" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP181" s="11" t="s">
-        <v>1324</v>
+        <v>1308</v>
       </c>
       <c r="AQ181" s="11" t="s">
-        <v>1325</v>
+        <v>1309</v>
       </c>
       <c r="AR181" s="11">
         <v>52</v>
       </c>
       <c r="AS181" s="36" t="s">
-        <v>1412</v>
+        <v>1396</v>
       </c>
       <c r="AT181" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU181" s="11" t="s">
-        <v>1323</v>
+        <v>1307</v>
       </c>
       <c r="AV181" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW181" s="14"/>
       <c r="AX181" s="44">
@@ -34266,7 +34561,7 @@
         <v>75</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="E182" s="26">
         <v>75020</v>
@@ -34280,7 +34575,7 @@
 75020 - Paris</v>
       </c>
       <c r="H182" s="15" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
       <c r="I182" s="12" t="s">
         <v>45</v>
@@ -34302,7 +34597,9 @@
       <c r="P182" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="Q182" s="34"/>
+      <c r="Q182" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R182" s="34" t="s">
         <v>103</v>
       </c>
@@ -34366,7 +34663,7 @@
       </c>
       <c r="AK182" s="10"/>
       <c r="AL182" s="10" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
       <c r="AM182" s="11"/>
       <c r="AN182" s="11"/>
@@ -34374,25 +34671,25 @@
         <v>367</v>
       </c>
       <c r="AP182" s="11" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="AQ182" s="11" t="s">
-        <v>1330</v>
+        <v>1314</v>
       </c>
       <c r="AR182" s="11">
         <v>53</v>
       </c>
       <c r="AS182" s="36" t="s">
-        <v>1413</v>
+        <v>1397</v>
       </c>
       <c r="AT182" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU182" s="11" t="s">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="AV182" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW182" s="14"/>
       <c r="AX182" s="44">
@@ -34416,7 +34713,7 @@
         <v>75</v>
       </c>
       <c r="D183" s="10" t="s">
-        <v>1333</v>
+        <v>1317</v>
       </c>
       <c r="E183" s="26">
         <v>75017</v>
@@ -34430,7 +34727,7 @@
 75017 - Paris</v>
       </c>
       <c r="H183" s="15" t="s">
-        <v>1334</v>
+        <v>1318</v>
       </c>
       <c r="I183" s="12" t="s">
         <v>45</v>
@@ -34452,7 +34749,9 @@
       <c r="P183" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="Q183" s="34"/>
+      <c r="Q183" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R183" s="34" t="s">
         <v>103</v>
       </c>
@@ -34516,35 +34815,35 @@
       </c>
       <c r="AK183" s="10"/>
       <c r="AL183" s="10" t="s">
-        <v>1337</v>
+        <v>1321</v>
       </c>
       <c r="AM183" s="11" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
       <c r="AN183" s="11"/>
       <c r="AO183" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP183" s="11" t="s">
-        <v>1358</v>
+        <v>1342</v>
       </c>
       <c r="AQ183" s="11" t="s">
-        <v>1359</v>
+        <v>1343</v>
       </c>
       <c r="AR183" s="11">
         <v>54</v>
       </c>
       <c r="AS183" s="36" t="s">
-        <v>1414</v>
+        <v>1398</v>
       </c>
       <c r="AT183" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU183" s="11" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="AV183" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW183" s="14"/>
       <c r="AX183" s="44">
@@ -34568,7 +34867,7 @@
         <v>92</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>1338</v>
+        <v>1322</v>
       </c>
       <c r="E184" s="26">
         <v>92100</v>
@@ -34582,7 +34881,7 @@
 92100 - Boulogne-Billancourt</v>
       </c>
       <c r="H184" s="15" t="s">
-        <v>1339</v>
+        <v>1323</v>
       </c>
       <c r="I184" s="12" t="s">
         <v>45</v>
@@ -34602,9 +34901,11 @@
         <v>141</v>
       </c>
       <c r="P184" s="12" t="s">
-        <v>1345</v>
-      </c>
-      <c r="Q184" s="34"/>
+        <v>1329</v>
+      </c>
+      <c r="Q184" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R184" s="34" t="s">
         <v>103</v>
       </c>
@@ -34670,35 +34971,35 @@
         <v>368</v>
       </c>
       <c r="AL184" s="10" t="s">
-        <v>1378</v>
+        <v>1362</v>
       </c>
       <c r="AM184" s="11" t="s">
-        <v>1377</v>
+        <v>1361</v>
       </c>
       <c r="AN184" s="11"/>
       <c r="AO184" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP184" s="11" t="s">
-        <v>1357</v>
+        <v>1341</v>
       </c>
       <c r="AQ184" s="11" t="s">
-        <v>1356</v>
+        <v>1340</v>
       </c>
       <c r="AR184" s="11">
         <v>55</v>
       </c>
       <c r="AS184" s="36" t="s">
-        <v>1415</v>
+        <v>1399</v>
       </c>
       <c r="AT184" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU184" s="11" t="s">
-        <v>1340</v>
+        <v>1324</v>
       </c>
       <c r="AV184" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW184" s="14"/>
       <c r="AX184" s="44">
@@ -34722,13 +35023,13 @@
         <v>62</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>1342</v>
+        <v>1326</v>
       </c>
       <c r="E185" s="26">
         <v>62520</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>1343</v>
+        <v>1327</v>
       </c>
       <c r="G185" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -34736,7 +35037,7 @@
 62520 - Le Touquet-Paris-Plage</v>
       </c>
       <c r="H185" s="15" t="s">
-        <v>1341</v>
+        <v>1325</v>
       </c>
       <c r="I185" s="12" t="s">
         <v>45</v>
@@ -34756,9 +35057,11 @@
         <v>86</v>
       </c>
       <c r="P185" s="12" t="s">
-        <v>1344</v>
-      </c>
-      <c r="Q185" s="34"/>
+        <v>1328</v>
+      </c>
+      <c r="Q185" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R185" s="34" t="s">
         <v>103</v>
       </c>
@@ -34824,35 +35127,35 @@
         <v>369</v>
       </c>
       <c r="AL185" s="10" t="s">
-        <v>1379</v>
+        <v>1363</v>
       </c>
       <c r="AM185" s="11" t="s">
-        <v>1375</v>
+        <v>1359</v>
       </c>
       <c r="AN185" s="11"/>
       <c r="AO185" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP185" s="11" t="s">
-        <v>1347</v>
+        <v>1331</v>
       </c>
       <c r="AQ185" s="11" t="s">
-        <v>1348</v>
+        <v>1332</v>
       </c>
       <c r="AR185" s="11">
         <v>56</v>
       </c>
       <c r="AS185" s="36" t="s">
-        <v>1416</v>
+        <v>1400</v>
       </c>
       <c r="AT185" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU185" s="11" t="s">
-        <v>1346</v>
+        <v>1330</v>
       </c>
       <c r="AV185" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW185" s="14"/>
       <c r="AX185" s="44">
@@ -34876,13 +35179,13 @@
         <v>21</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="E186" s="26">
         <v>21000</v>
       </c>
       <c r="F186" s="10" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
       <c r="G186" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -34890,7 +35193,7 @@
 21000 - Dijon</v>
       </c>
       <c r="H186" s="15" t="s">
-        <v>1351</v>
+        <v>1335</v>
       </c>
       <c r="I186" s="12" t="s">
         <v>45</v>
@@ -34910,9 +35213,11 @@
         <v>335</v>
       </c>
       <c r="P186" s="12" t="s">
-        <v>1352</v>
-      </c>
-      <c r="Q186" s="34"/>
+        <v>1336</v>
+      </c>
+      <c r="Q186" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R186" s="34" t="s">
         <v>103</v>
       </c>
@@ -34978,35 +35283,35 @@
         <v>369</v>
       </c>
       <c r="AL186" s="10" t="s">
-        <v>1380</v>
+        <v>1364</v>
       </c>
       <c r="AM186" s="11" t="s">
-        <v>1376</v>
+        <v>1360</v>
       </c>
       <c r="AN186" s="11"/>
       <c r="AO186" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP186" s="11" t="s">
-        <v>1355</v>
+        <v>1339</v>
       </c>
       <c r="AQ186" s="11" t="s">
-        <v>1354</v>
+        <v>1338</v>
       </c>
       <c r="AR186" s="11">
         <v>57</v>
       </c>
       <c r="AS186" s="36" t="s">
-        <v>1417</v>
+        <v>1401</v>
       </c>
       <c r="AT186" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU186" s="11" t="s">
-        <v>1353</v>
+        <v>1337</v>
       </c>
       <c r="AV186" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW186" s="14"/>
       <c r="AX186" s="44">
@@ -35030,13 +35335,13 @@
         <v>10</v>
       </c>
       <c r="D187" s="10" t="s">
-        <v>1360</v>
+        <v>1344</v>
       </c>
       <c r="E187" s="26">
         <v>10000</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>1361</v>
+        <v>1345</v>
       </c>
       <c r="G187" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -35044,7 +35349,7 @@
 10000 - Troyes</v>
       </c>
       <c r="H187" s="15" t="s">
-        <v>1362</v>
+        <v>1346</v>
       </c>
       <c r="I187" s="12" t="s">
         <v>45</v>
@@ -35064,9 +35369,11 @@
         <v>378</v>
       </c>
       <c r="P187" s="12" t="s">
-        <v>1363</v>
-      </c>
-      <c r="Q187" s="34"/>
+        <v>1347</v>
+      </c>
+      <c r="Q187" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R187" s="34" t="s">
         <v>103</v>
       </c>
@@ -35132,35 +35439,35 @@
         <v>369</v>
       </c>
       <c r="AL187" s="10" t="s">
-        <v>1381</v>
+        <v>1365</v>
       </c>
       <c r="AM187" s="11" t="s">
-        <v>1375</v>
+        <v>1359</v>
       </c>
       <c r="AN187" s="11"/>
       <c r="AO187" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP187" s="11" t="s">
-        <v>1365</v>
+        <v>1349</v>
       </c>
       <c r="AQ187" s="11" t="s">
-        <v>1366</v>
+        <v>1350</v>
       </c>
       <c r="AR187" s="11">
         <v>58</v>
       </c>
       <c r="AS187" s="36" t="s">
-        <v>1418</v>
+        <v>1402</v>
       </c>
       <c r="AT187" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU187" s="11" t="s">
-        <v>1364</v>
+        <v>1348</v>
       </c>
       <c r="AV187" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW187" s="14"/>
       <c r="AX187" s="44">
@@ -35184,7 +35491,7 @@
         <v>75</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>1367</v>
+        <v>1351</v>
       </c>
       <c r="E188" s="26">
         <v>75001</v>
@@ -35198,7 +35505,7 @@
 75001 - Paris</v>
       </c>
       <c r="H188" s="15" t="s">
-        <v>1368</v>
+        <v>1352</v>
       </c>
       <c r="I188" s="12" t="s">
         <v>45</v>
@@ -35218,9 +35525,11 @@
         <v>48</v>
       </c>
       <c r="P188" s="12" t="s">
-        <v>1369</v>
-      </c>
-      <c r="Q188" s="34"/>
+        <v>1353</v>
+      </c>
+      <c r="Q188" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R188" s="34" t="s">
         <v>103</v>
       </c>
@@ -35286,35 +35595,35 @@
         <v>368</v>
       </c>
       <c r="AL188" s="10" t="s">
-        <v>1382</v>
+        <v>1366</v>
       </c>
       <c r="AM188" s="11" t="s">
-        <v>1383</v>
+        <v>1367</v>
       </c>
       <c r="AN188" s="11"/>
       <c r="AO188" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP188" s="11" t="s">
-        <v>1371</v>
+        <v>1355</v>
       </c>
       <c r="AQ188" s="11" t="s">
-        <v>1372</v>
+        <v>1356</v>
       </c>
       <c r="AR188" s="11">
         <v>59</v>
       </c>
       <c r="AS188" s="36" t="s">
-        <v>1419</v>
+        <v>1403</v>
       </c>
       <c r="AT188" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU188" s="11" t="s">
-        <v>1370</v>
+        <v>1354</v>
       </c>
       <c r="AV188" s="13" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="AW188" s="14"/>
       <c r="AX188" s="44">
@@ -35338,21 +35647,22 @@
         <v>1</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>1388</v>
+        <v>1372</v>
       </c>
       <c r="E189" s="49" t="s">
-        <v>1386</v>
+        <v>1370</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>1387</v>
+        <v>1371</v>
       </c>
       <c r="G189" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;Tableau1[[#This Row],[Code Postal]]&amp;Tableau1[[#This Row],[Ville]]</f>
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Cap Émeraude
-Avenue du Capitaine Dhonne01 000Bourg-en-Bresse</v>
+Avenue du Capitaine Dhonne
+01 000 - Bourg-en-Bresse</v>
       </c>
       <c r="H189" s="15" t="s">
-        <v>1385</v>
+        <v>1369</v>
       </c>
       <c r="I189" s="12" t="s">
         <v>47</v>
@@ -35374,7 +35684,9 @@
       <c r="P189" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="Q189" s="34"/>
+      <c r="Q189" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R189" s="34" t="s">
         <v>103</v>
       </c>
@@ -35437,29 +35749,33 @@
       <c r="AI189" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="AJ189" s="10"/>
-      <c r="AK189" s="10"/>
+      <c r="AJ189" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK189" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="AL189" s="10" t="s">
-        <v>1392</v>
+        <v>1376</v>
       </c>
       <c r="AM189" s="11" t="s">
-        <v>1391</v>
+        <v>1375</v>
       </c>
       <c r="AN189" s="11"/>
       <c r="AO189" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP189" s="11" t="s">
-        <v>1389</v>
+        <v>1373</v>
       </c>
       <c r="AQ189" s="11" t="s">
-        <v>1390</v>
+        <v>1374</v>
       </c>
       <c r="AR189" s="11">
         <v>60</v>
       </c>
       <c r="AS189" s="36" t="s">
-        <v>1394</v>
+        <v>1378</v>
       </c>
       <c r="AT189" s="11" t="s">
         <v>75</v>
@@ -35468,7 +35784,7 @@
         <v>376</v>
       </c>
       <c r="AV189" s="13" t="s">
-        <v>1393</v>
+        <v>1377</v>
       </c>
       <c r="AW189" s="14"/>
       <c r="AX189" s="44">
@@ -35478,14 +35794,482 @@
       <c r="BG189"/>
       <c r="BH189" s="1"/>
     </row>
+    <row r="190" spans="1:60" ht="25.5">
+      <c r="A190" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B190" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Charente</v>
+      </c>
+      <c r="C190" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>16</v>
+      </c>
+      <c r="D190" s="10"/>
+      <c r="E190" s="26">
+        <v>16110</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G190" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v xml:space="preserve">
+16110 - Rivières</v>
+      </c>
+      <c r="H190" s="15" t="s">
+        <v>1416</v>
+      </c>
+      <c r="I190" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J190" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K190" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L190" s="10"/>
+      <c r="M190" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N190" s="36"/>
+      <c r="O190" s="34">
+        <v>700</v>
+      </c>
+      <c r="P190" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q190" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R190" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S190" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T190" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>105000</v>
+      </c>
+      <c r="U190" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>8750</v>
+      </c>
+      <c r="V190" s="12">
+        <v>150</v>
+      </c>
+      <c r="W190" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X190" s="12"/>
+      <c r="Y190" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z190" s="12"/>
+      <c r="AA190" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB190" s="12"/>
+      <c r="AC190" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD190" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE190" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>105000</v>
+      </c>
+      <c r="AF190" s="12" t="str">
+        <f t="shared" si="7"/>
+        <v>3 mois = 26 250 €</v>
+      </c>
+      <c r="AG190" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH190" s="46">
+        <v>0.03</v>
+      </c>
+      <c r="AI190" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ190" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK190" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL190" s="10" t="s">
+        <v>1418</v>
+      </c>
+      <c r="AM190" s="11" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AN190" s="11" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AO190" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP190" s="11" t="s">
+        <v>1421</v>
+      </c>
+      <c r="AQ190" s="11" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AR190" s="11">
+        <v>61</v>
+      </c>
+      <c r="AS190" s="36" t="s">
+        <v>1438</v>
+      </c>
+      <c r="AT190" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU190" s="11" t="s">
+        <v>1424</v>
+      </c>
+      <c r="AV190" s="13" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AW190" s="14"/>
+      <c r="AX190" s="44">
+        <v>46052</v>
+      </c>
+    </row>
+    <row r="191" spans="1:60" ht="38.25">
+      <c r="A191" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B191" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Pas-de-Calais</v>
+      </c>
+      <c r="C191" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>62</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E191" s="26">
+        <v>62217</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G191" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Boréal Parc
+rue de Bleuets
+62217 - Beaurains</v>
+      </c>
+      <c r="H191" s="15" t="s">
+        <v>1428</v>
+      </c>
+      <c r="I191" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J191" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K191" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L191" s="10"/>
+      <c r="M191" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N191" s="36"/>
+      <c r="O191" s="34">
+        <v>128</v>
+      </c>
+      <c r="P191" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q191" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R191" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S191" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T191" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>38400</v>
+      </c>
+      <c r="U191" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3200</v>
+      </c>
+      <c r="V191" s="12">
+        <v>300</v>
+      </c>
+      <c r="W191" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X191" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3584</v>
+      </c>
+      <c r="Y191" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>298.66666666666669</v>
+      </c>
+      <c r="Z191" s="12">
+        <v>28</v>
+      </c>
+      <c r="AA191" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1216</v>
+      </c>
+      <c r="AB191" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="AC191" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD191" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE191" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>43200</v>
+      </c>
+      <c r="AF191" s="12" t="str">
+        <f t="shared" ref="AF191:AF192" si="9">"3 mois = "&amp;TEXT(ROUND(3/12*T191,0),"### ### ##0 €")</f>
+        <v>3 mois = 9 600 €</v>
+      </c>
+      <c r="AG191" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH191" s="46">
+        <v>0.03</v>
+      </c>
+      <c r="AI191" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ191" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK191" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL191" s="10" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AM191" s="11" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AN191" s="11" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AO191" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP191" s="11" t="s">
+        <v>1432</v>
+      </c>
+      <c r="AQ191" s="11" t="s">
+        <v>1431</v>
+      </c>
+      <c r="AR191" s="11" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AS191" s="36" t="s">
+        <v>1439</v>
+      </c>
+      <c r="AT191" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU191" s="11" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AV191" s="13" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AW191" s="14"/>
+      <c r="AX191" s="44">
+        <v>46052</v>
+      </c>
+    </row>
+    <row r="192" spans="1:60" ht="38.25">
+      <c r="A192" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B192" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Pas-de-Calais</v>
+      </c>
+      <c r="C192" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>62</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E192" s="26">
+        <v>62217</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G192" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Boréal Parc
+rue de Bleuets
+62217 - Beaurains</v>
+      </c>
+      <c r="H192" s="15" t="s">
+        <v>1428</v>
+      </c>
+      <c r="I192" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J192" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K192" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L192" s="10"/>
+      <c r="M192" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N192" s="36"/>
+      <c r="O192" s="34">
+        <v>40</v>
+      </c>
+      <c r="P192" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q192" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R192" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S192" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T192" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>24000</v>
+      </c>
+      <c r="U192" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2000</v>
+      </c>
+      <c r="V192" s="12">
+        <v>600</v>
+      </c>
+      <c r="W192" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X192" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1120</v>
+      </c>
+      <c r="Y192" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>93.333333333333329</v>
+      </c>
+      <c r="Z192" s="12">
+        <v>28</v>
+      </c>
+      <c r="AA192" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>380</v>
+      </c>
+      <c r="AB192" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="AC192" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD192" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE192" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>25500</v>
+      </c>
+      <c r="AF192" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 6 000 €</v>
+      </c>
+      <c r="AG192" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH192" s="46">
+        <v>0.03</v>
+      </c>
+      <c r="AI192" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ192" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK192" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="AL192" s="10" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AM192" s="11" t="s">
+        <v>1437</v>
+      </c>
+      <c r="AN192" s="11" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AO192" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP192" s="11" t="s">
+        <v>1433</v>
+      </c>
+      <c r="AQ192" s="11" t="s">
+        <v>1434</v>
+      </c>
+      <c r="AR192" s="11" t="s">
+        <v>1423</v>
+      </c>
+      <c r="AS192" s="36" t="s">
+        <v>1440</v>
+      </c>
+      <c r="AT192" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU192" s="11"/>
+      <c r="AV192" s="13" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AW192" s="14"/>
+      <c r="AX192" s="44">
+        <v>46052</v>
+      </c>
+    </row>
     <row r="204" spans="6:6">
       <c r="F204" s="1" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="205" spans="6:6">
       <c r="F205" s="1" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
     </row>
   </sheetData>
@@ -35642,6 +36426,9 @@
     <hyperlink ref="H189" r:id="rId149" xr:uid="{6D139DEB-1BCB-45F1-9FA5-40A114985687}"/>
     <hyperlink ref="H139" r:id="rId150" xr:uid="{069CCB02-48CE-4D86-8BBE-DFAEAC941704}"/>
     <hyperlink ref="H180" r:id="rId151" xr:uid="{3FF7903C-E5BA-4ED9-88DD-9F4AF755FB57}"/>
+    <hyperlink ref="H190" r:id="rId152" xr:uid="{B58FC76B-D0FB-47D2-9309-07FBB7AE8F26}"/>
+    <hyperlink ref="H191" r:id="rId153" xr:uid="{5ACAB395-A666-4978-812B-9B6039F53703}"/>
+    <hyperlink ref="H192" r:id="rId154" xr:uid="{21A42A74-18EE-46BA-BF13-26B8D1F6FB47}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -35650,7 +36437,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId152"/>
+    <tablePart r:id="rId155"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EF4A99-C005-42E2-A1BA-892473E4438F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADB663D-8109-4D60-9A66-F493525EE4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5767" uniqueCount="1451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6321" uniqueCount="1544">
   <si>
     <t>Contact</t>
   </si>
@@ -4401,6 +4401,286 @@
   </si>
   <si>
     <t>Local situé dans la Patte d'Oie d'Herblay. 60M de flux annuel.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RJ2QRVrW96tKL7ur6</t>
+  </si>
+  <si>
+    <t>Centre commercial Boisseuil
+Route de Toulouse</t>
+  </si>
+  <si>
+    <t>Boisseuil</t>
+  </si>
+  <si>
+    <t>3 bis</t>
+  </si>
+  <si>
+    <t>11 bis</t>
+  </si>
+  <si>
+    <t>16 bis</t>
+  </si>
+  <si>
+    <t>16 ter</t>
+  </si>
+  <si>
+    <t>24 bis</t>
+  </si>
+  <si>
+    <t>29 bis</t>
+  </si>
+  <si>
+    <t>30 bis</t>
+  </si>
+  <si>
+    <t>30 ter</t>
+  </si>
+  <si>
+    <t>31 bis</t>
+  </si>
+  <si>
+    <t>39 bis</t>
+  </si>
+  <si>
+    <t>K56</t>
+  </si>
+  <si>
+    <t>140 + 94 (réserve)</t>
+  </si>
+  <si>
+    <t>45 + 9 (réserve)</t>
+  </si>
+  <si>
+    <t>390 + 78 (réserve)</t>
+  </si>
+  <si>
+    <t>30 + 18 (réserve)</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RJ2QRVrW96tKL7ur7</t>
+  </si>
+  <si>
+    <t>63.1</t>
+  </si>
+  <si>
+    <t>63.2</t>
+  </si>
+  <si>
+    <t>63.3</t>
+  </si>
+  <si>
+    <t>63.4</t>
+  </si>
+  <si>
+    <t>63.5</t>
+  </si>
+  <si>
+    <t>63.6</t>
+  </si>
+  <si>
+    <t>63.7</t>
+  </si>
+  <si>
+    <t>63.8</t>
+  </si>
+  <si>
+    <t>63.9</t>
+  </si>
+  <si>
+    <t>63.10</t>
+  </si>
+  <si>
+    <t>63.11</t>
+  </si>
+  <si>
+    <t>63.12</t>
+  </si>
+  <si>
+    <t>63.13</t>
+  </si>
+  <si>
+    <t>63.14</t>
+  </si>
+  <si>
+    <t>63.15</t>
+  </si>
+  <si>
+    <t>63.16</t>
+  </si>
+  <si>
+    <t>63.17</t>
+  </si>
+  <si>
+    <t>63.18</t>
+  </si>
+  <si>
+    <t>63.19</t>
+  </si>
+  <si>
+    <t>63.20</t>
+  </si>
+  <si>
+    <t>63.21</t>
+  </si>
+  <si>
+    <t>63.22</t>
+  </si>
+  <si>
+    <t>Fnac, Sephora, JD, Jules, Histoire d'Or, Promod, Nocibé</t>
+  </si>
+  <si>
+    <t>45.777644</t>
+  </si>
+  <si>
+    <t>45.777648</t>
+  </si>
+  <si>
+    <t>1.3079232</t>
+  </si>
+  <si>
+    <t>45.777587</t>
+  </si>
+  <si>
+    <t>1.307970</t>
+  </si>
+  <si>
+    <t>45.778069</t>
+  </si>
+  <si>
+    <t>1.308084</t>
+  </si>
+  <si>
+    <t>45.778001</t>
+  </si>
+  <si>
+    <t>1.308245</t>
+  </si>
+  <si>
+    <t>15 ter</t>
+  </si>
+  <si>
+    <t>Flux annuel : 2,5M. Centre commercial au sud de Limoges avec un hypermarché à 60 M€ hors essence, dans une zone commercial Retail Park avec Kiabi, King Jouet, Aldi, Chaussea, McDonald's…</t>
+  </si>
+  <si>
+    <t>63.23</t>
+  </si>
+  <si>
+    <t>45.777693</t>
+  </si>
+  <si>
+    <t>1.308492</t>
+  </si>
+  <si>
+    <t>1.308529</t>
+  </si>
+  <si>
+    <t>45.777624</t>
+  </si>
+  <si>
+    <t>1.308347</t>
+  </si>
+  <si>
+    <t>45.777803</t>
+  </si>
+  <si>
+    <t>1.308585</t>
+  </si>
+  <si>
+    <t>45.778245</t>
+  </si>
+  <si>
+    <t>1.308796</t>
+  </si>
+  <si>
+    <t>45.778275</t>
+  </si>
+  <si>
+    <t>1.308923</t>
+  </si>
+  <si>
+    <t>45.778260</t>
+  </si>
+  <si>
+    <t>1.309398</t>
+  </si>
+  <si>
+    <t>45.778192</t>
+  </si>
+  <si>
+    <t>1.309527</t>
+  </si>
+  <si>
+    <t>45.778097</t>
+  </si>
+  <si>
+    <t>1.309610</t>
+  </si>
+  <si>
+    <t>45.778067</t>
+  </si>
+  <si>
+    <t>1.309519</t>
+  </si>
+  <si>
+    <t>45.778052</t>
+  </si>
+  <si>
+    <t>1.309436</t>
+  </si>
+  <si>
+    <t>45.778045</t>
+  </si>
+  <si>
+    <t>1.309369</t>
+  </si>
+  <si>
+    <t>45.777932</t>
+  </si>
+  <si>
+    <t>1.309036</t>
+  </si>
+  <si>
+    <t>45.778342</t>
+  </si>
+  <si>
+    <t>1.309653</t>
+  </si>
+  <si>
+    <t>45.778445</t>
+  </si>
+  <si>
+    <t>1.309210</t>
+  </si>
+  <si>
+    <t>45.778274</t>
+  </si>
+  <si>
+    <t>1.308592</t>
+  </si>
+  <si>
+    <t>45.778189</t>
+  </si>
+  <si>
+    <t>1.308502</t>
+  </si>
+  <si>
+    <t>45.778145</t>
+  </si>
+  <si>
+    <t>1.308445</t>
+  </si>
+  <si>
+    <t>45.777951</t>
+  </si>
+  <si>
+    <t>1.309564</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/5%20Plan%20du%20centre.jpg</t>
   </si>
 </sst>
 </file>
@@ -5062,14 +5342,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX192" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AX192" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="/"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX215" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AX215" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="50">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="49" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -5464,7 +5738,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BH205"/>
+  <dimension ref="A1:BH227"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -5501,7 +5775,8 @@
     <col min="37" max="37" width="11.25" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9.625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="64.5" style="1" customWidth="1"/>
-    <col min="40" max="41" width="53.875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="53.875" style="1" customWidth="1"/>
+    <col min="41" max="41" width="50.25" style="1" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="41.5" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="17.625" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="19.25" style="1" bestFit="1" customWidth="1"/>
@@ -28989,9 +29264,15 @@
       <c r="AH147" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AI147" s="12"/>
-      <c r="AJ147" s="10"/>
-      <c r="AK147" s="10"/>
+      <c r="AI147" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ147" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK147" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="AL147" s="10"/>
       <c r="AM147" s="11" t="s">
         <v>1039</v>
@@ -30166,7 +30447,7 @@
       <c r="BG154"/>
       <c r="BH154" s="1"/>
     </row>
-    <row r="155" spans="1:60" ht="38.25" hidden="1">
+    <row r="155" spans="1:60" ht="38.25">
       <c r="A155" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -30326,7 +30607,7 @@
       <c r="BG155"/>
       <c r="BH155" s="1"/>
     </row>
-    <row r="156" spans="1:60" ht="38.25" hidden="1">
+    <row r="156" spans="1:60" ht="38.25">
       <c r="A156" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -30486,7 +30767,7 @@
       <c r="BG156"/>
       <c r="BH156" s="1"/>
     </row>
-    <row r="157" spans="1:60" ht="38.25" hidden="1">
+    <row r="157" spans="1:60" ht="38.25">
       <c r="A157" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Provence-Alpes-Côte d'Azur</v>
@@ -34505,9 +34786,11 @@
         <v>363</v>
       </c>
       <c r="AJ181" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="AK181" s="10"/>
+        <v>53</v>
+      </c>
+      <c r="AK181" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="AL181" s="10" t="s">
         <v>1310</v>
       </c>
@@ -34659,9 +34942,11 @@
         <v>363</v>
       </c>
       <c r="AJ182" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="AK182" s="10"/>
+        <v>53</v>
+      </c>
+      <c r="AK182" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="AL182" s="10" t="s">
         <v>1316</v>
       </c>
@@ -34811,9 +35096,11 @@
         <v>363</v>
       </c>
       <c r="AJ183" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="AK183" s="10"/>
+        <v>53</v>
+      </c>
+      <c r="AK183" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="AL183" s="10" t="s">
         <v>1321</v>
       </c>
@@ -36048,7 +36335,7 @@
         <v>43200</v>
       </c>
       <c r="AF191" s="12" t="str">
-        <f t="shared" ref="AF191:AF192" si="9">"3 mois = "&amp;TEXT(ROUND(3/12*T191,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AF191:AF215" si="9">"3 mois = "&amp;TEXT(ROUND(3/12*T191,0),"### ### ##0 €")</f>
         <v>3 mois = 9 600 €</v>
       </c>
       <c r="AG191" s="6" t="s">
@@ -36262,13 +36549,3499 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="204" spans="6:6">
-      <c r="F204" s="1" t="s">
+    <row r="193" spans="1:50" ht="38.25">
+      <c r="A193" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B193" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C193" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D193" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E193" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G193" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H193" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I193" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J193" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K193" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L193" s="10"/>
+      <c r="M193" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N193" s="36" t="s">
+        <v>1454</v>
+      </c>
+      <c r="O193" s="34">
+        <v>234</v>
+      </c>
+      <c r="P193" s="12" t="s">
+        <v>1465</v>
+      </c>
+      <c r="Q193" s="34">
+        <v>454</v>
+      </c>
+      <c r="R193" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S193" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T193" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>98280</v>
+      </c>
+      <c r="U193" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>8190</v>
+      </c>
+      <c r="V193" s="12">
+        <v>420</v>
+      </c>
+      <c r="W193" s="12"/>
+      <c r="X193" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>16380</v>
+      </c>
+      <c r="Y193" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1365</v>
+      </c>
+      <c r="Z193" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA193" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3744</v>
+      </c>
+      <c r="AB193" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC193" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>8658</v>
+      </c>
+      <c r="AD193" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE193" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>127062</v>
+      </c>
+      <c r="AF193" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 24 570 €</v>
+      </c>
+      <c r="AG193" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH193" s="12"/>
+      <c r="AI193" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ193" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK193" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL193" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM193" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN193" s="11"/>
+      <c r="AO193" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP193" s="11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="AQ193" s="11" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AR193" s="11" t="s">
+        <v>1471</v>
+      </c>
+      <c r="AS193" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT193" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU193" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV193" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW193" s="14"/>
+      <c r="AX193" s="44"/>
+    </row>
+    <row r="194" spans="1:50" ht="38.25">
+      <c r="A194" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B194" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C194" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D194" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E194" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G194" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H194" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I194" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J194" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K194" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L194" s="10"/>
+      <c r="M194" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N194" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="O194" s="34">
+        <v>220</v>
+      </c>
+      <c r="P194" s="12"/>
+      <c r="Q194" s="34">
+        <v>454</v>
+      </c>
+      <c r="R194" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S194" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T194" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>92400</v>
+      </c>
+      <c r="U194" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>7700</v>
+      </c>
+      <c r="V194" s="12">
+        <v>420</v>
+      </c>
+      <c r="W194" s="12"/>
+      <c r="X194" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>15400</v>
+      </c>
+      <c r="Y194" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1283.3333333333333</v>
+      </c>
+      <c r="Z194" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA194" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3520</v>
+      </c>
+      <c r="AB194" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC194" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>8140</v>
+      </c>
+      <c r="AD194" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE194" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>119460</v>
+      </c>
+      <c r="AF194" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 23 100 €</v>
+      </c>
+      <c r="AG194" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH194" s="12"/>
+      <c r="AI194" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ194" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK194" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL194" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM194" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN194" s="11"/>
+      <c r="AO194" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP194" s="11" t="s">
+        <v>1497</v>
+      </c>
+      <c r="AQ194" s="11" t="s">
+        <v>1498</v>
+      </c>
+      <c r="AR194" s="11" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AS194" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT194" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU194" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV194" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW194" s="14"/>
+      <c r="AX194" s="44"/>
+    </row>
+    <row r="195" spans="1:50" ht="38.25">
+      <c r="A195" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B195" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C195" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D195" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E195" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G195" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H195" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I195" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J195" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K195" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L195" s="10"/>
+      <c r="M195" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N195" s="36" t="s">
+        <v>1455</v>
+      </c>
+      <c r="O195" s="34">
+        <v>105</v>
+      </c>
+      <c r="P195" s="12"/>
+      <c r="Q195" s="34">
+        <v>222</v>
+      </c>
+      <c r="R195" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S195" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T195" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>31500</v>
+      </c>
+      <c r="U195" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2625</v>
+      </c>
+      <c r="V195" s="12">
+        <v>300</v>
+      </c>
+      <c r="W195" s="12"/>
+      <c r="X195" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>7350</v>
+      </c>
+      <c r="Y195" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>612.5</v>
+      </c>
+      <c r="Z195" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA195" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1680</v>
+      </c>
+      <c r="AB195" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC195" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3885</v>
+      </c>
+      <c r="AD195" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE195" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>44415</v>
+      </c>
+      <c r="AF195" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 7 875 €</v>
+      </c>
+      <c r="AG195" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH195" s="12"/>
+      <c r="AI195" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ195" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK195" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL195" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM195" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN195" s="11"/>
+      <c r="AO195" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP195" s="11" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AQ195" s="11" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AR195" s="11" t="s">
+        <v>1473</v>
+      </c>
+      <c r="AS195" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT195" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU195" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV195" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW195" s="14"/>
+      <c r="AX195" s="44"/>
+    </row>
+    <row r="196" spans="1:50" ht="38.25">
+      <c r="A196" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B196" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C196" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D196" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E196" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G196" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H196" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I196" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J196" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K196" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L196" s="10"/>
+      <c r="M196" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N196" s="36">
+        <v>12</v>
+      </c>
+      <c r="O196" s="34">
+        <v>117</v>
+      </c>
+      <c r="P196" s="12"/>
+      <c r="Q196" s="34">
+        <v>222</v>
+      </c>
+      <c r="R196" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S196" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T196" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>46800</v>
+      </c>
+      <c r="U196" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3900</v>
+      </c>
+      <c r="V196" s="12">
+        <v>400</v>
+      </c>
+      <c r="W196" s="12"/>
+      <c r="X196" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>8190</v>
+      </c>
+      <c r="Y196" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>682.5</v>
+      </c>
+      <c r="Z196" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA196" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1872</v>
+      </c>
+      <c r="AB196" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC196" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>4329</v>
+      </c>
+      <c r="AD196" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE196" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>61191</v>
+      </c>
+      <c r="AF196" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 11 700 €</v>
+      </c>
+      <c r="AG196" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH196" s="12"/>
+      <c r="AI196" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ196" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK196" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL196" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM196" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN196" s="11"/>
+      <c r="AO196" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP196" s="11" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AQ196" s="11" t="s">
+        <v>1502</v>
+      </c>
+      <c r="AR196" s="11" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AS196" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT196" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU196" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV196" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW196" s="14"/>
+      <c r="AX196" s="44"/>
+    </row>
+    <row r="197" spans="1:50" ht="38.25">
+      <c r="A197" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B197" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C197" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D197" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E197" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F197" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G197" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H197" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J197" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K197" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L197" s="10"/>
+      <c r="M197" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N197" s="36" t="s">
+        <v>1503</v>
+      </c>
+      <c r="O197" s="34">
+        <v>124</v>
+      </c>
+      <c r="P197" s="12"/>
+      <c r="Q197" s="34">
+        <v>209</v>
+      </c>
+      <c r="R197" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S197" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T197" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>64480</v>
+      </c>
+      <c r="U197" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5373.333333333333</v>
+      </c>
+      <c r="V197" s="12">
+        <v>520</v>
+      </c>
+      <c r="W197" s="12"/>
+      <c r="X197" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>8680</v>
+      </c>
+      <c r="Y197" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>723.33333333333337</v>
+      </c>
+      <c r="Z197" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA197" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1984</v>
+      </c>
+      <c r="AB197" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC197" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>4588</v>
+      </c>
+      <c r="AD197" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE197" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>79732</v>
+      </c>
+      <c r="AF197" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 16 120 €</v>
+      </c>
+      <c r="AG197" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH197" s="12"/>
+      <c r="AI197" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ197" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK197" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL197" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM197" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN197" s="11"/>
+      <c r="AO197" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP197" s="11" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AQ197" s="11" t="s">
+        <v>1507</v>
+      </c>
+      <c r="AR197" s="11" t="s">
+        <v>1475</v>
+      </c>
+      <c r="AS197" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT197" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU197" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV197" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW197" s="14"/>
+      <c r="AX197" s="44"/>
+    </row>
+    <row r="198" spans="1:50" ht="38.25">
+      <c r="A198" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B198" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C198" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E198" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G198" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H198" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I198" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J198" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K198" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L198" s="10"/>
+      <c r="M198" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N198" s="36" t="s">
+        <v>1456</v>
+      </c>
+      <c r="O198" s="34">
+        <v>54</v>
+      </c>
+      <c r="P198" s="12" t="s">
+        <v>1466</v>
+      </c>
+      <c r="Q198" s="34">
+        <v>209</v>
+      </c>
+      <c r="R198" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S198" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T198" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>28080</v>
+      </c>
+      <c r="U198" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2340</v>
+      </c>
+      <c r="V198" s="12">
+        <v>520</v>
+      </c>
+      <c r="W198" s="12"/>
+      <c r="X198" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3780</v>
+      </c>
+      <c r="Y198" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>315</v>
+      </c>
+      <c r="Z198" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA198" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>864</v>
+      </c>
+      <c r="AB198" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC198" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1998</v>
+      </c>
+      <c r="AD198" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE198" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>34722</v>
+      </c>
+      <c r="AF198" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 7 020 €</v>
+      </c>
+      <c r="AG198" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH198" s="12"/>
+      <c r="AI198" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ198" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK198" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL198" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM198" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN198" s="11"/>
+      <c r="AO198" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP198" s="11" t="s">
+        <v>1495</v>
+      </c>
+      <c r="AQ198" s="11" t="s">
+        <v>1508</v>
+      </c>
+      <c r="AR198" s="11" t="s">
+        <v>1476</v>
+      </c>
+      <c r="AS198" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT198" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU198" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV198" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW198" s="14"/>
+      <c r="AX198" s="44"/>
+    </row>
+    <row r="199" spans="1:50" ht="38.25">
+      <c r="A199" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B199" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C199" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D199" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E199" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G199" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H199" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I199" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J199" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K199" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L199" s="10"/>
+      <c r="M199" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N199" s="36" t="s">
+        <v>1457</v>
+      </c>
+      <c r="O199" s="34">
+        <v>31</v>
+      </c>
+      <c r="P199" s="12"/>
+      <c r="Q199" s="34">
+        <v>209</v>
+      </c>
+      <c r="R199" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S199" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T199" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>16120</v>
+      </c>
+      <c r="U199" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1343.3333333333333</v>
+      </c>
+      <c r="V199" s="12">
+        <v>520</v>
+      </c>
+      <c r="W199" s="12"/>
+      <c r="X199" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2170</v>
+      </c>
+      <c r="Y199" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>180.83333333333334</v>
+      </c>
+      <c r="Z199" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA199" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>496</v>
+      </c>
+      <c r="AB199" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC199" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1147</v>
+      </c>
+      <c r="AD199" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE199" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>19933</v>
+      </c>
+      <c r="AF199" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 4 030 €</v>
+      </c>
+      <c r="AG199" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH199" s="12"/>
+      <c r="AI199" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ199" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK199" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL199" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM199" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN199" s="11"/>
+      <c r="AO199" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP199" s="11" t="s">
+        <v>1509</v>
+      </c>
+      <c r="AQ199" s="11" t="s">
+        <v>1510</v>
+      </c>
+      <c r="AR199" s="11" t="s">
+        <v>1477</v>
+      </c>
+      <c r="AS199" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT199" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU199" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV199" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW199" s="14"/>
+      <c r="AX199" s="44"/>
+    </row>
+    <row r="200" spans="1:50" ht="38.25">
+      <c r="A200" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B200" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C200" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D200" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E200" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G200" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H200" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I200" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J200" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K200" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L200" s="10"/>
+      <c r="M200" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N200" s="36" t="s">
+        <v>610</v>
+      </c>
+      <c r="O200" s="34">
+        <v>77</v>
+      </c>
+      <c r="P200" s="12"/>
+      <c r="Q200" s="34"/>
+      <c r="R200" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S200" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T200" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>34650</v>
+      </c>
+      <c r="U200" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2887.5</v>
+      </c>
+      <c r="V200" s="12">
+        <v>450</v>
+      </c>
+      <c r="W200" s="12"/>
+      <c r="X200" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>5390</v>
+      </c>
+      <c r="Y200" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>449.16666666666669</v>
+      </c>
+      <c r="Z200" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA200" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1232</v>
+      </c>
+      <c r="AB200" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC200" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2849</v>
+      </c>
+      <c r="AD200" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE200" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>44121</v>
+      </c>
+      <c r="AF200" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 8 663 €</v>
+      </c>
+      <c r="AG200" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH200" s="12"/>
+      <c r="AI200" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ200" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK200" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL200" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM200" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN200" s="11"/>
+      <c r="AO200" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP200" s="11" t="s">
+        <v>1511</v>
+      </c>
+      <c r="AQ200" s="11" t="s">
+        <v>1512</v>
+      </c>
+      <c r="AR200" s="11" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AS200" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT200" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU200" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV200" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW200" s="14"/>
+      <c r="AX200" s="44"/>
+    </row>
+    <row r="201" spans="1:50" ht="38.25">
+      <c r="A201" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B201" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C201" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E201" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G201" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H201" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I201" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J201" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K201" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L201" s="10"/>
+      <c r="M201" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N201" s="36">
+        <v>23</v>
+      </c>
+      <c r="O201" s="34">
+        <v>151</v>
+      </c>
+      <c r="P201" s="12"/>
+      <c r="Q201" s="34">
+        <v>454</v>
+      </c>
+      <c r="R201" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S201" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T201" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>52850</v>
+      </c>
+      <c r="U201" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4404.166666666667</v>
+      </c>
+      <c r="V201" s="12">
+        <v>350</v>
+      </c>
+      <c r="W201" s="12"/>
+      <c r="X201" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>10570</v>
+      </c>
+      <c r="Y201" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>880.83333333333337</v>
+      </c>
+      <c r="Z201" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA201" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2416</v>
+      </c>
+      <c r="AB201" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC201" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>5587</v>
+      </c>
+      <c r="AD201" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE201" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>71423</v>
+      </c>
+      <c r="AF201" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 13 213 €</v>
+      </c>
+      <c r="AG201" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH201" s="12"/>
+      <c r="AI201" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ201" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK201" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL201" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM201" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN201" s="11"/>
+      <c r="AO201" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP201" s="11" t="s">
+        <v>1513</v>
+      </c>
+      <c r="AQ201" s="11" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AR201" s="11" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AS201" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT201" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU201" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV201" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW201" s="14"/>
+      <c r="AX201" s="44"/>
+    </row>
+    <row r="202" spans="1:50" ht="38.25">
+      <c r="A202" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B202" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C202" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E202" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G202" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H202" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I202" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J202" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K202" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L202" s="10"/>
+      <c r="M202" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N202" s="36">
+        <v>25</v>
+      </c>
+      <c r="O202" s="34">
+        <v>303</v>
+      </c>
+      <c r="P202" s="12"/>
+      <c r="Q202" s="34">
+        <v>454</v>
+      </c>
+      <c r="R202" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S202" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T202" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>106050</v>
+      </c>
+      <c r="U202" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>8837.5</v>
+      </c>
+      <c r="V202" s="12">
+        <v>350</v>
+      </c>
+      <c r="W202" s="12"/>
+      <c r="X202" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>21210</v>
+      </c>
+      <c r="Y202" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1767.5</v>
+      </c>
+      <c r="Z202" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA202" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>4848</v>
+      </c>
+      <c r="AB202" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC202" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>11211</v>
+      </c>
+      <c r="AD202" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE202" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>143319</v>
+      </c>
+      <c r="AF202" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 26 513 €</v>
+      </c>
+      <c r="AG202" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH202" s="12"/>
+      <c r="AI202" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ202" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK202" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL202" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM202" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN202" s="11"/>
+      <c r="AO202" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP202" s="11" t="s">
+        <v>1515</v>
+      </c>
+      <c r="AQ202" s="11" t="s">
+        <v>1516</v>
+      </c>
+      <c r="AR202" s="11" t="s">
+        <v>1480</v>
+      </c>
+      <c r="AS202" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT202" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU202" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV202" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW202" s="14"/>
+      <c r="AX202" s="44"/>
+    </row>
+    <row r="203" spans="1:50" ht="38.25">
+      <c r="A203" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B203" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C203" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E203" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G203" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H203" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I203" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J203" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K203" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L203" s="10"/>
+      <c r="M203" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N203" s="36" t="s">
+        <v>1458</v>
+      </c>
+      <c r="O203" s="34">
+        <v>185</v>
+      </c>
+      <c r="P203" s="12"/>
+      <c r="Q203" s="34"/>
+      <c r="R203" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S203" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T203" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>62900</v>
+      </c>
+      <c r="U203" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5241.666666666667</v>
+      </c>
+      <c r="V203" s="12">
+        <v>340</v>
+      </c>
+      <c r="W203" s="12"/>
+      <c r="X203" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>12950</v>
+      </c>
+      <c r="Y203" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1079.1666666666667</v>
+      </c>
+      <c r="Z203" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA203" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2960</v>
+      </c>
+      <c r="AB203" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC203" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>6845</v>
+      </c>
+      <c r="AD203" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE203" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>85655</v>
+      </c>
+      <c r="AF203" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 15 725 €</v>
+      </c>
+      <c r="AG203" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH203" s="12"/>
+      <c r="AI203" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ203" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK203" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL203" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM203" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN203" s="11"/>
+      <c r="AO203" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP203" s="11" t="s">
+        <v>1517</v>
+      </c>
+      <c r="AQ203" s="11" t="s">
+        <v>1518</v>
+      </c>
+      <c r="AR203" s="11" t="s">
+        <v>1481</v>
+      </c>
+      <c r="AS203" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT203" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU203" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV203" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW203" s="14"/>
+      <c r="AX203" s="44"/>
+    </row>
+    <row r="204" spans="1:50" ht="38.25">
+      <c r="A204" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B204" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C204" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D204" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E204" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G204" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H204" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I204" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J204" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K204" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L204" s="10"/>
+      <c r="M204" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N204" s="36" t="s">
+        <v>1459</v>
+      </c>
+      <c r="O204" s="34">
+        <v>106</v>
+      </c>
+      <c r="P204" s="12"/>
+      <c r="Q204" s="34">
+        <v>265</v>
+      </c>
+      <c r="R204" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S204" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T204" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>36040</v>
+      </c>
+      <c r="U204" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3003.3333333333335</v>
+      </c>
+      <c r="V204" s="12">
+        <v>340</v>
+      </c>
+      <c r="W204" s="12"/>
+      <c r="X204" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>7420</v>
+      </c>
+      <c r="Y204" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>618.33333333333337</v>
+      </c>
+      <c r="Z204" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA204" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1696</v>
+      </c>
+      <c r="AB204" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC204" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3922</v>
+      </c>
+      <c r="AD204" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE204" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>49078</v>
+      </c>
+      <c r="AF204" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 9 010 €</v>
+      </c>
+      <c r="AG204" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH204" s="12"/>
+      <c r="AI204" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ204" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK204" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL204" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM204" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN204" s="11"/>
+      <c r="AO204" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP204" s="11" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AQ204" s="11" t="s">
+        <v>1520</v>
+      </c>
+      <c r="AR204" s="11" t="s">
+        <v>1482</v>
+      </c>
+      <c r="AS204" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT204" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU204" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV204" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW204" s="14"/>
+      <c r="AX204" s="44"/>
+    </row>
+    <row r="205" spans="1:50" ht="38.25">
+      <c r="A205" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B205" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C205" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E205" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F205" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G205" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H205" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I205" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J205" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K205" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L205" s="10"/>
+      <c r="M205" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N205" s="36" t="s">
+        <v>1460</v>
+      </c>
+      <c r="O205" s="34">
+        <v>74</v>
+      </c>
+      <c r="P205" s="12"/>
+      <c r="Q205" s="34">
+        <v>265</v>
+      </c>
+      <c r="R205" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S205" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T205" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>25160</v>
+      </c>
+      <c r="U205" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2096.6666666666665</v>
+      </c>
+      <c r="V205" s="12">
+        <v>340</v>
+      </c>
+      <c r="W205" s="12"/>
+      <c r="X205" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>5180</v>
+      </c>
+      <c r="Y205" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>431.66666666666669</v>
+      </c>
+      <c r="Z205" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA205" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1184</v>
+      </c>
+      <c r="AB205" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC205" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2738</v>
+      </c>
+      <c r="AD205" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE205" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>34262</v>
+      </c>
+      <c r="AF205" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 6 290 €</v>
+      </c>
+      <c r="AG205" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH205" s="12"/>
+      <c r="AI205" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ205" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK205" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL205" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM205" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN205" s="11"/>
+      <c r="AO205" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP205" s="11" t="s">
+        <v>1521</v>
+      </c>
+      <c r="AQ205" s="11" t="s">
+        <v>1522</v>
+      </c>
+      <c r="AR205" s="11" t="s">
+        <v>1483</v>
+      </c>
+      <c r="AS205" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT205" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU205" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV205" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW205" s="14"/>
+      <c r="AX205" s="44"/>
+    </row>
+    <row r="206" spans="1:50" ht="38.25">
+      <c r="A206" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B206" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C206" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E206" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G206" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H206" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I206" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K206" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L206" s="10"/>
+      <c r="M206" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N206" s="36" t="s">
+        <v>1461</v>
+      </c>
+      <c r="O206" s="34">
+        <v>85</v>
+      </c>
+      <c r="P206" s="12"/>
+      <c r="Q206" s="34">
+        <v>265</v>
+      </c>
+      <c r="R206" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S206" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T206" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>28900</v>
+      </c>
+      <c r="U206" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2408.3333333333335</v>
+      </c>
+      <c r="V206" s="12">
+        <v>340</v>
+      </c>
+      <c r="W206" s="12"/>
+      <c r="X206" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>5950</v>
+      </c>
+      <c r="Y206" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>495.83333333333331</v>
+      </c>
+      <c r="Z206" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA206" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1360</v>
+      </c>
+      <c r="AB206" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC206" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3145</v>
+      </c>
+      <c r="AD206" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE206" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>39355</v>
+      </c>
+      <c r="AF206" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 7 225 €</v>
+      </c>
+      <c r="AG206" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH206" s="12"/>
+      <c r="AI206" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ206" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK206" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL206" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM206" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN206" s="11"/>
+      <c r="AO206" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP206" s="11" t="s">
+        <v>1523</v>
+      </c>
+      <c r="AQ206" s="11" t="s">
+        <v>1524</v>
+      </c>
+      <c r="AR206" s="11" t="s">
+        <v>1484</v>
+      </c>
+      <c r="AS206" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT206" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU206" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV206" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW206" s="14"/>
+      <c r="AX206" s="44"/>
+    </row>
+    <row r="207" spans="1:50" ht="38.25">
+      <c r="A207" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B207" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C207" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D207" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E207" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F207" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G207" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H207" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I207" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J207" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K207" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L207" s="10"/>
+      <c r="M207" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N207" s="36" t="s">
+        <v>1462</v>
+      </c>
+      <c r="O207" s="34">
+        <v>164</v>
+      </c>
+      <c r="P207" s="12"/>
+      <c r="Q207" s="34"/>
+      <c r="R207" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S207" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T207" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>55760</v>
+      </c>
+      <c r="U207" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4646.666666666667</v>
+      </c>
+      <c r="V207" s="12">
+        <v>340</v>
+      </c>
+      <c r="W207" s="12"/>
+      <c r="X207" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11480</v>
+      </c>
+      <c r="Y207" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>956.66666666666663</v>
+      </c>
+      <c r="Z207" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA207" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2624</v>
+      </c>
+      <c r="AB207" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC207" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>6068</v>
+      </c>
+      <c r="AD207" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE207" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>75932</v>
+      </c>
+      <c r="AF207" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 13 940 €</v>
+      </c>
+      <c r="AG207" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH207" s="12"/>
+      <c r="AI207" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ207" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK207" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL207" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM207" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN207" s="11"/>
+      <c r="AO207" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP207" s="11" t="s">
+        <v>1525</v>
+      </c>
+      <c r="AQ207" s="11" t="s">
+        <v>1526</v>
+      </c>
+      <c r="AR207" s="11" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AS207" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT207" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU207" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV207" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW207" s="14"/>
+      <c r="AX207" s="44"/>
+    </row>
+    <row r="208" spans="1:50" ht="38.25">
+      <c r="A208" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B208" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C208" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D208" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E208" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G208" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H208" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I208" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K208" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L208" s="10"/>
+      <c r="M208" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N208" s="36">
+        <v>32</v>
+      </c>
+      <c r="O208" s="34">
+        <v>138</v>
+      </c>
+      <c r="P208" s="12"/>
+      <c r="Q208" s="34"/>
+      <c r="R208" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S208" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T208" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>46920</v>
+      </c>
+      <c r="U208" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3910</v>
+      </c>
+      <c r="V208" s="12">
+        <v>340</v>
+      </c>
+      <c r="W208" s="12"/>
+      <c r="X208" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>9660</v>
+      </c>
+      <c r="Y208" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>805</v>
+      </c>
+      <c r="Z208" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA208" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2208</v>
+      </c>
+      <c r="AB208" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC208" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>5106</v>
+      </c>
+      <c r="AD208" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE208" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>63894</v>
+      </c>
+      <c r="AF208" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 11 730 €</v>
+      </c>
+      <c r="AG208" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH208" s="12"/>
+      <c r="AI208" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ208" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK208" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL208" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM208" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN208" s="11"/>
+      <c r="AO208" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP208" s="11" t="s">
+        <v>1527</v>
+      </c>
+      <c r="AQ208" s="11" t="s">
+        <v>1528</v>
+      </c>
+      <c r="AR208" s="11" t="s">
+        <v>1486</v>
+      </c>
+      <c r="AS208" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT208" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU208" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV208" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW208" s="14"/>
+      <c r="AX208" s="44"/>
+    </row>
+    <row r="209" spans="1:50" ht="38.25">
+      <c r="A209" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B209" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C209" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E209" s="26">
+        <v>87221</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G209" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87221 - Boisseuil</v>
+      </c>
+      <c r="H209" s="15" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I209" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J209" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K209" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L209" s="10"/>
+      <c r="M209" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N209" s="36" t="s">
+        <v>1469</v>
+      </c>
+      <c r="O209" s="34">
+        <v>205</v>
+      </c>
+      <c r="P209" s="12"/>
+      <c r="Q209" s="34"/>
+      <c r="R209" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S209" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T209" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>71750</v>
+      </c>
+      <c r="U209" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5979.166666666667</v>
+      </c>
+      <c r="V209" s="12">
+        <v>350</v>
+      </c>
+      <c r="W209" s="12"/>
+      <c r="X209" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>14350</v>
+      </c>
+      <c r="Y209" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1195.8333333333333</v>
+      </c>
+      <c r="Z209" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA209" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3280</v>
+      </c>
+      <c r="AB209" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC209" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>7585</v>
+      </c>
+      <c r="AD209" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE209" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>96965</v>
+      </c>
+      <c r="AF209" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 17 938 €</v>
+      </c>
+      <c r="AG209" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH209" s="12"/>
+      <c r="AI209" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ209" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK209" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL209" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM209" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN209" s="11"/>
+      <c r="AO209" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP209" s="11" t="s">
+        <v>1529</v>
+      </c>
+      <c r="AQ209" s="11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="AR209" s="11" t="s">
+        <v>1487</v>
+      </c>
+      <c r="AS209" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT209" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU209" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV209" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW209" s="14"/>
+      <c r="AX209" s="44"/>
+    </row>
+    <row r="210" spans="1:50" ht="38.25">
+      <c r="A210" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B210" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C210" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D210" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E210" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F210" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G210" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H210" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I210" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K210" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L210" s="10"/>
+      <c r="M210" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N210" s="36" t="s">
+        <v>1463</v>
+      </c>
+      <c r="O210" s="34">
+        <v>468</v>
+      </c>
+      <c r="P210" s="12" t="s">
+        <v>1467</v>
+      </c>
+      <c r="Q210" s="34"/>
+      <c r="R210" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S210" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T210" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>84240</v>
+      </c>
+      <c r="U210" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>7020</v>
+      </c>
+      <c r="V210" s="12">
+        <v>180</v>
+      </c>
+      <c r="W210" s="12"/>
+      <c r="X210" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>32760</v>
+      </c>
+      <c r="Y210" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>2730</v>
+      </c>
+      <c r="Z210" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA210" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>7488</v>
+      </c>
+      <c r="AB210" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC210" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>17316</v>
+      </c>
+      <c r="AD210" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE210" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>141804</v>
+      </c>
+      <c r="AF210" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 21 060 €</v>
+      </c>
+      <c r="AG210" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH210" s="12"/>
+      <c r="AI210" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ210" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK210" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL210" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM210" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN210" s="11"/>
+      <c r="AO210" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP210" s="11" t="s">
+        <v>1531</v>
+      </c>
+      <c r="AQ210" s="11" t="s">
+        <v>1532</v>
+      </c>
+      <c r="AR210" s="11" t="s">
+        <v>1488</v>
+      </c>
+      <c r="AS210" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT210" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU210" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV210" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW210" s="14"/>
+      <c r="AX210" s="44"/>
+    </row>
+    <row r="211" spans="1:50" ht="38.25">
+      <c r="A211" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B211" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C211" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D211" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E211" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F211" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G211" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H211" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J211" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K211" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L211" s="10"/>
+      <c r="M211" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N211" s="36">
+        <v>42</v>
+      </c>
+      <c r="O211" s="34">
+        <v>229</v>
+      </c>
+      <c r="P211" s="12"/>
+      <c r="Q211" s="34"/>
+      <c r="R211" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S211" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T211" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>73280</v>
+      </c>
+      <c r="U211" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>6106.666666666667</v>
+      </c>
+      <c r="V211" s="12">
+        <v>320</v>
+      </c>
+      <c r="W211" s="12"/>
+      <c r="X211" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>16030</v>
+      </c>
+      <c r="Y211" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1335.8333333333333</v>
+      </c>
+      <c r="Z211" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA211" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3664</v>
+      </c>
+      <c r="AB211" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC211" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>8473</v>
+      </c>
+      <c r="AD211" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE211" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>101447</v>
+      </c>
+      <c r="AF211" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 18 320 €</v>
+      </c>
+      <c r="AG211" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH211" s="12"/>
+      <c r="AI211" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ211" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK211" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL211" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM211" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN211" s="11"/>
+      <c r="AO211" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP211" s="11" t="s">
+        <v>1533</v>
+      </c>
+      <c r="AQ211" s="11" t="s">
+        <v>1534</v>
+      </c>
+      <c r="AR211" s="11" t="s">
+        <v>1489</v>
+      </c>
+      <c r="AS211" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT211" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU211" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV211" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW211" s="14"/>
+      <c r="AX211" s="44"/>
+    </row>
+    <row r="212" spans="1:50" ht="38.25">
+      <c r="A212" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B212" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C212" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D212" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E212" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G212" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H212" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K212" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L212" s="10"/>
+      <c r="M212" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N212" s="36">
+        <v>47</v>
+      </c>
+      <c r="O212" s="34">
+        <v>90</v>
+      </c>
+      <c r="P212" s="12"/>
+      <c r="Q212" s="34"/>
+      <c r="R212" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S212" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T212" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>32400</v>
+      </c>
+      <c r="U212" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2700</v>
+      </c>
+      <c r="V212" s="12">
+        <v>360</v>
+      </c>
+      <c r="W212" s="12"/>
+      <c r="X212" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>6300</v>
+      </c>
+      <c r="Y212" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>525</v>
+      </c>
+      <c r="Z212" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA212" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1440</v>
+      </c>
+      <c r="AB212" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC212" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3330</v>
+      </c>
+      <c r="AD212" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE212" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>43470</v>
+      </c>
+      <c r="AF212" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 8 100 €</v>
+      </c>
+      <c r="AG212" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH212" s="12"/>
+      <c r="AI212" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ212" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK212" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL212" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM212" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN212" s="11"/>
+      <c r="AO212" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP212" s="11" t="s">
+        <v>1535</v>
+      </c>
+      <c r="AQ212" s="11" t="s">
+        <v>1536</v>
+      </c>
+      <c r="AR212" s="11" t="s">
+        <v>1490</v>
+      </c>
+      <c r="AS212" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT212" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU212" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV212" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW212" s="14"/>
+      <c r="AX212" s="44"/>
+    </row>
+    <row r="213" spans="1:50" ht="38.25">
+      <c r="A213" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B213" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C213" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D213" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E213" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G213" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H213" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K213" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L213" s="10"/>
+      <c r="M213" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N213" s="36">
+        <v>48</v>
+      </c>
+      <c r="O213" s="34">
+        <v>174</v>
+      </c>
+      <c r="P213" s="12">
+        <v>358</v>
+      </c>
+      <c r="Q213" s="34"/>
+      <c r="R213" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S213" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T213" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>62640</v>
+      </c>
+      <c r="U213" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5220</v>
+      </c>
+      <c r="V213" s="12">
+        <v>360</v>
+      </c>
+      <c r="W213" s="12"/>
+      <c r="X213" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>12180</v>
+      </c>
+      <c r="Y213" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1015</v>
+      </c>
+      <c r="Z213" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA213" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2784</v>
+      </c>
+      <c r="AB213" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC213" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>6438</v>
+      </c>
+      <c r="AD213" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE213" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>84042</v>
+      </c>
+      <c r="AF213" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 15 660 €</v>
+      </c>
+      <c r="AG213" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH213" s="12"/>
+      <c r="AI213" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ213" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK213" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL213" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM213" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN213" s="11"/>
+      <c r="AO213" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP213" s="11" t="s">
+        <v>1537</v>
+      </c>
+      <c r="AQ213" s="11" t="s">
+        <v>1538</v>
+      </c>
+      <c r="AR213" s="11" t="s">
+        <v>1491</v>
+      </c>
+      <c r="AS213" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT213" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU213" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV213" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW213" s="14"/>
+      <c r="AX213" s="44"/>
+    </row>
+    <row r="214" spans="1:50" ht="38.25">
+      <c r="A214" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B214" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C214" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E214" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G214" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H214" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I214" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J214" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K214" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L214" s="10"/>
+      <c r="M214" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N214" s="36">
+        <v>49</v>
+      </c>
+      <c r="O214" s="34">
+        <v>184</v>
+      </c>
+      <c r="P214" s="12">
+        <v>358</v>
+      </c>
+      <c r="Q214" s="34"/>
+      <c r="R214" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S214" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T214" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>66240</v>
+      </c>
+      <c r="U214" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5520</v>
+      </c>
+      <c r="V214" s="12">
+        <v>360</v>
+      </c>
+      <c r="W214" s="12"/>
+      <c r="X214" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>12880</v>
+      </c>
+      <c r="Y214" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1073.3333333333333</v>
+      </c>
+      <c r="Z214" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA214" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2944</v>
+      </c>
+      <c r="AB214" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC214" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>6808</v>
+      </c>
+      <c r="AD214" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE214" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>88872</v>
+      </c>
+      <c r="AF214" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 16 560 €</v>
+      </c>
+      <c r="AG214" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH214" s="12"/>
+      <c r="AI214" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ214" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK214" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL214" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM214" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN214" s="11"/>
+      <c r="AO214" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP214" s="11" t="s">
+        <v>1539</v>
+      </c>
+      <c r="AQ214" s="11" t="s">
+        <v>1540</v>
+      </c>
+      <c r="AR214" s="11" t="s">
+        <v>1492</v>
+      </c>
+      <c r="AS214" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT214" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU214" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV214" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW214" s="14"/>
+      <c r="AX214" s="44"/>
+    </row>
+    <row r="215" spans="1:50" ht="38.25">
+      <c r="A215" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Nouvelle-Aquitaine</v>
+      </c>
+      <c r="B215" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haute-Vienne</v>
+      </c>
+      <c r="C215" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>87</v>
+      </c>
+      <c r="D215" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E215" s="26">
+        <v>87220</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G215" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Boisseuil
+Route de Toulouse
+87220 - Boisseuil</v>
+      </c>
+      <c r="H215" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I215" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J215" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K215" s="10" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L215" s="10"/>
+      <c r="M215" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N215" s="36" t="s">
+        <v>1464</v>
+      </c>
+      <c r="O215" s="34">
+        <v>48</v>
+      </c>
+      <c r="P215" s="12" t="s">
+        <v>1468</v>
+      </c>
+      <c r="Q215" s="34"/>
+      <c r="R215" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S215" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T215" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>36000</v>
+      </c>
+      <c r="U215" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3000</v>
+      </c>
+      <c r="V215" s="12">
+        <v>750</v>
+      </c>
+      <c r="W215" s="12"/>
+      <c r="X215" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3360</v>
+      </c>
+      <c r="Y215" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>280</v>
+      </c>
+      <c r="Z215" s="12">
+        <v>70</v>
+      </c>
+      <c r="AA215" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>768</v>
+      </c>
+      <c r="AB215" s="12">
+        <v>16</v>
+      </c>
+      <c r="AC215" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1776</v>
+      </c>
+      <c r="AD215" s="12">
+        <v>37</v>
+      </c>
+      <c r="AE215" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>41904</v>
+      </c>
+      <c r="AF215" s="12" t="str">
+        <f t="shared" si="9"/>
+        <v>3 mois = 9 000 €</v>
+      </c>
+      <c r="AG215" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH215" s="12"/>
+      <c r="AI215" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ215" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK215" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL215" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AM215" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AN215" s="11"/>
+      <c r="AO215" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP215" s="11" t="s">
+        <v>1541</v>
+      </c>
+      <c r="AQ215" s="11" t="s">
+        <v>1542</v>
+      </c>
+      <c r="AR215" s="11" t="s">
+        <v>1505</v>
+      </c>
+      <c r="AS215" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AT215" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU215" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV215" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW215" s="14"/>
+      <c r="AX215" s="44"/>
+    </row>
+    <row r="226" spans="6:6">
+      <c r="F226" s="1" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="205" spans="6:6">
-      <c r="F205" s="1" t="s">
+    <row r="227" spans="6:6">
+      <c r="F227" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -36429,6 +40202,29 @@
     <hyperlink ref="H190" r:id="rId152" xr:uid="{B58FC76B-D0FB-47D2-9309-07FBB7AE8F26}"/>
     <hyperlink ref="H191" r:id="rId153" xr:uid="{5ACAB395-A666-4978-812B-9B6039F53703}"/>
     <hyperlink ref="H192" r:id="rId154" xr:uid="{21A42A74-18EE-46BA-BF13-26B8D1F6FB47}"/>
+    <hyperlink ref="H193" r:id="rId155" xr:uid="{979A4771-81FC-497B-97EF-32C019953489}"/>
+    <hyperlink ref="H194" r:id="rId156" xr:uid="{234D72AD-6212-4E7C-8477-5EE09B54842C}"/>
+    <hyperlink ref="H195" r:id="rId157" xr:uid="{00FC64E2-B2F8-4262-AD93-67A69A51A2AE}"/>
+    <hyperlink ref="H198" r:id="rId158" xr:uid="{37D46FE9-659B-4E71-B1B0-2BAE5EB3E001}"/>
+    <hyperlink ref="H200" r:id="rId159" xr:uid="{C1FEA757-567F-46DB-8BE8-C181F4790348}"/>
+    <hyperlink ref="H202" r:id="rId160" xr:uid="{E5DA9A5D-81D1-4927-A98E-48C8E1B7F848}"/>
+    <hyperlink ref="H204" r:id="rId161" xr:uid="{BF1AC4BD-BCB3-41AE-BB4E-A4D7D4B9CA30}"/>
+    <hyperlink ref="H206" r:id="rId162" xr:uid="{F331605E-78A2-41C4-A9DE-125F32D6DA17}"/>
+    <hyperlink ref="H208" r:id="rId163" xr:uid="{CD04C61F-F4DD-4619-8D0C-B117149DDD16}"/>
+    <hyperlink ref="H211" r:id="rId164" xr:uid="{126CAEE5-AFE9-4D78-8299-0693794DBF35}"/>
+    <hyperlink ref="H213" r:id="rId165" xr:uid="{99CC6C3B-99A9-43A2-98C5-FB3C0CDBB22E}"/>
+    <hyperlink ref="H215" r:id="rId166" xr:uid="{5ACB8786-94C9-4AC5-891E-06289DFF8043}"/>
+    <hyperlink ref="H196" r:id="rId167" xr:uid="{2FDB9825-2079-4C7E-B037-8188CA0176F5}"/>
+    <hyperlink ref="H199" r:id="rId168" xr:uid="{A69F4B4C-FA3C-439D-BC44-569193F38E47}"/>
+    <hyperlink ref="H201" r:id="rId169" xr:uid="{46585970-332F-4A0A-9FB9-F74633BF4F42}"/>
+    <hyperlink ref="H203" r:id="rId170" xr:uid="{8D52DD5E-FD4A-4159-BFA0-B6EE5B956520}"/>
+    <hyperlink ref="H205" r:id="rId171" xr:uid="{DDFB99AD-CCF9-4F9C-B530-960F480ECD4B}"/>
+    <hyperlink ref="H207" r:id="rId172" xr:uid="{8C88AF55-D328-4D4E-ACE7-C01C70716F01}"/>
+    <hyperlink ref="H210" r:id="rId173" xr:uid="{A2384EAF-1892-4C85-B4DB-D89DEED6A1DD}"/>
+    <hyperlink ref="H212" r:id="rId174" xr:uid="{D6D56087-231C-4ABA-8429-E4BF41585FE5}"/>
+    <hyperlink ref="H214" r:id="rId175" xr:uid="{D09EAEF8-49AC-4164-AAB1-5DDF19295801}"/>
+    <hyperlink ref="H209" r:id="rId176" display="https://maps.app.goo.gl/RJ2QRVrW96tKL7ur6" xr:uid="{609C48FB-80B4-46B2-AA88-2F3D30BF6C33}"/>
+    <hyperlink ref="H197" r:id="rId177" xr:uid="{2E729EBE-5AE8-4BE9-AA51-7933BA8C3C79}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -36437,7 +40233,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId155"/>
+    <tablePart r:id="rId178"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADB663D-8109-4D60-9A66-F493525EE4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BED06F-2C55-47D8-A159-BAE481A2FB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6321" uniqueCount="1544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6344" uniqueCount="1545">
   <si>
     <t>Contact</t>
   </si>
@@ -4681,6 +4681,9 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/63.1%20-%20Limoges/5%20Plan%20du%20centre.jpg</t>
+  </si>
+  <si>
+    <t>3 500 € HT</t>
   </si>
 </sst>
 </file>
@@ -4811,7 +4814,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -4942,6 +4945,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -36622,7 +36631,9 @@
       <c r="V193" s="12">
         <v>420</v>
       </c>
-      <c r="W193" s="12"/>
+      <c r="W193" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X193" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>16380</v>
@@ -36659,7 +36670,9 @@
       <c r="AG193" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH193" s="12"/>
+      <c r="AH193" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI193" s="12" t="s">
         <v>363</v>
       </c>
@@ -36675,7 +36688,9 @@
       <c r="AM193" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN193" s="11"/>
+      <c r="AN193" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO193" s="5" t="s">
         <v>367</v>
       </c>
@@ -36774,7 +36789,9 @@
       <c r="V194" s="12">
         <v>420</v>
       </c>
-      <c r="W194" s="12"/>
+      <c r="W194" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X194" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>15400</v>
@@ -36811,7 +36828,9 @@
       <c r="AG194" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH194" s="12"/>
+      <c r="AH194" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI194" s="12" t="s">
         <v>363</v>
       </c>
@@ -36827,7 +36846,9 @@
       <c r="AM194" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN194" s="11"/>
+      <c r="AN194" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO194" s="5" t="s">
         <v>367</v>
       </c>
@@ -36926,7 +36947,9 @@
       <c r="V195" s="12">
         <v>300</v>
       </c>
-      <c r="W195" s="12"/>
+      <c r="W195" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X195" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>7350</v>
@@ -36963,7 +36986,9 @@
       <c r="AG195" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH195" s="12"/>
+      <c r="AH195" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI195" s="12" t="s">
         <v>380</v>
       </c>
@@ -36979,7 +37004,9 @@
       <c r="AM195" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN195" s="11"/>
+      <c r="AN195" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO195" s="5" t="s">
         <v>367</v>
       </c>
@@ -37078,7 +37105,9 @@
       <c r="V196" s="12">
         <v>400</v>
       </c>
-      <c r="W196" s="12"/>
+      <c r="W196" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X196" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>8190</v>
@@ -37115,7 +37144,9 @@
       <c r="AG196" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH196" s="12"/>
+      <c r="AH196" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI196" s="12" t="s">
         <v>363</v>
       </c>
@@ -37131,7 +37162,9 @@
       <c r="AM196" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN196" s="11"/>
+      <c r="AN196" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO196" s="5" t="s">
         <v>367</v>
       </c>
@@ -37230,7 +37263,9 @@
       <c r="V197" s="12">
         <v>520</v>
       </c>
-      <c r="W197" s="12"/>
+      <c r="W197" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X197" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>8680</v>
@@ -37267,7 +37302,9 @@
       <c r="AG197" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH197" s="12"/>
+      <c r="AH197" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI197" s="12" t="s">
         <v>363</v>
       </c>
@@ -37283,7 +37320,9 @@
       <c r="AM197" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN197" s="11"/>
+      <c r="AN197" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO197" s="5" t="s">
         <v>367</v>
       </c>
@@ -37384,7 +37423,9 @@
       <c r="V198" s="12">
         <v>520</v>
       </c>
-      <c r="W198" s="12"/>
+      <c r="W198" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X198" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>3780</v>
@@ -37421,7 +37462,9 @@
       <c r="AG198" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH198" s="12"/>
+      <c r="AH198" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI198" s="12" t="s">
         <v>363</v>
       </c>
@@ -37437,7 +37480,9 @@
       <c r="AM198" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN198" s="11"/>
+      <c r="AN198" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO198" s="5" t="s">
         <v>367</v>
       </c>
@@ -37536,7 +37581,9 @@
       <c r="V199" s="12">
         <v>520</v>
       </c>
-      <c r="W199" s="12"/>
+      <c r="W199" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X199" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>2170</v>
@@ -37573,7 +37620,9 @@
       <c r="AG199" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH199" s="12"/>
+      <c r="AH199" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI199" s="12" t="s">
         <v>363</v>
       </c>
@@ -37589,7 +37638,9 @@
       <c r="AM199" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN199" s="11"/>
+      <c r="AN199" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO199" s="5" t="s">
         <v>367</v>
       </c>
@@ -37686,7 +37737,9 @@
       <c r="V200" s="12">
         <v>450</v>
       </c>
-      <c r="W200" s="12"/>
+      <c r="W200" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X200" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>5390</v>
@@ -37723,7 +37776,9 @@
       <c r="AG200" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH200" s="12"/>
+      <c r="AH200" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI200" s="12" t="s">
         <v>363</v>
       </c>
@@ -37739,7 +37794,9 @@
       <c r="AM200" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN200" s="11"/>
+      <c r="AN200" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO200" s="5" t="s">
         <v>367</v>
       </c>
@@ -37838,7 +37895,9 @@
       <c r="V201" s="12">
         <v>350</v>
       </c>
-      <c r="W201" s="12"/>
+      <c r="W201" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X201" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>10570</v>
@@ -37875,7 +37934,9 @@
       <c r="AG201" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH201" s="12"/>
+      <c r="AH201" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI201" s="12" t="s">
         <v>363</v>
       </c>
@@ -37891,7 +37952,9 @@
       <c r="AM201" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN201" s="11"/>
+      <c r="AN201" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO201" s="5" t="s">
         <v>367</v>
       </c>
@@ -37990,7 +38053,9 @@
       <c r="V202" s="12">
         <v>350</v>
       </c>
-      <c r="W202" s="12"/>
+      <c r="W202" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X202" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>21210</v>
@@ -38027,7 +38092,9 @@
       <c r="AG202" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH202" s="12"/>
+      <c r="AH202" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI202" s="12" t="s">
         <v>380</v>
       </c>
@@ -38043,7 +38110,9 @@
       <c r="AM202" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN202" s="11"/>
+      <c r="AN202" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO202" s="5" t="s">
         <v>367</v>
       </c>
@@ -38140,7 +38209,9 @@
       <c r="V203" s="12">
         <v>340</v>
       </c>
-      <c r="W203" s="12"/>
+      <c r="W203" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X203" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>12950</v>
@@ -38177,7 +38248,9 @@
       <c r="AG203" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH203" s="12"/>
+      <c r="AH203" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI203" s="12" t="s">
         <v>363</v>
       </c>
@@ -38193,7 +38266,9 @@
       <c r="AM203" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN203" s="11"/>
+      <c r="AN203" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO203" s="5" t="s">
         <v>367</v>
       </c>
@@ -38292,7 +38367,9 @@
       <c r="V204" s="12">
         <v>340</v>
       </c>
-      <c r="W204" s="12"/>
+      <c r="W204" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X204" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>7420</v>
@@ -38329,7 +38406,9 @@
       <c r="AG204" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH204" s="12"/>
+      <c r="AH204" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI204" s="12" t="s">
         <v>380</v>
       </c>
@@ -38345,7 +38424,9 @@
       <c r="AM204" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN204" s="11"/>
+      <c r="AN204" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO204" s="5" t="s">
         <v>367</v>
       </c>
@@ -38444,7 +38525,9 @@
       <c r="V205" s="12">
         <v>340</v>
       </c>
-      <c r="W205" s="12"/>
+      <c r="W205" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X205" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>5180</v>
@@ -38481,7 +38564,9 @@
       <c r="AG205" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH205" s="12"/>
+      <c r="AH205" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI205" s="12" t="s">
         <v>380</v>
       </c>
@@ -38497,7 +38582,9 @@
       <c r="AM205" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN205" s="11"/>
+      <c r="AN205" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO205" s="5" t="s">
         <v>367</v>
       </c>
@@ -38596,7 +38683,9 @@
       <c r="V206" s="12">
         <v>340</v>
       </c>
-      <c r="W206" s="12"/>
+      <c r="W206" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X206" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>5950</v>
@@ -38633,7 +38722,9 @@
       <c r="AG206" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH206" s="12"/>
+      <c r="AH206" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI206" s="12" t="s">
         <v>363</v>
       </c>
@@ -38649,7 +38740,9 @@
       <c r="AM206" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN206" s="11"/>
+      <c r="AN206" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO206" s="5" t="s">
         <v>367</v>
       </c>
@@ -38746,7 +38839,9 @@
       <c r="V207" s="12">
         <v>340</v>
       </c>
-      <c r="W207" s="12"/>
+      <c r="W207" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X207" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>11480</v>
@@ -38783,7 +38878,9 @@
       <c r="AG207" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH207" s="12"/>
+      <c r="AH207" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI207" s="12" t="s">
         <v>363</v>
       </c>
@@ -38799,7 +38896,9 @@
       <c r="AM207" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN207" s="11"/>
+      <c r="AN207" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO207" s="5" t="s">
         <v>367</v>
       </c>
@@ -38896,7 +38995,9 @@
       <c r="V208" s="12">
         <v>340</v>
       </c>
-      <c r="W208" s="12"/>
+      <c r="W208" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X208" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>9660</v>
@@ -38933,7 +39034,9 @@
       <c r="AG208" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH208" s="12"/>
+      <c r="AH208" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI208" s="12" t="s">
         <v>363</v>
       </c>
@@ -38949,7 +39052,9 @@
       <c r="AM208" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN208" s="11"/>
+      <c r="AN208" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO208" s="5" t="s">
         <v>367</v>
       </c>
@@ -39046,7 +39151,9 @@
       <c r="V209" s="12">
         <v>350</v>
       </c>
-      <c r="W209" s="12"/>
+      <c r="W209" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X209" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>14350</v>
@@ -39083,7 +39190,9 @@
       <c r="AG209" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH209" s="12"/>
+      <c r="AH209" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI209" s="12" t="s">
         <v>363</v>
       </c>
@@ -39099,7 +39208,9 @@
       <c r="AM209" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN209" s="11"/>
+      <c r="AN209" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO209" s="5" t="s">
         <v>367</v>
       </c>
@@ -39198,7 +39309,9 @@
       <c r="V210" s="12">
         <v>180</v>
       </c>
-      <c r="W210" s="12"/>
+      <c r="W210" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X210" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>32760</v>
@@ -39235,7 +39348,9 @@
       <c r="AG210" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH210" s="12"/>
+      <c r="AH210" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI210" s="12" t="s">
         <v>363</v>
       </c>
@@ -39251,7 +39366,9 @@
       <c r="AM210" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN210" s="11"/>
+      <c r="AN210" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO210" s="5" t="s">
         <v>367</v>
       </c>
@@ -39348,7 +39465,9 @@
       <c r="V211" s="12">
         <v>320</v>
       </c>
-      <c r="W211" s="12"/>
+      <c r="W211" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X211" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>16030</v>
@@ -39385,7 +39504,9 @@
       <c r="AG211" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH211" s="12"/>
+      <c r="AH211" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI211" s="12" t="s">
         <v>380</v>
       </c>
@@ -39401,7 +39522,9 @@
       <c r="AM211" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN211" s="11"/>
+      <c r="AN211" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO211" s="5" t="s">
         <v>367</v>
       </c>
@@ -39498,7 +39621,9 @@
       <c r="V212" s="12">
         <v>360</v>
       </c>
-      <c r="W212" s="12"/>
+      <c r="W212" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X212" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>6300</v>
@@ -39535,7 +39660,9 @@
       <c r="AG212" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH212" s="12"/>
+      <c r="AH212" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI212" s="12" t="s">
         <v>363</v>
       </c>
@@ -39551,7 +39678,9 @@
       <c r="AM212" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN212" s="11"/>
+      <c r="AN212" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO212" s="5" t="s">
         <v>367</v>
       </c>
@@ -39650,7 +39779,9 @@
       <c r="V213" s="12">
         <v>360</v>
       </c>
-      <c r="W213" s="12"/>
+      <c r="W213" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X213" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>12180</v>
@@ -39687,7 +39818,9 @@
       <c r="AG213" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH213" s="12"/>
+      <c r="AH213" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI213" s="12" t="s">
         <v>363</v>
       </c>
@@ -39703,7 +39836,9 @@
       <c r="AM213" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN213" s="11"/>
+      <c r="AN213" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO213" s="5" t="s">
         <v>367</v>
       </c>
@@ -39802,7 +39937,9 @@
       <c r="V214" s="12">
         <v>360</v>
       </c>
-      <c r="W214" s="12"/>
+      <c r="W214" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X214" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>12880</v>
@@ -39839,7 +39976,9 @@
       <c r="AG214" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH214" s="12"/>
+      <c r="AH214" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI214" s="12" t="s">
         <v>363</v>
       </c>
@@ -39855,7 +39994,9 @@
       <c r="AM214" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN214" s="11"/>
+      <c r="AN214" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO214" s="5" t="s">
         <v>367</v>
       </c>
@@ -39954,7 +40095,9 @@
       <c r="V215" s="12">
         <v>750</v>
       </c>
-      <c r="W215" s="12"/>
+      <c r="W215" s="50">
+        <v>0.08</v>
+      </c>
       <c r="X215" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
         <v>3360</v>
@@ -39991,7 +40134,9 @@
       <c r="AG215" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AH215" s="12"/>
+      <c r="AH215" s="51">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI215" s="12" t="s">
         <v>363</v>
       </c>
@@ -40007,7 +40152,9 @@
       <c r="AM215" s="11" t="s">
         <v>1504</v>
       </c>
-      <c r="AN215" s="11"/>
+      <c r="AN215" s="11" t="s">
+        <v>1544</v>
+      </c>
       <c r="AO215" s="5" t="s">
         <v>367</v>
       </c>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BED06F-2C55-47D8-A159-BAE481A2FB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E60CBC1-BFED-401D-8B0B-F2D8D706453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6344" uniqueCount="1545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6488" uniqueCount="1583">
   <si>
     <t>Contact</t>
   </si>
@@ -4684,6 +4684,125 @@
   </si>
   <si>
     <t>3 500 € HT</t>
+  </si>
+  <si>
+    <t>Centre commercial Cœur Lozère
+Avenue de Ramilles</t>
+  </si>
+  <si>
+    <t>Mende</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7dsMYhd2KW95ZzZs5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7dsMYhd2KW95ZzZs6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7dsMYhd2KW95ZzZs7</t>
+  </si>
+  <si>
+    <t>Hyper Leclerc Blotzheim
+5 bis rue Pierre Clostermann</t>
+  </si>
+  <si>
+    <t>Blotzheim</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wNVbBxTsrAXKBrtc6</t>
+  </si>
+  <si>
+    <t>3/6/9 ans</t>
+  </si>
+  <si>
+    <t>112 €/m² = 50 000 € HT</t>
+  </si>
+  <si>
+    <t>Les galeries d'Huningue
+9 avenue d'Alsace</t>
+  </si>
+  <si>
+    <t>Les galeries d'Huningue
+7 avenue d'Alsace</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PkFc3TvBwkxAUjfeA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SsXW9FUhqGRYgzi97</t>
+  </si>
+  <si>
+    <t>Les galeries d'Hegenheim
+Rue d'Alschwill</t>
+  </si>
+  <si>
+    <t>Hegenheim</t>
+  </si>
+  <si>
+    <t>10 rue Alexandre Freund</t>
+  </si>
+  <si>
+    <t>Saint-Louis</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7edrJzm2ENiuUbcAA</t>
+  </si>
+  <si>
+    <t>Bureaux dans le Leclerc Drive. Place de parking / Accueil / 3 open space / Cuisine</t>
+  </si>
+  <si>
+    <t>154 €/m² = 38 500 € HT</t>
+  </si>
+  <si>
+    <t>186 €/m² = 55 800 € HT</t>
+  </si>
+  <si>
+    <t>186 €/m² = 113 088 € HT</t>
+  </si>
+  <si>
+    <t>186 €/m² = 47 802 € HT</t>
+  </si>
+  <si>
+    <t>65.1</t>
+  </si>
+  <si>
+    <t>65.2</t>
+  </si>
+  <si>
+    <t>Local disponible à la vente. Dans un retail Park avec drive Leclerc, à la frontière avec l'Allemagne et la Suisse</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/64%20-%20Blotzheim/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/64%20-%20Blotzheim/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/64%20-%20Blotzheim/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/64%20-%20Blotzheim/4%20plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/65.1%20-%20Huningue/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/65.1%20-%20Huningue/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/65.1%20-%20Huningue/3%20Plan.png</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/65.2%20-%20Huningue/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/65.2%20-%20Huningue/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/65.2%20-%20Huningue/3%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/66%20-%20Hegenheim/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/66%20-%20Hegenheim/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/66%20-%20Hegenheim/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/66%20-%20Hegenheim/4%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>47.607373</t>
+  </si>
+  <si>
+    <t>7.507876</t>
+  </si>
+  <si>
+    <t>47.597285</t>
+  </si>
+  <si>
+    <t>7.583632</t>
+  </si>
+  <si>
+    <t>47.589208</t>
+  </si>
+  <si>
+    <t>7.552250</t>
   </si>
 </sst>
 </file>
@@ -4814,7 +4933,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -4951,6 +5070,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5351,8 +5474,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX215" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AX215" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX223" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AX223" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="50">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="49" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -5747,7 +5870,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BH227"/>
+  <dimension ref="A1:BH232"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -29185,7 +29308,7 @@
       <c r="E147" s="26">
         <v>68330</v>
       </c>
-      <c r="F147" s="42" t="s">
+      <c r="F147" s="10" t="s">
         <v>890</v>
       </c>
       <c r="G147" s="39" t="str">
@@ -29303,7 +29426,7 @@
         <v>1040</v>
       </c>
       <c r="AT147" s="11" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="AU147" s="11"/>
       <c r="AV147" s="13" t="s">
@@ -36125,7 +36248,7 @@
         <v>48</v>
       </c>
       <c r="K190" s="10" t="s">
-        <v>103</v>
+        <v>1412</v>
       </c>
       <c r="L190" s="10"/>
       <c r="M190" s="12" t="s">
@@ -36716,7 +36839,9 @@
         <v>74</v>
       </c>
       <c r="AW193" s="14"/>
-      <c r="AX193" s="44"/>
+      <c r="AX193" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="194" spans="1:50" ht="38.25">
       <c r="A194" s="38" t="str">
@@ -36874,7 +36999,9 @@
         <v>74</v>
       </c>
       <c r="AW194" s="14"/>
-      <c r="AX194" s="44"/>
+      <c r="AX194" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="195" spans="1:50" ht="38.25">
       <c r="A195" s="38" t="str">
@@ -37032,7 +37159,9 @@
         <v>74</v>
       </c>
       <c r="AW195" s="14"/>
-      <c r="AX195" s="44"/>
+      <c r="AX195" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="196" spans="1:50" ht="38.25">
       <c r="A196" s="38" t="str">
@@ -37190,7 +37319,9 @@
         <v>74</v>
       </c>
       <c r="AW196" s="14"/>
-      <c r="AX196" s="44"/>
+      <c r="AX196" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="197" spans="1:50" ht="38.25">
       <c r="A197" s="38" t="str">
@@ -37348,7 +37479,9 @@
         <v>74</v>
       </c>
       <c r="AW197" s="14"/>
-      <c r="AX197" s="44"/>
+      <c r="AX197" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="198" spans="1:50" ht="38.25">
       <c r="A198" s="38" t="str">
@@ -37508,7 +37641,9 @@
         <v>74</v>
       </c>
       <c r="AW198" s="14"/>
-      <c r="AX198" s="44"/>
+      <c r="AX198" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="199" spans="1:50" ht="38.25">
       <c r="A199" s="38" t="str">
@@ -37666,7 +37801,9 @@
         <v>74</v>
       </c>
       <c r="AW199" s="14"/>
-      <c r="AX199" s="44"/>
+      <c r="AX199" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="200" spans="1:50" ht="38.25">
       <c r="A200" s="38" t="str">
@@ -37822,7 +37959,9 @@
         <v>74</v>
       </c>
       <c r="AW200" s="14"/>
-      <c r="AX200" s="44"/>
+      <c r="AX200" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="201" spans="1:50" ht="38.25">
       <c r="A201" s="38" t="str">
@@ -37980,7 +38119,9 @@
         <v>74</v>
       </c>
       <c r="AW201" s="14"/>
-      <c r="AX201" s="44"/>
+      <c r="AX201" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="202" spans="1:50" ht="38.25">
       <c r="A202" s="38" t="str">
@@ -38138,7 +38279,9 @@
         <v>74</v>
       </c>
       <c r="AW202" s="14"/>
-      <c r="AX202" s="44"/>
+      <c r="AX202" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="203" spans="1:50" ht="38.25">
       <c r="A203" s="38" t="str">
@@ -38294,7 +38437,9 @@
         <v>74</v>
       </c>
       <c r="AW203" s="14"/>
-      <c r="AX203" s="44"/>
+      <c r="AX203" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="204" spans="1:50" ht="38.25">
       <c r="A204" s="38" t="str">
@@ -38452,7 +38597,9 @@
         <v>74</v>
       </c>
       <c r="AW204" s="14"/>
-      <c r="AX204" s="44"/>
+      <c r="AX204" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="205" spans="1:50" ht="38.25">
       <c r="A205" s="38" t="str">
@@ -38610,7 +38757,9 @@
         <v>74</v>
       </c>
       <c r="AW205" s="14"/>
-      <c r="AX205" s="44"/>
+      <c r="AX205" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="206" spans="1:50" ht="38.25">
       <c r="A206" s="38" t="str">
@@ -38768,7 +38917,9 @@
         <v>74</v>
       </c>
       <c r="AW206" s="14"/>
-      <c r="AX206" s="44"/>
+      <c r="AX206" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="207" spans="1:50" ht="38.25">
       <c r="A207" s="38" t="str">
@@ -38924,7 +39075,9 @@
         <v>74</v>
       </c>
       <c r="AW207" s="14"/>
-      <c r="AX207" s="44"/>
+      <c r="AX207" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="208" spans="1:50" ht="38.25">
       <c r="A208" s="38" t="str">
@@ -39080,7 +39233,9 @@
         <v>74</v>
       </c>
       <c r="AW208" s="14"/>
-      <c r="AX208" s="44"/>
+      <c r="AX208" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="209" spans="1:50" ht="38.25">
       <c r="A209" s="38" t="str">
@@ -39236,7 +39391,9 @@
         <v>74</v>
       </c>
       <c r="AW209" s="14"/>
-      <c r="AX209" s="44"/>
+      <c r="AX209" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="210" spans="1:50" ht="38.25">
       <c r="A210" s="38" t="str">
@@ -39394,7 +39551,9 @@
         <v>74</v>
       </c>
       <c r="AW210" s="14"/>
-      <c r="AX210" s="44"/>
+      <c r="AX210" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="211" spans="1:50" ht="38.25">
       <c r="A211" s="38" t="str">
@@ -39550,7 +39709,9 @@
         <v>74</v>
       </c>
       <c r="AW211" s="14"/>
-      <c r="AX211" s="44"/>
+      <c r="AX211" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="212" spans="1:50" ht="38.25">
       <c r="A212" s="38" t="str">
@@ -39706,7 +39867,9 @@
         <v>74</v>
       </c>
       <c r="AW212" s="14"/>
-      <c r="AX212" s="44"/>
+      <c r="AX212" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="213" spans="1:50" ht="38.25">
       <c r="A213" s="38" t="str">
@@ -39864,7 +40027,9 @@
         <v>74</v>
       </c>
       <c r="AW213" s="14"/>
-      <c r="AX213" s="44"/>
+      <c r="AX213" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="214" spans="1:50" ht="38.25">
       <c r="A214" s="38" t="str">
@@ -40022,7 +40187,9 @@
         <v>74</v>
       </c>
       <c r="AW214" s="14"/>
-      <c r="AX214" s="44"/>
+      <c r="AX214" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="215" spans="1:50" ht="38.25">
       <c r="A215" s="38" t="str">
@@ -40180,15 +40347,1028 @@
         <v>74</v>
       </c>
       <c r="AW215" s="14"/>
-      <c r="AX215" s="44"/>
+      <c r="AX215" s="44">
+        <v>46058</v>
+      </c>
     </row>
-    <row r="226" spans="6:6">
-      <c r="F226" s="1" t="s">
+    <row r="216" spans="1:50" ht="38.25">
+      <c r="A216" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B216" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haut-Rhin</v>
+      </c>
+      <c r="C216" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>68</v>
+      </c>
+      <c r="D216" s="11" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E216" s="26">
+        <v>68730</v>
+      </c>
+      <c r="F216" s="42" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G216" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Hyper Leclerc Blotzheim
+5 bis rue Pierre Clostermann
+68730 - Blotzheim</v>
+      </c>
+      <c r="H216" s="15" t="s">
+        <v>1552</v>
+      </c>
+      <c r="I216" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K216" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L216" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M216" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N216" s="36"/>
+      <c r="O216" s="34">
+        <v>446</v>
+      </c>
+      <c r="P216" s="12"/>
+      <c r="Q216" s="34"/>
+      <c r="R216" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S216" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T216" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>66900</v>
+      </c>
+      <c r="U216" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5575</v>
+      </c>
+      <c r="V216" s="12">
+        <v>150</v>
+      </c>
+      <c r="W216" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X216" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1784</v>
+      </c>
+      <c r="Y216" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>148.66666666666666</v>
+      </c>
+      <c r="Z216" s="12">
+        <v>4</v>
+      </c>
+      <c r="AA216" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>4460</v>
+      </c>
+      <c r="AB216" s="12">
+        <v>10</v>
+      </c>
+      <c r="AC216" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD216" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE216" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>73144</v>
+      </c>
+      <c r="AF216" s="12"/>
+      <c r="AG216" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH216" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI216" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ216" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK216" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL216" s="10"/>
+      <c r="AM216" s="11"/>
+      <c r="AN216" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO216" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP216" s="11" t="s">
+        <v>1577</v>
+      </c>
+      <c r="AQ216" s="11" t="s">
+        <v>1578</v>
+      </c>
+      <c r="AR216" s="11">
+        <v>64</v>
+      </c>
+      <c r="AS216" s="36" t="s">
+        <v>1573</v>
+      </c>
+      <c r="AT216" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU216" s="11" t="s">
+        <v>1554</v>
+      </c>
+      <c r="AV216" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AW216" s="14"/>
+      <c r="AX216" s="44">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="217" spans="1:50" ht="38.25">
+      <c r="A217" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B217" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haut-Rhin</v>
+      </c>
+      <c r="C217" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>68</v>
+      </c>
+      <c r="D217" s="11" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E217" s="26">
+        <v>68330</v>
+      </c>
+      <c r="F217" s="42" t="s">
+        <v>890</v>
+      </c>
+      <c r="G217" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Les galeries d'Huningue
+9 avenue d'Alsace
+68330 - Huningue</v>
+      </c>
+      <c r="H217" s="15" t="s">
+        <v>1557</v>
+      </c>
+      <c r="I217" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J217" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K217" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L217" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M217" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N217" s="36" t="s">
+        <v>1572</v>
+      </c>
+      <c r="O217" s="34">
+        <v>300</v>
+      </c>
+      <c r="P217" s="12"/>
+      <c r="Q217" s="34"/>
+      <c r="R217" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S217" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T217" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>60000</v>
+      </c>
+      <c r="U217" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="V217" s="12">
+        <v>200</v>
+      </c>
+      <c r="W217" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X217" s="12"/>
+      <c r="Y217" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z217" s="12"/>
+      <c r="AA217" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB217" s="12"/>
+      <c r="AC217" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD217" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE217" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>60000</v>
+      </c>
+      <c r="AF217" s="12"/>
+      <c r="AG217" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH217" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI217" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ217" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK217" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL217" s="10"/>
+      <c r="AM217" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AN217" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO217" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP217" s="11" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AQ217" s="11" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AR217" s="11" t="s">
+        <v>1569</v>
+      </c>
+      <c r="AS217" s="36" t="s">
+        <v>1574</v>
+      </c>
+      <c r="AT217" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU217" s="11" t="s">
+        <v>1566</v>
+      </c>
+      <c r="AV217" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AW217" s="14"/>
+      <c r="AX217" s="44">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="218" spans="1:50" ht="38.25">
+      <c r="A218" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B218" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haut-Rhin</v>
+      </c>
+      <c r="C218" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>68</v>
+      </c>
+      <c r="D218" s="11" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E218" s="26">
+        <v>68331</v>
+      </c>
+      <c r="F218" s="42" t="s">
+        <v>890</v>
+      </c>
+      <c r="G218" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Les galeries d'Huningue
+7 avenue d'Alsace
+68331 - Huningue</v>
+      </c>
+      <c r="H218" s="15" t="s">
+        <v>1558</v>
+      </c>
+      <c r="I218" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K218" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L218" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M218" s="12" t="s">
+        <v>1179</v>
+      </c>
+      <c r="N218" s="36"/>
+      <c r="O218" s="34">
+        <v>608</v>
+      </c>
+      <c r="P218" s="12"/>
+      <c r="Q218" s="34"/>
+      <c r="R218" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S218" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T218" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>121600</v>
+      </c>
+      <c r="U218" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>10133.333333333334</v>
+      </c>
+      <c r="V218" s="12">
+        <v>200</v>
+      </c>
+      <c r="W218" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X218" s="12"/>
+      <c r="Y218" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z218" s="12"/>
+      <c r="AA218" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB218" s="12"/>
+      <c r="AC218" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD218" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE218" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>121600</v>
+      </c>
+      <c r="AF218" s="12"/>
+      <c r="AG218" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH218" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI218" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ218" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK218" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL218" s="10"/>
+      <c r="AM218" s="11" t="s">
+        <v>1571</v>
+      </c>
+      <c r="AN218" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO218" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP218" s="11" t="s">
+        <v>1579</v>
+      </c>
+      <c r="AQ218" s="11" t="s">
+        <v>1580</v>
+      </c>
+      <c r="AR218" s="11" t="s">
+        <v>1570</v>
+      </c>
+      <c r="AS218" s="36" t="s">
+        <v>1575</v>
+      </c>
+      <c r="AT218" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU218" s="11" t="s">
+        <v>1567</v>
+      </c>
+      <c r="AV218" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AW218" s="14"/>
+      <c r="AX218" s="44">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="219" spans="1:50" ht="38.25">
+      <c r="A219" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B219" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haut-Rhin</v>
+      </c>
+      <c r="C219" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>68</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E219" s="26">
+        <v>68220</v>
+      </c>
+      <c r="F219" s="42" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G219" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Les galeries d'Hegenheim
+Rue d'Alschwill
+68220 - Hegenheim</v>
+      </c>
+      <c r="H219" s="52"/>
+      <c r="I219" s="12"/>
+      <c r="J219" s="12"/>
+      <c r="K219" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L219" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M219" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N219" s="36"/>
+      <c r="O219" s="34">
+        <v>257</v>
+      </c>
+      <c r="P219" s="12"/>
+      <c r="Q219" s="34"/>
+      <c r="R219" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S219" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T219" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>51400</v>
+      </c>
+      <c r="U219" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4283.333333333333</v>
+      </c>
+      <c r="V219" s="12">
+        <v>200</v>
+      </c>
+      <c r="W219" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X219" s="12"/>
+      <c r="Y219" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z219" s="12"/>
+      <c r="AA219" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB219" s="12"/>
+      <c r="AC219" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD219" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE219" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>51400</v>
+      </c>
+      <c r="AF219" s="12"/>
+      <c r="AG219" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH219" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI219" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ219" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK219" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL219" s="10"/>
+      <c r="AM219" s="11"/>
+      <c r="AN219" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO219" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP219" s="11"/>
+      <c r="AQ219" s="11"/>
+      <c r="AR219" s="11">
+        <v>66</v>
+      </c>
+      <c r="AS219" s="36" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AT219" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU219" s="11" t="s">
+        <v>1568</v>
+      </c>
+      <c r="AV219" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AW219" s="14"/>
+      <c r="AX219" s="44">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="220" spans="1:50" ht="25.5">
+      <c r="A220" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B220" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Haut-Rhin</v>
+      </c>
+      <c r="C220" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>68</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E220" s="26">
+        <v>68300</v>
+      </c>
+      <c r="F220" s="42" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G220" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>10 rue Alexandre Freund
+68300 - Saint-Louis</v>
+      </c>
+      <c r="H220" s="15" t="s">
+        <v>1563</v>
+      </c>
+      <c r="I220" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J220" s="12"/>
+      <c r="K220" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="L220" s="10"/>
+      <c r="M220" s="12"/>
+      <c r="N220" s="36"/>
+      <c r="O220" s="34">
+        <v>250</v>
+      </c>
+      <c r="P220" s="12"/>
+      <c r="Q220" s="34"/>
+      <c r="R220" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S220" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T220" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>43750</v>
+      </c>
+      <c r="U220" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3645.8333333333335</v>
+      </c>
+      <c r="V220" s="12">
+        <v>175</v>
+      </c>
+      <c r="W220" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X220" s="12"/>
+      <c r="Y220" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z220" s="12"/>
+      <c r="AA220" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2000</v>
+      </c>
+      <c r="AB220" s="12">
+        <v>8</v>
+      </c>
+      <c r="AC220" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD220" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE220" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>45750</v>
+      </c>
+      <c r="AF220" s="12"/>
+      <c r="AG220" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH220" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI220" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ220" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK220" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL220" s="10"/>
+      <c r="AM220" s="11" t="s">
+        <v>1564</v>
+      </c>
+      <c r="AN220" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO220" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP220" s="11" t="s">
+        <v>1581</v>
+      </c>
+      <c r="AQ220" s="11" t="s">
+        <v>1582</v>
+      </c>
+      <c r="AR220" s="11">
+        <v>67</v>
+      </c>
+      <c r="AS220" s="36"/>
+      <c r="AT220" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU220" s="11" t="s">
+        <v>1565</v>
+      </c>
+      <c r="AV220" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AW220" s="14"/>
+      <c r="AX220" s="44">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="221" spans="1:50" ht="38.25">
+      <c r="A221" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Occitanie</v>
+      </c>
+      <c r="B221" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Lozère</v>
+      </c>
+      <c r="C221" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>48</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E221" s="26">
+        <v>48000</v>
+      </c>
+      <c r="F221" s="10" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G221" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Cœur Lozère
+Avenue de Ramilles
+48000 - Mende</v>
+      </c>
+      <c r="H221" s="15" t="s">
+        <v>1547</v>
+      </c>
+      <c r="I221" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J221" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K221" s="10"/>
+      <c r="L221" s="10"/>
+      <c r="M221" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N221" s="36"/>
+      <c r="O221" s="34"/>
+      <c r="P221" s="12"/>
+      <c r="Q221" s="34"/>
+      <c r="R221" s="10"/>
+      <c r="S221" s="12"/>
+      <c r="T221" s="12"/>
+      <c r="U221" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V221" s="12"/>
+      <c r="W221" s="12"/>
+      <c r="X221" s="12"/>
+      <c r="Y221" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z221" s="12"/>
+      <c r="AA221" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB221" s="12"/>
+      <c r="AC221" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD221" s="12"/>
+      <c r="AE221" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF221" s="12"/>
+      <c r="AG221" s="12"/>
+      <c r="AH221" s="12"/>
+      <c r="AI221" s="12"/>
+      <c r="AJ221" s="10"/>
+      <c r="AK221" s="10"/>
+      <c r="AL221" s="10"/>
+      <c r="AM221" s="11"/>
+      <c r="AN221" s="11"/>
+      <c r="AO221" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP221" s="11"/>
+      <c r="AQ221" s="11"/>
+      <c r="AR221" s="11"/>
+      <c r="AS221" s="36"/>
+      <c r="AT221" s="11"/>
+      <c r="AU221" s="11"/>
+      <c r="AV221" s="13"/>
+      <c r="AW221" s="14"/>
+      <c r="AX221" s="44"/>
+    </row>
+    <row r="222" spans="1:50" ht="38.25">
+      <c r="A222" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Occitanie</v>
+      </c>
+      <c r="B222" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Lozère</v>
+      </c>
+      <c r="C222" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>48</v>
+      </c>
+      <c r="D222" s="11" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E222" s="26">
+        <v>48001</v>
+      </c>
+      <c r="F222" s="10" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G222" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Cœur Lozère
+Avenue de Ramilles
+48001 - Mende</v>
+      </c>
+      <c r="H222" s="15" t="s">
+        <v>1548</v>
+      </c>
+      <c r="I222" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J222" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K222" s="10"/>
+      <c r="L222" s="10"/>
+      <c r="M222" s="12" t="s">
+        <v>1179</v>
+      </c>
+      <c r="N222" s="36"/>
+      <c r="O222" s="34"/>
+      <c r="P222" s="12"/>
+      <c r="Q222" s="34"/>
+      <c r="R222" s="10"/>
+      <c r="S222" s="12"/>
+      <c r="T222" s="12"/>
+      <c r="U222" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V222" s="12"/>
+      <c r="W222" s="12"/>
+      <c r="X222" s="12"/>
+      <c r="Y222" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z222" s="12"/>
+      <c r="AA222" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB222" s="12"/>
+      <c r="AC222" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD222" s="12"/>
+      <c r="AE222" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF222" s="12"/>
+      <c r="AG222" s="12"/>
+      <c r="AH222" s="12"/>
+      <c r="AI222" s="12"/>
+      <c r="AJ222" s="10"/>
+      <c r="AK222" s="10"/>
+      <c r="AL222" s="10"/>
+      <c r="AM222" s="11"/>
+      <c r="AN222" s="11"/>
+      <c r="AO222" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP222" s="11"/>
+      <c r="AQ222" s="11"/>
+      <c r="AR222" s="11"/>
+      <c r="AS222" s="36"/>
+      <c r="AT222" s="11"/>
+      <c r="AU222" s="11"/>
+      <c r="AV222" s="13"/>
+      <c r="AW222" s="14"/>
+      <c r="AX222" s="44"/>
+    </row>
+    <row r="223" spans="1:50" ht="38.25">
+      <c r="A223" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Occitanie</v>
+      </c>
+      <c r="B223" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Lozère</v>
+      </c>
+      <c r="C223" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>48</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E223" s="26">
+        <v>48002</v>
+      </c>
+      <c r="F223" s="10" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G223" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre commercial Cœur Lozère
+Avenue de Ramilles
+48002 - Mende</v>
+      </c>
+      <c r="H223" s="15" t="s">
+        <v>1549</v>
+      </c>
+      <c r="I223" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J223" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K223" s="10" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L223" s="10"/>
+      <c r="M223" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N223" s="36"/>
+      <c r="O223" s="34"/>
+      <c r="P223" s="12"/>
+      <c r="Q223" s="34"/>
+      <c r="R223" s="10"/>
+      <c r="S223" s="12"/>
+      <c r="T223" s="12"/>
+      <c r="U223" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V223" s="12"/>
+      <c r="W223" s="12"/>
+      <c r="X223" s="12"/>
+      <c r="Y223" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z223" s="12"/>
+      <c r="AA223" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB223" s="12"/>
+      <c r="AC223" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD223" s="12"/>
+      <c r="AE223" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF223" s="12"/>
+      <c r="AG223" s="12"/>
+      <c r="AH223" s="12"/>
+      <c r="AI223" s="12"/>
+      <c r="AJ223" s="10"/>
+      <c r="AK223" s="10"/>
+      <c r="AL223" s="10"/>
+      <c r="AM223" s="11"/>
+      <c r="AN223" s="11"/>
+      <c r="AO223" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP223" s="11"/>
+      <c r="AQ223" s="11"/>
+      <c r="AR223" s="11"/>
+      <c r="AS223" s="36"/>
+      <c r="AT223" s="11"/>
+      <c r="AU223" s="11"/>
+      <c r="AV223" s="13"/>
+      <c r="AW223" s="14"/>
+      <c r="AX223" s="44"/>
+    </row>
+    <row r="231" spans="6:6">
+      <c r="F231" s="1" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="227" spans="6:6">
-      <c r="F227" s="1" t="s">
+    <row r="232" spans="6:6">
+      <c r="F232" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -40306,72 +41486,79 @@
     <hyperlink ref="H143" r:id="rId109" xr:uid="{01C599EF-C1DF-4C31-ADC2-E79CCD9D3420}"/>
     <hyperlink ref="H145" r:id="rId110" xr:uid="{48DF072A-5724-4516-9EB9-B2B092F9ECBF}"/>
     <hyperlink ref="H146" r:id="rId111" xr:uid="{2D52890D-990D-499F-92B9-790A6B56B2C1}"/>
-    <hyperlink ref="H147" r:id="rId112" xr:uid="{D89787FE-D414-4ADC-AC02-C8B9D2520919}"/>
-    <hyperlink ref="H148" r:id="rId113" xr:uid="{83F81C45-2D7B-4019-9457-DB12A08DE525}"/>
-    <hyperlink ref="H149" r:id="rId114" xr:uid="{5DD490B2-A51A-488D-BCDE-B83932141509}"/>
-    <hyperlink ref="H150" r:id="rId115" xr:uid="{8FDF2590-E1B8-4CE8-9753-7BFB747102D3}"/>
-    <hyperlink ref="H151" r:id="rId116" xr:uid="{F9E1A7BC-0810-451D-AAC4-F0BE420D1B9F}"/>
-    <hyperlink ref="H152" r:id="rId117" xr:uid="{6B38E304-7485-42E7-9EFC-3CDA0B79C692}"/>
-    <hyperlink ref="H153" r:id="rId118" xr:uid="{9BAD643D-2774-4811-AF7F-3253EB54E8FC}"/>
-    <hyperlink ref="H154" r:id="rId119" xr:uid="{8C4EE05C-7B50-4EF6-B2F7-FACAB92DA663}"/>
-    <hyperlink ref="H158" r:id="rId120" xr:uid="{0D1E98E9-4BCF-4406-AFDA-600010FB176B}"/>
-    <hyperlink ref="H159" r:id="rId121" xr:uid="{580F9DBE-E800-4F84-BEDC-E8B38FD61F7A}"/>
-    <hyperlink ref="H160" r:id="rId122" xr:uid="{372123E9-8C5B-4111-8443-C1645E86AD4D}"/>
-    <hyperlink ref="H161" r:id="rId123" xr:uid="{CC20D8BA-62C0-4205-8CD5-E236C90A7669}"/>
-    <hyperlink ref="H168" r:id="rId124" xr:uid="{D9CEB66C-2A2B-4C50-90E4-25DDB2866B82}"/>
-    <hyperlink ref="H169" r:id="rId125" xr:uid="{77194CDF-321B-4F1D-8892-C65AB2918B74}"/>
-    <hyperlink ref="H170" r:id="rId126" xr:uid="{A510C509-E61B-4228-AC93-D0093532C7D2}"/>
-    <hyperlink ref="H171" r:id="rId127" xr:uid="{13D66F57-470F-41F4-93A6-03D5A2A4CCDB}"/>
-    <hyperlink ref="H172" r:id="rId128" xr:uid="{5B7EA501-9646-45C8-A6A4-6075F4FADE70}"/>
-    <hyperlink ref="H173" r:id="rId129" xr:uid="{6D822EC9-F492-4D93-A1BA-8FA65E1327B7}"/>
-    <hyperlink ref="H175" r:id="rId130" xr:uid="{3C8BCE0A-AAD1-4E3F-915C-B7BFA9B07703}"/>
-    <hyperlink ref="H176" r:id="rId131" xr:uid="{EB1761D0-DA2C-4FCB-8A87-DC3BF56A199A}"/>
-    <hyperlink ref="H174" r:id="rId132" xr:uid="{AC7B9731-155A-409D-B7DE-6A2C81027D18}"/>
-    <hyperlink ref="H177" r:id="rId133" xr:uid="{ED7C6A33-7CA0-4B59-BFC3-713467DF5837}"/>
-    <hyperlink ref="H155" r:id="rId134" xr:uid="{84DBA056-5C11-4ECE-9D32-78D0DE5AACCA}"/>
-    <hyperlink ref="H156" r:id="rId135" xr:uid="{3F6F7192-2423-4CFD-AC54-5D69482DCDAA}"/>
-    <hyperlink ref="H157" r:id="rId136" xr:uid="{34F05E83-B67A-4D2E-97A2-715EF4DB16F0}"/>
-    <hyperlink ref="H178" r:id="rId137" xr:uid="{0DCDD234-61DD-4535-96A0-1CB0ED1C39E2}"/>
-    <hyperlink ref="H162" r:id="rId138" xr:uid="{69AC0ECC-2E2A-4A8B-BC81-EF4428A37640}"/>
-    <hyperlink ref="H163:H167" r:id="rId139" display="https://maps.app.goo.gl/jjHUN2H4tKUGyBEQ7" xr:uid="{2DDA41A9-46D6-46F1-BFA4-95D30FE59882}"/>
-    <hyperlink ref="H179" r:id="rId140" xr:uid="{F6366A42-B67C-40CD-AFBC-6C8424BEB013}"/>
-    <hyperlink ref="H181" r:id="rId141" xr:uid="{AC4BD242-08DC-4A93-AF73-32CF15E14420}"/>
-    <hyperlink ref="H182" r:id="rId142" xr:uid="{3FEF2131-529B-4B74-9649-3B4B1CFC2613}"/>
-    <hyperlink ref="H183" r:id="rId143" xr:uid="{3F02EB48-A165-461F-8BAF-AC050FE23690}"/>
-    <hyperlink ref="H184" r:id="rId144" xr:uid="{145A22A7-33A1-43C0-A440-9E0FD9BB1AD1}"/>
-    <hyperlink ref="H185" r:id="rId145" xr:uid="{A5000FCA-4DF3-47B7-97D9-DAAC213C360B}"/>
-    <hyperlink ref="H186" r:id="rId146" xr:uid="{9FF463BE-AA91-4BC5-AE7D-4936D1C6D265}"/>
-    <hyperlink ref="H187" r:id="rId147" xr:uid="{EED7450E-F5F5-483A-B269-54C932486E0F}"/>
-    <hyperlink ref="H188" r:id="rId148" xr:uid="{B52E97C0-A3E5-471B-BD01-7BEB96586BB6}"/>
-    <hyperlink ref="H189" r:id="rId149" xr:uid="{6D139DEB-1BCB-45F1-9FA5-40A114985687}"/>
-    <hyperlink ref="H139" r:id="rId150" xr:uid="{069CCB02-48CE-4D86-8BBE-DFAEAC941704}"/>
-    <hyperlink ref="H180" r:id="rId151" xr:uid="{3FF7903C-E5BA-4ED9-88DD-9F4AF755FB57}"/>
-    <hyperlink ref="H190" r:id="rId152" xr:uid="{B58FC76B-D0FB-47D2-9309-07FBB7AE8F26}"/>
-    <hyperlink ref="H191" r:id="rId153" xr:uid="{5ACAB395-A666-4978-812B-9B6039F53703}"/>
-    <hyperlink ref="H192" r:id="rId154" xr:uid="{21A42A74-18EE-46BA-BF13-26B8D1F6FB47}"/>
-    <hyperlink ref="H193" r:id="rId155" xr:uid="{979A4771-81FC-497B-97EF-32C019953489}"/>
-    <hyperlink ref="H194" r:id="rId156" xr:uid="{234D72AD-6212-4E7C-8477-5EE09B54842C}"/>
-    <hyperlink ref="H195" r:id="rId157" xr:uid="{00FC64E2-B2F8-4262-AD93-67A69A51A2AE}"/>
-    <hyperlink ref="H198" r:id="rId158" xr:uid="{37D46FE9-659B-4E71-B1B0-2BAE5EB3E001}"/>
-    <hyperlink ref="H200" r:id="rId159" xr:uid="{C1FEA757-567F-46DB-8BE8-C181F4790348}"/>
-    <hyperlink ref="H202" r:id="rId160" xr:uid="{E5DA9A5D-81D1-4927-A98E-48C8E1B7F848}"/>
-    <hyperlink ref="H204" r:id="rId161" xr:uid="{BF1AC4BD-BCB3-41AE-BB4E-A4D7D4B9CA30}"/>
-    <hyperlink ref="H206" r:id="rId162" xr:uid="{F331605E-78A2-41C4-A9DE-125F32D6DA17}"/>
-    <hyperlink ref="H208" r:id="rId163" xr:uid="{CD04C61F-F4DD-4619-8D0C-B117149DDD16}"/>
-    <hyperlink ref="H211" r:id="rId164" xr:uid="{126CAEE5-AFE9-4D78-8299-0693794DBF35}"/>
-    <hyperlink ref="H213" r:id="rId165" xr:uid="{99CC6C3B-99A9-43A2-98C5-FB3C0CDBB22E}"/>
-    <hyperlink ref="H215" r:id="rId166" xr:uid="{5ACB8786-94C9-4AC5-891E-06289DFF8043}"/>
-    <hyperlink ref="H196" r:id="rId167" xr:uid="{2FDB9825-2079-4C7E-B037-8188CA0176F5}"/>
-    <hyperlink ref="H199" r:id="rId168" xr:uid="{A69F4B4C-FA3C-439D-BC44-569193F38E47}"/>
-    <hyperlink ref="H201" r:id="rId169" xr:uid="{46585970-332F-4A0A-9FB9-F74633BF4F42}"/>
-    <hyperlink ref="H203" r:id="rId170" xr:uid="{8D52DD5E-FD4A-4159-BFA0-B6EE5B956520}"/>
-    <hyperlink ref="H205" r:id="rId171" xr:uid="{DDFB99AD-CCF9-4F9C-B530-960F480ECD4B}"/>
-    <hyperlink ref="H207" r:id="rId172" xr:uid="{8C88AF55-D328-4D4E-ACE7-C01C70716F01}"/>
-    <hyperlink ref="H210" r:id="rId173" xr:uid="{A2384EAF-1892-4C85-B4DB-D89DEED6A1DD}"/>
-    <hyperlink ref="H212" r:id="rId174" xr:uid="{D6D56087-231C-4ABA-8429-E4BF41585FE5}"/>
-    <hyperlink ref="H214" r:id="rId175" xr:uid="{D09EAEF8-49AC-4164-AAB1-5DDF19295801}"/>
-    <hyperlink ref="H209" r:id="rId176" display="https://maps.app.goo.gl/RJ2QRVrW96tKL7ur6" xr:uid="{609C48FB-80B4-46B2-AA88-2F3D30BF6C33}"/>
-    <hyperlink ref="H197" r:id="rId177" xr:uid="{2E729EBE-5AE8-4BE9-AA51-7933BA8C3C79}"/>
+    <hyperlink ref="H148" r:id="rId112" xr:uid="{83F81C45-2D7B-4019-9457-DB12A08DE525}"/>
+    <hyperlink ref="H149" r:id="rId113" xr:uid="{5DD490B2-A51A-488D-BCDE-B83932141509}"/>
+    <hyperlink ref="H150" r:id="rId114" xr:uid="{8FDF2590-E1B8-4CE8-9753-7BFB747102D3}"/>
+    <hyperlink ref="H151" r:id="rId115" xr:uid="{F9E1A7BC-0810-451D-AAC4-F0BE420D1B9F}"/>
+    <hyperlink ref="H152" r:id="rId116" xr:uid="{6B38E304-7485-42E7-9EFC-3CDA0B79C692}"/>
+    <hyperlink ref="H153" r:id="rId117" xr:uid="{9BAD643D-2774-4811-AF7F-3253EB54E8FC}"/>
+    <hyperlink ref="H154" r:id="rId118" xr:uid="{8C4EE05C-7B50-4EF6-B2F7-FACAB92DA663}"/>
+    <hyperlink ref="H158" r:id="rId119" xr:uid="{0D1E98E9-4BCF-4406-AFDA-600010FB176B}"/>
+    <hyperlink ref="H159" r:id="rId120" xr:uid="{580F9DBE-E800-4F84-BEDC-E8B38FD61F7A}"/>
+    <hyperlink ref="H160" r:id="rId121" xr:uid="{372123E9-8C5B-4111-8443-C1645E86AD4D}"/>
+    <hyperlink ref="H161" r:id="rId122" xr:uid="{CC20D8BA-62C0-4205-8CD5-E236C90A7669}"/>
+    <hyperlink ref="H168" r:id="rId123" xr:uid="{D9CEB66C-2A2B-4C50-90E4-25DDB2866B82}"/>
+    <hyperlink ref="H169" r:id="rId124" xr:uid="{77194CDF-321B-4F1D-8892-C65AB2918B74}"/>
+    <hyperlink ref="H170" r:id="rId125" xr:uid="{A510C509-E61B-4228-AC93-D0093532C7D2}"/>
+    <hyperlink ref="H171" r:id="rId126" xr:uid="{13D66F57-470F-41F4-93A6-03D5A2A4CCDB}"/>
+    <hyperlink ref="H172" r:id="rId127" xr:uid="{5B7EA501-9646-45C8-A6A4-6075F4FADE70}"/>
+    <hyperlink ref="H173" r:id="rId128" xr:uid="{6D822EC9-F492-4D93-A1BA-8FA65E1327B7}"/>
+    <hyperlink ref="H175" r:id="rId129" xr:uid="{3C8BCE0A-AAD1-4E3F-915C-B7BFA9B07703}"/>
+    <hyperlink ref="H176" r:id="rId130" xr:uid="{EB1761D0-DA2C-4FCB-8A87-DC3BF56A199A}"/>
+    <hyperlink ref="H174" r:id="rId131" xr:uid="{AC7B9731-155A-409D-B7DE-6A2C81027D18}"/>
+    <hyperlink ref="H177" r:id="rId132" xr:uid="{ED7C6A33-7CA0-4B59-BFC3-713467DF5837}"/>
+    <hyperlink ref="H155" r:id="rId133" xr:uid="{84DBA056-5C11-4ECE-9D32-78D0DE5AACCA}"/>
+    <hyperlink ref="H156" r:id="rId134" xr:uid="{3F6F7192-2423-4CFD-AC54-5D69482DCDAA}"/>
+    <hyperlink ref="H157" r:id="rId135" xr:uid="{34F05E83-B67A-4D2E-97A2-715EF4DB16F0}"/>
+    <hyperlink ref="H178" r:id="rId136" xr:uid="{0DCDD234-61DD-4535-96A0-1CB0ED1C39E2}"/>
+    <hyperlink ref="H162" r:id="rId137" xr:uid="{69AC0ECC-2E2A-4A8B-BC81-EF4428A37640}"/>
+    <hyperlink ref="H163:H167" r:id="rId138" display="https://maps.app.goo.gl/jjHUN2H4tKUGyBEQ7" xr:uid="{2DDA41A9-46D6-46F1-BFA4-95D30FE59882}"/>
+    <hyperlink ref="H179" r:id="rId139" xr:uid="{F6366A42-B67C-40CD-AFBC-6C8424BEB013}"/>
+    <hyperlink ref="H181" r:id="rId140" xr:uid="{AC4BD242-08DC-4A93-AF73-32CF15E14420}"/>
+    <hyperlink ref="H182" r:id="rId141" xr:uid="{3FEF2131-529B-4B74-9649-3B4B1CFC2613}"/>
+    <hyperlink ref="H183" r:id="rId142" xr:uid="{3F02EB48-A165-461F-8BAF-AC050FE23690}"/>
+    <hyperlink ref="H184" r:id="rId143" xr:uid="{145A22A7-33A1-43C0-A440-9E0FD9BB1AD1}"/>
+    <hyperlink ref="H185" r:id="rId144" xr:uid="{A5000FCA-4DF3-47B7-97D9-DAAC213C360B}"/>
+    <hyperlink ref="H186" r:id="rId145" xr:uid="{9FF463BE-AA91-4BC5-AE7D-4936D1C6D265}"/>
+    <hyperlink ref="H187" r:id="rId146" xr:uid="{EED7450E-F5F5-483A-B269-54C932486E0F}"/>
+    <hyperlink ref="H188" r:id="rId147" xr:uid="{B52E97C0-A3E5-471B-BD01-7BEB96586BB6}"/>
+    <hyperlink ref="H189" r:id="rId148" xr:uid="{6D139DEB-1BCB-45F1-9FA5-40A114985687}"/>
+    <hyperlink ref="H139" r:id="rId149" xr:uid="{069CCB02-48CE-4D86-8BBE-DFAEAC941704}"/>
+    <hyperlink ref="H180" r:id="rId150" xr:uid="{3FF7903C-E5BA-4ED9-88DD-9F4AF755FB57}"/>
+    <hyperlink ref="H190" r:id="rId151" xr:uid="{B58FC76B-D0FB-47D2-9309-07FBB7AE8F26}"/>
+    <hyperlink ref="H191" r:id="rId152" xr:uid="{5ACAB395-A666-4978-812B-9B6039F53703}"/>
+    <hyperlink ref="H192" r:id="rId153" xr:uid="{21A42A74-18EE-46BA-BF13-26B8D1F6FB47}"/>
+    <hyperlink ref="H193" r:id="rId154" xr:uid="{979A4771-81FC-497B-97EF-32C019953489}"/>
+    <hyperlink ref="H194" r:id="rId155" xr:uid="{234D72AD-6212-4E7C-8477-5EE09B54842C}"/>
+    <hyperlink ref="H195" r:id="rId156" xr:uid="{00FC64E2-B2F8-4262-AD93-67A69A51A2AE}"/>
+    <hyperlink ref="H198" r:id="rId157" xr:uid="{37D46FE9-659B-4E71-B1B0-2BAE5EB3E001}"/>
+    <hyperlink ref="H200" r:id="rId158" xr:uid="{C1FEA757-567F-46DB-8BE8-C181F4790348}"/>
+    <hyperlink ref="H202" r:id="rId159" xr:uid="{E5DA9A5D-81D1-4927-A98E-48C8E1B7F848}"/>
+    <hyperlink ref="H204" r:id="rId160" xr:uid="{BF1AC4BD-BCB3-41AE-BB4E-A4D7D4B9CA30}"/>
+    <hyperlink ref="H206" r:id="rId161" xr:uid="{F331605E-78A2-41C4-A9DE-125F32D6DA17}"/>
+    <hyperlink ref="H208" r:id="rId162" xr:uid="{CD04C61F-F4DD-4619-8D0C-B117149DDD16}"/>
+    <hyperlink ref="H211" r:id="rId163" xr:uid="{126CAEE5-AFE9-4D78-8299-0693794DBF35}"/>
+    <hyperlink ref="H213" r:id="rId164" xr:uid="{99CC6C3B-99A9-43A2-98C5-FB3C0CDBB22E}"/>
+    <hyperlink ref="H215" r:id="rId165" xr:uid="{5ACB8786-94C9-4AC5-891E-06289DFF8043}"/>
+    <hyperlink ref="H196" r:id="rId166" xr:uid="{2FDB9825-2079-4C7E-B037-8188CA0176F5}"/>
+    <hyperlink ref="H199" r:id="rId167" xr:uid="{A69F4B4C-FA3C-439D-BC44-569193F38E47}"/>
+    <hyperlink ref="H201" r:id="rId168" xr:uid="{46585970-332F-4A0A-9FB9-F74633BF4F42}"/>
+    <hyperlink ref="H203" r:id="rId169" xr:uid="{8D52DD5E-FD4A-4159-BFA0-B6EE5B956520}"/>
+    <hyperlink ref="H205" r:id="rId170" xr:uid="{DDFB99AD-CCF9-4F9C-B530-960F480ECD4B}"/>
+    <hyperlink ref="H207" r:id="rId171" xr:uid="{8C88AF55-D328-4D4E-ACE7-C01C70716F01}"/>
+    <hyperlink ref="H210" r:id="rId172" xr:uid="{A2384EAF-1892-4C85-B4DB-D89DEED6A1DD}"/>
+    <hyperlink ref="H212" r:id="rId173" xr:uid="{D6D56087-231C-4ABA-8429-E4BF41585FE5}"/>
+    <hyperlink ref="H214" r:id="rId174" xr:uid="{D09EAEF8-49AC-4164-AAB1-5DDF19295801}"/>
+    <hyperlink ref="H209" r:id="rId175" display="https://maps.app.goo.gl/RJ2QRVrW96tKL7ur6" xr:uid="{609C48FB-80B4-46B2-AA88-2F3D30BF6C33}"/>
+    <hyperlink ref="H197" r:id="rId176" xr:uid="{2E729EBE-5AE8-4BE9-AA51-7933BA8C3C79}"/>
+    <hyperlink ref="H221" r:id="rId177" xr:uid="{CCF25449-1659-4582-89F9-12D2B6EE3579}"/>
+    <hyperlink ref="H222" r:id="rId178" display="https://maps.app.goo.gl/7dsMYhd2KW95ZzZs5" xr:uid="{EC1AD3C9-DDCC-4E6E-B2E9-DAF4ADC35D2C}"/>
+    <hyperlink ref="H223" r:id="rId179" display="https://maps.app.goo.gl/7dsMYhd2KW95ZzZs5" xr:uid="{50958474-7E87-4C6E-8635-C114CA360BBD}"/>
+    <hyperlink ref="H216" r:id="rId180" xr:uid="{9041352D-F93F-4B8D-B1AB-6E12264A34EA}"/>
+    <hyperlink ref="H217" r:id="rId181" xr:uid="{FB6C0D8E-2AF1-40BC-BE6E-2992CB054D78}"/>
+    <hyperlink ref="H218" r:id="rId182" xr:uid="{1F235C3F-C9DB-4C11-8CCF-0C97AB89EBD7}"/>
+    <hyperlink ref="H220" r:id="rId183" xr:uid="{388632CD-FE0B-4C31-ACA8-6DA26C4D8ADF}"/>
+    <hyperlink ref="H147" r:id="rId184" xr:uid="{D89787FE-D414-4ADC-AC02-C8B9D2520919}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -40380,7 +41567,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId178"/>
+    <tablePart r:id="rId185"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E60CBC1-BFED-401D-8B0B-F2D8D706453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663BDF42-6DA8-4271-8B94-77DF6F261FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6488" uniqueCount="1583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7208" uniqueCount="1707">
   <si>
     <t>Contact</t>
   </si>
@@ -4803,6 +4803,378 @@
   </si>
   <si>
     <t>7.552250</t>
+  </si>
+  <si>
+    <t>5 rue Victor Hugo</t>
+  </si>
+  <si>
+    <t>Alfortville</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oK3xmMU55tobrmn87</t>
+  </si>
+  <si>
+    <t>Bron</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vYJoaUYwYjP8JKaEA</t>
+  </si>
+  <si>
+    <t>Place du général Jean Raby</t>
+  </si>
+  <si>
+    <t>1 000 €HT</t>
+  </si>
+  <si>
+    <t>Colombes</t>
+  </si>
+  <si>
+    <t>Joué les Tours</t>
+  </si>
+  <si>
+    <t>Lille Fives</t>
+  </si>
+  <si>
+    <t>Lille Hellemmes</t>
+  </si>
+  <si>
+    <t>Montreuil</t>
+  </si>
+  <si>
+    <t>Poissy</t>
+  </si>
+  <si>
+    <t>Saint-Ouen</t>
+  </si>
+  <si>
+    <t>La Queue en Brie</t>
+  </si>
+  <si>
+    <t>Lyon Confluence</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>8 et 9</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>6A</t>
+  </si>
+  <si>
+    <t>6B</t>
+  </si>
+  <si>
+    <t>Bat. 2 - L1</t>
+  </si>
+  <si>
+    <t>Bat. 2 - L2</t>
+  </si>
+  <si>
+    <t>2200</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>rue du Colonel Arnaud Beltrame</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZPoo7HsyrDthxYXT7</t>
+  </si>
+  <si>
+    <t>32 boulevard de Finlande</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jtsXLNMtupvw8FSD8</t>
+  </si>
+  <si>
+    <t>rue de la rotière</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BD22NECiYNrbeSTe7</t>
+  </si>
+  <si>
+    <t>178 rue Faidherbes</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/me3i2cvSJCdtSR2q6</t>
+  </si>
+  <si>
+    <t>boulevard de l'usine</t>
+  </si>
+  <si>
+    <t>297 rue de Rosny</t>
+  </si>
+  <si>
+    <t>299 rue de Rosny</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tetcRbeEJe7WMZv5A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BiMxAnX6CZMYp9hx6</t>
+  </si>
+  <si>
+    <t>30 rue Maurice Clerc</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/u1kz5AiezeXSAGLR7</t>
+  </si>
+  <si>
+    <t>12 bis rue des Bateliers</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KQauYVyzMqgPPWgM8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oQw4ZXEQVPp4zXL68</t>
+  </si>
+  <si>
+    <t>rue Dunoyer de Segonzac</t>
+  </si>
+  <si>
+    <t>Allée Louis Thomas Achille</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rYXwsZdHTTd2e5Xo7</t>
+  </si>
+  <si>
+    <t>68.1</t>
+  </si>
+  <si>
+    <t>68.2</t>
+  </si>
+  <si>
+    <t>78.2</t>
+  </si>
+  <si>
+    <t>68.3</t>
+  </si>
+  <si>
+    <t>Hyper U Mende</t>
+  </si>
+  <si>
+    <t>Braxton</t>
+  </si>
+  <si>
+    <t>250 €/m² = 35 000 €</t>
+  </si>
+  <si>
+    <t>139 €/m² = 31 780 €</t>
+  </si>
+  <si>
+    <t>80 €/m² = 29 040 €</t>
+  </si>
+  <si>
+    <t>183 €/m² = 20 130 €</t>
+  </si>
+  <si>
+    <t>183 €/m² = 20 500 €</t>
+  </si>
+  <si>
+    <t>349 €/m² = 30 030 €</t>
+  </si>
+  <si>
+    <t>330 €/m² = 30 030 €</t>
+  </si>
+  <si>
+    <t>150 €/m² = 25 050 €</t>
+  </si>
+  <si>
+    <t>150 €/m² = 18 450 €</t>
+  </si>
+  <si>
+    <t>80 €/m² = 16 004 €</t>
+  </si>
+  <si>
+    <t>157 €/m² = 8 454 €</t>
+  </si>
+  <si>
+    <t>140 €/m² = 21 000 €</t>
+  </si>
+  <si>
+    <t>199 €/m² = 10 400 €</t>
+  </si>
+  <si>
+    <t>198 €/m² = 7 600 €</t>
+  </si>
+  <si>
+    <t>116 €/m² = 20 000 €</t>
+  </si>
+  <si>
+    <t>147 €/m² = 46 995 €</t>
+  </si>
+  <si>
+    <t>150 €/m² = 42 060 €</t>
+  </si>
+  <si>
+    <t>184 €/m² = 24 300 €</t>
+  </si>
+  <si>
+    <t>184 €/m² = 20 370 €</t>
+  </si>
+  <si>
+    <t>310 €/m² = 40 000 €</t>
+  </si>
+  <si>
+    <t>250 €/m² = 13 193 €</t>
+  </si>
+  <si>
+    <t>200 €/m² = 30 446 €</t>
+  </si>
+  <si>
+    <t>205 €/m² = 19 526 €</t>
+  </si>
+  <si>
+    <t>260 €/m² = 9 789 €</t>
+  </si>
+  <si>
+    <t>168 €/m² = 41 716 €</t>
+  </si>
+  <si>
+    <t>131 €/m² = 34 610 €</t>
+  </si>
+  <si>
+    <t>200 €/m² = 34 866 €</t>
+  </si>
+  <si>
+    <t>133 €/m² = 31 811 €</t>
+  </si>
+  <si>
+    <t>70.1</t>
+  </si>
+  <si>
+    <t>70.2</t>
+  </si>
+  <si>
+    <t>70.3</t>
+  </si>
+  <si>
+    <t>70.4</t>
+  </si>
+  <si>
+    <t>70.5</t>
+  </si>
+  <si>
+    <t>70.6</t>
+  </si>
+  <si>
+    <t>70.7</t>
+  </si>
+  <si>
+    <t>70.8</t>
+  </si>
+  <si>
+    <t>74.1</t>
+  </si>
+  <si>
+    <t>74.2</t>
+  </si>
+  <si>
+    <t>74.3</t>
+  </si>
+  <si>
+    <t>75.1</t>
+  </si>
+  <si>
+    <t>75.2</t>
+  </si>
+  <si>
+    <t>76.1</t>
+  </si>
+  <si>
+    <t>76.2</t>
+  </si>
+  <si>
+    <t>78.1</t>
+  </si>
+  <si>
+    <t>78.3</t>
+  </si>
+  <si>
+    <t>78.4</t>
+  </si>
+  <si>
+    <t>79.1</t>
+  </si>
+  <si>
+    <t>79.2</t>
+  </si>
+  <si>
+    <t>79.3</t>
+  </si>
+  <si>
+    <t>79.4</t>
+  </si>
+  <si>
+    <t>44.515376</t>
+  </si>
+  <si>
+    <t>3.479772</t>
+  </si>
+  <si>
+    <t>44.515273</t>
+  </si>
+  <si>
+    <t>3.479533</t>
+  </si>
+  <si>
+    <t>44.515519</t>
+  </si>
+  <si>
+    <t>3.479734</t>
+  </si>
+  <si>
+    <t>419 + 138</t>
+  </si>
+  <si>
+    <t>42 000 € HT</t>
+  </si>
+  <si>
+    <t>6 000 € HT</t>
+  </si>
+  <si>
+    <t>60 000 € HT</t>
+  </si>
+  <si>
+    <t>Gemo, King Jouet, Sport 2000, …</t>
+  </si>
+  <si>
+    <t>Seul Hypermarché de la Lozère. CA de 75 M€, dans une bonne zone commerciale avec McDonald's, Bricomarché, Feu Vert, But, Picard, Gamm Vert…</t>
+  </si>
+  <si>
+    <t>300 + 80</t>
+  </si>
+  <si>
+    <t>Cession de droit au bail. Seul Hypermarché de la Lozère. CA de 75 M€, dans une bonne zone commerciale avec McDonald's, Bricomarché, Feu Vert, But, Picard, Gamm Vert…</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/5%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>Location ou à vendre. Seul Hypermarché de la Lozère. CA de 75 M€, dans une bonne zone commerciale avec McDonald's, Bricomarché, Feu Vert, But, Picard, Gamm Vert…</t>
   </si>
 </sst>
 </file>
@@ -5474,8 +5846,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX223" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AX223" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX251" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AX251" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="50">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="49" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -5870,7 +6242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BH232"/>
+  <dimension ref="A1:BH255"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -5907,8 +6279,8 @@
     <col min="37" max="37" width="11.25" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9.625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="64.5" style="1" customWidth="1"/>
-    <col min="40" max="40" width="53.875" style="1" customWidth="1"/>
-    <col min="41" max="41" width="50.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="24.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="50.25" style="1" customWidth="1"/>
     <col min="42" max="42" width="41.5" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="17.625" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="19.25" style="1" bestFit="1" customWidth="1"/>
@@ -40968,7 +41340,9 @@
         <v>1206</v>
       </c>
       <c r="L220" s="10"/>
-      <c r="M220" s="12"/>
+      <c r="M220" s="12" t="s">
+        <v>103</v>
+      </c>
       <c r="N220" s="36"/>
       <c r="O220" s="34">
         <v>250</v>
@@ -41106,65 +41480,125 @@
       <c r="J221" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K221" s="10"/>
+      <c r="K221" s="10" t="s">
+        <v>103</v>
+      </c>
       <c r="L221" s="10"/>
       <c r="M221" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="N221" s="36"/>
-      <c r="O221" s="34"/>
-      <c r="P221" s="12"/>
+        <v>1179</v>
+      </c>
+      <c r="N221" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="O221" s="34">
+        <v>557</v>
+      </c>
+      <c r="P221" s="12" t="s">
+        <v>1697</v>
+      </c>
       <c r="Q221" s="34"/>
-      <c r="R221" s="10"/>
-      <c r="S221" s="12"/>
-      <c r="T221" s="12"/>
+      <c r="R221" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S221" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T221" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>83550</v>
+      </c>
       <c r="U221" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V221" s="12"/>
-      <c r="W221" s="12"/>
-      <c r="X221" s="12"/>
+        <v>6962.5</v>
+      </c>
+      <c r="V221" s="12">
+        <v>150</v>
+      </c>
+      <c r="W221" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X221" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>8355</v>
+      </c>
       <c r="Y221" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z221" s="12"/>
+        <v>696.25</v>
+      </c>
+      <c r="Z221" s="12">
+        <v>15</v>
+      </c>
       <c r="AA221" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB221" s="12"/>
+        <v>7519.5</v>
+      </c>
+      <c r="AB221" s="12">
+        <v>13.5</v>
+      </c>
       <c r="AC221" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AD221" s="12"/>
+      <c r="AD221" s="12" t="s">
+        <v>103</v>
+      </c>
       <c r="AE221" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
+        <v>99424.5</v>
       </c>
       <c r="AF221" s="12"/>
-      <c r="AG221" s="12"/>
-      <c r="AH221" s="12"/>
-      <c r="AI221" s="12"/>
-      <c r="AJ221" s="10"/>
-      <c r="AK221" s="10"/>
-      <c r="AL221" s="10"/>
-      <c r="AM221" s="11"/>
-      <c r="AN221" s="11"/>
+      <c r="AG221" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH221" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI221" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ221" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK221" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL221" s="10" t="s">
+        <v>1701</v>
+      </c>
+      <c r="AM221" s="11" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AN221" s="11" t="s">
+        <v>103</v>
+      </c>
       <c r="AO221" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="AP221" s="11"/>
-      <c r="AQ221" s="11"/>
-      <c r="AR221" s="11"/>
-      <c r="AS221" s="36"/>
-      <c r="AT221" s="11"/>
-      <c r="AU221" s="11"/>
-      <c r="AV221" s="13"/>
+      <c r="AP221" s="11" t="s">
+        <v>1691</v>
+      </c>
+      <c r="AQ221" s="11" t="s">
+        <v>1692</v>
+      </c>
+      <c r="AR221" s="11" t="s">
+        <v>1635</v>
+      </c>
+      <c r="AS221" s="36" t="s">
+        <v>1705</v>
+      </c>
+      <c r="AT221" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU221" s="11" t="s">
+        <v>1700</v>
+      </c>
+      <c r="AV221" s="13" t="s">
+        <v>1639</v>
+      </c>
       <c r="AW221" s="14"/>
-      <c r="AX221" s="44"/>
+      <c r="AX221" s="44">
+        <v>46071</v>
+      </c>
     </row>
     <row r="222" spans="1:50" ht="38.25">
       <c r="A222" s="38" t="str">
@@ -41183,7 +41617,7 @@
         <v>1545</v>
       </c>
       <c r="E222" s="26">
-        <v>48001</v>
+        <v>48000</v>
       </c>
       <c r="F222" s="10" t="s">
         <v>1546</v>
@@ -41192,7 +41626,7 @@
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Centre commercial Cœur Lozère
 Avenue de Ramilles
-48001 - Mende</v>
+48000 - Mende</v>
       </c>
       <c r="H222" s="15" t="s">
         <v>1548</v>
@@ -41203,24 +41637,43 @@
       <c r="J222" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K222" s="10"/>
+      <c r="K222" s="10" t="s">
+        <v>103</v>
+      </c>
       <c r="L222" s="10"/>
       <c r="M222" s="12" t="s">
         <v>1179</v>
       </c>
-      <c r="N222" s="36"/>
-      <c r="O222" s="34"/>
-      <c r="P222" s="12"/>
+      <c r="N222" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="O222" s="34">
+        <v>380</v>
+      </c>
+      <c r="P222" s="12" t="s">
+        <v>1703</v>
+      </c>
       <c r="Q222" s="34"/>
-      <c r="R222" s="10"/>
-      <c r="S222" s="12"/>
-      <c r="T222" s="12"/>
+      <c r="R222" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S222" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T222" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>66500</v>
+      </c>
       <c r="U222" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V222" s="12"/>
-      <c r="W222" s="12"/>
+        <v>5541.666666666667</v>
+      </c>
+      <c r="V222" s="12">
+        <v>175</v>
+      </c>
+      <c r="W222" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="X222" s="12"/>
       <c r="Y222" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
@@ -41236,32 +41689,66 @@
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AD222" s="12"/>
+      <c r="AD222" s="12" t="s">
+        <v>103</v>
+      </c>
       <c r="AE222" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
+        <v>66500</v>
       </c>
       <c r="AF222" s="12"/>
-      <c r="AG222" s="12"/>
-      <c r="AH222" s="12"/>
-      <c r="AI222" s="12"/>
-      <c r="AJ222" s="10"/>
-      <c r="AK222" s="10"/>
-      <c r="AL222" s="10"/>
-      <c r="AM222" s="11"/>
-      <c r="AN222" s="11"/>
+      <c r="AG222" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH222" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI222" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ222" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK222" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL222" s="10" t="s">
+        <v>1701</v>
+      </c>
+      <c r="AM222" s="11" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AN222" s="11" t="s">
+        <v>103</v>
+      </c>
       <c r="AO222" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="AP222" s="11"/>
-      <c r="AQ222" s="11"/>
-      <c r="AR222" s="11"/>
-      <c r="AS222" s="36"/>
-      <c r="AT222" s="11"/>
-      <c r="AU222" s="11"/>
-      <c r="AV222" s="13"/>
+      <c r="AP222" s="11" t="s">
+        <v>1693</v>
+      </c>
+      <c r="AQ222" s="11" t="s">
+        <v>1694</v>
+      </c>
+      <c r="AR222" s="11" t="s">
+        <v>1636</v>
+      </c>
+      <c r="AS222" s="36" t="s">
+        <v>1705</v>
+      </c>
+      <c r="AT222" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU222" s="11" t="s">
+        <v>1698</v>
+      </c>
+      <c r="AV222" s="13" t="s">
+        <v>1639</v>
+      </c>
       <c r="AW222" s="14"/>
-      <c r="AX222" s="44"/>
+      <c r="AX222" s="44">
+        <v>46071</v>
+      </c>
     </row>
     <row r="223" spans="1:50" ht="38.25">
       <c r="A223" s="38" t="str">
@@ -41280,7 +41767,7 @@
         <v>1545</v>
       </c>
       <c r="E223" s="26">
-        <v>48002</v>
+        <v>48000</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>1546</v>
@@ -41289,7 +41776,7 @@
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
         <v>Centre commercial Cœur Lozère
 Avenue de Ramilles
-48002 - Mende</v>
+48000 - Mende</v>
       </c>
       <c r="H223" s="15" t="s">
         <v>1549</v>
@@ -41308,18 +41795,31 @@
         <v>103</v>
       </c>
       <c r="N223" s="36"/>
-      <c r="O223" s="34"/>
+      <c r="O223" s="34">
+        <v>45</v>
+      </c>
       <c r="P223" s="12"/>
       <c r="Q223" s="34"/>
-      <c r="R223" s="10"/>
-      <c r="S223" s="12"/>
-      <c r="T223" s="12"/>
+      <c r="R223" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S223" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T223" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>22500</v>
+      </c>
       <c r="U223" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V223" s="12"/>
-      <c r="W223" s="12"/>
+        <v>1875</v>
+      </c>
+      <c r="V223" s="12">
+        <v>500</v>
+      </c>
+      <c r="W223" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="X223" s="12"/>
       <c r="Y223" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
@@ -41335,40 +41835,4264 @@
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
       </c>
-      <c r="AD223" s="12"/>
+      <c r="AD223" s="12" t="s">
+        <v>103</v>
+      </c>
       <c r="AE223" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="AF223" s="12"/>
-      <c r="AG223" s="12"/>
-      <c r="AH223" s="12"/>
-      <c r="AI223" s="12"/>
-      <c r="AJ223" s="10"/>
-      <c r="AK223" s="10"/>
-      <c r="AL223" s="10"/>
-      <c r="AM223" s="11"/>
-      <c r="AN223" s="11"/>
+      <c r="AG223" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH223" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI223" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ223" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK223" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="AL223" s="10" t="s">
+        <v>1701</v>
+      </c>
+      <c r="AM223" s="11" t="s">
+        <v>1702</v>
+      </c>
+      <c r="AN223" s="11" t="s">
+        <v>103</v>
+      </c>
       <c r="AO223" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="AP223" s="11"/>
-      <c r="AQ223" s="11"/>
-      <c r="AR223" s="11"/>
-      <c r="AS223" s="36"/>
-      <c r="AT223" s="11"/>
-      <c r="AU223" s="11"/>
-      <c r="AV223" s="13"/>
+      <c r="AP223" s="11" t="s">
+        <v>1695</v>
+      </c>
+      <c r="AQ223" s="11" t="s">
+        <v>1696</v>
+      </c>
+      <c r="AR223" s="11" t="s">
+        <v>1638</v>
+      </c>
+      <c r="AS223" s="36" t="s">
+        <v>1705</v>
+      </c>
+      <c r="AT223" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU223" s="11" t="s">
+        <v>1699</v>
+      </c>
+      <c r="AV223" s="13" t="s">
+        <v>1639</v>
+      </c>
       <c r="AW223" s="14"/>
-      <c r="AX223" s="44"/>
+      <c r="AX223" s="44">
+        <v>46071</v>
+      </c>
     </row>
-    <row r="231" spans="6:6">
-      <c r="F231" s="1" t="s">
+    <row r="224" spans="1:50" ht="25.5">
+      <c r="A224" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B224" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C224" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E224" s="26">
+        <v>94140</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G224" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>5 rue Victor Hugo
+94140 - Alfortville</v>
+      </c>
+      <c r="H224" s="15" t="s">
+        <v>1585</v>
+      </c>
+      <c r="I224" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J224" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K224" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L224" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M224" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N224" s="36"/>
+      <c r="O224" s="34">
+        <v>140</v>
+      </c>
+      <c r="P224" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q224" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R224" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S224" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T224" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>42000</v>
+      </c>
+      <c r="U224" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3500</v>
+      </c>
+      <c r="V224" s="12">
+        <v>300</v>
+      </c>
+      <c r="W224" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X224" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2623.6</v>
+      </c>
+      <c r="Y224" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>218.63333333333333</v>
+      </c>
+      <c r="Z224" s="12">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AA224" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB224" s="12"/>
+      <c r="AC224" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD224" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE224" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>44623.6</v>
+      </c>
+      <c r="AF224" s="12" t="str">
+        <f t="shared" ref="AF224:AF251" si="10">"3 mois = "&amp;TEXT(ROUND(3/12*T224,0),"### ### ##0 €")</f>
+        <v>3 mois = 10 500 €</v>
+      </c>
+      <c r="AG224" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH224" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI224" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ224" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK224" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL224" s="10"/>
+      <c r="AM224" s="11"/>
+      <c r="AN224" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO224" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP224" s="11"/>
+      <c r="AQ224" s="11"/>
+      <c r="AR224" s="11">
+        <v>69</v>
+      </c>
+      <c r="AS224" s="36"/>
+      <c r="AT224" s="11"/>
+      <c r="AU224" s="11" t="s">
+        <v>1641</v>
+      </c>
+      <c r="AV224" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW224" s="14"/>
+      <c r="AX224" s="44"/>
+    </row>
+    <row r="225" spans="1:50" ht="25.5">
+      <c r="A225" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B225" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C225" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D225" s="10" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E225" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G225" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Place du général Jean Raby
+69500 - Bron</v>
+      </c>
+      <c r="H225" s="15" t="s">
+        <v>1587</v>
+      </c>
+      <c r="I225" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J225" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K225" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L225" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M225" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N225" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="O225" s="34">
+        <v>228</v>
+      </c>
+      <c r="P225" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q225" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R225" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S225" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T225" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>45600</v>
+      </c>
+      <c r="U225" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3800</v>
+      </c>
+      <c r="V225" s="12">
+        <v>200</v>
+      </c>
+      <c r="W225" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X225" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3312.8399999999997</v>
+      </c>
+      <c r="Y225" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>276.07</v>
+      </c>
+      <c r="Z225" s="12">
+        <v>14.53</v>
+      </c>
+      <c r="AA225" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB225" s="12"/>
+      <c r="AC225" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD225" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE225" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>48912.84</v>
+      </c>
+      <c r="AF225" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 11 400 €</v>
+      </c>
+      <c r="AG225" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH225" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI225" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ225" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK225" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL225" s="10"/>
+      <c r="AM225" s="11"/>
+      <c r="AN225" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO225" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP225" s="11"/>
+      <c r="AQ225" s="11"/>
+      <c r="AR225" s="11" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AS225" s="36"/>
+      <c r="AT225" s="11"/>
+      <c r="AU225" s="11" t="s">
+        <v>1642</v>
+      </c>
+      <c r="AV225" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW225" s="14"/>
+      <c r="AX225" s="44"/>
+    </row>
+    <row r="226" spans="1:50" ht="25.5">
+      <c r="A226" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B226" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C226" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D226" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E226" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F226" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G226" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue du Colonel Arnaud Beltrame
+69500 - Bron</v>
+      </c>
+      <c r="H226" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I226" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J226" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K226" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L226" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M226" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N226" s="36" t="s">
+        <v>1187</v>
+      </c>
+      <c r="O226" s="34">
+        <v>363</v>
+      </c>
+      <c r="P226" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q226" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R226" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S226" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T226" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>54450</v>
+      </c>
+      <c r="U226" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4537.5</v>
+      </c>
+      <c r="V226" s="12">
+        <v>150</v>
+      </c>
+      <c r="W226" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X226" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1190.6399999999999</v>
+      </c>
+      <c r="Y226" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>99.219999999999985</v>
+      </c>
+      <c r="Z226" s="12">
+        <v>3.28</v>
+      </c>
+      <c r="AA226" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB226" s="12"/>
+      <c r="AC226" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD226" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE226" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>55640.639999999999</v>
+      </c>
+      <c r="AF226" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 13 613 €</v>
+      </c>
+      <c r="AG226" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH226" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI226" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ226" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK226" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL226" s="10"/>
+      <c r="AM226" s="11"/>
+      <c r="AN226" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO226" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP226" s="11"/>
+      <c r="AQ226" s="11"/>
+      <c r="AR226" s="11" t="s">
+        <v>1670</v>
+      </c>
+      <c r="AS226" s="36"/>
+      <c r="AT226" s="11"/>
+      <c r="AU226" s="11" t="s">
+        <v>1643</v>
+      </c>
+      <c r="AV226" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW226" s="14"/>
+      <c r="AX226" s="44"/>
+    </row>
+    <row r="227" spans="1:50" ht="25.5">
+      <c r="A227" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B227" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C227" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D227" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E227" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F227" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G227" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue du Colonel Arnaud Beltrame
+69500 - Bron</v>
+      </c>
+      <c r="H227" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I227" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J227" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K227" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L227" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M227" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N227" s="36" t="s">
+        <v>1599</v>
+      </c>
+      <c r="O227" s="34">
+        <v>110</v>
+      </c>
+      <c r="P227" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q227" s="34">
+        <v>222</v>
+      </c>
+      <c r="R227" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S227" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T227" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>27500</v>
+      </c>
+      <c r="U227" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2291.6666666666665</v>
+      </c>
+      <c r="V227" s="12">
+        <v>250</v>
+      </c>
+      <c r="W227" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X227" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>359.7</v>
+      </c>
+      <c r="Y227" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>29.974999999999998</v>
+      </c>
+      <c r="Z227" s="12">
+        <v>3.27</v>
+      </c>
+      <c r="AA227" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB227" s="12"/>
+      <c r="AC227" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD227" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE227" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>27859.7</v>
+      </c>
+      <c r="AF227" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 6 875 €</v>
+      </c>
+      <c r="AG227" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH227" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI227" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ227" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK227" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL227" s="10"/>
+      <c r="AM227" s="11"/>
+      <c r="AN227" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO227" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP227" s="11"/>
+      <c r="AQ227" s="11"/>
+      <c r="AR227" s="11" t="s">
+        <v>1671</v>
+      </c>
+      <c r="AS227" s="36"/>
+      <c r="AT227" s="11"/>
+      <c r="AU227" s="11" t="s">
+        <v>1644</v>
+      </c>
+      <c r="AV227" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW227" s="14"/>
+      <c r="AX227" s="44"/>
+    </row>
+    <row r="228" spans="1:50" ht="25.5">
+      <c r="A228" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B228" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C228" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D228" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E228" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F228" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G228" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue du Colonel Arnaud Beltrame
+69500 - Bron</v>
+      </c>
+      <c r="H228" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I228" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J228" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K228" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L228" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M228" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N228" s="36" t="s">
+        <v>1200</v>
+      </c>
+      <c r="O228" s="34">
+        <v>112</v>
+      </c>
+      <c r="P228" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q228" s="34">
+        <v>222</v>
+      </c>
+      <c r="R228" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S228" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T228" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>28000</v>
+      </c>
+      <c r="U228" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2333.3333333333335</v>
+      </c>
+      <c r="V228" s="12">
+        <v>250</v>
+      </c>
+      <c r="W228" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X228" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>243.04</v>
+      </c>
+      <c r="Y228" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>20.253333333333334</v>
+      </c>
+      <c r="Z228" s="12">
+        <v>2.17</v>
+      </c>
+      <c r="AA228" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB228" s="12"/>
+      <c r="AC228" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD228" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE228" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>28243.040000000001</v>
+      </c>
+      <c r="AF228" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 7 000 €</v>
+      </c>
+      <c r="AG228" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH228" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI228" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ228" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK228" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL228" s="10"/>
+      <c r="AM228" s="11"/>
+      <c r="AN228" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO228" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP228" s="11"/>
+      <c r="AQ228" s="11"/>
+      <c r="AR228" s="11" t="s">
+        <v>1672</v>
+      </c>
+      <c r="AS228" s="36"/>
+      <c r="AT228" s="11"/>
+      <c r="AU228" s="11" t="s">
+        <v>1645</v>
+      </c>
+      <c r="AV228" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW228" s="14"/>
+      <c r="AX228" s="44"/>
+    </row>
+    <row r="229" spans="1:50" ht="25.5">
+      <c r="A229" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B229" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C229" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D229" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E229" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F229" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G229" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue du Colonel Arnaud Beltrame
+69500 - Bron</v>
+      </c>
+      <c r="H229" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I229" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J229" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K229" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L229" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M229" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N229" s="36" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O229" s="34">
+        <v>86</v>
+      </c>
+      <c r="P229" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q229" s="34">
+        <v>179</v>
+      </c>
+      <c r="R229" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S229" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T229" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>38700</v>
+      </c>
+      <c r="U229" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3225</v>
+      </c>
+      <c r="V229" s="12">
+        <v>450</v>
+      </c>
+      <c r="W229" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X229" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>283.8</v>
+      </c>
+      <c r="Y229" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>23.650000000000002</v>
+      </c>
+      <c r="Z229" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="AA229" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB229" s="12"/>
+      <c r="AC229" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD229" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE229" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>38983.800000000003</v>
+      </c>
+      <c r="AF229" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 9 675 €</v>
+      </c>
+      <c r="AG229" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH229" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI229" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ229" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK229" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL229" s="10"/>
+      <c r="AM229" s="11"/>
+      <c r="AN229" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO229" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP229" s="11"/>
+      <c r="AQ229" s="11"/>
+      <c r="AR229" s="11" t="s">
+        <v>1673</v>
+      </c>
+      <c r="AS229" s="36"/>
+      <c r="AT229" s="11"/>
+      <c r="AU229" s="11" t="s">
+        <v>1646</v>
+      </c>
+      <c r="AV229" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW229" s="14"/>
+      <c r="AX229" s="44"/>
+    </row>
+    <row r="230" spans="1:50" ht="25.5">
+      <c r="A230" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B230" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C230" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D230" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E230" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F230" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G230" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue du Colonel Arnaud Beltrame
+69500 - Bron</v>
+      </c>
+      <c r="H230" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I230" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J230" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K230" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L230" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M230" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N230" s="36" t="s">
+        <v>1601</v>
+      </c>
+      <c r="O230" s="34">
+        <v>91</v>
+      </c>
+      <c r="P230" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q230" s="34">
+        <v>179</v>
+      </c>
+      <c r="R230" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S230" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T230" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>36400</v>
+      </c>
+      <c r="U230" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3033.3333333333335</v>
+      </c>
+      <c r="V230" s="12">
+        <v>400</v>
+      </c>
+      <c r="W230" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X230" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>322.14</v>
+      </c>
+      <c r="Y230" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>26.844999999999999</v>
+      </c>
+      <c r="Z230" s="12">
+        <v>3.54</v>
+      </c>
+      <c r="AA230" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB230" s="12"/>
+      <c r="AC230" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD230" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE230" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>36722.14</v>
+      </c>
+      <c r="AF230" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 9 100 €</v>
+      </c>
+      <c r="AG230" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH230" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI230" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ230" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK230" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL230" s="10"/>
+      <c r="AM230" s="11"/>
+      <c r="AN230" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO230" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP230" s="11"/>
+      <c r="AQ230" s="11"/>
+      <c r="AR230" s="11" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AS230" s="36"/>
+      <c r="AT230" s="11"/>
+      <c r="AU230" s="11" t="s">
+        <v>1647</v>
+      </c>
+      <c r="AV230" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW230" s="14"/>
+      <c r="AX230" s="44"/>
+    </row>
+    <row r="231" spans="1:50" ht="25.5">
+      <c r="A231" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B231" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C231" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D231" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E231" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F231" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G231" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue du Colonel Arnaud Beltrame
+69500 - Bron</v>
+      </c>
+      <c r="H231" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I231" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J231" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K231" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L231" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M231" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N231" s="36" t="s">
+        <v>1602</v>
+      </c>
+      <c r="O231" s="34">
+        <v>167</v>
+      </c>
+      <c r="P231" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q231" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R231" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S231" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T231" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>33400</v>
+      </c>
+      <c r="U231" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2783.3333333333335</v>
+      </c>
+      <c r="V231" s="12">
+        <v>200</v>
+      </c>
+      <c r="W231" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X231" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>646.29</v>
+      </c>
+      <c r="Y231" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>53.857499999999995</v>
+      </c>
+      <c r="Z231" s="12">
+        <v>3.87</v>
+      </c>
+      <c r="AA231" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB231" s="12"/>
+      <c r="AC231" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD231" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE231" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>34046.29</v>
+      </c>
+      <c r="AF231" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 8 350 €</v>
+      </c>
+      <c r="AG231" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH231" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI231" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ231" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK231" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL231" s="10"/>
+      <c r="AM231" s="11"/>
+      <c r="AN231" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO231" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP231" s="11"/>
+      <c r="AQ231" s="11"/>
+      <c r="AR231" s="11" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AS231" s="36"/>
+      <c r="AT231" s="11"/>
+      <c r="AU231" s="11" t="s">
+        <v>1648</v>
+      </c>
+      <c r="AV231" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW231" s="14"/>
+      <c r="AX231" s="44"/>
+    </row>
+    <row r="232" spans="1:50" ht="25.5">
+      <c r="A232" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B232" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C232" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D232" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E232" s="26">
+        <v>69500</v>
+      </c>
+      <c r="F232" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G232" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue du Colonel Arnaud Beltrame
+69500 - Bron</v>
+      </c>
+      <c r="H232" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I232" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J232" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K232" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L232" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M232" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N232" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="O232" s="34">
+        <v>123</v>
+      </c>
+      <c r="P232" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q232" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R232" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S232" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T232" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>24600</v>
+      </c>
+      <c r="U232" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2050</v>
+      </c>
+      <c r="V232" s="12">
+        <v>200</v>
+      </c>
+      <c r="W232" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X232" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>476.01</v>
+      </c>
+      <c r="Y232" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>39.667499999999997</v>
+      </c>
+      <c r="Z232" s="12">
+        <v>3.87</v>
+      </c>
+      <c r="AA232" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB232" s="12"/>
+      <c r="AC232" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD232" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE232" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>25076.01</v>
+      </c>
+      <c r="AF232" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 6 150 €</v>
+      </c>
+      <c r="AG232" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH232" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI232" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ232" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK232" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL232" s="10"/>
+      <c r="AM232" s="11"/>
+      <c r="AN232" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO232" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP232" s="11"/>
+      <c r="AQ232" s="11"/>
+      <c r="AR232" s="11" t="s">
+        <v>1676</v>
+      </c>
+      <c r="AS232" s="36"/>
+      <c r="AT232" s="11"/>
+      <c r="AU232" s="11" t="s">
+        <v>1649</v>
+      </c>
+      <c r="AV232" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW232" s="14"/>
+      <c r="AX232" s="44"/>
+    </row>
+    <row r="233" spans="1:50" ht="25.5">
+      <c r="A233" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B233" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Hauts-de-Seine</v>
+      </c>
+      <c r="C233" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>92</v>
+      </c>
+      <c r="D233" s="10" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E233" s="26">
+        <v>92700</v>
+      </c>
+      <c r="F233" s="10" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G233" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>32 boulevard de Finlande
+92700 - Colombes</v>
+      </c>
+      <c r="H233" s="15" t="s">
+        <v>1617</v>
+      </c>
+      <c r="I233" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J233" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K233" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L233" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M233" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N233" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="O233" s="34">
+        <v>200</v>
+      </c>
+      <c r="P233" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q233" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R233" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S233" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T233" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>30000</v>
+      </c>
+      <c r="U233" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2500</v>
+      </c>
+      <c r="V233" s="12">
+        <v>150</v>
+      </c>
+      <c r="W233" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X233" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y233" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z233" s="12"/>
+      <c r="AA233" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB233" s="12"/>
+      <c r="AC233" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD233" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE233" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>30000</v>
+      </c>
+      <c r="AF233" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 7 500 €</v>
+      </c>
+      <c r="AG233" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH233" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI233" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ233" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK233" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL233" s="10"/>
+      <c r="AM233" s="11"/>
+      <c r="AN233" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO233" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP233" s="11"/>
+      <c r="AQ233" s="11"/>
+      <c r="AR233" s="11">
+        <v>71</v>
+      </c>
+      <c r="AS233" s="36"/>
+      <c r="AT233" s="11"/>
+      <c r="AU233" s="11" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AV233" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW233" s="14"/>
+      <c r="AX233" s="44"/>
+    </row>
+    <row r="234" spans="1:50" ht="25.5">
+      <c r="A234" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Centre-Val de Loire</v>
+      </c>
+      <c r="B234" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Indre-et-Loire</v>
+      </c>
+      <c r="C234" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>37</v>
+      </c>
+      <c r="D234" s="10" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E234" s="26">
+        <v>37300</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G234" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue de la rotière
+37300 - Joué les Tours</v>
+      </c>
+      <c r="H234" s="15" t="s">
+        <v>1619</v>
+      </c>
+      <c r="I234" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J234" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K234" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L234" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M234" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N234" s="36"/>
+      <c r="O234" s="34">
+        <v>54</v>
+      </c>
+      <c r="P234" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q234" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R234" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S234" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T234" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>10800</v>
+      </c>
+      <c r="U234" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>900</v>
+      </c>
+      <c r="V234" s="12">
+        <v>200</v>
+      </c>
+      <c r="W234" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X234" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>99.36</v>
+      </c>
+      <c r="Y234" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="Z234" s="12">
+        <v>1.84</v>
+      </c>
+      <c r="AA234" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB234" s="12"/>
+      <c r="AC234" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD234" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE234" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>10899.36</v>
+      </c>
+      <c r="AF234" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 2 700 €</v>
+      </c>
+      <c r="AG234" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH234" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI234" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ234" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK234" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL234" s="10"/>
+      <c r="AM234" s="11"/>
+      <c r="AN234" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO234" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP234" s="11"/>
+      <c r="AQ234" s="11"/>
+      <c r="AR234" s="11">
+        <v>72</v>
+      </c>
+      <c r="AS234" s="36"/>
+      <c r="AT234" s="11"/>
+      <c r="AU234" s="11" t="s">
+        <v>1651</v>
+      </c>
+      <c r="AV234" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW234" s="14"/>
+      <c r="AX234" s="44"/>
+    </row>
+    <row r="235" spans="1:50" ht="25.5">
+      <c r="A235" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B235" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Nord</v>
+      </c>
+      <c r="C235" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>59</v>
+      </c>
+      <c r="D235" s="10" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E235" s="26">
+        <v>59800</v>
+      </c>
+      <c r="F235" s="10" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G235" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>boulevard de l'usine
+59800 - Lille Fives</v>
+      </c>
+      <c r="H235" s="15"/>
+      <c r="I235" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J235" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K235" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L235" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M235" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N235" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="O235" s="34">
+        <v>150</v>
+      </c>
+      <c r="P235" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q235" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R235" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S235" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T235" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>30000</v>
+      </c>
+      <c r="U235" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2500</v>
+      </c>
+      <c r="V235" s="12">
+        <v>200</v>
+      </c>
+      <c r="W235" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X235" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>877.5</v>
+      </c>
+      <c r="Y235" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>73.125</v>
+      </c>
+      <c r="Z235" s="12">
+        <v>5.85</v>
+      </c>
+      <c r="AA235" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB235" s="12"/>
+      <c r="AC235" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD235" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE235" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>30877.5</v>
+      </c>
+      <c r="AF235" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 7 500 €</v>
+      </c>
+      <c r="AG235" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH235" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI235" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ235" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK235" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL235" s="10"/>
+      <c r="AM235" s="11"/>
+      <c r="AN235" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO235" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP235" s="11"/>
+      <c r="AQ235" s="11"/>
+      <c r="AR235" s="11">
+        <v>73</v>
+      </c>
+      <c r="AS235" s="36"/>
+      <c r="AT235" s="11"/>
+      <c r="AU235" s="11" t="s">
+        <v>1652</v>
+      </c>
+      <c r="AV235" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW235" s="14"/>
+      <c r="AX235" s="44"/>
+    </row>
+    <row r="236" spans="1:50" ht="25.5">
+      <c r="A236" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B236" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Nord</v>
+      </c>
+      <c r="C236" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>59</v>
+      </c>
+      <c r="D236" s="10" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E236" s="26">
+        <v>59800</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G236" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>178 rue Faidherbes
+59800 - Lille Hellemmes</v>
+      </c>
+      <c r="H236" s="15" t="s">
+        <v>1621</v>
+      </c>
+      <c r="I236" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J236" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K236" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L236" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M236" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N236" s="36" t="s">
+        <v>1603</v>
+      </c>
+      <c r="O236" s="34">
+        <v>52</v>
+      </c>
+      <c r="P236" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q236" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R236" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S236" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T236" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>13000</v>
+      </c>
+      <c r="U236" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1083.3333333333333</v>
+      </c>
+      <c r="V236" s="12">
+        <v>250</v>
+      </c>
+      <c r="W236" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X236" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2766.92</v>
+      </c>
+      <c r="Y236" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>230.57666666666668</v>
+      </c>
+      <c r="Z236" s="12">
+        <v>53.21</v>
+      </c>
+      <c r="AA236" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB236" s="12"/>
+      <c r="AC236" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD236" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE236" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>15766.92</v>
+      </c>
+      <c r="AF236" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 3 250 €</v>
+      </c>
+      <c r="AG236" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH236" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI236" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ236" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK236" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL236" s="10"/>
+      <c r="AM236" s="11"/>
+      <c r="AN236" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO236" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP236" s="11"/>
+      <c r="AQ236" s="11"/>
+      <c r="AR236" s="11" t="s">
+        <v>1677</v>
+      </c>
+      <c r="AS236" s="36"/>
+      <c r="AT236" s="11"/>
+      <c r="AU236" s="11" t="s">
+        <v>1653</v>
+      </c>
+      <c r="AV236" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW236" s="14"/>
+      <c r="AX236" s="44"/>
+    </row>
+    <row r="237" spans="1:50" ht="25.5">
+      <c r="A237" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B237" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Nord</v>
+      </c>
+      <c r="C237" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>59</v>
+      </c>
+      <c r="D237" s="10" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E237" s="26">
+        <v>59800</v>
+      </c>
+      <c r="F237" s="10" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G237" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>178 rue Faidherbes
+59800 - Lille Hellemmes</v>
+      </c>
+      <c r="H237" s="15" t="s">
+        <v>1621</v>
+      </c>
+      <c r="I237" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J237" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K237" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L237" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M237" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N237" s="36" t="s">
+        <v>1604</v>
+      </c>
+      <c r="O237" s="34">
+        <v>38</v>
+      </c>
+      <c r="P237" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q237" s="34">
+        <v>211</v>
+      </c>
+      <c r="R237" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S237" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T237" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>9500</v>
+      </c>
+      <c r="U237" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>791.66666666666663</v>
+      </c>
+      <c r="V237" s="12">
+        <v>250</v>
+      </c>
+      <c r="W237" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X237" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>717.82</v>
+      </c>
+      <c r="Y237" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>59.818333333333335</v>
+      </c>
+      <c r="Z237" s="12">
+        <v>18.89</v>
+      </c>
+      <c r="AA237" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB237" s="12"/>
+      <c r="AC237" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD237" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE237" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>10217.82</v>
+      </c>
+      <c r="AF237" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 2 375 €</v>
+      </c>
+      <c r="AG237" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH237" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI237" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ237" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK237" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL237" s="10"/>
+      <c r="AM237" s="11"/>
+      <c r="AN237" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO237" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP237" s="11"/>
+      <c r="AQ237" s="11"/>
+      <c r="AR237" s="11" t="s">
+        <v>1678</v>
+      </c>
+      <c r="AS237" s="36"/>
+      <c r="AT237" s="11"/>
+      <c r="AU237" s="11" t="s">
+        <v>1654</v>
+      </c>
+      <c r="AV237" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW237" s="14"/>
+      <c r="AX237" s="44"/>
+    </row>
+    <row r="238" spans="1:50" ht="25.5">
+      <c r="A238" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Hauts-de-France</v>
+      </c>
+      <c r="B238" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Nord</v>
+      </c>
+      <c r="C238" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>59</v>
+      </c>
+      <c r="D238" s="10" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E238" s="26">
+        <v>59800</v>
+      </c>
+      <c r="F238" s="10" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G238" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>178 rue Faidherbes
+59800 - Lille Hellemmes</v>
+      </c>
+      <c r="H238" s="15" t="s">
+        <v>1621</v>
+      </c>
+      <c r="I238" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J238" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K238" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L238" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M238" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N238" s="36" t="s">
+        <v>1605</v>
+      </c>
+      <c r="O238" s="34">
+        <v>173</v>
+      </c>
+      <c r="P238" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q238" s="34">
+        <v>211</v>
+      </c>
+      <c r="R238" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S238" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T238" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>34600</v>
+      </c>
+      <c r="U238" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2883.3333333333335</v>
+      </c>
+      <c r="V238" s="12">
+        <v>200</v>
+      </c>
+      <c r="W238" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X238" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>560.52</v>
+      </c>
+      <c r="Y238" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>46.71</v>
+      </c>
+      <c r="Z238" s="12">
+        <v>3.24</v>
+      </c>
+      <c r="AA238" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB238" s="12"/>
+      <c r="AC238" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD238" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE238" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>35160.519999999997</v>
+      </c>
+      <c r="AF238" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 8 650 €</v>
+      </c>
+      <c r="AG238" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH238" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI238" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ238" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK238" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL238" s="10"/>
+      <c r="AM238" s="11"/>
+      <c r="AN238" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO238" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP238" s="11"/>
+      <c r="AQ238" s="11"/>
+      <c r="AR238" s="11" t="s">
+        <v>1679</v>
+      </c>
+      <c r="AS238" s="36"/>
+      <c r="AT238" s="11"/>
+      <c r="AU238" s="11" t="s">
+        <v>1655</v>
+      </c>
+      <c r="AV238" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW238" s="14"/>
+      <c r="AX238" s="44"/>
+    </row>
+    <row r="239" spans="1:50" ht="25.5">
+      <c r="A239" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B239" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Seine-Saint-Denis</v>
+      </c>
+      <c r="C239" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>93</v>
+      </c>
+      <c r="D239" s="10" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E239" s="26">
+        <v>93100</v>
+      </c>
+      <c r="F239" s="10" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G239" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>297 rue de Rosny
+93100 - Montreuil</v>
+      </c>
+      <c r="H239" s="15" t="s">
+        <v>1625</v>
+      </c>
+      <c r="I239" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J239" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K239" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L239" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M239" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N239" s="36" t="s">
+        <v>1606</v>
+      </c>
+      <c r="O239" s="34">
+        <v>320</v>
+      </c>
+      <c r="P239" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q239" s="34">
+        <v>600</v>
+      </c>
+      <c r="R239" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S239" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T239" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>64000</v>
+      </c>
+      <c r="U239" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5333.333333333333</v>
+      </c>
+      <c r="V239" s="12">
+        <v>200</v>
+      </c>
+      <c r="W239" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X239" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y239" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z239" s="12"/>
+      <c r="AA239" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB239" s="12"/>
+      <c r="AC239" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD239" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE239" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>64000</v>
+      </c>
+      <c r="AF239" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 16 000 €</v>
+      </c>
+      <c r="AG239" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH239" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI239" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ239" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK239" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL239" s="10"/>
+      <c r="AM239" s="11"/>
+      <c r="AN239" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO239" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP239" s="11"/>
+      <c r="AQ239" s="11"/>
+      <c r="AR239" s="11" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AS239" s="36"/>
+      <c r="AT239" s="11"/>
+      <c r="AU239" s="11" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AV239" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW239" s="14"/>
+      <c r="AX239" s="44"/>
+    </row>
+    <row r="240" spans="1:50" ht="25.5">
+      <c r="A240" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B240" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Seine-Saint-Denis</v>
+      </c>
+      <c r="C240" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>93</v>
+      </c>
+      <c r="D240" s="10" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E240" s="26">
+        <v>93100</v>
+      </c>
+      <c r="F240" s="10" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G240" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>299 rue de Rosny
+93100 - Montreuil</v>
+      </c>
+      <c r="H240" s="15" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I240" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J240" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K240" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L240" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M240" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N240" s="36" t="s">
+        <v>1607</v>
+      </c>
+      <c r="O240" s="34">
+        <v>280</v>
+      </c>
+      <c r="P240" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q240" s="34">
+        <v>600</v>
+      </c>
+      <c r="R240" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S240" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T240" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>56000</v>
+      </c>
+      <c r="U240" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4666.666666666667</v>
+      </c>
+      <c r="V240" s="12">
+        <v>200</v>
+      </c>
+      <c r="W240" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X240" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y240" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z240" s="12"/>
+      <c r="AA240" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB240" s="12"/>
+      <c r="AC240" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD240" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE240" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>56000</v>
+      </c>
+      <c r="AF240" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 14 000 €</v>
+      </c>
+      <c r="AG240" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH240" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI240" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ240" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK240" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL240" s="10"/>
+      <c r="AM240" s="11"/>
+      <c r="AN240" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO240" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP240" s="11"/>
+      <c r="AQ240" s="11"/>
+      <c r="AR240" s="11" t="s">
+        <v>1681</v>
+      </c>
+      <c r="AS240" s="36"/>
+      <c r="AT240" s="11"/>
+      <c r="AU240" s="11" t="s">
+        <v>1657</v>
+      </c>
+      <c r="AV240" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW240" s="14"/>
+      <c r="AX240" s="44"/>
+    </row>
+    <row r="241" spans="1:50" ht="25.5">
+      <c r="A241" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B241" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Yvelines</v>
+      </c>
+      <c r="C241" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>78</v>
+      </c>
+      <c r="D241" s="10" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E241" s="26">
+        <v>78300</v>
+      </c>
+      <c r="F241" s="10" t="s">
+        <v>1595</v>
+      </c>
+      <c r="G241" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>30 rue Maurice Clerc
+78300 - Poissy</v>
+      </c>
+      <c r="H241" s="15" t="s">
+        <v>1628</v>
+      </c>
+      <c r="I241" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J241" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K241" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L241" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M241" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N241" s="36" t="s">
+        <v>1608</v>
+      </c>
+      <c r="O241" s="34">
+        <v>123</v>
+      </c>
+      <c r="P241" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q241" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R241" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S241" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T241" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>30750</v>
+      </c>
+      <c r="U241" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2562.5</v>
+      </c>
+      <c r="V241" s="12">
+        <v>250</v>
+      </c>
+      <c r="W241" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X241" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1138.98</v>
+      </c>
+      <c r="Y241" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>94.915000000000006</v>
+      </c>
+      <c r="Z241" s="12">
+        <v>9.26</v>
+      </c>
+      <c r="AA241" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB241" s="12"/>
+      <c r="AC241" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD241" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE241" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>31888.98</v>
+      </c>
+      <c r="AF241" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 7 688 €</v>
+      </c>
+      <c r="AG241" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH241" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI241" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ241" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK241" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL241" s="10"/>
+      <c r="AM241" s="11"/>
+      <c r="AN241" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO241" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP241" s="11"/>
+      <c r="AQ241" s="11"/>
+      <c r="AR241" s="11" t="s">
+        <v>1682</v>
+      </c>
+      <c r="AS241" s="36"/>
+      <c r="AT241" s="11"/>
+      <c r="AU241" s="11" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AV241" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW241" s="14"/>
+      <c r="AX241" s="44"/>
+    </row>
+    <row r="242" spans="1:50" ht="25.5">
+      <c r="A242" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B242" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Yvelines</v>
+      </c>
+      <c r="C242" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>78</v>
+      </c>
+      <c r="D242" s="10" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E242" s="26">
+        <v>78300</v>
+      </c>
+      <c r="F242" s="10" t="s">
+        <v>1595</v>
+      </c>
+      <c r="G242" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>30 rue Maurice Clerc
+78300 - Poissy</v>
+      </c>
+      <c r="H242" s="15" t="s">
+        <v>1628</v>
+      </c>
+      <c r="I242" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J242" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K242" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L242" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M242" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N242" s="36" t="s">
+        <v>1609</v>
+      </c>
+      <c r="O242" s="34">
+        <v>111</v>
+      </c>
+      <c r="P242" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q242" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R242" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S242" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T242" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>27750</v>
+      </c>
+      <c r="U242" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2312.5</v>
+      </c>
+      <c r="V242" s="12">
+        <v>250</v>
+      </c>
+      <c r="W242" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X242" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1279.83</v>
+      </c>
+      <c r="Y242" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>106.65249999999999</v>
+      </c>
+      <c r="Z242" s="12">
+        <v>11.53</v>
+      </c>
+      <c r="AA242" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB242" s="12"/>
+      <c r="AC242" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD242" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE242" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>29029.83</v>
+      </c>
+      <c r="AF242" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 6 938 €</v>
+      </c>
+      <c r="AG242" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH242" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI242" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ242" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK242" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL242" s="10"/>
+      <c r="AM242" s="11"/>
+      <c r="AN242" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO242" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP242" s="11"/>
+      <c r="AQ242" s="11"/>
+      <c r="AR242" s="11" t="s">
+        <v>1683</v>
+      </c>
+      <c r="AS242" s="36"/>
+      <c r="AT242" s="11"/>
+      <c r="AU242" s="11" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AV242" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW242" s="14"/>
+      <c r="AX242" s="44"/>
+    </row>
+    <row r="243" spans="1:50" ht="25.5">
+      <c r="A243" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B243" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Seine-Saint-Denis</v>
+      </c>
+      <c r="C243" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>93</v>
+      </c>
+      <c r="D243" s="10" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E243" s="26">
+        <v>93400</v>
+      </c>
+      <c r="F243" s="10" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G243" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>12 bis rue des Bateliers
+93400 - Saint-Ouen</v>
+      </c>
+      <c r="H243" s="15" t="s">
+        <v>1630</v>
+      </c>
+      <c r="I243" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J243" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K243" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L243" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M243" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N243" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="O243" s="34">
+        <v>129</v>
+      </c>
+      <c r="P243" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q243" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R243" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S243" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T243" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>45150</v>
+      </c>
+      <c r="U243" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3762.5</v>
+      </c>
+      <c r="V243" s="12">
+        <v>350</v>
+      </c>
+      <c r="W243" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X243" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y243" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z243" s="12"/>
+      <c r="AA243" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB243" s="12"/>
+      <c r="AC243" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD243" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE243" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>45150</v>
+      </c>
+      <c r="AF243" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 11 288 €</v>
+      </c>
+      <c r="AG243" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH243" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI243" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ243" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK243" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL243" s="10"/>
+      <c r="AM243" s="11"/>
+      <c r="AN243" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO243" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP243" s="11"/>
+      <c r="AQ243" s="11"/>
+      <c r="AR243" s="11">
+        <v>77</v>
+      </c>
+      <c r="AS243" s="36"/>
+      <c r="AT243" s="11"/>
+      <c r="AU243" s="11" t="s">
+        <v>1660</v>
+      </c>
+      <c r="AV243" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW243" s="14"/>
+      <c r="AX243" s="44"/>
+    </row>
+    <row r="244" spans="1:50" ht="25.5">
+      <c r="A244" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B244" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C244" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D244" s="10" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E244" s="26">
+        <v>94510</v>
+      </c>
+      <c r="F244" s="10" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G244" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue Dunoyer de Segonzac
+94510 - La Queue en Brie</v>
+      </c>
+      <c r="H244" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I244" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J244" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K244" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L244" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M244" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N244" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="O244" s="34">
+        <v>53</v>
+      </c>
+      <c r="P244" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q244" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R244" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S244" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T244" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>15900</v>
+      </c>
+      <c r="U244" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1325</v>
+      </c>
+      <c r="V244" s="12">
+        <v>300</v>
+      </c>
+      <c r="W244" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X244" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y244" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z244" s="12"/>
+      <c r="AA244" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB244" s="12"/>
+      <c r="AC244" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD244" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE244" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>15900</v>
+      </c>
+      <c r="AF244" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 3 975 €</v>
+      </c>
+      <c r="AG244" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH244" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI244" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ244" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK244" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL244" s="10"/>
+      <c r="AM244" s="11"/>
+      <c r="AN244" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO244" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP244" s="11"/>
+      <c r="AQ244" s="11"/>
+      <c r="AR244" s="11" t="s">
+        <v>1684</v>
+      </c>
+      <c r="AS244" s="36"/>
+      <c r="AT244" s="11"/>
+      <c r="AU244" s="11" t="s">
+        <v>1661</v>
+      </c>
+      <c r="AV244" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW244" s="14"/>
+      <c r="AX244" s="44"/>
+    </row>
+    <row r="245" spans="1:50" ht="25.5">
+      <c r="A245" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B245" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C245" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D245" s="10" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E245" s="26">
+        <v>94511</v>
+      </c>
+      <c r="F245" s="10" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G245" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue Dunoyer de Segonzac
+94511 - La Queue en Brie</v>
+      </c>
+      <c r="H245" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I245" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J245" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K245" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L245" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M245" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N245" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="O245" s="34">
+        <v>152</v>
+      </c>
+      <c r="P245" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q245" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R245" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S245" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T245" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>38000</v>
+      </c>
+      <c r="U245" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3166.6666666666665</v>
+      </c>
+      <c r="V245" s="12">
+        <v>250</v>
+      </c>
+      <c r="W245" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X245" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y245" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z245" s="12"/>
+      <c r="AA245" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB245" s="12"/>
+      <c r="AC245" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD245" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE245" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>38000</v>
+      </c>
+      <c r="AF245" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 9 500 €</v>
+      </c>
+      <c r="AG245" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH245" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI245" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ245" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK245" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL245" s="10"/>
+      <c r="AM245" s="11"/>
+      <c r="AN245" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO245" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP245" s="11"/>
+      <c r="AQ245" s="11"/>
+      <c r="AR245" s="11" t="s">
+        <v>1637</v>
+      </c>
+      <c r="AS245" s="36"/>
+      <c r="AT245" s="11"/>
+      <c r="AU245" s="11" t="s">
+        <v>1662</v>
+      </c>
+      <c r="AV245" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW245" s="14"/>
+      <c r="AX245" s="44"/>
+    </row>
+    <row r="246" spans="1:50" ht="25.5">
+      <c r="A246" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B246" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C246" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E246" s="26">
+        <v>94512</v>
+      </c>
+      <c r="F246" s="10" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G246" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue Dunoyer de Segonzac
+94512 - La Queue en Brie</v>
+      </c>
+      <c r="H246" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I246" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J246" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K246" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L246" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M246" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N246" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="O246" s="34">
+        <v>95</v>
+      </c>
+      <c r="P246" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q246" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R246" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S246" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T246" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>23750</v>
+      </c>
+      <c r="U246" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1979.1666666666667</v>
+      </c>
+      <c r="V246" s="12">
+        <v>250</v>
+      </c>
+      <c r="W246" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X246" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y246" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z246" s="12"/>
+      <c r="AA246" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB246" s="12"/>
+      <c r="AC246" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD246" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE246" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>23750</v>
+      </c>
+      <c r="AF246" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 5 938 €</v>
+      </c>
+      <c r="AG246" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH246" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI246" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ246" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK246" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL246" s="10"/>
+      <c r="AM246" s="11"/>
+      <c r="AN246" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO246" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP246" s="11"/>
+      <c r="AQ246" s="11"/>
+      <c r="AR246" s="11" t="s">
+        <v>1685</v>
+      </c>
+      <c r="AS246" s="36"/>
+      <c r="AT246" s="11"/>
+      <c r="AU246" s="11" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AV246" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW246" s="14"/>
+      <c r="AX246" s="44"/>
+    </row>
+    <row r="247" spans="1:50" ht="25.5">
+      <c r="A247" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B247" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-de-Marne</v>
+      </c>
+      <c r="C247" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>94</v>
+      </c>
+      <c r="D247" s="10" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E247" s="26">
+        <v>94513</v>
+      </c>
+      <c r="F247" s="10" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G247" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>rue Dunoyer de Segonzac
+94513 - La Queue en Brie</v>
+      </c>
+      <c r="H247" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I247" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J247" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K247" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L247" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M247" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N247" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="O247" s="34">
+        <v>38</v>
+      </c>
+      <c r="P247" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q247" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R247" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S247" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T247" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11400</v>
+      </c>
+      <c r="U247" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>950</v>
+      </c>
+      <c r="V247" s="12">
+        <v>300</v>
+      </c>
+      <c r="W247" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X247" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y247" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z247" s="12"/>
+      <c r="AA247" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB247" s="12"/>
+      <c r="AC247" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD247" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE247" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>11400</v>
+      </c>
+      <c r="AF247" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 2 850 €</v>
+      </c>
+      <c r="AG247" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH247" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI247" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ247" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK247" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL247" s="10"/>
+      <c r="AM247" s="11"/>
+      <c r="AN247" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO247" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP247" s="11"/>
+      <c r="AQ247" s="11"/>
+      <c r="AR247" s="11" t="s">
+        <v>1686</v>
+      </c>
+      <c r="AS247" s="36"/>
+      <c r="AT247" s="11"/>
+      <c r="AU247" s="11" t="s">
+        <v>1664</v>
+      </c>
+      <c r="AV247" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW247" s="14"/>
+      <c r="AX247" s="44"/>
+    </row>
+    <row r="248" spans="1:50" ht="25.5">
+      <c r="A248" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B248" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C248" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E248" s="26">
+        <v>69002</v>
+      </c>
+      <c r="F248" s="10" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G248" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Allée Louis Thomas Achille
+69002 - Lyon Confluence</v>
+      </c>
+      <c r="H248" s="15" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I248" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J248" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K248" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L248" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M248" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N248" s="36" t="s">
+        <v>1610</v>
+      </c>
+      <c r="O248" s="34">
+        <v>248</v>
+      </c>
+      <c r="P248" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q248" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R248" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S248" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T248" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>62000</v>
+      </c>
+      <c r="U248" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>5166.666666666667</v>
+      </c>
+      <c r="V248" s="12">
+        <v>250</v>
+      </c>
+      <c r="W248" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X248" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y248" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z248" s="12"/>
+      <c r="AA248" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB248" s="12"/>
+      <c r="AC248" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD248" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE248" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>62000</v>
+      </c>
+      <c r="AF248" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 15 500 €</v>
+      </c>
+      <c r="AG248" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH248" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI248" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ248" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK248" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL248" s="10"/>
+      <c r="AM248" s="11"/>
+      <c r="AN248" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO248" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP248" s="11"/>
+      <c r="AQ248" s="11"/>
+      <c r="AR248" s="11" t="s">
+        <v>1687</v>
+      </c>
+      <c r="AS248" s="36"/>
+      <c r="AT248" s="11"/>
+      <c r="AU248" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="AV248" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW248" s="14"/>
+      <c r="AX248" s="44"/>
+    </row>
+    <row r="249" spans="1:50" ht="25.5">
+      <c r="A249" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B249" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C249" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E249" s="26">
+        <v>69002</v>
+      </c>
+      <c r="F249" s="10" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G249" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Allée Louis Thomas Achille
+69002 - Lyon Confluence</v>
+      </c>
+      <c r="H249" s="15" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I249" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J249" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K249" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L249" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M249" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N249" s="36" t="s">
+        <v>1611</v>
+      </c>
+      <c r="O249" s="34">
+        <v>264</v>
+      </c>
+      <c r="P249" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q249" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R249" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S249" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T249" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>52800</v>
+      </c>
+      <c r="U249" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4400</v>
+      </c>
+      <c r="V249" s="12">
+        <v>200</v>
+      </c>
+      <c r="W249" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X249" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y249" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z249" s="12"/>
+      <c r="AA249" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB249" s="12"/>
+      <c r="AC249" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD249" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE249" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>52800</v>
+      </c>
+      <c r="AF249" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 13 200 €</v>
+      </c>
+      <c r="AG249" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH249" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI249" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ249" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK249" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL249" s="10"/>
+      <c r="AM249" s="11"/>
+      <c r="AN249" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO249" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP249" s="11"/>
+      <c r="AQ249" s="11"/>
+      <c r="AR249" s="11" t="s">
+        <v>1688</v>
+      </c>
+      <c r="AS249" s="36"/>
+      <c r="AT249" s="11"/>
+      <c r="AU249" s="11" t="s">
+        <v>1666</v>
+      </c>
+      <c r="AV249" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW249" s="14"/>
+      <c r="AX249" s="44"/>
+    </row>
+    <row r="250" spans="1:50" ht="25.5">
+      <c r="A250" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B250" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C250" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D250" s="10" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E250" s="26">
+        <v>69002</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G250" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Allée Louis Thomas Achille
+69002 - Lyon Confluence</v>
+      </c>
+      <c r="H250" s="15" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I250" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J250" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K250" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L250" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M250" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N250" s="36" t="s">
+        <v>1612</v>
+      </c>
+      <c r="O250" s="34">
+        <v>174</v>
+      </c>
+      <c r="P250" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q250" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R250" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S250" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T250" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>43500</v>
+      </c>
+      <c r="U250" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3625</v>
+      </c>
+      <c r="V250" s="12">
+        <v>250</v>
+      </c>
+      <c r="W250" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X250" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y250" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z250" s="12"/>
+      <c r="AA250" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB250" s="12"/>
+      <c r="AC250" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD250" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE250" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>43500</v>
+      </c>
+      <c r="AF250" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 10 875 €</v>
+      </c>
+      <c r="AG250" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH250" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI250" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ250" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK250" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL250" s="10"/>
+      <c r="AM250" s="11"/>
+      <c r="AN250" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO250" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP250" s="11"/>
+      <c r="AQ250" s="11"/>
+      <c r="AR250" s="11" t="s">
+        <v>1689</v>
+      </c>
+      <c r="AS250" s="36"/>
+      <c r="AT250" s="11"/>
+      <c r="AU250" s="11" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AV250" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW250" s="14"/>
+      <c r="AX250" s="44"/>
+    </row>
+    <row r="251" spans="1:50" ht="25.5">
+      <c r="A251" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Auvergne-Rhône-Alpes</v>
+      </c>
+      <c r="B251" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Rhône</v>
+      </c>
+      <c r="C251" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>69</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E251" s="26">
+        <v>69002</v>
+      </c>
+      <c r="F251" s="10" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G251" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Allée Louis Thomas Achille
+69002 - Lyon Confluence</v>
+      </c>
+      <c r="H251" s="15" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I251" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J251" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K251" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L251" s="53" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M251" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N251" s="36" t="s">
+        <v>1613</v>
+      </c>
+      <c r="O251" s="34">
+        <v>239</v>
+      </c>
+      <c r="P251" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q251" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R251" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S251" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T251" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>47800</v>
+      </c>
+      <c r="U251" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3983.3333333333335</v>
+      </c>
+      <c r="V251" s="12">
+        <v>200</v>
+      </c>
+      <c r="W251" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X251" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
+      <c r="Y251" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z251" s="12"/>
+      <c r="AA251" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB251" s="12"/>
+      <c r="AC251" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD251" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE251" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>47800</v>
+      </c>
+      <c r="AF251" s="12" t="str">
+        <f t="shared" si="10"/>
+        <v>3 mois = 11 950 €</v>
+      </c>
+      <c r="AG251" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH251" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AI251" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ251" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK251" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL251" s="10"/>
+      <c r="AM251" s="11"/>
+      <c r="AN251" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AO251" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP251" s="11"/>
+      <c r="AQ251" s="11"/>
+      <c r="AR251" s="11" t="s">
+        <v>1690</v>
+      </c>
+      <c r="AS251" s="36"/>
+      <c r="AT251" s="11"/>
+      <c r="AU251" s="11" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AV251" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AW251" s="14"/>
+      <c r="AX251" s="44"/>
+    </row>
+    <row r="252" spans="1:50">
+      <c r="A252" s="38"/>
+      <c r="B252" s="38"/>
+      <c r="C252" s="38"/>
+      <c r="D252" s="10"/>
+      <c r="E252" s="10"/>
+      <c r="F252" s="10"/>
+      <c r="G252" s="39"/>
+      <c r="H252" s="52"/>
+      <c r="I252" s="12"/>
+      <c r="J252" s="12"/>
+      <c r="K252" s="10"/>
+      <c r="L252" s="10"/>
+      <c r="M252" s="12"/>
+      <c r="N252" s="36"/>
+      <c r="O252" s="34"/>
+      <c r="P252" s="12"/>
+      <c r="Q252" s="34"/>
+      <c r="R252" s="10"/>
+      <c r="S252" s="12"/>
+      <c r="T252" s="12"/>
+      <c r="U252" s="12"/>
+      <c r="V252" s="12"/>
+      <c r="W252" s="12"/>
+      <c r="X252" s="12"/>
+      <c r="Y252" s="12"/>
+      <c r="Z252" s="12"/>
+      <c r="AA252" s="12"/>
+      <c r="AB252" s="12"/>
+      <c r="AC252" s="12"/>
+      <c r="AD252" s="12"/>
+      <c r="AE252" s="12"/>
+      <c r="AF252" s="12"/>
+      <c r="AG252" s="12"/>
+      <c r="AH252" s="12"/>
+      <c r="AI252" s="12"/>
+      <c r="AJ252" s="10"/>
+      <c r="AK252" s="10"/>
+      <c r="AL252" s="10"/>
+      <c r="AM252" s="11"/>
+      <c r="AN252" s="11"/>
+      <c r="AO252" s="11"/>
+      <c r="AP252" s="11"/>
+      <c r="AQ252" s="11"/>
+      <c r="AR252" s="11"/>
+      <c r="AS252" s="36"/>
+      <c r="AT252" s="11"/>
+      <c r="AU252" s="11"/>
+      <c r="AV252" s="13"/>
+      <c r="AW252" s="14"/>
+      <c r="AX252" s="44"/>
+    </row>
+    <row r="253" spans="1:50">
+      <c r="A253" s="38"/>
+      <c r="B253" s="38"/>
+      <c r="C253" s="38"/>
+      <c r="D253" s="10"/>
+      <c r="E253" s="10"/>
+      <c r="F253" s="10"/>
+      <c r="G253" s="39"/>
+      <c r="H253" s="52"/>
+      <c r="I253" s="12"/>
+      <c r="J253" s="12"/>
+      <c r="K253" s="10"/>
+      <c r="L253" s="10"/>
+      <c r="M253" s="12"/>
+      <c r="N253" s="36"/>
+      <c r="O253" s="34"/>
+      <c r="P253" s="12"/>
+      <c r="Q253" s="34"/>
+      <c r="R253" s="10"/>
+      <c r="S253" s="12"/>
+      <c r="T253" s="12"/>
+      <c r="U253" s="12"/>
+      <c r="V253" s="12"/>
+      <c r="W253" s="12"/>
+      <c r="X253" s="12"/>
+      <c r="Y253" s="12"/>
+      <c r="Z253" s="12"/>
+      <c r="AA253" s="12"/>
+      <c r="AB253" s="12"/>
+      <c r="AC253" s="12"/>
+      <c r="AD253" s="12"/>
+      <c r="AE253" s="12"/>
+      <c r="AF253" s="12"/>
+      <c r="AG253" s="12"/>
+      <c r="AH253" s="12"/>
+      <c r="AI253" s="12"/>
+      <c r="AJ253" s="10"/>
+      <c r="AK253" s="10"/>
+      <c r="AL253" s="10"/>
+      <c r="AM253" s="11"/>
+      <c r="AN253" s="11"/>
+      <c r="AO253" s="11"/>
+      <c r="AP253" s="11"/>
+      <c r="AQ253" s="11"/>
+      <c r="AR253" s="11"/>
+      <c r="AS253" s="36"/>
+      <c r="AT253" s="11"/>
+      <c r="AU253" s="11"/>
+      <c r="AV253" s="13"/>
+      <c r="AW253" s="14"/>
+      <c r="AX253" s="44"/>
+    </row>
+    <row r="254" spans="1:50">
+      <c r="F254" s="1" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="232" spans="6:6">
-      <c r="F232" s="1" t="s">
+    <row r="255" spans="1:50">
+      <c r="F255" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -41559,6 +46283,26 @@
     <hyperlink ref="H218" r:id="rId182" xr:uid="{1F235C3F-C9DB-4C11-8CCF-0C97AB89EBD7}"/>
     <hyperlink ref="H220" r:id="rId183" xr:uid="{388632CD-FE0B-4C31-ACA8-6DA26C4D8ADF}"/>
     <hyperlink ref="H147" r:id="rId184" xr:uid="{D89787FE-D414-4ADC-AC02-C8B9D2520919}"/>
+    <hyperlink ref="H224" r:id="rId185" xr:uid="{ACBC6070-DAD9-4FE2-8D5C-716E5B266865}"/>
+    <hyperlink ref="H225" r:id="rId186" xr:uid="{B52E1D96-F637-4C15-B8D6-DE07EFCCD7D4}"/>
+    <hyperlink ref="H226" r:id="rId187" xr:uid="{85EEEDCF-82EF-4023-9786-A3975D56DCCD}"/>
+    <hyperlink ref="H227:H232" r:id="rId188" display="https://maps.app.goo.gl/ZPoo7HsyrDthxYXT7" xr:uid="{BC72D3BA-193A-4590-A139-45FD14E16D29}"/>
+    <hyperlink ref="H233" r:id="rId189" xr:uid="{CD3468AF-EFE4-4CA7-A470-92A73B92CFB8}"/>
+    <hyperlink ref="H234" r:id="rId190" xr:uid="{346E6C25-BB0F-44A0-8892-BC68069BAA7A}"/>
+    <hyperlink ref="H236" r:id="rId191" xr:uid="{C3673093-0EB3-431E-A819-C56087625C52}"/>
+    <hyperlink ref="H237" r:id="rId192" xr:uid="{5FD41EE0-E32F-4B42-9354-0A62AD7E219E}"/>
+    <hyperlink ref="H238" r:id="rId193" xr:uid="{FED85340-EAA2-4E7A-8432-7A3BE5D6AD3B}"/>
+    <hyperlink ref="H239" r:id="rId194" xr:uid="{868312A7-9941-4FDE-B477-B5C112A5D556}"/>
+    <hyperlink ref="H240" r:id="rId195" xr:uid="{9C135695-9C00-4C5F-913A-8013B376DD95}"/>
+    <hyperlink ref="H241" r:id="rId196" xr:uid="{7B5795EF-4703-4B84-8920-EE6B31A463D3}"/>
+    <hyperlink ref="H242" r:id="rId197" xr:uid="{89FEC483-A001-4B45-B8FA-C0133C0159FE}"/>
+    <hyperlink ref="H243" r:id="rId198" xr:uid="{3DFB2647-894B-43B0-92A3-00B341C0DA0D}"/>
+    <hyperlink ref="H244" r:id="rId199" xr:uid="{408D462D-C0B8-47D0-B218-E428030F0641}"/>
+    <hyperlink ref="H245" r:id="rId200" xr:uid="{712B7062-EA0E-4D1F-A272-DF16C4B7C670}"/>
+    <hyperlink ref="H246" r:id="rId201" xr:uid="{D15EAC12-EA3F-4DA4-8740-E655D87FD258}"/>
+    <hyperlink ref="H247" r:id="rId202" xr:uid="{D3414EB2-CD56-43D6-9D9C-98082550958C}"/>
+    <hyperlink ref="H248" r:id="rId203" xr:uid="{6B91A769-147A-4650-A292-F429547DB920}"/>
+    <hyperlink ref="H249:H251" r:id="rId204" display="https://maps.app.goo.gl/rYXwsZdHTTd2e5Xo7" xr:uid="{E8CD37E8-5D1B-46C7-BF51-57B83D1F1C37}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -41567,7 +46311,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId185"/>
+    <tablePart r:id="rId205"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663BDF42-6DA8-4271-8B94-77DF6F261FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC9AB6E-78C0-41C4-8A35-25C35238350B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -4715,9 +4715,6 @@
     <t>3/6/9 ans</t>
   </si>
   <si>
-    <t>112 €/m² = 50 000 € HT</t>
-  </si>
-  <si>
     <t>Les galeries d'Huningue
 9 avenue d'Alsace</t>
   </si>
@@ -4751,18 +4748,6 @@
     <t>Bureaux dans le Leclerc Drive. Place de parking / Accueil / 3 open space / Cuisine</t>
   </si>
   <si>
-    <t>154 €/m² = 38 500 € HT</t>
-  </si>
-  <si>
-    <t>186 €/m² = 55 800 € HT</t>
-  </si>
-  <si>
-    <t>186 €/m² = 113 088 € HT</t>
-  </si>
-  <si>
-    <t>186 €/m² = 47 802 € HT</t>
-  </si>
-  <si>
     <t>65.1</t>
   </si>
   <si>
@@ -5150,15 +5135,6 @@
     <t>419 + 138</t>
   </si>
   <si>
-    <t>42 000 € HT</t>
-  </si>
-  <si>
-    <t>6 000 € HT</t>
-  </si>
-  <si>
-    <t>60 000 € HT</t>
-  </si>
-  <si>
     <t>Gemo, King Jouet, Sport 2000, …</t>
   </si>
   <si>
@@ -5175,6 +5151,30 @@
   </si>
   <si>
     <t>Location ou à vendre. Seul Hypermarché de la Lozère. CA de 75 M€, dans une bonne zone commerciale avec McDonald's, Bricomarché, Feu Vert, But, Picard, Gamm Vert…</t>
+  </si>
+  <si>
+    <t>110 €/m² = 42 000 €</t>
+  </si>
+  <si>
+    <t>112 €/m² = 50 000 €</t>
+  </si>
+  <si>
+    <t>186 €/m² = 55 800 €</t>
+  </si>
+  <si>
+    <t>186 €/m² = 113 088 €</t>
+  </si>
+  <si>
+    <t>186 €/m² = 47 802 €</t>
+  </si>
+  <si>
+    <t>154 €/m² = 38 500 €</t>
+  </si>
+  <si>
+    <t>108 €/m² = 60 000 €</t>
+  </si>
+  <si>
+    <t>133 €/m² = 6 000 €</t>
   </si>
 </sst>
 </file>
@@ -40849,22 +40849,22 @@
         <v>367</v>
       </c>
       <c r="AP216" s="11" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="AQ216" s="11" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="AR216" s="11">
         <v>64</v>
       </c>
       <c r="AS216" s="36" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="AT216" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU216" s="11" t="s">
-        <v>1554</v>
+        <v>1700</v>
       </c>
       <c r="AV216" s="13" t="s">
         <v>1036</v>
@@ -40888,7 +40888,7 @@
         <v>68</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="E217" s="26">
         <v>68330</v>
@@ -40903,7 +40903,7 @@
 68330 - Huningue</v>
       </c>
       <c r="H217" s="15" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="I217" s="12" t="s">
         <v>47</v>
@@ -40921,7 +40921,7 @@
         <v>103</v>
       </c>
       <c r="N217" s="36" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="O217" s="34">
         <v>300</v>
@@ -41003,16 +41003,16 @@
         <v>1029</v>
       </c>
       <c r="AR217" s="11" t="s">
+        <v>1564</v>
+      </c>
+      <c r="AS217" s="36" t="s">
         <v>1569</v>
-      </c>
-      <c r="AS217" s="36" t="s">
-        <v>1574</v>
       </c>
       <c r="AT217" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU217" s="11" t="s">
-        <v>1566</v>
+        <v>1701</v>
       </c>
       <c r="AV217" s="13" t="s">
         <v>1036</v>
@@ -41036,7 +41036,7 @@
         <v>68</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="E218" s="26">
         <v>68331</v>
@@ -41051,7 +41051,7 @@
 68331 - Huningue</v>
       </c>
       <c r="H218" s="15" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="I218" s="12" t="s">
         <v>47</v>
@@ -41134,7 +41134,7 @@
       </c>
       <c r="AL218" s="10"/>
       <c r="AM218" s="11" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="AN218" s="11" t="s">
         <v>103</v>
@@ -41143,22 +41143,22 @@
         <v>367</v>
       </c>
       <c r="AP218" s="11" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="AQ218" s="11" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="AR218" s="11" t="s">
+        <v>1565</v>
+      </c>
+      <c r="AS218" s="36" t="s">
         <v>1570</v>
-      </c>
-      <c r="AS218" s="36" t="s">
-        <v>1575</v>
       </c>
       <c r="AT218" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU218" s="11" t="s">
-        <v>1567</v>
+        <v>1702</v>
       </c>
       <c r="AV218" s="13" t="s">
         <v>1036</v>
@@ -41182,13 +41182,13 @@
         <v>68</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="E219" s="26">
         <v>68220</v>
       </c>
       <c r="F219" s="42" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="G219" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -41286,13 +41286,13 @@
         <v>66</v>
       </c>
       <c r="AS219" s="36" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="AT219" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU219" s="11" t="s">
-        <v>1568</v>
+        <v>1703</v>
       </c>
       <c r="AV219" s="13" t="s">
         <v>1036</v>
@@ -41316,13 +41316,13 @@
         <v>68</v>
       </c>
       <c r="D220" s="10" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="E220" s="26">
         <v>68300</v>
       </c>
       <c r="F220" s="42" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G220" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -41330,7 +41330,7 @@
 68300 - Saint-Louis</v>
       </c>
       <c r="H220" s="15" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="I220" s="12" t="s">
         <v>47</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="AL220" s="10"/>
       <c r="AM220" s="11" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="AN220" s="11" t="s">
         <v>103</v>
@@ -41420,10 +41420,10 @@
         <v>367</v>
       </c>
       <c r="AP220" s="11" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="AQ220" s="11" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="AR220" s="11">
         <v>67</v>
@@ -41433,7 +41433,7 @@
         <v>75</v>
       </c>
       <c r="AU220" s="11" t="s">
-        <v>1565</v>
+        <v>1704</v>
       </c>
       <c r="AV220" s="13" t="s">
         <v>1036</v>
@@ -41494,7 +41494,7 @@
         <v>557</v>
       </c>
       <c r="P221" s="12" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="Q221" s="34"/>
       <c r="R221" s="34" t="s">
@@ -41563,10 +41563,10 @@
         <v>369</v>
       </c>
       <c r="AL221" s="10" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
       <c r="AM221" s="11" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
       <c r="AN221" s="11" t="s">
         <v>103</v>
@@ -41575,25 +41575,25 @@
         <v>367</v>
       </c>
       <c r="AP221" s="11" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="AQ221" s="11" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="AR221" s="11" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="AS221" s="36" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="AT221" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU221" s="11" t="s">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="AV221" s="13" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="AW221" s="14"/>
       <c r="AX221" s="44">
@@ -41651,7 +41651,7 @@
         <v>380</v>
       </c>
       <c r="P222" s="12" t="s">
-        <v>1703</v>
+        <v>1695</v>
       </c>
       <c r="Q222" s="34"/>
       <c r="R222" s="34" t="s">
@@ -41713,10 +41713,10 @@
         <v>369</v>
       </c>
       <c r="AL222" s="10" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
       <c r="AM222" s="11" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
       <c r="AN222" s="11" t="s">
         <v>103</v>
@@ -41725,25 +41725,25 @@
         <v>367</v>
       </c>
       <c r="AP222" s="11" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="AQ222" s="11" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
       <c r="AR222" s="11" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="AS222" s="36" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="AT222" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU222" s="11" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="AV222" s="13" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="AW222" s="14"/>
       <c r="AX222" s="44">
@@ -41859,10 +41859,10 @@
         <v>368</v>
       </c>
       <c r="AL223" s="10" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
       <c r="AM223" s="11" t="s">
-        <v>1702</v>
+        <v>1694</v>
       </c>
       <c r="AN223" s="11" t="s">
         <v>103</v>
@@ -41871,25 +41871,25 @@
         <v>367</v>
       </c>
       <c r="AP223" s="11" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="AQ223" s="11" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="AR223" s="11" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="AS223" s="36" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="AT223" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU223" s="11" t="s">
-        <v>1699</v>
+        <v>1706</v>
       </c>
       <c r="AV223" s="13" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="AW223" s="14"/>
       <c r="AX223" s="44">
@@ -41910,13 +41910,13 @@
         <v>94</v>
       </c>
       <c r="D224" s="10" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="E224" s="26">
         <v>94140</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="G224" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -41924,7 +41924,7 @@
 94140 - Alfortville</v>
       </c>
       <c r="H224" s="15" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="I224" s="12" t="s">
         <v>45</v>
@@ -42020,7 +42020,7 @@
       <c r="AL224" s="10"/>
       <c r="AM224" s="11"/>
       <c r="AN224" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO224" s="5" t="s">
         <v>367</v>
@@ -42033,10 +42033,10 @@
       <c r="AS224" s="36"/>
       <c r="AT224" s="11"/>
       <c r="AU224" s="11" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="AV224" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW224" s="14"/>
       <c r="AX224" s="44"/>
@@ -42055,13 +42055,13 @@
         <v>69</v>
       </c>
       <c r="D225" s="10" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="E225" s="26">
         <v>69500</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G225" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -42069,7 +42069,7 @@
 69500 - Bron</v>
       </c>
       <c r="H225" s="15" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="I225" s="12" t="s">
         <v>45</v>
@@ -42167,7 +42167,7 @@
       <c r="AL225" s="10"/>
       <c r="AM225" s="11"/>
       <c r="AN225" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO225" s="5" t="s">
         <v>367</v>
@@ -42175,15 +42175,15 @@
       <c r="AP225" s="11"/>
       <c r="AQ225" s="11"/>
       <c r="AR225" s="11" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="AS225" s="36"/>
       <c r="AT225" s="11"/>
       <c r="AU225" s="11" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
       <c r="AV225" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW225" s="14"/>
       <c r="AX225" s="44"/>
@@ -42202,13 +42202,13 @@
         <v>69</v>
       </c>
       <c r="D226" s="10" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="E226" s="26">
         <v>69500</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G226" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -42216,7 +42216,7 @@
 69500 - Bron</v>
       </c>
       <c r="H226" s="15" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="I226" s="12" t="s">
         <v>45</v>
@@ -42314,7 +42314,7 @@
       <c r="AL226" s="10"/>
       <c r="AM226" s="11"/>
       <c r="AN226" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO226" s="5" t="s">
         <v>367</v>
@@ -42322,15 +42322,15 @@
       <c r="AP226" s="11"/>
       <c r="AQ226" s="11"/>
       <c r="AR226" s="11" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="AS226" s="36"/>
       <c r="AT226" s="11"/>
       <c r="AU226" s="11" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="AV226" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW226" s="14"/>
       <c r="AX226" s="44"/>
@@ -42349,13 +42349,13 @@
         <v>69</v>
       </c>
       <c r="D227" s="10" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="E227" s="26">
         <v>69500</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G227" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -42363,7 +42363,7 @@
 69500 - Bron</v>
       </c>
       <c r="H227" s="15" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="I227" s="12" t="s">
         <v>45</v>
@@ -42381,7 +42381,7 @@
         <v>103</v>
       </c>
       <c r="N227" s="36" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="O227" s="34">
         <v>110</v>
@@ -42461,7 +42461,7 @@
       <c r="AL227" s="10"/>
       <c r="AM227" s="11"/>
       <c r="AN227" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO227" s="5" t="s">
         <v>367</v>
@@ -42469,15 +42469,15 @@
       <c r="AP227" s="11"/>
       <c r="AQ227" s="11"/>
       <c r="AR227" s="11" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="AS227" s="36"/>
       <c r="AT227" s="11"/>
       <c r="AU227" s="11" t="s">
-        <v>1644</v>
+        <v>1639</v>
       </c>
       <c r="AV227" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW227" s="14"/>
       <c r="AX227" s="44"/>
@@ -42496,13 +42496,13 @@
         <v>69</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="E228" s="26">
         <v>69500</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G228" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -42510,7 +42510,7 @@
 69500 - Bron</v>
       </c>
       <c r="H228" s="15" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="I228" s="12" t="s">
         <v>45</v>
@@ -42608,7 +42608,7 @@
       <c r="AL228" s="10"/>
       <c r="AM228" s="11"/>
       <c r="AN228" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO228" s="5" t="s">
         <v>367</v>
@@ -42616,15 +42616,15 @@
       <c r="AP228" s="11"/>
       <c r="AQ228" s="11"/>
       <c r="AR228" s="11" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
       <c r="AS228" s="36"/>
       <c r="AT228" s="11"/>
       <c r="AU228" s="11" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="AV228" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW228" s="14"/>
       <c r="AX228" s="44"/>
@@ -42643,13 +42643,13 @@
         <v>69</v>
       </c>
       <c r="D229" s="10" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="E229" s="26">
         <v>69500</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G229" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -42657,7 +42657,7 @@
 69500 - Bron</v>
       </c>
       <c r="H229" s="15" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="I229" s="12" t="s">
         <v>45</v>
@@ -42675,7 +42675,7 @@
         <v>103</v>
       </c>
       <c r="N229" s="36" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="O229" s="34">
         <v>86</v>
@@ -42755,7 +42755,7 @@
       <c r="AL229" s="10"/>
       <c r="AM229" s="11"/>
       <c r="AN229" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO229" s="5" t="s">
         <v>367</v>
@@ -42763,15 +42763,15 @@
       <c r="AP229" s="11"/>
       <c r="AQ229" s="11"/>
       <c r="AR229" s="11" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
       <c r="AS229" s="36"/>
       <c r="AT229" s="11"/>
       <c r="AU229" s="11" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
       <c r="AV229" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW229" s="14"/>
       <c r="AX229" s="44"/>
@@ -42790,13 +42790,13 @@
         <v>69</v>
       </c>
       <c r="D230" s="10" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="E230" s="26">
         <v>69500</v>
       </c>
       <c r="F230" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G230" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -42804,7 +42804,7 @@
 69500 - Bron</v>
       </c>
       <c r="H230" s="15" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="I230" s="12" t="s">
         <v>45</v>
@@ -42822,7 +42822,7 @@
         <v>103</v>
       </c>
       <c r="N230" s="36" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="O230" s="34">
         <v>91</v>
@@ -42902,7 +42902,7 @@
       <c r="AL230" s="10"/>
       <c r="AM230" s="11"/>
       <c r="AN230" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO230" s="5" t="s">
         <v>367</v>
@@ -42910,15 +42910,15 @@
       <c r="AP230" s="11"/>
       <c r="AQ230" s="11"/>
       <c r="AR230" s="11" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="AS230" s="36"/>
       <c r="AT230" s="11"/>
       <c r="AU230" s="11" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="AV230" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW230" s="14"/>
       <c r="AX230" s="44"/>
@@ -42937,13 +42937,13 @@
         <v>69</v>
       </c>
       <c r="D231" s="10" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="E231" s="26">
         <v>69500</v>
       </c>
       <c r="F231" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G231" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -42951,7 +42951,7 @@
 69500 - Bron</v>
       </c>
       <c r="H231" s="15" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="I231" s="12" t="s">
         <v>45</v>
@@ -42969,7 +42969,7 @@
         <v>103</v>
       </c>
       <c r="N231" s="36" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="O231" s="34">
         <v>167</v>
@@ -43049,7 +43049,7 @@
       <c r="AL231" s="10"/>
       <c r="AM231" s="11"/>
       <c r="AN231" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO231" s="5" t="s">
         <v>367</v>
@@ -43057,15 +43057,15 @@
       <c r="AP231" s="11"/>
       <c r="AQ231" s="11"/>
       <c r="AR231" s="11" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="AS231" s="36"/>
       <c r="AT231" s="11"/>
       <c r="AU231" s="11" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
       <c r="AV231" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW231" s="14"/>
       <c r="AX231" s="44"/>
@@ -43084,13 +43084,13 @@
         <v>69</v>
       </c>
       <c r="D232" s="10" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="E232" s="26">
         <v>69500</v>
       </c>
       <c r="F232" s="10" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="G232" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -43098,7 +43098,7 @@
 69500 - Bron</v>
       </c>
       <c r="H232" s="15" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="I232" s="12" t="s">
         <v>45</v>
@@ -43196,7 +43196,7 @@
       <c r="AL232" s="10"/>
       <c r="AM232" s="11"/>
       <c r="AN232" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO232" s="5" t="s">
         <v>367</v>
@@ -43204,15 +43204,15 @@
       <c r="AP232" s="11"/>
       <c r="AQ232" s="11"/>
       <c r="AR232" s="11" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
       <c r="AS232" s="36"/>
       <c r="AT232" s="11"/>
       <c r="AU232" s="11" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
       <c r="AV232" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW232" s="14"/>
       <c r="AX232" s="44"/>
@@ -43231,13 +43231,13 @@
         <v>92</v>
       </c>
       <c r="D233" s="10" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
       <c r="E233" s="26">
         <v>92700</v>
       </c>
       <c r="F233" s="10" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="G233" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -43245,7 +43245,7 @@
 92700 - Colombes</v>
       </c>
       <c r="H233" s="15" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
       <c r="I233" s="12" t="s">
         <v>45</v>
@@ -43341,7 +43341,7 @@
       <c r="AL233" s="10"/>
       <c r="AM233" s="11"/>
       <c r="AN233" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO233" s="5" t="s">
         <v>367</v>
@@ -43354,10 +43354,10 @@
       <c r="AS233" s="36"/>
       <c r="AT233" s="11"/>
       <c r="AU233" s="11" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="AV233" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW233" s="14"/>
       <c r="AX233" s="44"/>
@@ -43376,13 +43376,13 @@
         <v>37</v>
       </c>
       <c r="D234" s="10" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="E234" s="26">
         <v>37300</v>
       </c>
       <c r="F234" s="10" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="G234" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -43390,7 +43390,7 @@
 37300 - Joué les Tours</v>
       </c>
       <c r="H234" s="15" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="I234" s="12" t="s">
         <v>45</v>
@@ -43486,7 +43486,7 @@
       <c r="AL234" s="10"/>
       <c r="AM234" s="11"/>
       <c r="AN234" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO234" s="5" t="s">
         <v>367</v>
@@ -43499,10 +43499,10 @@
       <c r="AS234" s="36"/>
       <c r="AT234" s="11"/>
       <c r="AU234" s="11" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="AV234" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW234" s="14"/>
       <c r="AX234" s="44"/>
@@ -43521,13 +43521,13 @@
         <v>59</v>
       </c>
       <c r="D235" s="10" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="E235" s="26">
         <v>59800</v>
       </c>
       <c r="F235" s="10" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="G235" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -43631,7 +43631,7 @@
       <c r="AL235" s="10"/>
       <c r="AM235" s="11"/>
       <c r="AN235" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO235" s="5" t="s">
         <v>367</v>
@@ -43644,10 +43644,10 @@
       <c r="AS235" s="36"/>
       <c r="AT235" s="11"/>
       <c r="AU235" s="11" t="s">
-        <v>1652</v>
+        <v>1647</v>
       </c>
       <c r="AV235" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW235" s="14"/>
       <c r="AX235" s="44"/>
@@ -43666,13 +43666,13 @@
         <v>59</v>
       </c>
       <c r="D236" s="10" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="E236" s="26">
         <v>59800</v>
       </c>
       <c r="F236" s="10" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="G236" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -43680,7 +43680,7 @@
 59800 - Lille Hellemmes</v>
       </c>
       <c r="H236" s="15" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="I236" s="12" t="s">
         <v>45</v>
@@ -43698,7 +43698,7 @@
         <v>103</v>
       </c>
       <c r="N236" s="36" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="O236" s="34">
         <v>52</v>
@@ -43778,7 +43778,7 @@
       <c r="AL236" s="10"/>
       <c r="AM236" s="11"/>
       <c r="AN236" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO236" s="5" t="s">
         <v>367</v>
@@ -43786,15 +43786,15 @@
       <c r="AP236" s="11"/>
       <c r="AQ236" s="11"/>
       <c r="AR236" s="11" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="AS236" s="36"/>
       <c r="AT236" s="11"/>
       <c r="AU236" s="11" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
       <c r="AV236" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW236" s="14"/>
       <c r="AX236" s="44"/>
@@ -43813,13 +43813,13 @@
         <v>59</v>
       </c>
       <c r="D237" s="10" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="E237" s="26">
         <v>59800</v>
       </c>
       <c r="F237" s="10" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="G237" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -43827,7 +43827,7 @@
 59800 - Lille Hellemmes</v>
       </c>
       <c r="H237" s="15" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="I237" s="12" t="s">
         <v>45</v>
@@ -43845,7 +43845,7 @@
         <v>103</v>
       </c>
       <c r="N237" s="36" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="O237" s="34">
         <v>38</v>
@@ -43925,7 +43925,7 @@
       <c r="AL237" s="10"/>
       <c r="AM237" s="11"/>
       <c r="AN237" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO237" s="5" t="s">
         <v>367</v>
@@ -43933,15 +43933,15 @@
       <c r="AP237" s="11"/>
       <c r="AQ237" s="11"/>
       <c r="AR237" s="11" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
       <c r="AS237" s="36"/>
       <c r="AT237" s="11"/>
       <c r="AU237" s="11" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="AV237" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW237" s="14"/>
       <c r="AX237" s="44"/>
@@ -43960,13 +43960,13 @@
         <v>59</v>
       </c>
       <c r="D238" s="10" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="E238" s="26">
         <v>59800</v>
       </c>
       <c r="F238" s="10" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="G238" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -43974,7 +43974,7 @@
 59800 - Lille Hellemmes</v>
       </c>
       <c r="H238" s="15" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="I238" s="12" t="s">
         <v>45</v>
@@ -43992,7 +43992,7 @@
         <v>103</v>
       </c>
       <c r="N238" s="36" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="O238" s="34">
         <v>173</v>
@@ -44072,7 +44072,7 @@
       <c r="AL238" s="10"/>
       <c r="AM238" s="11"/>
       <c r="AN238" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO238" s="5" t="s">
         <v>367</v>
@@ -44080,15 +44080,15 @@
       <c r="AP238" s="11"/>
       <c r="AQ238" s="11"/>
       <c r="AR238" s="11" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="AS238" s="36"/>
       <c r="AT238" s="11"/>
       <c r="AU238" s="11" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="AV238" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW238" s="14"/>
       <c r="AX238" s="44"/>
@@ -44107,13 +44107,13 @@
         <v>93</v>
       </c>
       <c r="D239" s="10" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="E239" s="26">
         <v>93100</v>
       </c>
       <c r="F239" s="10" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="G239" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -44121,7 +44121,7 @@
 93100 - Montreuil</v>
       </c>
       <c r="H239" s="15" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="I239" s="12" t="s">
         <v>45</v>
@@ -44139,7 +44139,7 @@
         <v>103</v>
       </c>
       <c r="N239" s="36" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="O239" s="34">
         <v>320</v>
@@ -44217,7 +44217,7 @@
       <c r="AL239" s="10"/>
       <c r="AM239" s="11"/>
       <c r="AN239" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO239" s="5" t="s">
         <v>367</v>
@@ -44225,15 +44225,15 @@
       <c r="AP239" s="11"/>
       <c r="AQ239" s="11"/>
       <c r="AR239" s="11" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="AS239" s="36"/>
       <c r="AT239" s="11"/>
       <c r="AU239" s="11" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
       <c r="AV239" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW239" s="14"/>
       <c r="AX239" s="44"/>
@@ -44252,13 +44252,13 @@
         <v>93</v>
       </c>
       <c r="D240" s="10" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="E240" s="26">
         <v>93100</v>
       </c>
       <c r="F240" s="10" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="G240" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -44266,7 +44266,7 @@
 93100 - Montreuil</v>
       </c>
       <c r="H240" s="15" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="I240" s="12" t="s">
         <v>45</v>
@@ -44284,7 +44284,7 @@
         <v>103</v>
       </c>
       <c r="N240" s="36" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="O240" s="34">
         <v>280</v>
@@ -44362,7 +44362,7 @@
       <c r="AL240" s="10"/>
       <c r="AM240" s="11"/>
       <c r="AN240" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO240" s="5" t="s">
         <v>367</v>
@@ -44370,15 +44370,15 @@
       <c r="AP240" s="11"/>
       <c r="AQ240" s="11"/>
       <c r="AR240" s="11" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="AS240" s="36"/>
       <c r="AT240" s="11"/>
       <c r="AU240" s="11" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="AV240" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW240" s="14"/>
       <c r="AX240" s="44"/>
@@ -44397,13 +44397,13 @@
         <v>78</v>
       </c>
       <c r="D241" s="10" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="E241" s="26">
         <v>78300</v>
       </c>
       <c r="F241" s="10" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="G241" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -44411,7 +44411,7 @@
 78300 - Poissy</v>
       </c>
       <c r="H241" s="15" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="I241" s="12" t="s">
         <v>45</v>
@@ -44429,7 +44429,7 @@
         <v>103</v>
       </c>
       <c r="N241" s="36" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="O241" s="34">
         <v>123</v>
@@ -44509,7 +44509,7 @@
       <c r="AL241" s="10"/>
       <c r="AM241" s="11"/>
       <c r="AN241" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO241" s="5" t="s">
         <v>367</v>
@@ -44517,15 +44517,15 @@
       <c r="AP241" s="11"/>
       <c r="AQ241" s="11"/>
       <c r="AR241" s="11" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
       <c r="AS241" s="36"/>
       <c r="AT241" s="11"/>
       <c r="AU241" s="11" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
       <c r="AV241" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW241" s="14"/>
       <c r="AX241" s="44"/>
@@ -44544,13 +44544,13 @@
         <v>78</v>
       </c>
       <c r="D242" s="10" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="E242" s="26">
         <v>78300</v>
       </c>
       <c r="F242" s="10" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="G242" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -44558,7 +44558,7 @@
 78300 - Poissy</v>
       </c>
       <c r="H242" s="15" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="I242" s="12" t="s">
         <v>45</v>
@@ -44576,7 +44576,7 @@
         <v>103</v>
       </c>
       <c r="N242" s="36" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="O242" s="34">
         <v>111</v>
@@ -44656,7 +44656,7 @@
       <c r="AL242" s="10"/>
       <c r="AM242" s="11"/>
       <c r="AN242" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO242" s="5" t="s">
         <v>367</v>
@@ -44664,15 +44664,15 @@
       <c r="AP242" s="11"/>
       <c r="AQ242" s="11"/>
       <c r="AR242" s="11" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="AS242" s="36"/>
       <c r="AT242" s="11"/>
       <c r="AU242" s="11" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
       <c r="AV242" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW242" s="14"/>
       <c r="AX242" s="44"/>
@@ -44691,13 +44691,13 @@
         <v>93</v>
       </c>
       <c r="D243" s="10" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="E243" s="26">
         <v>93400</v>
       </c>
       <c r="F243" s="10" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="G243" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -44705,7 +44705,7 @@
 93400 - Saint-Ouen</v>
       </c>
       <c r="H243" s="15" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
       <c r="I243" s="12" t="s">
         <v>45</v>
@@ -44801,7 +44801,7 @@
       <c r="AL243" s="10"/>
       <c r="AM243" s="11"/>
       <c r="AN243" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO243" s="5" t="s">
         <v>367</v>
@@ -44814,10 +44814,10 @@
       <c r="AS243" s="36"/>
       <c r="AT243" s="11"/>
       <c r="AU243" s="11" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="AV243" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW243" s="14"/>
       <c r="AX243" s="44"/>
@@ -44836,13 +44836,13 @@
         <v>94</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="E244" s="26">
         <v>94510</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="G244" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -44850,7 +44850,7 @@
 94510 - La Queue en Brie</v>
       </c>
       <c r="H244" s="15" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="I244" s="12" t="s">
         <v>45</v>
@@ -44946,7 +44946,7 @@
       <c r="AL244" s="10"/>
       <c r="AM244" s="11"/>
       <c r="AN244" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO244" s="5" t="s">
         <v>367</v>
@@ -44954,15 +44954,15 @@
       <c r="AP244" s="11"/>
       <c r="AQ244" s="11"/>
       <c r="AR244" s="11" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="AS244" s="36"/>
       <c r="AT244" s="11"/>
       <c r="AU244" s="11" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
       <c r="AV244" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW244" s="14"/>
       <c r="AX244" s="44"/>
@@ -44981,13 +44981,13 @@
         <v>94</v>
       </c>
       <c r="D245" s="10" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="E245" s="26">
         <v>94511</v>
       </c>
       <c r="F245" s="10" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="G245" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -44995,7 +44995,7 @@
 94511 - La Queue en Brie</v>
       </c>
       <c r="H245" s="15" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="I245" s="12" t="s">
         <v>45</v>
@@ -45091,7 +45091,7 @@
       <c r="AL245" s="10"/>
       <c r="AM245" s="11"/>
       <c r="AN245" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO245" s="5" t="s">
         <v>367</v>
@@ -45099,15 +45099,15 @@
       <c r="AP245" s="11"/>
       <c r="AQ245" s="11"/>
       <c r="AR245" s="11" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
       <c r="AS245" s="36"/>
       <c r="AT245" s="11"/>
       <c r="AU245" s="11" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
       <c r="AV245" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW245" s="14"/>
       <c r="AX245" s="44"/>
@@ -45126,13 +45126,13 @@
         <v>94</v>
       </c>
       <c r="D246" s="10" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="E246" s="26">
         <v>94512</v>
       </c>
       <c r="F246" s="10" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="G246" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -45140,7 +45140,7 @@
 94512 - La Queue en Brie</v>
       </c>
       <c r="H246" s="15" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="I246" s="12" t="s">
         <v>45</v>
@@ -45236,7 +45236,7 @@
       <c r="AL246" s="10"/>
       <c r="AM246" s="11"/>
       <c r="AN246" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO246" s="5" t="s">
         <v>367</v>
@@ -45244,15 +45244,15 @@
       <c r="AP246" s="11"/>
       <c r="AQ246" s="11"/>
       <c r="AR246" s="11" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="AS246" s="36"/>
       <c r="AT246" s="11"/>
       <c r="AU246" s="11" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="AV246" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW246" s="14"/>
       <c r="AX246" s="44"/>
@@ -45271,13 +45271,13 @@
         <v>94</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="E247" s="26">
         <v>94513</v>
       </c>
       <c r="F247" s="10" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="G247" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -45285,7 +45285,7 @@
 94513 - La Queue en Brie</v>
       </c>
       <c r="H247" s="15" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="I247" s="12" t="s">
         <v>45</v>
@@ -45381,7 +45381,7 @@
       <c r="AL247" s="10"/>
       <c r="AM247" s="11"/>
       <c r="AN247" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO247" s="5" t="s">
         <v>367</v>
@@ -45389,15 +45389,15 @@
       <c r="AP247" s="11"/>
       <c r="AQ247" s="11"/>
       <c r="AR247" s="11" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="AS247" s="36"/>
       <c r="AT247" s="11"/>
       <c r="AU247" s="11" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
       <c r="AV247" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW247" s="14"/>
       <c r="AX247" s="44"/>
@@ -45416,13 +45416,13 @@
         <v>69</v>
       </c>
       <c r="D248" s="10" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="E248" s="26">
         <v>69002</v>
       </c>
       <c r="F248" s="10" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="G248" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -45430,7 +45430,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H248" s="15" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="I248" s="12" t="s">
         <v>45</v>
@@ -45448,7 +45448,7 @@
         <v>103</v>
       </c>
       <c r="N248" s="36" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="O248" s="34">
         <v>248</v>
@@ -45526,7 +45526,7 @@
       <c r="AL248" s="10"/>
       <c r="AM248" s="11"/>
       <c r="AN248" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO248" s="5" t="s">
         <v>367</v>
@@ -45534,15 +45534,15 @@
       <c r="AP248" s="11"/>
       <c r="AQ248" s="11"/>
       <c r="AR248" s="11" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="AS248" s="36"/>
       <c r="AT248" s="11"/>
       <c r="AU248" s="11" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="AV248" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW248" s="14"/>
       <c r="AX248" s="44"/>
@@ -45561,13 +45561,13 @@
         <v>69</v>
       </c>
       <c r="D249" s="10" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="E249" s="26">
         <v>69002</v>
       </c>
       <c r="F249" s="10" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="G249" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -45575,7 +45575,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H249" s="15" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="I249" s="12" t="s">
         <v>45</v>
@@ -45593,7 +45593,7 @@
         <v>103</v>
       </c>
       <c r="N249" s="36" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="O249" s="34">
         <v>264</v>
@@ -45671,7 +45671,7 @@
       <c r="AL249" s="10"/>
       <c r="AM249" s="11"/>
       <c r="AN249" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO249" s="5" t="s">
         <v>367</v>
@@ -45679,15 +45679,15 @@
       <c r="AP249" s="11"/>
       <c r="AQ249" s="11"/>
       <c r="AR249" s="11" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
       <c r="AS249" s="36"/>
       <c r="AT249" s="11"/>
       <c r="AU249" s="11" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="AV249" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW249" s="14"/>
       <c r="AX249" s="44"/>
@@ -45706,13 +45706,13 @@
         <v>69</v>
       </c>
       <c r="D250" s="10" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="E250" s="26">
         <v>69002</v>
       </c>
       <c r="F250" s="10" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="G250" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -45720,7 +45720,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H250" s="15" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="I250" s="12" t="s">
         <v>45</v>
@@ -45738,7 +45738,7 @@
         <v>103</v>
       </c>
       <c r="N250" s="36" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="O250" s="34">
         <v>174</v>
@@ -45816,7 +45816,7 @@
       <c r="AL250" s="10"/>
       <c r="AM250" s="11"/>
       <c r="AN250" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO250" s="5" t="s">
         <v>367</v>
@@ -45824,15 +45824,15 @@
       <c r="AP250" s="11"/>
       <c r="AQ250" s="11"/>
       <c r="AR250" s="11" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="AS250" s="36"/>
       <c r="AT250" s="11"/>
       <c r="AU250" s="11" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="AV250" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW250" s="14"/>
       <c r="AX250" s="44"/>
@@ -45851,13 +45851,13 @@
         <v>69</v>
       </c>
       <c r="D251" s="10" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="E251" s="26">
         <v>69002</v>
       </c>
       <c r="F251" s="10" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="G251" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -45865,7 +45865,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H251" s="15" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="I251" s="12" t="s">
         <v>45</v>
@@ -45883,7 +45883,7 @@
         <v>103</v>
       </c>
       <c r="N251" s="36" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="O251" s="34">
         <v>239</v>
@@ -45961,7 +45961,7 @@
       <c r="AL251" s="10"/>
       <c r="AM251" s="11"/>
       <c r="AN251" s="11" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="AO251" s="5" t="s">
         <v>367</v>
@@ -45969,15 +45969,15 @@
       <c r="AP251" s="11"/>
       <c r="AQ251" s="11"/>
       <c r="AR251" s="11" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
       <c r="AS251" s="36"/>
       <c r="AT251" s="11"/>
       <c r="AU251" s="11" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="AV251" s="13" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="AW251" s="14"/>
       <c r="AX251" s="44"/>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC9AB6E-78C0-41C4-8A35-25C35238350B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F5950D9-3702-45E2-9B09-89626CED3219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7208" uniqueCount="1707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7220" uniqueCount="1708">
   <si>
     <t>Contact</t>
   </si>
@@ -5175,6 +5175,9 @@
   </si>
   <si>
     <t>133 €/m² = 6 000 €</t>
+  </si>
+  <si>
+    <t>2 500 € HT</t>
   </si>
 </sst>
 </file>
@@ -9305,7 +9308,9 @@
       <c r="AM19" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN19" s="11"/>
+      <c r="AN19" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO19" s="5" t="s">
         <v>367</v>
       </c>
@@ -9465,7 +9470,9 @@
       <c r="AM20" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN20" s="11"/>
+      <c r="AN20" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO20" s="5" t="s">
         <v>367</v>
       </c>
@@ -9625,7 +9632,9 @@
       <c r="AM21" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN21" s="11"/>
+      <c r="AN21" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO21" s="5" t="s">
         <v>367</v>
       </c>
@@ -9785,7 +9794,9 @@
       <c r="AM22" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN22" s="11"/>
+      <c r="AN22" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO22" s="5" t="s">
         <v>367</v>
       </c>
@@ -9945,7 +9956,9 @@
       <c r="AM23" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN23" s="11"/>
+      <c r="AN23" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO23" s="5" t="s">
         <v>367</v>
       </c>
@@ -10105,7 +10118,9 @@
       <c r="AM24" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN24" s="11"/>
+      <c r="AN24" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO24" s="5" t="s">
         <v>367</v>
       </c>
@@ -10265,7 +10280,9 @@
       <c r="AM25" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN25" s="11"/>
+      <c r="AN25" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO25" s="5" t="s">
         <v>367</v>
       </c>
@@ -10425,7 +10442,9 @@
       <c r="AM26" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN26" s="11"/>
+      <c r="AN26" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO26" s="5" t="s">
         <v>367</v>
       </c>
@@ -10585,7 +10604,9 @@
       <c r="AM27" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN27" s="11"/>
+      <c r="AN27" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO27" s="5" t="s">
         <v>367</v>
       </c>
@@ -10745,7 +10766,9 @@
       <c r="AM28" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN28" s="11"/>
+      <c r="AN28" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO28" s="5" t="s">
         <v>367</v>
       </c>
@@ -10905,7 +10928,9 @@
       <c r="AM29" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN29" s="11"/>
+      <c r="AN29" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO29" s="5" t="s">
         <v>367</v>
       </c>
@@ -11065,7 +11090,9 @@
       <c r="AM30" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="AN30" s="11"/>
+      <c r="AN30" s="11" t="s">
+        <v>1707</v>
+      </c>
       <c r="AO30" s="5" t="s">
         <v>367</v>
       </c>
@@ -41619,7 +41646,7 @@
       <c r="E222" s="26">
         <v>48000</v>
       </c>
-      <c r="F222" s="10" t="s">
+      <c r="F222" s="42" t="s">
         <v>1546</v>
       </c>
       <c r="G222" s="39" t="str">
@@ -41769,7 +41796,7 @@
       <c r="E223" s="26">
         <v>48000</v>
       </c>
-      <c r="F223" s="10" t="s">
+      <c r="F223" s="42" t="s">
         <v>1546</v>
       </c>
       <c r="G223" s="39" t="str">
@@ -41915,7 +41942,7 @@
       <c r="E224" s="26">
         <v>94140</v>
       </c>
-      <c r="F224" s="10" t="s">
+      <c r="F224" s="42" t="s">
         <v>1579</v>
       </c>
       <c r="G224" s="39" t="str">
@@ -42060,7 +42087,7 @@
       <c r="E225" s="26">
         <v>69500</v>
       </c>
-      <c r="F225" s="10" t="s">
+      <c r="F225" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G225" s="39" t="str">
@@ -42207,7 +42234,7 @@
       <c r="E226" s="26">
         <v>69500</v>
       </c>
-      <c r="F226" s="10" t="s">
+      <c r="F226" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G226" s="39" t="str">
@@ -42354,7 +42381,7 @@
       <c r="E227" s="26">
         <v>69500</v>
       </c>
-      <c r="F227" s="10" t="s">
+      <c r="F227" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G227" s="39" t="str">
@@ -42501,7 +42528,7 @@
       <c r="E228" s="26">
         <v>69500</v>
       </c>
-      <c r="F228" s="10" t="s">
+      <c r="F228" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G228" s="39" t="str">
@@ -42648,7 +42675,7 @@
       <c r="E229" s="26">
         <v>69500</v>
       </c>
-      <c r="F229" s="10" t="s">
+      <c r="F229" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G229" s="39" t="str">
@@ -42795,7 +42822,7 @@
       <c r="E230" s="26">
         <v>69500</v>
       </c>
-      <c r="F230" s="10" t="s">
+      <c r="F230" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G230" s="39" t="str">
@@ -42942,7 +42969,7 @@
       <c r="E231" s="26">
         <v>69500</v>
       </c>
-      <c r="F231" s="10" t="s">
+      <c r="F231" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G231" s="39" t="str">
@@ -43089,7 +43116,7 @@
       <c r="E232" s="26">
         <v>69500</v>
       </c>
-      <c r="F232" s="10" t="s">
+      <c r="F232" s="42" t="s">
         <v>1581</v>
       </c>
       <c r="G232" s="39" t="str">
@@ -43236,7 +43263,7 @@
       <c r="E233" s="26">
         <v>92700</v>
       </c>
-      <c r="F233" s="10" t="s">
+      <c r="F233" s="42" t="s">
         <v>1585</v>
       </c>
       <c r="G233" s="39" t="str">
@@ -43381,7 +43408,7 @@
       <c r="E234" s="26">
         <v>37300</v>
       </c>
-      <c r="F234" s="10" t="s">
+      <c r="F234" s="42" t="s">
         <v>1586</v>
       </c>
       <c r="G234" s="39" t="str">
@@ -43526,7 +43553,7 @@
       <c r="E235" s="26">
         <v>59800</v>
       </c>
-      <c r="F235" s="10" t="s">
+      <c r="F235" s="42" t="s">
         <v>1587</v>
       </c>
       <c r="G235" s="39" t="str">
@@ -43671,7 +43698,7 @@
       <c r="E236" s="26">
         <v>59800</v>
       </c>
-      <c r="F236" s="10" t="s">
+      <c r="F236" s="42" t="s">
         <v>1588</v>
       </c>
       <c r="G236" s="39" t="str">
@@ -43818,7 +43845,7 @@
       <c r="E237" s="26">
         <v>59800</v>
       </c>
-      <c r="F237" s="10" t="s">
+      <c r="F237" s="42" t="s">
         <v>1588</v>
       </c>
       <c r="G237" s="39" t="str">
@@ -43965,7 +43992,7 @@
       <c r="E238" s="26">
         <v>59800</v>
       </c>
-      <c r="F238" s="10" t="s">
+      <c r="F238" s="42" t="s">
         <v>1588</v>
       </c>
       <c r="G238" s="39" t="str">
@@ -44112,7 +44139,7 @@
       <c r="E239" s="26">
         <v>93100</v>
       </c>
-      <c r="F239" s="10" t="s">
+      <c r="F239" s="42" t="s">
         <v>1589</v>
       </c>
       <c r="G239" s="39" t="str">
@@ -44257,7 +44284,7 @@
       <c r="E240" s="26">
         <v>93100</v>
       </c>
-      <c r="F240" s="10" t="s">
+      <c r="F240" s="42" t="s">
         <v>1589</v>
       </c>
       <c r="G240" s="39" t="str">
@@ -44402,7 +44429,7 @@
       <c r="E241" s="26">
         <v>78300</v>
       </c>
-      <c r="F241" s="10" t="s">
+      <c r="F241" s="42" t="s">
         <v>1590</v>
       </c>
       <c r="G241" s="39" t="str">
@@ -44549,7 +44576,7 @@
       <c r="E242" s="26">
         <v>78300</v>
       </c>
-      <c r="F242" s="10" t="s">
+      <c r="F242" s="42" t="s">
         <v>1590</v>
       </c>
       <c r="G242" s="39" t="str">
@@ -44696,7 +44723,7 @@
       <c r="E243" s="26">
         <v>93400</v>
       </c>
-      <c r="F243" s="10" t="s">
+      <c r="F243" s="42" t="s">
         <v>1591</v>
       </c>
       <c r="G243" s="39" t="str">
@@ -44841,7 +44868,7 @@
       <c r="E244" s="26">
         <v>94510</v>
       </c>
-      <c r="F244" s="10" t="s">
+      <c r="F244" s="42" t="s">
         <v>1592</v>
       </c>
       <c r="G244" s="39" t="str">
@@ -44986,7 +45013,7 @@
       <c r="E245" s="26">
         <v>94511</v>
       </c>
-      <c r="F245" s="10" t="s">
+      <c r="F245" s="42" t="s">
         <v>1592</v>
       </c>
       <c r="G245" s="39" t="str">
@@ -45131,7 +45158,7 @@
       <c r="E246" s="26">
         <v>94512</v>
       </c>
-      <c r="F246" s="10" t="s">
+      <c r="F246" s="42" t="s">
         <v>1592</v>
       </c>
       <c r="G246" s="39" t="str">
@@ -45276,7 +45303,7 @@
       <c r="E247" s="26">
         <v>94513</v>
       </c>
-      <c r="F247" s="10" t="s">
+      <c r="F247" s="42" t="s">
         <v>1592</v>
       </c>
       <c r="G247" s="39" t="str">
@@ -45421,7 +45448,7 @@
       <c r="E248" s="26">
         <v>69002</v>
       </c>
-      <c r="F248" s="10" t="s">
+      <c r="F248" s="42" t="s">
         <v>1593</v>
       </c>
       <c r="G248" s="39" t="str">
@@ -45566,7 +45593,7 @@
       <c r="E249" s="26">
         <v>69002</v>
       </c>
-      <c r="F249" s="10" t="s">
+      <c r="F249" s="42" t="s">
         <v>1593</v>
       </c>
       <c r="G249" s="39" t="str">
@@ -45711,7 +45738,7 @@
       <c r="E250" s="26">
         <v>69002</v>
       </c>
-      <c r="F250" s="10" t="s">
+      <c r="F250" s="42" t="s">
         <v>1593</v>
       </c>
       <c r="G250" s="39" t="str">
@@ -45856,7 +45883,7 @@
       <c r="E251" s="26">
         <v>69002</v>
       </c>
-      <c r="F251" s="10" t="s">
+      <c r="F251" s="42" t="s">
         <v>1593</v>
       </c>
       <c r="G251" s="39" t="str">

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EF7839-E65B-4B25-BEBB-570F8F4A42E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D256C18-04EE-4FA4-B2D9-B1BEEEEB747D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7432" uniqueCount="1828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7458" uniqueCount="1833">
   <si>
     <t>Contact</t>
   </si>
@@ -5539,6 +5539,21 @@
   </si>
   <si>
     <t>4.097248</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AWwG6d4P1DxPWbZ87</t>
+  </si>
+  <si>
+    <t>Boulevard de Tilsit - Carrefour ZAC du Pont des Rayons</t>
+  </si>
+  <si>
+    <t>49.127416</t>
+  </si>
+  <si>
+    <t>2.246095</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/82%20-%20L'Isle-Adam/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/82%20-%20L'Isle-Adam/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/82%20-%20L'Isle-Adam/3%20Plan.jpg</t>
   </si>
 </sst>
 </file>
@@ -6219,8 +6234,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX256" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AX256" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX257" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AX257" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="50">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="49" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -47163,7 +47178,10 @@
       <c r="W255" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="X255" s="12"/>
+      <c r="X255" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="Y255" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -47192,7 +47210,9 @@
       <c r="AH255" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AI255" s="12"/>
+      <c r="AI255" s="12" t="s">
+        <v>363</v>
+      </c>
       <c r="AJ255" s="10" t="s">
         <v>375</v>
       </c>
@@ -47252,7 +47272,7 @@
       <c r="E256" s="26">
         <v>30100</v>
       </c>
-      <c r="F256" s="10" t="s">
+      <c r="F256" s="54" t="s">
         <v>1824</v>
       </c>
       <c r="G256" s="39" t="str">
@@ -47306,7 +47326,10 @@
       <c r="W256" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="X256" s="12"/>
+      <c r="X256" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>0</v>
+      </c>
       <c r="Y256" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
         <v>0</v>
@@ -47374,12 +47397,155 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="270" spans="6:6">
+    <row r="257" spans="1:50" ht="38.25">
+      <c r="A257" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Ile-de-France</v>
+      </c>
+      <c r="B257" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Val-D'Oise</v>
+      </c>
+      <c r="C257" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>95</v>
+      </c>
+      <c r="D257" s="11" t="s">
+        <v>1829</v>
+      </c>
+      <c r="E257" s="26">
+        <v>95290</v>
+      </c>
+      <c r="F257" s="54" t="s">
+        <v>980</v>
+      </c>
+      <c r="G257" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Boulevard de Tilsit - Carrefour ZAC du Pont des Rayons
+95290 - L'Isle-Adam</v>
+      </c>
+      <c r="H257" s="15" t="s">
+        <v>1828</v>
+      </c>
+      <c r="I257" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J257" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K257" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L257" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M257" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N257" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="O257" s="34">
+        <v>760</v>
+      </c>
+      <c r="P257" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q257" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R257" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S257" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T257" s="12"/>
+      <c r="U257" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V257" s="12"/>
+      <c r="W257" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X257" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>31160</v>
+      </c>
+      <c r="Y257" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>2596.6666666666665</v>
+      </c>
+      <c r="Z257" s="12">
+        <v>41</v>
+      </c>
+      <c r="AA257" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB257" s="12"/>
+      <c r="AC257" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD257" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE257" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>31160</v>
+      </c>
+      <c r="AF257" s="12"/>
+      <c r="AG257" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH257" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI257" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ257" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK257" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL257" s="10"/>
+      <c r="AM257" s="11"/>
+      <c r="AN257" s="11"/>
+      <c r="AO257" s="11"/>
+      <c r="AP257" s="11" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AQ257" s="11" t="s">
+        <v>1831</v>
+      </c>
+      <c r="AR257" s="11">
+        <v>82</v>
+      </c>
+      <c r="AS257" s="36" t="s">
+        <v>1832</v>
+      </c>
+      <c r="AT257" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU257" s="11"/>
+      <c r="AV257" s="13" t="s">
+        <v>943</v>
+      </c>
+      <c r="AW257" s="14"/>
+      <c r="AX257" s="44">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="270" spans="1:50">
       <c r="F270" s="1" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="271" spans="6:6">
+    <row r="271" spans="1:50">
       <c r="F271" s="1" t="s">
         <v>1020</v>
       </c>
@@ -47589,6 +47755,7 @@
     <hyperlink ref="H141" r:id="rId200" xr:uid="{C5A3DF91-92D1-4C68-91E5-2339E158AAC9}"/>
     <hyperlink ref="H255" r:id="rId201" xr:uid="{D488917C-1773-46C8-AE24-C0150C67D2BC}"/>
     <hyperlink ref="H256" r:id="rId202" xr:uid="{FA4BB291-4E0D-4A6E-9E43-DF05E067866A}"/>
+    <hyperlink ref="H257" r:id="rId203" xr:uid="{8ED2A142-1C2D-4EEF-B2C9-8E7DBF014473}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -47597,7 +47764,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId203"/>
+    <tablePart r:id="rId204"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D256C18-04EE-4FA4-B2D9-B1BEEEEB747D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D40A8F0-3E41-47E9-A9F7-172647A200C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7458" uniqueCount="1833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7459" uniqueCount="1834">
   <si>
     <t>Contact</t>
   </si>
@@ -5554,6 +5554,9 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/82%20-%20L'Isle-Adam/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/82%20-%20L'Isle-Adam/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/82%20-%20L'Isle-Adam/3%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/69%20-%20Alfortville/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/69%20-%20Alfortville/2%20Plan.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/69%20-%20Alfortville/3%20Plan%20Mesure.jpg</t>
   </si>
 </sst>
 </file>
@@ -42629,7 +42632,7 @@
       </c>
       <c r="N226" s="36"/>
       <c r="O226" s="34">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>103</v>
@@ -42645,11 +42648,11 @@
       </c>
       <c r="T226" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>42000</v>
+        <v>42900</v>
       </c>
       <c r="U226" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>3500</v>
+        <v>3575</v>
       </c>
       <c r="V226" s="12">
         <v>300</v>
@@ -42659,11 +42662,11 @@
       </c>
       <c r="X226" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>2623.6</v>
+        <v>2679.8199999999997</v>
       </c>
       <c r="Y226" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>218.63333333333333</v>
+        <v>223.3183333333333</v>
       </c>
       <c r="Z226" s="12">
         <v>18.739999999999998</v>
@@ -42682,11 +42685,11 @@
       </c>
       <c r="AE226" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>44623.6</v>
+        <v>45579.82</v>
       </c>
       <c r="AF226" s="12" t="str">
         <f t="shared" ref="AF226:AF254" si="10">"3 mois = "&amp;TEXT(ROUND(3/12*T226,0),"### ### ##0 €")</f>
-        <v>3 mois = 10 500 €</v>
+        <v>3 mois = 10 725 €</v>
       </c>
       <c r="AG226" s="12" t="s">
         <v>103</v>
@@ -42720,7 +42723,9 @@
       <c r="AR226" s="11">
         <v>69</v>
       </c>
-      <c r="AS226" s="36"/>
+      <c r="AS226" s="36" t="s">
+        <v>1833</v>
+      </c>
       <c r="AT226" s="11" t="s">
         <v>75</v>
       </c>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D40A8F0-3E41-47E9-A9F7-172647A200C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA491AC-6B0E-42C2-9295-81F10A5B3E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7459" uniqueCount="1834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7487" uniqueCount="1835">
   <si>
     <t>Contact</t>
   </si>
@@ -5060,9 +5060,6 @@
     <t>3.479734</t>
   </si>
   <si>
-    <t>419 + 138</t>
-  </si>
-  <si>
     <t>Gemo, King Jouet, Sport 2000, …</t>
   </si>
   <si>
@@ -5557,6 +5554,12 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/69%20-%20Alfortville/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/69%20-%20Alfortville/2%20Plan.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/69%20-%20Alfortville/3%20Plan%20Mesure.jpg</t>
+  </si>
+  <si>
+    <t>420 + 138</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/5%20Plan.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/6%20Fa%C3%A7ade.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/7%20Plan%20RDC.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/68.1%20-%20Mende/8%20Plan%20Mezzanine.jpg</t>
   </si>
 </sst>
 </file>
@@ -9678,7 +9681,7 @@
         <v>377</v>
       </c>
       <c r="AN19" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO19" s="5" t="s">
         <v>367</v>
@@ -9839,7 +9842,7 @@
         <v>377</v>
       </c>
       <c r="AN20" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO20" s="5" t="s">
         <v>367</v>
@@ -10000,7 +10003,7 @@
         <v>377</v>
       </c>
       <c r="AN21" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO21" s="5" t="s">
         <v>367</v>
@@ -10161,7 +10164,7 @@
         <v>377</v>
       </c>
       <c r="AN22" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO22" s="5" t="s">
         <v>367</v>
@@ -10322,7 +10325,7 @@
         <v>377</v>
       </c>
       <c r="AN23" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO23" s="5" t="s">
         <v>367</v>
@@ -10483,7 +10486,7 @@
         <v>377</v>
       </c>
       <c r="AN24" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO24" s="5" t="s">
         <v>367</v>
@@ -10644,7 +10647,7 @@
         <v>377</v>
       </c>
       <c r="AN25" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO25" s="5" t="s">
         <v>367</v>
@@ -10805,7 +10808,7 @@
         <v>377</v>
       </c>
       <c r="AN26" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO26" s="5" t="s">
         <v>367</v>
@@ -10966,7 +10969,7 @@
         <v>377</v>
       </c>
       <c r="AN27" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO27" s="5" t="s">
         <v>367</v>
@@ -11127,7 +11130,7 @@
         <v>377</v>
       </c>
       <c r="AN28" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO28" s="5" t="s">
         <v>367</v>
@@ -11288,7 +11291,7 @@
         <v>377</v>
       </c>
       <c r="AN29" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO29" s="5" t="s">
         <v>367</v>
@@ -11449,7 +11452,7 @@
         <v>377</v>
       </c>
       <c r="AN30" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO30" s="5" t="s">
         <v>367</v>
@@ -23076,10 +23079,10 @@
         <v>438</v>
       </c>
       <c r="AM103" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN103" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO103" s="5" t="s">
         <v>367</v>
@@ -23239,10 +23242,10 @@
         <v>438</v>
       </c>
       <c r="AM104" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN104" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO104" s="5" t="s">
         <v>367</v>
@@ -23407,10 +23410,10 @@
         <v>438</v>
       </c>
       <c r="AM105" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN105" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO105" s="5" t="s">
         <v>367</v>
@@ -23570,10 +23573,10 @@
         <v>438</v>
       </c>
       <c r="AM106" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN106" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO106" s="5" t="s">
         <v>367</v>
@@ -23733,10 +23736,10 @@
         <v>438</v>
       </c>
       <c r="AM107" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN107" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO107" s="5" t="s">
         <v>367</v>
@@ -23896,10 +23899,10 @@
         <v>438</v>
       </c>
       <c r="AM108" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN108" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO108" s="5" t="s">
         <v>367</v>
@@ -24059,10 +24062,10 @@
         <v>438</v>
       </c>
       <c r="AM109" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN109" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO109" s="5" t="s">
         <v>367</v>
@@ -24222,10 +24225,10 @@
         <v>438</v>
       </c>
       <c r="AM110" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN110" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO110" s="5" t="s">
         <v>367</v>
@@ -24385,10 +24388,10 @@
         <v>438</v>
       </c>
       <c r="AM111" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN111" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO111" s="5" t="s">
         <v>367</v>
@@ -24548,10 +24551,10 @@
         <v>438</v>
       </c>
       <c r="AM112" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN112" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO112" s="5" t="s">
         <v>367</v>
@@ -24712,10 +24715,10 @@
         <v>438</v>
       </c>
       <c r="AM113" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN113" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO113" s="5" t="s">
         <v>367</v>
@@ -24876,10 +24879,10 @@
         <v>438</v>
       </c>
       <c r="AM114" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN114" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO114" s="5" t="s">
         <v>367</v>
@@ -25040,10 +25043,10 @@
         <v>438</v>
       </c>
       <c r="AM115" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN115" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO115" s="5" t="s">
         <v>367</v>
@@ -25204,10 +25207,10 @@
         <v>438</v>
       </c>
       <c r="AM116" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN116" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AO116" s="5" t="s">
         <v>367</v>
@@ -25919,7 +25922,9 @@
       <c r="K121" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L121" s="12"/>
+      <c r="L121" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M121" s="12" t="s">
         <v>103</v>
       </c>
@@ -26080,7 +26085,9 @@
       <c r="K122" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L122" s="12"/>
+      <c r="L122" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M122" s="12" t="s">
         <v>103</v>
       </c>
@@ -26241,7 +26248,9 @@
       <c r="K123" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L123" s="12"/>
+      <c r="L123" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M123" s="12" t="s">
         <v>103</v>
       </c>
@@ -26402,7 +26411,9 @@
       <c r="K124" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L124" s="12"/>
+      <c r="L124" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M124" s="12" t="s">
         <v>103</v>
       </c>
@@ -26563,7 +26574,9 @@
       <c r="K125" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L125" s="12"/>
+      <c r="L125" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M125" s="12" t="s">
         <v>103</v>
       </c>
@@ -26724,7 +26737,9 @@
       <c r="K126" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L126" s="12"/>
+      <c r="L126" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M126" s="12" t="s">
         <v>103</v>
       </c>
@@ -26884,7 +26899,9 @@
       <c r="K127" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L127" s="12"/>
+      <c r="L127" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M127" s="12" t="s">
         <v>103</v>
       </c>
@@ -27044,7 +27061,9 @@
       <c r="K128" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L128" s="12"/>
+      <c r="L128" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M128" s="12" t="s">
         <v>103</v>
       </c>
@@ -27204,7 +27223,9 @@
       <c r="K129" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L129" s="12"/>
+      <c r="L129" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M129" s="12" t="s">
         <v>103</v>
       </c>
@@ -27364,7 +27385,9 @@
       <c r="K130" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L130" s="12"/>
+      <c r="L130" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M130" s="12" t="s">
         <v>103</v>
       </c>
@@ -27524,7 +27547,9 @@
       <c r="K131" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L131" s="12"/>
+      <c r="L131" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M131" s="12" t="s">
         <v>103</v>
       </c>
@@ -27684,7 +27709,9 @@
       <c r="K132" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L132" s="12"/>
+      <c r="L132" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M132" s="12" t="s">
         <v>103</v>
       </c>
@@ -27844,7 +27871,9 @@
       <c r="K133" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L133" s="12"/>
+      <c r="L133" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M133" s="12" t="s">
         <v>103</v>
       </c>
@@ -28004,7 +28033,9 @@
       <c r="K134" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L134" s="12"/>
+      <c r="L134" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M134" s="12" t="s">
         <v>103</v>
       </c>
@@ -28164,7 +28195,9 @@
       <c r="K135" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L135" s="12"/>
+      <c r="L135" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M135" s="12" t="s">
         <v>103</v>
       </c>
@@ -28324,7 +28357,9 @@
       <c r="K136" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L136" s="12"/>
+      <c r="L136" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M136" s="12" t="s">
         <v>103</v>
       </c>
@@ -28484,7 +28519,9 @@
       <c r="K137" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L137" s="12"/>
+      <c r="L137" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M137" s="12" t="s">
         <v>103</v>
       </c>
@@ -28644,7 +28681,9 @@
       <c r="K138" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L138" s="12"/>
+      <c r="L138" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M138" s="12" t="s">
         <v>103</v>
       </c>
@@ -28739,10 +28778,10 @@
         <v>367</v>
       </c>
       <c r="AP138" s="11" t="s">
+        <v>1803</v>
+      </c>
+      <c r="AQ138" s="11" t="s">
         <v>1804</v>
-      </c>
-      <c r="AQ138" s="11" t="s">
-        <v>1805</v>
       </c>
       <c r="AR138" s="11" t="s">
         <v>1377</v>
@@ -28804,7 +28843,9 @@
       <c r="K139" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L139" s="12"/>
+      <c r="L139" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M139" s="12" t="s">
         <v>103</v>
       </c>
@@ -28899,10 +28940,10 @@
         <v>367</v>
       </c>
       <c r="AP139" s="11" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AQ139" s="11" t="s">
         <v>1806</v>
-      </c>
-      <c r="AQ139" s="11" t="s">
-        <v>1807</v>
       </c>
       <c r="AR139" s="11" t="s">
         <v>1378</v>
@@ -28964,12 +29005,14 @@
       <c r="K140" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L140" s="12"/>
+      <c r="L140" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M140" s="12" t="s">
         <v>103</v>
       </c>
       <c r="N140" s="36" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="O140" s="34">
         <v>55</v>
@@ -29059,16 +29102,16 @@
         <v>367</v>
       </c>
       <c r="AP140" s="11" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AQ140" s="11" t="s">
         <v>1808</v>
       </c>
-      <c r="AQ140" s="11" t="s">
-        <v>1809</v>
-      </c>
       <c r="AR140" s="11" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="AS140" s="36" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="AT140" s="11" t="s">
         <v>75</v>
@@ -29124,12 +29167,14 @@
       <c r="K141" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L141" s="12"/>
+      <c r="L141" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M141" s="12" t="s">
         <v>103</v>
       </c>
       <c r="N141" s="36" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="O141" s="34">
         <v>61</v>
@@ -29219,16 +29264,16 @@
         <v>367</v>
       </c>
       <c r="AP141" s="11" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AQ141" s="11" t="s">
         <v>1810</v>
       </c>
-      <c r="AQ141" s="11" t="s">
+      <c r="AR141" s="11" t="s">
+        <v>1802</v>
+      </c>
+      <c r="AS141" s="36" t="s">
         <v>1811</v>
-      </c>
-      <c r="AR141" s="11" t="s">
-        <v>1803</v>
-      </c>
-      <c r="AS141" s="36" t="s">
-        <v>1812</v>
       </c>
       <c r="AT141" s="11" t="s">
         <v>75</v>
@@ -29284,7 +29329,9 @@
       <c r="K142" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L142" s="12"/>
+      <c r="L142" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M142" s="12" t="s">
         <v>103</v>
       </c>
@@ -29442,7 +29489,9 @@
       <c r="K143" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L143" s="12"/>
+      <c r="L143" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M143" s="12" t="s">
         <v>103</v>
       </c>
@@ -29600,7 +29649,9 @@
       <c r="K144" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L144" s="12"/>
+      <c r="L144" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M144" s="12" t="s">
         <v>103</v>
       </c>
@@ -29758,7 +29809,9 @@
       <c r="K145" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L145" s="12"/>
+      <c r="L145" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M145" s="12" t="s">
         <v>103</v>
       </c>
@@ -29916,7 +29969,9 @@
       <c r="K146" s="12" t="s">
         <v>1405</v>
       </c>
-      <c r="L146" s="12"/>
+      <c r="L146" s="53" t="s">
+        <v>1546</v>
+      </c>
       <c r="M146" s="12" t="s">
         <v>1178</v>
       </c>
@@ -32904,7 +32959,7 @@
         <v>1274</v>
       </c>
       <c r="AM164" s="11" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="AN164" s="11" t="s">
         <v>1398</v>
@@ -33068,7 +33123,7 @@
         <v>1274</v>
       </c>
       <c r="AM165" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="AN165" s="11" t="s">
         <v>1398</v>
@@ -33230,7 +33285,7 @@
         <v>1274</v>
       </c>
       <c r="AM166" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="AN166" s="11" t="s">
         <v>1398</v>
@@ -33392,7 +33447,7 @@
         <v>1274</v>
       </c>
       <c r="AM167" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="AN167" s="11" t="s">
         <v>1398</v>
@@ -33554,7 +33609,7 @@
         <v>1274</v>
       </c>
       <c r="AM168" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="AN168" s="11" t="s">
         <v>1398</v>
@@ -33716,7 +33771,7 @@
         <v>1274</v>
       </c>
       <c r="AM169" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="AN169" s="11" t="s">
         <v>1398</v>
@@ -41553,7 +41608,7 @@
         <v>75</v>
       </c>
       <c r="AU218" s="11" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="AV218" s="13" t="s">
         <v>1035</v>
@@ -41701,7 +41756,7 @@
         <v>75</v>
       </c>
       <c r="AU219" s="11" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="AV219" s="13" t="s">
         <v>1035</v>
@@ -41847,7 +41902,7 @@
         <v>75</v>
       </c>
       <c r="AU220" s="11" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="AV220" s="13" t="s">
         <v>1035</v>
@@ -41981,7 +42036,7 @@
         <v>75</v>
       </c>
       <c r="AU221" s="11" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="AV221" s="13" t="s">
         <v>1035</v>
@@ -42122,7 +42177,7 @@
         <v>75</v>
       </c>
       <c r="AU222" s="11" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="AV222" s="13" t="s">
         <v>1035</v>
@@ -42180,10 +42235,10 @@
         <v>358</v>
       </c>
       <c r="O223" s="34">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P223" s="12" t="s">
-        <v>1668</v>
+        <v>1833</v>
       </c>
       <c r="Q223" s="34"/>
       <c r="R223" s="34" t="s">
@@ -42194,11 +42249,11 @@
       </c>
       <c r="T223" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>83550</v>
+        <v>83700</v>
       </c>
       <c r="U223" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>6962.5</v>
+        <v>6975</v>
       </c>
       <c r="V223" s="12">
         <v>150</v>
@@ -42208,18 +42263,18 @@
       </c>
       <c r="X223" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>8355</v>
+        <v>14508</v>
       </c>
       <c r="Y223" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>696.25</v>
+        <v>1209</v>
       </c>
       <c r="Z223" s="12">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AA223" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>7519.5</v>
+        <v>7533</v>
       </c>
       <c r="AB223" s="12">
         <v>13.5</v>
@@ -42233,7 +42288,7 @@
       </c>
       <c r="AE223" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>99424.5</v>
+        <v>105741</v>
       </c>
       <c r="AF223" s="12"/>
       <c r="AG223" s="6" t="s">
@@ -42252,10 +42307,10 @@
         <v>369</v>
       </c>
       <c r="AL223" s="10" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="AM223" s="11" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AN223" s="11" t="s">
         <v>103</v>
@@ -42273,13 +42328,13 @@
         <v>1608</v>
       </c>
       <c r="AS223" s="36" t="s">
-        <v>1673</v>
+        <v>1834</v>
       </c>
       <c r="AT223" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU223" s="11" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="AV223" s="13" t="s">
         <v>1612</v>
@@ -42340,7 +42395,7 @@
         <v>380</v>
       </c>
       <c r="P224" s="12" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="Q224" s="34"/>
       <c r="R224" s="34" t="s">
@@ -42363,17 +42418,24 @@
       <c r="W224" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="X224" s="12"/>
+      <c r="X224" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>9880</v>
+      </c>
       <c r="Y224" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z224" s="12"/>
+        <v>823.33333333333337</v>
+      </c>
+      <c r="Z224" s="12">
+        <v>26</v>
+      </c>
       <c r="AA224" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB224" s="12"/>
+        <v>5320</v>
+      </c>
+      <c r="AB224" s="12">
+        <v>14</v>
+      </c>
       <c r="AC224" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -42383,7 +42445,7 @@
       </c>
       <c r="AE224" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>66500</v>
+        <v>81700</v>
       </c>
       <c r="AF224" s="12"/>
       <c r="AG224" s="6" t="s">
@@ -42402,10 +42464,10 @@
         <v>369</v>
       </c>
       <c r="AL224" s="10" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="AM224" s="11" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="AN224" s="11" t="s">
         <v>103</v>
@@ -42423,13 +42485,13 @@
         <v>1609</v>
       </c>
       <c r="AS224" s="36" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="AT224" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU224" s="11" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="AV224" s="13" t="s">
         <v>1612</v>
@@ -42487,12 +42549,16 @@
       <c r="O225" s="34">
         <v>45</v>
       </c>
-      <c r="P225" s="12"/>
-      <c r="Q225" s="34"/>
+      <c r="P225" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q225" s="34" t="s">
+        <v>103</v>
+      </c>
       <c r="R225" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="S225" s="34" t="s">
+      <c r="S225" s="6" t="s">
         <v>103</v>
       </c>
       <c r="T225" s="12">
@@ -42509,17 +42575,24 @@
       <c r="W225" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="X225" s="12"/>
+      <c r="X225" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1170</v>
+      </c>
       <c r="Y225" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z225" s="12"/>
+        <v>97.5</v>
+      </c>
+      <c r="Z225" s="12">
+        <v>26</v>
+      </c>
       <c r="AA225" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB225" s="12"/>
+        <v>630</v>
+      </c>
+      <c r="AB225" s="12">
+        <v>14</v>
+      </c>
       <c r="AC225" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -42529,7 +42602,7 @@
       </c>
       <c r="AE225" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>22500</v>
+        <v>24300</v>
       </c>
       <c r="AF225" s="12"/>
       <c r="AG225" s="6" t="s">
@@ -42548,10 +42621,10 @@
         <v>368</v>
       </c>
       <c r="AL225" s="10" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AM225" s="11" t="s">
         <v>1669</v>
-      </c>
-      <c r="AM225" s="11" t="s">
-        <v>1670</v>
       </c>
       <c r="AN225" s="11" t="s">
         <v>103</v>
@@ -42569,13 +42642,13 @@
         <v>1611</v>
       </c>
       <c r="AS225" s="36" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="AT225" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU225" s="11" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AV225" s="13" t="s">
         <v>1612</v>
@@ -42613,7 +42686,7 @@
 94140 - Alfortville</v>
       </c>
       <c r="H226" s="15" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="I226" s="12" t="s">
         <v>45</v>
@@ -42715,16 +42788,16 @@
         <v>367</v>
       </c>
       <c r="AP226" s="11" t="s">
+        <v>1792</v>
+      </c>
+      <c r="AQ226" s="11" t="s">
         <v>1793</v>
-      </c>
-      <c r="AQ226" s="11" t="s">
-        <v>1794</v>
       </c>
       <c r="AR226" s="11">
         <v>69</v>
       </c>
       <c r="AS226" s="36" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="AT226" s="11" t="s">
         <v>75</v>
@@ -42768,7 +42841,7 @@
 69500 - Bron</v>
       </c>
       <c r="H227" s="15" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="I227" s="12" t="s">
         <v>45</v>
@@ -42872,16 +42945,16 @@
         <v>367</v>
       </c>
       <c r="AP227" s="11" t="s">
+        <v>1763</v>
+      </c>
+      <c r="AQ227" s="11" t="s">
         <v>1764</v>
-      </c>
-      <c r="AQ227" s="11" t="s">
-        <v>1765</v>
       </c>
       <c r="AR227" s="11" t="s">
         <v>1640</v>
       </c>
       <c r="AS227" s="36" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="AT227" s="11" t="s">
         <v>75</v>
@@ -42925,7 +42998,7 @@
 69500 - Bron</v>
       </c>
       <c r="H228" s="15" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="I228" s="12" t="s">
         <v>45</v>
@@ -43029,16 +43102,16 @@
         <v>367</v>
       </c>
       <c r="AP228" s="11" t="s">
+        <v>1765</v>
+      </c>
+      <c r="AQ228" s="11" t="s">
         <v>1766</v>
-      </c>
-      <c r="AQ228" s="11" t="s">
-        <v>1767</v>
       </c>
       <c r="AR228" s="11" t="s">
         <v>1641</v>
       </c>
       <c r="AS228" s="36" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="AT228" s="11" t="s">
         <v>75</v>
@@ -43082,7 +43155,7 @@
 69500 - Bron</v>
       </c>
       <c r="H229" s="15" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="I229" s="12" t="s">
         <v>45</v>
@@ -43186,16 +43259,16 @@
         <v>367</v>
       </c>
       <c r="AP229" s="11" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AQ229" s="11" t="s">
         <v>1768</v>
-      </c>
-      <c r="AQ229" s="11" t="s">
-        <v>1769</v>
       </c>
       <c r="AR229" s="11" t="s">
         <v>1642</v>
       </c>
       <c r="AS229" s="36" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="AT229" s="11" t="s">
         <v>75</v>
@@ -43239,7 +43312,7 @@
 69500 - Bron</v>
       </c>
       <c r="H230" s="15" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="I230" s="12" t="s">
         <v>45</v>
@@ -43343,16 +43416,16 @@
         <v>367</v>
       </c>
       <c r="AP230" s="11" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AQ230" s="11" t="s">
         <v>1770</v>
-      </c>
-      <c r="AQ230" s="11" t="s">
-        <v>1771</v>
       </c>
       <c r="AR230" s="11" t="s">
         <v>1643</v>
       </c>
       <c r="AS230" s="36" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="AT230" s="11" t="s">
         <v>75</v>
@@ -43396,7 +43469,7 @@
 69500 - Bron</v>
       </c>
       <c r="H231" s="15" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="I231" s="12" t="s">
         <v>45</v>
@@ -43500,22 +43573,22 @@
         <v>367</v>
       </c>
       <c r="AP231" s="11" t="s">
+        <v>1771</v>
+      </c>
+      <c r="AQ231" s="11" t="s">
         <v>1772</v>
-      </c>
-      <c r="AQ231" s="11" t="s">
-        <v>1773</v>
       </c>
       <c r="AR231" s="11" t="s">
         <v>1644</v>
       </c>
       <c r="AS231" s="36" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="AT231" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU231" s="11" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="AV231" s="13" t="s">
         <v>1613</v>
@@ -43553,7 +43626,7 @@
 69500 - Bron</v>
       </c>
       <c r="H232" s="15" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="I232" s="12" t="s">
         <v>45</v>
@@ -43657,22 +43730,22 @@
         <v>367</v>
       </c>
       <c r="AP232" s="11" t="s">
+        <v>1773</v>
+      </c>
+      <c r="AQ232" s="11" t="s">
         <v>1774</v>
-      </c>
-      <c r="AQ232" s="11" t="s">
-        <v>1775</v>
       </c>
       <c r="AR232" s="11" t="s">
         <v>1645</v>
       </c>
       <c r="AS232" s="36" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="AT232" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU232" s="11" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="AV232" s="13" t="s">
         <v>1613</v>
@@ -43710,7 +43783,7 @@
 69500 - Bron</v>
       </c>
       <c r="H233" s="15" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="I233" s="12" t="s">
         <v>45</v>
@@ -43814,16 +43887,16 @@
         <v>367</v>
       </c>
       <c r="AP233" s="11" t="s">
+        <v>1779</v>
+      </c>
+      <c r="AQ233" s="11" t="s">
         <v>1780</v>
-      </c>
-      <c r="AQ233" s="11" t="s">
-        <v>1781</v>
       </c>
       <c r="AR233" s="11" t="s">
         <v>1646</v>
       </c>
       <c r="AS233" s="36" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="AT233" s="11" t="s">
         <v>75</v>
@@ -43867,7 +43940,7 @@
 69501 - Bron</v>
       </c>
       <c r="H234" s="15" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="I234" s="12" t="s">
         <v>45</v>
@@ -43885,7 +43958,7 @@
         <v>103</v>
       </c>
       <c r="N234" s="36" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="O234" s="34">
         <v>93</v>
@@ -43963,28 +44036,28 @@
       <c r="AL234" s="10"/>
       <c r="AM234" s="11"/>
       <c r="AN234" s="11" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="AO234" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP234" s="11" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AQ234" s="11" t="s">
         <v>1782</v>
-      </c>
-      <c r="AQ234" s="11" t="s">
-        <v>1783</v>
       </c>
       <c r="AR234" s="11" t="s">
         <v>1647</v>
       </c>
       <c r="AS234" s="36" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="AT234" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU234" s="11" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="AV234" s="13" t="s">
         <v>1613</v>
@@ -44022,7 +44095,7 @@
 69500 - Bron</v>
       </c>
       <c r="H235" s="15" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="I235" s="12" t="s">
         <v>45</v>
@@ -44126,16 +44199,16 @@
         <v>367</v>
       </c>
       <c r="AP235" s="11" t="s">
+        <v>1783</v>
+      </c>
+      <c r="AQ235" s="11" t="s">
         <v>1784</v>
       </c>
-      <c r="AQ235" s="11" t="s">
-        <v>1785</v>
-      </c>
       <c r="AR235" s="11" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="AS235" s="36" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="AT235" s="11" t="s">
         <v>75</v>
@@ -44165,7 +44238,7 @@
         <v>92</v>
       </c>
       <c r="D236" s="10" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E236" s="26">
         <v>92700</v>
@@ -44179,7 +44252,7 @@
 92700 - Colombes</v>
       </c>
       <c r="H236" s="15" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="I236" s="12" t="s">
         <v>45</v>
@@ -44281,16 +44354,16 @@
         <v>367</v>
       </c>
       <c r="AP236" s="11" t="s">
+        <v>1695</v>
+      </c>
+      <c r="AQ236" s="11" t="s">
         <v>1696</v>
-      </c>
-      <c r="AQ236" s="11" t="s">
-        <v>1697</v>
       </c>
       <c r="AR236" s="11">
         <v>71</v>
       </c>
       <c r="AS236" s="36" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="AT236" s="11" t="s">
         <v>75</v>
@@ -44320,7 +44393,7 @@
         <v>37</v>
       </c>
       <c r="D237" s="10" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E237" s="26">
         <v>37300</v>
@@ -44334,7 +44407,7 @@
 37300 - Joué les Tours</v>
       </c>
       <c r="H237" s="15" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="I237" s="12" t="s">
         <v>45</v>
@@ -44436,10 +44509,10 @@
         <v>367</v>
       </c>
       <c r="AP237" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="AQ237" s="11" t="s">
         <v>1795</v>
-      </c>
-      <c r="AQ237" s="11" t="s">
-        <v>1796</v>
       </c>
       <c r="AR237" s="11">
         <v>72</v>
@@ -44473,7 +44546,7 @@
         <v>59</v>
       </c>
       <c r="D238" s="10" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E238" s="26">
         <v>59800</v>
@@ -44487,7 +44560,7 @@
 59800 - Lille Fives</v>
       </c>
       <c r="H238" s="15" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="I238" s="12" t="s">
         <v>45</v>
@@ -44591,16 +44664,16 @@
         <v>367</v>
       </c>
       <c r="AP238" s="11" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="AQ238" s="11" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="AR238" s="11">
         <v>73</v>
       </c>
       <c r="AS238" s="36" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="AT238" s="11" t="s">
         <v>75</v>
@@ -44748,16 +44821,16 @@
         <v>367</v>
       </c>
       <c r="AP239" s="11" t="s">
+        <v>1702</v>
+      </c>
+      <c r="AQ239" s="11" t="s">
         <v>1703</v>
-      </c>
-      <c r="AQ239" s="11" t="s">
-        <v>1704</v>
       </c>
       <c r="AR239" s="11" t="s">
         <v>1648</v>
       </c>
       <c r="AS239" s="36" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="AT239" s="11" t="s">
         <v>75</v>
@@ -44905,16 +44978,16 @@
         <v>367</v>
       </c>
       <c r="AP240" s="11" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="AQ240" s="11" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="AR240" s="11" t="s">
         <v>1649</v>
       </c>
       <c r="AS240" s="36" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="AT240" s="11" t="s">
         <v>75</v>
@@ -45062,16 +45135,16 @@
         <v>367</v>
       </c>
       <c r="AP241" s="11" t="s">
+        <v>1705</v>
+      </c>
+      <c r="AQ241" s="11" t="s">
         <v>1706</v>
-      </c>
-      <c r="AQ241" s="11" t="s">
-        <v>1707</v>
       </c>
       <c r="AR241" s="11" t="s">
         <v>1650</v>
       </c>
       <c r="AS241" s="36" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AT241" s="11" t="s">
         <v>75</v>
@@ -45115,7 +45188,7 @@
 93100 - Montreuil</v>
       </c>
       <c r="H242" s="15" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="I242" s="12" t="s">
         <v>45</v>
@@ -45217,16 +45290,16 @@
         <v>367</v>
       </c>
       <c r="AP242" s="11" t="s">
+        <v>1713</v>
+      </c>
+      <c r="AQ242" s="11" t="s">
         <v>1714</v>
-      </c>
-      <c r="AQ242" s="11" t="s">
-        <v>1715</v>
       </c>
       <c r="AR242" s="11" t="s">
         <v>1651</v>
       </c>
       <c r="AS242" s="36" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="AT242" s="11" t="s">
         <v>75</v>
@@ -45270,7 +45343,7 @@
 93100 - Montreuil</v>
       </c>
       <c r="H243" s="15" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="I243" s="12" t="s">
         <v>45</v>
@@ -45372,16 +45445,16 @@
         <v>367</v>
       </c>
       <c r="AP243" s="11" t="s">
+        <v>1715</v>
+      </c>
+      <c r="AQ243" s="11" t="s">
         <v>1716</v>
-      </c>
-      <c r="AQ243" s="11" t="s">
-        <v>1717</v>
       </c>
       <c r="AR243" s="11" t="s">
         <v>1652</v>
       </c>
       <c r="AS243" s="36" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="AT243" s="11" t="s">
         <v>75</v>
@@ -45425,7 +45498,7 @@
 78300 - Poissy</v>
       </c>
       <c r="H244" s="15" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="I244" s="12" t="s">
         <v>45</v>
@@ -45529,16 +45602,16 @@
         <v>367</v>
       </c>
       <c r="AP244" s="11" t="s">
+        <v>1720</v>
+      </c>
+      <c r="AQ244" s="11" t="s">
         <v>1721</v>
-      </c>
-      <c r="AQ244" s="11" t="s">
-        <v>1722</v>
       </c>
       <c r="AR244" s="11" t="s">
         <v>1653</v>
       </c>
       <c r="AS244" s="36" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="AT244" s="11" t="s">
         <v>75</v>
@@ -45568,7 +45641,7 @@
         <v>78</v>
       </c>
       <c r="D245" s="10" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E245" s="26">
         <v>78300</v>
@@ -45582,7 +45655,7 @@
 78300 - Poissy</v>
       </c>
       <c r="H245" s="15" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="I245" s="12" t="s">
         <v>45</v>
@@ -45686,16 +45759,16 @@
         <v>367</v>
       </c>
       <c r="AP245" s="11" t="s">
+        <v>1722</v>
+      </c>
+      <c r="AQ245" s="11" t="s">
         <v>1723</v>
-      </c>
-      <c r="AQ245" s="11" t="s">
-        <v>1724</v>
       </c>
       <c r="AR245" s="11" t="s">
         <v>1654</v>
       </c>
       <c r="AS245" s="36" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="AT245" s="11" t="s">
         <v>75</v>
@@ -45739,7 +45812,7 @@
 93400 - Saint-Ouen</v>
       </c>
       <c r="H246" s="15" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="I246" s="12" t="s">
         <v>45</v>
@@ -45763,7 +45836,7 @@
         <v>142</v>
       </c>
       <c r="P246" s="6" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="Q246" s="34" t="s">
         <v>103</v>
@@ -45841,16 +45914,16 @@
         <v>367</v>
       </c>
       <c r="AP246" s="11" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="AQ246" s="11" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="AR246" s="11">
         <v>77</v>
       </c>
       <c r="AS246" s="36" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="AT246" s="11" t="s">
         <v>75</v>
@@ -45894,7 +45967,7 @@
 94513 - La Queue en Brie</v>
       </c>
       <c r="H247" s="15" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="I247" s="12" t="s">
         <v>45</v>
@@ -45996,16 +46069,16 @@
         <v>367</v>
       </c>
       <c r="AP247" s="11" t="s">
+        <v>1736</v>
+      </c>
+      <c r="AQ247" s="11" t="s">
         <v>1737</v>
-      </c>
-      <c r="AQ247" s="11" t="s">
-        <v>1738</v>
       </c>
       <c r="AR247" s="11" t="s">
         <v>1655</v>
       </c>
       <c r="AS247" s="36" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="AT247" s="11" t="s">
         <v>75</v>
@@ -46049,7 +46122,7 @@
 94512 - La Queue en Brie</v>
       </c>
       <c r="H248" s="15" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="I248" s="12" t="s">
         <v>45</v>
@@ -46151,16 +46224,16 @@
         <v>367</v>
       </c>
       <c r="AP248" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="AQ248" s="11" t="s">
         <v>1739</v>
-      </c>
-      <c r="AQ248" s="11" t="s">
-        <v>1740</v>
       </c>
       <c r="AR248" s="11" t="s">
         <v>1610</v>
       </c>
       <c r="AS248" s="36" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="AT248" s="11" t="s">
         <v>75</v>
@@ -46204,7 +46277,7 @@
 94511 - La Queue en Brie</v>
       </c>
       <c r="H249" s="15" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="I249" s="12" t="s">
         <v>45</v>
@@ -46306,16 +46379,16 @@
         <v>367</v>
       </c>
       <c r="AP249" s="11" t="s">
+        <v>1740</v>
+      </c>
+      <c r="AQ249" s="11" t="s">
         <v>1741</v>
-      </c>
-      <c r="AQ249" s="11" t="s">
-        <v>1742</v>
       </c>
       <c r="AR249" s="11" t="s">
         <v>1656</v>
       </c>
       <c r="AS249" s="36" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="AT249" s="11" t="s">
         <v>75</v>
@@ -46359,7 +46432,7 @@
 94510 - La Queue en Brie</v>
       </c>
       <c r="H250" s="15" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="I250" s="12" t="s">
         <v>45</v>
@@ -46461,16 +46534,16 @@
         <v>367</v>
       </c>
       <c r="AP250" s="11" t="s">
+        <v>1742</v>
+      </c>
+      <c r="AQ250" s="11" t="s">
         <v>1743</v>
-      </c>
-      <c r="AQ250" s="11" t="s">
-        <v>1744</v>
       </c>
       <c r="AR250" s="11" t="s">
         <v>1657</v>
       </c>
       <c r="AS250" s="36" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="AT250" s="11" t="s">
         <v>75</v>
@@ -46514,7 +46587,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H251" s="15" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="I251" s="12" t="s">
         <v>45</v>
@@ -46538,7 +46611,7 @@
         <v>248</v>
       </c>
       <c r="P251" s="6" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="Q251" s="34">
         <v>512</v>
@@ -46547,7 +46620,7 @@
         <v>240</v>
       </c>
       <c r="S251" s="6" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="T251" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
@@ -46616,16 +46689,16 @@
         <v>367</v>
       </c>
       <c r="AP251" s="11" t="s">
+        <v>1755</v>
+      </c>
+      <c r="AQ251" s="11" t="s">
         <v>1756</v>
-      </c>
-      <c r="AQ251" s="11" t="s">
-        <v>1757</v>
       </c>
       <c r="AR251" s="11" t="s">
         <v>1658</v>
       </c>
       <c r="AS251" s="36" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="AT251" s="11" t="s">
         <v>75</v>
@@ -46669,7 +46742,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H252" s="15" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="I252" s="12" t="s">
         <v>45</v>
@@ -46693,7 +46766,7 @@
         <v>264</v>
       </c>
       <c r="P252" s="6" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="Q252" s="34">
         <v>512</v>
@@ -46702,7 +46775,7 @@
         <v>252</v>
       </c>
       <c r="S252" s="6" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="T252" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
@@ -46771,16 +46844,16 @@
         <v>367</v>
       </c>
       <c r="AP252" s="11" t="s">
+        <v>1757</v>
+      </c>
+      <c r="AQ252" s="11" t="s">
         <v>1758</v>
-      </c>
-      <c r="AQ252" s="11" t="s">
-        <v>1759</v>
       </c>
       <c r="AR252" s="11" t="s">
         <v>1659</v>
       </c>
       <c r="AS252" s="36" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="AT252" s="11" t="s">
         <v>75</v>
@@ -46824,7 +46897,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H253" s="15" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="I253" s="12" t="s">
         <v>45</v>
@@ -46926,16 +46999,16 @@
         <v>367</v>
       </c>
       <c r="AP253" s="11" t="s">
+        <v>1759</v>
+      </c>
+      <c r="AQ253" s="11" t="s">
         <v>1760</v>
-      </c>
-      <c r="AQ253" s="11" t="s">
-        <v>1761</v>
       </c>
       <c r="AR253" s="11" t="s">
         <v>1660</v>
       </c>
       <c r="AS253" s="36" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="AT253" s="11" t="s">
         <v>75</v>
@@ -46979,7 +47052,7 @@
 69002 - Lyon Confluence</v>
       </c>
       <c r="H254" s="15" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="I254" s="12" t="s">
         <v>45</v>
@@ -47003,7 +47076,7 @@
         <v>239</v>
       </c>
       <c r="P254" s="6" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="Q254" s="34" t="s">
         <v>103</v>
@@ -47012,7 +47085,7 @@
         <v>235</v>
       </c>
       <c r="S254" s="6" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="T254" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
@@ -47081,16 +47154,16 @@
         <v>367</v>
       </c>
       <c r="AP254" s="11" t="s">
+        <v>1761</v>
+      </c>
+      <c r="AQ254" s="11" t="s">
         <v>1762</v>
-      </c>
-      <c r="AQ254" s="11" t="s">
-        <v>1763</v>
       </c>
       <c r="AR254" s="11" t="s">
         <v>1661</v>
       </c>
       <c r="AS254" s="36" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="AT254" s="11" t="s">
         <v>75</v>
@@ -47120,13 +47193,13 @@
         <v>30</v>
       </c>
       <c r="D255" s="10" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E255" s="26">
         <v>30130</v>
       </c>
       <c r="F255" s="10" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="G255" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -47134,7 +47207,7 @@
 30130 - Pont-Saint-Esprit</v>
       </c>
       <c r="H255" s="15" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="I255" s="12" t="s">
         <v>47</v>
@@ -47226,32 +47299,32 @@
       </c>
       <c r="AL255" s="10"/>
       <c r="AM255" s="11" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="AN255" s="11"/>
       <c r="AO255" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP255" s="11" t="s">
+        <v>1817</v>
+      </c>
+      <c r="AQ255" s="11" t="s">
         <v>1818</v>
-      </c>
-      <c r="AQ255" s="11" t="s">
-        <v>1819</v>
       </c>
       <c r="AR255" s="11">
         <v>80</v>
       </c>
       <c r="AS255" s="36" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="AT255" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU255" s="11" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="AV255" s="13" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="AW255" s="14"/>
       <c r="AX255" s="44">
@@ -47272,13 +47345,13 @@
         <v>30</v>
       </c>
       <c r="D256" s="11" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="E256" s="26">
         <v>30100</v>
       </c>
       <c r="F256" s="54" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="G256" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -47287,7 +47360,7 @@
 30100 - Alès</v>
       </c>
       <c r="H256" s="15" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="I256" s="12" t="s">
         <v>47</v>
@@ -47379,23 +47452,23 @@
         <v>367</v>
       </c>
       <c r="AP256" s="11" t="s">
+        <v>1825</v>
+      </c>
+      <c r="AQ256" s="11" t="s">
         <v>1826</v>
-      </c>
-      <c r="AQ256" s="11" t="s">
-        <v>1827</v>
       </c>
       <c r="AR256" s="11">
         <v>81</v>
       </c>
       <c r="AS256" s="36" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="AT256" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU256" s="11"/>
       <c r="AV256" s="13" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="AW256" s="14"/>
       <c r="AX256" s="44">
@@ -47416,7 +47489,7 @@
         <v>95</v>
       </c>
       <c r="D257" s="11" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E257" s="26">
         <v>95290</v>
@@ -47430,7 +47503,7 @@
 95290 - L'Isle-Adam</v>
       </c>
       <c r="H257" s="15" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="I257" s="12" t="s">
         <v>47</v>
@@ -47522,16 +47595,16 @@
       <c r="AN257" s="11"/>
       <c r="AO257" s="11"/>
       <c r="AP257" s="11" t="s">
+        <v>1829</v>
+      </c>
+      <c r="AQ257" s="11" t="s">
         <v>1830</v>
-      </c>
-      <c r="AQ257" s="11" t="s">
-        <v>1831</v>
       </c>
       <c r="AR257" s="11">
         <v>82</v>
       </c>
       <c r="AS257" s="36" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="AT257" s="11" t="s">
         <v>75</v>
@@ -47980,6 +48053,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7478568B-3EC6-468D-91B9-4ADDA7A3C567}">
+  <sheetPr codeName="Feuil1"/>
   <dimension ref="C5:M106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
@@ -49135,6 +49209,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2525349D-A5C0-4F8F-A82B-809A118FF03F}">
+  <sheetPr codeName="Feuil4"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData/>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E24EBBE-3759-4653-9A02-1CD32265D904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0E85F2-30F7-4D09-95F9-CA7797673498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7545" uniqueCount="1852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7598" uniqueCount="1867">
   <si>
     <t>Contact</t>
   </si>
@@ -5611,6 +5611,51 @@
   </si>
   <si>
     <t>Cession de droit au bail, dans le cadre d'un départ à la retraite. 1er centre commercial de l'Ain. 1,3 M de Tickets hyper/an. 50 magasins</t>
+  </si>
+  <si>
+    <t>Anet</t>
+  </si>
+  <si>
+    <t>Leclerc Anet</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NkkbpN9r686ViCMz7</t>
+  </si>
+  <si>
+    <t>48.862174</t>
+  </si>
+  <si>
+    <t>1.458129</t>
+  </si>
+  <si>
+    <t>Forfait de charges. Galerie du Leclerc d'Anet : 70 M€ hors essence. CA Total de la zone : 150 M€</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/1.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/2.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/3.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/4.png https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/5.png</t>
+  </si>
+  <si>
+    <t>11 rue Diane de Poitiers</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/urSsbk4EKDxKevN88</t>
+  </si>
+  <si>
+    <t>Local en pied d'immeuble. Surface de 120 m² de surface de vente + 70 m² de réserve arrière + cave</t>
+  </si>
+  <si>
+    <t>Restaurants, coiffeur, boulangerie, commerce de proximité</t>
+  </si>
+  <si>
+    <t>Saïd Bettache</t>
+  </si>
+  <si>
+    <t>48.857358</t>
+  </si>
+  <si>
+    <t>1.438630</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/6.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/7.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/8.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/9.jpg</t>
   </si>
 </sst>
 </file>
@@ -6291,8 +6336,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX259" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AX259" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX261" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AX261" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="50">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="49" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -47998,6 +48043,293 @@
         <v>46099</v>
       </c>
     </row>
+    <row r="260" spans="1:50" ht="25.5">
+      <c r="A260" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Centre-Val de Loire</v>
+      </c>
+      <c r="B260" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Eure-et-Loir</v>
+      </c>
+      <c r="C260" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>28</v>
+      </c>
+      <c r="D260" s="11" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E260" s="26">
+        <v>28260</v>
+      </c>
+      <c r="F260" s="10" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G260" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Leclerc Anet
+28260 - Anet</v>
+      </c>
+      <c r="H260" s="15" t="s">
+        <v>1854</v>
+      </c>
+      <c r="I260" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J260" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K260" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L260" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M260" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N260" s="36"/>
+      <c r="O260" s="34">
+        <v>120</v>
+      </c>
+      <c r="P260" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q260" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R260" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S260" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T260" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>42000</v>
+      </c>
+      <c r="U260" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>3500</v>
+      </c>
+      <c r="V260" s="12">
+        <v>350</v>
+      </c>
+      <c r="W260" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X260" s="12"/>
+      <c r="Y260" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z260" s="12"/>
+      <c r="AA260" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB260" s="12"/>
+      <c r="AC260" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD260" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE260" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>42000</v>
+      </c>
+      <c r="AF260" s="12"/>
+      <c r="AG260" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH260" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI260" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ260" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK260" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="AL260" s="10"/>
+      <c r="AM260" s="11" t="s">
+        <v>1857</v>
+      </c>
+      <c r="AN260" s="11"/>
+      <c r="AO260" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP260" s="11" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AQ260" s="11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="AR260" s="11">
+        <v>84</v>
+      </c>
+      <c r="AS260" s="36" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AT260" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU260" s="11"/>
+      <c r="AV260" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="AW260" s="14"/>
+      <c r="AX260" s="44">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="261" spans="1:50" ht="25.5">
+      <c r="A261" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Centre-Val de Loire</v>
+      </c>
+      <c r="B261" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Eure-et-Loir</v>
+      </c>
+      <c r="C261" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>28</v>
+      </c>
+      <c r="D261" s="11" t="s">
+        <v>1859</v>
+      </c>
+      <c r="E261" s="26">
+        <v>28260</v>
+      </c>
+      <c r="F261" s="10" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G261" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>11 rue Diane de Poitiers
+28260 - Anet</v>
+      </c>
+      <c r="H261" s="15" t="s">
+        <v>1860</v>
+      </c>
+      <c r="I261" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J261" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K261" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L261" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M261" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N261" s="36"/>
+      <c r="O261" s="34">
+        <v>190</v>
+      </c>
+      <c r="P261" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q261" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R261" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="S261" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="T261" s="12"/>
+      <c r="U261" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V261" s="12"/>
+      <c r="W261" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X261" s="12"/>
+      <c r="Y261" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z261" s="12"/>
+      <c r="AA261" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB261" s="12"/>
+      <c r="AC261" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD261" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE261" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF261" s="12"/>
+      <c r="AG261" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH261" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI261" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ261" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK261" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL261" s="10" t="s">
+        <v>1862</v>
+      </c>
+      <c r="AM261" s="11" t="s">
+        <v>1861</v>
+      </c>
+      <c r="AN261" s="11"/>
+      <c r="AO261" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP261" s="11" t="s">
+        <v>1864</v>
+      </c>
+      <c r="AQ261" s="11" t="s">
+        <v>1865</v>
+      </c>
+      <c r="AR261" s="11">
+        <v>85</v>
+      </c>
+      <c r="AS261" s="36" t="s">
+        <v>1866</v>
+      </c>
+      <c r="AT261" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU261" s="11"/>
+      <c r="AV261" s="13" t="s">
+        <v>1863</v>
+      </c>
+      <c r="AW261" s="14"/>
+      <c r="AX261" s="44">
+        <v>46132</v>
+      </c>
+    </row>
     <row r="271" spans="1:50">
       <c r="F271" s="1" t="s">
         <v>1018</v>
@@ -48216,6 +48548,8 @@
     <hyperlink ref="H258" r:id="rId203" xr:uid="{8ED2A142-1C2D-4EEF-B2C9-8E7DBF014473}"/>
     <hyperlink ref="H259" r:id="rId204" xr:uid="{3EE40D55-CEE4-48CB-B1B7-513D68E9C6A6}"/>
     <hyperlink ref="H192" r:id="rId205" display="https://maps.app.goo.gl/e1ddei1i8yHZXuQi8" xr:uid="{75B930EA-6D01-4FF4-A61B-C6AEA8DAC1AA}"/>
+    <hyperlink ref="H260" r:id="rId206" xr:uid="{B791AC49-8556-4BE6-8345-FA11843C584F}"/>
+    <hyperlink ref="H261" r:id="rId207" xr:uid="{246CD591-7D7F-4917-83C9-04BFB04148F6}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -48224,7 +48558,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId206"/>
+    <tablePart r:id="rId208"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0E85F2-30F7-4D09-95F9-CA7797673498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2D63B0-5E62-4905-A536-AC98E6C669C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -5631,9 +5631,6 @@
     <t>Forfait de charges. Galerie du Leclerc d'Anet : 70 M€ hors essence. CA Total de la zone : 150 M€</t>
   </si>
   <si>
-    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/1.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/2.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/3.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/4.png https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/5.png</t>
-  </si>
-  <si>
     <t>11 rue Diane de Poitiers</t>
   </si>
   <si>
@@ -5656,6 +5653,9 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/6.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/7.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/8.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/85%20-%20Anet/9.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/1.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/84%20-%20Anet%20Leclerc/5.jpg</t>
   </si>
 </sst>
 </file>
@@ -48174,7 +48174,7 @@
         <v>84</v>
       </c>
       <c r="AS260" s="36" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AT260" s="11" t="s">
         <v>75</v>
@@ -48202,7 +48202,7 @@
         <v>28</v>
       </c>
       <c r="D261" s="11" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="E261" s="26">
         <v>28260</v>
@@ -48216,7 +48216,7 @@
 28260 - Anet</v>
       </c>
       <c r="H261" s="15" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I261" s="12" t="s">
         <v>45</v>
@@ -48297,33 +48297,33 @@
         <v>53</v>
       </c>
       <c r="AL261" s="10" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="AM261" s="11" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="AN261" s="11"/>
       <c r="AO261" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AP261" s="11" t="s">
+        <v>1863</v>
+      </c>
+      <c r="AQ261" s="11" t="s">
         <v>1864</v>
-      </c>
-      <c r="AQ261" s="11" t="s">
-        <v>1865</v>
       </c>
       <c r="AR261" s="11">
         <v>85</v>
       </c>
       <c r="AS261" s="36" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="AT261" s="11" t="s">
         <v>75</v>
       </c>
       <c r="AU261" s="11"/>
       <c r="AV261" s="13" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="AW261" s="14"/>
       <c r="AX261" s="44">

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2D63B0-5E62-4905-A536-AC98E6C669C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C6E87E-BE0E-40F9-A537-B36CDD364FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau recherche" sheetId="2" r:id="rId1"/>
@@ -32331,14 +32331,14 @@
       </c>
       <c r="T160" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>312750</v>
+        <v>278000</v>
       </c>
       <c r="U160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>26062.5</v>
+        <v>23166.666666666668</v>
       </c>
       <c r="V160" s="12">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="W160" s="6" t="s">
         <v>103</v>
@@ -32370,15 +32370,15 @@
       </c>
       <c r="AE160" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>343330</v>
+        <v>308580</v>
       </c>
       <c r="AF160" s="12" t="str">
         <f t="shared" si="7"/>
-        <v>3 mois = 78 188 €</v>
+        <v>3 mois = 69 500 €</v>
       </c>
       <c r="AG160" s="12" t="str">
         <f>"6 mois = "&amp;TEXT(ROUND(6/12*T160,0),"### ### ##0 €")</f>
-        <v>6 mois = 156 375 €</v>
+        <v>6 mois = 139 000 €</v>
       </c>
       <c r="AH160" s="46">
         <v>0.05</v>
@@ -34782,14 +34782,14 @@
       </c>
       <c r="T175" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>123200</v>
+        <v>107800</v>
       </c>
       <c r="U175" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>10266.666666666666</v>
+        <v>8983.3333333333339</v>
       </c>
       <c r="V175" s="12">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="W175" s="6" t="s">
         <v>103</v>
@@ -34821,15 +34821,15 @@
       </c>
       <c r="AE175" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>142912</v>
+        <v>127512</v>
       </c>
       <c r="AF175" s="12" t="str">
         <f t="shared" si="7"/>
-        <v>3 mois = 30 800 €</v>
+        <v>3 mois = 26 950 €</v>
       </c>
       <c r="AG175" s="12" t="str">
         <f t="shared" si="8"/>
-        <v>6 mois = 61 600 €</v>
+        <v>6 mois = 53 900 €</v>
       </c>
       <c r="AH175" s="46">
         <v>0.05</v>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C6E87E-BE0E-40F9-A537-B36CDD364FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE5B13D-2150-44C1-9BA8-5B9AEDB2C549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau recherche" sheetId="2" r:id="rId1"/>
@@ -25560,14 +25560,14 @@
       </c>
       <c r="T118" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>167700</v>
+        <v>89440</v>
       </c>
       <c r="U118" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>13975</v>
+        <v>7453.333333333333</v>
       </c>
       <c r="V118" s="12">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="W118" s="6" t="s">
         <v>103</v>
@@ -25599,11 +25599,11 @@
       </c>
       <c r="AE118" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>212755.4</v>
+        <v>134495.4</v>
       </c>
       <c r="AF118" s="12" t="str">
         <f>"2 mois = "&amp;TEXT(ROUND(2/12*T118,0),"### ### ##0 €")</f>
-        <v>2 mois = 27 950 €</v>
+        <v>2 mois = 14 907 €</v>
       </c>
       <c r="AG118" s="6" t="s">
         <v>103</v>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AB779C-8142-4B68-A49D-236327EAC3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9246ED5B-8A93-407F-BBB8-1B83171D6849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8092" uniqueCount="1922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8845" uniqueCount="2030">
   <si>
     <t>Contact</t>
   </si>
@@ -5843,6 +5843,330 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/86.1%20-%20Angers/1.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/86.1%20-%20Angers/2.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/86.1%20-%20Angers/3.png;https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/86.1%20-%20Angers/4.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/86.1%20-%20Angers/5%20Situation%20ext%C3%A9rieur.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/86.1%20-%20Angers/6%20Plan%20RDC.png; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/86.1%20-%20Angers/7%20Plan%20R%2B1.png</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Xe5mVhv32b2SqSBH7</t>
+  </si>
+  <si>
+    <t>390 Rue Jean Marie Tjibaou</t>
+  </si>
+  <si>
+    <t>9 - 10</t>
+  </si>
+  <si>
+    <t>12 - 13 - 14</t>
+  </si>
+  <si>
+    <t>20 - 21</t>
+  </si>
+  <si>
+    <t>22 - 23 - 24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>27 - 28</t>
+  </si>
+  <si>
+    <t>31 - 32</t>
+  </si>
+  <si>
+    <t>33 - 34 - 35 - 36</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>41 - 42</t>
+  </si>
+  <si>
+    <t>Action pharmacie, optique, services</t>
+  </si>
+  <si>
+    <t>87.1</t>
+  </si>
+  <si>
+    <t>87.4</t>
+  </si>
+  <si>
+    <t>87.5</t>
+  </si>
+  <si>
+    <t>87.3</t>
+  </si>
+  <si>
+    <t>87.2</t>
+  </si>
+  <si>
+    <t>87.6</t>
+  </si>
+  <si>
+    <t>87.7</t>
+  </si>
+  <si>
+    <t>87.8</t>
+  </si>
+  <si>
+    <t>87.9</t>
+  </si>
+  <si>
+    <t>87.10</t>
+  </si>
+  <si>
+    <t>87.11</t>
+  </si>
+  <si>
+    <t>87.12</t>
+  </si>
+  <si>
+    <t>87.13</t>
+  </si>
+  <si>
+    <t>87.14</t>
+  </si>
+  <si>
+    <t>87.15</t>
+  </si>
+  <si>
+    <t>87.16</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/87.1%20-%20Avignon/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/87.1%20-%20Avignon/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/87.1%20-%20Avignon/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/87.1%20-%20Avignon/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/87.1%20-%20Avignon/5%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>43.928433</t>
+  </si>
+  <si>
+    <t>4.792630</t>
+  </si>
+  <si>
+    <t>43.928534</t>
+  </si>
+  <si>
+    <t>4.792429</t>
+  </si>
+  <si>
+    <t>43.928578</t>
+  </si>
+  <si>
+    <t>4.792287</t>
+  </si>
+  <si>
+    <t>43.928372</t>
+  </si>
+  <si>
+    <t>4.792252</t>
+  </si>
+  <si>
+    <t>43.928337</t>
+  </si>
+  <si>
+    <t>4.792491</t>
+  </si>
+  <si>
+    <t>43.928163</t>
+  </si>
+  <si>
+    <t>4.792649</t>
+  </si>
+  <si>
+    <t>43.928091</t>
+  </si>
+  <si>
+    <t>4.792702</t>
+  </si>
+  <si>
+    <t>43.927993</t>
+  </si>
+  <si>
+    <t>4.792767</t>
+  </si>
+  <si>
+    <t>43.927912</t>
+  </si>
+  <si>
+    <t>4.792842</t>
+  </si>
+  <si>
+    <t>43.927831</t>
+  </si>
+  <si>
+    <t>4.792920</t>
+  </si>
+  <si>
+    <t>43.927721</t>
+  </si>
+  <si>
+    <t>4.792989</t>
+  </si>
+  <si>
+    <t>43.927566</t>
+  </si>
+  <si>
+    <t>4.792981</t>
+  </si>
+  <si>
+    <t>43.927464</t>
+  </si>
+  <si>
+    <t>4.792928</t>
+  </si>
+  <si>
+    <t>43.927305</t>
+  </si>
+  <si>
+    <t>4.793035</t>
+  </si>
+  <si>
+    <t>43.927375</t>
+  </si>
+  <si>
+    <t>4.793191</t>
+  </si>
+  <si>
+    <t>43.927556</t>
+  </si>
+  <si>
+    <t>4.793279</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gbVM7iJLGEuEUtKL8</t>
+  </si>
+  <si>
+    <t>Savonnières-devant-Bar</t>
+  </si>
+  <si>
+    <t>Centre Commercial Auchan, 1 Rue de Longeville</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>88.1</t>
+  </si>
+  <si>
+    <t>88.2</t>
+  </si>
+  <si>
+    <t>88.3</t>
+  </si>
+  <si>
+    <t>88.4</t>
+  </si>
+  <si>
+    <t>88.5</t>
+  </si>
+  <si>
+    <t>88.6</t>
+  </si>
+  <si>
+    <t>88.7</t>
+  </si>
+  <si>
+    <t>88.8</t>
+  </si>
+  <si>
+    <t>48.759734</t>
+  </si>
+  <si>
+    <t>5.183675</t>
+  </si>
+  <si>
+    <t>48.759787</t>
+  </si>
+  <si>
+    <t>5.183294</t>
+  </si>
+  <si>
+    <t>48.759805</t>
+  </si>
+  <si>
+    <t>5.183109</t>
+  </si>
+  <si>
+    <t>48.759831</t>
+  </si>
+  <si>
+    <t>5.183028</t>
+  </si>
+  <si>
+    <t>48.759936</t>
+  </si>
+  <si>
+    <t>5.182924</t>
+  </si>
+  <si>
+    <t>5.182543</t>
+  </si>
+  <si>
+    <t>48.759969</t>
+  </si>
+  <si>
+    <t>48.759990</t>
+  </si>
+  <si>
+    <t>5.182452</t>
+  </si>
+  <si>
+    <t>48.759932</t>
+  </si>
+  <si>
+    <t>5.182444</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/88.1%20-%20Bar-Le-Duc/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/88.1%20-%20Bar-Le-Duc/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/88.1%20-%20Bar-Le-Duc/3%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tZBVFakEc2vBKi3x6</t>
+  </si>
+  <si>
+    <t>Beaune</t>
+  </si>
+  <si>
+    <t>Auchan, 1 Rue de Longeville</t>
+  </si>
+  <si>
+    <t>89.1</t>
+  </si>
+  <si>
+    <t>89.2</t>
+  </si>
+  <si>
+    <t>89.3</t>
+  </si>
+  <si>
+    <t>89.4</t>
+  </si>
+  <si>
+    <t>47.016321</t>
+  </si>
+  <si>
+    <t>4.838673</t>
+  </si>
+  <si>
+    <t>47.016195</t>
+  </si>
+  <si>
+    <t>4.838646</t>
+  </si>
+  <si>
+    <t>47.016138</t>
+  </si>
+  <si>
+    <t>4.837680</t>
+  </si>
+  <si>
+    <t>47.016142</t>
+  </si>
+  <si>
+    <t>4.838048</t>
+  </si>
+  <si>
+    <t>Beaune St-Jacques, 9 Av. du Général de Gaulle</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/5%20Plan.jpg</t>
   </si>
 </sst>
 </file>
@@ -6523,8 +6847,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX284" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:AX284" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}" name="Tableau1" displayName="Tableau1" ref="A1:AX318" totalsRowShown="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:AX318" xr:uid="{C496A065-E5CA-44EF-B6AE-AC366F12DAEC}"/>
   <tableColumns count="50">
     <tableColumn id="43" xr3:uid="{DE1D6443-0E1C-43C0-8BC8-BDC69562CB95}" name="Région" dataDxfId="49" dataCellStyle="Normal 2">
       <calculatedColumnFormula>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</calculatedColumnFormula>
@@ -6919,7 +7243,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C491A860-D730-4E53-986A-F9417B64BAFA}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:BG299"/>
+  <dimension ref="A1:BG327"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -48639,7 +48963,7 @@
         <v>70240</v>
       </c>
       <c r="AF262" s="12" t="str">
-        <f t="shared" ref="AF262:AF277" si="15">"3 mois = "&amp;TEXT(ROUND(3/12*T262,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AF262:AF305" si="15">"3 mois = "&amp;TEXT(ROUND(3/12*T262,0),"### ### ##0 €")</f>
         <v>3 mois = 12 000 €</v>
       </c>
       <c r="AG262" s="12" t="s">
@@ -51047,72 +51371,98 @@
     <row r="278" spans="1:50" ht="25.5">
       <c r="A278" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Pays de la Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B278" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Maine-et-Loire</v>
+        <v>Vaucluse</v>
       </c>
       <c r="C278" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D278" s="10" t="s">
-        <v>1853</v>
+        <v>1923</v>
       </c>
       <c r="E278" s="26">
-        <v>49000</v>
+        <v>84000</v>
       </c>
       <c r="F278" s="10" t="s">
-        <v>1852</v>
+        <v>1061</v>
       </c>
       <c r="G278" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>10 Rue du Grand Launay
-49000 - Angers</v>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
       </c>
       <c r="H278" s="15" t="s">
-        <v>1854</v>
+        <v>1922</v>
       </c>
       <c r="I278" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J278" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K278" s="10"/>
-      <c r="L278" s="10"/>
-      <c r="M278" s="12"/>
-      <c r="N278" s="36"/>
-      <c r="O278" s="34"/>
-      <c r="P278" s="12"/>
-      <c r="Q278" s="34"/>
-      <c r="R278" s="10"/>
-      <c r="S278" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="K278" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L278" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M278" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N278" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="O278" s="34">
+        <v>76</v>
+      </c>
+      <c r="P278" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q278" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R278" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S278" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="T278" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="U278" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V278" s="12"/>
-      <c r="W278" s="12"/>
+        <v>1266.6666666666667</v>
+      </c>
+      <c r="V278" s="12">
+        <v>200</v>
+      </c>
+      <c r="W278" s="34" t="s">
+        <v>98</v>
+      </c>
       <c r="X278" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>3040</v>
       </c>
       <c r="Y278" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z278" s="12"/>
+        <v>253.33333333333334</v>
+      </c>
+      <c r="Z278" s="12">
+        <v>40</v>
+      </c>
       <c r="AA278" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB278" s="12"/>
+        <v>1596</v>
+      </c>
+      <c r="AB278" s="12">
+        <v>21</v>
+      </c>
       <c r="AC278" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -51120,15 +51470,26 @@
       <c r="AD278" s="12"/>
       <c r="AE278" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF278" s="12"/>
-      <c r="AG278" s="12"/>
-      <c r="AH278" s="12"/>
-      <c r="AI278" s="12"/>
+        <v>19836</v>
+      </c>
+      <c r="AF278" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 3 800 €</v>
+      </c>
+      <c r="AG278" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH278" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI278" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ278" s="10"/>
       <c r="AK278" s="10"/>
-      <c r="AL278" s="10"/>
+      <c r="AL278" s="10" t="s">
+        <v>1934</v>
+      </c>
       <c r="AM278" s="11"/>
       <c r="AN278" s="11" t="s">
         <v>1386</v>
@@ -51136,10 +51497,18 @@
       <c r="AO278" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="AP278" s="11"/>
-      <c r="AQ278" s="11"/>
-      <c r="AR278" s="11"/>
-      <c r="AS278" s="36"/>
+      <c r="AP278" s="11" t="s">
+        <v>1952</v>
+      </c>
+      <c r="AQ278" s="11" t="s">
+        <v>1953</v>
+      </c>
+      <c r="AR278" s="11" t="s">
+        <v>1935</v>
+      </c>
+      <c r="AS278" s="36" t="s">
+        <v>1951</v>
+      </c>
       <c r="AT278" s="11" t="s">
         <v>70</v>
       </c>
@@ -51155,72 +51524,98 @@
     <row r="279" spans="1:50" ht="25.5">
       <c r="A279" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Pays de la Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B279" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Maine-et-Loire</v>
+        <v>Vaucluse</v>
       </c>
       <c r="C279" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D279" s="10" t="s">
-        <v>1853</v>
+        <v>1923</v>
       </c>
       <c r="E279" s="26">
-        <v>49000</v>
+        <v>84000</v>
       </c>
       <c r="F279" s="10" t="s">
-        <v>1852</v>
+        <v>1061</v>
       </c>
       <c r="G279" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>10 Rue du Grand Launay
-49000 - Angers</v>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
       </c>
       <c r="H279" s="15" t="s">
-        <v>1854</v>
+        <v>1922</v>
       </c>
       <c r="I279" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J279" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K279" s="10"/>
-      <c r="L279" s="10"/>
-      <c r="M279" s="12"/>
-      <c r="N279" s="36"/>
-      <c r="O279" s="34"/>
-      <c r="P279" s="12"/>
-      <c r="Q279" s="34"/>
-      <c r="R279" s="10"/>
-      <c r="S279" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="K279" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L279" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M279" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N279" s="36" t="s">
+        <v>895</v>
+      </c>
+      <c r="O279" s="34">
+        <v>223</v>
+      </c>
+      <c r="P279" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q279" s="34">
+        <v>307</v>
+      </c>
+      <c r="R279" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S279" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="T279" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>44600</v>
       </c>
       <c r="U279" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V279" s="12"/>
-      <c r="W279" s="12"/>
+        <v>3716.6666666666665</v>
+      </c>
+      <c r="V279" s="12">
+        <v>200</v>
+      </c>
+      <c r="W279" s="34" t="s">
+        <v>98</v>
+      </c>
       <c r="X279" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="Y279" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z279" s="12"/>
+        <v>743.33333333333337</v>
+      </c>
+      <c r="Z279" s="12">
+        <v>40</v>
+      </c>
       <c r="AA279" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB279" s="12"/>
+        <v>4683</v>
+      </c>
+      <c r="AB279" s="12">
+        <v>21</v>
+      </c>
       <c r="AC279" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -51228,15 +51623,26 @@
       <c r="AD279" s="12"/>
       <c r="AE279" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF279" s="12"/>
-      <c r="AG279" s="12"/>
-      <c r="AH279" s="12"/>
-      <c r="AI279" s="12"/>
+        <v>58203</v>
+      </c>
+      <c r="AF279" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 11 150 €</v>
+      </c>
+      <c r="AG279" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH279" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI279" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ279" s="10"/>
       <c r="AK279" s="10"/>
-      <c r="AL279" s="10"/>
+      <c r="AL279" s="10" t="s">
+        <v>1934</v>
+      </c>
       <c r="AM279" s="11"/>
       <c r="AN279" s="11" t="s">
         <v>1386</v>
@@ -51244,10 +51650,18 @@
       <c r="AO279" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="AP279" s="11"/>
-      <c r="AQ279" s="11"/>
-      <c r="AR279" s="11"/>
-      <c r="AS279" s="36"/>
+      <c r="AP279" s="11" t="s">
+        <v>1954</v>
+      </c>
+      <c r="AQ279" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AR279" s="11" t="s">
+        <v>1939</v>
+      </c>
+      <c r="AS279" s="36" t="s">
+        <v>1951</v>
+      </c>
       <c r="AT279" s="11" t="s">
         <v>70</v>
       </c>
@@ -51263,72 +51677,98 @@
     <row r="280" spans="1:50" ht="25.5">
       <c r="A280" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Pays de la Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B280" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Maine-et-Loire</v>
+        <v>Vaucluse</v>
       </c>
       <c r="C280" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>1853</v>
+        <v>1923</v>
       </c>
       <c r="E280" s="26">
-        <v>49000</v>
+        <v>84000</v>
       </c>
       <c r="F280" s="10" t="s">
-        <v>1852</v>
+        <v>1061</v>
       </c>
       <c r="G280" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>10 Rue du Grand Launay
-49000 - Angers</v>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
       </c>
       <c r="H280" s="15" t="s">
-        <v>1854</v>
+        <v>1922</v>
       </c>
       <c r="I280" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J280" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K280" s="10"/>
-      <c r="L280" s="10"/>
-      <c r="M280" s="12"/>
-      <c r="N280" s="36"/>
-      <c r="O280" s="34"/>
-      <c r="P280" s="12"/>
-      <c r="Q280" s="34"/>
-      <c r="R280" s="10"/>
-      <c r="S280" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="K280" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L280" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M280" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N280" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="O280" s="34">
+        <v>84</v>
+      </c>
+      <c r="P280" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q280" s="34">
+        <v>307</v>
+      </c>
+      <c r="R280" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S280" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="T280" s="12">
         <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="U280" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V280" s="12"/>
-      <c r="W280" s="12"/>
+        <v>1400</v>
+      </c>
+      <c r="V280" s="12">
+        <v>200</v>
+      </c>
+      <c r="W280" s="34" t="s">
+        <v>98</v>
+      </c>
       <c r="X280" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="Y280" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z280" s="12"/>
+        <v>280</v>
+      </c>
+      <c r="Z280" s="12">
+        <v>40</v>
+      </c>
       <c r="AA280" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB280" s="12"/>
+        <v>1764</v>
+      </c>
+      <c r="AB280" s="12">
+        <v>21</v>
+      </c>
       <c r="AC280" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -51336,15 +51776,26 @@
       <c r="AD280" s="12"/>
       <c r="AE280" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF280" s="12"/>
-      <c r="AG280" s="12"/>
-      <c r="AH280" s="12"/>
-      <c r="AI280" s="12"/>
+        <v>21924</v>
+      </c>
+      <c r="AF280" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 4 200 €</v>
+      </c>
+      <c r="AG280" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH280" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI280" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ280" s="10"/>
       <c r="AK280" s="10"/>
-      <c r="AL280" s="10"/>
+      <c r="AL280" s="10" t="s">
+        <v>1934</v>
+      </c>
       <c r="AM280" s="11"/>
       <c r="AN280" s="11" t="s">
         <v>1386</v>
@@ -51352,10 +51803,18 @@
       <c r="AO280" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="AP280" s="11"/>
-      <c r="AQ280" s="11"/>
-      <c r="AR280" s="11"/>
-      <c r="AS280" s="36"/>
+      <c r="AP280" s="11" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AQ280" s="11" t="s">
+        <v>1957</v>
+      </c>
+      <c r="AR280" s="11" t="s">
+        <v>1938</v>
+      </c>
+      <c r="AS280" s="36" t="s">
+        <v>1951</v>
+      </c>
       <c r="AT280" s="11" t="s">
         <v>70</v>
       </c>
@@ -51371,69 +51830,98 @@
     <row r="281" spans="1:50" ht="25.5">
       <c r="A281" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Pays de la Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B281" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Maine-et-Loire</v>
+        <v>Vaucluse</v>
       </c>
       <c r="C281" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D281" s="10" t="s">
-        <v>1853</v>
+        <v>1923</v>
       </c>
       <c r="E281" s="26">
-        <v>49000</v>
+        <v>84000</v>
       </c>
       <c r="F281" s="10" t="s">
-        <v>1852</v>
+        <v>1061</v>
       </c>
       <c r="G281" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>10 Rue du Grand Launay
-49000 - Angers</v>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
       </c>
       <c r="H281" s="15" t="s">
-        <v>1854</v>
+        <v>1922</v>
       </c>
       <c r="I281" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J281" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K281" s="10"/>
-      <c r="L281" s="10"/>
-      <c r="M281" s="12"/>
-      <c r="N281" s="36"/>
-      <c r="O281" s="34"/>
-      <c r="P281" s="12"/>
-      <c r="Q281" s="34"/>
-      <c r="R281" s="10"/>
-      <c r="S281" s="12"/>
-      <c r="T281" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="K281" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L281" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M281" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N281" s="36" t="s">
+        <v>1924</v>
+      </c>
+      <c r="O281" s="34">
+        <v>279</v>
+      </c>
+      <c r="P281" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q281" s="34">
+        <v>429</v>
+      </c>
+      <c r="R281" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S281" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T281" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>55800</v>
+      </c>
       <c r="U281" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V281" s="12"/>
-      <c r="W281" s="12"/>
+        <v>4650</v>
+      </c>
+      <c r="V281" s="12">
+        <v>200</v>
+      </c>
+      <c r="W281" s="34" t="s">
+        <v>98</v>
+      </c>
       <c r="X281" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>11160</v>
       </c>
       <c r="Y281" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z281" s="12"/>
+        <v>930</v>
+      </c>
+      <c r="Z281" s="12">
+        <v>40</v>
+      </c>
       <c r="AA281" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB281" s="12"/>
+        <v>5859</v>
+      </c>
+      <c r="AB281" s="12">
+        <v>21</v>
+      </c>
       <c r="AC281" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -51441,15 +51929,30 @@
       <c r="AD281" s="12"/>
       <c r="AE281" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF281" s="12"/>
-      <c r="AG281" s="12"/>
-      <c r="AH281" s="12"/>
-      <c r="AI281" s="12"/>
-      <c r="AJ281" s="10"/>
-      <c r="AK281" s="10"/>
-      <c r="AL281" s="10"/>
+        <v>72819</v>
+      </c>
+      <c r="AF281" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 13 950 €</v>
+      </c>
+      <c r="AG281" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH281" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI281" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ281" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK281" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="AL281" s="10" t="s">
+        <v>1934</v>
+      </c>
       <c r="AM281" s="11"/>
       <c r="AN281" s="11" t="s">
         <v>1386</v>
@@ -51457,10 +51960,18 @@
       <c r="AO281" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="AP281" s="11"/>
-      <c r="AQ281" s="11"/>
-      <c r="AR281" s="11"/>
-      <c r="AS281" s="36"/>
+      <c r="AP281" s="11" t="s">
+        <v>1958</v>
+      </c>
+      <c r="AQ281" s="11" t="s">
+        <v>1959</v>
+      </c>
+      <c r="AR281" s="11" t="s">
+        <v>1936</v>
+      </c>
+      <c r="AS281" s="36" t="s">
+        <v>1951</v>
+      </c>
       <c r="AT281" s="11" t="s">
         <v>70</v>
       </c>
@@ -51476,69 +51987,98 @@
     <row r="282" spans="1:50" ht="25.5">
       <c r="A282" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Pays de la Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B282" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Maine-et-Loire</v>
+        <v>Vaucluse</v>
       </c>
       <c r="C282" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D282" s="10" t="s">
-        <v>1853</v>
+        <v>1923</v>
       </c>
       <c r="E282" s="26">
-        <v>49000</v>
+        <v>84000</v>
       </c>
       <c r="F282" s="10" t="s">
-        <v>1852</v>
+        <v>1061</v>
       </c>
       <c r="G282" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>10 Rue du Grand Launay
-49000 - Angers</v>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
       </c>
       <c r="H282" s="15" t="s">
-        <v>1854</v>
+        <v>1922</v>
       </c>
       <c r="I282" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J282" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K282" s="10"/>
-      <c r="L282" s="10"/>
-      <c r="M282" s="12"/>
-      <c r="N282" s="36"/>
-      <c r="O282" s="34"/>
-      <c r="P282" s="12"/>
-      <c r="Q282" s="34"/>
-      <c r="R282" s="10"/>
-      <c r="S282" s="12"/>
-      <c r="T282" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="K282" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L282" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M282" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N282" s="36" t="s">
+        <v>1925</v>
+      </c>
+      <c r="O282" s="34">
+        <v>150</v>
+      </c>
+      <c r="P282" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q282" s="34">
+        <v>429</v>
+      </c>
+      <c r="R282" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S282" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T282" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>30000</v>
+      </c>
       <c r="U282" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V282" s="12"/>
-      <c r="W282" s="12"/>
+        <v>2500</v>
+      </c>
+      <c r="V282" s="12">
+        <v>200</v>
+      </c>
+      <c r="W282" s="34" t="s">
+        <v>98</v>
+      </c>
       <c r="X282" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="Y282" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z282" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="Z282" s="12">
+        <v>40</v>
+      </c>
       <c r="AA282" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB282" s="12"/>
+        <v>3150</v>
+      </c>
+      <c r="AB282" s="12">
+        <v>21</v>
+      </c>
       <c r="AC282" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -51546,15 +52086,26 @@
       <c r="AD282" s="12"/>
       <c r="AE282" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF282" s="12"/>
-      <c r="AG282" s="12"/>
-      <c r="AH282" s="12"/>
-      <c r="AI282" s="12"/>
+        <v>39150</v>
+      </c>
+      <c r="AF282" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 7 500 €</v>
+      </c>
+      <c r="AG282" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH282" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI282" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ282" s="10"/>
       <c r="AK282" s="10"/>
-      <c r="AL282" s="10"/>
+      <c r="AL282" s="10" t="s">
+        <v>1934</v>
+      </c>
       <c r="AM282" s="11"/>
       <c r="AN282" s="11" t="s">
         <v>1386</v>
@@ -51562,10 +52113,18 @@
       <c r="AO282" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="AP282" s="11"/>
-      <c r="AQ282" s="11"/>
-      <c r="AR282" s="11"/>
-      <c r="AS282" s="36"/>
+      <c r="AP282" s="11" t="s">
+        <v>1960</v>
+      </c>
+      <c r="AQ282" s="11" t="s">
+        <v>1961</v>
+      </c>
+      <c r="AR282" s="11" t="s">
+        <v>1937</v>
+      </c>
+      <c r="AS282" s="36" t="s">
+        <v>1951</v>
+      </c>
       <c r="AT282" s="11" t="s">
         <v>70</v>
       </c>
@@ -51581,69 +52140,98 @@
     <row r="283" spans="1:50" ht="25.5">
       <c r="A283" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Pays de la Loire</v>
+        <v>Provence-Alpes-Côte d'Azur</v>
       </c>
       <c r="B283" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Maine-et-Loire</v>
+        <v>Vaucluse</v>
       </c>
       <c r="C283" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D283" s="10" t="s">
-        <v>1853</v>
+        <v>1923</v>
       </c>
       <c r="E283" s="26">
-        <v>49000</v>
+        <v>84000</v>
       </c>
       <c r="F283" s="10" t="s">
-        <v>1852</v>
+        <v>1061</v>
       </c>
       <c r="G283" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>10 Rue du Grand Launay
-49000 - Angers</v>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
       </c>
       <c r="H283" s="15" t="s">
-        <v>1854</v>
+        <v>1922</v>
       </c>
       <c r="I283" s="12" t="s">
         <v>47</v>
       </c>
       <c r="J283" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K283" s="10"/>
-      <c r="L283" s="10"/>
-      <c r="M283" s="12"/>
-      <c r="N283" s="36"/>
-      <c r="O283" s="34"/>
-      <c r="P283" s="12"/>
-      <c r="Q283" s="34"/>
-      <c r="R283" s="10"/>
-      <c r="S283" s="12"/>
-      <c r="T283" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="K283" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L283" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M283" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N283" s="36" t="s">
+        <v>587</v>
+      </c>
+      <c r="O283" s="34">
+        <v>58</v>
+      </c>
+      <c r="P283" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q283" s="34">
+        <v>610</v>
+      </c>
+      <c r="R283" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S283" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T283" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11600</v>
+      </c>
       <c r="U283" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V283" s="12"/>
-      <c r="W283" s="12"/>
+        <v>966.66666666666663</v>
+      </c>
+      <c r="V283" s="12">
+        <v>200</v>
+      </c>
+      <c r="W283" s="34" t="s">
+        <v>98</v>
+      </c>
       <c r="X283" s="6">
         <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
-        <v>0</v>
+        <v>2320</v>
       </c>
       <c r="Y283" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z283" s="12"/>
+        <v>193.33333333333334</v>
+      </c>
+      <c r="Z283" s="12">
+        <v>40</v>
+      </c>
       <c r="AA283" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB283" s="12"/>
+        <v>1218</v>
+      </c>
+      <c r="AB283" s="12">
+        <v>21</v>
+      </c>
       <c r="AC283" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -51651,15 +52239,26 @@
       <c r="AD283" s="12"/>
       <c r="AE283" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF283" s="12"/>
-      <c r="AG283" s="12"/>
-      <c r="AH283" s="12"/>
-      <c r="AI283" s="12"/>
+        <v>15138</v>
+      </c>
+      <c r="AF283" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 2 900 €</v>
+      </c>
+      <c r="AG283" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH283" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI283" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ283" s="10"/>
       <c r="AK283" s="10"/>
-      <c r="AL283" s="10"/>
+      <c r="AL283" s="10" t="s">
+        <v>1934</v>
+      </c>
       <c r="AM283" s="11"/>
       <c r="AN283" s="11" t="s">
         <v>1386</v>
@@ -51667,10 +52266,18 @@
       <c r="AO283" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="AP283" s="11"/>
-      <c r="AQ283" s="11"/>
-      <c r="AR283" s="11"/>
-      <c r="AS283" s="36"/>
+      <c r="AP283" s="11" t="s">
+        <v>1962</v>
+      </c>
+      <c r="AQ283" s="11" t="s">
+        <v>1963</v>
+      </c>
+      <c r="AR283" s="11" t="s">
+        <v>1940</v>
+      </c>
+      <c r="AS283" s="36" t="s">
+        <v>1951</v>
+      </c>
       <c r="AT283" s="11" t="s">
         <v>70</v>
       </c>
@@ -51683,59 +52290,101 @@
       <c r="AW283" s="14"/>
       <c r="AX283" s="44"/>
     </row>
-    <row r="284" spans="1:50">
-      <c r="A284" s="38" t="e">
+    <row r="284" spans="1:50" ht="25.5">
+      <c r="A284" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B284" s="38" t="e">
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B284" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C284" s="38" t="e">
+        <v>Vaucluse</v>
+      </c>
+      <c r="C284" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D284" s="10"/>
-      <c r="E284" s="10"/>
-      <c r="F284" s="10"/>
+        <v>84</v>
+      </c>
+      <c r="D284" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E284" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F284" s="10" t="s">
+        <v>1061</v>
+      </c>
       <c r="G284" s="39" t="str">
-        <f>Tableau1[[#This Row],[Rue]]&amp;Tableau1[[#This Row],[Code Postal]]&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v/>
-      </c>
-      <c r="H284" s="52" t="e" cm="1">
-        <f t="array" aca="1" ref="H284" ca="1">Extrait_hyperlien(#REF!)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I284" s="12"/>
-      <c r="J284" s="12"/>
-      <c r="K284" s="10"/>
-      <c r="L284" s="10"/>
-      <c r="M284" s="12"/>
-      <c r="N284" s="36"/>
-      <c r="O284" s="34"/>
-      <c r="P284" s="12"/>
-      <c r="Q284" s="34"/>
-      <c r="R284" s="10"/>
-      <c r="S284" s="12"/>
-      <c r="T284" s="12"/>
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H284" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I284" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J284" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K284" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L284" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M284" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N284" s="36" t="s">
+        <v>1926</v>
+      </c>
+      <c r="O284" s="34">
+        <v>164</v>
+      </c>
+      <c r="P284" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q284" s="34">
+        <v>610</v>
+      </c>
+      <c r="R284" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S284" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T284" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>32800</v>
+      </c>
       <c r="U284" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V284" s="12"/>
-      <c r="W284" s="12"/>
-      <c r="X284" s="12"/>
+        <v>2733.3333333333335</v>
+      </c>
+      <c r="V284" s="12">
+        <v>200</v>
+      </c>
+      <c r="W284" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X284" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>6560</v>
+      </c>
       <c r="Y284" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z284" s="12"/>
+        <v>546.66666666666663</v>
+      </c>
+      <c r="Z284" s="12">
+        <v>40</v>
+      </c>
       <c r="AA284" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB284" s="12"/>
+        <v>3444</v>
+      </c>
+      <c r="AB284" s="12">
+        <v>21</v>
+      </c>
       <c r="AC284" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -51743,15 +52392,26 @@
       <c r="AD284" s="12"/>
       <c r="AE284" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF284" s="12"/>
-      <c r="AG284" s="12"/>
-      <c r="AH284" s="12"/>
-      <c r="AI284" s="12"/>
+        <v>42804</v>
+      </c>
+      <c r="AF284" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 8 200 €</v>
+      </c>
+      <c r="AG284" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH284" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI284" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ284" s="10"/>
       <c r="AK284" s="10"/>
-      <c r="AL284" s="10"/>
+      <c r="AL284" s="10" t="s">
+        <v>1934</v>
+      </c>
       <c r="AM284" s="11"/>
       <c r="AN284" s="11" t="s">
         <v>1386</v>
@@ -51759,23 +52419,4467 @@
       <c r="AO284" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="AP284" s="11"/>
-      <c r="AQ284" s="11"/>
-      <c r="AR284" s="11"/>
-      <c r="AS284" s="36"/>
-      <c r="AT284" s="11"/>
-      <c r="AU284" s="11"/>
-      <c r="AV284" s="13"/>
+      <c r="AP284" s="11" t="s">
+        <v>1964</v>
+      </c>
+      <c r="AQ284" s="11" t="s">
+        <v>1965</v>
+      </c>
+      <c r="AR284" s="11" t="s">
+        <v>1941</v>
+      </c>
+      <c r="AS284" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT284" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU284" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV284" s="13" t="s">
+        <v>1871</v>
+      </c>
       <c r="AW284" s="14"/>
       <c r="AX284" s="44"/>
     </row>
-    <row r="298" spans="6:6">
-      <c r="F298" s="1" t="s">
+    <row r="285" spans="1:50" ht="25.5">
+      <c r="A285" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B285" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C285" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D285" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E285" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F285" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G285" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H285" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I285" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J285" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K285" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L285" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M285" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N285" s="36" t="s">
+        <v>1927</v>
+      </c>
+      <c r="O285" s="34">
+        <v>278</v>
+      </c>
+      <c r="P285" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q285" s="34">
+        <v>610</v>
+      </c>
+      <c r="R285" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S285" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T285" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>55600</v>
+      </c>
+      <c r="U285" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4633.333333333333</v>
+      </c>
+      <c r="V285" s="12">
+        <v>200</v>
+      </c>
+      <c r="W285" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X285" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11120</v>
+      </c>
+      <c r="Y285" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>926.66666666666663</v>
+      </c>
+      <c r="Z285" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA285" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>5838</v>
+      </c>
+      <c r="AB285" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC285" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD285" s="12"/>
+      <c r="AE285" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>72558</v>
+      </c>
+      <c r="AF285" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 13 900 €</v>
+      </c>
+      <c r="AG285" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH285" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI285" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ285" s="10"/>
+      <c r="AK285" s="10"/>
+      <c r="AL285" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM285" s="11"/>
+      <c r="AN285" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO285" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP285" s="11" t="s">
+        <v>1966</v>
+      </c>
+      <c r="AQ285" s="11" t="s">
+        <v>1967</v>
+      </c>
+      <c r="AR285" s="11" t="s">
+        <v>1942</v>
+      </c>
+      <c r="AS285" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT285" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU285" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV285" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW285" s="14"/>
+      <c r="AX285" s="44"/>
+    </row>
+    <row r="286" spans="1:50" ht="25.5">
+      <c r="A286" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B286" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C286" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D286" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E286" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F286" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G286" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H286" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I286" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J286" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K286" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L286" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M286" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N286" s="36" t="s">
+        <v>1928</v>
+      </c>
+      <c r="O286" s="34">
+        <v>54</v>
+      </c>
+      <c r="P286" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q286" s="34">
+        <v>610</v>
+      </c>
+      <c r="R286" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S286" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T286" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>10800</v>
+      </c>
+      <c r="U286" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>900</v>
+      </c>
+      <c r="V286" s="12">
+        <v>200</v>
+      </c>
+      <c r="W286" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X286" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2160</v>
+      </c>
+      <c r="Y286" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>180</v>
+      </c>
+      <c r="Z286" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA286" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1134</v>
+      </c>
+      <c r="AB286" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC286" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD286" s="12"/>
+      <c r="AE286" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>14094</v>
+      </c>
+      <c r="AF286" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 2 700 €</v>
+      </c>
+      <c r="AG286" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH286" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI286" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ286" s="10"/>
+      <c r="AK286" s="10"/>
+      <c r="AL286" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM286" s="11"/>
+      <c r="AN286" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO286" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP286" s="11" t="s">
+        <v>1968</v>
+      </c>
+      <c r="AQ286" s="11" t="s">
+        <v>1969</v>
+      </c>
+      <c r="AR286" s="11" t="s">
+        <v>1943</v>
+      </c>
+      <c r="AS286" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT286" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU286" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV286" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW286" s="14"/>
+      <c r="AX286" s="44"/>
+    </row>
+    <row r="287" spans="1:50" ht="25.5">
+      <c r="A287" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B287" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C287" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D287" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E287" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F287" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G287" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H287" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I287" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J287" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K287" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L287" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M287" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N287" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="O287" s="34">
+        <v>56</v>
+      </c>
+      <c r="P287" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q287" s="34">
+        <v>610</v>
+      </c>
+      <c r="R287" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S287" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T287" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11200</v>
+      </c>
+      <c r="U287" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>933.33333333333337</v>
+      </c>
+      <c r="V287" s="12">
+        <v>200</v>
+      </c>
+      <c r="W287" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X287" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2240</v>
+      </c>
+      <c r="Y287" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>186.66666666666666</v>
+      </c>
+      <c r="Z287" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA287" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1176</v>
+      </c>
+      <c r="AB287" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC287" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD287" s="12"/>
+      <c r="AE287" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>14616</v>
+      </c>
+      <c r="AF287" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 2 800 €</v>
+      </c>
+      <c r="AG287" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH287" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI287" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ287" s="10"/>
+      <c r="AK287" s="10"/>
+      <c r="AL287" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM287" s="11"/>
+      <c r="AN287" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO287" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP287" s="11" t="s">
+        <v>1970</v>
+      </c>
+      <c r="AQ287" s="11" t="s">
+        <v>1971</v>
+      </c>
+      <c r="AR287" s="11" t="s">
+        <v>1944</v>
+      </c>
+      <c r="AS287" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT287" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU287" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV287" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW287" s="14"/>
+      <c r="AX287" s="44"/>
+    </row>
+    <row r="288" spans="1:50" ht="25.5">
+      <c r="A288" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B288" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C288" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D288" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E288" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F288" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G288" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H288" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I288" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J288" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K288" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L288" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M288" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N288" s="36" t="s">
+        <v>1929</v>
+      </c>
+      <c r="O288" s="34">
+        <v>107</v>
+      </c>
+      <c r="P288" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q288" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R288" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S288" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T288" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>21400</v>
+      </c>
+      <c r="U288" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1783.3333333333333</v>
+      </c>
+      <c r="V288" s="12">
+        <v>200</v>
+      </c>
+      <c r="W288" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X288" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>4280</v>
+      </c>
+      <c r="Y288" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>356.66666666666669</v>
+      </c>
+      <c r="Z288" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA288" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2247</v>
+      </c>
+      <c r="AB288" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC288" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD288" s="12"/>
+      <c r="AE288" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>27927</v>
+      </c>
+      <c r="AF288" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 5 350 €</v>
+      </c>
+      <c r="AG288" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH288" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI288" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ288" s="10"/>
+      <c r="AK288" s="10"/>
+      <c r="AL288" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM288" s="11"/>
+      <c r="AN288" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO288" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP288" s="11" t="s">
+        <v>1972</v>
+      </c>
+      <c r="AQ288" s="11" t="s">
+        <v>1973</v>
+      </c>
+      <c r="AR288" s="11" t="s">
+        <v>1945</v>
+      </c>
+      <c r="AS288" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT288" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU288" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV288" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW288" s="14"/>
+      <c r="AX288" s="44"/>
+    </row>
+    <row r="289" spans="1:50" ht="25.5">
+      <c r="A289" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B289" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C289" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D289" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E289" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F289" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G289" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H289" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I289" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J289" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K289" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L289" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M289" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N289" s="36" t="s">
+        <v>1930</v>
+      </c>
+      <c r="O289" s="34">
+        <v>63</v>
+      </c>
+      <c r="P289" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q289" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R289" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S289" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T289" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>12600</v>
+      </c>
+      <c r="U289" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1050</v>
+      </c>
+      <c r="V289" s="12">
+        <v>200</v>
+      </c>
+      <c r="W289" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X289" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2520</v>
+      </c>
+      <c r="Y289" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>210</v>
+      </c>
+      <c r="Z289" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA289" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1323</v>
+      </c>
+      <c r="AB289" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC289" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD289" s="12"/>
+      <c r="AE289" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>16443</v>
+      </c>
+      <c r="AF289" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 3 150 €</v>
+      </c>
+      <c r="AG289" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH289" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI289" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ289" s="10"/>
+      <c r="AK289" s="10"/>
+      <c r="AL289" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM289" s="11"/>
+      <c r="AN289" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO289" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP289" s="11" t="s">
+        <v>1974</v>
+      </c>
+      <c r="AQ289" s="11" t="s">
+        <v>1975</v>
+      </c>
+      <c r="AR289" s="11" t="s">
+        <v>1946</v>
+      </c>
+      <c r="AS289" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT289" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU289" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV289" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW289" s="14"/>
+      <c r="AX289" s="44"/>
+    </row>
+    <row r="290" spans="1:50" ht="25.5">
+      <c r="A290" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B290" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C290" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D290" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E290" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F290" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G290" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H290" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I290" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J290" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K290" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L290" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M290" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N290" s="36" t="s">
+        <v>1931</v>
+      </c>
+      <c r="O290" s="34">
+        <v>282</v>
+      </c>
+      <c r="P290" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q290" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R290" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S290" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T290" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>56400</v>
+      </c>
+      <c r="U290" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>4700</v>
+      </c>
+      <c r="V290" s="12">
+        <v>200</v>
+      </c>
+      <c r="W290" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X290" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>11280</v>
+      </c>
+      <c r="Y290" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>940</v>
+      </c>
+      <c r="Z290" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA290" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>5922</v>
+      </c>
+      <c r="AB290" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC290" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD290" s="12"/>
+      <c r="AE290" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>73602</v>
+      </c>
+      <c r="AF290" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 14 100 €</v>
+      </c>
+      <c r="AG290" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH290" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI290" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ290" s="10"/>
+      <c r="AK290" s="10"/>
+      <c r="AL290" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM290" s="11"/>
+      <c r="AN290" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO290" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP290" s="11" t="s">
+        <v>1976</v>
+      </c>
+      <c r="AQ290" s="11" t="s">
+        <v>1977</v>
+      </c>
+      <c r="AR290" s="11" t="s">
+        <v>1947</v>
+      </c>
+      <c r="AS290" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT290" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU290" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV290" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW290" s="14"/>
+      <c r="AX290" s="44"/>
+    </row>
+    <row r="291" spans="1:50" ht="25.5">
+      <c r="A291" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B291" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C291" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D291" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E291" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F291" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G291" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H291" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I291" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J291" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K291" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L291" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M291" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N291" s="36" t="s">
+        <v>1932</v>
+      </c>
+      <c r="O291" s="34">
+        <v>104</v>
+      </c>
+      <c r="P291" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q291" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R291" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S291" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T291" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>20800</v>
+      </c>
+      <c r="U291" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1733.3333333333333</v>
+      </c>
+      <c r="V291" s="12">
+        <v>200</v>
+      </c>
+      <c r="W291" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X291" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>4160</v>
+      </c>
+      <c r="Y291" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>346.66666666666669</v>
+      </c>
+      <c r="Z291" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA291" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2184</v>
+      </c>
+      <c r="AB291" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC291" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD291" s="12"/>
+      <c r="AE291" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>27144</v>
+      </c>
+      <c r="AF291" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 5 200 €</v>
+      </c>
+      <c r="AG291" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH291" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI291" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ291" s="10"/>
+      <c r="AK291" s="10"/>
+      <c r="AL291" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM291" s="11"/>
+      <c r="AN291" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO291" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP291" s="11" t="s">
+        <v>1978</v>
+      </c>
+      <c r="AQ291" s="11" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AR291" s="11" t="s">
+        <v>1948</v>
+      </c>
+      <c r="AS291" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT291" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU291" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV291" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW291" s="14"/>
+      <c r="AX291" s="44"/>
+    </row>
+    <row r="292" spans="1:50" ht="25.5">
+      <c r="A292" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B292" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C292" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D292" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E292" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F292" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G292" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H292" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I292" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J292" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K292" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L292" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M292" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N292" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="O292" s="34">
+        <v>142</v>
+      </c>
+      <c r="P292" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q292" s="34">
+        <v>184</v>
+      </c>
+      <c r="R292" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S292" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T292" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>28400</v>
+      </c>
+      <c r="U292" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2366.6666666666665</v>
+      </c>
+      <c r="V292" s="12">
+        <v>200</v>
+      </c>
+      <c r="W292" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X292" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>5680</v>
+      </c>
+      <c r="Y292" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>473.33333333333331</v>
+      </c>
+      <c r="Z292" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA292" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2982</v>
+      </c>
+      <c r="AB292" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC292" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD292" s="12"/>
+      <c r="AE292" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>37062</v>
+      </c>
+      <c r="AF292" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 7 100 €</v>
+      </c>
+      <c r="AG292" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH292" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI292" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ292" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK292" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="AL292" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM292" s="11"/>
+      <c r="AN292" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO292" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP292" s="11" t="s">
+        <v>1980</v>
+      </c>
+      <c r="AQ292" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="AR292" s="11" t="s">
+        <v>1949</v>
+      </c>
+      <c r="AS292" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT292" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU292" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV292" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW292" s="14"/>
+      <c r="AX292" s="44"/>
+    </row>
+    <row r="293" spans="1:50" ht="25.5">
+      <c r="A293" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Provence-Alpes-Côte d'Azur</v>
+      </c>
+      <c r="B293" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Vaucluse</v>
+      </c>
+      <c r="C293" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>84</v>
+      </c>
+      <c r="D293" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E293" s="26">
+        <v>84000</v>
+      </c>
+      <c r="F293" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G293" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>390 Rue Jean Marie Tjibaou
+84000 - Avignon</v>
+      </c>
+      <c r="H293" s="15" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I293" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J293" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K293" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L293" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M293" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N293" s="36" t="s">
+        <v>1933</v>
+      </c>
+      <c r="O293" s="34">
+        <v>172</v>
+      </c>
+      <c r="P293" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q293" s="34">
+        <v>184</v>
+      </c>
+      <c r="R293" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S293" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T293" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>34400</v>
+      </c>
+      <c r="U293" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2866.6666666666665</v>
+      </c>
+      <c r="V293" s="12">
+        <v>200</v>
+      </c>
+      <c r="W293" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X293" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>6880</v>
+      </c>
+      <c r="Y293" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>573.33333333333337</v>
+      </c>
+      <c r="Z293" s="12">
+        <v>40</v>
+      </c>
+      <c r="AA293" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3612</v>
+      </c>
+      <c r="AB293" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC293" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD293" s="12"/>
+      <c r="AE293" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>44892</v>
+      </c>
+      <c r="AF293" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 8 600 €</v>
+      </c>
+      <c r="AG293" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH293" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI293" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ293" s="10"/>
+      <c r="AK293" s="10"/>
+      <c r="AL293" s="10" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AM293" s="11"/>
+      <c r="AN293" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO293" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP293" s="11" t="s">
+        <v>1982</v>
+      </c>
+      <c r="AQ293" s="11" t="s">
+        <v>1983</v>
+      </c>
+      <c r="AR293" s="11" t="s">
+        <v>1950</v>
+      </c>
+      <c r="AS293" s="36" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AT293" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU293" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV293" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW293" s="14"/>
+      <c r="AX293" s="44"/>
+    </row>
+    <row r="294" spans="1:50" ht="38.25">
+      <c r="A294" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B294" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C294" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D294" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E294" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F294" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G294" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H294" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I294" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J294" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K294" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L294" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M294" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N294" s="36" t="s">
+        <v>1560</v>
+      </c>
+      <c r="O294" s="34">
+        <v>51</v>
+      </c>
+      <c r="P294" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q294" s="34">
+        <v>162</v>
+      </c>
+      <c r="R294" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S294" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T294" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>10200</v>
+      </c>
+      <c r="U294" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>850</v>
+      </c>
+      <c r="V294" s="12">
+        <v>200</v>
+      </c>
+      <c r="W294" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X294" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2805</v>
+      </c>
+      <c r="Y294" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>233.75</v>
+      </c>
+      <c r="Z294" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA294" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>714</v>
+      </c>
+      <c r="AB294" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC294" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD294" s="12"/>
+      <c r="AE294" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>13719</v>
+      </c>
+      <c r="AF294" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 2 550 €</v>
+      </c>
+      <c r="AG294" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH294" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI294" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ294" s="10"/>
+      <c r="AK294" s="10"/>
+      <c r="AL294" s="10"/>
+      <c r="AM294" s="11"/>
+      <c r="AN294" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO294" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP294" s="11" t="s">
+        <v>2002</v>
+      </c>
+      <c r="AQ294" s="11" t="s">
+        <v>2003</v>
+      </c>
+      <c r="AR294" s="11" t="s">
+        <v>1988</v>
+      </c>
+      <c r="AS294" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT294" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU294" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV294" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW294" s="14"/>
+      <c r="AX294" s="44"/>
+    </row>
+    <row r="295" spans="1:50" ht="38.25">
+      <c r="A295" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B295" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C295" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D295" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E295" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F295" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G295" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H295" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I295" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J295" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K295" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L295" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M295" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N295" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="O295" s="34">
+        <v>111</v>
+      </c>
+      <c r="P295" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q295" s="34">
+        <v>162</v>
+      </c>
+      <c r="R295" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S295" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T295" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>22200</v>
+      </c>
+      <c r="U295" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1850</v>
+      </c>
+      <c r="V295" s="12">
+        <v>200</v>
+      </c>
+      <c r="W295" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X295" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>6105</v>
+      </c>
+      <c r="Y295" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>508.75</v>
+      </c>
+      <c r="Z295" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA295" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1554</v>
+      </c>
+      <c r="AB295" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC295" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD295" s="12"/>
+      <c r="AE295" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>29859</v>
+      </c>
+      <c r="AF295" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 5 550 €</v>
+      </c>
+      <c r="AG295" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH295" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI295" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ295" s="10"/>
+      <c r="AK295" s="10"/>
+      <c r="AL295" s="10"/>
+      <c r="AM295" s="11"/>
+      <c r="AN295" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO295" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP295" s="11" t="s">
+        <v>2000</v>
+      </c>
+      <c r="AQ295" s="11" t="s">
+        <v>2001</v>
+      </c>
+      <c r="AR295" s="11" t="s">
+        <v>1989</v>
+      </c>
+      <c r="AS295" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT295" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU295" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV295" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW295" s="14"/>
+      <c r="AX295" s="44"/>
+    </row>
+    <row r="296" spans="1:50" ht="38.25">
+      <c r="A296" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B296" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C296" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D296" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E296" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F296" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G296" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H296" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I296" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J296" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K296" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L296" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M296" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N296" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="O296" s="34">
+        <v>68</v>
+      </c>
+      <c r="P296" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q296" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R296" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S296" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T296" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>13600</v>
+      </c>
+      <c r="U296" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1133.3333333333333</v>
+      </c>
+      <c r="V296" s="12">
+        <v>200</v>
+      </c>
+      <c r="W296" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X296" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>3740</v>
+      </c>
+      <c r="Y296" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>311.66666666666669</v>
+      </c>
+      <c r="Z296" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA296" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>952</v>
+      </c>
+      <c r="AB296" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC296" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD296" s="12"/>
+      <c r="AE296" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>18292</v>
+      </c>
+      <c r="AF296" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 3 400 €</v>
+      </c>
+      <c r="AG296" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH296" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI296" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ296" s="10"/>
+      <c r="AK296" s="10"/>
+      <c r="AL296" s="10"/>
+      <c r="AM296" s="11"/>
+      <c r="AN296" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO296" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP296" s="11" t="s">
+        <v>1998</v>
+      </c>
+      <c r="AQ296" s="11" t="s">
+        <v>1999</v>
+      </c>
+      <c r="AR296" s="11" t="s">
+        <v>1990</v>
+      </c>
+      <c r="AS296" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT296" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU296" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV296" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW296" s="14"/>
+      <c r="AX296" s="44"/>
+    </row>
+    <row r="297" spans="1:50" ht="38.25">
+      <c r="A297" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B297" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C297" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D297" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E297" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F297" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G297" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H297" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I297" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J297" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K297" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L297" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M297" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N297" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="O297" s="34">
+        <v>794</v>
+      </c>
+      <c r="P297" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q297" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R297" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S297" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T297" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>158800</v>
+      </c>
+      <c r="U297" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>13233.333333333334</v>
+      </c>
+      <c r="V297" s="12">
+        <v>200</v>
+      </c>
+      <c r="W297" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X297" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>43670</v>
+      </c>
+      <c r="Y297" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>3639.1666666666665</v>
+      </c>
+      <c r="Z297" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA297" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>11116</v>
+      </c>
+      <c r="AB297" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC297" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD297" s="12"/>
+      <c r="AE297" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>213586</v>
+      </c>
+      <c r="AF297" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 39 700 €</v>
+      </c>
+      <c r="AG297" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH297" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI297" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ297" s="10"/>
+      <c r="AK297" s="10"/>
+      <c r="AL297" s="10"/>
+      <c r="AM297" s="11"/>
+      <c r="AN297" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO297" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP297" s="11" t="s">
+        <v>1996</v>
+      </c>
+      <c r="AQ297" s="11" t="s">
+        <v>1997</v>
+      </c>
+      <c r="AR297" s="11" t="s">
+        <v>1991</v>
+      </c>
+      <c r="AS297" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT297" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU297" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV297" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW297" s="14"/>
+      <c r="AX297" s="44"/>
+    </row>
+    <row r="298" spans="1:50" ht="38.25">
+      <c r="A298" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B298" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C298" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E298" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F298" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G298" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H298" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I298" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J298" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K298" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L298" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M298" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N298" s="36" t="s">
+        <v>1987</v>
+      </c>
+      <c r="O298" s="34">
+        <v>100</v>
+      </c>
+      <c r="P298" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q298" s="34">
+        <v>221</v>
+      </c>
+      <c r="R298" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S298" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T298" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>20000</v>
+      </c>
+      <c r="U298" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1666.6666666666667</v>
+      </c>
+      <c r="V298" s="12">
+        <v>200</v>
+      </c>
+      <c r="W298" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X298" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>5500</v>
+      </c>
+      <c r="Y298" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>458.33333333333331</v>
+      </c>
+      <c r="Z298" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA298" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1400</v>
+      </c>
+      <c r="AB298" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC298" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD298" s="12"/>
+      <c r="AE298" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>26900</v>
+      </c>
+      <c r="AF298" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 5 000 €</v>
+      </c>
+      <c r="AG298" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH298" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI298" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ298" s="10"/>
+      <c r="AK298" s="10"/>
+      <c r="AL298" s="10"/>
+      <c r="AM298" s="11"/>
+      <c r="AN298" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO298" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP298" s="11" t="s">
+        <v>2008</v>
+      </c>
+      <c r="AQ298" s="11" t="s">
+        <v>2009</v>
+      </c>
+      <c r="AR298" s="11" t="s">
+        <v>1992</v>
+      </c>
+      <c r="AS298" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT298" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU298" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV298" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW298" s="14"/>
+      <c r="AX298" s="44"/>
+    </row>
+    <row r="299" spans="1:50" ht="38.25">
+      <c r="A299" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B299" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C299" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D299" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E299" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F299" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G299" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H299" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I299" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J299" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K299" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L299" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M299" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N299" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="O299" s="34">
+        <v>100</v>
+      </c>
+      <c r="P299" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q299" s="34">
+        <v>221</v>
+      </c>
+      <c r="R299" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S299" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T299" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>20000</v>
+      </c>
+      <c r="U299" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1666.6666666666667</v>
+      </c>
+      <c r="V299" s="12">
+        <v>200</v>
+      </c>
+      <c r="W299" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X299" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>5500</v>
+      </c>
+      <c r="Y299" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>458.33333333333331</v>
+      </c>
+      <c r="Z299" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA299" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1400</v>
+      </c>
+      <c r="AB299" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC299" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD299" s="12"/>
+      <c r="AE299" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>26900</v>
+      </c>
+      <c r="AF299" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 5 000 €</v>
+      </c>
+      <c r="AG299" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH299" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI299" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ299" s="10"/>
+      <c r="AK299" s="10"/>
+      <c r="AL299" s="10"/>
+      <c r="AM299" s="11"/>
+      <c r="AN299" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO299" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP299" s="11" t="s">
+        <v>2007</v>
+      </c>
+      <c r="AQ299" s="11" t="s">
+        <v>2006</v>
+      </c>
+      <c r="AR299" s="11" t="s">
+        <v>1993</v>
+      </c>
+      <c r="AS299" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT299" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU299" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV299" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW299" s="14"/>
+      <c r="AX299" s="44"/>
+    </row>
+    <row r="300" spans="1:50" ht="38.25">
+      <c r="A300" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B300" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C300" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D300" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E300" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F300" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G300" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H300" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I300" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J300" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K300" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L300" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M300" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N300" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="O300" s="34">
+        <v>37</v>
+      </c>
+      <c r="P300" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q300" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R300" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S300" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T300" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>7400</v>
+      </c>
+      <c r="U300" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>616.66666666666663</v>
+      </c>
+      <c r="V300" s="12">
+        <v>200</v>
+      </c>
+      <c r="W300" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X300" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>2035</v>
+      </c>
+      <c r="Y300" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>169.58333333333334</v>
+      </c>
+      <c r="Z300" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA300" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>518</v>
+      </c>
+      <c r="AB300" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC300" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD300" s="12"/>
+      <c r="AE300" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>9953</v>
+      </c>
+      <c r="AF300" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 1 850 €</v>
+      </c>
+      <c r="AG300" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH300" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI300" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ300" s="10"/>
+      <c r="AK300" s="10"/>
+      <c r="AL300" s="10"/>
+      <c r="AM300" s="11"/>
+      <c r="AN300" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO300" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP300" s="11" t="s">
+        <v>2004</v>
+      </c>
+      <c r="AQ300" s="11" t="s">
+        <v>2005</v>
+      </c>
+      <c r="AR300" s="11" t="s">
+        <v>1994</v>
+      </c>
+      <c r="AS300" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT300" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU300" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV300" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW300" s="14"/>
+      <c r="AX300" s="44"/>
+    </row>
+    <row r="301" spans="1:50" ht="25.5">
+      <c r="A301" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B301" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C301" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D301" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E301" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F301" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G301" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H301" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I301" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J301" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K301" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L301" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M301" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N301" s="36" t="s">
+        <v>462</v>
+      </c>
+      <c r="O301" s="34">
+        <v>21</v>
+      </c>
+      <c r="P301" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q301" s="34">
+        <v>221</v>
+      </c>
+      <c r="R301" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S301" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T301" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>4200</v>
+      </c>
+      <c r="U301" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>350</v>
+      </c>
+      <c r="V301" s="12">
+        <v>200</v>
+      </c>
+      <c r="W301" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X301" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>1155</v>
+      </c>
+      <c r="Y301" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>96.25</v>
+      </c>
+      <c r="Z301" s="12">
+        <v>55</v>
+      </c>
+      <c r="AA301" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>294</v>
+      </c>
+      <c r="AB301" s="12">
+        <v>14</v>
+      </c>
+      <c r="AC301" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD301" s="12"/>
+      <c r="AE301" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>5649</v>
+      </c>
+      <c r="AF301" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 1 050 €</v>
+      </c>
+      <c r="AG301" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH301" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI301" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ301" s="10"/>
+      <c r="AK301" s="10"/>
+      <c r="AL301" s="10"/>
+      <c r="AM301" s="11"/>
+      <c r="AN301" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO301" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP301" s="11" t="s">
+        <v>2010</v>
+      </c>
+      <c r="AQ301" s="11" t="s">
+        <v>2011</v>
+      </c>
+      <c r="AR301" s="11" t="s">
+        <v>1995</v>
+      </c>
+      <c r="AS301" s="36" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AT301" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU301" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV301" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW301" s="14"/>
+      <c r="AX301" s="44"/>
+    </row>
+    <row r="302" spans="1:50" ht="25.5">
+      <c r="A302" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Bourgogne-Franche-Comté</v>
+      </c>
+      <c r="B302" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Côte-d'Or</v>
+      </c>
+      <c r="C302" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>21</v>
+      </c>
+      <c r="D302" s="10" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E302" s="26">
+        <v>21200</v>
+      </c>
+      <c r="F302" s="10" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G302" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Beaune St-Jacques, 9 Av. du Général de Gaulle
+21200 - Beaune</v>
+      </c>
+      <c r="H302" s="15" t="s">
+        <v>2013</v>
+      </c>
+      <c r="I302" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J302" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K302" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L302" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M302" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N302" s="36" t="s">
+        <v>351</v>
+      </c>
+      <c r="O302" s="34">
+        <v>176</v>
+      </c>
+      <c r="P302" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q302" s="34">
+        <v>593</v>
+      </c>
+      <c r="R302" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S302" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T302" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>35200</v>
+      </c>
+      <c r="U302" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2933.3333333333335</v>
+      </c>
+      <c r="V302" s="12">
+        <v>200</v>
+      </c>
+      <c r="W302" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X302" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>7920</v>
+      </c>
+      <c r="Y302" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>660</v>
+      </c>
+      <c r="Z302" s="12">
+        <v>45</v>
+      </c>
+      <c r="AA302" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>3520</v>
+      </c>
+      <c r="AB302" s="12">
+        <v>20</v>
+      </c>
+      <c r="AC302" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD302" s="12"/>
+      <c r="AE302" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>46640</v>
+      </c>
+      <c r="AF302" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 8 800 €</v>
+      </c>
+      <c r="AG302" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH302" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI302" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ302" s="10"/>
+      <c r="AK302" s="10"/>
+      <c r="AL302" s="10"/>
+      <c r="AM302" s="11"/>
+      <c r="AN302" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO302" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP302" s="11" t="s">
+        <v>2020</v>
+      </c>
+      <c r="AQ302" s="11" t="s">
+        <v>2021</v>
+      </c>
+      <c r="AR302" s="11" t="s">
+        <v>2016</v>
+      </c>
+      <c r="AS302" s="36" t="s">
+        <v>2029</v>
+      </c>
+      <c r="AT302" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU302" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV302" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW302" s="14"/>
+      <c r="AX302" s="44"/>
+    </row>
+    <row r="303" spans="1:50" ht="25.5">
+      <c r="A303" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Bourgogne-Franche-Comté</v>
+      </c>
+      <c r="B303" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Côte-d'Or</v>
+      </c>
+      <c r="C303" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>21</v>
+      </c>
+      <c r="D303" s="10" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E303" s="26">
+        <v>21200</v>
+      </c>
+      <c r="F303" s="10" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G303" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Beaune St-Jacques, 9 Av. du Général de Gaulle
+21200 - Beaune</v>
+      </c>
+      <c r="H303" s="15" t="s">
+        <v>2013</v>
+      </c>
+      <c r="I303" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J303" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K303" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L303" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M303" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N303" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="O303" s="34">
+        <v>417</v>
+      </c>
+      <c r="P303" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q303" s="34">
+        <v>593</v>
+      </c>
+      <c r="R303" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S303" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T303" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>83400</v>
+      </c>
+      <c r="U303" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>6950</v>
+      </c>
+      <c r="V303" s="12">
+        <v>200</v>
+      </c>
+      <c r="W303" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X303" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>18765</v>
+      </c>
+      <c r="Y303" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>1563.75</v>
+      </c>
+      <c r="Z303" s="12">
+        <v>45</v>
+      </c>
+      <c r="AA303" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>8340</v>
+      </c>
+      <c r="AB303" s="12">
+        <v>20</v>
+      </c>
+      <c r="AC303" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD303" s="12"/>
+      <c r="AE303" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>110505</v>
+      </c>
+      <c r="AF303" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 20 850 €</v>
+      </c>
+      <c r="AG303" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH303" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI303" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ303" s="10"/>
+      <c r="AK303" s="10"/>
+      <c r="AL303" s="10"/>
+      <c r="AM303" s="11"/>
+      <c r="AN303" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO303" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP303" s="11" t="s">
+        <v>2022</v>
+      </c>
+      <c r="AQ303" s="11" t="s">
+        <v>2023</v>
+      </c>
+      <c r="AR303" s="11" t="s">
+        <v>2017</v>
+      </c>
+      <c r="AS303" s="36" t="s">
+        <v>2029</v>
+      </c>
+      <c r="AT303" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU303" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV303" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW303" s="14"/>
+      <c r="AX303" s="44"/>
+    </row>
+    <row r="304" spans="1:50" ht="25.5">
+      <c r="A304" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Bourgogne-Franche-Comté</v>
+      </c>
+      <c r="B304" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Côte-d'Or</v>
+      </c>
+      <c r="C304" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>21</v>
+      </c>
+      <c r="D304" s="10" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E304" s="26">
+        <v>21200</v>
+      </c>
+      <c r="F304" s="10" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G304" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Beaune St-Jacques, 9 Av. du Général de Gaulle
+21200 - Beaune</v>
+      </c>
+      <c r="H304" s="15" t="s">
+        <v>2013</v>
+      </c>
+      <c r="I304" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J304" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K304" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L304" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M304" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N304" s="36" t="s">
+        <v>465</v>
+      </c>
+      <c r="O304" s="34">
+        <v>145</v>
+      </c>
+      <c r="P304" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q304" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R304" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S304" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T304" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>29000</v>
+      </c>
+      <c r="U304" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>2416.6666666666665</v>
+      </c>
+      <c r="V304" s="12">
+        <v>200</v>
+      </c>
+      <c r="W304" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X304" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>6525</v>
+      </c>
+      <c r="Y304" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>543.75</v>
+      </c>
+      <c r="Z304" s="12">
+        <v>45</v>
+      </c>
+      <c r="AA304" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>2900</v>
+      </c>
+      <c r="AB304" s="12">
+        <v>20</v>
+      </c>
+      <c r="AC304" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD304" s="12"/>
+      <c r="AE304" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>38425</v>
+      </c>
+      <c r="AF304" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 7 250 €</v>
+      </c>
+      <c r="AG304" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH304" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI304" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ304" s="10"/>
+      <c r="AK304" s="10"/>
+      <c r="AL304" s="10"/>
+      <c r="AM304" s="11"/>
+      <c r="AN304" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO304" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP304" s="11" t="s">
+        <v>2024</v>
+      </c>
+      <c r="AQ304" s="11" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AR304" s="11" t="s">
+        <v>2018</v>
+      </c>
+      <c r="AS304" s="36" t="s">
+        <v>2029</v>
+      </c>
+      <c r="AT304" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU304" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV304" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW304" s="14"/>
+      <c r="AX304" s="44"/>
+    </row>
+    <row r="305" spans="1:50" ht="25.5">
+      <c r="A305" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Bourgogne-Franche-Comté</v>
+      </c>
+      <c r="B305" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Côte-d'Or</v>
+      </c>
+      <c r="C305" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>21</v>
+      </c>
+      <c r="D305" s="10" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E305" s="26">
+        <v>21200</v>
+      </c>
+      <c r="F305" s="10" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G305" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Beaune St-Jacques, 9 Av. du Général de Gaulle
+21200 - Beaune</v>
+      </c>
+      <c r="H305" s="15" t="s">
+        <v>2013</v>
+      </c>
+      <c r="I305" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J305" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K305" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L305" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M305" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N305" s="36" t="s">
+        <v>466</v>
+      </c>
+      <c r="O305" s="34">
+        <v>91</v>
+      </c>
+      <c r="P305" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q305" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R305" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S305" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T305" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>18200</v>
+      </c>
+      <c r="U305" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>1516.6666666666667</v>
+      </c>
+      <c r="V305" s="12">
+        <v>200</v>
+      </c>
+      <c r="W305" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X305" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>4095</v>
+      </c>
+      <c r="Y305" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>341.25</v>
+      </c>
+      <c r="Z305" s="12">
+        <v>45</v>
+      </c>
+      <c r="AA305" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>1820</v>
+      </c>
+      <c r="AB305" s="12">
+        <v>20</v>
+      </c>
+      <c r="AC305" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD305" s="12"/>
+      <c r="AE305" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>24115</v>
+      </c>
+      <c r="AF305" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 4 550 €</v>
+      </c>
+      <c r="AG305" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH305" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI305" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ305" s="10"/>
+      <c r="AK305" s="10"/>
+      <c r="AL305" s="10"/>
+      <c r="AM305" s="11"/>
+      <c r="AN305" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO305" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP305" s="11" t="s">
+        <v>2026</v>
+      </c>
+      <c r="AQ305" s="11" t="s">
+        <v>2027</v>
+      </c>
+      <c r="AR305" s="11" t="s">
+        <v>2019</v>
+      </c>
+      <c r="AS305" s="36" t="s">
+        <v>2029</v>
+      </c>
+      <c r="AT305" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU305" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV305" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AW305" s="14"/>
+      <c r="AX305" s="44"/>
+    </row>
+    <row r="306" spans="1:50" ht="38.25">
+      <c r="A306" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B306" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C306" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D306" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E306" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F306" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G306" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H306" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I306" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J306" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K306" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L306" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M306" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N306" s="36"/>
+      <c r="O306" s="34"/>
+      <c r="P306" s="12"/>
+      <c r="Q306" s="34"/>
+      <c r="R306" s="10"/>
+      <c r="S306" s="12"/>
+      <c r="T306" s="12"/>
+      <c r="U306" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V306" s="12"/>
+      <c r="W306" s="12"/>
+      <c r="X306" s="12"/>
+      <c r="Y306" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z306" s="12"/>
+      <c r="AA306" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB306" s="12"/>
+      <c r="AC306" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD306" s="12"/>
+      <c r="AE306" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF306" s="12"/>
+      <c r="AG306" s="12"/>
+      <c r="AH306" s="12"/>
+      <c r="AI306" s="12"/>
+      <c r="AJ306" s="10"/>
+      <c r="AK306" s="10"/>
+      <c r="AL306" s="10"/>
+      <c r="AM306" s="11"/>
+      <c r="AN306" s="11"/>
+      <c r="AO306" s="11"/>
+      <c r="AP306" s="11"/>
+      <c r="AQ306" s="11"/>
+      <c r="AR306" s="11"/>
+      <c r="AS306" s="36"/>
+      <c r="AT306" s="11"/>
+      <c r="AU306" s="11"/>
+      <c r="AV306" s="13"/>
+      <c r="AW306" s="14"/>
+      <c r="AX306" s="44"/>
+    </row>
+    <row r="307" spans="1:50" ht="38.25">
+      <c r="A307" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B307" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C307" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D307" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E307" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F307" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G307" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H307" s="15"/>
+      <c r="I307" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J307" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K307" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L307" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M307" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N307" s="36"/>
+      <c r="O307" s="34"/>
+      <c r="P307" s="12"/>
+      <c r="Q307" s="34"/>
+      <c r="R307" s="10"/>
+      <c r="S307" s="12"/>
+      <c r="T307" s="12"/>
+      <c r="U307" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V307" s="12"/>
+      <c r="W307" s="12"/>
+      <c r="X307" s="12"/>
+      <c r="Y307" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z307" s="12"/>
+      <c r="AA307" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB307" s="12"/>
+      <c r="AC307" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD307" s="12"/>
+      <c r="AE307" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF307" s="12"/>
+      <c r="AG307" s="12"/>
+      <c r="AH307" s="12"/>
+      <c r="AI307" s="12"/>
+      <c r="AJ307" s="10"/>
+      <c r="AK307" s="10"/>
+      <c r="AL307" s="10"/>
+      <c r="AM307" s="11"/>
+      <c r="AN307" s="11"/>
+      <c r="AO307" s="11"/>
+      <c r="AP307" s="11"/>
+      <c r="AQ307" s="11"/>
+      <c r="AR307" s="11"/>
+      <c r="AS307" s="36"/>
+      <c r="AT307" s="11"/>
+      <c r="AU307" s="11"/>
+      <c r="AV307" s="13"/>
+      <c r="AW307" s="14"/>
+      <c r="AX307" s="44"/>
+    </row>
+    <row r="308" spans="1:50" ht="38.25">
+      <c r="A308" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B308" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C308" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D308" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E308" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F308" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G308" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H308" s="15"/>
+      <c r="I308" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J308" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K308" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L308" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M308" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N308" s="36"/>
+      <c r="O308" s="34"/>
+      <c r="P308" s="12"/>
+      <c r="Q308" s="34"/>
+      <c r="R308" s="10"/>
+      <c r="S308" s="12"/>
+      <c r="T308" s="12"/>
+      <c r="U308" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V308" s="12"/>
+      <c r="W308" s="12"/>
+      <c r="X308" s="12"/>
+      <c r="Y308" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z308" s="12"/>
+      <c r="AA308" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB308" s="12"/>
+      <c r="AC308" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD308" s="12"/>
+      <c r="AE308" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF308" s="12"/>
+      <c r="AG308" s="12"/>
+      <c r="AH308" s="12"/>
+      <c r="AI308" s="12"/>
+      <c r="AJ308" s="10"/>
+      <c r="AK308" s="10"/>
+      <c r="AL308" s="10"/>
+      <c r="AM308" s="11"/>
+      <c r="AN308" s="11"/>
+      <c r="AO308" s="11"/>
+      <c r="AP308" s="11"/>
+      <c r="AQ308" s="11"/>
+      <c r="AR308" s="11"/>
+      <c r="AS308" s="36"/>
+      <c r="AT308" s="11"/>
+      <c r="AU308" s="11"/>
+      <c r="AV308" s="13"/>
+      <c r="AW308" s="14"/>
+      <c r="AX308" s="44"/>
+    </row>
+    <row r="309" spans="1:50" ht="38.25">
+      <c r="A309" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B309" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C309" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D309" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E309" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F309" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G309" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H309" s="15"/>
+      <c r="I309" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J309" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K309" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L309" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M309" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N309" s="36"/>
+      <c r="O309" s="34"/>
+      <c r="P309" s="12"/>
+      <c r="Q309" s="34"/>
+      <c r="R309" s="10"/>
+      <c r="S309" s="12"/>
+      <c r="T309" s="12"/>
+      <c r="U309" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V309" s="12"/>
+      <c r="W309" s="12"/>
+      <c r="X309" s="12"/>
+      <c r="Y309" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z309" s="12"/>
+      <c r="AA309" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB309" s="12"/>
+      <c r="AC309" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD309" s="12"/>
+      <c r="AE309" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF309" s="12"/>
+      <c r="AG309" s="12"/>
+      <c r="AH309" s="12"/>
+      <c r="AI309" s="12"/>
+      <c r="AJ309" s="10"/>
+      <c r="AK309" s="10"/>
+      <c r="AL309" s="10"/>
+      <c r="AM309" s="11"/>
+      <c r="AN309" s="11"/>
+      <c r="AO309" s="11"/>
+      <c r="AP309" s="11"/>
+      <c r="AQ309" s="11"/>
+      <c r="AR309" s="11"/>
+      <c r="AS309" s="36"/>
+      <c r="AT309" s="11"/>
+      <c r="AU309" s="11"/>
+      <c r="AV309" s="13"/>
+      <c r="AW309" s="14"/>
+      <c r="AX309" s="44"/>
+    </row>
+    <row r="310" spans="1:50" ht="38.25">
+      <c r="A310" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B310" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C310" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D310" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E310" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F310" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G310" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H310" s="15"/>
+      <c r="I310" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J310" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K310" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L310" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M310" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N310" s="36"/>
+      <c r="O310" s="34"/>
+      <c r="P310" s="12"/>
+      <c r="Q310" s="34"/>
+      <c r="R310" s="10"/>
+      <c r="S310" s="12"/>
+      <c r="T310" s="12"/>
+      <c r="U310" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V310" s="12"/>
+      <c r="W310" s="12"/>
+      <c r="X310" s="12"/>
+      <c r="Y310" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z310" s="12"/>
+      <c r="AA310" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB310" s="12"/>
+      <c r="AC310" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD310" s="12"/>
+      <c r="AE310" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF310" s="12"/>
+      <c r="AG310" s="12"/>
+      <c r="AH310" s="12"/>
+      <c r="AI310" s="12"/>
+      <c r="AJ310" s="10"/>
+      <c r="AK310" s="10"/>
+      <c r="AL310" s="10"/>
+      <c r="AM310" s="11"/>
+      <c r="AN310" s="11"/>
+      <c r="AO310" s="11"/>
+      <c r="AP310" s="11"/>
+      <c r="AQ310" s="11"/>
+      <c r="AR310" s="11"/>
+      <c r="AS310" s="36"/>
+      <c r="AT310" s="11"/>
+      <c r="AU310" s="11"/>
+      <c r="AV310" s="13"/>
+      <c r="AW310" s="14"/>
+      <c r="AX310" s="44"/>
+    </row>
+    <row r="311" spans="1:50" ht="38.25">
+      <c r="A311" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B311" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C311" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D311" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E311" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F311" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G311" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H311" s="15"/>
+      <c r="I311" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J311" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K311" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L311" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M311" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N311" s="36"/>
+      <c r="O311" s="34"/>
+      <c r="P311" s="12"/>
+      <c r="Q311" s="34"/>
+      <c r="R311" s="10"/>
+      <c r="S311" s="12"/>
+      <c r="T311" s="12"/>
+      <c r="U311" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V311" s="12"/>
+      <c r="W311" s="12"/>
+      <c r="X311" s="12"/>
+      <c r="Y311" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z311" s="12"/>
+      <c r="AA311" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB311" s="12"/>
+      <c r="AC311" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD311" s="12"/>
+      <c r="AE311" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF311" s="12"/>
+      <c r="AG311" s="12"/>
+      <c r="AH311" s="12"/>
+      <c r="AI311" s="12"/>
+      <c r="AJ311" s="10"/>
+      <c r="AK311" s="10"/>
+      <c r="AL311" s="10"/>
+      <c r="AM311" s="11"/>
+      <c r="AN311" s="11"/>
+      <c r="AO311" s="11"/>
+      <c r="AP311" s="11"/>
+      <c r="AQ311" s="11"/>
+      <c r="AR311" s="11"/>
+      <c r="AS311" s="36"/>
+      <c r="AT311" s="11"/>
+      <c r="AU311" s="11"/>
+      <c r="AV311" s="13"/>
+      <c r="AW311" s="14"/>
+      <c r="AX311" s="44"/>
+    </row>
+    <row r="312" spans="1:50" ht="38.25">
+      <c r="A312" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B312" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C312" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E312" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F312" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G312" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H312" s="15"/>
+      <c r="I312" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J312" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K312" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L312" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M312" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N312" s="36"/>
+      <c r="O312" s="34"/>
+      <c r="P312" s="12"/>
+      <c r="Q312" s="34"/>
+      <c r="R312" s="10"/>
+      <c r="S312" s="12"/>
+      <c r="T312" s="12"/>
+      <c r="U312" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V312" s="12"/>
+      <c r="W312" s="12"/>
+      <c r="X312" s="12"/>
+      <c r="Y312" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z312" s="12"/>
+      <c r="AA312" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB312" s="12"/>
+      <c r="AC312" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD312" s="12"/>
+      <c r="AE312" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF312" s="12"/>
+      <c r="AG312" s="12"/>
+      <c r="AH312" s="12"/>
+      <c r="AI312" s="12"/>
+      <c r="AJ312" s="10"/>
+      <c r="AK312" s="10"/>
+      <c r="AL312" s="10"/>
+      <c r="AM312" s="11"/>
+      <c r="AN312" s="11"/>
+      <c r="AO312" s="11"/>
+      <c r="AP312" s="11"/>
+      <c r="AQ312" s="11"/>
+      <c r="AR312" s="11"/>
+      <c r="AS312" s="36"/>
+      <c r="AT312" s="11"/>
+      <c r="AU312" s="11"/>
+      <c r="AV312" s="13"/>
+      <c r="AW312" s="14"/>
+      <c r="AX312" s="44"/>
+    </row>
+    <row r="313" spans="1:50" ht="38.25">
+      <c r="A313" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B313" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C313" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D313" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E313" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F313" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G313" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H313" s="15"/>
+      <c r="I313" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J313" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K313" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L313" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M313" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N313" s="36"/>
+      <c r="O313" s="34"/>
+      <c r="P313" s="12"/>
+      <c r="Q313" s="34"/>
+      <c r="R313" s="10"/>
+      <c r="S313" s="12"/>
+      <c r="T313" s="12"/>
+      <c r="U313" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V313" s="12"/>
+      <c r="W313" s="12"/>
+      <c r="X313" s="12"/>
+      <c r="Y313" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z313" s="12"/>
+      <c r="AA313" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB313" s="12"/>
+      <c r="AC313" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD313" s="12"/>
+      <c r="AE313" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF313" s="12"/>
+      <c r="AG313" s="12"/>
+      <c r="AH313" s="12"/>
+      <c r="AI313" s="12"/>
+      <c r="AJ313" s="10"/>
+      <c r="AK313" s="10"/>
+      <c r="AL313" s="10"/>
+      <c r="AM313" s="11"/>
+      <c r="AN313" s="11"/>
+      <c r="AO313" s="11"/>
+      <c r="AP313" s="11"/>
+      <c r="AQ313" s="11"/>
+      <c r="AR313" s="11"/>
+      <c r="AS313" s="36"/>
+      <c r="AT313" s="11"/>
+      <c r="AU313" s="11"/>
+      <c r="AV313" s="13"/>
+      <c r="AW313" s="14"/>
+      <c r="AX313" s="44"/>
+    </row>
+    <row r="314" spans="1:50" ht="38.25">
+      <c r="A314" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B314" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C314" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D314" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E314" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F314" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G314" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H314" s="15"/>
+      <c r="I314" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J314" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K314" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L314" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M314" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N314" s="36"/>
+      <c r="O314" s="34"/>
+      <c r="P314" s="12"/>
+      <c r="Q314" s="34"/>
+      <c r="R314" s="10"/>
+      <c r="S314" s="12"/>
+      <c r="T314" s="12"/>
+      <c r="U314" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V314" s="12"/>
+      <c r="W314" s="12"/>
+      <c r="X314" s="12"/>
+      <c r="Y314" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z314" s="12"/>
+      <c r="AA314" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB314" s="12"/>
+      <c r="AC314" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD314" s="12"/>
+      <c r="AE314" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF314" s="12"/>
+      <c r="AG314" s="12"/>
+      <c r="AH314" s="12"/>
+      <c r="AI314" s="12"/>
+      <c r="AJ314" s="10"/>
+      <c r="AK314" s="10"/>
+      <c r="AL314" s="10"/>
+      <c r="AM314" s="11"/>
+      <c r="AN314" s="11"/>
+      <c r="AO314" s="11"/>
+      <c r="AP314" s="11"/>
+      <c r="AQ314" s="11"/>
+      <c r="AR314" s="11"/>
+      <c r="AS314" s="36"/>
+      <c r="AT314" s="11"/>
+      <c r="AU314" s="11"/>
+      <c r="AV314" s="13"/>
+      <c r="AW314" s="14"/>
+      <c r="AX314" s="44"/>
+    </row>
+    <row r="315" spans="1:50" ht="38.25">
+      <c r="A315" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B315" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C315" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D315" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E315" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F315" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G315" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H315" s="15"/>
+      <c r="I315" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J315" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K315" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L315" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M315" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N315" s="36"/>
+      <c r="O315" s="34"/>
+      <c r="P315" s="12"/>
+      <c r="Q315" s="34"/>
+      <c r="R315" s="10"/>
+      <c r="S315" s="12"/>
+      <c r="T315" s="12"/>
+      <c r="U315" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V315" s="12"/>
+      <c r="W315" s="12"/>
+      <c r="X315" s="12"/>
+      <c r="Y315" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z315" s="12"/>
+      <c r="AA315" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB315" s="12"/>
+      <c r="AC315" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD315" s="12"/>
+      <c r="AE315" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF315" s="12"/>
+      <c r="AG315" s="12"/>
+      <c r="AH315" s="12"/>
+      <c r="AI315" s="12"/>
+      <c r="AJ315" s="10"/>
+      <c r="AK315" s="10"/>
+      <c r="AL315" s="10"/>
+      <c r="AM315" s="11"/>
+      <c r="AN315" s="11"/>
+      <c r="AO315" s="11"/>
+      <c r="AP315" s="11"/>
+      <c r="AQ315" s="11"/>
+      <c r="AR315" s="11"/>
+      <c r="AS315" s="36"/>
+      <c r="AT315" s="11"/>
+      <c r="AU315" s="11"/>
+      <c r="AV315" s="13"/>
+      <c r="AW315" s="14"/>
+      <c r="AX315" s="44"/>
+    </row>
+    <row r="316" spans="1:50" ht="38.25">
+      <c r="A316" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B316" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C316" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D316" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E316" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F316" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G316" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H316" s="15"/>
+      <c r="I316" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J316" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K316" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L316" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M316" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N316" s="36"/>
+      <c r="O316" s="34"/>
+      <c r="P316" s="12"/>
+      <c r="Q316" s="34"/>
+      <c r="R316" s="10"/>
+      <c r="S316" s="12"/>
+      <c r="T316" s="12"/>
+      <c r="U316" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V316" s="12"/>
+      <c r="W316" s="12"/>
+      <c r="X316" s="12"/>
+      <c r="Y316" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z316" s="12"/>
+      <c r="AA316" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB316" s="12"/>
+      <c r="AC316" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD316" s="12"/>
+      <c r="AE316" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF316" s="12"/>
+      <c r="AG316" s="12"/>
+      <c r="AH316" s="12"/>
+      <c r="AI316" s="12"/>
+      <c r="AJ316" s="10"/>
+      <c r="AK316" s="10"/>
+      <c r="AL316" s="10"/>
+      <c r="AM316" s="11"/>
+      <c r="AN316" s="11"/>
+      <c r="AO316" s="11"/>
+      <c r="AP316" s="11"/>
+      <c r="AQ316" s="11"/>
+      <c r="AR316" s="11"/>
+      <c r="AS316" s="36"/>
+      <c r="AT316" s="11"/>
+      <c r="AU316" s="11"/>
+      <c r="AV316" s="13"/>
+      <c r="AW316" s="14"/>
+      <c r="AX316" s="44"/>
+    </row>
+    <row r="317" spans="1:50" ht="38.25">
+      <c r="A317" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>Grand Est</v>
+      </c>
+      <c r="B317" s="38" t="str">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>Meuse</v>
+      </c>
+      <c r="C317" s="38">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>55</v>
+      </c>
+      <c r="D317" s="10" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E317" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F317" s="10" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G317" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v>Centre Commercial Auchan, 1 Rue de Longeville
+55000 - Savonnières-devant-Bar</v>
+      </c>
+      <c r="H317" s="15"/>
+      <c r="I317" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J317" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K317" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L317" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M317" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N317" s="36"/>
+      <c r="O317" s="34"/>
+      <c r="P317" s="12"/>
+      <c r="Q317" s="34"/>
+      <c r="R317" s="10"/>
+      <c r="S317" s="12"/>
+      <c r="T317" s="12"/>
+      <c r="U317" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V317" s="12"/>
+      <c r="W317" s="12"/>
+      <c r="X317" s="12"/>
+      <c r="Y317" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z317" s="12"/>
+      <c r="AA317" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB317" s="12"/>
+      <c r="AC317" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD317" s="12"/>
+      <c r="AE317" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF317" s="12"/>
+      <c r="AG317" s="12"/>
+      <c r="AH317" s="12"/>
+      <c r="AI317" s="12"/>
+      <c r="AJ317" s="10"/>
+      <c r="AK317" s="10"/>
+      <c r="AL317" s="10"/>
+      <c r="AM317" s="11"/>
+      <c r="AN317" s="11"/>
+      <c r="AO317" s="11"/>
+      <c r="AP317" s="11"/>
+      <c r="AQ317" s="11"/>
+      <c r="AR317" s="11"/>
+      <c r="AS317" s="36"/>
+      <c r="AT317" s="11"/>
+      <c r="AU317" s="11"/>
+      <c r="AV317" s="13"/>
+      <c r="AW317" s="14"/>
+      <c r="AX317" s="44"/>
+    </row>
+    <row r="318" spans="1:50">
+      <c r="A318" s="38" t="e">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B318" s="38" t="e">
+        <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C318" s="38" t="e">
+        <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D318" s="10"/>
+      <c r="E318" s="10"/>
+      <c r="F318" s="10"/>
+      <c r="G318" s="39" t="str">
+        <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
+        <v xml:space="preserve">
+ - </v>
+      </c>
+      <c r="H318" s="52" t="e" cm="1">
+        <f t="array" aca="1" ref="H318" ca="1">Extrait_hyperlien(#REF!)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I318" s="12"/>
+      <c r="J318" s="12"/>
+      <c r="K318" s="10"/>
+      <c r="L318" s="10"/>
+      <c r="M318" s="12"/>
+      <c r="N318" s="36"/>
+      <c r="O318" s="34"/>
+      <c r="P318" s="12"/>
+      <c r="Q318" s="34"/>
+      <c r="R318" s="10"/>
+      <c r="S318" s="12"/>
+      <c r="T318" s="12"/>
+      <c r="U318" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V318" s="12"/>
+      <c r="W318" s="12"/>
+      <c r="X318" s="12"/>
+      <c r="Y318" s="12">
+        <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
+        <v>0</v>
+      </c>
+      <c r="Z318" s="12"/>
+      <c r="AA318" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AB318" s="12"/>
+      <c r="AC318" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
+        <v>0</v>
+      </c>
+      <c r="AD318" s="12"/>
+      <c r="AE318" s="12">
+        <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
+        <v>0</v>
+      </c>
+      <c r="AF318" s="12"/>
+      <c r="AG318" s="12"/>
+      <c r="AH318" s="12"/>
+      <c r="AI318" s="12"/>
+      <c r="AJ318" s="10"/>
+      <c r="AK318" s="10"/>
+      <c r="AL318" s="10"/>
+      <c r="AM318" s="11"/>
+      <c r="AN318" s="11"/>
+      <c r="AO318" s="11"/>
+      <c r="AP318" s="11"/>
+      <c r="AQ318" s="11"/>
+      <c r="AR318" s="11"/>
+      <c r="AS318" s="36"/>
+      <c r="AT318" s="11"/>
+      <c r="AU318" s="11"/>
+      <c r="AV318" s="13"/>
+      <c r="AW318" s="14"/>
+      <c r="AX318" s="44"/>
+    </row>
+    <row r="326" spans="6:6">
+      <c r="F326" s="1" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="299" spans="6:6">
-      <c r="F299" s="1" t="s">
+    <row r="327" spans="6:6">
+      <c r="F327" s="1" t="s">
         <v>996</v>
       </c>
     </row>
@@ -51999,18 +57103,28 @@
     <hyperlink ref="H274" r:id="rId215" xr:uid="{9252F765-54A8-4365-B655-1CEB35A665E2}"/>
     <hyperlink ref="H276" r:id="rId216" xr:uid="{5E682CD6-A1E9-4669-AB24-37B56F75E248}"/>
     <hyperlink ref="H278" r:id="rId217" xr:uid="{9910A7B1-BC6F-44B9-A1B5-CDE437CE8C67}"/>
-    <hyperlink ref="H280" r:id="rId218" xr:uid="{C6CC8D32-EFB7-4427-BBEE-6847C3DB7F5A}"/>
-    <hyperlink ref="H282" r:id="rId219" xr:uid="{108D86F9-0E5F-49CA-9DAB-BF55C9E582F7}"/>
-    <hyperlink ref="H265" r:id="rId220" xr:uid="{3760C67A-B702-490D-B7BF-10D045F6DBCA}"/>
-    <hyperlink ref="H267" r:id="rId221" xr:uid="{74366FF4-BD79-4A4E-95B6-ACBE8796C1CD}"/>
-    <hyperlink ref="H269" r:id="rId222" xr:uid="{6387CEAD-2485-4AAD-A042-A804233A8F62}"/>
-    <hyperlink ref="H271" r:id="rId223" xr:uid="{95B81931-1443-4FA3-B65D-1E58CD1E85CD}"/>
-    <hyperlink ref="H273" r:id="rId224" xr:uid="{D3CFA2EC-4DC9-42C4-AA87-F31AA4632399}"/>
-    <hyperlink ref="H275" r:id="rId225" xr:uid="{1026C532-9542-4C3D-807F-C730F1C6A6E0}"/>
-    <hyperlink ref="H277" r:id="rId226" xr:uid="{575408C7-3CD2-4A9F-B53A-B6A883510B8A}"/>
-    <hyperlink ref="H279" r:id="rId227" xr:uid="{2E771A86-F027-4A08-960E-356EF9406F5D}"/>
-    <hyperlink ref="H281" r:id="rId228" xr:uid="{9A7BCA4F-0249-4D3F-BEE5-3C570496DF04}"/>
-    <hyperlink ref="H283" r:id="rId229" xr:uid="{4D14BC35-53D9-45D8-A88E-10076DA549C4}"/>
+    <hyperlink ref="H265" r:id="rId218" xr:uid="{3760C67A-B702-490D-B7BF-10D045F6DBCA}"/>
+    <hyperlink ref="H267" r:id="rId219" xr:uid="{74366FF4-BD79-4A4E-95B6-ACBE8796C1CD}"/>
+    <hyperlink ref="H269" r:id="rId220" xr:uid="{6387CEAD-2485-4AAD-A042-A804233A8F62}"/>
+    <hyperlink ref="H271" r:id="rId221" xr:uid="{95B81931-1443-4FA3-B65D-1E58CD1E85CD}"/>
+    <hyperlink ref="H273" r:id="rId222" xr:uid="{D3CFA2EC-4DC9-42C4-AA87-F31AA4632399}"/>
+    <hyperlink ref="H275" r:id="rId223" xr:uid="{1026C532-9542-4C3D-807F-C730F1C6A6E0}"/>
+    <hyperlink ref="H277" r:id="rId224" xr:uid="{575408C7-3CD2-4A9F-B53A-B6A883510B8A}"/>
+    <hyperlink ref="H279" r:id="rId225" xr:uid="{2F10B6EB-65C5-478E-804D-CED8FF9BBA43}"/>
+    <hyperlink ref="H280" r:id="rId226" xr:uid="{D990A4C0-561C-4371-B28E-A3B279B3B0C0}"/>
+    <hyperlink ref="H282" r:id="rId227" xr:uid="{C77B3F00-9E90-48BB-84E8-7863535B54FF}"/>
+    <hyperlink ref="H284" r:id="rId228" xr:uid="{34596A82-7C41-4201-B1A8-58B27D8893E8}"/>
+    <hyperlink ref="H286" r:id="rId229" xr:uid="{5F674D0E-15A4-4560-8CFA-3848B94A746A}"/>
+    <hyperlink ref="H288" r:id="rId230" xr:uid="{6701594D-30D8-430F-9B0B-A00148A37DD6}"/>
+    <hyperlink ref="H290" r:id="rId231" xr:uid="{B07E8029-DD04-4347-B16E-77ED782FEE6F}"/>
+    <hyperlink ref="H292" r:id="rId232" xr:uid="{2E39182C-3664-49F0-BAF5-CCB66A0EB117}"/>
+    <hyperlink ref="H281" r:id="rId233" xr:uid="{D8FAB089-5DA1-4163-B592-08A788ECDB61}"/>
+    <hyperlink ref="H283" r:id="rId234" xr:uid="{D0E96C71-0CA6-4430-B910-10DEC30CF5DC}"/>
+    <hyperlink ref="H285" r:id="rId235" xr:uid="{1F988F3C-B5EB-4DE2-B6CC-343B8651A0FF}"/>
+    <hyperlink ref="H287" r:id="rId236" xr:uid="{0ADBD325-5248-4D36-9BD2-13C41E83B9AA}"/>
+    <hyperlink ref="H289" r:id="rId237" xr:uid="{91E6E8D9-6A78-4A1A-918F-959C07CFE9DF}"/>
+    <hyperlink ref="H291" r:id="rId238" xr:uid="{6348A3C5-2EC8-492B-A5CD-4D326901BC6B}"/>
+    <hyperlink ref="H293" r:id="rId239" xr:uid="{6D66F3E1-8804-4654-B4C9-6068638177DC}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -52019,7 +57133,7 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId230"/>
+    <tablePart r:id="rId240"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9246ED5B-8A93-407F-BBB8-1B83171D6849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1EA996-4934-4FAA-BC16-26BB96847E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -53824,7 +53824,7 @@
       <c r="AW293" s="14"/>
       <c r="AX293" s="44"/>
     </row>
-    <row r="294" spans="1:50" ht="38.25">
+    <row r="294" spans="1:50" ht="25.5">
       <c r="A294" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -53975,7 +53975,7 @@
       <c r="AW294" s="14"/>
       <c r="AX294" s="44"/>
     </row>
-    <row r="295" spans="1:50" ht="38.25">
+    <row r="295" spans="1:50" ht="25.5">
       <c r="A295" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -54126,7 +54126,7 @@
       <c r="AW295" s="14"/>
       <c r="AX295" s="44"/>
     </row>
-    <row r="296" spans="1:50" ht="38.25">
+    <row r="296" spans="1:50" ht="25.5">
       <c r="A296" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -54277,7 +54277,7 @@
       <c r="AW296" s="14"/>
       <c r="AX296" s="44"/>
     </row>
-    <row r="297" spans="1:50" ht="38.25">
+    <row r="297" spans="1:50" ht="25.5">
       <c r="A297" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -54428,7 +54428,7 @@
       <c r="AW297" s="14"/>
       <c r="AX297" s="44"/>
     </row>
-    <row r="298" spans="1:50" ht="38.25">
+    <row r="298" spans="1:50" ht="25.5">
       <c r="A298" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -54579,7 +54579,7 @@
       <c r="AW298" s="14"/>
       <c r="AX298" s="44"/>
     </row>
-    <row r="299" spans="1:50" ht="38.25">
+    <row r="299" spans="1:50" ht="25.5">
       <c r="A299" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -54730,7 +54730,7 @@
       <c r="AW299" s="14"/>
       <c r="AX299" s="44"/>
     </row>
-    <row r="300" spans="1:50" ht="38.25">
+    <row r="300" spans="1:50" ht="25.5">
       <c r="A300" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Grand Est</v>
@@ -55032,7 +55032,7 @@
       <c r="AW301" s="14"/>
       <c r="AX301" s="44"/>
     </row>
-    <row r="302" spans="1:50" ht="25.5">
+    <row r="302" spans="1:50" ht="38.25">
       <c r="A302" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -55183,7 +55183,7 @@
       <c r="AW302" s="14"/>
       <c r="AX302" s="44"/>
     </row>
-    <row r="303" spans="1:50" ht="25.5">
+    <row r="303" spans="1:50" ht="38.25">
       <c r="A303" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -55334,7 +55334,7 @@
       <c r="AW303" s="14"/>
       <c r="AX303" s="44"/>
     </row>
-    <row r="304" spans="1:50" ht="25.5">
+    <row r="304" spans="1:50" ht="38.25">
       <c r="A304" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>
@@ -55485,7 +55485,7 @@
       <c r="AW304" s="14"/>
       <c r="AX304" s="44"/>
     </row>
-    <row r="305" spans="1:50" ht="25.5">
+    <row r="305" spans="1:50" ht="38.25">
       <c r="A305" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
         <v>Bourgogne-Franche-Comté</v>

--- a/Liste des lots.xlsx
+++ b/Liste des lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MYCLOUD-0C8EDF\Kettenmeyer\SMBG Conseil\Recherches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1EA996-4934-4FAA-BC16-26BB96847E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353912B3-0DEB-40B1-A731-7AC221D1572C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{169502BA-60CD-4080-B99D-F957FB39AAC1}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8845" uniqueCount="2030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8949" uniqueCount="2049">
   <si>
     <t>Contact</t>
   </si>
@@ -6037,9 +6037,6 @@
     <t>Savonnières-devant-Bar</t>
   </si>
   <si>
-    <t>Centre Commercial Auchan, 1 Rue de Longeville</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -6167,6 +6164,66 @@
   </si>
   <si>
     <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/89.1%20-%20Beaune/5%20Plan.jpg</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/zhoYzL66k21Lqwzr5</t>
+  </si>
+  <si>
+    <t>Calais</t>
+  </si>
+  <si>
+    <t>Auchan 1 Av. Roger Salengro</t>
+  </si>
+  <si>
+    <t>90.1</t>
+  </si>
+  <si>
+    <t>90.2</t>
+  </si>
+  <si>
+    <t>90.3</t>
+  </si>
+  <si>
+    <t>90.4</t>
+  </si>
+  <si>
+    <t>90.5</t>
+  </si>
+  <si>
+    <t>50.944042</t>
+  </si>
+  <si>
+    <t>1.807726</t>
+  </si>
+  <si>
+    <t>50.943924</t>
+  </si>
+  <si>
+    <t>1.807787</t>
+  </si>
+  <si>
+    <t>50.944126</t>
+  </si>
+  <si>
+    <t>1.808190</t>
+  </si>
+  <si>
+    <t>50.944170</t>
+  </si>
+  <si>
+    <t>1.808356</t>
+  </si>
+  <si>
+    <t>50.944255</t>
+  </si>
+  <si>
+    <t>1.809059</t>
+  </si>
+  <si>
+    <t>Hyper à 100 M€ HT de CA</t>
+  </si>
+  <si>
+    <t>https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/90.1%20-%20Calais/1.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/90.1%20-%20Calais/2.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/90.1%20-%20Calais/3.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/90.1%20-%20Calais/4.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/90.1%20-%20Calais/5.jpg; https://pub-843c46afc4cb41489909bce00c9b143d.r2.dev/90.1%20-%20Calais/6%20Plan%20du%20centre.jpg</t>
   </si>
 </sst>
 </file>
@@ -48963,7 +49020,7 @@
         <v>70240</v>
       </c>
       <c r="AF262" s="12" t="str">
-        <f t="shared" ref="AF262:AF305" si="15">"3 mois = "&amp;TEXT(ROUND(3/12*T262,0),"### ### ##0 €")</f>
+        <f t="shared" ref="AF262:AF310" si="15">"3 mois = "&amp;TEXT(ROUND(3/12*T262,0),"### ### ##0 €")</f>
         <v>3 mois = 12 000 €</v>
       </c>
       <c r="AG262" s="12" t="s">
@@ -53838,7 +53895,7 @@
         <v>55</v>
       </c>
       <c r="D294" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E294" s="26">
         <v>55000</v>
@@ -53952,16 +54009,16 @@
         <v>361</v>
       </c>
       <c r="AP294" s="11" t="s">
+        <v>2001</v>
+      </c>
+      <c r="AQ294" s="11" t="s">
         <v>2002</v>
       </c>
-      <c r="AQ294" s="11" t="s">
-        <v>2003</v>
-      </c>
       <c r="AR294" s="11" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="AS294" s="36" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AT294" s="11" t="s">
         <v>70</v>
@@ -53989,7 +54046,7 @@
         <v>55</v>
       </c>
       <c r="D295" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E295" s="26">
         <v>55000</v>
@@ -54103,16 +54160,16 @@
         <v>361</v>
       </c>
       <c r="AP295" s="11" t="s">
+        <v>1999</v>
+      </c>
+      <c r="AQ295" s="11" t="s">
         <v>2000</v>
       </c>
-      <c r="AQ295" s="11" t="s">
-        <v>2001</v>
-      </c>
       <c r="AR295" s="11" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AS295" s="36" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AT295" s="11" t="s">
         <v>70</v>
@@ -54140,7 +54197,7 @@
         <v>55</v>
       </c>
       <c r="D296" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E296" s="26">
         <v>55000</v>
@@ -54254,16 +54311,16 @@
         <v>361</v>
       </c>
       <c r="AP296" s="11" t="s">
+        <v>1997</v>
+      </c>
+      <c r="AQ296" s="11" t="s">
         <v>1998</v>
       </c>
-      <c r="AQ296" s="11" t="s">
-        <v>1999</v>
-      </c>
       <c r="AR296" s="11" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="AS296" s="36" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AT296" s="11" t="s">
         <v>70</v>
@@ -54291,7 +54348,7 @@
         <v>55</v>
       </c>
       <c r="D297" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E297" s="26">
         <v>55000</v>
@@ -54405,16 +54462,16 @@
         <v>361</v>
       </c>
       <c r="AP297" s="11" t="s">
+        <v>1995</v>
+      </c>
+      <c r="AQ297" s="11" t="s">
         <v>1996</v>
       </c>
-      <c r="AQ297" s="11" t="s">
-        <v>1997</v>
-      </c>
       <c r="AR297" s="11" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="AS297" s="36" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AT297" s="11" t="s">
         <v>70</v>
@@ -54442,7 +54499,7 @@
         <v>55</v>
       </c>
       <c r="D298" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E298" s="26">
         <v>55000</v>
@@ -54474,7 +54531,7 @@
         <v>98</v>
       </c>
       <c r="N298" s="36" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="O298" s="34">
         <v>100</v>
@@ -54556,16 +54613,16 @@
         <v>361</v>
       </c>
       <c r="AP298" s="11" t="s">
+        <v>2007</v>
+      </c>
+      <c r="AQ298" s="11" t="s">
         <v>2008</v>
       </c>
-      <c r="AQ298" s="11" t="s">
-        <v>2009</v>
-      </c>
       <c r="AR298" s="11" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="AS298" s="36" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AT298" s="11" t="s">
         <v>70</v>
@@ -54593,7 +54650,7 @@
         <v>55</v>
       </c>
       <c r="D299" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E299" s="26">
         <v>55000</v>
@@ -54707,16 +54764,16 @@
         <v>361</v>
       </c>
       <c r="AP299" s="11" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="AQ299" s="11" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="AR299" s="11" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="AS299" s="36" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AT299" s="11" t="s">
         <v>70</v>
@@ -54744,7 +54801,7 @@
         <v>55</v>
       </c>
       <c r="D300" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E300" s="26">
         <v>55000</v>
@@ -54858,16 +54915,16 @@
         <v>361</v>
       </c>
       <c r="AP300" s="11" t="s">
+        <v>2003</v>
+      </c>
+      <c r="AQ300" s="11" t="s">
         <v>2004</v>
       </c>
-      <c r="AQ300" s="11" t="s">
-        <v>2005</v>
-      </c>
       <c r="AR300" s="11" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="AS300" s="36" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AT300" s="11" t="s">
         <v>70</v>
@@ -54895,7 +54952,7 @@
         <v>55</v>
       </c>
       <c r="D301" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E301" s="26">
         <v>55000</v>
@@ -55009,16 +55066,16 @@
         <v>361</v>
       </c>
       <c r="AP301" s="11" t="s">
+        <v>2009</v>
+      </c>
+      <c r="AQ301" s="11" t="s">
         <v>2010</v>
       </c>
-      <c r="AQ301" s="11" t="s">
+      <c r="AR301" s="11" t="s">
+        <v>1994</v>
+      </c>
+      <c r="AS301" s="36" t="s">
         <v>2011</v>
-      </c>
-      <c r="AR301" s="11" t="s">
-        <v>1995</v>
-      </c>
-      <c r="AS301" s="36" t="s">
-        <v>2012</v>
       </c>
       <c r="AT301" s="11" t="s">
         <v>70</v>
@@ -55046,13 +55103,13 @@
         <v>21</v>
       </c>
       <c r="D302" s="10" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E302" s="26">
         <v>21200</v>
       </c>
       <c r="F302" s="10" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G302" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -55060,7 +55117,7 @@
 21200 - Beaune</v>
       </c>
       <c r="H302" s="15" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I302" s="12" t="s">
         <v>47</v>
@@ -55160,16 +55217,16 @@
         <v>361</v>
       </c>
       <c r="AP302" s="11" t="s">
+        <v>2019</v>
+      </c>
+      <c r="AQ302" s="11" t="s">
         <v>2020</v>
       </c>
-      <c r="AQ302" s="11" t="s">
-        <v>2021</v>
-      </c>
       <c r="AR302" s="11" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="AS302" s="36" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="AT302" s="11" t="s">
         <v>70</v>
@@ -55197,13 +55254,13 @@
         <v>21</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E303" s="26">
         <v>21200</v>
       </c>
       <c r="F303" s="10" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G303" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -55211,7 +55268,7 @@
 21200 - Beaune</v>
       </c>
       <c r="H303" s="15" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I303" s="12" t="s">
         <v>47</v>
@@ -55311,16 +55368,16 @@
         <v>361</v>
       </c>
       <c r="AP303" s="11" t="s">
+        <v>2021</v>
+      </c>
+      <c r="AQ303" s="11" t="s">
         <v>2022</v>
       </c>
-      <c r="AQ303" s="11" t="s">
-        <v>2023</v>
-      </c>
       <c r="AR303" s="11" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="AS303" s="36" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="AT303" s="11" t="s">
         <v>70</v>
@@ -55348,13 +55405,13 @@
         <v>21</v>
       </c>
       <c r="D304" s="10" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E304" s="26">
         <v>21200</v>
       </c>
       <c r="F304" s="10" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G304" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -55362,7 +55419,7 @@
 21200 - Beaune</v>
       </c>
       <c r="H304" s="15" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I304" s="12" t="s">
         <v>47</v>
@@ -55462,16 +55519,16 @@
         <v>361</v>
       </c>
       <c r="AP304" s="11" t="s">
+        <v>2023</v>
+      </c>
+      <c r="AQ304" s="11" t="s">
         <v>2024</v>
       </c>
-      <c r="AQ304" s="11" t="s">
-        <v>2025</v>
-      </c>
       <c r="AR304" s="11" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="AS304" s="36" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="AT304" s="11" t="s">
         <v>70</v>
@@ -55499,13 +55556,13 @@
         <v>21</v>
       </c>
       <c r="D305" s="10" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E305" s="26">
         <v>21200</v>
       </c>
       <c r="F305" s="10" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G305" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
@@ -55513,7 +55570,7 @@
 21200 - Beaune</v>
       </c>
       <c r="H305" s="15" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I305" s="12" t="s">
         <v>47</v>
@@ -55613,16 +55670,16 @@
         <v>361</v>
       </c>
       <c r="AP305" s="11" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AQ305" s="11" t="s">
         <v>2026</v>
       </c>
-      <c r="AQ305" s="11" t="s">
-        <v>2027</v>
-      </c>
       <c r="AR305" s="11" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="AS305" s="36" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="AT305" s="11" t="s">
         <v>70</v>
@@ -55636,35 +55693,35 @@
       <c r="AW305" s="14"/>
       <c r="AX305" s="44"/>
     </row>
-    <row r="306" spans="1:50" ht="38.25">
+    <row r="306" spans="1:50" ht="25.5">
       <c r="A306" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Hauts-de-France</v>
       </c>
       <c r="B306" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Meuse</v>
+        <v>Pas-de-Calais</v>
       </c>
       <c r="C306" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D306" s="10" t="s">
-        <v>1986</v>
+        <v>2031</v>
       </c>
       <c r="E306" s="26">
-        <v>55000</v>
+        <v>62100</v>
       </c>
       <c r="F306" s="10" t="s">
-        <v>1985</v>
+        <v>2030</v>
       </c>
       <c r="G306" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>Centre Commercial Auchan, 1 Rue de Longeville
-55000 - Savonnières-devant-Bar</v>
+        <v>Auchan 1 Av. Roger Salengro
+62100 - Calais</v>
       </c>
       <c r="H306" s="15" t="s">
-        <v>1984</v>
+        <v>2029</v>
       </c>
       <c r="I306" s="12" t="s">
         <v>47</v>
@@ -55681,30 +55738,56 @@
       <c r="M306" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="N306" s="36"/>
-      <c r="O306" s="34"/>
-      <c r="P306" s="12"/>
-      <c r="Q306" s="34"/>
-      <c r="R306" s="10"/>
-      <c r="S306" s="12"/>
-      <c r="T306" s="12"/>
+      <c r="N306" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="O306" s="34">
+        <v>202</v>
+      </c>
+      <c r="P306" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q306" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R306" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S306" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T306" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>60600</v>
+      </c>
       <c r="U306" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V306" s="12"/>
-      <c r="W306" s="12"/>
-      <c r="X306" s="12"/>
+        <v>5050</v>
+      </c>
+      <c r="V306" s="12">
+        <v>300</v>
+      </c>
+      <c r="W306" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X306" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>9090</v>
+      </c>
       <c r="Y306" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z306" s="12"/>
+        <v>757.5</v>
+      </c>
+      <c r="Z306" s="12">
+        <v>45</v>
+      </c>
       <c r="AA306" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB306" s="12"/>
+        <v>5454</v>
+      </c>
+      <c r="AB306" s="12">
+        <v>27</v>
+      </c>
       <c r="AC306" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -55712,56 +55795,87 @@
       <c r="AD306" s="12"/>
       <c r="AE306" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF306" s="12"/>
-      <c r="AG306" s="12"/>
-      <c r="AH306" s="12"/>
-      <c r="AI306" s="12"/>
+        <v>75144</v>
+      </c>
+      <c r="AF306" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 15 150 €</v>
+      </c>
+      <c r="AG306" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH306" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI306" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ306" s="10"/>
       <c r="AK306" s="10"/>
       <c r="AL306" s="10"/>
-      <c r="AM306" s="11"/>
-      <c r="AN306" s="11"/>
-      <c r="AO306" s="11"/>
-      <c r="AP306" s="11"/>
-      <c r="AQ306" s="11"/>
-      <c r="AR306" s="11"/>
-      <c r="AS306" s="36"/>
-      <c r="AT306" s="11"/>
-      <c r="AU306" s="11"/>
-      <c r="AV306" s="13"/>
+      <c r="AM306" s="11" t="s">
+        <v>2047</v>
+      </c>
+      <c r="AN306" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO306" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP306" s="11" t="s">
+        <v>2037</v>
+      </c>
+      <c r="AQ306" s="11" t="s">
+        <v>2038</v>
+      </c>
+      <c r="AR306" s="11" t="s">
+        <v>2032</v>
+      </c>
+      <c r="AS306" s="36" t="s">
+        <v>2048</v>
+      </c>
+      <c r="AT306" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU306" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AV306" s="13" t="s">
+        <v>1871</v>
+      </c>
       <c r="AW306" s="14"/>
       <c r="AX306" s="44"/>
     </row>
-    <row r="307" spans="1:50" ht="38.25">
+    <row r="307" spans="1:50" ht="25.5">
       <c r="A307" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,3)</f>
-        <v>Grand Est</v>
+        <v>Hauts-de-France</v>
       </c>
       <c r="B307" s="38" t="str">
         <f>VLOOKUP(Tableau1[[#This Row],[N° Département]],Feuil1!$C$6:$E$106,2)</f>
-        <v>Meuse</v>
+        <v>Pas-de-Calais</v>
       </c>
       <c r="C307" s="38">
         <f>LEFT(Tableau1[[#This Row],[Code Postal]],2)*1</f>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D307" s="10" t="s">
-        <v>1986</v>
+        <v>2031</v>
       </c>
       <c r="E307" s="26">
-        <v>55000</v>
+        <v>62101</v>
       </c>
       <c r="F307" s="10" t="s">
-        <v>1985</v>
+        <v>2030</v>
       </c>
       <c r="G307" s="39" t="str">
         <f>Tableau1[[#This Row],[Rue]]&amp;CHAR(10)&amp;Tableau1[[#This Row],[Code Postal]]&amp;" - "&amp;Tableau1[[#This Row],[Ville]]</f>
-        <v>Centre Commercial Auchan, 1 Rue de Longeville
-55000 - Savonnières-devant-Bar</v>
-      </c>
-      <c r="H307" s="15"/>
+        <v>Auchan 1 Av. Roger Salengro
+62101 - Calais</v>
+      </c>
+      <c r="H307" s="15" t="s">
+        <v>2029</v>
+      </c>
       <c r="I307" s="12" t="s">
         <v>47</v>
       </c>
@@ -55777,30 +55891,56 @@
       <c r="M307" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="N307" s="36"/>
-      <c r="O307" s="34"/>
-      <c r="P307" s="12"/>
-      <c r="Q307" s="34"/>
-      <c r="R307" s="10"/>
-      <c r="S307" s="12"/>
-      <c r="T307" s="12"/>
+      <c r="N307" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="O307" s="34">
+        <v>152</v>
+      </c>
+      <c r="P307" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q307" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R307" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="S307" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T307" s="12">
+        <f>Tableau1[[#This Row],[Loyer €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>45600</v>
+      </c>
       <c r="U307" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]/12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V307" s="12"/>
-      <c r="W307" s="12"/>
-      <c r="X307" s="12"/>
+        <v>3800</v>
+      </c>
+      <c r="V307" s="12">
+        <v>300</v>
+      </c>
+      <c r="W307" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="X307" s="6">
+        <f>Tableau1[[#This Row],[Charges €/m²]]*Tableau1[[#This Row],[Surface GLA]]</f>
+        <v>6840</v>
+      </c>
       <c r="Y307" s="12">
         <f>Tableau1[[#This Row],[Charges annuelles]]/12</f>
-        <v>0</v>
-      </c>
-      <c r="Z307" s="12"/>
+        <v>570</v>
+      </c>
+      <c r="Z307" s="12">
+        <v>45</v>
+      </c>
       <c r="AA307" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Taxe foncière €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
-        <v>0</v>
-      </c>
-      <c r="AB307" s="12"/>
+        <v>4104</v>
+      </c>
+      <c r="AB307" s="12">
+        <v>27</v>
+      </c>
       <c r="AC307" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Marketing €/m²]]*Tableau1[[#This Row],[Surface GLA]],)</f>
         <v>0</v>
@@ -55808,56 +55948,87 @@
       <c r="AD307" s="12"/>
       <c r="AE307" s="12">
         <f>IFERROR(Tableau1[[#This Row],[Loyer annuel]]+Tableau1[[#This Row],[Charges annuelles]]+Tableau1[[#This Row],[Taxe foncière]]+Tableau1[[#This Row],[Marketing]],"")</f>
-        <v>0</v>
-      </c>
-      <c r="AF307" s="12"/>
-      <c r="AG307" s="12"/>
-      <c r="AH307" s="12"/>
-      <c r="AI307" s="12"/>
+        <v>56544</v>
+      </c>
+      <c r="AF307" s="12" t="str">
+        <f t="shared" si="15"/>
+        <v>3 mois = 11 400 €</v>
+      </c>
+      <c r="AG307" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH307" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI307" s="12" t="s">
+        <v>357</v>
+      </c>
       <c r="AJ307" s="10"/>
       <c r="AK307" s="10"/>
       <c r="AL307" s="10"/>
-      <c r="AM307" s="11"/>
-      <c r="AN307" s="11"/>
-      <c r="AO307" s="11"/>
-      <c r="AP307" s="11"/>
-      <c r="AQ307" s="11"/>
-      <c r="AR307" s="11"/>
-      <c r="AS307" s="36"/>
-      <c r="AT307" s="11"/>
-      <c r="AU307" s="11"/>
-      <c r="AV307" s="13"/>
+      <c r="AM307" s="11" t="s">
+        <v>2047</v>
+      </c>
+      <c r="AN307" s="11" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO307" s="5" t="s">
+